--- a/delegated_authorization_research.xlsx
+++ b/delegated_authorization_research.xlsx
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="6" t="n">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="D11" s="7" t="n"/>
     </row>
@@ -906,7 +906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F132"/>
+  <dimension ref="A1:F140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, Jul 5 2026; authors: Adrian Farrel (Old Dog Consulting), Kehan Yao (China Mobile), Roland Schott (Deutsche Telekom), Nic Williams (Infoblox). At rev 03 the most mature DAWN document after the requirements draft; Farrel/Williams authorship signals serious WG momentum. IETF 126 (Bangkok, Jul 2026) has DAWN BoF time.</t>
+          <t>Revision -04, Jul 26 2026; authors: Adrian Farrel (Old Dog Consulting), Kehan Yao (China Mobile), Roland Schott (Deutsche Telekom), Nic Williams (Infoblox). Updated immediately ahead of IETF 126 DAWN BoF. At rev 04 the most mature DAWN document after the requirements draft; Farrel/Williams authorship signals serious WG momentum.</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Revision -04, Jun 12 2026; authors: Arashmid Akhavain, Hesham Moussa (Huawei Canada), Daniel King (Old Dog Consulting). King co-authorship ties this to draft-king-dawn-requirements already in corpus; together they are the two foundational DAWN framing documents.</t>
+          <t>Revision -05, Jul 19 2026; authors: Arashmid Akhavain, Hesham Moussa (Huawei Canada), Daniel King (Old Dog Consulting). King co-authorship ties this to draft-king-dawn-requirements already in corpus; together they are the two foundational DAWN framing documents. Updated ahead of IETF 126 DAWN BoF.</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>IESG-approved; currently in RFC Editor queue (status: Waiting on Authors — outstanding SECDIR 'Has issues' and OPSDIR 'Not ready' flags unresolved; no RFC number assigned yet as of Jul 2026). The canonical multi-domain delegation pattern referenced by most agent and zero-trust drafts.</t>
+          <t>Revision -17, Jul 22 2026 — rapid iteration signal heading into IETF 126. Previously IESG-approved and in RFC Editor queue; no RFC number assigned yet as of Jul 2026. The canonical multi-domain delegation pattern referenced by most agent and zero-trust drafts.</t>
         </is>
       </c>
     </row>
@@ -1435,27 +1435,27 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>draft-ietf-oauth-transaction-tokens — Transaction Tokens (Txn-Tokens)</t>
+          <t>draft-sharma-oauth-identity-propagation-context — Identity Propagation Context for Multi-Hop Delegation in OAuth 2.0</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>An IETF WG draft defining short-lived signed JWTs that propagate immutable user identity and authorization context through internal call chains within a trust domain.</t>
+          <t>Defines a signed JSON Identity Propagation Context (IPC) that carries per-hop cryptographic re-signing of delegation chain metadata at trust boundaries, complementing RFC 8693 Token Exchange by enabling identity propagation through multi-service chains without requiring a Security Token Service interaction at every hop.</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-transaction-tokens/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sharma-oauth-identity-propagation-context/</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth WG)</t>
+          <t>IETF (individual)</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Revision -09 published 6 Jul 2026 (was -08 Mar 2026); co-authored by Tulshibagwale (CAEP inventor), Fletcher, and Kasselman. -09 reorganized the Request Context section, changed JWT body claims from OPTIONAL to RECOMMENDED, and enhanced security considerations for invalidated access tokens. Still in WGLC; IESG submission milestone Dec 2026.</t>
+          <t>Revision -01, Jul 23 2026 (first filed -00 Jul 23 2026); author: Sharma. Cluster B (cross-domain identity chaining) companion to draft-ietf-oauth-identity-chaining. HTTP, gRPC, and Kafka protocol bindings specified — the first explicit event-streaming protocol binding in this family. The per-hop re-signing model is a structural alternative to token-based chains, trading token bloat for per-hop cryptographic commitment.</t>
         </is>
       </c>
     </row>
@@ -1465,17 +1465,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>draft-ietf-oauth-first-party-apps — OAuth 2.0 for First-Party Applications</t>
+          <t>draft-ietf-oauth-transaction-tokens — Transaction Tokens (Txn-Tokens)</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>An IETF WG draft defining an Authorization Challenge Endpoint that lets first-party native apps drive a browserless OAuth flow while still supporting step-up authentication via RFC 9470.</t>
+          <t>An IETF WG draft defining short-lived signed JWTs that propagate immutable user identity and authorization context through internal call chains within a trust domain.</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-first-party-apps/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-transaction-tokens/</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Revision -04, published 1 Jul 2026; explicitly excluded for third-party use because it requires high AS↔client trust.</t>
+          <t>Revision -09 published 6 Jul 2026 (was -08 Mar 2026); co-authored by Tulshibagwale (CAEP inventor), Fletcher, and Kasselman. -09 reorganized the Request Context section, changed JWT body claims from OPTIONAL to RECOMMENDED, and enhanced security considerations for invalidated access tokens. Still in WGLC; IESG submission milestone Dec 2026.</t>
         </is>
       </c>
     </row>
@@ -1495,17 +1495,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>draft-ietf-oauth-attestation-based-client-auth — OAuth 2.0 Attestation-Based Client Authentication</t>
+          <t>draft-ietf-oauth-first-party-apps — OAuth 2.0 for First-Party Applications</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>An IETF WG draft (Looker/Bastian/Bormann) introducing two JWTs — a Client Attestation issued by a Client Attester and a Client Attestation PoP signed by the client instance — that travel in HTTP headers to let traditionally-public clients authenticate to the AS without a shared secret.</t>
+          <t>An IETF WG draft defining an Authorization Challenge Endpoint that lets first-party native apps drive a browserless OAuth flow while still supporting step-up authentication via RFC 9470.</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-attestation-based-client-auth/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-first-party-apps/</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Revision -10, Jul 2026 (was -08 Mar 2026). -10 added a 'client_attestation_pop_methods_supported' metadata parameter, created a new 'OAuth Client Attestation Proof-of-Possession Methods' registry, clarified that PoP mechanisms from other specs are permitted, and refined DPoP combined-mode handling. Relates to the RATS Passport Model per RFC 9334; RATS attestation procedures themselves are deliberately out of scope. The 'client instance' framing pairs naturally with the McGuinness Client Instance Assertion and AI Agent Instance drafts.</t>
+          <t>Revision -04, published 1 Jul 2026; explicitly excluded for third-party use because it requires high AS↔client trust.</t>
         </is>
       </c>
     </row>
@@ -1525,17 +1525,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>draft-ietf-oauth-spiffe-client-auth — OAuth SPIFFE Client Authentication</t>
+          <t>draft-ietf-oauth-attestation-based-client-auth — OAuth 2.0 Attestation-Based Client Authentication</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>An IETF WG draft (Schwenkschuster/Kasselman/Rose-NIST/Thorgersen-IBM) profiling RFC 7521, RFC 7523, and OAuth attestation-based client auth so that SPIFFE-enabled workloads can authenticate to OAuth ASes using JWT-SVID, WIT-SVID, or X.509-SVID credentials instead of shared client secrets.</t>
+          <t>An IETF WG draft (Looker/Bastian/Bormann) introducing two JWTs — a Client Attestation issued by a Client Attester and a Client Attestation PoP signed by the client instance — that travel in HTTP headers to let traditionally-public clients authenticate to the AS without a shared secret.</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-spiffe-client-auth/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-attestation-based-client-auth/</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, March 2026 (re-slugged from draft-schwenkschuster-oauth-spiffe-client-auth after WG adoption); the protocol bridge between SPIFFE/WIMSE workload identity and the OAuth client-auth surface.</t>
+          <t>Revision -10, Jul 2026 (was -08 Mar 2026). -10 added a 'client_attestation_pop_methods_supported' metadata parameter, created a new 'OAuth Client Attestation Proof-of-Possession Methods' registry, clarified that PoP mechanisms from other specs are permitted, and refined DPoP combined-mode handling. Relates to the RATS Passport Model per RFC 9334; RATS attestation procedures themselves are deliberately out of scope. The 'client instance' framing pairs naturally with the McGuinness Client Instance Assertion and AI Agent Instance drafts.</t>
         </is>
       </c>
     </row>
@@ -1555,27 +1555,27 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>draft-kahrer-oauth-client-challenge-protocol — OAuth Client Challenge Protocol</t>
+          <t>draft-ietf-oauth-spiffe-client-auth — OAuth SPIFFE Client Authentication</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft from Judith Kahrer (Curity) defining a new 'insufficient_client_authorization' error code so the authorization server can dynamically challenge the client mid-flow for an additional assertion, verifiable presentation, or proof-of-possession material — enabling just-in-time and step-up client authorization.</t>
+          <t>An IETF WG draft (Schwenkschuster/Kasselman/Rose-NIST/Thorgersen-IBM) profiling RFC 7521, RFC 7523, and OAuth attestation-based client auth so that SPIFFE-enabled workloads can authenticate to OAuth ASes using JWT-SVID, WIT-SVID, or X.509-SVID credentials instead of shared client secrets.</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-kahrer-oauth-client-challenge-protocol/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-spiffe-client-auth/</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual)</t>
+          <t>IETF (OAuth WG)</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Revision -00 published 19 May 2026; deliberately distinct from first-party-apps (challenges the CLIENT, not the user) and works for both first- and third-party clients. Cites Mastercard Verifiable Intent as a use case, linking it directly to the mandate/RAR pattern OVID implements.</t>
+          <t>Revision -01, March 2026 (re-slugged from draft-schwenkschuster-oauth-spiffe-client-auth after WG adoption); the protocol bridge between SPIFFE/WIMSE workload identity and the OAuth client-auth surface.</t>
         </is>
       </c>
     </row>
@@ -1585,27 +1585,27 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>draft-ietf-oauth-browser-based-apps — OAuth 2.0 for Browser-Based Applications</t>
+          <t>draft-kahrer-oauth-client-challenge-protocol — OAuth Client Challenge Protocol</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>An IETF WG draft establishing the Backend-for-Frontend (BFF) and other architectural patterns as current best practice for SPAs given browser-resident token-storage limitations.</t>
+          <t>An IETF individual draft from Judith Kahrer (Curity) defining a new 'insufficient_client_authorization' error code so the authorization server can dynamically challenge the client mid-flow for an additional assertion, verifiable presentation, or proof-of-possession material — enabling just-in-time and step-up client authorization.</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-browser-based-apps/</t>
+          <t>https://datatracker.ietf.org/doc/draft-kahrer-oauth-client-challenge-protocol/</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth WG)</t>
+          <t>IETF (individual)</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Revision -26 (Dec 2025); critical for any delegated-authorization design touching SPAs because it codifies why pure-browser refresh tokens are deprecated.</t>
+          <t>Revision -00 published 19 May 2026; deliberately distinct from first-party-apps (challenges the CLIENT, not the user) and works for both first- and third-party clients. Cites Mastercard Verifiable Intent as a use case, linking it directly to the mandate/RAR pattern OVID implements.</t>
         </is>
       </c>
     </row>
@@ -1615,17 +1615,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>draft-ietf-oauth-security-topics-update — Updates to OAuth 2.0 Security BCP</t>
+          <t>draft-ietf-oauth-browser-based-apps — OAuth 2.0 for Browser-Based Applications</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>An IETF WG draft that extends RFC 9700 with new countermeasures, notably rules against audience-injection attacks where a client authenticates to multiple authorization servers.</t>
+          <t>An IETF WG draft establishing the Backend-for-Frontend (BFF) and other architectural patterns as current best practice for SPAs given browser-resident token-storage limitations.</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-security-topics-update/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-browser-based-apps/</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, March 2026; co-authored by University of Stuttgart (FAPI formal-analysis team) so the recommendations are formally grounded.</t>
+          <t>Revision -26 (Dec 2025); critical for any delegated-authorization design touching SPAs because it codifies why pure-browser refresh tokens are deprecated.</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>draft-ietf-oauth-client-id-metadata-document — OAuth Client ID Metadata Document</t>
+          <t>draft-ietf-oauth-security-topics-update — Updates to OAuth 2.0 Security BCP</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Defines a mechanism for OAuth clients to identify themselves to authorization servers via a URL as the client_id, pointing to a published JSON document containing client metadata — enabling dynamic client identification without prior registration.</t>
+          <t>An IETF WG draft that extends RFC 9700 with new countermeasures, notably rules against audience-injection attacks where a client authenticates to multiple authorization servers.</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-client-id-metadata-document/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-security-topics-update/</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, Jul 2026; OAuth WG-adopted. Directly relevant to AI agent deployments where agents may be registered via discoverable metadata documents rather than static registrations. Complements draft-king-dawn-requirements (discovery layer) by providing the OAuth-layer registration artifact.</t>
+          <t>Revision -01, March 2026; co-authored by University of Stuttgart (FAPI formal-analysis team) so the recommendations are formally grounded.</t>
         </is>
       </c>
     </row>
@@ -1675,17 +1675,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>draft-ietf-oauth-refresh-token-expiration — OAuth 2.0 Refresh Token and Authorization Expiration</t>
+          <t>draft-ietf-oauth-client-id-metadata-document — OAuth Client ID Metadata Document</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Extends OAuth 2.0 with new token endpoint response parameters specifying refresh token expiration and user authorization expiration, making expiry semantics explicit and interoperable across implementations.</t>
+          <t>Defines a mechanism for OAuth clients to identify themselves to authorization servers via a URL as the client_id, pointing to a published JSON document containing client metadata — enabling dynamic client identification without prior registration.</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-refresh-token-expiration/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-client-id-metadata-document/</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, Jul 2026; OAuth WG-adopted. Relevant to long-running agent sessions: explicit authorization expiration addresses the gap where refresh tokens survive past the user's intended authorization window — a known risk in agentic delegation scenarios.</t>
+          <t>Revision -02, Jul 2026; OAuth WG-adopted. Directly relevant to AI agent deployments where agents may be registered via discoverable metadata documents rather than static registrations. Complements draft-king-dawn-requirements (discovery layer) by providing the OAuth-layer registration artifact.</t>
         </is>
       </c>
     </row>
@@ -1705,27 +1705,27 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-actor-profile — OAuth Actor Profile for Delegation</t>
+          <t>draft-ietf-oauth-refresh-token-expiration — OAuth 2.0 Refresh Token and Authorization Expiration</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Karl McGuinness's individual draft profiling the RFC 8693 'act' claim with required iss, optional sub_profile entity classification, and uniform processing across JWT assertion grants, JWT access tokens, and Transaction Tokens.</t>
+          <t>Extends OAuth 2.0 with new token endpoint response parameters specifying refresh token expiration and user authorization expiration, making expiry semantics explicit and interoperable across implementations.</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/html/draft-mcguinness-oauth-actor-profile-00</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-refresh-token-expiration/</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual)</t>
+          <t>IETF (OAuth WG)</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Revision -00 published 30 April 2026; defines depth-1+ chain validation, cycle-aware construction, and bearer-to-PoP upgrade — the most complete actor-representation profile to date.</t>
+          <t>Revision -03, Jul 2026; OAuth WG-adopted. Relevant to long-running agent sessions: explicit authorization expiration addresses the gap where refresh tokens survive past the user's intended authorization window — a known risk in agentic delegation scenarios.</t>
         </is>
       </c>
     </row>
@@ -1735,17 +1735,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>draft-mw-oauth-actor-chain — Cryptographically Verifiable Actor Chains for OAuth 2.0 Token Exchange</t>
+          <t>draft-mcguinness-oauth-actor-profile — OAuth Actor Profile for Delegation</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft (Prasad/Krishnan/Lopez/Addepalli) defining six actor-chain profiles for RFC 8693 — Declared/Verified × Full/Subset/Actor-Only Disclosure — that preserve and cryptographically validate delegation-path continuity across successive token exchanges instead of relying on RFC 8693's informational-only nested act claims.</t>
+          <t>Karl McGuinness's individual draft profiling the RFC 8693 'act' claim with required iss, optional sub_profile entity classification, and uniform processing across JWT assertion grants, JWT access tokens, and Transaction Tokens.</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mw-oauth-actor-chain/</t>
+          <t>https://datatracker.ietf.org/doc/html/draft-mcguinness-oauth-actor-profile-00</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 30 Jun 2026 (was -00 May 2026; re-slugged from draft-mw-spice-actor-chain-05); a complementary alternative to the McGuinness Actor Profile that directly addresses RFC 8693's chain-splicing weakness by making the chain itself cryptographically verifiable rather than just informational.</t>
+          <t>Revision -00 published 30 April 2026; defines depth-1+ chain validation, cycle-aware construction, and bearer-to-PoP upgrade — the most complete actor-representation profile to date.</t>
         </is>
       </c>
     </row>
@@ -1765,17 +1765,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-client-instance-assertion — OAuth Client Instance Assertion</t>
+          <t>draft-mw-oauth-actor-chain — Cryptographically Verifiable Actor Chains for OAuth 2.0 Token Exchange</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Karl McGuinness's individual draft for representing a specific running instance of an OAuth client (rather than just the client registration) so authorization servers can bind grants to a concrete instance.</t>
+          <t>An IETF individual draft (Prasad/Krishnan/Lopez/Addepalli) defining six actor-chain profiles for RFC 8693 — Declared/Verified × Full/Subset/Actor-Only Disclosure — that preserve and cryptographically validate delegation-path continuity across successive token exchanges instead of relying on RFC 8693's informational-only nested act claims.</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-client-instance-assertion/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mw-oauth-actor-chain/</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Note: full draft text was not retrievable through automated fetch at time of writing — recommend reading directly. Companion to the Actor Profile draft and to attestation-based client auth.</t>
+          <t>Revision -01, 30 Jun 2026 (was -00 May 2026; re-slugged from draft-mw-spice-actor-chain-05); a complementary alternative to the McGuinness Actor Profile that directly addresses RFC 8693's chain-splicing weakness by making the chain itself cryptographically verifiable rather than just informational.</t>
         </is>
       </c>
     </row>
@@ -1795,17 +1795,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-resource-token-resp — OAuth 2.0 Resource Parameter in Access Token Response</t>
+          <t>draft-mcguinness-oauth-client-instance-assertion — OAuth Client Instance Assertion</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>A McGuinness/Skokan individual draft adding a 'resource' parameter to the OAuth access token response so clients can confirm which resource the issued token is valid for, mitigating resource mix-up attacks especially in deployments that use RFC 8707 Resource Indicators.</t>
+          <t>Karl McGuinness's individual draft for representing a specific running instance of an OAuth client (rather than just the client registration) so authorization servers can bind grants to a concrete instance.</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-resource-token-resp/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-client-instance-assertion/</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Revision -03 (March 2026). Filip Skokan added as co-author in -03. Complements RFC 8707 / RFC 9700 / RFC 9207 by adding issuance-time confirmation to the discovery-time mechanisms. Notable for the agent-authz corpus because dynamic resource discovery is a core agent pattern and resource-mix-up attacks are amplified when agents juggle many short-lived tokens.</t>
+          <t>Note: full draft text was not retrievable through automated fetch at time of writing — recommend reading directly. Companion to the Actor Profile draft and to attestation-based client auth.</t>
         </is>
       </c>
     </row>
@@ -1825,17 +1825,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-rfc9728bis — Update to OAuth 2.0 Protected Resource Metadata Resource Identifier Validation</t>
+          <t>draft-mcguinness-oauth-resource-token-resp — OAuth 2.0 Resource Parameter in Access Token Response</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>A McGuinness individual draft updating Section 3.3 of RFC 9728 (Protected Resource Metadata) so the resource value can be any URI sharing the same TLS origin as the requested URL whose path is a prefix of it — broadening the set of WWW-Authenticate response use cases without changing the rest of RFC 9728.</t>
+          <t>A McGuinness/Skokan individual draft adding a 'resource' parameter to the OAuth access token response so clients can confirm which resource the issued token is valid for, mitigating resource mix-up attacks especially in deployments that use RFC 8707 Resource Indicators.</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-rfc9728bis/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-resource-token-resp/</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Revision -01 (Feb 2026). A small targeted correction to the PRM validation rule. Notable as supporting infrastructure for the McGuinness Mission-Bound OAuth work — PRM is the substrate for Resource AS / Resource Server discovery of required RAR types under that profile.</t>
+          <t>Revision -03 (March 2026). Filip Skokan added as co-author in -03. Complements RFC 8707 / RFC 9700 / RFC 9207 by adding issuance-time confirmation to the discovery-time mechanisms. Notable for the agent-authz corpus because dynamic resource discovery is a core agent pattern and resource-mix-up attacks are amplified when agents juggle many short-lived tokens.</t>
         </is>
       </c>
     </row>
@@ -1855,17 +1855,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-token-xchg-target-svc-disco — OAuth 2.0 Token Exchange Target Service Discovery</t>
+          <t>draft-mcguinness-oauth-rfc9728bis — Update to OAuth 2.0 Protected Resource Metadata Resource Identifier Validation</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>A McGuinness/Parecki individual draft defining a discovery endpoint that, given a subject token, returns the set of available target services (audiences, resources, scopes) the holder can request via RFC 8693 Token Exchange — accepting any registered subject_token_type so it supports advanced flows including identity chaining and cross-domain delegation.</t>
+          <t>A McGuinness individual draft updating Section 3.3 of RFC 9728 (Protected Resource Metadata) so the resource value can be any URI sharing the same TLS origin as the requested URL whose path is a prefix of it — broadening the set of WWW-Authenticate response use cases without changing the rest of RFC 9728.</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcguinness-token-xchg-target-svc-disco/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-rfc9728bis/</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Revision -01 (Feb 2026), co-authored with Aaron Parecki (Okta). Fills a discovery gap that ID-JAG and the Transaction Token Chaining Profile both implicitly assume — clients today must know which audience to request, which doesn't compose with open-world agentic flows where the right downstream service is determined at runtime.</t>
+          <t>Revision -01 (Feb 2026). A small targeted correction to the PRM validation rule. Notable as supporting infrastructure for the McGuinness Mission-Bound OAuth work — PRM is the substrate for Resource AS / Resource Server discovery of required RAR types under that profile.</t>
         </is>
       </c>
     </row>
@@ -1885,17 +1885,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-actor-receipts — OAuth Actor Receipts for Delegation Provenance</t>
+          <t>draft-mcguinness-token-xchg-target-svc-disco — OAuth 2.0 Token Exchange Target Service Discovery</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>A McGuinness companion draft to the Actor Profile, aiming to provide per-hop signed receipts as the verifiable provenance layer that the Actor Profile (which keeps the 'act' chain informational) deliberately leaves out. Pulls over the provenance gap from the core profile so each principal in a delegation chain can produce independent cryptographic evidence.</t>
+          <t>A McGuinness/Parecki individual draft defining a discovery endpoint that, given a subject token, returns the set of available target services (audiences, resources, scopes) the holder can request via RFC 8693 Token Exchange — accepting any registered subject_token_type so it supports advanced flows including identity chaining and cross-domain delegation.</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-actor-receipts/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-token-xchg-target-svc-disco/</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 4 Jul 2026; now formally on IETF Datatracker (was GitHub-only pre-publication through Jun 2026). Recommended companion to the Actor Profile when a deployment needs Verified Full Disclosure mode (per the Mission-Bound OAuth Runtime Enforcement Profile's Actor Provenance Module). Completes a triad with actor-profile and actor-proofs — receipts provide provenance, proofs provide cryptographic per-hop accountability.</t>
+          <t>Revision -01 (Feb 2026), co-authored with Aaron Parecki (Okta). Fills a discovery gap that ID-JAG and the Transaction Token Chaining Profile both implicitly assume — clients today must know which audience to request, which doesn't compose with open-world agentic flows where the right downstream service is determined at runtime.</t>
         </is>
       </c>
     </row>
@@ -1915,17 +1915,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-actor-proofs — OAuth Actor-Signed Hop Proofs</t>
+          <t>draft-mcguinness-oauth-actor-receipts — OAuth Actor Receipts for Delegation Provenance</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Introduces the 'actor_proofs' claim — a signed per-hop proof chain where each actor signs its own participation and the target binding it authorized for that hop; proofs are hash-chained and validated using actor verification keys from trusted sources, with optional references to sibling actor receipts.</t>
+          <t>A McGuinness companion draft to the Actor Profile, aiming to provide per-hop signed receipts as the verifiable provenance layer that the Actor Profile (which keeps the 'act' chain informational) deliberately leaves out. Pulls over the provenance gap from the core profile so each principal in a delegation chain can produce independent cryptographic evidence.</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-actor-proofs/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-actor-receipts/</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 4 Jul 2026. Completes the actor triad with actor-profile (chain structure) and actor-receipts (provenance) — actor-proofs closes the cryptographic accountability gap. Filed the same day as ai-agent-instance, id-assertion-framework, and domain-authorized-issuer — McGuinness submitted four new I-Ds on Jul 4-6, bringing his total to 11 individual I-Ds on Datatracker.</t>
+          <t>Revision -00, 4 Jul 2026; now formally on IETF Datatracker (was GitHub-only pre-publication through Jun 2026). Recommended companion to the Actor Profile when a deployment needs Verified Full Disclosure mode (per the Mission-Bound OAuth Runtime Enforcement Profile's Actor Provenance Module). Completes a triad with actor-profile and actor-proofs — receipts provide provenance, proofs provide cryptographic per-hop accountability.</t>
         </is>
       </c>
     </row>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-insufficient-claims — OAuth 2.0 Insufficient Claims Challenge</t>
+          <t>draft-mcguinness-oauth-actor-proofs — OAuth Actor-Signed Hop Proofs</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>A McGuinness individual draft defining an insufficient_claims error code and required_claims parameter enabling authorization servers and protected resources to signal precisely which claims are missing from a presented credential. Allows resource servers to request enriched credentials carrying specific missing attributes rather than returning a generic 401.</t>
+          <t>Introduces the 'actor_proofs' claim — a signed per-hop proof chain where each actor signs its own participation and the target binding it authorized for that hop; proofs are hash-chained and validated using actor verification keys from trusted sources, with optional references to sibling actor receipts.</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-insufficient-claims/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-actor-proofs/</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 27 May 2026. Enables just-in-time claim negotiation in multi-agent delegation chains where the acting party must assemble claims from multiple sources. Natural companion to the Actor Profile and Client Instance Assertion — those drafts define the identity structure; this one provides the feedback loop when that structure is incomplete at the RS.</t>
+          <t>Revision -00, 4 Jul 2026. Completes the actor triad with actor-profile (chain structure) and actor-receipts (provenance) — actor-proofs closes the cryptographic accountability gap. Filed the same day as ai-agent-instance, id-assertion-framework, and domain-authorized-issuer — McGuinness submitted four new I-Ds on Jul 4-6, bringing his total to 11 individual I-Ds on Datatracker.</t>
         </is>
       </c>
     </row>
@@ -1975,17 +1975,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-ai-agent-instance — OAuth 2.0 AI Agent Instance Profile</t>
+          <t>draft-mcguinness-oauth-insufficient-claims — OAuth 2.0 Insufficient Claims Challenge</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Profiles OAuth 2.0 for deployments where a single client ID represents an agent platform running many concurrent agent instances; defines claims conveying attested agent instance identity and provenance from an agent attester to the AS, with delegation-chain semantics for sub-agents. Claims are carrier-independent, compatible with both Client Instance Assertions and Client Attestation JWT.</t>
+          <t>A McGuinness individual draft defining an insufficient_claims error code and required_claims parameter enabling authorization servers and protected resources to signal precisely which claims are missing from a presented credential. Allows resource servers to request enriched credentials carrying specific missing attributes rather than returning a generic 401.</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-ai-agent-instance/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-insufficient-claims/</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 4 Jul 2026. Fills the gap between a registered OAuth client ID (platform-level) and a running agent instance (runtime-level) — the level at which delegation chains, attestation, and revocation actually operate. Companion to draft-mcguinness-oauth-client-instance-assertion (general instance framing) and draft-mcguinness-oauth-actor-profile (chain representation).</t>
+          <t>Revision -00, 27 May 2026. Enables just-in-time claim negotiation in multi-agent delegation chains where the acting party must assemble claims from multiple sources. Natural companion to the Actor Profile and Client Instance Assertion — those drafts define the identity structure; this one provides the feedback loop when that structure is incomplete at the RS.</t>
         </is>
       </c>
     </row>
@@ -2005,17 +2005,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-id-assertion-framework — OAuth Identity Assertion Trust Framework</t>
+          <t>draft-mcguinness-oauth-ai-agent-instance — OAuth 2.0 AI Agent Instance Profile</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Addresses the gap where issuer authentication alone does not prove AS authority over subject namespaces; defines an Authority Delegation Model with independent trust-evaluation categories and an Identity Assertion Issuer Trust Policy (JSON document declaring required trust methods) that Resource ASes evaluate before accepting identity assertions.</t>
+          <t>Profiles OAuth 2.0 for deployments where a single client ID represents an agent platform running many concurrent agent instances; defines claims conveying attested agent instance identity and provenance from an agent attester to the AS, with delegation-chain semantics for sub-agents. Claims are carrier-independent, compatible with both Client Instance Assertions and Client Attestation JWT.</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-id-assertion-framework/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-ai-agent-instance/</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 4 Jul 2026. Directly motivates and companions draft-mcguinness-oauth-domain-authorized-issuer (below) which provides a DNS-based trust method. Addresses the 'who is allowed to assert identities in this namespace?' question that ID-JAG and the identity-chaining WG draft assume resolved but do not specify.</t>
+          <t>Revision -00, 4 Jul 2026. Fills the gap between a registered OAuth client ID (platform-level) and a running agent instance (runtime-level) — the level at which delegation chains, attestation, and revocation actually operate. Companion to draft-mcguinness-oauth-client-instance-assertion (general instance framing) and draft-mcguinness-oauth-actor-profile (chain representation).</t>
         </is>
       </c>
     </row>
@@ -2035,17 +2035,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-domain-authorized-issuer — OAuth Domain-Authorized Issuer Trust Method</t>
+          <t>draft-mcguinness-oauth-id-assertion-framework — OAuth Identity Assertion Trust Framework</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>DNS domain owners publish a policy (DNS TXT record at _oauth-issuer-policy.{domain} or HTTPS well-known fallback) listing the OAuth ASes authorized to assert identities in that namespace; Resource ASes use this to validate assertion issuers before accepting identity assertions or chaining tokens. Pattern echoes CAA/SPF/DKIM. Non-transitive — flat authorization, no delegation chains.</t>
+          <t>Addresses the gap where issuer authentication alone does not prove AS authority over subject namespaces; defines an Authority Delegation Model with independent trust-evaluation categories and an Identity Assertion Issuer Trust Policy (JSON document declaring required trust methods) that Resource ASes evaluate before accepting identity assertions.</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-domain-authorized-issuer/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-id-assertion-framework/</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 4 Jul 2026. Implements one trust method for draft-mcguinness-oauth-id-assertion-framework. DNS-based approach is lightweight and operationally familiar; the non-transitive design avoids the amplification risks of transitive trust chains. Closes the 'how do you know the AS is allowed to speak for this domain?' gap that cross-domain identity chaining has always assumed away.</t>
+          <t>Revision -00, 4 Jul 2026. Directly motivates and companions draft-mcguinness-oauth-domain-authorized-issuer (below) which provides a DNS-based trust method. Addresses the 'who is allowed to assert identities in this namespace?' question that ID-JAG and the identity-chaining WG draft assume resolved but do not specify.</t>
         </is>
       </c>
     </row>
@@ -2065,17 +2065,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-mission — Mission-Bound Authorization for OAuth 2.0</t>
+          <t>draft-mcguinness-oauth-domain-authorized-issuer — OAuth Domain-Authorized Issuer Trust Method</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Introduces 'Mission' — a durable, integrity-bound artifact stored at the AS representing an approved task; clients submit Mission Intent via PAR, ASes derive concrete permissions, and approvers grant consent via integrity anchors. Access tokens carry a 'mission' claim; issuance is gated by the Mission's lifecycle state, enabling revocation governance and audit trails for multi-step agent operations.</t>
+          <t>DNS domain owners publish a policy (DNS TXT record at _oauth-issuer-policy.{domain} or HTTPS well-known fallback) listing the OAuth ASes authorized to assert identities in that namespace; Resource ASes use this to validate assertion issuers before accepting identity assertions or chaining tokens. Pattern echoes CAA/SPF/DKIM. Non-transitive — flat authorization, no delegation chains.</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-mission/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-domain-authorized-issuer/</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 6 Jul 2026. This is the formal I-D target for the 'Mission-Bound OAuth MVP' blog post (May 2026, Industry tab) — the five-wire-addition protocol that makes the user-approved task a first-class OAuth object. Paired with the runtime enforcement profile (still not on Datatracker as of Jul 10). The Mission lifecycle (pending_approval → active → suspended → revoked → expired → completed → rejected) and the proposal_hash/consent_rendering_hash binding anchor what was approved versus what the user saw.</t>
+          <t>Revision -00, 4 Jul 2026. Implements one trust method for draft-mcguinness-oauth-id-assertion-framework. DNS-based approach is lightweight and operationally familiar; the non-transitive design avoids the amplification risks of transitive trust chains. Closes the 'how do you know the AS is allowed to speak for this domain?' gap that cross-domain identity chaining has always assumed away.</t>
         </is>
       </c>
     </row>
@@ -2095,17 +2095,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>draft-mishra-oauth-agent-grants — Delegated Agent Authorization Protocol (DAAP)</t>
+          <t>draft-mcguinness-oauth-mission — Mission-Bound Authorization for OAuth 2.0</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft addressing runtime agent identity for dynamically-spawned agents, multi-agent sub-delegation with depth-limiting, and cascade revocation of an entire delegation subtree when any ancestor is revoked.</t>
+          <t>Introduces 'Mission' — a durable, integrity-bound artifact stored at the AS representing an approved task; clients submit Mission Intent via PAR, ASes derive concrete permissions, and approvers grant consent via integrity anchors. Access tokens carry a 'mission' claim; issuance is gated by the Mission's lifecycle state, enabling revocation governance and audit trails for multi-step agent operations.</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mishra-oauth-agent-grants/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-mission/</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Revision -01 (March 2026); registers new JWT claims (agt, dev, grnt, scp, bdg) — a more aggressive alternative to RFC 8693 with budget-bounded grants. Overlaps with draft-niyikiza-oauth-attenuating-agent-tokens; OAuth WG will likely expect consolidation.</t>
+          <t>Revision -00, 6 Jul 2026. This is the formal I-D target for the 'Mission-Bound OAuth MVP' blog post (May 2026, Industry tab) — the five-wire-addition protocol that makes the user-approved task a first-class OAuth object. Paired with the runtime enforcement profile (still not on Datatracker as of Jul 10). The Mission lifecycle (pending_approval → active → suspended → revoked → expired → completed → rejected) and the proposal_hash/consent_rendering_hash binding anchor what was approved versus what the user saw.</t>
         </is>
       </c>
     </row>
@@ -2125,17 +2125,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>draft-kuehlewind-audit-architecture — Architecture for Auditing AI Agent Delegation and Interactions</t>
+          <t>draft-mishra-oauth-agent-grants — Delegated Agent Authorization Protocol (DAAP)</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft from Mirja Kühlewind (Ericsson, former IETF TSV-AD) and Henk Birkholz (Fraunhofer SIT, lead author of RFC 9334 RATS and SCITT architecture) defining four record types — Interaction, Action, Delegation, and Authorization Transition — and an Audit Context that propagates across OAuth + WIMSE + RATS + SCITT to make agent behaviour verifiably auditable end-to-end.</t>
+          <t>An IETF individual draft addressing runtime agent identity for dynamically-spawned agents, multi-agent sub-delegation with depth-limiting, and cascade revocation of an entire delegation subtree when any ancestor is revoked.</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-kuehlewind-audit-architecture/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mishra-oauth-agent-grants/</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Revision -00 published 18 May 2026; the cross-layer integration piece — explicitly composes the McGuinness Actor Profile, Transaction Tokens, identity-chaining, ID-JAG, WIMSE, RATS, and SCITT into a single auditable architecture with 11 proposed work items. The treats-Agent-as-untrusted threat model is what regulators (SOX, PSD2, EU AI Act) actually want.</t>
+          <t>Revision -01 (March 2026); registers new JWT claims (agt, dev, grnt, scp, bdg) — a more aggressive alternative to RFC 8693 with budget-bounded grants. Overlaps with draft-niyikiza-oauth-attenuating-agent-tokens; OAuth WG will likely expect consolidation.</t>
         </is>
       </c>
     </row>
@@ -2155,17 +2155,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>draft-birkholz-verifiable-agent-conversations — Verifiable Agent Conversation Records</t>
+          <t>draft-kuehlewind-audit-architecture — Architecture for Auditing AI Agent Delegation and Interactions</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft (Birkholz/Heldt/Steele) defining a CDDL data format — with both JSON and CBOR encodings — for tamper-evident, verifiably-signed records of agent conversations, agent reasoning traces, tool calls, and system events that support long-term evidentiary value across chains of custody.</t>
+          <t>An IETF individual draft from Mirja Kühlewind (Ericsson, former IETF TSV-AD) and Henk Birkholz (Fraunhofer SIT, lead author of RFC 9334 RATS and SCITT architecture) defining four record types — Interaction, Action, Delegation, and Authorization Transition — and an Audit Context that propagates across OAuth + WIMSE + RATS + SCITT to make agent behaviour verifiably auditable end-to-end.</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-birkholz-verifiable-agent-conversations/</t>
+          <t>https://datatracker.ietf.org/doc/draft-kuehlewind-audit-architecture/</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Revision -00 published 25 Feb 2026; presented at IETF 125 dispatch and hotrfc. The canonical Interaction-Record format for the Kuehlewind audit architecture. Motivating examples are concrete: agents acting beyond scope, CoT divergence, and 'sandbagging' during evaluations.</t>
+          <t>Revision -00 published 18 May 2026; the cross-layer integration piece — explicitly composes the McGuinness Actor Profile, Transaction Tokens, identity-chaining, ID-JAG, WIMSE, RATS, and SCITT into a single auditable architecture with 11 proposed work items. The treats-Agent-as-untrusted threat model is what regulators (SOX, PSD2, EU AI Act) actually want.</t>
         </is>
       </c>
     </row>
@@ -2185,17 +2185,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>draft-klrc-aiagent-auth — AI Agent Authentication and Authorization</t>
+          <t>draft-birkholz-verifiable-agent-conversations — Verifiable Agent Conversation Records</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft that does not invent new protocols but composes WIMSE/SPIFFE workload identity, OAuth 2.x, and OpenID SSF to authenticate and delegate authority to AI agents.</t>
+          <t>An IETF individual draft (Birkholz/Heldt/Steele) defining a CDDL data format — with both JSON and CBOR encodings — for tamper-evident, verifiably-signed records of agent conversations, agent reasoning traces, tool calls, and system events that support long-term evidentiary value across chains of custody.</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/html/draft-klrc-aiagent-auth-00</t>
+          <t>https://datatracker.ietf.org/doc/draft-birkholz-verifiable-agent-conversations/</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, March 2026; introduces 'Agent Identity Management System (AIMS)' and is the cleanest standards-based framing of agent-as-workload.</t>
+          <t>Revision -00 published 25 Feb 2026; presented at IETF 125 dispatch and hotrfc. The canonical Interaction-Record format for the Kuehlewind audit architecture. Motivating examples are concrete: agents acting beyond scope, CoT divergence, and 'sandbagging' during evaluations.</t>
         </is>
       </c>
     </row>
@@ -2215,17 +2215,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>draft-niyikiza-oauth-attenuating-agent-tokens — Attenuating Authorization Tokens for Agentic Delegation Chains</t>
+          <t>draft-klrc-aiagent-auth — AI Agent Authentication and Authorization</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft extending RFC 9396 Rich Authorization Requests with monotonic attenuation at each delegation hop, offline chain verification, and a typed constraint vocabulary for tool-level argument restrictions.</t>
+          <t>An IETF individual draft that does not invent new protocols but composes WIMSE/SPIFFE workload identity, OAuth 2.x, and OpenID SSF to authenticate and delegate authority to AI agents.</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-niyikiza-oauth-attenuating-agent-tokens/</t>
+          <t>https://datatracker.ietf.org/doc/html/draft-klrc-aiagent-auth-00</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, March 2026; arguably the strongest purely-OAuth-grounded delegation draft — offline verification is a key scalability property. Good path to OAuth WG adoption; overlaps with draft-mishra-oauth-agent-grants and will likely need to be consolidated with it.</t>
+          <t>Revision -00, March 2026; introduces 'Agent Identity Management System (AIMS)' and is the cleanest standards-based framing of agent-as-workload.</t>
         </is>
       </c>
     </row>
@@ -2245,17 +2245,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>draft-singla-agent-identity-protocol — AIP: Decentralized Identity and Delegation for AI Agents</t>
+          <t>draft-niyikiza-oauth-attenuating-agent-tokens — Attenuating Authorization Tokens for Agentic Delegation Chains</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft proposing a six-layer model (identity through reputation) for AI agents with W3C DID anchoring, a Delegation Depth counter, three Grant ceremony tiers (G1/G2/G3), DPoP proof-of-possession, and an MCP integration layer.</t>
+          <t>An IETF individual draft extending RFC 9396 Rich Authorization Requests with monotonic attenuation at each delegation hop, offline chain verification, and a typed constraint vocabulary for tool-level argument restrictions.</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-singla-agent-identity-protocol/</t>
+          <t>https://datatracker.ietf.org/doc/draft-niyikiza-oauth-attenuating-agent-tokens/</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 17 April 2026; the most comprehensive identity framework in the set. The W3C DID dependency will face IETF pushback, the 75+ page scope needs reduction, and the 'AIP' name collision with two other drafts (draft-prakash-aip, draft-aip-agent-identity-protocol) must be resolved.</t>
+          <t>Revision -00, March 2026; arguably the strongest purely-OAuth-grounded delegation draft — offline verification is a key scalability property. Good path to OAuth WG adoption; overlaps with draft-mishra-oauth-agent-grants and will likely need to be consolidated with it.</t>
         </is>
       </c>
     </row>
@@ -2275,17 +2275,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>draft-prakash-aip — AIP: Verifiable Delegation for AI Agent Systems</t>
+          <t>draft-singla-agent-identity-protocol — AIP: Decentralized Identity and Delegation for AI Agents</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft introducing Invocation-Bound Capability Tokens (IBCTs) in two modes — compact (JWT/Ed25519) for single-hop and chained (Biscuit + Datalog) for multi-hop — with bindings for MCP, A2A, and HTTP APIs.</t>
+          <t>An IETF individual draft proposing a six-layer model (identity through reputation) for AI agents with W3C DID anchoring, a Delegation Depth counter, three Grant ceremony tiers (G1/G2/G3), DPoP proof-of-possession, and an MCP integration layer.</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-prakash-aip/</t>
+          <t>https://datatracker.ietf.org/doc/draft-singla-agent-identity-protocol/</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 27 March 2026; technically strong — Biscuit + Datalog is well-suited to scope attenuation. The 'AIP' name collision with draft-singla-agent-identity-protocol and draft-aip-agent-identity-protocol is a blocking issue for WG adoption.</t>
+          <t>Revision -00, 17 April 2026; the most comprehensive identity framework in the set. The W3C DID dependency will face IETF pushback, the 75+ page scope needs reduction, and the 'AIP' name collision with two other drafts (draft-prakash-aip, draft-aip-agent-identity-protocol) must be resolved.</t>
         </is>
       </c>
     </row>
@@ -2305,17 +2305,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>draft-goswami-agentic-jwt — Secure Intent Protocol: JWT-Compatible Agentic Identity and Workflow Management</t>
+          <t>draft-prakash-aip — AIP: Verifiable Delegation for AI Agent Systems</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft defining an Agentic JWT extension to OAuth 2.0 with a Supervisor Agent role for sub-agent coordination, explicitly addressing the 'intent-execution separation' gap and adding workflow-step authorization.</t>
+          <t>An IETF individual draft introducing Invocation-Bound Capability Tokens (IBCTs) in two modes — compact (JWT/Ed25519) for single-hop and chained (Biscuit + Datalog) for multi-hop — with bindings for MCP, A2A, and HTTP APIs.</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-goswami-agentic-jwt/</t>
+          <t>https://datatracker.ietf.org/doc/draft-prakash-aip/</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, December 2025; the intent-execution-separation framing is insightful and distinguishing. The workflow-step authorization approach is novel but may face skepticism in the OAuth WG.</t>
+          <t>Revision -00, 27 March 2026; technically strong — Biscuit + Datalog is well-suited to scope attenuation. The 'AIP' name collision with draft-singla-agent-identity-protocol and draft-aip-agent-identity-protocol is a blocking issue for WG adoption.</t>
         </is>
       </c>
     </row>
@@ -2335,17 +2335,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>draft-ni-wimse-ai-agent-identity — WIMSE Applicability for AI Agents</t>
+          <t>draft-goswami-agentic-jwt — Secure Intent Protocol: JWT-Compatible Agentic Identity and Workflow Management</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft mapping the WIMSE workload-identity architecture to AI-agent use cases and establishing credential-management mechanisms for agentic AI within the WIMSE framework.</t>
+          <t>An IETF individual draft defining an Agentic JWT extension to OAuth 2.0 with a Supervisor Agent role for sub-agent coordination, explicitly addressing the 'intent-execution separation' gap and adding workflow-step authorization.</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ni-wimse-ai-agent-identity/</t>
+          <t>https://datatracker.ietf.org/doc/draft-goswami-agentic-jwt/</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, February 2026; an important bridge between the WIMSE WG and the AI agent space. If an AI-agent WG is ever chartered, this applicability statement is essential groundwork. Co-authored with Liu, who also leads the related security-requirements draft.</t>
+          <t>Revision -00, December 2025; the intent-execution-separation framing is insightful and distinguishing. The workflow-step authorization approach is novel but may face skepticism in the OAuth WG.</t>
         </is>
       </c>
     </row>
@@ -2365,17 +2365,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>draft-sharif-agent-identity-framework — Agent Identity Framework: Trust and Identity for Autonomous AI Agents</t>
+          <t>draft-ni-wimse-ai-agent-identity — WIMSE Applicability for AI Agents</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft proposing a five-layer model (identity, authorization, attestation, evidence, trust) for autonomous AI agents, with a gap analysis between current Internet standards and agent requirements.</t>
+          <t>An IETF individual draft mapping the WIMSE workload-identity architecture to AI-agent use cases and establishing credential-management mechanisms for agentic AI within the WIMSE framework.</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sharif-agent-identity-framework/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ni-wimse-ai-agent-identity/</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 6 April 2026; more gap-analysis than protocol spec. Useful as problem statement. Five-layer model is a reasonable decomposition but insufficient as a standalone contribution. Part of the Sharif cluster (with -agent-audit-trail, -attp, etc.).</t>
+          <t>Revision -02, February 2026; an important bridge between the WIMSE WG and the AI agent space. If an AI-agent WG is ever chartered, this applicability statement is essential groundwork. Co-authored with Liu, who also leads the related security-requirements draft.</t>
         </is>
       </c>
     </row>
@@ -2395,17 +2395,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>draft-aip-agent-identity-protocol — AIP: Agentic Authentication and Authorized Policy Enforcement</t>
+          <t>draft-sharif-agent-identity-framework — Agent Identity Framework: Trust and Identity for Autonomous AI Agents</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft defining an AIP Token signed per tool call (agent ID, tool, nonce, timestamp, signature), an AgentPolicy YAML format for per-tool argument constraints and DLP rules, and a Human-in-the-Loop proxy enforcement model.</t>
+          <t>An IETF individual draft proposing a five-layer model (identity, authorization, attestation, evidence, trust) for autonomous AI agents, with a gap analysis between current Internet standards and agent requirements.</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-aip-agent-identity-protocol/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sharif-agent-identity-framework/</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 16 March 2026; implementation-focused. YAML policy approach is pragmatic but not interoperable-by-design. HITL integration is a valuable safety feature. Third member of the 'AIP' name-collision triple — must be resolved before any can progress.</t>
+          <t>Revision -00, 6 April 2026; more gap-analysis than protocol spec. Useful as problem statement. Five-layer model is a reasonable decomposition but insufficient as a standalone contribution. Part of the Sharif cluster (with -agent-audit-trail, -attp, etc.).</t>
         </is>
       </c>
     </row>
@@ -2425,17 +2425,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>draft-liu-oauth-chain-delegation — Delegation Chain for OAuth 2.0</t>
+          <t>draft-sharif-x509-agent-identity-profile — X.509 Certificate Profile for Autonomous AI Agent Identity</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Introduces a delegation_chain JWT claim as a structured companion to RFC 8693's act claim; delegation_chain records the complete delegation history as an ordered array with per-hop authorization constraints and optional cryptographic confirmation from each delegating agent. Supports cross-domain delegation with integrated user consent interaction.</t>
+          <t>Defines a new X.509v3 AgentIdentity extension encoding graduated trust levels (0–4), operational capabilities, delegation constraints, and revocation endpoints for autonomous AI agent certificates. Maintains backward compatibility with standard X.509v3 parsers (extension marked non-critical) and integrates with SPIFFE workload identity frameworks.</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-liu-oauth-chain-delegation/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sharif-x509-agent-identity-profile/</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 6 Jun 2026; authors: Dapeng Liu, Judy Zhu, Suresh Krishnan (Ericsson), Aaron Parecki (Okta). Provides the structured delegation lineage that act alone cannot express; strong overlap with draft-mw-oauth-actor-chain and draft-niyikiza-oauth-attenuating-agent-tokens — OAuth WG will likely expect consolidation across these three.</t>
+          <t>Revision -02, Jul 26 2026 (first filed Jul 20 2026); part of the Sharif cluster. Fills the PKI-layer identity gap that draft-ietf-wimse-workload-creds left open — workload-creds specifies credential issuance, this profiles X.509v3 for the agent-specific certificate case. Graduated trust taxonomy (0–4) and kill-switch revocation are referenced by draft-sweeney-wimse-credential-delegation.</t>
         </is>
       </c>
     </row>
@@ -2455,17 +2455,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>draft-fletcher-transaction-token-chaining-profile — Transaction Token Authorization Grant Profile for OAuth Identity and Authorization Chaining</t>
+          <t>draft-aip-agent-identity-protocol — AIP: Agentic Authentication and Authorized Policy Enforcement</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Establishes a framework for using Transaction Tokens as subject credentials in OAuth 2.0 Token Exchange requests (RFC 8693), enabling services within one trust domain to obtain JWT authorization grants for accessing resources across domain boundaries without exposing internal token formats.</t>
+          <t>An IETF individual draft defining an AIP Token signed per tool call (agent ID, tool, nonce, timestamp, signature), an AgentPolicy YAML format for per-tool argument constraints and DLP rules, and a Human-in-the-Loop proxy enforcement model.</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-fletcher-transaction-token-chaining-profile/</t>
+          <t>https://datatracker.ietf.org/doc/draft-aip-agent-identity-protocol/</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 6 Jul 2026 (was -01 Jun 2026); authors: George Fletcher (Practical Identity LLC), Pieter Kasselman (Defakto Security), Sean O'Dell (CVS Health). Directly bridges draft-ietf-oauth-transaction-tokens and draft-ietf-oauth-identity-chaining (both in corpus), closing the 'how do TX Tokens actually cross domains' gap. Note: lead author is the corpus maintainer.</t>
+          <t>Revision -00, 16 March 2026; implementation-focused. YAML policy approach is pragmatic but not interoperable-by-design. HITL integration is a valuable safety feature. Third member of the 'AIP' name-collision triple — must be resolved before any can progress.</t>
         </is>
       </c>
     </row>
@@ -2485,17 +2485,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>draft-zhu-oauth-async-delegation — Sender-Constrained Delegation Handle for Asynchronous OAuth 2.0 Identity Chaining</t>
+          <t>draft-liu-oauth-chain-delegation — Delegation Chain for OAuth 2.0</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Introduces a Delegation Handle — a sender-constrained, audience-locked JWT issued by authorization servers — enabling acting clients to refresh chained access tokens without re-prompting an offline end user while maintaining strict policy bounds and identity chains.</t>
+          <t>Introduces a delegation_chain JWT claim as a structured companion to RFC 8693's act claim; delegation_chain records the complete delegation history as an ordered array with per-hop authorization constraints and optional cryptographic confirmation from each delegating agent. Supports cross-domain delegation with integrated user consent interaction.</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-zhu-oauth-async-delegation/</t>
+          <t>https://datatracker.ietf.org/doc/draft-liu-oauth-chain-delegation/</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 22 May 2026; authors: Larry Zhu, Sam Currie (Atlassian). Addresses a concrete gap in agent delegation: what happens when the delegating human is not present to re-authorize. Directly relevant to long-running agentic workflows using draft-ietf-oauth-identity-chaining.</t>
+          <t>Revision -00, 6 Jun 2026; authors: Dapeng Liu, Judy Zhu, Suresh Krishnan (Ericsson), Aaron Parecki (Okta). Provides the structured delegation lineage that act alone cannot express; strong overlap with draft-mw-oauth-actor-chain and draft-niyikiza-oauth-attenuating-agent-tokens — OAuth WG will likely expect consolidation across these three.</t>
         </is>
       </c>
     </row>
@@ -2515,17 +2515,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>draft-emerson-oauth-user-mediated-delivery — User-Mediated Credential Delivery for AI Agents</t>
+          <t>draft-fletcher-transaction-token-chaining-profile — Transaction Token Authorization Grant Profile for OAuth Identity and Authorization Chaining</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Proposes user-mediated credential delivery as a complementary OAuth authorization primitive for AI agent frameworks: rather than delivering credentials through automated channels controlled by the agent or its platform, places the authorization decision and credential delivery step in the user's hands even when the agent is autonomous.</t>
+          <t>Establishes a framework for using Transaction Tokens as subject credentials in OAuth 2.0 Token Exchange requests (RFC 8693), enabling services within one trust domain to obtain JWT authorization grants for accessing resources across domain boundaries without exposing internal token formats.</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-emerson-oauth-user-mediated-delivery/</t>
+          <t>https://datatracker.ietf.org/doc/draft-fletcher-transaction-token-chaining-profile/</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, Jul 2026; author: Matt Emerson. Novel complement to draft-zhu-oauth-async-delegation — where Zhu handles the case of offline delegation continuation, Emerson argues some credential deliveries should always route through the user even in automated pipelines. Addresses prompt-injection and social-engineering risks in agent credential chains.</t>
+          <t>Revision -02, 6 Jul 2026 (was -01 Jun 2026); authors: George Fletcher (Practical Identity LLC), Pieter Kasselman (Defakto Security), Sean O'Dell (CVS Health). Directly bridges draft-ietf-oauth-transaction-tokens and draft-ietf-oauth-identity-chaining (both in corpus), closing the 'how do TX Tokens actually cross domains' gap. Note: lead author is the corpus maintainer.</t>
         </is>
       </c>
     </row>
@@ -2545,17 +2545,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>draft-chen-oauth-agent-revocation — OAuth 2.0 Agent Authorization Explicit Revocation</t>
+          <t>draft-zhu-oauth-async-delegation — Sender-Constrained Delegation Handle for Asynchronous OAuth 2.0 Identity Chaining</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Extends RFC 7009 token revocation for agent-based scenarios: introduces batch revocation by agent ID, cascading revocation across delegation chains, conditional revocation options, and verifiable audit trails.</t>
+          <t>Introduces a Delegation Handle — a sender-constrained, audience-locked JWT issued by authorization servers — enabling acting clients to refresh chained access tokens without re-prompting an offline end user while maintaining strict policy bounds and identity chains.</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-chen-oauth-agent-revocation/</t>
+          <t>https://datatracker.ietf.org/doc/draft-zhu-oauth-async-delegation/</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 27 Apr 2026; authors: Meiling Chen, Li Su (China Mobile). Fills the lifecycle management gap — existing RFC 7009 revocation is single-token and client-centric, but agent delegation chains require cascade semantics. Natural companion to draft-ietf-oauth-transaction-tokens and draft-niyikiza-oauth-attenuating-agent-tokens.</t>
+          <t>Revision -04, Jul 23 2026 (first filed -00, 22 May 2026); authors: Larry Zhu, Sam Currie (Atlassian). Addresses a concrete gap in agent delegation: what happens when the delegating human is not present to re-authorize. Directly relevant to long-running agentic workflows using draft-ietf-oauth-identity-chaining. Active revision pace — -04 within ~2 months of initial filing.</t>
         </is>
       </c>
     </row>
@@ -2575,17 +2575,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>draft-jiang-oauth-intent-admission — Intent Admission Assertions for Agentic Systems</t>
+          <t>draft-emerson-oauth-user-mediated-delivery — User-Mediated Credential Delivery for AI Agents</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Defines a signed, verifiable Intent Admission Assertion (IAA) that an admission point creates after verifying agent identity, evaluating permissions against policy, and — when required — obtaining explicit user consent; the IAA is transmitted to the execution endpoint which re-validates before proceeding. Leverages OAuth and RFC 9396 Rich Authorization Requests.</t>
+          <t>Proposes user-mediated credential delivery as a complementary OAuth authorization primitive for AI agent frameworks: rather than delivering credentials through automated channels controlled by the agent or its platform, places the authorization decision and credential delivery step in the user's hands even when the agent is autonomous.</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-jiang-oauth-intent-admission/</t>
+          <t>https://datatracker.ietf.org/doc/draft-emerson-oauth-user-mediated-delivery/</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 23 Jun 2026; authors: Yuning Jiang, Lun Li, Yurong Song, Faye Liu (Huawei). The required_consent path maps directly to the HITL pattern central to the corpus. Companion to draft-jiang-intent-security (threat model) from the same Huawei group.</t>
+          <t>Revision -00, Jul 2026; author: Matt Emerson. Novel complement to draft-zhu-oauth-async-delegation — where Zhu handles the case of offline delegation continuation, Emerson argues some credential deliveries should always route through the user even in automated pipelines. Addresses prompt-injection and social-engineering risks in agent credential chains.</t>
         </is>
       </c>
     </row>
@@ -2605,17 +2605,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>draft-ni-oauth-batch-authorization-delegation — Batch Authorization Delegation</t>
+          <t>draft-gerber-oauth-deferred-token-response — Deferred Token Response</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Defines a mechanism for delegating a batch of fine-grained, actor-bound permissions in a single request across multiple collaborating actors; uses RFC 9396 RAR to carry per-actor authorization_details and RFC 8693 Token Exchange for sub-agent delegation, targeting multi-agent orchestration where a leader-agent receives batch permissions and delegates subsets to sub-agents.</t>
+          <t>Defines an OAuth 2.1 extension enabling authorization servers to defer access-token issuance by returning a deferral code the client polls or receives via callback; designed for use cases including fraud review, identity verification, autonomous agent approvals, and enterprise governance workflows where immediate token issuance is not appropriate.</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ni-oauth-batch-authorization-delegation/</t>
+          <t>https://datatracker.ietf.org/doc/draft-gerber-oauth-deferred-token-response/</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 3 Jul 2026; authors: Ni Yuan, Peter Chunchi Liu (Huawei). Addresses the round-trip overhead problem in large-scale multi-agent orchestration — individual delegation exchanges per sub-agent don't scale. Complements draft-song-oauth-ai-agent-collaborate-authz (same Huawei group, coordination focus) and draft-niyikiza-oauth-attenuating-agent-tokens (attenuation semantics). The RAR-based batch approach aligns well with the OAuth WG's RAR investment.</t>
+          <t>Revision -00, Jun 23 2026; presented at IETF 126 OAuth WG. May be the closest current Datatracker analog to the still-pending draft-mcguinness-oauth-deferred-code-processing — note in comments if the McGuinness variant eventually files, as the two may need consolidation. The async issuance pattern directly enables human-approval workflows in agentic pipelines without requiring the agent to remain connected while awaiting the authorization decision.</t>
         </is>
       </c>
     </row>
@@ -2635,17 +2635,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>draft-liu-oauth-a2a-profile — Agent-to-Agent (A2A) Profile for OAuth Transaction Tokens</t>
+          <t>draft-chen-oauth-agent-revocation — OAuth 2.0 Agent Authorization Explicit Revocation</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Defines a profile for using OAuth Transaction Tokens in distributed agent-to-agent communication scenarios; specifies mechanisms for embedding call-chain context within tokens to preserve agent identity, authorization information, and operational flow across agent workloads in trusted environments.</t>
+          <t>Extends RFC 7009 token revocation for agent-based scenarios: introduces batch revocation by agent ID, cascading revocation across delegation chains, conditional revocation options, and verifiable audit trails.</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-liu-oauth-a2a-profile/</t>
+          <t>https://datatracker.ietf.org/doc/draft-chen-oauth-agent-revocation/</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>EXPIRED. Revision -00, Oct 2025; authors: Peter Chunchi Liu, Ni Yuan (Huawei) — same author pair as draft-ni-oauth-batch-authorization-delegation. Directly profiles draft-ietf-oauth-transaction-tokens for A2A use; overlaps significantly with draft-araut-oauth-transaction-tokens-for-agents. Never revised; likely deferred rather than abandoned given both authors remain active in the corpus through Jul 2026.</t>
+          <t>Revision -00, 27 Apr 2026; authors: Meiling Chen, Li Su (China Mobile). Fills the lifecycle management gap — existing RFC 7009 revocation is single-token and client-centric, but agent delegation chains require cascade semantics. Natural companion to draft-ietf-oauth-transaction-tokens and draft-niyikiza-oauth-attenuating-agent-tokens.</t>
         </is>
       </c>
     </row>
@@ -2665,17 +2665,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>draft-song-oauth-ai-agent-collaborate-authz — OAuth 2.0 Extension for Multi-AI Agent Collaboration</t>
+          <t>draft-jiang-oauth-intent-admission — Intent Admission Assertions for Agentic Systems</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Extends OAuth 2.0 for coordinated multi-agent task groups: defines a collaborative authorization flow allowing a lead agent to obtain delegation tokens for sub-agents, with shared task context, coordinated scope attenuation, and cross-agent session binding.</t>
+          <t>Defines a signed, verifiable Intent Admission Assertion (IAA) that an admission point creates after verifying agent identity, evaluating permissions against policy, and — when required — obtaining explicit user consent; the IAA is transmitted to the execution endpoint which re-validates before proceeding. Leverages OAuth and RFC 9396 Rich Authorization Requests.</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-song-oauth-ai-agent-collaborate-authz/</t>
+          <t>https://datatracker.ietf.org/doc/draft-jiang-oauth-intent-admission/</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, Jun/Jul 2026; authors: Yurong Song (Huawei) and colleagues. Addresses the multi-agent coordination gap at the OAuth layer — complements draft-jiang-oauth-intent-admission from the same Huawei group. Distinct from single-hop delegation drafts in explicitly modeling lead-agent-to-sub-agent scope sharing.</t>
+          <t>Revision -00, 23 Jun 2026; authors: Yuning Jiang, Lun Li, Yurong Song, Faye Liu (Huawei). The required_consent path maps directly to the HITL pattern central to the corpus. Companion to draft-jiang-intent-security (threat model) from the same Huawei group.</t>
         </is>
       </c>
     </row>
@@ -2695,17 +2695,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>draft-kroehl-agentic-trust-aae — Agent Authorization Envelope (AAE)</t>
+          <t>draft-ni-oauth-batch-authorization-delegation — Batch Authorization Delegation</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Specifies the AAE, a structured authorization container with three mandatory components — MANDATE, CONSTRAINTS, and VALIDITY — providing a machine-evaluable, cryptographically verifiable authorization assertion using W3C DIDs and Verifiable Credentials.</t>
+          <t>Defines a mechanism for delegating a batch of fine-grained, actor-bound permissions in a single request across multiple collaborating actors; uses RFC 9396 RAR to carry per-actor authorization_details and RFC 8693 Token Exchange for sub-agent delegation, targeting multi-agent orchestration where a leader-agent receives batch permissions and delegates subsets to sub-agents.</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-kroehl-agentic-trust-aae/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ni-oauth-batch-authorization-delegation/</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 21 May 2026; author: Lars Kersten Kroehl (CryptoKRI GmbH). Occupies similar design space to draft-mcguinness-oauth-actor-profile but uses a DID/VC substrate rather than OAuth — provides a useful alternative approach for non-OAuth deployments.</t>
+          <t>Revision -00, 3 Jul 2026; authors: Ni Yuan, Peter Chunchi Liu (Huawei). Addresses the round-trip overhead problem in large-scale multi-agent orchestration — individual delegation exchanges per sub-agent don't scale. Complements draft-song-oauth-ai-agent-collaborate-authz (same Huawei group, coordination focus) and draft-niyikiza-oauth-attenuating-agent-tokens (attenuation semantics). The RAR-based batch approach aligns well with the OAuth WG's RAR investment.</t>
         </is>
       </c>
     </row>
@@ -2725,17 +2725,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>draft-pidlisnyi-aps — Agent Passport System (APS)</t>
+          <t>draft-liu-oauth-a2a-profile — Agent-to-Agent (A2A) Profile for OAuth Transaction Tokens</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Specifies Ed25519-based agent passports, scoped delegation chains with constraints across seven dimensions (a lattice model where delegation monotonically narrows capabilities), cascade revocation, a three-signature policy chain, signed receipts, and MCP bindings; includes reference implementations in TypeScript and Python.</t>
+          <t>Defines a profile for using OAuth Transaction Tokens in distributed agent-to-agent communication scenarios; specifies mechanisms for embedding call-chain context within tokens to preserve agent identity, authorization information, and operational flow across agent workloads in trusted environments.</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-pidlisnyi-aps/</t>
+          <t>https://datatracker.ietf.org/doc/draft-liu-oauth-a2a-profile/</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 14 May 2026; author: Tymofii Pidlisnyi (AEOESS). Among the most comprehensive standalone agent authz specs in the wave — the seven-dimension constraint lattice and MCP binding make it directly implementable against Model Context Protocol deployments alongside draft-serra-mcp-discovery-uri.</t>
+          <t>EXPIRED. Revision -00, Oct 2025; authors: Peter Chunchi Liu, Ni Yuan (Huawei) — same author pair as draft-ni-oauth-batch-authorization-delegation. Directly profiles draft-ietf-oauth-transaction-tokens for A2A use; overlaps significantly with draft-araut-oauth-transaction-tokens-for-agents. Never revised; likely deferred rather than abandoned given both authors remain active in the corpus through Jul 2026.</t>
         </is>
       </c>
     </row>
@@ -2755,17 +2755,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>draft-serra-mcp-discovery-uri — The mcp URI Scheme and MCP Server Discovery Mechanism</t>
+          <t>draft-song-oauth-ai-agent-collaborate-authz — OAuth 2.0 Extension for Multi-AI Agent Collaboration</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft defining an 'mcp://' URI scheme combined with /.well-known/mcp-server (RFC 8615) and a DNS TXT fallback for discovery of Model Context Protocol servers.</t>
+          <t>Extends OAuth 2.0 for coordinated multi-agent task groups: defines a collaborative authorization flow allowing a lead agent to obtain delegation tokens for sub-agents, with shared task context, coordinated scope attenuation, and cross-agent session binding.</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-serra-mcp-discovery-uri/</t>
+          <t>https://datatracker.ietf.org/doc/draft-song-oauth-ai-agent-collaborate-authz/</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Already at revision -04 (March 2026), suggesting active iteration; narrow scope, clean design, and the strongest IANA-registration candidate in the set. OAuth 2.1 for auth is deliberately out of scope.</t>
+          <t>Revision -02, Jun/Jul 2026; authors: Yurong Song (Huawei) and colleagues. Addresses the multi-agent coordination gap at the OAuth layer — complements draft-jiang-oauth-intent-admission from the same Huawei group. Distinct from single-hop delegation drafts in explicitly modeling lead-agent-to-sub-agent scope sharing.</t>
         </is>
       </c>
     </row>
@@ -2785,17 +2785,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>draft-sharif-attp — ATTP: Agent Trust Transport Protocol</t>
+          <t>draft-kroehl-agentic-trust-aae — Agent Authorization Envelope (AAE)</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft defining trust levels L0–L4 mapped to PSD2 Strong Customer Authentication requirements, with bindings for MCP (MCPS), REST, A2A, gRPC, and GraphQL; supersedes draft-sharif-agent-payment-trust.</t>
+          <t>Specifies the AAE, a structured authorization container with three mandatory components — MANDATE, CONSTRAINTS, and VALIDITY — providing a machine-evaluable, cryptographically verifiable authorization assertion using W3C DIDs and Verifiable Credentials.</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sharif-attp/</t>
+          <t>https://datatracker.ietf.org/doc/draft-kroehl-agentic-trust-aae/</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, April 2026; regulatory mapping appendices (PSD2, PCI DSS) are notable — one of the few drafts engaging financial regulation directly. Ambitious scope. Part of the Sharif cluster.</t>
+          <t>Revision -00, 21 May 2026; author: Lars Kersten Kroehl (CryptoKRI GmbH). Occupies similar design space to draft-mcguinness-oauth-actor-profile but uses a DID/VC substrate rather than OAuth — provides a useful alternative approach for non-OAuth deployments.</t>
         </is>
       </c>
     </row>
@@ -2815,17 +2815,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>draft-sharif-agent-transport-protocol — Agent Transport Protocol (ATP): Async Store-and-Forward for AI Agents</t>
+          <t>draft-pidlisnyi-aps — Agent Passport System (APS)</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft defining async store-and-forward messaging semantics with cryptographic identity per relay hop, trust scoring at ingress, capability negotiation, and interop with Google A2A, MCP, and FIPA ACL; transport-agnostic over TCP/TLS/QUIC.</t>
+          <t>Specifies Ed25519-based agent passports, scoped delegation chains with constraints across seven dimensions (a lattice model where delegation monotonically narrows capabilities), cascade revocation, a three-signature policy chain, signed receipts, and MCP bindings; includes reference implementations in TypeScript and Python.</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sharif-agent-transport-protocol/</t>
+          <t>https://datatracker.ietf.org/doc/draft-pidlisnyi-aps/</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 28 March 2026; addresses a real gap — most agent protocols assume synchronous availability, and store-and-forward is appropriate for long-running agentic tasks. Scope is broad and needs narrowing.</t>
+          <t>Revision -01, 14 May 2026; author: Tymofii Pidlisnyi (AEOESS). Among the most comprehensive standalone agent authz specs in the wave — the seven-dimension constraint lattice and MCP binding make it directly implementable against Model Context Protocol deployments alongside draft-serra-mcp-discovery-uri.</t>
         </is>
       </c>
     </row>
@@ -2845,17 +2845,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>draft-sharif-agent-audit-trail — Agent Audit Trail (AAT): Standard Logging Format for Autonomous AI Systems</t>
+          <t>draft-serra-mcp-discovery-uri — The mcp URI Scheme and MCP Server Discovery Mechanism</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft defining a JSON-based audit record with mandatory fields (agent identity, action classification, outcome tracking, trust level) using RFC 8785 JSON Canonicalization and RFC 9562 UUIDs.</t>
+          <t>An IETF individual draft defining an 'mcp://' URI scheme combined with /.well-known/mcp-server (RFC 8615) and a DNS TXT fallback for discovery of Model Context Protocol servers.</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sharif-agent-audit-trail/</t>
+          <t>https://datatracker.ietf.org/doc/draft-serra-mcp-discovery-uri/</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 29 March 2026; orthogonal to delegation but important for compliance — standardized audit-log format is a genuine gap. Complements identity frameworks well. A sibling/alternative to the Kuehlewind audit architecture which takes a far more ambitious cross-layer approach.</t>
+          <t>Already at revision -04 (March 2026), suggesting active iteration; narrow scope, clean design, and the strongest IANA-registration candidate in the set. OAuth 2.1 for auth is deliberately out of scope.</t>
         </is>
       </c>
     </row>
@@ -2875,17 +2875,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>draft-aiendpoint-ai-discovery — The AI Discovery Endpoint</t>
+          <t>draft-sharif-attp — ATTP: Agent Trust Transport Protocol</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft defining a /.well-known/ai URI suffix for programmatic service capability discovery by AI agents — letting agents discover what an endpoint supports without having to parse human-oriented documentation; requests IANA well-known URI registration.</t>
+          <t>An IETF individual draft defining trust levels L0–L4 mapped to PSD2 Strong Customer Authentication requirements, with bindings for MCP (MCPS), REST, A2A, gRPC, and GraphQL; supersedes draft-sharif-agent-payment-trust.</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-aiendpoint-ai-discovery/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sharif-attp/</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, March 2026; complementary to MCP discovery but broader (not MCP-specific). Needs differentiation from OpenAPI/service-description work to gain traction.</t>
+          <t>Revision -00, April 2026; regulatory mapping appendices (PSD2, PCI DSS) are notable — one of the few drafts engaging financial regulation directly. Ambitious scope. Part of the Sharif cluster.</t>
         </is>
       </c>
     </row>
@@ -2905,17 +2905,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>draft-hood-independent-agtp — Agent Transfer Protocol (AGTP)</t>
+          <t>draft-sharif-agent-transport-protocol — Agent Transport Protocol (ATP): Async Store-and-Forward for AI Agents</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft proposing a dedicated application-layer protocol for AI agent traffic on port 4480 (TCP/TLS and QUIC) with an agtp:// URI scheme, arguing that HTTP is insufficient because agent-generated intent-driven traffic is indistinguishable from human-initiated requests. Defines a Runtime Contract Negotiation Substrate (RCNS) with eighteen methods split into cognitive verbs (QUERY, DISCOVER, DESCRIBE, SUMMARIZE, PLAN, PROPOSE) and mechanics verbs (EXECUTE, DELEGATE, ESCALATE, CONFIRM, SUSPEND, NOTIFY), mandatory agent identity headers, and protocol-level authority scope declaration.</t>
+          <t>An IETF individual draft defining async store-and-forward messaging semantics with cryptographic identity per relay hop, trust scoring at ingress, capability negotiation, and interop with Google A2A, MCP, and FIPA ACL; transport-agnostic over TCP/TLS/QUIC.</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-hood-independent-agtp/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sharif-agent-transport-protocol/</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Revision -09, 28 Jun 2026 (was -08 May 2026); supersedes draft-hood-independent-atp. Companion specs in the same family: AGTP-API, AGTP-CERT, AGTP-MERCHANT, AGTP-IDENTIFIERS, AGTP-TRUST. Mandatory TLS 1.3+. Ambitious scope — a new transport layer rather than an HTTP profile. The cognitive/mechanics verb split is a distinctive design choice; contrasts with draft-sharif-agent-transport-protocol which layers async store-and-forward on top of existing transports rather than replacing them.</t>
+          <t>Revision -00, 28 March 2026; addresses a real gap — most agent protocols assume synchronous availability, and store-and-forward is appropriate for long-running agentic tasks. Scope is broad and needs narrowing.</t>
         </is>
       </c>
     </row>
@@ -2935,17 +2935,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>draft-hood-agtp-ard — ARD Binding for AGTP: Agentic Resource Discovery over the Agent Transfer Protocol</t>
+          <t>draft-sharif-agent-audit-trail — Agent Audit Trail (AAT): Standard Logging Format for Autonomous AI Systems</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Specifies how Agentic Resource Discovery (ARD) composes with AGTP, defining a catalog entry type for ARD manifests, aligning AGTP's identity model with ARD's trustManifest, and providing an AGTP-native binding for publishing ARD catalogs over AGTP substrate rather than HTTPS.</t>
+          <t>An IETF individual draft defining a JSON-based audit record with mandatory fields (agent identity, action classification, outcome tracking, trust level) using RFC 8785 JSON Canonicalization and RFC 9562 UUIDs.</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-hood-agtp-ard/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sharif-agent-audit-trail/</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 18 Jun 2026; author: Chris Hood (Nomotic). Extends the AGTP family (draft-hood-independent-agtp in corpus). The trustManifest identity alignment is the piece relevant to the agent identity thread; the rest is transport-layer plumbing for AGTP deployments.</t>
+          <t>Revision -00, 29 March 2026; orthogonal to delegation but important for compliance — standardized audit-log format is a genuine gap. Complements identity frameworks well. A sibling/alternative to the Kuehlewind audit architecture which takes a far more ambitious cross-layer approach.</t>
         </is>
       </c>
     </row>
@@ -2965,17 +2965,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>draft-hood-agtp-api — AGTP-API: Verbs, Paths, Endpoints, and Synthesis</t>
+          <t>draft-aiendpoint-ai-discovery — The AI Discovery Endpoint</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Establishes the full application-layer contract for AGTP agent–server interactions: approved method catalog, path grammar, endpoint primitives, semantic metadata blocks, server manifests, and runtime contract negotiation substrate. Defines how agents and servers negotiate capabilities and authority before action methods are invoked.</t>
+          <t>An IETF individual draft defining a /.well-known/ai URI suffix for programmatic service capability discovery by AI agents — letting agents discover what an endpoint supports without having to parse human-oriented documentation; requests IANA well-known URI registration.</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-hood-agtp-api/</t>
+          <t>https://datatracker.ietf.org/doc/draft-aiendpoint-ai-discovery/</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, May 26 2026; author: Chris Hood (Nomotic). The normative protocol contract layer for AGTP, complementing draft-hood-independent-agtp (transport) and draft-hood-agtp-trust (trust model). The AGTP family now spans 18 drafts; this is the API-layer anchor.</t>
+          <t>Revision -00, March 2026; complementary to MCP discovery but broader (not MCP-specific). Needs differentiation from OpenAPI/service-description work to gain traction.</t>
         </is>
       </c>
     </row>
@@ -2995,17 +2995,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>draft-hood-agtp-trust — AGTP Trust and Verification Specification</t>
+          <t>draft-hood-independent-agtp — Agent Transfer Protocol (AGTP)</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Defines AGTP's three-tier trust model (Tier 1 Verified / Tier 2 Org-Asserted / Tier 3 Experimental) and a continuous behavioral trust score (0.0–1.0) used by infrastructure components for runtime trust-aware routing. Standardizes the evidence substrate, score format, freshness requirements, and consumer-side evaluation rules without mandating the scoring algorithm.</t>
+          <t>An IETF individual draft proposing a dedicated application-layer protocol for AI agent traffic on port 4480 (TCP/TLS and QUIC) with an agtp:// URI scheme, arguing that HTTP is insufficient because agent-generated intent-driven traffic is indistinguishable from human-initiated requests. Defines a Runtime Contract Negotiation Substrate (RCNS) with eighteen methods split into cognitive verbs (QUERY, DISCOVER, DESCRIBE, SUMMARIZE, PLAN, PROPOSE) and mechanics verbs (EXECUTE, DELEGATE, ESCALATE, CONFIRM, SUSPEND, NOTIFY), mandatory agent identity headers, and protocol-level authority scope declaration.</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-hood-agtp-trust/</t>
+          <t>https://datatracker.ietf.org/doc/draft-hood-independent-agtp/</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, Jun 28 2026; author: Chris Hood (Nomotic). The continuous 0.0–1.0 trust score model contrasts with draft-sharif-attp's discrete L0–L4 levels and Larry Lewis's atp-core continuous scoring — three independent designs in the same design space.</t>
+          <t>Revision -09, 28 Jun 2026 (was -08 May 2026); supersedes draft-hood-independent-atp. Companion specs in the same family: AGTP-API, AGTP-CERT, AGTP-MERCHANT, AGTP-IDENTIFIERS, AGTP-TRUST. Mandatory TLS 1.3+. Ambitious scope — a new transport layer rather than an HTTP profile. The cognitive/mechanics verb split is a distinctive design choice; contrasts with draft-sharif-agent-transport-protocol which layers async store-and-forward on top of existing transports rather than replacing them.</t>
         </is>
       </c>
     </row>
@@ -3025,17 +3025,17 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>draft-hood-agtp-agent-cert — AGTP Agent Certificate Extension</t>
+          <t>draft-hood-agtp-ard — ARD Binding for AGTP: Agentic Resource Discovery over the Agent Transfer Protocol</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Specifies an X.509 v3 extension that cryptographically binds AGTP agent identity headers to TLS mutual authentication, enabling infrastructure components (Scope-Enforcement Points, load balancers, governance gateways) to verify agent identity at the network layer without application-layer access. Includes session-level revocation via AGTP NOTIFY broadcast.</t>
+          <t>Specifies how Agentic Resource Discovery (ARD) composes with AGTP, defining a catalog entry type for ARD manifests, aligning AGTP's identity model with ARD's trustManifest, and providing an AGTP-native binding for publishing ARD catalogs over AGTP substrate rather than HTTPS.</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-hood-agtp-agent-cert/</t>
+          <t>https://datatracker.ietf.org/doc/draft-hood-agtp-ard/</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, Jun 28 2026; author: Chris Hood (Nomotic). The PKI-binding companion to the AGTP identity model; positions AGTP agent identity within existing X.509 / TLS infrastructure. Relevant to WebBotAuth comparison — both use PKI for bot/agent identity but at different layers.</t>
+          <t>Revision -00, 18 Jun 2026; author: Chris Hood (Nomotic). Extends the AGTP family (draft-hood-independent-agtp in corpus). The trustManifest identity alignment is the piece relevant to the agent identity thread; the rest is transport-layer plumbing for AGTP deployments.</t>
         </is>
       </c>
     </row>
@@ -3055,17 +3055,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>draft-jernalczyk-intentweb-agent-manifest — IntentWeb AgentManifest</t>
+          <t>draft-hood-agtp-api — AGTP-API: Verbs, Paths, Endpoints, and Synthesis</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Defines a JSON document that websites publish to describe identity, trusted knowledge, agent-facing capabilities, structured bindings, risk levels, consent requirements, authentication expectations, audit rules, and policies — enabling AI agents to comprehend website functionality and safely perform actions without scraping or fragile UI automation.</t>
+          <t>Establishes the full application-layer contract for AGTP agent–server interactions: approved method catalog, path grammar, endpoint primitives, semantic metadata blocks, server manifests, and runtime contract negotiation substrate. Defines how agents and servers negotiate capabilities and authority before action methods are invoked.</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-jernalczyk-intentweb-agent-manifest/</t>
+          <t>https://datatracker.ietf.org/doc/draft-hood-agtp-api/</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 6 Jul 2026; author: Mariusz Jernalczyk (IntentWeb). Website-side complement to agent identity drafts; sits in the Discovery &amp; Transport cluster alongside draft-hood-agtp-ard and the DAWN/.well-known discovery thread. Single author, no-affiliation submission — early stage but addresses a real discovery gap.</t>
+          <t>Revision -01, May 26 2026; author: Chris Hood (Nomotic). The normative protocol contract layer for AGTP, complementing draft-hood-independent-agtp (transport) and draft-hood-agtp-trust (trust model). The AGTP family now spans 18 drafts; this is the API-layer anchor.</t>
         </is>
       </c>
     </row>
@@ -3085,17 +3085,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>draft-bu-agentproto-security-principal-binding — Security Principal and Verifier Binding for Agent Communication Protocols</t>
+          <t>draft-hood-agtp-trust — AGTP Trust and Verification Specification</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Addresses how agent communication protocols carry claims about user authority, agent instance identity, tool or external-resource identity, delegation state, session continuity, and action evidence; each claim has a different verifier, freshness requirement, failure mode, and security consequence, requiring explicit binding rather than collapsing all claims into a single assertion.</t>
+          <t>Defines AGTP's three-tier trust model (Tier 1 Verified / Tier 2 Org-Asserted / Tier 3 Experimental) and a continuous behavioral trust score (0.0–1.0) used by infrastructure components for runtime trust-aware routing. Standardizes the evidence substrate, score format, freshness requirements, and consumer-side evaluation rules without mandating the scoring algorithm.</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-bu-agentproto-security-principal-binding/</t>
+          <t>https://datatracker.ietf.org/doc/draft-hood-agtp-trust/</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, Jul 2026. Fills a gap in the AGTP family (draft-hood-independent-agtp in corpus) and is relevant to any agent communication protocol carrying mixed-provenance claims. The verifier-separation model is the missing security architecture layer between protocol transport and authorization enforcement.</t>
+          <t>Revision -02, Jun 28 2026; author: Chris Hood (Nomotic). The continuous 0.0–1.0 trust score model contrasts with draft-sharif-attp's discrete L0–L4 levels and Larry Lewis's atp-core continuous scoring — three independent designs in the same design space.</t>
         </is>
       </c>
     </row>
@@ -3115,17 +3115,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>draft-fane-opena2a-aap — OpenA2A Agent Authorization Protocol (AAP)</t>
+          <t>draft-hood-agtp-agent-cert — AGTP Agent Certificate Extension</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Establishes authorization mechanisms for AI agent systems through cryptographic identity assertions and scoped capability grants. Introduces a broker layer that separates credentials from the agent's reasoning context, specifically to prevent prompt injection attacks from leaking authorization state while enabling cross-agent delegation.</t>
+          <t>Specifies an X.509 v3 extension that cryptographically binds AGTP agent identity headers to TLS mutual authentication, enabling infrastructure components (Scope-Enforcement Points, load balancers, governance gateways) to verify agent identity at the network layer without application-layer access. Includes session-level revocation via AGTP NOTIFY broadcast.</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-fane-opena2a-aap/</t>
+          <t>https://datatracker.ietf.org/doc/draft-hood-agtp-agent-cert/</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, Jul 6 2026; author: Abdel Fane (OpenA2A). Filed Jul 6 alongside a companion draft-fane-opena2a-aip which adds a fourth 'AIP' name collision to the existing Singla/Prakash/aip-agent-identity-protocol triple. The AAP authorization layer is the piece most relevant to OAuth boundary analysis.</t>
+          <t>Revision -03, Jun 28 2026; author: Chris Hood (Nomotic). The PKI-binding companion to the AGTP identity model; positions AGTP agent identity within existing X.509 / TLS infrastructure. Relevant to WebBotAuth comparison — both use PKI for bot/agent identity but at different layers.</t>
         </is>
       </c>
     </row>
@@ -3145,17 +3145,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>draft-ni-a2a-ai-agent-security-requirements — Security Requirements for AI Agents</t>
+          <t>draft-jernalczyk-intentweb-agent-manifest — IntentWeb AgentManifest</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft enumerating security requirements for AI agents, covering identity, authorization chaining across domains, and integration points with WIMSE, OAuth identity chaining, and the A2A OAuth profile.</t>
+          <t>Defines a JSON document that websites publish to describe identity, trusted knowledge, agent-facing capabilities, structured bindings, risk levels, consent requirements, authentication expectations, audit rules, and policies — enabling AI agents to comprehend website functionality and safely perform actions without scraping or fragile UI automation.</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ni-a2a-ai-agent-security-requirements/</t>
+          <t>https://datatracker.ietf.org/doc/draft-jernalczyk-intentweb-agent-manifest/</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, February 2026; essential scaffolding for an eventual AI-agent WG. Well-connected to existing IETF work and authored by Ni and Liu, who also lead the WIMSE AI-agent identity draft.</t>
+          <t>Revision -00, 6 Jul 2026; author: Mariusz Jernalczyk (IntentWeb). Website-side complement to agent identity drafts; sits in the Discovery &amp; Transport cluster alongside draft-hood-agtp-ard and the DAWN/.well-known discovery thread. Single author, no-affiliation submission — early stage but addresses a real discovery gap.</t>
         </is>
       </c>
     </row>
@@ -3175,17 +3175,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>draft-rosenberg-aiproto-framework — Framework, Use Cases and Requirements for AI Agent Protocols</t>
+          <t>draft-bu-agentproto-security-principal-binding — Security Principal and Verifier Binding for Agent Communication Protocols</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft providing a comprehensive AI-agent communications framework that covers user↔agent, agent↔API, and agent↔agent interactions; surveys MCP, A2A, and Agntcy; and sets the stage for IETF standards activity.</t>
+          <t>Addresses how agent communication protocols carry claims about user authority, agent instance identity, tool or external-resource identity, delegation state, session continuity, and action evidence; each claim has a different verifier, freshness requirement, failure mode, and security consequence, requiring explicit binding rather than collapsing all claims into a single assertion.</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-rosenberg-aiproto-framework/</t>
+          <t>https://datatracker.ietf.org/doc/draft-bu-agentproto-security-principal-binding/</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, October 2025; Rosenberg (Five9) and Jennings (Cisco) are credible long-time IETF contributors. Important landscape document but likely expired (April 2026); watch for a -01 refresh post-IETF 123.</t>
+          <t>Revision -02, Jul 2026. Fills a gap in the AGTP family (draft-hood-independent-agtp in corpus) and is relevant to any agent communication protocol carrying mixed-provenance claims. The verifier-separation model is the missing security architecture layer between protocol transport and authorization enforcement.</t>
         </is>
       </c>
     </row>
@@ -3205,17 +3205,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>draft-rosenberg-aiproto-cheq — CHEQ: A Protocol for Confirmation of AI Agent Decisions (HITL)</t>
+          <t>draft-fane-opena2a-aap — OpenA2A Agent Authorization Protocol (AAP)</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft defining an out-of-band Human-in-the-Loop confirmation protocol for agent tool calls, eliminating LLM-hallucination risk for consequential actions and enabling sensitive operations (e.g., banking) without exposing data to the agent.</t>
+          <t>Establishes authorization mechanisms for AI agent systems through cryptographic identity assertions and scoped capability grants. Introduces a broker layer that separates credentials from the agent's reasoning context, specifically to prevent prompt injection attacks from leaking authorization state while enabling cross-agent delegation.</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-rosenberg-aiproto-cheq/</t>
+          <t>https://datatracker.ietf.org/doc/draft-fane-opena2a-aap/</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, October 2025; out-of-band HITL confirmation model is valuable and complements delegation frameworks. Likely expired (April 2026); worth tracking for a -01 refresh.</t>
+          <t>Revision -01, Jul 22 2026 (first filed -00 Jul 6 2026); author: Abdel Fane (OpenA2A). Companion draft-fane-opena2a-aip also updated to -01 Jul 22, adding a fourth 'AIP' name collision to the existing Singla/Prakash/aip-agent-identity-protocol triple. The AAP authorization layer is the piece most relevant to OAuth boundary analysis.</t>
         </is>
       </c>
     </row>
@@ -3235,27 +3235,27 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>draft-sharif-agent-payment-trust — Trust Scoring and Identity Verification for AI Agent Payment Transactions (SUPERSEDED)</t>
+          <t>draft-ni-a2a-ai-agent-security-requirements — Security Requirements for AI Agents</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft introducing an Agent Passport — a cryptographic delegation certificate intended to serve as the PSD2 'something you have' factor — and a trust-scoring model for payment transactions mapped to PCI DSS v4.0.1.</t>
+          <t>An IETF individual draft enumerating security requirements for AI agents, covering identity, authorization chaining across domains, and integration points with WIMSE, OAuth identity chaining, and the A2A OAuth profile.</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sharif-agent-payment-trust/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ni-a2a-ai-agent-security-requirements/</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual, superseded)</t>
+          <t>IETF (individual)</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>SUPERSEDED by draft-sharif-attp-00 (April 2026). Retained for historical context — the Agent Passport concept is interesting but needs formal grounding; the ATTP successor generalizes it across transport bindings.</t>
+          <t>Revision -01, February 2026; essential scaffolding for an eventual AI-agent WG. Well-connected to existing IETF work and authored by Ni and Liu, who also lead the WIMSE AI-agent identity draft.</t>
         </is>
       </c>
     </row>
@@ -3265,17 +3265,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>draft-stephan-ai-agent-6g — AI Agent Protocols for 6G Systems</t>
+          <t>draft-chapman-a2a-mls — End-to-End Encryption and Purpose-Bound Governance for Agent-to-Agent Messaging</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft translating use cases and service requirements from 3GPP TR 22.870 into IETF agent-protocol requirements, covering autonomous vehicles, privacy preservation, and anomaly detection.</t>
+          <t>Extends the Agent2Agent (A2A) protocol with message-level E2E confidentiality using MLS (Messaging Layer Security); defines a Governed Object signed message envelope carrying semantic type, payload, purpose declaration, and expiry; mandates receiver-side processing rules enforcing declared purposes and rejecting expired or replayed messages.</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-stephan-ai-agent-6g/</t>
+          <t>https://datatracker.ietf.org/doc/draft-chapman-a2a-mls/</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, October 2025; strong operator backing (Orange, Deutsche Telekom, Telefonica, China Mobile, Huawei). Requirements-oriented and important for 3GPP/IETF coordination. May be expired (April 2026); watch for an update.</t>
+          <t>Revision -00, Jul 28 2026; author: Chapman. Adds the transport-security and semantic-governance layer the A2A protocol family was missing. MLS binding anchors agent identity to Ed25519 did:key DIDs. The Governed Object envelope's purpose-declaration mechanism directly addresses the intent-drift threat identified in draft-jiang-intent-security (corpus). Likely to be referenced by other A2A family drafts as the baseline confidentiality profile.</t>
         </is>
       </c>
     </row>
@@ -3295,17 +3295,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>draft-jimenez-t2trg-iot-agent — Agentic AI Operation of Constrained RESTful Environments</t>
+          <t>draft-rosenberg-aiproto-framework — Framework, Use Cases and Requirements for AI Agent Protocols</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft (T2TRG affiliated) describing agentic AI (ReAct, smolagents) operating on CoAP/CoRE constrained-IoT environments, with a reference implementation provided.</t>
+          <t>An IETF individual draft providing a comprehensive AI-agent communications framework that covers user↔agent, agent↔API, and agent↔agent interactions; surveys MCP, A2A, and Agntcy; and sets the stage for IETF standards activity.</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-jimenez-t2trg-iot-agent/</t>
+          <t>https://datatracker.ietf.org/doc/draft-rosenberg-aiproto-framework/</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 14 April 2026; unique in targeting constrained IoT environments. T2TRG affiliation and reference implementation are positive signals. Niche but fills an unaddressed gap.</t>
+          <t>Revision -00, October 2025; Rosenberg (Five9) and Jennings (Cisco) are credible long-time IETF contributors. Important landscape document but likely expired (April 2026); watch for a -01 refresh post-IETF 123.</t>
         </is>
       </c>
     </row>
@@ -3325,17 +3325,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>draft-li-oauth-delegated-authorization — OAuth 2.0 Delegated Authorization</t>
+          <t>draft-rosenberg-aiproto-cheq — CHEQ: A Protocol for Confirmation of AI Agent Decisions (HITL)</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft from Huawei authors that extends OAuth 2.0 with a hierarchical 'delegation token' model so a client can mint subordinate, narrowly-scoped access tokens for delegated parties.</t>
+          <t>An IETF individual draft defining an out-of-band Human-in-the-Loop confirmation protocol for agent tool calls, eliminating LLM-hallucination risk for consequential actions and enabling sensitive operations (e.g., banking) without exposing data to the agent.</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-li-oauth-delegated-authorization/</t>
+          <t>https://datatracker.ietf.org/doc/draft-rosenberg-aiproto-cheq/</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, March 2026 (Informational); directly addresses over-privileged tokens and is one of the few drafts using the literal term 'delegated authorization'.</t>
+          <t>Revision -00, October 2025; out-of-band HITL confirmation model is valuable and complements delegation frameworks. Likely expired (April 2026); worth tracking for a -01 refresh.</t>
         </is>
       </c>
     </row>
@@ -3355,27 +3355,27 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>draft-araut-oauth-transaction-tokens-for-agents — Transaction Tokens For Agents</t>
+          <t>draft-sharif-agent-payment-trust — Trust Scoring and Identity Verification for AI Agent Payment Transactions (SUPERSEDED)</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft from Ashay Raut (Amazon) profiling Transaction Tokens for agent-based workflows by adding 'act' for the agent identity, an 'agentic_ctx' claim carrying agent_type/intent/allowed_actions/environment_constraints, RFC 9396 RAR integration, and an 'actchain' claim for multi-agent delegation lineage.</t>
+          <t>An IETF individual draft introducing an Agent Passport — a cryptographic delegation certificate intended to serve as the PSD2 'something you have' factor — and a trust-scoring model for payment transactions mapped to PCI DSS v4.0.1.</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-araut-oauth-transaction-tokens-for-agents/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sharif-agent-payment-trust/</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual)</t>
+          <t>IETF (individual, superseded)</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Revision -01 (May 2026) under the new slug — re-slugged from draft-oauth-transaction-tokens-for-agents-06; the -06 added the actchain delegation lineage, RAR-driven agentic_ctx, and a TTS check that blocks chain-splicing attacks. Conservative extension of the WG Transaction Tokens draft and an easier path to standardization.</t>
+          <t>SUPERSEDED by draft-sharif-attp-00 (April 2026). Retained for historical context — the Agent Passport concept is interesting but needs formal grounding; the ATTP successor generalizes it across transport bindings.</t>
         </is>
       </c>
     </row>
@@ -3385,17 +3385,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>draft-oauth-ai-agents-on-behalf-of-user — On-Behalf-Of User Authorization for AI Agents</t>
+          <t>draft-stephan-ai-agent-6g — AI Agent Protocols for 6G Systems</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft adding requested_actor and actor_token parameters to the OAuth authorization-code flow so the user gives explicit consent per agent, with the resulting delegation chain documented in the access-token claims.</t>
+          <t>An IETF individual draft translating use cases and service requirements from 3GPP TR 22.870 into IETF agent-protocol requirements, covering autonomous vehicles, privacy preservation, and anomaly detection.</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-oauth-ai-agents-on-behalf-of-user/</t>
+          <t>https://datatracker.ietf.org/doc/draft-stephan-ai-agent-6g/</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Revision -02 was submitted August 2025; likely due for -03 refresh. Builds naturally on RFC 6749 + RFC 8693 + RFC 7636 PKCE — one of the most 'IETF-ready' delegation drafts and a strong WG-adoption candidate after the OAuth recharter.</t>
+          <t>Revision -02, October 2025; strong operator backing (Orange, Deutsche Telekom, Telefonica, China Mobile, Huawei). Requirements-oriented and important for 3GPP/IETF coordination. May be expired (April 2026); watch for an update.</t>
         </is>
       </c>
     </row>
@@ -3415,17 +3415,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>draft-rosomakho-oauth-txn-challenge — OAuth Transaction Authorization Challenge</t>
+          <t>draft-jimenez-t2trg-iot-agent — Agentic AI Operation of Constrained RESTful Environments</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>An OAuth mechanism enabling protected resources to demand transaction-specific authorization through challenges. When a request involves an agent or automated workflow, the RS returns a challenge to the client; the client presents it to the AS, which validates it, obtains human approval, and issues an access token with RFC 9396 authorization_details describing the approved operation. Positions as complementary to RFC 9470 (Step-Up Authentication) — that spec handles authentication freshness; this one handles authorization specificity.</t>
+          <t>An IETF individual draft (T2TRG affiliated) describing agentic AI (ReAct, smolagents) operating on CoAP/CoRE constrained-IoT environments, with a reference implementation provided.</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-rosomakho-oauth-txn-challenge/</t>
+          <t>https://datatracker.ietf.org/doc/draft-jimenez-t2trg-iot-agent/</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, submitted 25 June 2026. Authors: Yaroslav Rosomakho (Zscaler), Brian Campbell (Ping Identity), Karl McGuinness (Independent), Pieter Kasselman (Defakto). Strong author lineup — Campbell is a prolific OAuth WG contributor, Kasselman co-authored Transaction Tokens and First-Party Apps, McGuinness brings the Mission-Bound OAuth context. The RS-initiated challenge model is distinct from ARAP (which operates at the PDP/PEP layer via AuthZEN) but addresses the same 'denial is not the end' problem — here at the OAuth RS/AS layer rather than the AuthZEN layer.</t>
+          <t>Revision -00, 14 April 2026; unique in targeting constrained IoT environments. T2TRG affiliation and reference implementation are positive signals. Niche but fills an unaddressed gap.</t>
         </is>
       </c>
     </row>
@@ -3445,17 +3445,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>draft-lee-orprg-permit-receipts — Permit Receipts for Permit-Before-Commit Authorization</t>
+          <t>draft-li-oauth-delegated-authorization — OAuth 2.0 Delegated Authorization</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Defines requirements and an abstract data model for PermitReceipts: a verifier evaluates canonicalized effect requests, action digests, policy epochs, validity intervals, and revocation status before any protected effect is committed at an effect boundary. Covers verifier behavior, failure semantics, and candidate registries.</t>
+          <t>An IETF individual draft from Huawei authors that extends OAuth 2.0 with a hierarchical 'delegation token' model so a client can mint subordinate, narrowly-scoped access tokens for delegated parties.</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-lee-orprg-permit-receipts/</t>
+          <t>https://datatracker.ietf.org/doc/draft-li-oauth-delegated-authorization/</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 4 Jun 2026; author: Yong Bok Lee (Meridian Verity Group). The most complete standalone framework for pre-commit authorization in the current wave; intended to ground IETF discussion on scope and profiles. Seeks guidance on appropriate organizational placement.</t>
+          <t>Revision -01, March 2026 (Informational); directly addresses over-privileged tokens and is one of the few drafts using the literal term 'delegated authorization'.</t>
         </is>
       </c>
     </row>
@@ -3475,17 +3475,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>draft-nelson-agent-delegation-receipts — Delegation Receipt Protocol for AI Agent Authorization</t>
+          <t>draft-araut-oauth-transaction-tokens-for-agents — Transaction Tokens For Agents</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Specifies the Delegation Receipt Protocol (DRP) where users sign Authorization Objects (containing scope boundaries, time constraints, instruction hashes, and model state commitments) that are published to an append-only log before the agent runtime gains control. Removes operators as trusted intermediaries by making the user's private key the sole signing authority.</t>
+          <t>An IETF individual draft from Ashay Raut (Amazon) profiling Transaction Tokens for agent-based workflows by adding 'act' for the agent identity, an 'agentic_ctx' claim carrying agent_type/intent/allowed_actions/environment_constraints, RFC 9396 RAR integration, and an 'actchain' claim for multi-agent delegation lineage.</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-nelson-agent-delegation-receipts/</t>
+          <t>https://datatracker.ietf.org/doc/draft-araut-oauth-transaction-tokens-for-agents/</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Revision -10, 13 Jun 2026; author: Ryan Nelson (Authproof). At version 10, the most iterated individual draft in the pre-action authorization space. The commitment-before-execution architecture — sign before the agent runs, not after — is distinctive and directly addresses the prompt-injection attack surface.</t>
+          <t>Revision -01 (May 2026) under the new slug — re-slugged from draft-oauth-transaction-tokens-for-agents-06; the -06 added the actchain delegation lineage, RAR-driven agentic_ctx, and a TTS check that blocks chain-splicing attacks. Conservative extension of the WG Transaction Tokens draft and an easier path to standardization.</t>
         </is>
       </c>
     </row>
@@ -3505,17 +3505,17 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>draft-williams-intent-token — The Intent Token: A Cryptographic Authorization Primitive for Autonomous Agents</t>
+          <t>draft-oauth-ai-agents-on-behalf-of-user — On-Behalf-Of User Authorization for AI Agents</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Specifies a cryptographic authorization primitive that binds an autonomous agent action to a cryptographically signed, human-declared authorization envelope before execution. Addresses the gap in OAuth 2.0 frameworks that govern access to resources but not what agents are permitted to do at the moment of action. Positioned as complementary to OAuth, not a replacement.</t>
+          <t>An IETF individual draft adding requested_actor and actor_token parameters to the OAuth authorization-code flow so the user gives explicit consent per agent, with the resulting delegation chain documented in the access-token claims.</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-williams-intent-token/</t>
+          <t>https://datatracker.ietf.org/doc/draft-oauth-ai-agents-on-behalf-of-user/</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 22 Jun 2026; author: Jeffrey Williams (Independent). Overlaps conceptually with draft-kroehl-agentic-trust-aae and draft-nelson-agent-delegation-receipts; worth tracking as a lighter-weight alternative to both.</t>
+          <t>Revision -02 was submitted August 2025; likely due for -03 refresh. Builds naturally on RFC 6749 + RFC 8693 + RFC 7636 PKCE — one of the most 'IETF-ready' delegation drafts and a strong WG-adoption candidate after the OAuth recharter.</t>
         </is>
       </c>
     </row>
@@ -3535,17 +3535,17 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>draft-pereira-licet-human-intent — LICET: Multi-Modal Physiological Human-Intent Verification for Autonomous AI Agent Authorization</t>
+          <t>draft-rosomakho-oauth-txn-challenge — OAuth Transaction Authorization Challenge</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Proposes a biometric HITL protocol fusing ECG, electrodermal activity, and Mahalanobis statistical distance to cryptographically verify genuine human intent — not just credential possession — before authorizing autonomous AI agent actions, with ZK proofs enabling third-party audit without exposing raw biometric data.</t>
+          <t>An OAuth mechanism enabling protected resources to demand transaction-specific authorization through challenges. When a request involves an agent or automated workflow, the RS returns a challenge to the client; the client presents it to the AS, which validates it, obtains human approval, and issues an access token with RFC 9396 authorization_details describing the approved operation. Positions as complementary to RFC 9470 (Step-Up Authentication) — that spec handles authentication freshness; this one handles authorization specificity.</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-pereira-licet-human-intent/</t>
+          <t>https://datatracker.ietf.org/doc/draft-rosomakho-oauth-txn-challenge/</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 2 Jul 2026. The most novel and technically niche HITL proposal in the current wave — complements draft-rosenberg-aiproto-cheq (out-of-band HITL confirmation) and draft-sato-soos-hem (kernel-enforced escalation) by grounding human intent in physiological signal rather than credential or UI interaction.</t>
+          <t>Revision -00, submitted 25 June 2026. Authors: Yaroslav Rosomakho (Zscaler), Brian Campbell (Ping Identity), Karl McGuinness (Independent), Pieter Kasselman (Defakto). Strong author lineup — Campbell is a prolific OAuth WG contributor, Kasselman co-authored Transaction Tokens and First-Party Apps, McGuinness brings the Mission-Bound OAuth context. The RS-initiated challenge model is distinct from ARAP (which operates at the PDP/PEP layer via AuthZEN) but addresses the same 'denial is not the end' problem — here at the OAuth RS/AS layer rather than the AuthZEN layer.</t>
         </is>
       </c>
     </row>
@@ -3565,17 +3565,17 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>draft-reece-wimse-cross-org-delegation — Cross-Organizational Delegation for Workload and Agent Identity</t>
+          <t>draft-lee-orprg-permit-receipts — Permit Receipts for Permit-Before-Commit Authorization</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>A problem statement and requirements draft identifying that existing workload and token-based authorization mechanisms were designed for a single trust domain, describing the cross-organizational agent delegation gap, and enumerating requirements for solutions — without proposing specific technical approaches.</t>
+          <t>Defines requirements and an abstract data model for PermitReceipts: a verifier evaluates canonicalized effect requests, action digests, policy epochs, validity intervals, and revocation status before any protected effect is committed at an effect boundary. Covers verifier behavior, failure semantics, and candidate registries.</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-reece-wimse-cross-org-delegation/</t>
+          <t>https://datatracker.ietf.org/doc/draft-lee-orprg-permit-receipts/</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 25 Jun 2026; author: Morgan Reece (TowerGuardian Consulting). The problem-statement companion to the corpus's operational drafts; likely to feed into WIMSE WG scope expansion and is directly in scope for draft-kuehlewind-audit-architecture's composition graph.</t>
+          <t>Revision -00, 4 Jun 2026; author: Yong Bok Lee (Meridian Verity Group). The most complete standalone framework for pre-commit authorization in the current wave; intended to ground IETF discussion on scope and profiles. Seeks guidance on appropriate organizational placement.</t>
         </is>
       </c>
     </row>
@@ -3595,17 +3595,17 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>draft-jiang-wimse-heterogeneous-credential — Heterogeneous Credential Verification for Workload and Agentic Systems</t>
+          <t>draft-nelson-agent-delegation-receipts — Delegation Receipt Protocol for AI Agent Authorization</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Specifies mechanisms for representing credential sets, identifying credential types, determining appropriate verifiers, normalizing verification results across different formats (workload tokens, OAuth, X.509, attestation), and combining results into a single handling decision.</t>
+          <t>Specifies the Delegation Receipt Protocol (DRP) where users sign Authorization Objects (containing scope boundaries, time constraints, instruction hashes, and model state commitments) that are published to an append-only log before the agent runtime gains control. Removes operators as trusted intermediaries by making the user's private key the sole signing authority.</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-jiang-wimse-heterogeneous-credential/</t>
+          <t>https://datatracker.ietf.org/doc/draft-nelson-agent-delegation-receipts/</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 30 Jun 2026 (was -00 Jun 2026); authors: Yuning Jiang, Donghui Wang, Yurong Song, Faye Liu (Huawei). Solves the practical problem of agentic systems receiving credentials in multiple formats from different issuers. Fills a gap left by draft-ni-wimse-ai-agent-identity (corpus) which describes the identity problem but not multi-format credential handling.</t>
+          <t>Revision -10, 13 Jun 2026; author: Ryan Nelson (Authproof). At version 10, the most iterated individual draft in the pre-action authorization space. The commitment-before-execution architecture — sign before the agent runs, not after — is distinctive and directly addresses the prompt-injection attack surface.</t>
         </is>
       </c>
     </row>
@@ -3625,17 +3625,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>draft-munoz-wimse-authorization-evidence — Signed Authorization-Evidence Records for WIMSE-Authorized AI Agent Actions</t>
+          <t>draft-williams-intent-token — The Intent Token: A Cryptographic Authorization Primitive for Autonomous Agents</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Specifies a signed authorization-evidence record (Permit) for WIMSE-authorized AI actions, cryptographically binding to the dispatched request bytes via HTTP Message Signatures, OAuth access tokens, and Shared Signals Framework eventing — without modifying existing standards.</t>
+          <t>Specifies a cryptographic authorization primitive that binds an autonomous agent action to a cryptographically signed, human-declared authorization envelope before execution. Addresses the gap in OAuth 2.0 frameworks that govern access to resources but not what agents are permitted to do at the moment of action. Positioned as complementary to OAuth, not a replacement.</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-munoz-wimse-authorization-evidence/</t>
+          <t>https://datatracker.ietf.org/doc/draft-williams-intent-token/</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 15 May 2026; author: Christian Munoz (Keel API). Profiles WIMSE for AI agent actions and satisfies audit requirements; companion to the SCITT permit profile below. Extends the corpus WIMSE thread (draft-ni-wimse-ai-agent-identity) with a concrete evidence artifact.</t>
+          <t>Revision -01, 22 Jun 2026; author: Jeffrey Williams (Independent). Overlaps conceptually with draft-kroehl-agentic-trust-aae and draft-nelson-agent-delegation-receipts; worth tracking as a lighter-weight alternative to both.</t>
         </is>
       </c>
     </row>
@@ -3655,17 +3655,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>draft-schwenkschuster-wimse-trust-domain-discovery — WIMSE Trust Domain Discovery</t>
+          <t>draft-pereira-licet-human-intent — LICET: Multi-Modal Physiological Human-Intent Verification for Autonomous AI Agent Authorization</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Fills a gap in the WIMSE architecture by defining how relying parties obtain cryptographic trust anchors for workload identity credentials; specifies the WIMSE Trust Bundle (a JSON document with freshness metadata) and a well-known HTTPS discovery endpoint resolving trust domain names to their trust bundles, following OpenID Connect Discovery / OAuth 2.0 patterns.</t>
+          <t>Proposes a biometric HITL protocol fusing ECG, electrodermal activity, and Mahalanobis statistical distance to cryptographically verify genuine human intent — not just credential possession — before authorizing autonomous AI agent actions, with ZK proofs enabling third-party audit without exposing raw biometric data.</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-schwenkschuster-wimse-trust-domain-discovery/</t>
+          <t>https://datatracker.ietf.org/doc/draft-pereira-licet-human-intent/</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 3 Jul 2026; authors: Arndt Schwenkschuster (Defakto Security), Yaroslav Rosomakho (Zscaler). Directly complements draft-schwenkschuster-wimse-credential-exchange (corpus). The kuehlewind-audit-architecture HUB assumes resolvable trust anchors — this provides the discovery mechanism. Rosomakho co-authorship ties it to draft-rosomakho-oauth-txn-challenge.</t>
+          <t>Revision -01, 2 Jul 2026. The most novel and technically niche HITL proposal in the current wave — complements draft-rosenberg-aiproto-cheq (out-of-band HITL confirmation) and draft-sato-soos-hem (kernel-enforced escalation) by grounding human intent in physiological signal rather than credential or UI interaction.</t>
         </is>
       </c>
     </row>
@@ -3685,17 +3685,17 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>draft-winmagic-wimse-condition-bounded-credentials — Condition-Bounded Credentials for Workload and Agent Identity</t>
+          <t>draft-reece-wimse-cross-org-delegation — Cross-Organizational Delegation for Workload and Agent Identity</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Proposes hardware-rooted, non-exfiltratable workload credentials whose validity is conditioned on attested runtime posture rather than expiration time — so a credential becomes invalid if the workload's attestation evidence degrades, regardless of the stated expiry.</t>
+          <t>A problem statement and requirements draft identifying that existing workload and token-based authorization mechanisms were designed for a single trust domain, describing the cross-organizational agent delegation gap, and enumerating requirements for solutions — without proposing specific technical approaches.</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-winmagic-wimse-condition-bounded-credentials/</t>
+          <t>https://datatracker.ietf.org/doc/draft-reece-wimse-cross-org-delegation/</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 6 Jul 2026; author: WinMagic. Extends the WIMSE credential model with posture-conditioned validity — distinct from time-bounded credentials in that security policy changes at the hardware/attestation layer instantly invalidate the credential. Bridges the RATS attestation thread and the WIMSE identity thread in the corpus.</t>
+          <t>Revision -00, 25 Jun 2026; author: Morgan Reece (TowerGuardian Consulting). The problem-statement companion to the corpus's operational drafts; likely to feed into WIMSE WG scope expansion and is directly in scope for draft-kuehlewind-audit-architecture's composition graph.</t>
         </is>
       </c>
     </row>
@@ -3715,17 +3715,17 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>draft-munoz-scitt-permit-profile — A SCITT Profile for Pre-Execution AI Action Authorization Records</t>
+          <t>draft-jiang-wimse-heterogeneous-credential — Heterogeneous Credential Verification for Workload and Agentic Systems</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>SCITT profile for the Pre-Execution Authorization Record (Permit), documenting policy-evaluated decisions before AI agent action dispatch with cryptographic binding proving 'authorized request equals dispatched request.' Composes with adjacent profiles for human-authority binding, post-execution evidence, and content-refusal events via referencing mechanisms.</t>
+          <t>Specifies mechanisms for representing credential sets, identifying credential types, determining appropriate verifiers, normalizing verification results across different formats (workload tokens, OAuth, X.509, attestation), and combining results into a single handling decision.</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-munoz-scitt-permit-profile/</t>
+          <t>https://datatracker.ietf.org/doc/draft-jiang-wimse-heterogeneous-credential/</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 15 May 2026; author: Christian Munoz (Keel API). SCITT-anchored analog of the WIMSE evidence record; companion to draft-munoz-wimse-authorization-evidence from the same author. Connects to draft-sharif-agent-audit-trail and draft-kuehlewind-audit-architecture (both in corpus).</t>
+          <t>Revision -01, 30 Jun 2026 (was -00 Jun 2026); authors: Yuning Jiang, Donghui Wang, Yurong Song, Faye Liu (Huawei). Solves the practical problem of agentic systems receiving credentials in multiple formats from different issuers. Fills a gap left by draft-ni-wimse-ai-agent-identity (corpus) which describes the identity problem but not multi-format credential handling.</t>
         </is>
       </c>
     </row>
@@ -3745,17 +3745,17 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>draft-marques-asqav-compliance-receipts — Compliance Profile of Signed Action Receipts for AI Agents</t>
+          <t>draft-munoz-wimse-authorization-evidence — Signed Authorization-Evidence Records for WIMSE-Authorized AI Agent Actions</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Establishes a compliance framework for signed action receipts from AI agents, mandating specific fields, cryptographic anchoring, hash-chain linkage, risk/incident classification, cross-agent envelope binding, and enforcement attestation with retention floors tied to EU AI Act, DORA, NIST AI RMF, HIPAA, SEC Rule 17a-4, and CIRCIA.</t>
+          <t>Specifies a signed authorization-evidence record (Permit) for WIMSE-authorized AI actions, cryptographically binding to the dispatched request bytes via HTTP Message Signatures, OAuth access tokens, and Shared Signals Framework eventing — without modifying existing standards.</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-marques-asqav-compliance-receipts/</t>
+          <t>https://datatracker.ietf.org/doc/draft-munoz-wimse-authorization-evidence/</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>Revision -06, 1 Jul 2026 (was -05 May 2026); author: João André Gomes Marques. The most legally grounded receipt profile in the wave — at revision 06, relatively mature. Complements draft-sharif-agent-audit-trail (corpus) with a multi-regulation compliance overlay.</t>
+          <t>Revision -00, 15 May 2026; author: Christian Munoz (Keel API). Profiles WIMSE for AI agent actions and satisfies audit requirements; companion to the SCITT permit profile below. Extends the corpus WIMSE thread (draft-ni-wimse-ai-agent-identity) with a concrete evidence artifact.</t>
         </is>
       </c>
     </row>
@@ -3775,17 +3775,17 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>draft-mih-scitt-agent-action-capsule — An Agent Action Capsule Profile for SCITT</t>
+          <t>draft-schwenkschuster-wimse-trust-domain-discovery — WIMSE Trust Domain Discovery</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Defines a SCITT statement profile (Agent Action Capsule) documenting agent actions with outcome status (executed, blocked, denied, errored, timed out), evaluated constraints, committed-effect binding, and a human-in-the-loop flag; records a Capsule for every verdict including refusals. COSE Signed Statement format; registrable in SCITT Transparency Services.</t>
+          <t>Fills a gap in the WIMSE architecture by defining how relying parties obtain cryptographic trust anchors for workload identity credentials; specifies the WIMSE Trust Bundle (a JSON document with freshness metadata) and a well-known HTTPS discovery endpoint resolving trust domain names to their trust bundles, following OpenID Connect Discovery / OAuth 2.0 patterns.</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mih-scitt-agent-action-capsule/</t>
+          <t>https://datatracker.ietf.org/doc/draft-schwenkschuster-wimse-trust-domain-discovery/</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 6 Jul 2026 (was -01 Jun 2026); author: Steven Mih (Action State Group). -02 added an 'honest human-in-the-loop' flag distinguishing actual HITL from automated policy. Provides auditor-grade evidence that decision gates functioned; the HITL flag directly tracks the corpus theme.</t>
+          <t>Revision -00, 3 Jul 2026; authors: Arndt Schwenkschuster (Defakto Security), Yaroslav Rosomakho (Zscaler). Directly complements draft-schwenkschuster-wimse-credential-exchange (corpus). The kuehlewind-audit-architecture HUB assumes resolvable trust anchors — this provides the discovery mechanism. Rosomakho co-authorship ties it to draft-rosomakho-oauth-txn-challenge.</t>
         </is>
       </c>
     </row>
@@ -3805,17 +3805,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>draft-mih-sato-agent-accountability-composition — Agent Accountability: Composition and Conformance</t>
+          <t>draft-winmagic-wimse-condition-bounded-credentials — Condition-Bounded Credentials for Workload and Agent Identity</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Addresses how to answer accountability questions about cross-domain autonomous agent actions for auditors and regulators who do not trust the operator; defines a composition model assembling multiple independently verifiable artifacts (workload credentials, delegation tokens, action capsules, attestation results) into a single accountability record with a conformance evaluation framework.</t>
+          <t>Proposes hardware-rooted, non-exfiltratable workload credentials whose validity is conditioned on attested runtime posture rather than expiration time — so a credential becomes invalid if the workload's attestation evidence degrades, regardless of the stated expiry.</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mih-sato-agent-accountability-composition/</t>
+          <t>https://datatracker.ietf.org/doc/draft-winmagic-wimse-condition-bounded-credentials/</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, Jul 2026; authors: Steven Mih (Action State Group) + Tom Sato (MyAuberge K.K.) — collaboration between the two principal authors of draft-mih-scitt-agent-action-capsule (corpus) and the SOOS governance suite (corpus). Operates above individual SCITT profiles; the accountability-composition layer the kuehlewind-audit-architecture HUB depends on but does not yet specify.</t>
+          <t>Revision -01, 6 Jul 2026; author: WinMagic. Extends the WIMSE credential model with posture-conditioned validity — distinct from time-bounded credentials in that security policy changes at the hardware/attestation layer instantly invalidate the credential. Bridges the RATS attestation thread and the WIMSE identity thread in the corpus.</t>
         </is>
       </c>
     </row>
@@ -3835,17 +3835,17 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>draft-car-rer-artifact — RER Run Artifact Format: Hash-Chained, Signed Records of AI Inference Execution</t>
+          <t>draft-rampalli-pedigree — PEDIGREE: Per-Hop Cryptographic Delegation for Workload and AI Agent Identity</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Specifies a cryptographically signed JSON record for AI inference runs including a signed envelope declaring permissions and limits, a hash-chained event log covering all model and tool calls, and a runtime signature binding envelope and log to the producing implementation. Enables offline verification by parties uninvolved in the original run.</t>
+          <t>Extends SPIFFE workload identity with cryptographic per-hop delegation using monotonic scope attenuation enforced at mint and verify; uses Cedar-policy mandates with static-analysis proofs and parent-token re-verification to detect parent-swap attacks. Defines an Operator Ceiling binding all sub-agent authority to the parent's declared mandate.</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-car-rer-artifact/</t>
+          <t>https://datatracker.ietf.org/doc/draft-rampalli-pedigree/</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 12 Jun 2026; author: Kayla Cardillo (Tech Enrichment). Relevant for post-hoc audit of what permissions an agent claimed during execution; companion to the SCITT profiles but more focused on inference traceability than authorization decisions.</t>
+          <t>Revision -00, Apr 25 2026; author: Karthik Rampalli (Glyphzero, Inc.) — same author as draft-rampalli-cross-org-delegation-mapping and draft-rampalli-scitt-capsule-provenance-binding (both in corpus). Presented at WIMSE WG as proposed new work at IETF 126 (Bangkok, Jul 2026). Cedar-policy static-analysis attenuation proofs are a unique contribution relative to other delegation-chain drafts. Note: draft-rampalli-cross-org-delegation-mapping (corpus) references the 'PEDIGREE model' — this is the normative definition.</t>
         </is>
       </c>
     </row>
@@ -3865,17 +3865,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>draft-noa-scitt-ai-agent-receipt — A SCITT Profile for AI-Agent Action Receipts</t>
+          <t>draft-sweeney-wimse-credential-delegation — Credential Delegation Protocol for AI Agents in Multi-System Environments</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Defines a minimal SCITT profile: COSE_Sign1 Signed Statements with canonicalized payloads, hash-chained for ordering, registrable in SCITT Transparency Services. Explicitly does NOT assert agent correctness, safety, or real-world outcomes — only tamper-evident, signature-verifiable records of action, principal, policy identity, and verdict.</t>
+          <t>Composes RFC 8693 Token Exchange, RFC 9449 DPoP, RFC 9396 Rich Authorization Requests, and OpenID Connect CIBA into a unified delegation flow for autonomous AI agents accessing protected resources across providers; introduces ephemeral agent identities via did:key, capability-shaped attenuated delegation tokens, credential wrapping preventing raw OAuth tokens from reaching agents, synchronous revocation cascading, and tamper-evident audit chains.</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-noa-scitt-ai-agent-receipt/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sweeney-wimse-credential-delegation/</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 23 Jun 2026; author: Tora Toraman (NordenSoft). The minimalist end of the SCITT profile spectrum; useful for corpus completeness alongside the more comprehensive draft-mih-scitt-agent-action-capsule.</t>
+          <t>Revision -00, Jul 28 2026; author: Sweeney. Explicitly designed as a WIMSE companion, citing draft-klrc-aiagent-auth as its target framework. The widest synthesis of OAuth primitives in the WIMSE extension cluster — DPoP + RAR + CIBA + Token Exchange in one flow. The credential-wrapping model (raw tokens never reach the agent) directly addresses the secret-exposure threat formalized in arXiv:2604.24920 (SUDP paper, now in corpus).</t>
         </is>
       </c>
     </row>
@@ -3895,17 +3895,17 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>draft-rampalli-scitt-capsule-provenance-binding — Binding Per-Action Authorization and Memory Provenance into Agent Action Capsules</t>
+          <t>draft-munoz-scitt-permit-profile — A SCITT Profile for Pre-Execution AI Action Authorization Records</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Specifies how to bind three components into AAC records: what was executed ('did'), whether it was authorized ('may'), and the source of the belief that motivated the action ('why-believed'); uses optional payload extensions carrying authorization token references, memory chain roots, and quarantine attestations without modifying AAC core protected-header claims.</t>
+          <t>SCITT profile for the Pre-Execution Authorization Record (Permit), documenting policy-evaluated decisions before AI agent action dispatch with cryptographic binding proving 'authorized request equals dispatched request.' Composes with adjacent profiles for human-authority binding, post-execution evidence, and content-refusal events via referencing mechanisms.</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-rampalli-scitt-capsule-provenance-binding/</t>
+          <t>https://datatracker.ietf.org/doc/draft-munoz-scitt-permit-profile/</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 5 Jul 2026; author: Karthik Rampalli (Glyphzero, Inc.). Extends draft-mih-scitt-agent-action-capsule with memory provenance — the 'why-believed' component is novel among SCITT profiles. Includes a defensive publication notice waiving patent claims on the core binding technique.</t>
+          <t>Revision -00, 15 May 2026; author: Christian Munoz (Keel API). SCITT-anchored analog of the WIMSE evidence record; companion to draft-munoz-wimse-authorization-evidence from the same author. Connects to draft-sharif-agent-audit-trail and draft-kuehlewind-audit-architecture (both in corpus).</t>
         </is>
       </c>
     </row>
@@ -3925,17 +3925,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>draft-rampalli-cross-org-delegation-mapping — A Layered Requirements Mapping for Cross-Organization Agent Delegation</t>
+          <t>draft-marques-asqav-compliance-receipts — Compliance Profile of Signed Action Receipts for AI Agents</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Records a comparative mapping of two evidence layers for cross-organization AI agent delegation — per-hop delegation chains (PEDIGREE model) and named-human authorization roots (EMILIA Protocol binding and evidence-graph drafts) — evaluated against the nine requirements of draft-reece-wimse-cross-org-delegation under a multi-tier organizational architecture.</t>
+          <t>Establishes a compliance framework for signed action receipts from AI agents, mandating specific fields, cryptographic anchoring, hash-chain linkage, risk/incident classification, cross-agent envelope binding, and enforcement attestation with retention floors tied to EU AI Act, DORA, NIST AI RMF, HIPAA, SEC Rule 17a-4, and CIRCIA.</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-rampalli-cross-org-delegation-mapping/</t>
+          <t>https://datatracker.ietf.org/doc/draft-marques-asqav-compliance-receipts/</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>Revision -05, Jul 2026; author: Karthik Rampalli (Glyphzero, Inc.) — same author as draft-rampalli-scitt-capsule-provenance-binding (corpus). Rev-05 signals active iteration; the mapping bridges two otherwise disconnected design families and is the first document to formally cross-reference EMILIA Protocol against WIMSE cross-org requirements.</t>
+          <t>Revision -06, 1 Jul 2026 (was -05 May 2026); author: João André Gomes Marques. The most legally grounded receipt profile in the wave — at revision 06, relatively mature. Complements draft-sharif-agent-audit-trail (corpus) with a multi-regulation compliance overlay.</t>
         </is>
       </c>
     </row>
@@ -3955,17 +3955,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>draft-nobuo-scitt-composite-evidence-verification — Composite Evidence Verification for SCITT Statement Graphs</t>
+          <t>draft-mih-scitt-agent-action-capsule — An Agent Action Capsule Profile for SCITT</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Defines a composite verifier function for checking collections of SCITT Signed Statements, receipts, object bindings, and relationship edges under a named verification profile; provides structured reporting on validation status, missing evidence, outdated information, and conflicting claims — targeting auditors needing to evaluate multiple interconnected statements.</t>
+          <t>Defines a SCITT statement profile (Agent Action Capsule) documenting agent actions with outcome status (executed, blocked, denied, errored, timed out), evaluated constraints, committed-effect binding, and a human-in-the-loop flag; records a Capsule for every verdict including refusals. COSE Signed Statement format; registrable in SCITT Transparency Services.</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-nobuo-scitt-composite-evidence-verification/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mih-scitt-agent-action-capsule/</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 7 Jul 2026; author: Nobuo Aoki (SOKENDAI). Operates above individual SCITT profiles (AAC, permits, compliance receipts all in corpus) — the 'how do you verify all of them together' layer that draft-kuehlewind-audit-architecture implies but does not yet specify. Watch for Kühlewind/Birkholz pickup.</t>
+          <t>Revision -02, 6 Jul 2026 (was -01 Jun 2026); author: Steven Mih (Action State Group). -02 added an 'honest human-in-the-loop' flag distinguishing actual HITL from automated policy. Provides auditor-grade evidence that decision gates functioned; the HITL flag directly tracks the corpus theme.</t>
         </is>
       </c>
     </row>
@@ -3985,17 +3985,17 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>draft-schrock-ep-authorization-receipts — Authorization Receipts for High-Risk Agent Actions</t>
+          <t>draft-mih-sato-agent-accountability-composition — Agent Accountability: Composition and Conformance</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Defines the EMILIA Protocol (EP) authorization receipt — a COSE_Sign1 artifact that cryptographically binds a named human principal to a specific high-risk agent action before execution, providing auditors and counterparties a tamper-evident record that a real human authorized the consequential step.</t>
+          <t>Addresses how to answer accountability questions about cross-domain autonomous agent actions for auditors and regulators who do not trust the operator; defines a composition model assembling multiple independently verifiable artifacts (workload credentials, delegation tokens, action capsules, attestation results) into a single accountability record with a conformance evaluation framework.</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-authorization-receipts/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mih-sato-agent-accountability-composition/</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>Revision -06, Jul 2026. The base artifact for the EMILIA Protocol family; companion drafts draft-schrock-ep-authorization-evidence-chain, draft-schrock-ep-action-evidence-graph, draft-schrock-ep-quorum, and draft-schrock-ep-evidence-record all build on or reference this receipt format. Rev-06 indicates active iteration. Draft-rampalli-cross-org-delegation-mapping (corpus) formally maps EMILIA Protocol receipts against the nine reece-wimse-cross-org-delegation requirements.</t>
+          <t>Revision -00, Jul 2026; authors: Steven Mih (Action State Group) + Tom Sato (MyAuberge K.K.) — collaboration between the two principal authors of draft-mih-scitt-agent-action-capsule (corpus) and the SOOS governance suite (corpus). Operates above individual SCITT profiles; the accountability-composition layer the kuehlewind-audit-architecture HUB depends on but does not yet specify.</t>
         </is>
       </c>
     </row>
@@ -4015,17 +4015,17 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>draft-schrock-ep-action-evidence-graph — Action Evidence Graphs and Evidence Policy Replay for High-Risk Agent Actions (EP-AEG)</t>
+          <t>draft-car-rer-artifact — RER Run Artifact Format: Hash-Chained, Signed Records of AI Inference Execution</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Composes the full set of signed artifacts about an AI agent action — workload identity credentials, delegation tokens, transaction tokens, runtime attestation results, pre-execution policy permits, and EMILIA Protocol authorization receipts — into a single verifiable action evidence graph; defines evidence policy replay for auditing past actions against policy versions current at the time.</t>
+          <t>Specifies a cryptographically signed JSON record for AI inference runs including a signed envelope declaring permissions and limits, a hash-chained event log covering all model and tool calls, and a runtime signature binding envelope and log to the producing implementation. Enables offline verification by parties uninvolved in the original run.</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-action-evidence-graph/</t>
+          <t>https://datatracker.ietf.org/doc/draft-car-rer-artifact/</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, Jul 2026. The graph composition layer above the individual SCITT profiles and receipts already in corpus; the 'single verifiable artifact' problem that draft-nobuo-scitt-composite-evidence-verification (corpus) approaches from the SCITT statement side. Together these two drafts define the evidence graph landscape.</t>
+          <t>Revision -01, 12 Jun 2026; author: Kayla Cardillo (Tech Enrichment). Relevant for post-hoc audit of what permissions an agent claimed during execution; companion to the SCITT profiles but more focused on inference traceability than authorization decisions.</t>
         </is>
       </c>
     </row>
@@ -4045,17 +4045,17 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>draft-schrock-ep-authorization-evidence-chain — Authorization Evidence Chains: Composing Heterogeneous Agent-Authorization Receipts (EP-AEC)</t>
+          <t>draft-noa-scitt-ai-agent-receipt — A SCITT Profile for AI-Agent Action Receipts</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Defines a mechanism for composing EMILIA Protocol authorization receipts from different systems and issuers into a single authorization evidence chain, enabling auditors to verify a heterogeneous chain of human approvals across organizational boundaries without requiring a common receipt format.</t>
+          <t>Defines a minimal SCITT profile: COSE_Sign1 Signed Statements with canonicalized payloads, hash-chained for ordering, registrable in SCITT Transparency Services. Explicitly does NOT assert agent correctness, safety, or real-world outcomes — only tamper-evident, signature-verifiable records of action, principal, policy identity, and verdict.</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-authorization-evidence-chain/</t>
+          <t>https://datatracker.ietf.org/doc/draft-noa-scitt-ai-agent-receipt/</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, Jul 2026. The cross-system interoperability layer for EMILIA Protocol receipts; directly addresses the scenario where draft-reece-wimse-cross-org-delegation (corpus) operates and authorization evidence must span administrative domains. Rev-02 indicates active development.</t>
+          <t>Revision -00, 23 Jun 2026; author: Tora Toraman (NordenSoft). The minimalist end of the SCITT profile spectrum; useful for corpus completeness alongside the more comprehensive draft-mih-scitt-agent-action-capsule.</t>
         </is>
       </c>
     </row>
@@ -4075,17 +4075,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>draft-schrock-ep-quorum — Multi-Party Quorum Authorization for High-Risk Agent Actions (EP-QUORUM)</t>
+          <t>draft-rampalli-scitt-capsule-provenance-binding — Binding Per-Action Authorization and Memory Provenance into Agent Action Capsules</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Defines EP-QUORUM, a multi-party authorization profile for EMILIA Protocol authorization receipts; extends the base receipt (which binds one human to one action) to require a quorum of named human approvals before an action may proceed, with configurable thresholds, role requirements, and time-bounded approval windows.</t>
+          <t>Specifies how to bind three components into AAC records: what was executed ('did'), whether it was authorized ('may'), and the source of the belief that motivated the action ('why-believed'); uses optional payload extensions carrying authorization token references, memory chain roots, and quarantine attestations without modifying AAC core protected-header claims.</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-quorum/</t>
+          <t>https://datatracker.ietf.org/doc/draft-rampalli-scitt-capsule-provenance-binding/</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, Jul 2026. The enterprise governance complement to the base EP receipt; relevant for high-risk regulated workflows (financial transactions, medical orders, critical infrastructure changes) where single-human authorization is insufficient. Rev-02 indicates active iteration.</t>
+          <t>Revision -00, 5 Jul 2026; author: Karthik Rampalli (Glyphzero, Inc.). Extends draft-mih-scitt-agent-action-capsule with memory provenance — the 'why-believed' component is novel among SCITT profiles. Includes a defensive publication notice waiving patent claims on the core binding technique.</t>
         </is>
       </c>
     </row>
@@ -4105,17 +4105,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>draft-schrock-ep-evidence-record — Long-Term, Crypto-Agile Preservation of Authorization Evidence (EP-EVIDENCE-RECORD)</t>
+          <t>draft-rampalli-cross-org-delegation-mapping — A Layered Requirements Mapping for Cross-Organization Agent Delegation</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Defines a long-term, crypto-agile record format for preserving EMILIA Protocol authorization evidence under regulatory retention mandates; addresses algorithm deprecation over multi-year retention periods (DORA 5-year, HIPAA 6-year, SEC 17a-4 requirements) using a re-signing model that preserves evidentiary chain of custody.</t>
+          <t>Records a comparative mapping of two evidence layers for cross-organization AI agent delegation — per-hop delegation chains (PEDIGREE model) and named-human authorization roots (EMILIA Protocol binding and evidence-graph drafts) — evaluated against the nine requirements of draft-reece-wimse-cross-org-delegation under a multi-tier organizational architecture.</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-evidence-record/</t>
+          <t>https://datatracker.ietf.org/doc/draft-rampalli-cross-org-delegation-mapping/</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, Jul 2026. The regulatory compliance layer for EMILIA Protocol; directly connects to the kuehlewind-audit-architecture HUB (corpus) requirement for audit evidence that survives algorithm sunset. The DORA/HIPAA/SEC citation grounds the spec in concrete regulatory obligations.</t>
+          <t>Revision -05, Jul 2026; author: Karthik Rampalli (Glyphzero, Inc.) — same author as draft-rampalli-scitt-capsule-provenance-binding (corpus). Rev-05 signals active iteration; the mapping bridges two otherwise disconnected design families and is the first document to formally cross-reference EMILIA Protocol against WIMSE cross-org requirements.</t>
         </is>
       </c>
     </row>
@@ -4135,17 +4135,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>draft-tsyrulnikov-rats-attested-inference-receipt — Attested Inference Receipt (AIR): A COSE/CWT Profile for Confidential AI Inference</t>
+          <t>draft-nobuo-scitt-composite-evidence-verification — Composite Evidence Verification for SCITT Statement Graphs</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>Defines the Attested Inference Receipt (AIR), a COSE_Sign1 envelope carrying CWT claims profiled per the Entity Attestation Token (EAT) framework; an AIR receipt cryptographically binds model identity, input/output hashes, TEE attestation evidence, and operational telemetry into a single signed artifact verifiable by parties not present at inference time.</t>
+          <t>Defines a composite verifier function for checking collections of SCITT Signed Statements, receipts, object bindings, and relationship edges under a named verification profile; provides structured reporting on validation status, missing evidence, outdated information, and conflicting claims — targeting auditors needing to evaluate multiple interconnected statements.</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-tsyrulnikov-rats-attested-inference-receipt/</t>
+          <t>https://datatracker.ietf.org/doc/draft-nobuo-scitt-composite-evidence-verification/</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, Jul 2026. The RATS-layer complement to the SCITT profiles in corpus: where SCITT profiles (mih-scitt-agent-action-capsule, marques-asqav-compliance-receipts) record authorization and governance events, AIR records what the model actually computed — model identity, I/O content hashes, and TEE attestation linking the computation to trusted hardware. Together they address the full audit evidence stack.</t>
+          <t>Revision -00, 7 Jul 2026; author: Nobuo Aoki (SOKENDAI). Operates above individual SCITT profiles (AAC, permits, compliance receipts all in corpus) — the 'how do you verify all of them together' layer that draft-kuehlewind-audit-architecture implies but does not yet specify. Watch for Kühlewind/Birkholz pickup.</t>
         </is>
       </c>
     </row>
@@ -4165,17 +4165,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>draft-sato-soos-mjwt — The Mandate JWT (MJWT) for Agentic AI Systems</t>
+          <t>draft-schrock-ep-authorization-receipts — Authorization Receipts for High-Risk Agent Actions</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Introduces the Mandate JWT — a WIMSE workload credential profile binding agent authority to specific Sovereign Object instances under named human principals, with cryptographically enforced delegation ceilings and a six-dimensional Narrowing Property preventing sub-agents from exceeding root authority.</t>
+          <t>Defines the EMILIA Protocol (EP) authorization receipt — a COSE_Sign1 artifact that cryptographically binds a named human principal to a specific high-risk agent action before execution, providing auditors and counterparties a tamper-evident record that a real human authorized the consequential step.</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sato-soos-mjwt/</t>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-authorization-receipts/</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 10 Jun 2026; author: Tom Sato (MyAuberge K.K.). The authorization token primitive for the SOOS governance protocol family. Directly comparable to draft-mcguinness-oauth-client-instance-assertion but uses a WIMSE/Sovereign Object substrate rather than OAuth.</t>
+          <t>Revision -08, Jul 21 2026. The base artifact for the EMILIA Protocol family; companion drafts draft-schrock-ep-authorization-evidence-chain, draft-schrock-ep-action-evidence-graph, draft-schrock-ep-quorum, and draft-schrock-ep-evidence-record all build on or reference this receipt format. Active iteration pace — -08 by late Jul 2026. Draft-rampalli-cross-org-delegation-mapping (corpus) formally maps EMILIA Protocol receipts against the nine reece-wimse-cross-org-delegation requirements.</t>
         </is>
       </c>
     </row>
@@ -4195,17 +4195,17 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>draft-sato-soos-mad — Multi-Agent Delegation in Sovereign Object Systems</t>
+          <t>draft-schrock-ep-action-evidence-graph — Action Evidence Graphs and Evidence Policy Replay for High-Risk Agent Actions (EP-AEG)</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>Specifies three core mechanisms for multi-agent delegation accountability: the Narrowing Property (capability non-amplification), five formally defined object topology patterns for runtime relationships, and cluster coordination primitives for parallel execution with aggregation rules. Version 02 adds revocation-during-execution handling and partial-completion routing to human oversight.</t>
+          <t>Composes the full set of signed artifacts about an AI agent action — workload identity credentials, delegation tokens, transaction tokens, runtime attestation results, pre-execution policy permits, and EMILIA Protocol authorization receipts — into a single verifiable action evidence graph; defines evidence policy replay for auditing past actions against policy versions current at the time.</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sato-soos-mad/</t>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-action-evidence-graph/</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 10 Jun 2026; author: Tom Sato (MyAuberge K.K.). Claims to address gaps the OpenID Foundation identifies as unsolved in multi-agent authorization. The five topology patterns are a useful vocabulary for describing agent-to-agent relationship structures.</t>
+          <t>Revision -00, Jul 2026. The graph composition layer above the individual SCITT profiles and receipts already in corpus; the 'single verifiable artifact' problem that draft-nobuo-scitt-composite-evidence-verification (corpus) approaches from the SCITT statement side. Together these two drafts define the evidence graph landscape.</t>
         </is>
       </c>
     </row>
@@ -4225,17 +4225,17 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>draft-sato-soos-hem — The Human Escalation Mechanism (HEM) for Agentic AI Systems</t>
+          <t>draft-schrock-ep-authorization-evidence-chain — Authorization Evidence Chains: Composing Heterogeneous Agent-Authorization Receipts (EP-AEC)</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Defines a kernel-enforced mechanism placing agent sessions in a pending state when human judgment is required, routing structured escalation requests to designated human decision-makers, and prohibiting all state transitions until a human decision is received. Defines five decision types and a dual-layer architecture (LLM-HEM and SOOS-HEM).</t>
+          <t>Defines a mechanism for composing EMILIA Protocol authorization receipts from different systems and issuers into a single authorization evidence chain, enabling auditors to verify a heterogeneous chain of human approvals across organizational boundaries without requiring a common receipt format.</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sato-soos-hem/</t>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-authorization-evidence-chain/</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>Revision -05, 30 Jun 2026 (was -04 Jun 2026); author: Tom Sato (MyAuberge K.K.). The most normative HITL protocol in the current wave; explicitly aligns with EU AI Act Article 14 requirements for high-risk AI system oversight. Counterpart to ARAP (AuthZEN WG) at the protocol level vs. the OAuth/AuthZEN layer.</t>
+          <t>Revision -02, Jul 2026. The cross-system interoperability layer for EMILIA Protocol receipts; directly addresses the scenario where draft-reece-wimse-cross-org-delegation (corpus) operates and authorization evidence must span administrative domains. Rev-02 indicates active development.</t>
         </is>
       </c>
     </row>
@@ -4255,17 +4255,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>draft-sato-soos-idp — The Intent Declaration Primitive (IDP) for Agentic AI Systems</t>
+          <t>draft-schrock-ep-quorum — Multi-Party Quorum Authorization for High-Risk Agent Actions (EP-QUORUM)</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>Specifies a structured declaration mechanism committing AI agent intent to tamper-evident logs before actions are taken, enabling post-hoc review and EU AI Act Article 12 compliance for high-risk systems.</t>
+          <t>Defines EP-QUORUM, a multi-party authorization profile for EMILIA Protocol authorization receipts; extends the base receipt (which binds one human to one action) to require a quorum of named human approvals before an action may proceed, with configurable thresholds, role requirements, and time-bounded approval windows.</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sato-soos-idp/</t>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-quorum/</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>Revision -05, 30 Jun 2026 (was -04 Jun 2026); author: Tom Sato (MyAuberge K.K.). The log-before-execute pattern mirrors draft-nelson-agent-delegation-receipts but operates at the intent declaration level rather than the user-authorization level. Pairs with GAR (below) to form a complete pre/post audit trail.</t>
+          <t>Revision -02, Jul 2026. The enterprise governance complement to the base EP receipt; relevant for high-risk regulated workflows (financial transactions, medical orders, critical infrastructure changes) where single-human authorization is insufficient. Rev-02 indicates active iteration.</t>
         </is>
       </c>
     </row>
@@ -4285,17 +4285,17 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>draft-sato-soos-gar — The Governance Audit Record (GAR) for Agentic AI Systems</t>
+          <t>draft-schrock-ep-evidence-record — Long-Term, Crypto-Agile Preservation of Authorization Evidence (EP-EVIDENCE-RECORD)</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>Defines GAR, an audit framework with five audit types, a Session Audit Record, and an Audit Alert mechanism; collects, signs, and makes governance events from IDP, HEM, and associated SOOS primitives available for regulatory inspection via an append-only, non-suppressible SCITT-anchored audit stream with Authority Lifecycle Events covering the complete revocation-recovery cycle.</t>
+          <t>Defines a long-term, crypto-agile record format for preserving EMILIA Protocol authorization evidence under regulatory retention mandates; addresses algorithm deprecation over multi-year retention periods (DORA 5-year, HIPAA 6-year, SEC 17a-4 requirements) using a re-signing model that preserves evidentiary chain of custody.</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sato-soos-gar/</t>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-evidence-record/</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, 28 Jun 2026 (was -02 Jun 10). -03 added OpenTelemetry attribute namespace for governance observability, a GAR Processor spec for converting OTel signals to audit records with integrity verification, four new Authority Lifecycle Event categories (policy conflict scenarios, statutory interpretation changes), and mandatory provenance fields for policy evaluation records. The integrator for the SOOS family, analogous to how draft-kuehlewind-audit-architecture integrates the broader IETF agent draft landscape.</t>
+          <t>Revision -01, Jul 2026. The regulatory compliance layer for EMILIA Protocol; directly connects to the kuehlewind-audit-architecture HUB (corpus) requirement for audit evidence that survives algorithm sunset. The DORA/HIPAA/SEC citation grounds the spec in concrete regulatory obligations.</t>
         </is>
       </c>
     </row>
@@ -4315,17 +4315,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>draft-jiang-intent-security — Security Considerations and Requirements for Intent-Based Requests in Agentic Systems</t>
+          <t>draft-kumaresan-counter-sign — counter-sign: An Open Protocol for Agent-to-Human Authorization</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Solution-agnostic threat analysis covering tampering, privilege escalation, constraint violations, and intent drift in intent-based agentic systems, with a reference model, attack scenarios, and security requirements covering authentication, admission control, constraint validation, and multi-hop integrity.</t>
+          <t>Defines a protocol where agents sign intent objects for consequential actions and humans return cryptographic countersignatures (approve/reject); includes an Enrollment Registry binding actors to signing keys, quorum models for multi-approver scenarios, and tamper-evident receipt logs. Explicitly out of scope for agent-to-service auth — addresses the 'human approval cannot be forged after the fact' problem.</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-jiang-intent-security/</t>
+          <t>https://datatracker.ietf.org/doc/draft-kumaresan-counter-sign/</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, 22 Jun 2026; authors: Yuning Jiang, Lun Li, Yurong Song, Faye Liu (Huawei). The threat-model companion to draft-jiang-oauth-intent-admission from the same group; likely intended to inform the broader IETF agentic AI security discussion.</t>
+          <t>Revision -00, Jul 21 2026; author: Kumaresan. Human-countersignature model makes it a direct complement to the EMILIA Protocol family (schrock-ep-*) and to draft-sato-soos-hem (HEM) — EMILIA and HEM handle the pre-execution authorization decision, counter-sign handles the cryptographic non-repudiation that the human approval actually happened. The Enrollment Registry is analogous to WebBotAuth's Signature Agent Card registry but for human approvers.</t>
         </is>
       </c>
     </row>
@@ -4345,17 +4345,17 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>draft-haberkamp-ipp — Intent Provenance Protocol (IPP)</t>
+          <t>draft-thallapelly-oasnt — OASNT: Attested Action Authorization Tokens</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Specifies a cryptographic infrastructure standard for carrying verified human intent through chains of autonomous AI agent actions; defines the Intent Token, a signed, bounded, and tamper-evident data structure that travels with every agentic action so downstream agents and resource servers can verify that the chain traces to a real human authorization.</t>
+          <t>Defines a JWS-based single-use, short-lived token binding a specific human-approved action to the exact rendered disclosure text the approver saw — 'What You See Is What You Sign' (WYSIWYG) — with optional binding to a concrete HTTP request. Requires hardware-resident secure element signature and device runtime integrity assessment.</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-haberkamp-ipp/</t>
+          <t>https://datatracker.ietf.org/doc/draft-thallapelly-oasnt/</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, Jul 2026. Addresses the 'intent drift' threat class from draft-jiang-intent-security (corpus) with a concrete token artifact; complements the EMILIA Protocol receipts (authorization at the action level) with an intent record at the delegation chain level. The traveling Intent Token model is distinct from both SOOS Mandate JWTs (Sato, governance substrate) and McGuinness Actor Profiles (delegation chain encoding in existing OAuth tokens).</t>
+          <t>Revision -01, Jul 24 2026 (first filed Jul 21 2026); author: Thallapelly. Hardware-bound, WYSIWYG authorization token — distinct from software-only pre-action permit approaches such as draft-kumaresan-counter-sign (above) and the EMILIA Protocol family. The WYSIWYG disclosure binding addresses UI redress attacks where an agent's rendered action description differs from the actual HTTP request being authorized. Hardware PoP requirement makes this the highest-assurance pre-action permit in the current wave.</t>
         </is>
       </c>
     </row>
@@ -4375,17 +4375,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>draft-li-dmsc-macp — Multi-agent Collaboration Protocol Suites Architecture</t>
+          <t>draft-tsyrulnikov-rats-attested-inference-receipt — Attested Inference Receipt (AIR): A COSE/CWT Profile for Confidential AI Inference</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Defines a protocol suite and architectural framework for secure, scalable multi-agent collaboration covering trusted agent onboarding, capability-based discovery, distributed capability synchronization, and secure agent-to-agent interaction. Specifies a gateway-centric architecture where an Agent Gateway mediates capability negotiation and trust establishment between collaborating agents.</t>
+          <t>Defines the Attested Inference Receipt (AIR), a COSE_Sign1 envelope carrying CWT claims profiled per the Entity Attestation Token (EAT) framework; an AIR receipt cryptographically binds model identity, input/output hashes, TEE attestation evidence, and operational telemetry into a single signed artifact verifiable by parties not present at inference time.</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-li-dmsc-macp/</t>
+          <t>https://datatracker.ietf.org/doc/draft-tsyrulnikov-rats-attested-inference-receipt/</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>Revision -05, 26 May 2026; active (expires Nov 2026); authors: Xueting Li (China Telecom), Bing Liu (Huawei), Jun Liu (Beijing U of Posts &amp; Telecom), Chenguang Du (Tsinghua), Lianhua Zhang (AsiaInfo). Replaces draft-li-dmsc-mcps-agw. Anchors a DMSC family of companion drafts covering intent-based interconnection, task protocol, gateway directory sync, semantic interaction, and gateway requirements. No explicit OAuth or WIMSE dependencies — operates at the agent coordination layer above transport, below authorization.</t>
+          <t>Revision -02, Jul 2026. The RATS-layer complement to the SCITT profiles in corpus: where SCITT profiles (mih-scitt-agent-action-capsule, marques-asqav-compliance-receipts) record authorization and governance events, AIR records what the model actually computed — model identity, I/O content hashes, and TEE attestation linking the computation to trusted hardware. Together they address the full audit evidence stack.</t>
         </is>
       </c>
     </row>
@@ -4405,17 +4405,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>draft-li-dmsc-inf-architecture — Dynamic Multi-agent Secured Collaboration Infrastructure Architecture</t>
+          <t>draft-sato-soos-mjwt — The Mandate JWT (MJWT) for Agentic AI Systems</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>Approaches DMSC from the network-infrastructure perspective: proposes capability-based forwarding and semantic routing at the network layer, where agent capability metadata influences packet-forwarding decisions rather than routing based solely on addresses. The most mature DMSC document at rev 07; predates and informs the MACP architecture draft.</t>
+          <t>Introduces the Mandate JWT — a WIMSE workload credential profile binding agent authority to specific Sovereign Object instances under named human principals, with cryptographically enforced delegation ceilings and a six-dimensional Narrowing Property preventing sub-agents from exceeding root authority.</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-li-dmsc-inf-architecture/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sato-soos-mjwt/</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>Revision -07, May 22 2026; authors: Xueting Li (China Telecom), Aijun Wang (China Telecom), Bing Liu (Huawei), Changwang Lin (New H3C). Infrastructure-layer complement to draft-li-dmsc-macp (protocol suite). The DMSC family now has 14+ companion drafts from Chinese telecom/academic groups — this is the architectural anchor.</t>
+          <t>Revision -01, 10 Jun 2026; author: Tom Sato (MyAuberge K.K.). The authorization token primitive for the SOOS governance protocol family. Directly comparable to draft-mcguinness-oauth-client-instance-assertion but uses a WIMSE/Sovereign Object substrate rather than OAuth.</t>
         </is>
       </c>
     </row>
@@ -4435,17 +4435,17 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>draft-sz-dmsc-iaip — Intent-based Agent Interconnection Protocol at Agent Gateway</t>
+          <t>draft-sato-soos-mad — Multi-Agent Delegation in Sovereign Object Systems</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>Defines semantic capability advertisement and intent-driven routing at DMSC agent gateways: agents publish capability profiles in a structured format and the gateway matches incoming task intents to available agents, replacing fixed-address routing with dynamic semantic matching. The core routing-layer protocol for DMSC inter-agent communication.</t>
+          <t>Specifies three core mechanisms for multi-agent delegation accountability: the Narrowing Property (capability non-amplification), five formally defined object topology patterns for runtime relationships, and cluster coordination primitives for parallel execution with aggregation rules. Version 02 adds revocation-during-execution handling and partial-completion routing to human oversight.</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sz-dmsc-iaip/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sato-soos-mad/</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, May 2026; authors: Sheng Sun, Xinyi Zhang (CAS/CNIC), Qiangzhou Gao (Huawei), Min Liu, Yuwei Wang (ICT, CAS). The intent-based routing mechanism that distinguishes DMSC from address-based protocols; relevant to the DAWN boundary question — DMSC embeds discovery in the gateway routing layer rather than treating it as a separate protocol.</t>
+          <t>Revision -02, 10 Jun 2026; author: Tom Sato (MyAuberge K.K.). Claims to address gaps the OpenID Foundation identifies as unsolved in multi-agent authorization. The five topology patterns are a useful vocabulary for describing agent-to-agent relationship structures.</t>
         </is>
       </c>
     </row>
@@ -4465,17 +4465,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>draft-yang-dmsc-ioa-task-protocol — Internet of Agents Task Protocol for Heterogeneous Agent Collaboration</t>
+          <t>draft-sato-soos-hem — The Human Escalation Mechanism (HEM) for Agentic AI Systems</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>Establishes a session and task coordination layer with finite-state-machine-based dialogue management, dynamic team assembly, and nested team hierarchies for distributed heterogeneous agent collaboration. Addresses the multi-agent task lifecycle from assignment through completion and audit across heterogeneous agent implementations.</t>
+          <t>Defines a kernel-enforced mechanism placing agent sessions in a pending state when human judgment is required, routing structured escalation requests to designated human decision-makers, and prohibiting all state transitions until a human decision is received. Defines five decision types and a dual-layer architecture (LLM-HEM and SOOS-HEM).</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-yang-dmsc-ioa-task-protocol/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sato-soos-hem/</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, Apr 21 2026; authors: Cheng Yang (BUPT), Zhiyuan Liu (Tsinghua), Aijun Wang (China Telecom). The task-coordination layer above the DMSC gateway routing; covers multi-domain and 6G/ITS scenarios. Distinct from OAuth-layer delegation in that it orchestrates task state rather than token issuance.</t>
+          <t>Revision -05, 30 Jun 2026 (was -04 Jun 2026); author: Tom Sato (MyAuberge K.K.). The most normative HITL protocol in the current wave; explicitly aligns with EU AI Act Article 14 requirements for high-risk AI system oversight. Counterpart to ARAP (AuthZEN WG) at the protocol level vs. the OAuth/AuthZEN layer.</t>
         </is>
       </c>
     </row>
@@ -4495,17 +4495,17 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>draft-dunbar-dmsc-gw-scenarios-gap-analysis — Deployment Scenarios and Gap Analysis for AI Agent Gateway</t>
+          <t>draft-sato-soos-idp — The Intent Declaration Primitive (IDP) for Agentic AI Systems</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>Surveys single-domain to multi-domain deployment scenarios for AI Agent Gateways and identifies concrete gaps where existing protocols (specifically MCP and Google's A2A) cannot satisfy governance, policy enforcement, and cross-organizational trust requirements — particularly in regulated financial services and telecom environments.</t>
+          <t>Specifies a structured declaration mechanism committing AI agent intent to tamper-evident logs before actions are taken, enabling post-hoc review and EU AI Act Article 12 compliance for high-risk systems.</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-dunbar-dmsc-gw-scenarios-gap-analysis/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sato-soos-idp/</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, Jul 2 2026; authors: Linda Dunbar (Futurewei), YiFei Wang (China Telecom), Bing Liu (Huawei). The most directly useful DMSC document for the boundary analysis: explicitly names MCP and A2A as insufficient and articulates where the DMSC gateway fills the gap. The regulated-environment focus (financial services, telco) distinguishes DMSC's use-case target from OAuth-centric approaches.</t>
+          <t>Revision -05, 30 Jun 2026 (was -04 Jun 2026); author: Tom Sato (MyAuberge K.K.). The log-before-execute pattern mirrors draft-nelson-agent-delegation-receipts but operates at the intent declaration level rather than the user-authorization level. Pairs with GAR (below) to form a complete pre/post audit trail.</t>
         </is>
       </c>
     </row>
@@ -4525,17 +4525,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>draft-somoza-dmsc-atn-agent-trust-negotiation — Agent Trust Negotiation: Capability, Delegation, and Provenance Binding</t>
+          <t>draft-sato-soos-gar — The Governance Audit Record (GAR) for Agentic AI Systems</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>Specifies the Agent Trust Negotiation (ATN) protocol, which binds four artifacts — capability manifests, delegation chains, provenance attestations, and session receipts — to agent identities via a handshake state machine producing mutually verified, scope-bounded sessions with SCITT-suitable audit records.</t>
+          <t>Defines GAR, an audit framework with five audit types, a Session Audit Record, and an Audit Alert mechanism; collects, signs, and makes governance events from IDP, HEM, and associated SOOS primitives available for regulatory inspection via an append-only, non-suppressible SCITT-anchored audit stream with Authority Lifecycle Events covering the complete revocation-recovery cycle.</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-somoza-dmsc-atn-agent-trust-negotiation/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sato-soos-gar/</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 29 May 2026; author: Enrique Somoza (Independent). Operates above discovery mechanisms and positions itself between the discovery layer (DAWN, MCP) and the authorization layer (WIMSE, OAuth). Relevant as an agent-to-agent trust establishment handshake protocol.</t>
+          <t>Revision -03, 28 Jun 2026 (was -02 Jun 10). -03 added OpenTelemetry attribute namespace for governance observability, a GAR Processor spec for converting OTel signals to audit records with integrity verification, four new Authority Lifecycle Event categories (policy conflict scenarios, statutory interpretation changes), and mandatory provenance fields for policy evaluation records. The integrator for the SOOS family, analogous to how draft-kuehlewind-audit-architecture integrates the broader IETF agent draft landscape.</t>
         </is>
       </c>
     </row>
@@ -4555,17 +4555,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>draft-mcgraw-httpapi-agent-budget — The Delegation HTTP Authentication Scheme for Request-Bound Authority</t>
+          <t>draft-jiang-intent-security — Security Considerations and Requirements for Intent-Based Requests in Agentic Systems</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>Defines the 'Delegation' HTTP authentication scheme and response semantics for delegated-authority challenges using HTTP status codes and Problem Details, plus a CBOR/COSE proof format. The initial authority profile is 'Budget,' using post-quantum ML-DSA to prove spending or resource-consumption limits.</t>
+          <t>Solution-agnostic threat analysis covering tampering, privilege escalation, constraint violations, and intent drift in intent-based agentic systems, with a reference model, attack scenarios, and security requirements covering authentication, admission control, constraint validation, and multi-hop integrity.</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcgraw-httpapi-agent-budget/</t>
+          <t>https://datatracker.ietf.org/doc/draft-jiang-intent-security/</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 15 Jun 2026; author: John Paul McGraw Jr. (TaskHawk Systems). HTTP-layer bounded delegation with post-quantum crypto; distinct from OAuth-layer delegation in that the authority proof travels in the Authorization header. Complements x401 (Industry tab) at the HTTP challenge-response layer.</t>
+          <t>Revision -03, 22 Jun 2026; authors: Yuning Jiang, Lun Li, Yurong Song, Faye Liu (Huawei). The threat-model companion to draft-jiang-oauth-intent-admission from the same group; likely intended to inform the broader IETF agentic AI security discussion.</t>
         </is>
       </c>
     </row>
@@ -4585,17 +4585,17 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>draft-vauban-x402-delegation-binding — x402 Delegation Binding for Agentic HTTP Pipelines</t>
+          <t>draft-haberkamp-ipp — Intent Provenance Protocol (IPP)</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>Addresses the security gap where x402 V2 payment grants issued to one agent could be misused by another in the same pipeline, introducing three binding mechanisms: a JCS-derived agent identity pseudonym, a nonce for anti-replay, and a depth-limiting field for transitive delegation.</t>
+          <t>Specifies a cryptographic infrastructure standard for carrying verified human intent through chains of autonomous AI agent actions; defines the Intent Token, a signed, bounded, and tamper-evident data structure that travels with every agentic action so downstream agents and resource servers can verify that the chain traces to a real human authorization.</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-vauban-x402-delegation-binding/</t>
+          <t>https://datatracker.ietf.org/doc/draft-haberkamp-ipp/</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 25 May 2026; author: Vauban Research. Narrowly scoped to payment pipelines but the delegation-binding pattern (pseudonymous identity + anti-replay + depth-limit) is applicable broadly. Validated across five language runtimes with A2A and MCP integration guidance.</t>
+          <t>Revision -01, Jul 2026. Addresses the 'intent drift' threat class from draft-jiang-intent-security (corpus) with a concrete token artifact; complements the EMILIA Protocol receipts (authorization at the action level) with an intent record at the delegation chain level. The traveling Intent Token model is distinct from both SOOS Mandate JWTs (Sato, governance substrate) and McGuinness Actor Profiles (delegation chain encoding in existing OAuth tokens).</t>
         </is>
       </c>
     </row>
@@ -4615,17 +4615,17 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>draft-samal-vap — Verifiable Agent Protocol (VAP): Intent-Bound Admission Control and Audit for Agent Tool Invocation</t>
+          <t>draft-li-dmsc-macp — Multi-agent Collaboration Protocol Suites Architecture</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>Specifies VAP as a defense-in-depth layer adding declarations of purpose and session budget commitments to tool invocation requests (targeting MCP-style protocols), enabling servers to perform admission control before execution via four messages carried in existing protocol metadata.</t>
+          <t>Defines a protocol suite and architectural framework for secure, scalable multi-agent collaboration covering trusted agent onboarding, capability-based discovery, distributed capability synchronization, and secure agent-to-agent interaction. Specifies a gateway-centric architecture where an Agent Gateway mediates capability negotiation and trust establishment between collaborating agents.</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-samal-vap/</t>
+          <t>https://datatracker.ietf.org/doc/draft-li-dmsc-macp/</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 3 Jun 2026; author: Kruttidipta Samal (Independent). Lightweight and protocol-agnostic; addresses erroneous agent behavior, cost control, and audit trails without replacing existing auth mechanisms. Practical tool-invocation-level authorization layer for MCP deployments.</t>
+          <t>Revision -06, Jul 20 2026; active; authors: Xueting Li (China Telecom), Bing Liu (Huawei), Jun Liu (Beijing U of Posts &amp; Telecom), Chenguang Du (Tsinghua), Lianhua Zhang (AsiaInfo). Replaces draft-li-dmsc-mcps-agw. Anchors a DMSC family of companion drafts covering intent-based interconnection, task protocol, gateway directory sync, semantic interaction, and gateway requirements. No explicit OAuth or WIMSE dependencies — operates at the agent coordination layer above transport, below authorization.</t>
         </is>
       </c>
     </row>
@@ -4645,17 +4645,17 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>draft-khera-aurora — Agent Unification, Runtime, and Operational Responsibility Attestation (AURORA)</t>
+          <t>draft-li-dmsc-inf-architecture — Dynamic Multi-agent Secured Collaboration Infrastructure Architecture</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>A two-layer framework unifying hardware-enclave-backed Runtime Integrity Attestation with scoped, cryptographically bound Authority Delegation; enables agents to prove both operational authority and runtime integrity simultaneously.</t>
+          <t>Approaches DMSC from the network-infrastructure perspective: proposes capability-based forwarding and semantic routing at the network layer, where agent capability metadata influences packet-forwarding decisions rather than routing based solely on addresses. The most mature DMSC document at rev 07; predates and informs the MACP architecture draft.</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-khera-aurora/</t>
+          <t>https://datatracker.ietf.org/doc/draft-li-dmsc-inf-architecture/</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 5 Jun 2026; author: Ankur Khera. Addresses the gap where delegation tokens don't prove the runtime environment is trustworthy — relevant where delegation must be paired with platform attestation (enterprise/regulated deployments). Bridges the RATS attestation thread and the OAuth delegation thread.</t>
+          <t>Revision -07, May 22 2026; authors: Xueting Li (China Telecom), Aijun Wang (China Telecom), Bing Liu (Huawei), Changwang Lin (New H3C). Infrastructure-layer complement to draft-li-dmsc-macp (protocol suite). The DMSC family now has 14+ companion drafts from Chinese telecom/academic groups — this is the architectural anchor.</t>
         </is>
       </c>
     </row>
@@ -4675,17 +4675,17 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>draft-borthwick-msebenzi-environment-state — Verifiable Intent — environment.* Constraint Family</t>
+          <t>draft-sz-dmsc-iaip — Intent-based Agent Interconnection Protocol at Agent Gateway</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>Defines the environment.* constraint family for agent-authorization mandate vocabularies, covering external conditions at transaction execution time (venue availability, wallet funding) that existing transactional constraints cannot address. Extends agent authorization mandate frameworks with environmental precondition checking.</t>
+          <t>Defines semantic capability advertisement and intent-driven routing at DMSC agent gateways: agents publish capability profiles in a structured format and the gateway matches incoming task intents to available agents, replacing fixed-address routing with dynamic semantic matching. The core routing-layer protocol for DMSC inter-agent communication.</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-borthwick-msebenzi-environment-state/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sz-dmsc-iaip/</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 13 Jun 2026; authors: Douglas Cameron Borthwick (InsumerAPI), Michael Msebenzi (Headless Oracle). Narrow but practically important for financial and commerce agent workflows; connects to draft-mcgraw-httpapi-agent-budget and draft-vauban-x402-delegation-binding.</t>
+          <t>Revision -02, May 2026; authors: Sheng Sun, Xinyi Zhang (CAS/CNIC), Qiangzhou Gao (Huawei), Min Liu, Yuwei Wang (ICT, CAS). The intent-based routing mechanism that distinguishes DMSC from address-based protocols; relevant to the DAWN boundary question — DMSC embeds discovery in the gateway routing layer rather than treating it as a separate protocol.</t>
         </is>
       </c>
     </row>
@@ -4705,17 +4705,17 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>draft-chen-oauth-agent-authz-use-cases — Agent Authorization Use Cases and Gap Analysis for OAuth 2.0</t>
+          <t>draft-yang-dmsc-ioa-task-protocol — Internet of Agents Task Protocol for Heterogeneous Agent Collaboration</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>A framework-level analysis enumerating agentic authorization use cases — delegated task execution, multi-agent coordination, long-running workflows, capability attenuation — and mapping each against current OAuth 2.0 mechanisms to identify gaps that require new extensions or profiles.</t>
+          <t>Establishes a session and task coordination layer with finite-state-machine-based dialogue management, dynamic team assembly, and nested team hierarchies for distributed heterogeneous agent collaboration. Addresses the multi-agent task lifecycle from assignment through completion and audit across heterogeneous agent implementations.</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-chen-oauth-agent-authz-use-cases/</t>
+          <t>https://datatracker.ietf.org/doc/draft-yang-dmsc-ioa-task-protocol/</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 5 Jul 2026; useful problem-statement companion to the OAuth recharter's 'Complex Delegation' milestone. Gap analysis directly motivates several other drafts in this corpus — a natural reference document for the OAuth WG scoping discussion.</t>
+          <t>Revision -03, Apr 21 2026; authors: Cheng Yang (BUPT), Zhiyuan Liu (Tsinghua), Aijun Wang (China Telecom). The task-coordination layer above the DMSC gateway routing; covers multi-domain and 6G/ITS scenarios. Distinct from OAuth-layer delegation in that it orchestrates task state rather than token issuance.</t>
         </is>
       </c>
     </row>
@@ -4735,17 +4735,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>draft-agnihotri-oauth-agent-impl-status — Implementation Status of OAuth Identity Chaining and Transaction Tokens</t>
+          <t>draft-dunbar-dmsc-gw-scenarios-gap-analysis — Deployment Scenarios and Gap Analysis for AI Agent Gateway</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>An RFC 7942–compliant implementation status report tracking open-source implementations of draft-ietf-oauth-identity-chaining and draft-ietf-oauth-transaction-tokens against the relevant spec requirements.</t>
+          <t>Surveys single-domain to multi-domain deployment scenarios for AI Agent Gateways and identifies concrete gaps where existing protocols (specifically MCP and Google's A2A) cannot satisfy governance, policy enforcement, and cross-organizational trust requirements — particularly in regulated financial services and telecom environments.</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-agnihotri-oauth-agent-impl-status/</t>
+          <t>https://datatracker.ietf.org/doc/draft-dunbar-dmsc-gw-scenarios-gap-analysis/</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, Jun 2026; provides the implementation evidence required to advance both WG drafts toward IESG submission. Informational companion to the two WG drafts — not a protocol spec but tracking their standardization progress.</t>
+          <t>Revision -02, Jul 2 2026; authors: Linda Dunbar (Futurewei), YiFei Wang (China Telecom), Bing Liu (Huawei). The most directly useful DMSC document for the boundary analysis: explicitly names MCP and A2A as insufficient and articulates where the DMSC gateway fills the gap. The regulated-environment focus (financial services, telco) distinguishes DMSC's use-case target from OAuth-centric approaches.</t>
         </is>
       </c>
     </row>
@@ -4765,17 +4765,17 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>draft-hardt-oauth-aauth-protocol — AAuth Protocol</t>
+          <t>draft-somoza-dmsc-atn-agent-trust-negotiation — Agent Trust Negotiation: Capability, Delegation, and Provenance Binding</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>A new clean-sheet authorization protocol from Dick Hardt (original OAuth author) defining proof-of-possession by default, resource-signed challenges, agent identity without pre-registration, deferred 202 responses, and AS-to-AS federation for the agent ecosystem.</t>
+          <t>Specifies the Agent Trust Negotiation (ATN) protocol, which binds four artifacts — capability manifests, delegation chains, provenance attestations, and session receipts — to agent identities via a handshake state machine producing mutually verified, scope-bounded sessions with SCITT-suitable audit records.</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-hardt-oauth-aauth-protocol/</t>
+          <t>https://datatracker.ietf.org/doc/draft-somoza-dmsc-atn-agent-trust-negotiation/</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>Revision -09, Jul 4 2026; slug gained 'oauth' infix at this revision (was draft-hardt-aauth-protocol). Now formally adds four resource access modes including agent governance. The design rationale section explicitly explains why AAuth is not GNAP, not OAuth, not DPoP and not mTLS — important read for anyone planning a new agent-auth stack. OUTLIER: zero OAuth dependencies.</t>
+          <t>Revision -00, 29 May 2026; author: Enrique Somoza (Independent). Operates above discovery mechanisms and positions itself between the discovery layer (DAWN, MCP) and the authorization layer (WIMSE, OAuth). Relevant as an agent-to-agent trust establishment handshake protocol.</t>
         </is>
       </c>
     </row>
@@ -4795,17 +4795,17 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>draft-chen-oauth-roadmap — Comprehensive Roadmap for OAuth 2.0 Standards and Drafts</t>
+          <t>draft-mcgraw-httpapi-agent-budget — The Delegation HTTP Authentication Scheme for Request-Bound Authority</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>An IETF informational draft that maps the entire OAuth 2.0 ecosystem of RFCs, BCPs, and active drafts into functional layers from core to extensions to industry profiles.</t>
+          <t>Defines the 'Delegation' HTTP authentication scheme and response semantics for delegated-authority challenges using HTTP status codes and Problem Details, plus a CBOR/COSE proof format. The initial authority profile is 'Budget,' using post-quantum ML-DSA to prove spending or resource-consumption limits.</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>https://www.ietf.org/archive/id/draft-chen-oauth-roadmap-00.html</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcgraw-httpapi-agent-budget/</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>Brand-new -00 draft (May 2026); the single most useful index when starting work in this area.</t>
+          <t>Revision -02, 15 Jun 2026; author: John Paul McGraw Jr. (TaskHawk Systems). HTTP-layer bounded delegation with post-quantum crypto; distinct from OAuth-layer delegation in that the authority proof travels in the Authorization header. Complements x401 (Industry tab) at the HTTP challenge-response layer.</t>
         </is>
       </c>
     </row>
@@ -4825,27 +4825,27 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>draft-ietf-wimse-workload-creds — WIMSE Workload Credentials</t>
+          <t>draft-vauban-x402-delegation-binding — x402 Delegation Binding for Agentic HTTP Pipelines</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>Defines the credential format and issuance profile for workload credentials in the WIMSE architecture, covering service-to-service authentication token types, local issuance mechanisms, and token exchange profiles for cross-trust-domain workload identity scenarios.</t>
+          <t>Addresses the security gap where x402 V2 payment grants issued to one agent could be misused by another in the same pipeline, introducing three binding mechanisms: a JCS-derived agent identity pseudonym, a nonce for anti-replay, and a depth-limiting field for transitive delegation.</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-wimse-workload-creds/</t>
+          <t>https://datatracker.ietf.org/doc/draft-vauban-x402-delegation-binding/</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>IETF (WIMSE WG)</t>
+          <t>IETF (individual)</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, Jul 2026; WIMSE WG-adopted. The credential issuance companion to draft-ietf-wimse-arch (architecture) and draft-ietf-wimse-identifier (identifiers) already in corpus. Three WG drafts now cover the full WIMSE stack: arch → identifier → workload-creds. Relevant to the WIMSE agent extension family (ni-wimse, reece, jiang, schwenkschuster) which assumes a credential format this draft now specifies.</t>
+          <t>Revision -01, 25 May 2026; author: Vauban Research. Narrowly scoped to payment pipelines but the delegation-binding pattern (pseudonymous identity + anti-replay + depth-limit) is applicable broadly. Validated across five language runtimes with A2A and MCP integration guidance.</t>
         </is>
       </c>
     </row>
@@ -4855,25 +4855,265 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
+          <t>draft-samal-vap — Verifiable Agent Protocol (VAP): Intent-Bound Admission Control and Audit for Agent Tool Invocation</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>Specifies VAP as a defense-in-depth layer adding declarations of purpose and session budget commitments to tool invocation requests (targeting MCP-style protocols), enabling servers to perform admission control before execution via four messages carried in existing protocol metadata.</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-samal-vap/</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 3 Jun 2026; author: Kruttidipta Samal (Independent). Lightweight and protocol-agnostic; addresses erroneous agent behavior, cost control, and audit trails without replacing existing auth mechanisms. Practical tool-invocation-level authorization layer for MCP deployments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>draft-khera-aurora — Agent Unification, Runtime, and Operational Responsibility Attestation (AURORA)</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>A two-layer framework unifying hardware-enclave-backed Runtime Integrity Attestation with scoped, cryptographically bound Authority Delegation; enables agents to prove both operational authority and runtime integrity simultaneously.</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-khera-aurora/</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 5 Jun 2026; author: Ankur Khera. Addresses the gap where delegation tokens don't prove the runtime environment is trustworthy — relevant where delegation must be paired with platform attestation (enterprise/regulated deployments). Bridges the RATS attestation thread and the OAuth delegation thread.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>draft-borthwick-msebenzi-environment-state — Verifiable Intent — environment.* Constraint Family</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>Defines the environment.* constraint family for agent-authorization mandate vocabularies, covering external conditions at transaction execution time (venue availability, wallet funding) that existing transactional constraints cannot address. Extends agent authorization mandate frameworks with environmental precondition checking.</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-borthwick-msebenzi-environment-state/</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 13 Jun 2026; authors: Douglas Cameron Borthwick (InsumerAPI), Michael Msebenzi (Headless Oracle). Narrow but practically important for financial and commerce agent workflows; connects to draft-mcgraw-httpapi-agent-budget and draft-vauban-x402-delegation-binding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>draft-chen-oauth-agent-authz-use-cases — Agent Authorization Use Cases and Gap Analysis for OAuth 2.0</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>A framework-level analysis enumerating agentic authorization use cases — delegated task execution, multi-agent coordination, long-running workflows, capability attenuation — and mapping each against current OAuth 2.0 mechanisms to identify gaps that require new extensions or profiles.</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-chen-oauth-agent-authz-use-cases/</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 5 Jul 2026; useful problem-statement companion to the OAuth recharter's 'Complex Delegation' milestone. Gap analysis directly motivates several other drafts in this corpus — a natural reference document for the OAuth WG scoping discussion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>draft-agnihotri-oauth-agent-impl-status — Implementation Status of OAuth Identity Chaining and Transaction Tokens</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>An RFC 7942–compliant implementation status report tracking open-source implementations of draft-ietf-oauth-identity-chaining and draft-ietf-oauth-transaction-tokens against the relevant spec requirements.</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-agnihotri-oauth-agent-impl-status/</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, Jun 2026; provides the implementation evidence required to advance both WG drafts toward IESG submission. Informational companion to the two WG drafts — not a protocol spec but tracking their standardization progress.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>draft-hardt-oauth-aauth-protocol — AAuth Protocol</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>A new clean-sheet authorization protocol from Dick Hardt (original OAuth author) defining proof-of-possession by default, resource-signed challenges, agent identity without pre-registration, deferred 202 responses, and AS-to-AS federation for the agent ecosystem.</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hardt-oauth-aauth-protocol/</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>Revision -09, Jul 4 2026; slug gained 'oauth' infix at this revision (was draft-hardt-aauth-protocol). Now formally adds four resource access modes including agent governance. The design rationale section explicitly explains why AAuth is not GNAP, not OAuth, not DPoP and not mTLS — important read for anyone planning a new agent-auth stack. OUTLIER: zero OAuth dependencies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>draft-chen-oauth-roadmap — Comprehensive Roadmap for OAuth 2.0 Standards and Drafts</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>An IETF informational draft that maps the entire OAuth 2.0 ecosystem of RFCs, BCPs, and active drafts into functional layers from core to extensions to industry profiles.</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ietf.org/archive/id/draft-chen-oauth-roadmap-00.html</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>Brand-new -00 draft (May 2026); the single most useful index when starting work in this area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>draft-ietf-wimse-workload-creds — WIMSE Workload Credentials</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>Defines the credential format and issuance profile for workload credentials in the WIMSE architecture, covering service-to-service authentication token types, local issuance mechanisms, and token exchange profiles for cross-trust-domain workload identity scenarios.</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-wimse-workload-creds/</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>IETF (WIMSE WG)</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, Jul 2026; WIMSE WG-adopted. The credential issuance companion to draft-ietf-wimse-arch (architecture) and draft-ietf-wimse-identifier (identifiers) already in corpus. Three WG drafts now cover the full WIMSE stack: arch → identifier → workload-creds. Relevant to the WIMSE agent extension family (ni-wimse, reece, jiang, schwenkschuster) which assumes a credential format this draft now specifies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
           <t>Charter: WIMSE — Workload Identity in Multi-System Environments (charter-ietf-wimse-01)</t>
         </is>
       </c>
-      <c r="C132" s="5" t="inlineStr">
+      <c r="C140" s="5" t="inlineStr">
         <is>
           <t>The formal IETF charter for the WIMSE WG covering architecture, JOSE-based WIMSE tokens for service-to-service traffic, local token issuance, and token exchange profiles (likely based on RFC 8693) for cross-trust-domain workload identity.</t>
         </is>
       </c>
-      <c r="D132" s="9" t="inlineStr">
+      <c r="D140" s="9" t="inlineStr">
         <is>
           <t>https://datatracker.ietf.org/doc/charter-ietf-wimse/01/</t>
         </is>
       </c>
-      <c r="E132" s="5" t="inlineStr">
+      <c r="E140" s="5" t="inlineStr">
         <is>
           <t>IETF (WIMSE WG charter)</t>
         </is>
       </c>
-      <c r="F132" s="5" t="inlineStr">
+      <c r="F140" s="5" t="inlineStr">
         <is>
           <t>Approved 18 March 2026 (v01); explicitly liaises with OAuth, SCIM, SCITT, RATS, the OpenID Foundation, and CNCF/SPIFFE — the formal scope statement that anchors all WIMSE draft work.</t>
         </is>
@@ -5012,6 +5252,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId139"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5420,7 +5668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5589,17 +5837,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>NIST AI Agent Standards Initiative — Center for AI Standards and Innovation</t>
+          <t>NIST NCCoE Concept Paper — Accelerating the Adoption of Software and AI Agent Identity and Authorization</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>A NIST initiative within the Center for AI Standards and Innovation aimed at accelerating adoption of software and AI-agent identity and authorization standards.</t>
+          <t>US government concept paper proposing a National Cybersecurity Center of Excellence demonstration project for AI agent identity and authorization using OAuth 2.0, SPIFFE/SPIRE, and MCP; explicitly asks whether existing identity standards can serve AI agents without new standards and invites industry collaboration.</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/ai</t>
+          <t>https://csrc.nist.gov/pubs/other/2026/02/05/accelerating-the-adoption-of-software-and-ai-agent/ipd</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -5609,7 +5857,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>February 2026 NCCoE concept paper on 'Accelerating the Adoption of Software and AI Agent Identity and Authorization' is the key entry point.</t>
+          <t>Published Feb 5 2026; public comment closed Mar 9 2026. First US government program explicitly addressing interoperability and security standards for agentic AI. Directly references OAuth 2.0, SPIFFE/SPIRE, and MCP — the same stack the IETF corpus is standardizing — as the candidate technology foundation.</t>
         </is>
       </c>
     </row>
@@ -5619,25 +5867,55 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
+          <t>NSA Cybersecurity Information Sheet — MCP Security Design Considerations for AI-Driven Automation</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>17-page US government guidance on Model Context Protocol security risks and mitigations; identifies uncontrolled automated action escalation, lack of input screening, and overload attack susceptibility as primary risks; recommends filtering proxies and tight resource URL pinning beyond MCP's own documentation.</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>https://www.nsa.gov/Portals/75/documents/Cybersecurity/CSI_MCP_SECURITY.pdf</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>NSA (US government)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Published May 20 2026. NSA-tier imprimatur on MCP security; first US government guidance specifically on MCP. The risk categories (escalation, input screening gaps, overload) complement the IETF WebBotAuth and OAuth WG work that addresses the same attack surface from the standards side.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
           <t>EU AI Act broader enforcement (high-risk AI systems audit trails, August 2026)</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>EU regulation requiring auditable trails for high-risk AI systems, which in practice mandates the kind of cryptographic delegation chains being standardized in IETF agent drafts.</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>https://artificialintelligenceact.eu/</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>European Union (regulation)</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Compliance deadline shapes urgency for delegation-chain standardization; many vendors target Aug 2026 readiness.</t>
         </is>
@@ -5651,6 +5929,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5662,7 +5941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5855,6 +6134,216 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Authorization Propagation in Multi-Agent AI Systems: Identity Governance as Infrastructure (Tallam, arXiv:2605.05440)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Formalizes 'authorization propagation' as a distinct multi-agent security problem irreducible to prompt injection or classical RBAC/ABAC/ReBAC; identifies transitive delegation, aggregation inference, and temporal validity as three distinct sub-problems; derives seven structural requirements for multi-agent authorization architectures.</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.05440</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Published May 6 2026; author: Krti Tallam. The formal treatment maps directly onto the delegation-chain and audit-architecture cluster in the corpus. Introduces 'authorization propagation' as a term of art for the multi-hop delegation security problem that RFC 8693 and the Transaction Token family address at the protocol layer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Overlaying Governance: A Compositional Authorization Framework for Delegation and Scope in Agentic AI (Ibrahim &amp; Li, arXiv:2606.03518)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Introduces a compositional operator that overlays agentic authorization semantics — recursive delegation chains, time-limited authority, resource scope attenuation — onto existing relational policies without rewriting them; treats scope attenuation as a first-class primitive bounding an agent's access envelope.</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.03518</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Published Jun 2 2026; authors: Amjad Ibrahim, Yong Li. 'Resource scope attenuation' is the formal complement to what RAR-for-agents (draft-ietf-oauth-transaction-tokens) and the Mission-Bound OAuth series address at the protocol level. Provides the mathematical framing the IETF drafts reference but do not state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>SkillScope: Toward Fine-Grained Least-Privilege Enforcement for Agent Skills (Wu et al., arXiv:2605.05868)</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Uses graph-based static analysis to identify and constrain over-privileged agent skills (capability bundles packaging instructions and executable resources); validates against 68,312 real-world skills and finds 7,039 over-privileged; constrains over-privilege action instances by 88.56% while preserving task completion.</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.05868</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Published May 7 2026; authors: Jiangrong Wu, Yuhong Nan, Yixi Lin, et al. Empirical least-privilege measurement at production scale — the quantitative evidence base the protocol-layer corpus is missing. Graph-static-analysis approach complements the token-attenuation drafts (niyikiza-oauth-attenuating-agent-tokens, rampalli-pedigree) which enforce attenuation at runtime; SkillScope enforces it pre-deployment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>SUDP: Secret-Use Delegation Protocol for Agentic Systems (Yu et al., arXiv:2604.24920)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Formalizes the 'Agent Secret Use' problem — agents must cause user-authorized secret-backed operations without retaining reusable authority over those secrets — and proposes a three-role protocol (Requester, Authorizer, Custodian) with seven security properties covering authorization integrity and secret confidentiality.</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.24920</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Published Apr 27 2026 (v3 May 22 2026); author: Xiaohang Yu et al. Directly formalizes the problem that draft-sweeney-wimse-credential-delegation's credential-wrapping mechanism (raw tokens never reach the agent) addresses at the protocol layer. SUDP is the formal proof that credential-wrapping is necessary; sweeney is a concrete protocol instantiation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Before the Tool Call: Deterministic Pre-Action Authorization for Autonomous AI Agents (arXiv:2603.20953)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Proposes Open Agent Passport (OAP), an open specification that intercepts tool calls synchronously before execution, evaluates them against a declarative policy, and produces cryptographically signed audit records; enforces authorization decisions at 53ms median latency.</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2603.20953</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Published Mar 21 2026. Addresses the enforcement gap between token issuance and actual tool execution that OAuth alone cannot close — the protocol-layer corpus focuses on issuance-side mechanisms; OAP is the first empirically validated enforcement-side proposal with latency numbers. Complements draft-munoz-scitt-permit-profile (pre-execution permit) and the EMILIA Protocol family (post-execution receipts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Open Challenges in Multi-Agent Security (de Witt et al., arXiv:2505.02077)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Introduces 'multi-agent security' as a new field distinct from AI safety and traditional cybersecurity; covers threats emerging from agent-to-agent interaction — secret collusion, coordinated swarm attacks, disinformation cascades, and evasion via dispersion; derives a unified research agenda across AI security, multi-agent learning, distributed systems, and governance.</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2505.02077</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Published May 5 2025 (latest version Apr 29 2026); authors: Christian Schroeder de Witt + 23 co-authors (Oxford, DeepMind, MIT, others). 24-author collaboration is a strong legitimacy signal. The inter-agent trust threat model is directly relevant to the audit-architecture and delegation-chain clusters; provides the threat landscape that the IETF drafts respond to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Governing Dynamic Capabilities: Cryptographic Binding and Reproducibility Verification for AI Agent Tool Use (Zhou, arXiv:2603.14332)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Identifies the 'capability-identity gap' — agents acquire capabilities at runtime via MCP and A2A post-authorization, enabling silent capability escalation; proposes capability-bound agent certificates (X.509 v3 extensions with skills manifest hash), reproducibility commitments using LLM near-determinism, and a hash-linked verifiable interaction ledger.</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2603.14332</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Published Mar 2026; author: Ziling Zhou (Genupixel Technology). The capability-identity gap concept is distinct from what the current corpus addresses — token-attenuation drafts bound authority at issuance, but this gap occurs post-issuance as agents dynamically load new tools. Thematically adjacent to draft-sharif-x509-agent-identity-profile which also uses X.509v3 extensions for agent capability binding.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
@@ -5862,6 +6351,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5873,7 +6369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6312,27 +6808,27 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Solving the Identity Crisis for AI Agents (Uber Engineering)</t>
+          <t>Mission Architecture on AAuth (McGuinness, 15 Mar 2026)</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>A production engineering post from Uber describing their agent identity architecture: an Agent Registry (workload-to-agent mapping), a SPIRE-backed STS that issues short-lived JWTs with embedded actor chains at P99 below 40ms, an MCP Gateway as policy enforcement point, and an AI Agent Mesh for agent-to-agent communication. A standardized A2A client automates token exchange and chain propagation across agent hops.</t>
+          <t>Engages directly with Dick Hardt's AAuth protocol, examining whether AAuth's conversational flow and native agent identity could host Mission governance better than OAuth; concludes both architectures require an explicit, durable Mission object for lifecycle governance, approval evidence, and actor continuity — AAuth's strengths are transport-level, not governance-level.</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>https://www.uber.com/us/en/blog/solving-the-agent-identity-crisis/</t>
+          <t>https://notes.karlmcguinness.com/notes/mission-architecture-on-aauth/</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Industry blog (Uber Engineering)</t>
+          <t>Architect blog (Karl McGuinness)</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Published 21 May 2026; six-author post (Mathew, Borole, Huang, Burykin, Goel, Walsh) from Uber's platform engineering team. Architecture aligns with WIMSE workload identity (SPIRE as the credential foundation), RFC 8693 actor-chain propagation, and single-hop short-lived JWTs with audience-scoped claims. One of the few public disclosures of a production-grade agent identity system at hyperscaler scale — a real-world reference point for the corpus's delegation-chain design patterns.</t>
+          <t>Published Mar 15 2026; the fifth McGuinness blog entry in the corpus (the four-part Mission-Bound series above plus this standalone analysis). Significant because it directly engages draft-hardt-oauth-aauth-protocol (the corpus OUTLIER — zero OAuth dependencies), bridging the two most architecturally influential individual contributors in the corpus. McGuinness argues Mission governance requires a durable object regardless of transport; Hardt argues PoP-by-default and AS-to-AS federation require architectural replacement. These positions are complementary at different layers.</t>
         </is>
       </c>
     </row>
@@ -6342,27 +6838,27 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Agents Are Not Just Workloads (Patrick Parker, LinkedIn)</t>
+          <t>Enterprise-Managed Authorization for MCP (Paul Carleton, Anthropic MCP Blog, 18 Jun 2026)</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Argues that classifying AI agents as 'workloads' is a category error that corrupts identity architecture: workloads are a what-runs-where concept, agents are a who-acts-on-whose-authority concept. Identifies five breakdown areas where workload-identity patterns fail for agents: intent captured as static token claims, delegation gaps (no purpose binding or revocation paths), overlooked tool-catalog authorization surface, bearer-credential custody ambiguity under prompt injection, and mutable logs insufficient as tamper-evident authorization evidence.</t>
+          <t>Announces Enterprise-Managed Authorization (EMA) extension enabling SSO-based MCP server provisioning through enterprise identity providers, eliminating per-app OAuth friction; explicitly uses the Identity Assertion JWT Authorization Grant (ID-JAG) as the underlying token exchange mechanism. Early adopters include Okta, Claude, VS Code, Asana, Atlassian, Figma, and Supabase.</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/pulse/agents-just-workloads-patrick-parker-0qxte/</t>
+          <t>https://blog.modelcontextprotocol.io/posts/enterprise-managed-auth/</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Industry blog (LinkedIn)</t>
+          <t>Vendor blog (Anthropic / MCP)</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Published 9 Jun 2026. Proposes signature-based receipts binding relationships, authority, tasks, and bounds; runtime validation of generated task intent; and AuthZEN gateway-based enforcement. A principled counterpoint to the WIMSE-as-sufficient-for-agents framing — pairs well with the Uber Engineering post (which uses SPIRE/WIMSE as the credential foundation but adds actor chains and MCP gateway enforcement on top).</t>
+          <t>Published Jun 18 2026; author: Paul Carleton (MCP Core Maintainer). One of the first production deployments of draft-ietf-oauth-identity-assertion-authz-grant (ID-JAG, corpus WG draft) at enterprise scale. Multi-vendor adoption (8 platforms at launch) signals ID-JAG is de-facto production-ready even before RFC publication. Cross-App Access from Okta is the identity provider backbone.</t>
         </is>
       </c>
     </row>
@@ -6372,27 +6868,27 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Creating a Relationship Binding (Tom Jones)</t>
+          <t>Workload Identity: Key Takeaways from IETF 122 (Kasselman, Defakto Security, 26 Mar 2025)</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>A community whitepaper proposing a signed 'Consent to Create Binding' JWT/JWS message that establishes a subject-bound relationship identifier (UUID or DID) between a user and a set of agents or service providers. The message carries 16 mandatory/optional fields: issuer, subject, subject role, context (trust framework), permissions, device statement, identity proof, purpose of use, key material, and signature. Includes a lifecycle termination model (session, cookie, transaction, relationship, and legal-based retention scopes) and a companion 'Consent Receipt with Binding' response. A second section argues that relationship-based governance — binding actors through mutual obligations, escalation paths, and accountability chains — is more resilient for AI agent systems than representational approaches (policies, classifications, static maps).</t>
+          <t>Reports on WIMSE WG's adoption of three working-group drafts at IETF 122: WIMSE Architecture, Service-to-Service Authentication, and Workload Identity Practices; addresses AI agent identity requirements — credentialing every AI workload, least-privilege scope, and permission escalation mechanisms — within the WIMSE framework.</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>https://docs.google.com/document/d/1CwBDRbw147YlNld-UOlJ4lGvmpDIOCSI/edit#heading=h.kp911j18z01y</t>
+          <t>https://www.defakto.security/blog/workload-identity-key-takeaways-from-ietf-122/</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Community whitepaper</t>
+          <t>Practitioner blog (Defakto Security)</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>No publication date in the document; primary use case is healthcare (NIST IAL2/AAL2). Draws on Kantara's Distribute Assurance Specification for identity assurance levels and references OpenID Connect id_token as the closest existing message shape. The Consent to Create Binding message adds purpose of use, device statement, and lifecycle termination semantics that id_token lacks. Companion doc 'Digital Contracts Made Legally Valid' (separate Google Doc) covers giving the binding legal status. Relationship-governance argument is thematically aligned with Parker's 'Agents Are Not Just Workloads' — both argue that accountability chains and mutual obligations are the right governance primitive for agentic systems.</t>
+          <t>Published Mar 26 2025; author: Pieter Kasselman (VP Open Standards, Defakto Security) — co-author of draft-klrc-aiagent-auth, draft-fletcher-transaction-token-chaining-profile, and draft-ietf-oauth-first-party-apps (all in corpus). Documents the WIMSE WG milestone that provides the workload-identity substrate for the AI agent extension family; useful primary-source account of the IETF milestone from the author who subsequently filed klrc-aiagent-auth.</t>
         </is>
       </c>
     </row>
@@ -6402,27 +6898,27 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Intent Agent Native Authorization for Agentic Profiles (IANA-AP) (Martin Besozzi, Jul 2026)</t>
+          <t>Whither User-Managed Access in the AI Agent Era? (Eve Maler, Venn Factory, 10 Jul 2025)</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Proposes a four-phase runtime authorization lifecycle for AI agents: discovery (agent capabilities + API authorization mappings), intent computation (agent generates planned operations), review/approval (user provides explicit phishing-resistant consent via WebAuthn/FIDO2 passkeys before execution), and enforcement (every runtime invocation validated against the approved authorization artifact). Composes RFC 9396 RAR, OAuth FiPA, OpenID AuthZEN, MCP, SPIFFE JWT-SVIDs, and CEL policy mappings into a single coherent framework.</t>
+          <t>Examines whether UMA 2.0 remains relevant for AI agent delegation, distinguishing whether agents function as OAuth client apps or as requesting parties with their own legal standing; argues UMA 'basically exists for this' but identifies gaps: dynamic resource discovery, multi-level delegation tracking, and the need for standardized infrastructure analogous to Microsoft's On-Behalf-Of flow.</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>https://embesozzi.github.io/posts/martin-besozzi/intent-agent-native-authorization-agentic-profiles/</t>
+          <t>https://workshop.vennfactory.com/p/whither-user-managed-access-in-the</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Architect blog (Martin Besozzi)</t>
+          <t>Practitioner blog (Venn Factory)</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Updated July 2026; includes open specification and reference implementation on GitHub. The SARC (Subject, Action, Resource, Context) model and 'x-authz-mapping' Agentic Profile extension are novel additions. The four-phase pre-execution approval requirement directly parallels draft-nelson-agent-delegation-receipts and draft-sato-soos-idp — but grounds it in existing OAuth standards rather than new protocol primitives. One of the few practitioner-level posts that explicitly composes AuthZEN, RAR, and FiPA into a working agent authorization flow.</t>
+          <t>Published Jul 10 2025; author: Eve Maler (primary author of UMA 2.0, former VP Innovation at ForgeRock, W3C TAG). The UMA specification is in the Other Standards &amp; Govt tab; this is the spec author's own analysis of its applicability to AI agents. Identifies the same gaps (dynamic resource discovery, multi-level delegation) that the DAWN and identity-chaining IETF work addresses — useful bridge between the Kantara UMA entry and the active IETF corpus.</t>
         </is>
       </c>
     </row>
@@ -6432,27 +6928,27 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>AI Agent Authentication Gets the Hard Part Right. Authorization Is Still Your Problem. (Rock Cyber Musings)</t>
+          <t>Tangled Tokens and Authorized Agents (Justin Richer, 15 May 2025)</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>An analyst article arguing the new IETF agent-auth draft solves authentication via SPIFFE+WIMSE+OAuth but leaves authorization and policy enforcement as an unsolved open problem.</t>
+          <t>Examines how MCP's proxy model creates two distinct authorization contexts (agent-to-MCP-server and server-to-upstream-resource) that OAuth's pre-registration assumptions don't accommodate cleanly; argues for credential-mapping strategies adapted from email IMAP patterns and identifies unresolved tensions around static OAuth registration and MCP server allowlisting.</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>https://www.rockcybermusings.com/p/i-agent-authentication-authorization-gap</t>
+          <t>https://justinsecurity.medium.com/tangled-tokens-and-authorized-agents-331e4db02fb4</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Industry analysis blog</t>
+          <t>Practitioner blog (Justin Richer)</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Maps the IETF draft against MCP and the Colorado AI Act 'reasonable care' standard; pragmatic implementer perspective.</t>
+          <t>Published May 15 2025; author: Justin Richer (independent OAuth expert, co-author of OAuth 2.0 in Action, former GNAP WG co-chair). The IMAP credential-mapping analogy is the most concrete prior-art framing for the MCP authorization problem. Complements the Dan Moore Stack Overflow Blog post (below) which covers the MCP OAuth 2.1 spec detail; this post covers the architectural gap the spec doesn't resolve.</t>
         </is>
       </c>
     </row>
@@ -6462,27 +6958,27 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Agent Authentication &amp; Delegated Access (Zylos Research, April 2026)</t>
+          <t>Is That Allowed? Authentication and Authorization in Model Context Protocol (Dan Moore, Stack Overflow Blog, 21 Jan 2026)</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>A research-style industry article surveying OAuth flows, scoped tokens, and identity patterns specifically for AI agents, covering OAuth 2.1 baselines and chain-splicing risks.</t>
+          <t>Technical walkthrough of MCP's OAuth 2.1 implementation: Authorization Code grant with mandatory PKCE, RFC 9728 protected resource metadata for server discovery, and the RFC 8707 resource parameter; explicitly names the gap that MCP spec does not mandate how servers authenticate with backend services.</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>https://zylos.ai/research/2026-04-11-agent-authentication-delegated-access-oauth-scoped-tokens</t>
+          <t>https://stackoverflow.blog/2026/01/21/is-that-allowed-authentication-and-authorization-in-model-context-protocol/</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Industry research blog</t>
+          <t>Practitioner blog (Stack Overflow Blog)</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Documents the 'delegation chain splicing' attack against RFC 8693 actor-token chains formally raised on the OAuth WG list in early 2026.</t>
+          <t>Published Jan 21 2026; author: Dan Moore (Head of Developer Relations, FusionAuth). Directly references RFC 8414 (OAuth Server Metadata), RFC 8707 (Resource Indicators), RFC 9728 (Protected Resource Metadata) — all IETF corpus entries. Stack Overflow Blog platform gives this mainstream engineering reach. The gap identified (server-to-backend auth unspecified by MCP) is the same gap that draft-ietf-oauth-identity-assertion-authz-grant and klrc-aiagent-auth address.</t>
         </is>
       </c>
     </row>
@@ -6492,27 +6988,27 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>AuthZEN + Shared Signals Framework Series (Andrew Doering)</t>
+          <t>AI Agent Authentication Gets the Hard Part Right. Authorization Is Still Your Problem. (Rock Lambros, RockCyber Musings, 17 Mar 2026)</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>A multi-part technical blog walking through how AuthZEN (synchronous PDP/PEP) and SSF/CAEP (asynchronous events) combine into a continuous-authorization loop in real Microsoft Entra/M365 deployments.</t>
+          <t>Analyzes draft-klrc-aiagent-auth-00 in depth, praising its identity layer (WIMSE + SPIFFE composition) but flagging that the Security Considerations section contains only 'TODO Security'; recommends layering OPA or Cedar policy engines for actual authorization and names AuthZEN as a candidate gap-filler.</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>https://andrewdoering.org/blog/2026/authzen-shared-signals-framework-part-1-fundamentals/</t>
+          <t>https://www.rockcybermusings.com/p/i-agent-authentication-authorization-gap</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Industry blog</t>
+          <t>Practitioner blog (RockCyber Musings)</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Documents the 2026 asymmetry where Microsoft Entra is a CAEP transmitter for closed-loop CAE but not an external SSF receiver.</t>
+          <t>Published Mar 17 2026; author: Rock Lambros. One of the few practitioner posts that analyzes a specific IETF draft (draft-klrc-aiagent-auth, corpus) in depth and names the authorization gap that authentication alone doesn't close. The 'TODO Security' observation is accurate as of the -00 filing; check subsequent revisions for resolution.</t>
         </is>
       </c>
     </row>
@@ -6522,27 +7018,27 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Just-in-Time Authorization with OpenID SSE and CAEP (The New Stack, Tulshibagwale)</t>
+          <t>Least Privilege for AI Agents: Identity, Access, and Tool Binding (Microsoft Security Blog, 16 Jul 2026)</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>An article from CAEP's original inventor explaining how SSE+CAEP enable just-in-time authorization decisions instead of long-lived session-based access.</t>
+          <t>Microsoft's blueprint for applying least-privilege to agentic workloads: unique dedicated agent principals with named owners and explicit purpose statements, task-based roles scoped to specific resources, controlled tool access allowlists, and end-to-end auditability requirements; positions agent identity as a first-class security principal requiring the same governance as human identities.</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>https://thenewstack.io/just-in-time-authorization-with-openid-sse-and-caep/</t>
+          <t>https://www.microsoft.com/en-us/security/blog/2026/07/16/least-privilege-for-ai-agents-identity-access-and-tool-binding/</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Industry article (The New Stack)</t>
+          <t>Vendor blog (Microsoft Security)</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Background piece by Atul Tulshibagwale (SGNL CTO, CAEP inventor) explaining the architectural intent.</t>
+          <t>Published Jul 16 2026. Microsoft's most recent major position on least-privilege for agents; extends the earlier Azure and Microsoft Entra entries in the corpus with specific tool-binding guidance. The named-owner and explicit-purpose-statement requirements align directly with Mission-Bound OAuth's proposal_hash and consent_rendering_hash binding. First Microsoft Security Blog entry to use 'tool binding' as a security term of art.</t>
         </is>
       </c>
     </row>
@@ -6552,27 +7048,27 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>How AuthZEN, Shared Signals &amp; CAEP Complement Each Other (OpenID Foundation)</t>
+          <t>Solving the Identity Crisis for AI Agents (Uber Engineering)</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>An OpenID Foundation explainer arguing that AuthZEN and SSF/CAEP are complementary — sync access decisions vs async session updates — not competing standards.</t>
+          <t>A production engineering post from Uber describing their agent identity architecture: an Agent Registry (workload-to-agent mapping), a SPIRE-backed STS that issues short-lived JWTs with embedded actor chains at P99 below 40ms, an MCP Gateway as policy enforcement point, and an AI Agent Mesh for agent-to-agent communication. A standardized A2A client automates token exchange and chain propagation across agent hops.</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>https://openid.net/how-authzen-and-shared-signals-caep-complement-each-other/</t>
+          <t>https://www.uber.com/us/en/blog/solving-the-agent-identity-crisis/</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>OpenID Foundation</t>
+          <t>Industry blog (Uber Engineering)</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Useful when explaining the layering to stakeholders confused by the OpenID alphabet soup.</t>
+          <t>Published 21 May 2026; six-author post (Mathew, Borole, Huang, Burykin, Goel, Walsh) from Uber's platform engineering team. Architecture aligns with WIMSE workload identity (SPIRE as the credential foundation), RFC 8693 actor-chain propagation, and single-hop short-lived JWTs with audience-scoped claims. One of the few public disclosures of a production-grade agent identity system at hyperscaler scale — a real-world reference point for the corpus's delegation-chain design patterns.</t>
         </is>
       </c>
     </row>
@@ -6582,27 +7078,27 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>OAuth 2.1 Features You Can't Ignore in 2026 (Gutierrez, Medium)</t>
+          <t>Agents Are Not Just Workloads (Patrick Parker, LinkedIn)</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>A practitioner article summarizing why OAuth 2.1 — mandated PKCE, exact redirect matching, sender-constrained tokens — is the 2026 minimum bar for delegated authorization.</t>
+          <t>Argues that classifying AI agents as 'workloads' is a category error that corrupts identity architecture: workloads are a what-runs-where concept, agents are a who-acts-on-whose-authority concept. Identifies five breakdown areas where workload-identity patterns fail for agents: intent captured as static token claims, delegation gaps (no purpose binding or revocation paths), overlooked tool-catalog authorization surface, bearer-credential custody ambiguity under prompt injection, and mutable logs insufficient as tamper-evident authorization evidence.</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>https://rgutierrez2004.medium.com/oauth-2-1-features-you-cant-ignore-in-2026-a15f852cb723</t>
+          <t>https://www.linkedin.com/pulse/agents-just-workloads-patrick-parker-0qxte/</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Industry blog (Medium)</t>
+          <t>Industry blog (LinkedIn)</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Author is Cyber Intelligence Lead — IAM/AI at Oracle; concise piece suitable for executive briefings.</t>
+          <t>Published 9 Jun 2026. Proposes signature-based receipts binding relationships, authority, tasks, and bounds; runtime validation of generated task intent; and AuthZEN gateway-based enforcement. A principled counterpoint to the WIMSE-as-sufficient-for-agents framing — pairs well with the Uber Engineering post (which uses SPIRE/WIMSE as the credential foundation but adds actor chains and MCP gateway enforcement on top).</t>
         </is>
       </c>
     </row>
@@ -6612,27 +7108,27 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>RFC 9396: OAuth 2.0 Rich Authorization Requests (CIAM Weekly)</t>
+          <t>Creating a Relationship Binding (Tom Jones)</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>A practitioner deep-dive on RAR explaining why scopes alone don't carry transaction-level intent and how authorization_details is being adopted in payments and verifiable credentials.</t>
+          <t>A community whitepaper proposing a signed 'Consent to Create Binding' JWT/JWS message that establishes a subject-bound relationship identifier (UUID or DID) between a user and a set of agents or service providers. The message carries 16 mandatory/optional fields: issuer, subject, subject role, context (trust framework), permissions, device statement, identity proof, purpose of use, key material, and signature. Includes a lifecycle termination model (session, cookie, transaction, relationship, and legal-based retention scopes) and a companion 'Consent Receipt with Binding' response. A second section argues that relationship-based governance — binding actors through mutual obligations, escalation paths, and accountability chains — is more resilient for AI agent systems than representational approaches (policies, classifications, static maps).</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>https://ciamweekly.substack.com/p/rfc-9396-oauth-20-rich-authorization</t>
+          <t>https://docs.google.com/document/d/1CwBDRbw147YlNld-UOlJ4lGvmpDIOCSI/edit#heading=h.kp911j18z01y</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Industry newsletter</t>
+          <t>Community whitepaper</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Captures the current (March 2026) state of RAR adoption, including CAMARA telco APIs and DPV-purpose binding proposals.</t>
+          <t>No publication date in the document; primary use case is healthcare (NIST IAL2/AAL2). Draws on Kantara's Distribute Assurance Specification for identity assurance levels and references OpenID Connect id_token as the closest existing message shape. The Consent to Create Binding message adds purpose of use, device statement, and lifecycle termination semantics that id_token lacks. Companion doc 'Digital Contracts Made Legally Valid' (separate Google Doc) covers giving the binding legal status. Relationship-governance argument is thematically aligned with Parker's 'Agents Are Not Just Workloads' — both argue that accountability chains and mutual obligations are the right governance primitive for agentic systems.</t>
         </is>
       </c>
     </row>
@@ -6642,27 +7138,27 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Technical Deconstruction of MCP Authorization (kane.mx, Nov 2025)</t>
+          <t>Intent Agent Native Authorization for Agentic Profiles (IANA-AP) (Martin Besozzi, Jul 2026)</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>A long-form technical article showing that the Model Context Protocol's authorization spec is, in practice, an OAuth 2.1 profile combined with RFC 9728 protected-resource metadata and RFC 7591 dynamic registration.</t>
+          <t>Proposes a four-phase runtime authorization lifecycle for AI agents: discovery (agent capabilities + API authorization mappings), intent computation (agent generates planned operations), review/approval (user provides explicit phishing-resistant consent via WebAuthn/FIDO2 passkeys before execution), and enforcement (every runtime invocation validated against the approved authorization artifact). Composes RFC 9396 RAR, OAuth FiPA, OpenID AuthZEN, MCP, SPIFFE JWT-SVIDs, and CEL policy mappings into a single coherent framework.</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>https://kane.mx/posts/2025/mcp-authorization-oauth-rfc-deep-dive/</t>
+          <t>https://embesozzi.github.io/posts/martin-besozzi/intent-agent-native-authorization-agentic-profiles/</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Independent technical blog</t>
+          <t>Architect blog (Martin Besozzi)</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Calls out RFC 8707 (Resource Indicators) as the critical compatibility bottleneck since most major IdPs use proprietary audience parameters.</t>
+          <t>Updated July 2026; includes open specification and reference implementation on GitHub. The SARC (Subject, Action, Resource, Context) model and 'x-authz-mapping' Agentic Profile extension are novel additions. The four-phase pre-execution approval requirement directly parallels draft-nelson-agent-delegation-receipts and draft-sato-soos-idp — but grounds it in existing OAuth standards rather than new protocol primitives. One of the few practitioner-level posts that explicitly composes AuthZEN, RAR, and FiPA into a working agent authorization flow.</t>
         </is>
       </c>
     </row>
@@ -6672,27 +7168,27 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>AI Agents Authentication: How Autonomous Systems Prove Identity (GitGuardian)</t>
+          <t>AI Agent Authentication Gets the Hard Part Right. Authorization Is Still Your Problem. (Rock Cyber Musings)</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>A GitGuardian engineering article arguing that delegated, short-lived OAuth grants are structurally safer than the static API keys that produced 28.65M secret leaks in 2025.</t>
+          <t>An analyst article arguing the new IETF agent-auth draft solves authentication via SPIFFE+WIMSE+OAuth but leaves authorization and policy enforcement as an unsolved open problem.</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>https://blog.gitguardian.com/ai-agents-authentication-how-autonomous-systems-prove-identity/</t>
+          <t>https://www.rockcybermusings.com/p/i-agent-authentication-authorization-gap</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Industry blog (GitGuardian)</t>
+          <t>Industry analysis blog</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Useful for the 'why delegated authorization &gt; shared secrets' business case with concrete 2025 incident data.</t>
+          <t>Maps the IETF draft against MCP and the Colorado AI Act 'reasonable care' standard; pragmatic implementer perspective.</t>
         </is>
       </c>
     </row>
@@ -6702,27 +7198,27 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Workload Identity – Key Takeaways from IETF 122 (Defakto)</t>
+          <t>Agent Authentication &amp; Delegated Access (Zylos Research, April 2026)</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>A practitioner recap of IETF 122 covering the WIMSE Workload Identity Token, Credential Exchange, and side-meeting work on bot/agent web authentication.</t>
+          <t>A research-style industry article surveying OAuth flows, scoped tokens, and identity patterns specifically for AI agents, covering OAuth 2.1 baselines and chain-splicing risks.</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>https://www.defakto.security/blog/workload-identity-key-takeaways-from-ietf-122/</t>
+          <t>https://zylos.ai/research/2026-04-11-agent-authentication-delegated-access-oauth-scoped-tokens</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Industry blog (Defakto)</t>
+          <t>Industry research blog</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Author Pieter Kasselman is co-author of multiple key drafts (Transaction Tokens, First-Party Apps); strong primary-source view.</t>
+          <t>Documents the 'delegation chain splicing' attack against RFC 8693 actor-token chains formally raised on the OAuth WG list in early 2026.</t>
         </is>
       </c>
     </row>
@@ -6732,27 +7228,27 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>User-Managed Access (UMA) 2.0 Comprehensive Guide (SSOJet, Feb 2026)</t>
+          <t>AuthZEN + Shared Signals Framework Series (Andrew Doering)</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>A 2026 industry guide reframing UMA 2.0 for current CIAM contexts, covering resource-set registration, permission tickets, requesting-party tokens (RPTs), and policy externalization gains.</t>
+          <t>A multi-part technical blog walking through how AuthZEN (synchronous PDP/PEP) and SSF/CAEP (asynchronous events) combine into a continuous-authorization loop in real Microsoft Entra/M365 deployments.</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>https://ssojet.com/blog/user-managed-access-uma-2-0-comprehensive-guide</t>
+          <t>https://andrewdoering.org/blog/2026/authzen-shared-signals-framework-part-1-fundamentals/</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Industry blog (SSOJet)</t>
+          <t>Industry blog</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Cites Kantara analysis showing centralized-policy moves can cut authorization code 80% — useful pitch material.</t>
+          <t>Documents the 2026 asymmetry where Microsoft Entra is a CAEP transmitter for closed-loop CAE but not an external SSF receiver.</t>
         </is>
       </c>
     </row>
@@ -6762,27 +7258,27 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Decentralized Identity and Verifiable Credentials: The Enterprise Playbook 2026</t>
+          <t>Just-in-Time Authorization with OpenID SSE and CAEP (The New Stack, Tulshibagwale)</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>An enterprise-oriented guide explaining how W3C VCs, DIDs, and OpenID4VC enable the issuer-holder-verifier delegation model for digital credentials and EUDI Wallet acceptance.</t>
+          <t>An article from CAEP's original inventor explaining how SSE+CAEP enable just-in-time authorization decisions instead of long-lived session-based access.</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>https://securityboulevard.com/2026/03/decentralized-identity-and-verifiable-credentials-the-enterprise-playbook-2026/</t>
+          <t>https://thenewstack.io/just-in-time-authorization-with-openid-sse-and-caep/</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Industry article (Security Boulevard)</t>
+          <t>Industry article (The New Stack)</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Critical 2027 EU compliance dates: banks, telecom, healthcare, and very-large platforms must accept EUDI Wallet.</t>
+          <t>Background piece by Atul Tulshibagwale (SGNL CTO, CAEP inventor) explaining the architectural intent.</t>
         </is>
       </c>
     </row>
@@ -6792,27 +7288,27 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>OAuth 2.0 &amp; OpenID Connect: The Complete Guide to What the Standards Actually Say (Patil, Medium)</t>
+          <t>How AuthZEN, Shared Signals &amp; CAEP Complement Each Other (OpenID Foundation)</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>A practitioner-friendly synthesis covering OAuth 2.0 core, the OAuth 2.1 draft, RFC 9068 JWT access tokens, RFC 8252 native apps, and RFC 8628 device authorization.</t>
+          <t>An OpenID Foundation explainer arguing that AuthZEN and SSF/CAEP are complementary — sync access decisions vs async session updates — not competing standards.</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>https://mrutyunjaypatil.medium.com/oauth-2-0-openid-connect-the-complete-guide-to-what-the-standards-actually-say-e92f040a4251</t>
+          <t>https://openid.net/how-authzen-and-shared-signals-caep-complement-each-other/</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Industry blog (Medium)</t>
+          <t>OpenID Foundation</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Good handoff document for engineers new to the area; cites the current standards rather than legacy patterns.</t>
+          <t>Useful when explaining the layering to stakeholders confused by the OpenID alphabet soup.</t>
         </is>
       </c>
     </row>
@@ -6822,27 +7318,27 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn Engineering — OpenID Connect Authentication for Sign In with LinkedIn V2</t>
+          <t>OAuth 2.1 Features You Can't Ignore in 2026 (Gutierrez, Medium)</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn's own engineering write-up on adopting OpenID Connect on top of OAuth 2.0, explicitly distinguishing OAuth's delegated-access role from OIDC's identity-assertion role.</t>
+          <t>A practitioner article summarizing why OAuth 2.1 — mandated PKCE, exact redirect matching, sender-constrained tokens — is the 2026 minimum bar for delegated authorization.</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/developers/news/featured-updates/openid-connect-authentication</t>
+          <t>https://rgutierrez2004.medium.com/oauth-2-1-features-you-cant-ignore-in-2026-a15f852cb723</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Industry (LinkedIn Engineering)</t>
+          <t>Industry blog (Medium)</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Real-world example from LinkedIn explaining why they layered OIDC over an existing OAuth 2.0 delegated-access stack.</t>
+          <t>Author is Cyber Intelligence Lead — IAM/AI at Oracle; concise piece suitable for executive briefings.</t>
         </is>
       </c>
     </row>
@@ -6852,27 +7348,27 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Rich Authorization Requests (RAR) — Authlete Knowledge Base</t>
+          <t>RFC 9396: OAuth 2.0 Rich Authorization Requests (CIAM Weekly)</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>A vendor knowledge-base article giving worked examples of RAR's authorization_details object, including locations, actions, datatypes, and identifier fields with their Authlete bindings.</t>
+          <t>A practitioner deep-dive on RAR explaining why scopes alone don't carry transaction-level intent and how authorization_details is being adopted in payments and verifiable credentials.</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>https://www.authlete.com/kb/oauth-and-openid-connect/authorization-requests/rich-authorization-requests/</t>
+          <t>https://ciamweekly.substack.com/p/rfc-9396-oauth-20-rich-authorization</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Vendor documentation (Authlete)</t>
+          <t>Industry newsletter</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Authlete is one of the few certified FAPI 2.0 + RAR implementations; useful reference for concrete request bodies.</t>
+          <t>Captures the current (March 2026) state of RAR adoption, including CAMARA telco APIs and DPV-purpose binding proposals.</t>
         </is>
       </c>
     </row>
@@ -6882,27 +7378,27 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>An Introduction to Authorization Exchange (AuthZEN) — Curity</t>
+          <t>Technical Deconstruction of MCP Authorization (kane.mx, Nov 2025)</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>A vendor explainer comparing externalized-authorization patterns (OPA, Cedar, XACML, Zanzibar) and showing how AuthZEN's API normalizes the PDP/PEP wire protocol across them.</t>
+          <t>A long-form technical article showing that the Model Context Protocol's authorization spec is, in practice, an OAuth 2.1 profile combined with RFC 9728 protected-resource metadata and RFC 7591 dynamic registration.</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>https://curity.io/resources/learn/authzen/</t>
+          <t>https://kane.mx/posts/2025/mcp-authorization-oauth-rfc-deep-dive/</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Vendor blog (Curity)</t>
+          <t>Independent technical blog</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Curity is a member of the AuthZEN WG; positions AuthZEN as 'OpenID Connect for authorization' which has become the common framing.</t>
+          <t>Calls out RFC 8707 (Resource Indicators) as the critical compatibility bottleneck since most major IdPs use proprietary audience parameters.</t>
         </is>
       </c>
     </row>
@@ -6912,25 +7408,265 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
+          <t>AI Agents Authentication: How Autonomous Systems Prove Identity (GitGuardian)</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>A GitGuardian engineering article arguing that delegated, short-lived OAuth grants are structurally safer than the static API keys that produced 28.65M secret leaks in 2025.</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>https://blog.gitguardian.com/ai-agents-authentication-how-autonomous-systems-prove-identity/</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (GitGuardian)</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Useful for the 'why delegated authorization &gt; shared secrets' business case with concrete 2025 incident data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Workload Identity – Key Takeaways from IETF 122 (Defakto)</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>A practitioner recap of IETF 122 covering the WIMSE Workload Identity Token, Credential Exchange, and side-meeting work on bot/agent web authentication.</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>https://www.defakto.security/blog/workload-identity-key-takeaways-from-ietf-122/</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Defakto)</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Author Pieter Kasselman is co-author of multiple key drafts (Transaction Tokens, First-Party Apps); strong primary-source view.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>User-Managed Access (UMA) 2.0 Comprehensive Guide (SSOJet, Feb 2026)</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>A 2026 industry guide reframing UMA 2.0 for current CIAM contexts, covering resource-set registration, permission tickets, requesting-party tokens (RPTs), and policy externalization gains.</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>https://ssojet.com/blog/user-managed-access-uma-2-0-comprehensive-guide</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (SSOJet)</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Cites Kantara analysis showing centralized-policy moves can cut authorization code 80% — useful pitch material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Decentralized Identity and Verifiable Credentials: The Enterprise Playbook 2026</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>An enterprise-oriented guide explaining how W3C VCs, DIDs, and OpenID4VC enable the issuer-holder-verifier delegation model for digital credentials and EUDI Wallet acceptance.</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>https://securityboulevard.com/2026/03/decentralized-identity-and-verifiable-credentials-the-enterprise-playbook-2026/</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Industry article (Security Boulevard)</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>Critical 2027 EU compliance dates: banks, telecom, healthcare, and very-large platforms must accept EUDI Wallet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>OAuth 2.0 &amp; OpenID Connect: The Complete Guide to What the Standards Actually Say (Patil, Medium)</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>A practitioner-friendly synthesis covering OAuth 2.0 core, the OAuth 2.1 draft, RFC 9068 JWT access tokens, RFC 8252 native apps, and RFC 8628 device authorization.</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>https://mrutyunjaypatil.medium.com/oauth-2-0-openid-connect-the-complete-guide-to-what-the-standards-actually-say-e92f040a4251</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Medium)</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Good handoff document for engineers new to the area; cites the current standards rather than legacy patterns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn Engineering — OpenID Connect Authentication for Sign In with LinkedIn V2</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn's own engineering write-up on adopting OpenID Connect on top of OAuth 2.0, explicitly distinguishing OAuth's delegated-access role from OIDC's identity-assertion role.</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/developers/news/featured-updates/openid-connect-authentication</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Industry (LinkedIn Engineering)</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Real-world example from LinkedIn explaining why they layered OIDC over an existing OAuth 2.0 delegated-access stack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Rich Authorization Requests (RAR) — Authlete Knowledge Base</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>A vendor knowledge-base article giving worked examples of RAR's authorization_details object, including locations, actions, datatypes, and identifier fields with their Authlete bindings.</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>https://www.authlete.com/kb/oauth-and-openid-connect/authorization-requests/rich-authorization-requests/</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Vendor documentation (Authlete)</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Authlete is one of the few certified FAPI 2.0 + RAR implementations; useful reference for concrete request bodies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>An Introduction to Authorization Exchange (AuthZEN) — Curity</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>A vendor explainer comparing externalized-authorization patterns (OPA, Cedar, XACML, Zanzibar) and showing how AuthZEN's API normalizes the PDP/PEP wire protocol across them.</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>https://curity.io/resources/learn/authzen/</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Vendor blog (Curity)</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Curity is a member of the AuthZEN WG; positions AuthZEN as 'OpenID Connect for authorization' which has become the common framing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
           <t>ACLX — AI Output Governance (Proprietary)</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>A proprietary enforcement layer that intercepts AI-generated content between inference and delivery, evaluating it against OPA/Cedar policies, identity context, and a three-phase sensitivity detection stack: deterministic regex rules → ontology-based compilation-risk scoring → semantic LLM evaluation for novel synthesis. Four enforcement outcomes: ALLOW, REDACT, BLOCK, or ESCALATE to human review. Treats agents as first-class principals evaluated at the output boundary regardless of whether a session or IDP exists.</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D43" s="9" t="inlineStr">
         <is>
           <t>https://aclx.ai/</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>Proprietary product</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>No published specification. Identifies a gap the corpus standards map does not yet cover: identity (OIDC/SCIM/SPIFFE), signals (CAEP/SSF), policy (OAuth/AuthZEN/OPA), and enforcement (ZTA/RATS/SCITT) all have standards, but output evaluation — governing what the AI synthesizes rather than what the user was authorized to ask — has none. The synthesis-detection layer (AI compiling across individually-authorized sources to produce content crossing a higher sensitivity boundary) is a novel problem the corpus's existing standards do not address.</t>
         </is>
@@ -6972,6 +7708,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/delegated_authorization_research.xlsx
+++ b/delegated_authorization_research.xlsx
@@ -607,15 +607,15 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>IETF WG charters, requirements drafts, and active WG/individual drafts — including the OAuth WG recharter formally adding 'Complex Delegation' for agents and a six-draft McGuinness individual-submission cluster.</t>
+          <t>IETF WG charters, requirements drafts, and active WG/individual drafts — including the OAuth WG recharter formally adding 'Complex Delegation' for agents, and the 34-draft McGuinness Mission-Bound Authorization family (33 of them GitHub-only pre-publication).</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>139</v>
+        <v>251</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>★ THIS IS WHERE THE CURRENT WORK IS HAPPENING ★  OAuth recharter on 4 Jun 2026 IESG telechat.</t>
+          <t>★ THIS IS WHERE THE CURRENT WORK IS HAPPENING ★  OAuth recharter on 4 Jun 2026 IESG telechat. Aug 2026 sweep added 70 previously-untracked Datatracker drafts plus the Mission-Bound family.</t>
         </is>
       </c>
     </row>
@@ -691,11 +691,11 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Practitioner content; the five implementations at the top of the tab show what an implementable agent-delegation stack looks like today. The four McGuinness Mission-Bound OAuth posts (May–Jun 2026) form a coherent architectural argument.</t>
+          <t>Practitioner content; the five implementations at the top of the tab show what an implementable agent-delegation stack looks like today. The Aug 2026 sweep backfilled the full Control Plane blog (47 posts, 41 newly added) — the Agent Control Points series (Aug 2026) and the Mission-Bound Authorization handbook (Jul 2026) are the two most substantial arcs.</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="6" t="n">
-        <v>215</v>
+        <v>366</v>
       </c>
       <c r="D11" s="7" t="n"/>
     </row>
@@ -906,7 +906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F140"/>
+  <dimension ref="A1:F252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, Jun 26 2026; authors: Thibault Meunier (Cloudflare), Sandor Major (Google). Replaces draft-meunier-web-bot-auth-architecture. Pairs with draft-meunier-webbotauth-httpsig-directory for key discovery.</t>
+          <t>Revision -01, 6 Aug 2026 (was -00, Jun 26 2026); authors: Thibault Meunier (Cloudflare), Sandor Major (Google). Replaces draft-meunier-web-bot-auth-architecture. Pairs with draft-meunier-webbotauth-httpsig-directory for key discovery.</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Revision -09 published 6 Jul 2026 (was -08 Mar 2026); co-authored by Tulshibagwale (CAEP inventor), Fletcher, and Kasselman. -09 reorganized the Request Context section, changed JWT body claims from OPTIONAL to RECOMMENDED, and enhanced security considerations for invalidated access tokens. Still in WGLC; IESG submission milestone Dec 2026.</t>
+          <t>Revision -11, 4 Aug 2026 (was -09, published 6 Jul 2026 (was -08 Mar 2026)); co-authored by Tulshibagwale (CAEP inventor), Fletcher, and Kasselman. -09 reorganized the Request Context section, changed JWT body claims from OPTIONAL to RECOMMENDED, and enhanced security considerations for invalidated access tokens. Still in WGLC; IESG submission milestone Dec 2026.</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Revision -26 (Dec 2025); critical for any delegated-authorization design touching SPAs because it codifies why pure-browser refresh tokens are deprecated.</t>
+          <t>Revision -27, 11 Aug 2026 (was -26, (Dec 2025)); critical for any delegated-authorization design touching SPAs because it codifies why pure-browser refresh tokens are deprecated.</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, March 2026; introduces 'Agent Identity Management System (AIMS)' and is the cleanest standards-based framing of agent-as-workload.</t>
+          <t>Revision -03, 6 Jul 2026 (was -00, March 2026); introduces 'Agent Identity Management System (AIMS)' and is the cleanest standards-based framing of agent-as-workload.</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, Jul 26 2026 (first filed Jul 20 2026); part of the Sharif cluster. Fills the PKI-layer identity gap that draft-ietf-wimse-workload-creds left open — workload-creds specifies credential issuance, this profiles X.509v3 for the agent-specific certificate case. Graduated trust taxonomy (0–4) and kill-switch revocation are referenced by draft-sweeney-wimse-credential-delegation.</t>
+          <t>Revision -03, 31 Jul 2026 (was -02, Jul 26 2026 (first filed Jul 20 2026)); part of the Sharif cluster. Fills the PKI-layer identity gap that draft-ietf-wimse-workload-creds left open — workload-creds specifies credential issuance, this profiles X.509v3 for the agent-specific certificate case. Graduated trust taxonomy (0–4) and kill-switch revocation are referenced by draft-sweeney-wimse-credential-delegation.</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Revision -04, Jul 23 2026 (first filed -00, 22 May 2026); authors: Larry Zhu, Sam Currie (Atlassian). Addresses a concrete gap in agent delegation: what happens when the delegating human is not present to re-authorize. Directly relevant to long-running agentic workflows using draft-ietf-oauth-identity-chaining. Active revision pace — -04 within ~2 months of initial filing.</t>
+          <t>Revision -05, 3 Aug 2026 (was -04, Jul 23 2026 (first filed -00, 22 May 2026)); authors: Larry Zhu, Sam Currie (Atlassian). Addresses a concrete gap in agent delegation: what happens when the delegating human is not present to re-authorize. Directly relevant to long-running agentic workflows using draft-ietf-oauth-identity-chaining. Active revision pace — -04 within ~2 months of initial filing.</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 21 May 2026; author: Lars Kersten Kroehl (CryptoKRI GmbH). Occupies similar design space to draft-mcguinness-oauth-actor-profile but uses a DID/VC substrate rather than OAuth — provides a useful alternative approach for non-OAuth deployments.</t>
+          <t>Revision -01, 11 Aug 2026 (was -00, 21 May 2026); author: Lars Kersten Kroehl (CryptoKRI GmbH). Occupies similar design space to draft-mcguinness-oauth-actor-profile but uses a DID/VC substrate rather than OAuth — provides a useful alternative approach for non-OAuth deployments.</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, April 2026; regulatory mapping appendices (PSD2, PCI DSS) are notable — one of the few drafts engaging financial regulation directly. Ambitious scope. Part of the Sharif cluster.</t>
+          <t>Revision -01, 3 Jun 2026 (was -00, April 2026); regulatory mapping appendices (PSD2, PCI DSS) are notable — one of the few drafts engaging financial regulation directly. Ambitious scope. Part of the Sharif cluster.</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, March 2026; complementary to MCP discovery but broader (not MCP-specific). Needs differentiation from OpenAPI/service-description work to gain traction.</t>
+          <t>Revision -01, 28 Jul 2026 (was -00, March 2026); complementary to MCP discovery but broader (not MCP-specific). Needs differentiation from OpenAPI/service-description work to gain traction.</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, Jul 2026. Fills a gap in the AGTP family (draft-hood-independent-agtp in corpus) and is relevant to any agent communication protocol carrying mixed-provenance claims. The verifier-separation model is the missing security architecture layer between protocol transport and authorization enforcement.</t>
+          <t>Revision -05, 9 Aug 2026 (was -02, Jul 2026). Fills a gap in the AGTP family (draft-hood-independent-agtp in corpus) and is relevant to any agent communication protocol carrying mixed-provenance claims. The verifier-separation model is the missing security architecture layer between protocol transport and authorization enforcement.</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, Jul 22 2026 (first filed -00 Jul 6 2026); author: Abdel Fane (OpenA2A). Companion draft-fane-opena2a-aip also updated to -01 Jul 22, adding a fourth 'AIP' name collision to the existing Singla/Prakash/aip-agent-identity-protocol triple. The AAP authorization layer is the piece most relevant to OAuth boundary analysis.</t>
+          <t>Revision -01, 23 Jul 2026 (first filed -00 Jul 6 2026); author: Abdel Fane (OpenA2A). Companion draft-fane-opena2a-aip has since moved ahead to -02 (6 Aug 2026) while AAP holds at -01, adding a fourth 'AIP' name collision to the existing Singla/Prakash/aip-agent-identity-protocol triple. The AAP authorization layer is the piece most relevant to OAuth boundary analysis.</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, Jul 28 2026; author: Chapman. Adds the transport-security and semantic-governance layer the A2A protocol family was missing. MLS binding anchors agent identity to Ed25519 did:key DIDs. The Governed Object envelope's purpose-declaration mechanism directly addresses the intent-drift threat identified in draft-jiang-intent-security (corpus). Likely to be referenced by other A2A family drafts as the baseline confidentiality profile.</t>
+          <t>Revision -03, 1 Aug 2026 (was -00, Jul 28 2026); author: Chapman. Adds the transport-security and semantic-governance layer the A2A protocol family was missing. MLS binding anchors agent identity to Ed25519 did:key DIDs. The Governed Object envelope's purpose-declaration mechanism directly addresses the intent-drift threat identified in draft-jiang-intent-security (corpus). Likely to be referenced by other A2A family drafts as the baseline confidentiality profile.</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 25 Jun 2026; author: Morgan Reece (TowerGuardian Consulting). The problem-statement companion to the corpus's operational drafts; likely to feed into WIMSE WG scope expansion and is directly in scope for draft-kuehlewind-audit-architecture's composition graph.</t>
+          <t>Revision -01, 30 Jul 2026 (was -00, 25 Jun 2026); author: Morgan Reece (TowerGuardian Consulting). The problem-statement companion to the corpus's operational drafts; likely to feed into WIMSE WG scope expansion and is directly in scope for draft-kuehlewind-audit-architecture's composition graph.</t>
         </is>
       </c>
     </row>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>Revision -08, Jul 21 2026. The base artifact for the EMILIA Protocol family; companion drafts draft-schrock-ep-authorization-evidence-chain, draft-schrock-ep-action-evidence-graph, draft-schrock-ep-quorum, and draft-schrock-ep-evidence-record all build on or reference this receipt format. Active iteration pace — -08 by late Jul 2026. Draft-rampalli-cross-org-delegation-mapping (corpus) formally maps EMILIA Protocol receipts against the nine reece-wimse-cross-org-delegation requirements.</t>
+          <t>Revision -11, 10 Aug 2026 (was -08, Jul 21 2026). The base artifact for the EMILIA Protocol family; companion drafts draft-schrock-ep-authorization-evidence-chain, draft-schrock-ep-action-evidence-graph, draft-schrock-ep-quorum, and draft-schrock-ep-evidence-record all build on or reference this receipt format. Active iteration pace — -08 by late Jul 2026. Draft-rampalli-cross-org-delegation-mapping (corpus) formally maps EMILIA Protocol receipts against the nine reece-wimse-cross-org-delegation requirements.</t>
         </is>
       </c>
     </row>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, Jul 2026. The cross-system interoperability layer for EMILIA Protocol receipts; directly addresses the scenario where draft-reece-wimse-cross-org-delegation (corpus) operates and authorization evidence must span administrative domains. Rev-02 indicates active development.</t>
+          <t>Revision -05, 3 Aug 2026 (was -02, Jul 2026). The cross-system interoperability layer for EMILIA Protocol receipts; directly addresses the scenario where draft-reece-wimse-cross-org-delegation (corpus) operates and authorization evidence must span administrative domains. Rev-02 indicates active development.</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, Jul 2 2026; authors: Linda Dunbar (Futurewei), YiFei Wang (China Telecom), Bing Liu (Huawei). The most directly useful DMSC document for the boundary analysis: explicitly names MCP and A2A as insufficient and articulates where the DMSC gateway fills the gap. The regulated-environment focus (financial services, telco) distinguishes DMSC's use-case target from OAuth-centric approaches.</t>
+          <t>Revision -03, 7 Aug 2026 (was -02, Jul 2 2026); authors: Linda Dunbar (Futurewei), YiFei Wang (China Telecom), Bing Liu (Huawei). The most directly useful DMSC document for the boundary analysis: explicitly names MCP and A2A as insufficient and articulates where the DMSC gateway fills the gap. The regulated-environment focus (financial services, telco) distinguishes DMSC's use-case target from OAuth-centric approaches.</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>Revision -09, Jul 4 2026; slug gained 'oauth' infix at this revision (was draft-hardt-aauth-protocol). Now formally adds four resource access modes including agent governance. The design rationale section explicitly explains why AAuth is not GNAP, not OAuth, not DPoP and not mTLS — important read for anyone planning a new agent-auth stack. OUTLIER: zero OAuth dependencies.</t>
+          <t>Revision -10, 6 Aug 2026 (was -09, Jul 4 2026); slug gained 'oauth' infix at this revision (was draft-hardt-aauth-protocol). Now formally adds four resource access modes including agent governance. The design rationale section explicitly explains why AAuth is not GNAP, not OAuth, not DPoP and not mTLS — important read for anyone planning a new agent-auth stack. OUTLIER: zero OAuth dependencies.</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>https://www.ietf.org/archive/id/draft-chen-oauth-roadmap-00.html</t>
+          <t>https://datatracker.ietf.org/doc/draft-chen-oauth-roadmap/</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>Brand-new -00 draft (May 2026); the single most useful index when starting work in this area.</t>
+          <t>Revision -01, 6 May 2026 (was -00, May 2026); the single most useful index when starting work in this area. Link switched from the pinned -00 archive HTML to the Datatracker document page so it tracks the latest revision.</t>
         </is>
       </c>
     </row>
@@ -5116,6 +5116,3366 @@
       <c r="F140" s="5" t="inlineStr">
         <is>
           <t>Approved 18 March 2026 (v01); explicitly liaises with OAuth, SCIM, SCITT, RATS, the OpenID Foundation, and CNCF/SPIFFE — the formal scope statement that anchors all WIMSE draft work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-mission-harness — Mission-Aware Agent Harnesses</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>Agent harnesses preserve execution state across restarts, retries, background jobs, tool-connection reuse, and sub-agent orchestration. That continuity is not authority. This document defines an optional Mission-aware harness profile for deployments using Mission-Bound Authorization, with OAuth 2.0 as this version's normative substrate.</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-mission-harness.md</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Agent runtime; maturity: stable; adoption rung: “Recommended for AI agents”. Depends on 10 family draft(s) incl. mission-audit, mission-authzen, mission-discovery. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-mission-orchestration — Mission Orchestration and Unwinding</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>Mission runtime enforcement can refuse the next consequential action, but Mission termination can occur while an agent workflow is already in flight. This document defines an optional orchestration profile for Mission-governed workflows.</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-mission-orchestration.md</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Agent runtime; maturity: experimental; adoption rung: “Experimental”. Depends on 8 family draft(s) incl. mission-architecture, mission-authzen, mission-harness. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-mission-shaping — Mission Intent Shaping</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization for OAuth 2.0 defines a Mission Intent and the Authority Set an Authorization Server derives from it, but leaves the step that turns an open-ended task request into a candidate Mission Intent to deployment policy.</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-mission-shaping.md</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Approval-time; maturity: informational; adoption rung: “Advanced”. Depends on 10 family draft(s) incl. mission-aauth, mission-architecture, mission-authority-server. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-oauth-mission-approval — Mission Deferred Approval for OAuth 2.0</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization for OAuth 2.0 (the "issuance profile") records an approval event at which an Approver consents to a Mission's derived Authority Set, but it treats that event as immediate. A human review of an agent's Proposed Mission is often asynchronous. This document defines an optional Mission Deferred Approval profile. It profiles OAuth Deferred Token Response so a Mission approval can be deferred and polled.</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-approval.md</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Approval-time; maturity: stable; adoption rung: “Advanced”. Depends on 6 family draft(s) incl. mission-authority-server, mission-shaping, oauth-mission. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-oauth-mission-approval-revision — Mission Approval Revision for OAuth 2.0</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>Mission Deferred Approval for OAuth 2.0 defers a Mission approval and lets a client poll for the decision. A reviewer commonly approves a narrowed subset of a proposed Mission rather than an all-or-nothing outcome.</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-approval-revision.md</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Approval-time; maturity: experimental; adoption rung: “Experimental”. Depends on 5 family draft(s) incl. mission-shaping, oauth-mission, oauth-mission-approval. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-oauth-mission-consent-evidence — Mission Consent Evidence for OAuth 2.0</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization for OAuth 2.0 commits the approved Mission Intent and Authority Set, but does not commit the exact consent disclosure shown to the Approver. This document defines an optional Consent Evidence profile.</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-consent-evidence.md</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Approval-time; maturity: stable; adoption rung: “Recommended for AI agents”. Depends on 11 family draft(s) incl. mission-aauth, mission-audit, mission-authority-server. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-oauth-mission-template — Mission Template for OAuth 2.0</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>An agent that dispatches work at machine speed cannot pause for a fresh human approval at every run, and a standing Mission broad enough to cover every run over-provisions authority the agent holds the whole time. This document defines an experimental option between those two: the Mission Template.</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-template.md</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Approval-time; maturity: experimental; adoption rung: “Experimental”. Depends on 9 family draft(s) incl. mission-architecture, mission-runtime, oauth-mission. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-mission-architecture — An Architecture for Mission-Bound Authorization</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>A Mission is a durable, approval-backed governance object for authorization: the approved task, with a lifecycle, that authority is derived for, bound to, and gated on. It is not a new way to express authority. Read as one system, the Mission model defines a delegated-authority layer: authentication says who is acting, and entitlement governance says what a principal may hold; this layer governs the approved task itself.</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-mission-architecture.md</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Architecture; maturity: informational; adoption rung: “outside-ordering”. Depends on 31 family draft(s) incl. aauth-mission-expiry, mission-aauth, mission-aauth-management. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-mission-aauth — Mission Context Binding for AAuth</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>AAuth defines missions as optional, immutable authorization contexts for agent governance at a Person Server. A mission is approved through AAuth's native propose, clarify, and approve interaction, is identified by the native `approver` and `s256` reference, and accumulates an ordered mission log.</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-mission-aauth.md</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Bindings / substrate; maturity: stable; adoption rung: “By binding”. Depends on 2 family draft(s) incl. aauth-mission-expiry, mission-substrate. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-mission-authority-server — Mission Authority Server</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization for OAuth 2.0 defines the Mission, a durable, human-approved, integrity-bound authorization artifact, and binds it to OAuth issuance: the Authorization Server derives tokens under the Mission and gates them on its state. Many deployments cannot change their Authorization Server.</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-mission-authority-server.md</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F150" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Bindings / substrate; maturity: stable; adoption rung: “By binding”. Depends on 18 family draft(s) incl. mission-architecture, mission-audit, mission-authzen. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-mission-metering — Mission Consumption Metering</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization for OAuth 2.0 bounds an agent's authority by resources, actions, and constraints, and its runtime enforcement profile evaluates each consequential action at the point of use. Neither bounds how much of an approved authority a Mission may consume.</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-mission-metering.md</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F151" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Bindings / substrate; maturity: experimental; adoption rung: “Experimental”. Depends on 7 family draft(s) incl. mission-architecture, mission-authzen, mission-orchestration. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-mission-substrate — Mission Substrate Requirements</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>A Mission binds an actor to approved context under the governance of an identified controller. Authorization substrates realize that relationship in materially different ways. Some carry structured authority in credentials; others keep contextual policy at an online service and use substrate-native authorization at each resource.</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-mission-substrate.md</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Bindings / substrate; maturity: stable; adoption rung: “By binding”. Depends on 12 family draft(s) incl. mission-aauth, mission-architecture, mission-audit. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-mission-uma — Mission-Bound Authorization for UMA 2.0</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>User-Managed Access (UMA) 2.0 standardized the plumbing of asynchronous, party-asymmetric authorization: a requesting party and client that can only request, a resource owner who approves at the authorization server on their own schedule, a rotating permission ticket carrying the pending request, claims pushing at the token endpoint, a persisted claims token that carries continuity but grants nothing, and per-use introspection at the resource server.</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-mission-uma.md</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Bindings / substrate; maturity: sketch; adoption rung: “Experimental”. Depends on 24 family draft(s) incl. mission-aauth, mission-architecture, mission-audit. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-oauth-mission-issuance-grant — Mission Issuance Grant for OAuth 2.0</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>The standalone Mission Authority Server binding governs Missions with no change to an estate's Authorization Servers: tokens remain ordinary, and enforcement joins them to Missions at the point of use. That mode provides no Mission-bound credential and no issuance gating.</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-issuance-grant.md</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Bindings / substrate; maturity: stable; adoption rung: “By binding”. Depends on 8 family draft(s) incl. mission-architecture, mission-authority-server, mission-mandate. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-oauth-mission-continuation — Mission Continuation: Authorization Continuity for Mission-Bound Authorization</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>This document profiles authorization continuity for Mission-Bound Authorization. A Mission is the durable, grant-anchored record of what work remains authorized, under which constraints, on whose approval.</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-continuation.md</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Cross-domain projection; maturity: experimental; adoption rung: “Experimental”. Depends on 8 family draft(s) incl. mission-aauth, mission-architecture, mission-authzen. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-oauth-mission-cross-domain — Mission Cross-Domain Projection for OAuth 2.0</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>The Mission-Bound Authorization for OAuth 2.0 profile binds issued authority to a durable, human-approved Mission held by a single Authorization Server, the Mission Issuer. This document specifies that profile's optional cross-domain projection: a single hop that lets an Authorization Server in another trust domain, a Resource AS, honor a Mission it did not issue.</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-cross-domain.md</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Cross-domain projection; maturity: stable; adoption rung: “Advanced”. Depends on 8 family draft(s) incl. mission-architecture, mission-mandate, mission-runtime. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-aauth-mission-expiry — AAuth Mission Expiry</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>AAuth's approved mission blob MAY carry `expires_at`: an immutable, consent-bound lifetime the Person Server enforces on every decision path, capping every token carrying `mission_s256`. This document profiles that member: values are RFC 3339 date-times, deployments document their clock-skew posture, and the Person Server terminates promptly at the deadline.</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-aauth-mission-expiry.md</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Lifecycle; maturity: stable; adoption rung: “By binding”. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-mission-aauth-management — AAuth Mission Management</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>AAuth defines an immutable mission blob, identifies it by the native `{approver, s256}` mission reference, and gives a mission two states: `active` and `terminated`. It leaves revocation, delegation-tree queries, and administrative interfaces to a companion specification. This document defines that companion.</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-mission-aauth-management.md</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Lifecycle; maturity: stable; adoption rung: “By binding”. Depends on 4 family draft(s) incl. aauth-mission-expiry, mission-aauth, mission-architecture. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-mission-discovery — Mission Open-World Discovery</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>A Mission commits its authority at approval, but an open-world agent meets resources the approval could not name.</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-mission-discovery.md</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Lifecycle; maturity: experimental; adoption rung: “Experimental”. Depends on 13 family draft(s) incl. mission-aauth, mission-architecture, mission-audit. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-oauth-mission-containment — Mission Containment for OAuth 2.0</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization for OAuth 2.0 commits a Mission's authority at a single approval event: the approved Authority Set and its integrity anchors never change. This document defines Mission Containment, an optional layered extension for narrowing a live Mission without ending it.</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-containment.md</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Lifecycle; maturity: experimental; adoption rung: “Experimental”. Depends on 15 family draft(s) incl. mission-audit, mission-authzen, mission-discovery. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-oauth-mission-expansion — Mission Expansion for OAuth 2.0</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization for OAuth 2.0 commits a Mission's authority at a single approval event and defers widening: enlarging authority requires a new approval, a successor Mission. This document defines that successor mechanism as an optional, layered extension to the issuance profile.</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-expansion.md</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Lifecycle; maturity: stable; adoption rung: “Advanced”. Depends on 6 family draft(s) incl. mission-runtime, oauth-mission, oauth-mission-child-delegation. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-oauth-mission-management — Mission Management for OAuth 2.0</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>The Mission Status and Lifecycle profile observes and changes one Mission at a time and defers fleet-scale management.</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-management.md</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Lifecycle; maturity: stable; adoption rung: “Advanced”. Depends on 9 family draft(s) incl. mission-architecture, mission-audit, mission-authority-server. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-oauth-mission-progressive — Mission Progressive Authorization for OAuth 2.0</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>Mission Expansion for OAuth 2.0 widens an agent's authority only through a fresh human approval that creates a successor Mission. An open-ended agentic task often cannot have its full authority enumerated at the initial approval, which leaves a deployment choosing between over-provisioning a broad standing Mission and interrupting the user for a fresh approval at every step.</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-progressive.md</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Lifecycle; maturity: experimental; adoption rung: “Experimental”. Depends on 11 family draft(s) incl. mission-aauth, mission-architecture, mission-discovery. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-oauth-mission-signals — Mission Lifecycle Signals for OAuth 2.0</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>The Mission Status and Lifecycle profile names event-driven propagation (Mission state changes reaching consumers over a Shared Signals stream) as one way to bound revocation latency, but leaves the channel itself unspecified.</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-signals.md</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F164" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Lifecycle; maturity: stable; adoption rung: “Advanced”. Depends on 9 family draft(s) incl. mission-aauth, mission-audit, mission-authority-server. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-oauth-mission-status — Mission Status and Lifecycle for OAuth 2.0</t>
+        </is>
+      </c>
+      <c r="C165" s="5" t="inlineStr">
+        <is>
+          <t>The Mission-Bound Authorization for OAuth 2.0 profile binds issued authority to a durable, human-approved Mission and gates issuance on Mission state, but it observes Mission state only through token lifetime and optional token introspection.</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-status.md</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F165" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Lifecycle; maturity: stable; adoption rung: “Implementation minimum”. Depends on 9 family draft(s) incl. mission-aauth, mission-authority-server, mission-runtime. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-mission-audit — Mission Audit Transparency</t>
+        </is>
+      </c>
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization for OAuth 2.0 and its companions produce many evidence records: the approval event, lifecycle transitions, consent evidence, runtime decision and execution evidence, and further evidence types profiles define.</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-mission-audit.md</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F166" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Proof portability; maturity: stable; adoption rung: “Advanced”. Depends on 15 family draft(s) incl. mission-aauth, mission-architecture, mission-authority-server. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-mission-mandate — Mission Mandate</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="inlineStr">
+        <is>
+          <t>A Mission's committed facts (the approved task, the consented authority, the principals, and the expiry) live on the Mission record at its issuer, and a party outside the issuing domain cannot verify what was approved short of a token-exchange hop or trust in the issuer's own records.</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-mission-mandate.md</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F167" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Proof portability; maturity: stable; adoption rung: “Advanced”. Depends on 9 family draft(s) incl. mission-aauth, mission-audit, mission-authority-server. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-mission-authzen — Mission-Bound Runtime Enforcement: AuthZEN Profile</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Runtime Enforcement defines a substrate-independent decision contract: before each consequential action runs, a Policy Enforcement Point (PEP) obtains a permit from a Policy Decision Point (PDP) that evaluates the action against the established Mission. This document is the concrete OpenID AuthZEN binding of that contract.</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-mission-authzen.md</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F168" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Runtime enforcement; maturity: stable; adoption rung: “Implementation minimum”. Depends on 10 family draft(s) incl. mission-audit, mission-harness, mission-metering. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-mission-runtime — Mission-Bound Runtime Enforcement</t>
+        </is>
+      </c>
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies runtime enforcement for Mission-Bound Authorization: within a declared enforcement scope, no consequential action executes until a policy enforcement point obtains a permit from a policy decision point that evaluates the action and its concrete parameters against the Mission established for the acting credential.</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-mission-runtime.md</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Runtime enforcement; maturity: stable; adoption rung: “Implementation minimum”. Depends on 18 family draft(s) incl. mission-aauth, mission-architecture, mission-audit. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-mission-security-model — Mission Security Model</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization for OAuth 2.0 and its companion profiles spread enforcement across several components: a Mission Issuer, in one of three bindings (OAuth Authorization Server, standalone Mission Authority Server, AAuth Person Server), derives authority and, where it also issues tokens, gates issuance; a Policy Enforcement Point and Policy Decision Point evaluate each action; a harness establishes a mediated execution environment; a consent rendering layer discloses authority to an Approver; an orchestrator unwinds in-flight work; and optional services report Mission state, adjudicate requested authority, meter consumption, manage the Mission fleet, log evidence, and report completion events.</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-mission-security-model.md</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F170" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Security model; maturity: informational; adoption rung: “outside-ordering”. Depends on 28 family draft(s) incl. mission-aauth, mission-architecture, mission-audit. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-oauth-mission-work-products — Mission Work Products</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="inlineStr">
+        <is>
+          <t>Agents produce durable artifacts, files, messages, memory entries, queue events, packages, and directory names, that other agents and Missions later read. An artifact can carry knowledge across a boundary, but it must not carry authority across with it. This document defines, as an experimental companion to Mission-Bound Authorization for OAuth 2.0, how a work product records where it came from without becoming a grant.</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-work-products.md</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F171" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Security model; maturity: experimental; adoption rung: “Experimental”. Depends on 7 family draft(s) incl. mission-architecture, mission-audit, mission-security-model. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-oauth-mission-attenuation — Mission Offline Attenuation for OAuth 2.0</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization for OAuth 2.0 derives delegated authority through the Authorization Server: each narrowing is a derivation at the issuer. For deep sub-agent fan-out, the common agent topology, that puts the Authorization Server in the hot path as a latency and availability dependency. This document defines an optional Mission Offline Attenuation profile.</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-attenuation.md</t>
+        </is>
+      </c>
+      <c r="E172" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F172" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Sub-agents; maturity: experimental; adoption rung: “Experimental”. Depends on 7 family draft(s) incl. mission-harness, mission-runtime, oauth-mission. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-oauth-mission-child-delegation — Mission Child Delegation for OAuth 2.0</t>
+        </is>
+      </c>
+      <c r="C173" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization for OAuth 2.0 defines delegated tokens and the rule that authority narrows down a delegation chain. Agent harnesses, however, can spawn sub-agents whose work outlives a call frame or crosses a different execution boundary. This document defines an optional Mission Child Delegation profile.</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-child-delegation.md</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F173" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Sub-agents; maturity: stable; adoption rung: “Advanced”. Depends on 10 family draft(s) incl. mission-architecture, mission-harness, mission-metering. GitHub-only (pre-publication) — not on Datatracker as of 11 Aug 2026. Family is a 34-draft decomposition with a machine-readable family-manifest.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>draft-aap-oauth-profile — Agent Authorization Profile (AAP) for OAuth 2.0</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>This document defines the Agent Authorization Profile (AAP), an authorization profile for OAuth 2.0 and JWT designed for autonomous AI agents. AAP extends existing standards with structured claims and validation rules so that systems can reason about agent identity, task context, operational constraints, delegation chains, and human oversight requirements.</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-aap-oauth-profile/</t>
+        </is>
+      </c>
+      <c r="E174" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F174" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 11 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>draft-ietf-wimse-workload-identity-practices — Workload Identity Practices</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="inlineStr">
+        <is>
+          <t>This document describes industry practices for providing secure identities to workloads in container orchestration, cloud platforms, and other workload platforms. It explains how workloads obtain credentials for external authentication purposes, without managing long-lived secrets directly.</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-wimse-workload-identity-practices/</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="inlineStr">
+        <is>
+          <t>IETF (WIMSE WG)</t>
+        </is>
+      </c>
+      <c r="F175" s="5" t="inlineStr">
+        <is>
+          <t>Revision -06, 11 Aug 2026. WG-adopted draft. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>draft-schrock-ep-bounded-capability-receipts — Bounded Capability Receipts and Durable Spend Control for Agent Actions</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>Agents sometimes need bounded authority to perform more than one consequential action without obtaining a new human approval for every operation. A signed token alone cannot enforce a shared budget across replicas, survive retries safely, or distinguish an operation that never crossed an effect boundary from one whose outcome is unknown.</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-bounded-capability-receipts/</t>
+        </is>
+      </c>
+      <c r="E176" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F176" s="5" t="inlineStr">
+        <is>
+          <t>Revision -04, 11 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>draft-chueayen-attestation-receipts — Enforcement Attestation Receipts for AI Inference Decisions</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies a compact JSON attestation receipt for an AI inference decision. A receipt binds an outcome to a request hash under a published Ed25519 public key, so a party that does not trust the issuer's infrastructure can still verify offline what the issuer's signing key attested was decided.</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-chueayen-attestation-receipts/</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F177" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 8 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="5" t="inlineStr">
+        <is>
+          <t>draft-bezerra-anchors-command-provenance — Anchors: Post-Quantum Command Provenance for Autonomous Machine Links</t>
+        </is>
+      </c>
+      <c r="C178" s="5" t="inlineStr">
+        <is>
+          <t>Autonomous machines such as uncrewed aircraft, ground robots, and spacecraft execute commands issued by human operators and, increasingly, by AI agents.</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-bezerra-anchors-command-provenance/</t>
+        </is>
+      </c>
+      <c r="E178" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F178" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 7 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="5" t="inlineStr">
+        <is>
+          <t>draft-zehavi-oauth-authz-req-del-chain — OAuth Authorization Request Delegation Chain</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="inlineStr">
+        <is>
+          <t>Brokered OAuth redirect authorization requests involve intermediary authorization servers between a downstream client and the upstream authorization server that obtains user consent and issues tokens.</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-zehavi-oauth-authz-req-del-chain/</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F179" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 7 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="5" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="5" t="inlineStr">
+        <is>
+          <t>draft-gazitt-oauth-authzen-issuance — AuthZEN Profile for OAuth 2.0 Token Issuance</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="inlineStr">
+        <is>
+          <t>Numerous OAuth 2.0 specifications define a moment at which an authorization server decides whether to issue a security token, and each of them declares the decision itself to be a matter of local policy that is out of scope. The result is that a decision common to every OAuth deployment has no interoperable expression.</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-gazitt-oauth-authzen-issuance/</t>
+        </is>
+      </c>
+      <c r="E180" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F180" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 5 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>draft-gazitt-oauth-authzen-token-exchange — AuthZEN Binding for OAuth 2.0 Token Exchange</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t>OAuth 2.0 Token Exchange (RFC 8693) defines the moment at which an authorization server decides whether one party may obtain a token to act as, or on behalf of, another. It states that the decision is governed by policy, and does not define that policy.</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-gazitt-oauth-authzen-token-exchange/</t>
+        </is>
+      </c>
+      <c r="E181" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F181" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 5 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="5" t="inlineStr">
+        <is>
+          <t>draft-wang-dmsc-drisac — Distributed Registration and Information Synchronization of Agent Capabilities</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t>The large-scale deployment of autonomous AI Agents introduces challenges to capability description, registration, and discovery. Existing agent communication protocols mainly focus on application- layer interactions and typically rely on centralized registration and discovery mechanisms, which limit scalability, robustness, and semantic extensibility.</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-wang-dmsc-drisac/</t>
+        </is>
+      </c>
+      <c r="E182" s="5" t="inlineStr">
+        <is>
+          <t>IETF (DMSC-related, individual)</t>
+        </is>
+      </c>
+      <c r="F182" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 5 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="5" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
+        <is>
+          <t>draft-diaconu-agents-authz-info-sharing — Cross-Domain AuthZ Information sharing for Agents</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>Distributed Multi-Agent Systems consist of Agents and MCP Servers operating across multiple administrative domains, each with its own Identity Providers (IdPs) and Authorization Servers (AS).</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-diaconu-agents-authz-info-sharing/</t>
+        </is>
+      </c>
+      <c r="E183" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F183" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 4 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="5" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="5" t="inlineStr">
+        <is>
+          <t>draft-ietf-wimse-http-signature — WIMSE Workload-to-Workload Authentication with HTTP Signatures</t>
+        </is>
+      </c>
+      <c r="C184" s="5" t="inlineStr">
+        <is>
+          <t>The WIMSE architecture defines authentication and authorization for software workloads in a variety of runtime environments, from the most basic ones to complex multi-service, multi-cloud, multi-tenant deployments. This document defines one of the mechanisms to provide workload authentication, using HTTP Signatures.</t>
+        </is>
+      </c>
+      <c r="D184" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-wimse-http-signature/</t>
+        </is>
+      </c>
+      <c r="E184" s="5" t="inlineStr">
+        <is>
+          <t>IETF (WIMSE WG)</t>
+        </is>
+      </c>
+      <c r="F184" s="5" t="inlineStr">
+        <is>
+          <t>Revision -06, 4 Aug 2026. WG-adopted draft. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
+          <t>draft-carleton-workload-authz-grant — Workload Authorization Grant</t>
+        </is>
+      </c>
+      <c r="C185" s="5" t="inlineStr">
+        <is>
+          <t>This document profiles the Agent Identity Management System (AIMS) framework for agent platforms that host many agent instances per customer.</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-carleton-workload-authz-grant/</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 3 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="5" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
+        <is>
+          <t>draft-helixar-hdp-agentic-delegation — Human Delegation Provenance Protocol (HDP): Cryptographic Chain-of-Custody for Agentic AI Systems</t>
+        </is>
+      </c>
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>Agentic AI systems operate on behalf of human principals, often delegating tasks through multi-step chains of AI agents. There is currently no standard mechanism to record who authorized an agent to act, under what scope, and through what chain of delegation, in a way that can be verified offline, without a central registry, and without third-party trust anchors.</t>
+        </is>
+      </c>
+      <c r="D186" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-helixar-hdp-agentic-delegation/</t>
+        </is>
+      </c>
+      <c r="E186" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F186" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 3 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-oauth-id-continuation-assertion — Identity Continuation Assertion for OAuth 2.0 Token Exchange</t>
+        </is>
+      </c>
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t>This document defines the Identity Continuation Assertion, a short- lived, sender-constrained JWT used as an OAuth 2.0 Token Exchange subject token. It lets an Identity Provider (IdP) issue an onward Identity Assertion JWT Authorization Grant (ID-JAG) when a user's request crosses service boundaries after the user is no longer present.</t>
+        </is>
+      </c>
+      <c r="D187" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-id-continuation-assertion/</t>
+        </is>
+      </c>
+      <c r="E187" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 3 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="5" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="5" t="inlineStr">
+        <is>
+          <t>draft-parecki-oauth-jwt-dpop-grant — OAuth 2.0 JWT Authorization Grant with DPoP Binding</t>
+        </is>
+      </c>
+      <c r="C188" s="5" t="inlineStr">
+        <is>
+          <t>This specification defines a new OAuth 2.0 authorization grant type that uses a JSON Web Token (JWT) assertion to request an access token that is bound to a specific key using the Demonstration of Proof-of- Possession (DPoP) mechanism. This provides a higher level of security than a simple bearer token, as the client must prove possession of the key to use the access token.</t>
+        </is>
+      </c>
+      <c r="D188" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-parecki-oauth-jwt-dpop-grant/</t>
+        </is>
+      </c>
+      <c r="E188" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F188" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 3 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
+        <is>
+          <t>draft-mih-agent-accountability-conformance — Agent Accountability: A Conformance and Verification Method</t>
+        </is>
+      </c>
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t>An architecture for auditing agent-driven interactions (draft- kuehlewind-audit-architecture) identifies the record types an auditable agent system produces — interaction, action, delegation, and authorization-transition — and the role of an Auditor that determines whether recorded behaviour matched intent and the authorization in force.</t>
+        </is>
+      </c>
+      <c r="D189" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-mih-agent-accountability-conformance/</t>
+        </is>
+      </c>
+      <c r="E189" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 1 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="5" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="5" t="inlineStr">
+        <is>
+          <t>draft-okutomi-session-bound-agent-identity — A Verifier-Side Acceptance Profile for Channel-Bound Agent Identity and Authorization</t>
+        </is>
+      </c>
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t>This document defines a verifier-side acceptance profile for channel- bound Agent identity and authorization. It addresses context diversion, where cryptographically valid material is accepted for a different service, tenant, actor, task, target, delegation, or authority boundary than the verifier intended.</t>
+        </is>
+      </c>
+      <c r="D190" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-okutomi-session-bound-agent-identity/</t>
+        </is>
+      </c>
+      <c r="E190" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F190" s="5" t="inlineStr">
+        <is>
+          <t>Revision -06, 30 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="5" t="inlineStr">
+        <is>
+          <t>draft-richer-oauth-httpsig — OAuth Proof of Possession Tokens with HTTP Message Signatures</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="inlineStr">
+        <is>
+          <t>This extension to the OAuth 2.0 authorization framework defines a method for using HTTP Message Signatures to bind access tokens to keys held by OAuth 2.0 clients. Discussion Venues This note is to be removed before publishing as an RFC.</t>
+        </is>
+      </c>
+      <c r="D191" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-richer-oauth-httpsig/</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F191" s="5" t="inlineStr">
+        <is>
+          <t>Revision -03, 28 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="5" t="inlineStr">
+        <is>
+          <t>draft-schrock-action-remedy-receipts — Action Remedy Receipts for Consequential Agent Effects</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="inlineStr">
+        <is>
+          <t>Revocation cannot undo an effect that already occurred. A dispute does not authorize a refund, return, reversal, or other remedy. This document defines Action Remedy Receipts for recording a bounded dispute decision and a fresh compensating action without rewriting the original action or effect.</t>
+        </is>
+      </c>
+      <c r="D192" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-action-remedy-receipts/</t>
+        </is>
+      </c>
+      <c r="E192" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F192" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 28 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="5" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="5" t="inlineStr">
+        <is>
+          <t>draft-tonyai-a2a-trust — Agent-to-Agent Trust, Identity, and Verifiable Provenance</t>
+        </is>
+      </c>
+      <c r="C193" s="5" t="inlineStr">
+        <is>
+          <t>This document defines a trust model for agent-to-agent (A2A) interactions in multi-agent AI systems.</t>
+        </is>
+      </c>
+      <c r="D193" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-tonyai-a2a-trust/</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F193" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 25 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="5" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="5" t="inlineStr">
+        <is>
+          <t>draft-ambekar-oauth-epop — JSON Web Token (JWT) Profile for OAuth 2.0 Enveloped Proof of Possession (EPOP)</t>
+        </is>
+      </c>
+      <c r="C194" s="5" t="inlineStr">
+        <is>
+          <t>This specification defines a profile for OAuth 2.0 sender-constrained credentials in which access tokens and refresh tokens are cryptographically bound to the client's private key as a single inseparable envelope.</t>
+        </is>
+      </c>
+      <c r="D194" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ambekar-oauth-epop/</t>
+        </is>
+      </c>
+      <c r="E194" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F194" s="5" t="inlineStr">
+        <is>
+          <t>Revision -03, 24 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="5" t="inlineStr">
+        <is>
+          <t>draft-parecki-oauth-refresh-token-scope-response — OAuth 2.0 Refresh Token Scope</t>
+        </is>
+      </c>
+      <c r="C195" s="5" t="inlineStr">
+        <is>
+          <t>This specification defines a new OAuth 2.0 token response parameter, refresh_token_scope, that indicates the scope authorized for a refresh token when it differs from the scope of the access token issued alongside it.</t>
+        </is>
+      </c>
+      <c r="D195" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-parecki-oauth-refresh-token-scope-response/</t>
+        </is>
+      </c>
+      <c r="E195" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F195" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 24 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="5" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="5" t="inlineStr">
+        <is>
+          <t>draft-pro-adp-agent-discovery — Agent Discovery Protocol (ADP) v1.1 -- Well-Known Metadata and Interaction Layer</t>
+        </is>
+      </c>
+      <c r="C196" s="5" t="inlineStr">
+        <is>
+          <t>This document defines the Agent Discovery Protocol (ADP) v1.1, a layered protocol for discovering, verifying, and interacting with AI Agents on the Internet. ADP delegates DNS discovery to DNS-AID (SVCB records) and defines a Well-Known JSON metadata format, an Ed25519-based identity model, and the Agent Gateway Protocol (AGP) for real-time WebSocket messaging.</t>
+        </is>
+      </c>
+      <c r="D196" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-pro-adp-agent-discovery/</t>
+        </is>
+      </c>
+      <c r="E196" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F196" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 24 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="5" t="inlineStr">
+        <is>
+          <t>draft-ietf-oauth-rfc7523bis — Updates to OAuth 2.0 JSON Web Token (JWT) Client Authentication and Assertion-Based Authorization Grants</t>
+        </is>
+      </c>
+      <c r="C197" s="5" t="inlineStr">
+        <is>
+          <t>This document updates RFC7521, RFC7522, RFC7523 and RFC9126 with respect to the treatment of audience values in OAuth 2.0 Client Assertion Authentication and Assertion-based Authorization Grants to address a security vulnerability identified in the previous requirements for those audience values in multiple OAuth 2.0 specifications.</t>
+        </is>
+      </c>
+      <c r="D197" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-rfc7523bis/</t>
+        </is>
+      </c>
+      <c r="E197" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth WG)</t>
+        </is>
+      </c>
+      <c r="F197" s="5" t="inlineStr">
+        <is>
+          <t>Revision -11, 23 Jul 2026. WG-adopted draft. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="5" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="5" t="inlineStr">
+        <is>
+          <t>draft-kavian-aep-oauth-session-credential — OAuth Bearer Session Credential Grant Type for the Agent Enrollment Protocol</t>
+        </is>
+      </c>
+      <c r="C198" s="5" t="inlineStr">
+        <is>
+          <t>This document defines the OAuth Bearer session-credential grant type for the Agent Enrollment Protocol (AEP). The grant type lets an AEP Service issue an OAuth-style Bearer access token through the AEP Grant command while preserving baseline AEP client assertion authentication as the root of trust.</t>
+        </is>
+      </c>
+      <c r="D198" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-kavian-aep-oauth-session-credential/</t>
+        </is>
+      </c>
+      <c r="E198" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F198" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 23 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="5" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="5" t="inlineStr">
+        <is>
+          <t>draft-morrison-mcp-dns-discovery — Discovery of Model Context Protocol Servers via DNS TXT Records</t>
+        </is>
+      </c>
+      <c r="C199" s="5" t="inlineStr">
+        <is>
+          <t>This document defines a DNS-based mechanism for discovering Model Context Protocol (MCP) servers, the identity of the organisations that operate them, and a cryptographic identity envelope bound to an individual Sovereign-tier ~handle published under the same zone. Three TXT records are defined.</t>
+        </is>
+      </c>
+      <c r="D199" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-mcp-dns-discovery/</t>
+        </is>
+      </c>
+      <c r="E199" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F199" s="5" t="inlineStr">
+        <is>
+          <t>Revision -05, 23 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="5" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="5" t="inlineStr">
+        <is>
+          <t>draft-yossif-agent-mandate-problem — Problem Statement: Verifiable Human Mandates for Autonomous Agent Actions</t>
+        </is>
+      </c>
+      <c r="C200" s="5" t="inlineStr">
+        <is>
+          <t>An autonomous software agent commonly acts under authority a human granted at an earlier moment: the human expresses and authorizes an intent at one time, and the agent executes one or more concrete actions at a later time.</t>
+        </is>
+      </c>
+      <c r="D200" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-yossif-agent-mandate-problem/</t>
+        </is>
+      </c>
+      <c r="E200" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F200" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 22 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="5" t="inlineStr">
+        <is>
+          <t>draft-araut-oauth-transactiontokens-bcp — OAuth Transaction Tokens Best Current Practice</t>
+        </is>
+      </c>
+      <c r="C201" s="5" t="inlineStr">
+        <is>
+          <t>This document provides best current practices for implementing and deploying OAuth 2.0 Transaction Tokens as specified in draft-ietf- oauth-transaction-tokens. Transaction Tokens (Txn-Tokens) enable workloads in a trusted domain to preserve and propagate user identity and authorization context across service boundaries during the processing of external programmatic requests.</t>
+        </is>
+      </c>
+      <c r="D201" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-araut-oauth-transactiontokens-bcp/</t>
+        </is>
+      </c>
+      <c r="E201" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F201" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 20 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="5" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="5" t="inlineStr">
+        <is>
+          <t>draft-ccc-wimse-twi-extensions — WIMSE Extensions for Trustworthy Workload Identity</t>
+        </is>
+      </c>
+      <c r="C202" s="5" t="inlineStr">
+        <is>
+          <t>This document contains a gap analysis that is the output of the Confidential Computing Consortium identifying areas in the IETF WIMSE WG work where the current WIMSE architecture should be extended to accommodate workloads running in Confidential Computing environments. This document contains a high-level outline for these extensions.</t>
+        </is>
+      </c>
+      <c r="D202" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ccc-wimse-twi-extensions/</t>
+        </is>
+      </c>
+      <c r="E202" s="5" t="inlineStr">
+        <is>
+          <t>IETF (WIMSE-related, individual)</t>
+        </is>
+      </c>
+      <c r="F202" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 20 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="5" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="5" t="inlineStr">
+        <is>
+          <t>draft-chen-ai-agent-auth-new-requirements — New requirements for Authentication and Authorization in the AI Agents era</t>
+        </is>
+      </c>
+      <c r="C203" s="5" t="inlineStr">
+        <is>
+          <t>AI Agents are rapidly evolving from academic concepts into the core engines driving next-generation applications. However, their autonomy, dynamic nature, and complex delegation relationships pose a fundamental challenge to our existing authentication and authorization frameworks, which were designed for human users and traditional software.</t>
+        </is>
+      </c>
+      <c r="D203" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-chen-ai-agent-auth-new-requirements/</t>
+        </is>
+      </c>
+      <c r="E203" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F203" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 20 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="5" t="inlineStr">
+        <is>
+          <t>draft-dellaert-oauth-approval-based-dcr — OAuth 2.0 Approval-Based Dynamic Client Registration</t>
+        </is>
+      </c>
+      <c r="C204" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies an extension to the OAuth 2.0 Dynamic Client Registration Protocol ([RFC7591]) that enables registration of a client with an authorization server through an explicit approval step performed by an approving party, typically the user running the client, without requiring the client to possess an Initial Access Token (IAT) beforehand.</t>
+        </is>
+      </c>
+      <c r="D204" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-dellaert-oauth-approval-based-dcr/</t>
+        </is>
+      </c>
+      <c r="E204" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F204" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 20 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="5" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" s="5" t="inlineStr">
+        <is>
+          <t>draft-hemanth-oauth-ai-scopes — OAuth 2.0 Extension for AI Model Access</t>
+        </is>
+      </c>
+      <c r="C205" s="5" t="inlineStr">
+        <is>
+          <t>This document defines an extension to OAuth 2.0 for delegating scoped access to AI model APIs. It introduces a standardized scope syntax, resource indicators for AI providers, and token constraints suitable for AI workloads including spend limits and model restrictions.</t>
+        </is>
+      </c>
+      <c r="D205" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hemanth-oauth-ai-scopes/</t>
+        </is>
+      </c>
+      <c r="E205" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F205" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 20 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="5" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" s="5" t="inlineStr">
+        <is>
+          <t>draft-zhang-dmsc-mas-communication — Security Analysis of Multi-agents Secured Communication and Limitations of Existing Protocols</t>
+        </is>
+      </c>
+      <c r="C206" s="5" t="inlineStr">
+        <is>
+          <t>Multi-agents systems (MAS) increasingly cooperate through workflow, orchestrated, and mesh communication patterns. While existing Internet protocols provide confidentiality and endpoint authentication, they were not designed for agent-native semantics such as dynamic identity, computation-bounded requests, context integrity, and intermediary trust.</t>
+        </is>
+      </c>
+      <c r="D206" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-zhang-dmsc-mas-communication/</t>
+        </is>
+      </c>
+      <c r="E206" s="5" t="inlineStr">
+        <is>
+          <t>IETF (DMSC-related, individual)</t>
+        </is>
+      </c>
+      <c r="F206" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 20 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" s="5" t="inlineStr">
+        <is>
+          <t>draft-aravind-oauth-decision-subject — Decision-Subject Representation for Agent Authorization</t>
+        </is>
+      </c>
+      <c r="C207" s="5" t="inlineStr">
+        <is>
+          <t>This document defines dsub, an OPTIONAL, descriptive claim naming the *decision subject*, the party an automated agent's action is taken _upon_, as distinct from the acting agent (act) and the delegating principal (sub).</t>
+        </is>
+      </c>
+      <c r="D207" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-aravind-oauth-decision-subject/</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F207" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 19 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="5" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" s="5" t="inlineStr">
+        <is>
+          <t>draft-coetzee-oauth-spt-txn-tokens — Transaction-Bound Authorization Tokens for Software and AI Agents (SPT-Txn)</t>
+        </is>
+      </c>
+      <c r="C208" s="5" t="inlineStr">
+        <is>
+          <t>Current authorization is role-scoped: an actor is granted a role whose authority persists across every action it takes. This fails exactly when actors fail -- under compromise, prompt injection, or goal hijacking -- because a compromised actor retains full role authority.</t>
+        </is>
+      </c>
+      <c r="D208" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-coetzee-oauth-spt-txn-tokens/</t>
+        </is>
+      </c>
+      <c r="E208" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F208" s="5" t="inlineStr">
+        <is>
+          <t>Revision -03, 19 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="5" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-oauth-token-exchange-cnf — Confirmation Response Parameter for OAuth 2.0 Token Exchange</t>
+        </is>
+      </c>
+      <c r="C209" s="5" t="inlineStr">
+        <is>
+          <t>This specification defines a cnf response parameter for the OAuth 2.0 Token Exchange (RFC 8693) response. The parameter carries the confirmation method that the authorization server applied to the issued token, enabling clients to verify that sender-constraint binding (for example a DPoP key or mutual-TLS client certificate) was performed without inspecting the issued token.</t>
+        </is>
+      </c>
+      <c r="D209" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-token-exchange-cnf/</t>
+        </is>
+      </c>
+      <c r="E209" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F209" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 19 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="5" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" s="5" t="inlineStr">
+        <is>
+          <t>draft-skyfire-oauth-id-verification — Identity Verification Methods Values</t>
+        </is>
+      </c>
+      <c r="C210" s="5" t="inlineStr">
+        <is>
+          <t>Knowing how a person's identity was verified can be important when making trust decisions. This specification defines a claim and values for declaring how the person's identity was verified.</t>
+        </is>
+      </c>
+      <c r="D210" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-skyfire-oauth-id-verification/</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F210" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 19 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" s="5" t="inlineStr">
+        <is>
+          <t>draft-ietf-wimse-mutual-tls — Workload Authentication Using Mutual TLS</t>
+        </is>
+      </c>
+      <c r="C211" s="5" t="inlineStr">
+        <is>
+          <t>The WIMSE architecture defines authentication and authorization for software workloads in a variety of runtime environments, from the most basic ones to complex multi-service, multi-cloud, multi-tenant deployments. This document profiles a workload authentication based on X.509 workload identity certificates using mutual TLS (mTLS).</t>
+        </is>
+      </c>
+      <c r="D211" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-wimse-mutual-tls/</t>
+        </is>
+      </c>
+      <c r="E211" s="5" t="inlineStr">
+        <is>
+          <t>IETF (WIMSE WG)</t>
+        </is>
+      </c>
+      <c r="F211" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 6 Jul 2026. WG-adopted draft. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="5" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" s="5" t="inlineStr">
+        <is>
+          <t>draft-liu-ai-agent-authorization-integration — AI Agent Authorization Integration Framework</t>
+        </is>
+      </c>
+      <c r="C212" s="5" t="inlineStr">
+        <is>
+          <t>This document describes how to integrate multiple OAuth 2.0 extensions to enable secure authorization for AI agents acting on behalf of users. It combines cross-domain identity, policy-based authorization, user consent evidence, and multi-hop delegation into a cohesive framework for autonomous agent authorization.</t>
+        </is>
+      </c>
+      <c r="D212" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-liu-ai-agent-authorization-integration/</t>
+        </is>
+      </c>
+      <c r="E212" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F212" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 6 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="5" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" s="5" t="inlineStr">
+        <is>
+          <t>draft-ni-agent-entity-discovery — DNS-based Entity-Level Discovery and End-to-End Connection for AI Agents</t>
+        </is>
+      </c>
+      <c r="C213" s="5" t="inlineStr">
+        <is>
+          <t>This document defines a new DNS resource record type, Agent Entity Discovery (AED), to publish agent-specific trust anchors or direct match constraints for verifying an agent's certificate or token. This enables the cross-domain users or agents to authenticate, and establish secure, end-to-end connections directly with a private- domain agent entity.</t>
+        </is>
+      </c>
+      <c r="D213" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ni-agent-entity-discovery/</t>
+        </is>
+      </c>
+      <c r="E213" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F213" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 6 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="5" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" s="5" t="inlineStr">
+        <is>
+          <t>draft-shang-campus-agent-scope-down — Campus Agent Identification and Scope-Down Access Control</t>
+        </is>
+      </c>
+      <c r="C214" s="5" t="inlineStr">
+        <is>
+          <t>AI agents operating in enterprise campus networks execute user- delegated Tasks by invoking multiple tools and services, often without continuous user supervision. Traditional authorization models assume stable applications and human-driven interactions, creating a mismatch when applied to autonomous agents that can chain actions across heterogeneous systems.</t>
+        </is>
+      </c>
+      <c r="D214" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-shang-campus-agent-scope-down/</t>
+        </is>
+      </c>
+      <c r="E214" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F214" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 6 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="5" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" s="5" t="inlineStr">
+        <is>
+          <t>draft-yang-dmsc-gateway-mediation-layer — Gateway Mediation Layer for AI Agent Collaboration</t>
+        </is>
+      </c>
+      <c r="C215" s="5" t="inlineStr">
+        <is>
+          <t>Cross-domain and policy-controlled agent collaboration can require mediation decisions that are not always suitable for an agent client or an agent server alone.</t>
+        </is>
+      </c>
+      <c r="D215" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-yang-dmsc-gateway-mediation-layer/</t>
+        </is>
+      </c>
+      <c r="E215" s="5" t="inlineStr">
+        <is>
+          <t>IETF (DMSC-related, individual)</t>
+        </is>
+      </c>
+      <c r="F215" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 5 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" s="5" t="inlineStr">
+        <is>
+          <t>draft-cui-dawn-mdi-model — An Information Model for Minimum Discoverable Information (MDI)</t>
+        </is>
+      </c>
+      <c r="C216" s="5" t="inlineStr">
+        <is>
+          <t>The Discovery of Agents, Workloads, and Named Entities (DAWN) terminology document defines Minimum Discoverable Information (MDI) as the minimum information an entity must provide to be discoverable, but does not define its field-level content.</t>
+        </is>
+      </c>
+      <c r="D216" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-cui-dawn-mdi-model/</t>
+        </is>
+      </c>
+      <c r="E216" s="5" t="inlineStr">
+        <is>
+          <t>IETF (DAWN-related, individual)</t>
+        </is>
+      </c>
+      <c r="F216" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 3 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" s="5" t="inlineStr">
+        <is>
+          <t>draft-liu-oauth-cross-domain-txn-token — Cross-domain Transaction Tokens</t>
+        </is>
+      </c>
+      <c r="C217" s="5" t="inlineStr">
+        <is>
+          <t>This document describes a mechanism for Cross-Domain Transaction Tokens, which enables the safe maintenance and propagation of user identity, workload identities, and authorization context across multiple trust domains.</t>
+        </is>
+      </c>
+      <c r="D217" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-liu-oauth-cross-domain-txn-token/</t>
+        </is>
+      </c>
+      <c r="E217" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F217" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 3 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="5" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" s="5" t="inlineStr">
+        <is>
+          <t>draft-schrock-agent-action-manifest — The Agent Action Control Manifest: A Public Effect-Boundary Control Plane for Machine Actions</t>
+        </is>
+      </c>
+      <c r="C218" s="5" t="inlineStr">
+        <is>
+          <t>A growing set of specifications defines evidence _objects_ for machine actions: transparency statements, workload-identity and transaction tokens, permits, action capsules, and authorization, delegation, and inference receipts.</t>
+        </is>
+      </c>
+      <c r="D218" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-agent-action-manifest/</t>
+        </is>
+      </c>
+      <c r="E218" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F218" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 3 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="5" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" s="5" t="inlineStr">
+        <is>
+          <t>draft-schrock-human-authorization-binding — Binding Named-Human Authorization Evidence into Agent-Action Records</t>
+        </is>
+      </c>
+      <c r="C219" s="5" t="inlineStr">
+        <is>
+          <t>A recurring pattern spans the agent-action record formats now in development: a record about an agent's action reserves a place for "the human authorization" — an approver disposition, an authority context, a human-override field, an actor slot, a signed grant, an approval reference — and leaves its semantics undefined.</t>
+        </is>
+      </c>
+      <c r="D219" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-human-authorization-binding/</t>
+        </is>
+      </c>
+      <c r="E219" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F219" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 3 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="5" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" s="5" t="inlineStr">
+        <is>
+          <t>draft-xkumakichi-xaip-receipts — Signed Execution Receipts for AI Agent Tool Calls (XAIP Receipts)</t>
+        </is>
+      </c>
+      <c r="C220" s="5" t="inlineStr">
+        <is>
+          <t>This document defines a wire format for signed execution receipts produced by AI agents when they invoke tools, services, or other agents.</t>
+        </is>
+      </c>
+      <c r="D220" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-xkumakichi-xaip-receipts/</t>
+        </is>
+      </c>
+      <c r="E220" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F220" s="5" t="inlineStr">
+        <is>
+          <t>Revision -03, 2 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" s="5" t="inlineStr">
+        <is>
+          <t>draft-yang-dmsc-gateway-semantic-layer — Gateway Mediation Layer for AI Agent Collaboration</t>
+        </is>
+      </c>
+      <c r="C221" s="5" t="inlineStr">
+        <is>
+          <t>Cross-domain and policy-controlled agent collaboration can require mediation decisions that are not always suitable for an agent client or an agent server alone.</t>
+        </is>
+      </c>
+      <c r="D221" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-yang-dmsc-gateway-semantic-layer/</t>
+        </is>
+      </c>
+      <c r="E221" s="5" t="inlineStr">
+        <is>
+          <t>IETF (DMSC-related, individual)</t>
+        </is>
+      </c>
+      <c r="F221" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 2 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="5" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" s="5" t="inlineStr">
+        <is>
+          <t>draft-ni-batch-authorization-delegation — Batch Authorization Delegation</t>
+        </is>
+      </c>
+      <c r="C222" s="5" t="inlineStr">
+        <is>
+          <t>This document describes a mechanism for Batch Authorization Delegation, which enables a batch of fine-grained, actor-bound permissions in a single request and securely delegates them to multiple collaborating actors.</t>
+        </is>
+      </c>
+      <c r="D222" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ni-batch-authorization-delegation/</t>
+        </is>
+      </c>
+      <c r="E222" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F222" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 30 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="5" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" s="5" t="inlineStr">
+        <is>
+          <t>draft-ayoub-agis-agent-identity-system — AgIS: An Agent Identity System for DNS-Backed Verification of AI and Software Agents</t>
+        </is>
+      </c>
+      <c r="C223" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies AgIS, the Agent Identity System, a DNS-backed identity and verification profile for AI agents, autonomous software agents, and agentic services operating on the existing web.</t>
+        </is>
+      </c>
+      <c r="D223" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ayoub-agis-agent-identity-system/</t>
+        </is>
+      </c>
+      <c r="E223" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F223" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 29 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="5" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" s="5" t="inlineStr">
+        <is>
+          <t>draft-vicente-oauth-apm — Authorization Posture Mechanism (APM): Per-Transaction Consistency for OAuth 2.0</t>
+        </is>
+      </c>
+      <c r="C224" s="5" t="inlineStr">
+        <is>
+          <t>This document describes the Authorization Posture Mechanism (APM), a method by which an OAuth 2.0 [RFC6749] authorization server, or a resource server acting on its behalf, re-evaluates the mutual consistency of three bound factors -- the client certificate, the access token, and the device posture -- on a per-request basis for privileged operations, rather than only at session…</t>
+        </is>
+      </c>
+      <c r="D224" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-vicente-oauth-apm/</t>
+        </is>
+      </c>
+      <c r="E224" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F224" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 28 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="5" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" s="5" t="inlineStr">
+        <is>
+          <t>draft-duda-agent-id-framework — Self-Certifying Identity and Capability-Based Delegation for Autonomous AI Agents</t>
+        </is>
+      </c>
+      <c r="C225" s="5" t="inlineStr">
+        <is>
+          <t>We present an identity and delegation framework for secure AI agent communications. The framework introduces a set of entities including Client AI Agents, Service AI Agents, Agent Providers, and Agent Brokers, together with a Trustful Mutable Store responsible for maintaining cryptographically verifiable identity bindings.</t>
+        </is>
+      </c>
+      <c r="D225" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-duda-agent-id-framework/</t>
+        </is>
+      </c>
+      <c r="E225" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F225" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 26 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" s="5" t="inlineStr">
+        <is>
+          <t>draft-liu-oauth-authorization-evidence — Authorization Evidence and Audit Trail for OAuth 2.0 Access Tokens</t>
+        </is>
+      </c>
+      <c r="C226" s="5" t="inlineStr">
+        <is>
+          <t>This specification defines an authorization details type for including authorization evidence and audit trail information in OAuth 2.0 access tokens using the Rich Authorization Requests (RAR) framework.</t>
+        </is>
+      </c>
+      <c r="D226" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-liu-oauth-authorization-evidence/</t>
+        </is>
+      </c>
+      <c r="E226" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F226" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 22 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="5" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" s="5" t="inlineStr">
+        <is>
+          <t>draft-vandemeent-tibet-provenance — TIBET: Transaction/Interaction-Based Evidence Trail</t>
+        </is>
+      </c>
+      <c r="C227" s="5" t="inlineStr">
+        <is>
+          <t>This document defines TIBET (Transaction/Interaction-Based Evidence Trail), a data model and protocol for constructing cryptographically linked provenance chains over interactions between autonomous agents, human actors, and automated processes. A TIBET token captures four dimensions of provenance: content (ERIN), references (ERAAN), context (EROMHEEN), and intent (ERACHTER).</t>
+        </is>
+      </c>
+      <c r="D227" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-vandemeent-tibet-provenance/</t>
+        </is>
+      </c>
+      <c r="E227" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F227" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 17 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="5" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" s="5" t="inlineStr">
+        <is>
+          <t>draft-car-agents-txt-wellknown — AGENTS.TXT: Capability Declarations for Web Agents</t>
+        </is>
+      </c>
+      <c r="C228" s="5" t="inlineStr">
+        <is>
+          <t>This document requests registration of two Well-Known URIs under the "/.well-known/" path: "agents.txt" and "agents.json".</t>
+        </is>
+      </c>
+      <c r="D228" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-car-agents-txt-wellknown/</t>
+        </is>
+      </c>
+      <c r="E228" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F228" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 12 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="5" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" s="5" t="inlineStr">
+        <is>
+          <t>draft-liu-oauth-rego-policy — Rego Policy Language for OAuth 2.0 Authorization</t>
+        </is>
+      </c>
+      <c r="C229" s="5" t="inlineStr">
+        <is>
+          <t>AI agents exhibit dynamic, unpredictable behavior that cannot be fully described by traditional OAuth 2.0 scopes. This specification defines a behavioral authorization framework that enables clients, particularly AI agents, to propose Rego policy-based behavioral constraint contracts in OAuth 2.0 authorization flows using Rich Authorization Requests (RAR).</t>
+        </is>
+      </c>
+      <c r="D229" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-liu-oauth-rego-policy/</t>
+        </is>
+      </c>
+      <c r="E229" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F229" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 12 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="5" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" s="5" t="inlineStr">
+        <is>
+          <t>draft-ekahraman-oauth-attestation-authz-native-app — OAuth 2.0 Attestation Based Authorization for Native Applications</t>
+        </is>
+      </c>
+      <c r="C230" s="5" t="inlineStr">
+        <is>
+          <t>This document defines an extension to OAuth 2.0 [RFC6749] that enables Authorization Servers to consider Attestation Results presented by Native Applications when issuing access grants.</t>
+        </is>
+      </c>
+      <c r="D230" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ekahraman-oauth-attestation-authz-native-app/</t>
+        </is>
+      </c>
+      <c r="E230" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F230" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 9 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" s="5" t="inlineStr">
+        <is>
+          <t>draft-kay-dawn-use-cases — Use Cases for the Discovery of Agents, Workloads, and Named Entities</t>
+        </is>
+      </c>
+      <c r="C231" s="5" t="inlineStr">
+        <is>
+          <t>This document describes broad categories of use cases for the Discovery of Agents, Workloads, and Named Entities (DAWN). The purpose of the document is to illustrate situations in which entities need to discover other entities. This document does not define a discovery protocol, a registration procedure, a selection algorithm, or an agent-to-agent communication protocol.</t>
+        </is>
+      </c>
+      <c r="D231" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-kay-dawn-use-cases/</t>
+        </is>
+      </c>
+      <c r="E231" s="5" t="inlineStr">
+        <is>
+          <t>IETF (DAWN-related, individual)</t>
+        </is>
+      </c>
+      <c r="F231" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 7 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="5" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" s="5" t="inlineStr">
+        <is>
+          <t>draft-reddy-wimse-workload-attestation — WIMSE Workload Attestation</t>
+        </is>
+      </c>
+      <c r="C232" s="5" t="inlineStr">
+        <is>
+          <t>This document extends the WIMSE workload-to-workload authentication architecture with a mechanism for conveying attestation across TLS- terminating proxies, a deployment topology where TLS-layer attestation mechanisms lose their end-to-end security properties.</t>
+        </is>
+      </c>
+      <c r="D232" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-reddy-wimse-workload-attestation/</t>
+        </is>
+      </c>
+      <c r="E232" s="5" t="inlineStr">
+        <is>
+          <t>IETF (WIMSE-related, individual)</t>
+        </is>
+      </c>
+      <c r="F232" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 7 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="5" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" s="5" t="inlineStr">
+        <is>
+          <t>draft-madaras-preauth-receipts — PRE-RCT: Pre-Execution Authorization Receipt Format</t>
+        </is>
+      </c>
+      <c r="C233" s="5" t="inlineStr">
+        <is>
+          <t>This document defines PRE-RCT, the Pre-Execution Authorization Receipt, a cryptographically signed and attestation-aware receipt format used to record high-risk authorization events. PRE-RCT is intended for use with pre-execution authorization protocols such as GNA.</t>
+        </is>
+      </c>
+      <c r="D233" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-madaras-preauth-receipts/</t>
+        </is>
+      </c>
+      <c r="E233" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F233" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 6 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="5" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" s="5" t="inlineStr">
+        <is>
+          <t>draft-fulz-oauth-trust-binding — OAuth Trust Binding Extension (OTBE)</t>
+        </is>
+      </c>
+      <c r="C234" s="5" t="inlineStr">
+        <is>
+          <t>This document defines the OAuth Trust Binding Extension (OTBE), a mechanism allowing Resource Owners to explicitly authorize which Authorization Servers may assert their identity towards Relying Parties, mitigating silent impersonation and namespace-based identity capture.</t>
+        </is>
+      </c>
+      <c r="D234" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-fulz-oauth-trust-binding/</t>
+        </is>
+      </c>
+      <c r="E234" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F234" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 30 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="5" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" s="5" t="inlineStr">
+        <is>
+          <t>draft-somoza-atn-agent-trust-negotiation — Agent Trust Negotiation: Capability, Delegation, and Provenance Binding for AI Agents</t>
+        </is>
+      </c>
+      <c r="C235" s="5" t="inlineStr">
+        <is>
+          <t>This document defines the Agent Trust Negotiation (ATN) protocol. ATN sits above whatever mechanism is used to discover an agent identity and answers questions that discovery alone cannot: what is the agent permitted to do, under whose authority, with what provenance, and how do two agents reach a verifiable working agreement.</t>
+        </is>
+      </c>
+      <c r="D235" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-somoza-atn-agent-trust-negotiation/</t>
+        </is>
+      </c>
+      <c r="E235" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F235" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 28 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="5" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" s="5" t="inlineStr">
+        <is>
+          <t>draft-drake-agent-identity-registry — Agent Identity Registry System: A Federated Architecture for Hardware-Anchored Identity of Autonomous Entities</t>
+        </is>
+      </c>
+      <c r="C236" s="5" t="inlineStr">
+        <is>
+          <t>The Internet's identity infrastructure assumes human principals. As autonomous entities -- AI agents, robotic systems, and other non- human actors -- increasingly participate in both Internet protocols and physical society, no existing standard provides them with persistent, verifiable, hardware-anchored identity.</t>
+        </is>
+      </c>
+      <c r="D236" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-drake-agent-identity-registry/</t>
+        </is>
+      </c>
+      <c r="E236" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F236" s="5" t="inlineStr">
+        <is>
+          <t>Revision -03, 22 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="5" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" s="5" t="inlineStr">
+        <is>
+          <t>draft-iannone-dawn-privacy-considerations — Privacy Considerations for the Discovery of Agents, Workloads, and Named Entities (DAWN)</t>
+        </is>
+      </c>
+      <c r="C237" s="5" t="inlineStr">
+        <is>
+          <t>This document describes the privacy issues associated with the Discovery of Agents, Workloads, and Named Entities (DAWN). It provides general observations about typical current privacy practices in similar domains like, DNS, HTTP, and in general privacy in information retrieval.</t>
+        </is>
+      </c>
+      <c r="D237" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-iannone-dawn-privacy-considerations/</t>
+        </is>
+      </c>
+      <c r="E237" s="5" t="inlineStr">
+        <is>
+          <t>IETF (DAWN-related, individual)</t>
+        </is>
+      </c>
+      <c r="F237" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 22 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="5" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" s="5" t="inlineStr">
+        <is>
+          <t>draft-jiang-seat-dynamic-attestation — Dynamic Attestation for AI Agent Communication</t>
+        </is>
+      </c>
+      <c r="C238" s="5" t="inlineStr">
+        <is>
+          <t>This document describes a use case for conveying remote attestation information in association with Transport Layer Security (TLS) sessions in the context of AI agent communication.</t>
+        </is>
+      </c>
+      <c r="D238" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-jiang-seat-dynamic-attestation/</t>
+        </is>
+      </c>
+      <c r="E238" s="5" t="inlineStr">
+        <is>
+          <t>IETF (RATS/SEAT-related, individual)</t>
+        </is>
+      </c>
+      <c r="F238" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 17 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="5" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" s="5" t="inlineStr">
+        <is>
+          <t>draft-novak-rats-twi-attestation — Remote Attestation for Trustworthy Workload Identity</t>
+        </is>
+      </c>
+      <c r="C239" s="5" t="inlineStr">
+        <is>
+          <t>Trustworthy Workloads are workloads that operate in environments that provide isolation of data in use. This document describes how Trustworthy Workloads can acquire credentials containing stable identifiers, upon proving the trust in the environments in which they operate via Remote Attestation.</t>
+        </is>
+      </c>
+      <c r="D239" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-novak-rats-twi-attestation/</t>
+        </is>
+      </c>
+      <c r="E239" s="5" t="inlineStr">
+        <is>
+          <t>IETF (RATS/SEAT-related, individual)</t>
+        </is>
+      </c>
+      <c r="F239" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 9 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="5" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" s="5" t="inlineStr">
+        <is>
+          <t>draft-jimenez-agent-directory — Agent Directory</t>
+        </is>
+      </c>
+      <c r="C240" s="5" t="inlineStr">
+        <is>
+          <t>This document defines the Agent Directory (AD), a service where agents register their identity, capabilities, and reachable endpoints and where clients discover them by capability.</t>
+        </is>
+      </c>
+      <c r="D240" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-jimenez-agent-directory/</t>
+        </is>
+      </c>
+      <c r="E240" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F240" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 8 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" s="5" t="inlineStr">
+        <is>
+          <t>draft-hardt-aauth-bootstrap — AAuth Bootstrap Guidance</t>
+        </is>
+      </c>
+      <c r="C241" s="5" t="inlineStr">
+        <is>
+          <t>This document provides informational guidance for agent providers (APs) on enrolling agents and issuing AAuth agent tokens defined in [I-D.hardt-oauth-aauth-protocol]. It covers per-platform key handling, optional platform attestation, agent identifier strategies, and refresh patterns.</t>
+        </is>
+      </c>
+      <c r="D241" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hardt-aauth-bootstrap/</t>
+        </is>
+      </c>
+      <c r="E241" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F241" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 6 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="5" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" s="5" t="inlineStr">
+        <is>
+          <t>draft-abbott-mcp-ax — MCP Aggregation Protocol (MCP-AX): Hierarchical Tool Namespace Delegation for Model Context Protocol Servers</t>
+        </is>
+      </c>
+      <c r="C242" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies MCP-AX, an aggregation protocol for Model Context Protocol (MCP) servers. MCP-AX enables hierarchical composition of tool namespaces across heterogeneous networks of MCP servers, from cloud services to resource-constrained embedded devices.</t>
+        </is>
+      </c>
+      <c r="D242" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-abbott-mcp-ax/</t>
+        </is>
+      </c>
+      <c r="E242" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F242" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 5 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="5" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" s="5" t="inlineStr">
+        <is>
+          <t>draft-hori-agent-quality-graph — Agent Quality Graph (AQG): A Protocol for Evaluating AI Agent Trustworthiness via Delegation Graphs</t>
+        </is>
+      </c>
+      <c r="C243" s="5" t="inlineStr">
+        <is>
+          <t>This document describes the Agent Quality Graph (AQG) protocol, a method for evaluating and ranking AI agent trustworthiness based on delegation transaction graphs. As the number of autonomous AI agents grows rapidly, there is no standardized mechanism for determining which agents reliably complete delegated tasks.</t>
+        </is>
+      </c>
+      <c r="D243" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hori-agent-quality-graph/</t>
+        </is>
+      </c>
+      <c r="E243" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F243" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 2 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="5" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" s="5" t="inlineStr">
+        <is>
+          <t>draft-hopley-x402-cancellation-receipt — Categorical Mandate Cancellation Receipt Format for Agentic-Payment Flows</t>
+        </is>
+      </c>
+      <c r="C244" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies a categorical mandate cancellation receipt format for agentic-payment flows. The format records that a recurring-payment mandate or other standing payer-to-payee authorisation has been cancelled, by whom, for what reason, and with what effective date.</t>
+        </is>
+      </c>
+      <c r="D244" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hopley-x402-cancellation-receipt/</t>
+        </is>
+      </c>
+      <c r="E244" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F244" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 25 May 2026. Hopley x402 agentic-payment receipt cluster (4 drafts: compliance, settlement, refund, cancellation) — categorical receipt formats for agent-initiated payment flows. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="5" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" s="5" t="inlineStr">
+        <is>
+          <t>draft-hopley-x402-compliance-receipt — Categorical Compliance Screening Receipt Format for Agentic-Payment Flows</t>
+        </is>
+      </c>
+      <c r="C245" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies a categorical compliance screening receipt format for agentic-payment flows.</t>
+        </is>
+      </c>
+      <c r="D245" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hopley-x402-compliance-receipt/</t>
+        </is>
+      </c>
+      <c r="E245" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F245" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 25 May 2026. Hopley x402 agentic-payment receipt cluster (4 drafts: compliance, settlement, refund, cancellation) — categorical receipt formats for agent-initiated payment flows. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="5" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" s="5" t="inlineStr">
+        <is>
+          <t>draft-hopley-x402-refund-receipt — Categorical Refund Receipt Format for Agentic-Payment Flows</t>
+        </is>
+      </c>
+      <c r="C246" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies a categorical refund receipt format for agentic-payment flows.</t>
+        </is>
+      </c>
+      <c r="D246" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hopley-x402-refund-receipt/</t>
+        </is>
+      </c>
+      <c r="E246" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F246" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 25 May 2026. Hopley x402 agentic-payment receipt cluster (4 drafts: compliance, settlement, refund, cancellation) — categorical receipt formats for agent-initiated payment flows. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="5" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" s="5" t="inlineStr">
+        <is>
+          <t>draft-hopley-x402-settlement-attestation — Categorical Settlement Attestation Format for Agentic-Payment Flows</t>
+        </is>
+      </c>
+      <c r="C247" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies a categorical settlement attestation format for agentic-payment flows. The format records that a payment has reached a particular settlement state on a particular chain, at a particular instant, under the attesting party's risk model. The receipt format uses a closed enumeration of categorical outcomes (SETTLED, PENDING_FINALITY, REVERSED).</t>
+        </is>
+      </c>
+      <c r="D247" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hopley-x402-settlement-attestation/</t>
+        </is>
+      </c>
+      <c r="E247" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F247" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 25 May 2026. Hopley x402 agentic-payment receipt cluster (4 drafts: compliance, settlement, refund, cancellation) — categorical receipt formats for agent-initiated payment flows. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="5" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" s="5" t="inlineStr">
+        <is>
+          <t>draft-skyfire-oauth-aml-methods — Anti-Money Laundering Methods Values</t>
+        </is>
+      </c>
+      <c r="C248" s="5" t="inlineStr">
+        <is>
+          <t>Financial regulations require application of Anti-Money Laundering (AML) and Countering the Financing of Terrorism (CFT) methods in many jurisdictions worldwide. This specification defines a claim and values for declaring what AML/CFT methods were employed.</t>
+        </is>
+      </c>
+      <c r="D248" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-skyfire-oauth-aml-methods/</t>
+        </is>
+      </c>
+      <c r="E248" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F248" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 19 Jul 2026. Skyfire KYA/KYAPay cluster (6 drafts incl. draft-skyfire-oauth-id-verification already in corpus) — agent identity verification and payment claims for OAuth/JWT. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="5" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" s="5" t="inlineStr">
+        <is>
+          <t>draft-skyfire-oauth-amr-values — Additional Authentication Method Reference Values</t>
+        </is>
+      </c>
+      <c r="C249" s="5" t="inlineStr">
+        <is>
+          <t>The JWT "amr" (Authentication Methods References) claim contains values conveying authentication methods used in the authentication. This specification defines additional Authentication Method Reference values beyond those already registered to represent additional authentication methods in use today.</t>
+        </is>
+      </c>
+      <c r="D249" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-skyfire-oauth-amr-values/</t>
+        </is>
+      </c>
+      <c r="E249" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F249" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 19 Jul 2026. Skyfire KYA/KYAPay cluster (6 drafts incl. draft-skyfire-oauth-id-verification already in corpus) — agent identity verification and payment claims for OAuth/JWT. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="5" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" s="5" t="inlineStr">
+        <is>
+          <t>draft-skyfire-oauth-kyapay-token — KYAPay Token</t>
+        </is>
+      </c>
+      <c r="C250" s="5" t="inlineStr">
+        <is>
+          <t>This document defines a token format for agent identity and payment tokens in JSON Web Token (JWT) format. Authorization servers and resource servers from different vendors can leverage this token format to consume identity and payment tokens in an interoperable manner.</t>
+        </is>
+      </c>
+      <c r="D250" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-skyfire-oauth-kyapay-token/</t>
+        </is>
+      </c>
+      <c r="E250" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F250" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 19 Jul 2026. Skyfire KYA/KYAPay cluster (6 drafts incl. draft-skyfire-oauth-id-verification already in corpus) — agent identity verification and payment claims for OAuth/JWT. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" s="5" t="inlineStr">
+        <is>
+          <t>draft-skyfire-oauth-kyapay-token-exchange — KYAPay Token Exchange</t>
+        </is>
+      </c>
+      <c r="C251" s="5" t="inlineStr">
+        <is>
+          <t>This specification describes how KYAPay tokens can be exchanged for OAuth access tokens to dynamically grant agents access to resources they need to accomplish their mission.</t>
+        </is>
+      </c>
+      <c r="D251" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-skyfire-oauth-kyapay-token-exchange/</t>
+        </is>
+      </c>
+      <c r="E251" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F251" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 19 Jul 2026. Skyfire KYA/KYAPay cluster (6 drafts incl. draft-skyfire-oauth-id-verification already in corpus) — agent identity verification and payment claims for OAuth/JWT. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="5" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" s="5" t="inlineStr">
+        <is>
+          <t>draft-skyfire-oauth-using-kyapay-tokens — Using KYAPay Tokens</t>
+        </is>
+      </c>
+      <c r="C252" s="5" t="inlineStr">
+        <is>
+          <t>The KYAPay Token is a JSON Web Token (JWT) that carries verified identity ("Know Your Agent", KYA) and payment (PAY) information for requests made by software agents on behalf of human principals.</t>
+        </is>
+      </c>
+      <c r="D252" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-skyfire-oauth-using-kyapay-tokens/</t>
+        </is>
+      </c>
+      <c r="E252" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F252" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 19 Jul 2026. Skyfire KYA/KYAPay cluster (6 drafts incl. draft-skyfire-oauth-id-verification already in corpus) — agent identity verification and payment claims for OAuth/JWT. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
         </is>
       </c>
     </row>
@@ -5260,6 +8620,118 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId137"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D252" r:id="rId251"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6369,7 +9841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7008,7 +10480,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Published Mar 17 2026; author: Rock Lambros. One of the few practitioner posts that analyzes a specific IETF draft (draft-klrc-aiagent-auth, corpus) in depth and names the authorization gap that authentication alone doesn't close. The 'TODO Security' observation is accurate as of the -00 filing; check subsequent revisions for resolution.</t>
+          <t>Published Mar 17 2026; author: Rock Lambros. One of the few practitioner posts that analyzes a specific IETF draft (draft-klrc-aiagent-auth, corpus) in depth and names the authorization gap that authentication alone doesn't close. The 'TODO Security' observation was accurate as of the -00 filing; draft-klrc-aiagent-auth has since reached -03 (6 Jul 2026) — re-check whether Security Considerations were filled in.</t>
         </is>
       </c>
     </row>
@@ -7168,27 +10640,27 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>AI Agent Authentication Gets the Hard Part Right. Authorization Is Still Your Problem. (Rock Cyber Musings)</t>
+          <t>Agent Authentication &amp; Delegated Access (Zylos Research, April 2026)</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>An analyst article arguing the new IETF agent-auth draft solves authentication via SPIFFE+WIMSE+OAuth but leaves authorization and policy enforcement as an unsolved open problem.</t>
+          <t>A research-style industry article surveying OAuth flows, scoped tokens, and identity patterns specifically for AI agents, covering OAuth 2.1 baselines and chain-splicing risks.</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>https://www.rockcybermusings.com/p/i-agent-authentication-authorization-gap</t>
+          <t>https://zylos.ai/research/2026-04-11-agent-authentication-delegated-access-oauth-scoped-tokens</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Industry analysis blog</t>
+          <t>Industry research blog</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Maps the IETF draft against MCP and the Colorado AI Act 'reasonable care' standard; pragmatic implementer perspective.</t>
+          <t>Documents the 'delegation chain splicing' attack against RFC 8693 actor-token chains formally raised on the OAuth WG list in early 2026.</t>
         </is>
       </c>
     </row>
@@ -7198,27 +10670,27 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Agent Authentication &amp; Delegated Access (Zylos Research, April 2026)</t>
+          <t>AuthZEN + Shared Signals Framework Series (Andrew Doering)</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>A research-style industry article surveying OAuth flows, scoped tokens, and identity patterns specifically for AI agents, covering OAuth 2.1 baselines and chain-splicing risks.</t>
+          <t>A multi-part technical blog walking through how AuthZEN (synchronous PDP/PEP) and SSF/CAEP (asynchronous events) combine into a continuous-authorization loop in real Microsoft Entra/M365 deployments.</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>https://zylos.ai/research/2026-04-11-agent-authentication-delegated-access-oauth-scoped-tokens</t>
+          <t>https://andrewdoering.org/blog/2026/authzen-shared-signals-framework-part-1-fundamentals/</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Industry research blog</t>
+          <t>Industry blog</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Documents the 'delegation chain splicing' attack against RFC 8693 actor-token chains formally raised on the OAuth WG list in early 2026.</t>
+          <t>Documents the 2026 asymmetry where Microsoft Entra is a CAEP transmitter for closed-loop CAE but not an external SSF receiver.</t>
         </is>
       </c>
     </row>
@@ -7228,27 +10700,27 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>AuthZEN + Shared Signals Framework Series (Andrew Doering)</t>
+          <t>Just-in-Time Authorization with OpenID SSE and CAEP (The New Stack, Tulshibagwale)</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>A multi-part technical blog walking through how AuthZEN (synchronous PDP/PEP) and SSF/CAEP (asynchronous events) combine into a continuous-authorization loop in real Microsoft Entra/M365 deployments.</t>
+          <t>An article from CAEP's original inventor explaining how SSE+CAEP enable just-in-time authorization decisions instead of long-lived session-based access.</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>https://andrewdoering.org/blog/2026/authzen-shared-signals-framework-part-1-fundamentals/</t>
+          <t>https://thenewstack.io/just-in-time-authorization-with-openid-sse-and-caep/</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Industry blog</t>
+          <t>Industry article (The New Stack)</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Documents the 2026 asymmetry where Microsoft Entra is a CAEP transmitter for closed-loop CAE but not an external SSF receiver.</t>
+          <t>Background piece by Atul Tulshibagwale (SGNL CTO, CAEP inventor) explaining the architectural intent.</t>
         </is>
       </c>
     </row>
@@ -7258,27 +10730,27 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Just-in-Time Authorization with OpenID SSE and CAEP (The New Stack, Tulshibagwale)</t>
+          <t>How AuthZEN, Shared Signals &amp; CAEP Complement Each Other (OpenID Foundation)</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>An article from CAEP's original inventor explaining how SSE+CAEP enable just-in-time authorization decisions instead of long-lived session-based access.</t>
+          <t>An OpenID Foundation explainer arguing that AuthZEN and SSF/CAEP are complementary — sync access decisions vs async session updates — not competing standards.</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>https://thenewstack.io/just-in-time-authorization-with-openid-sse-and-caep/</t>
+          <t>https://openid.net/how-authzen-and-shared-signals-caep-complement-each-other/</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Industry article (The New Stack)</t>
+          <t>OpenID Foundation</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Background piece by Atul Tulshibagwale (SGNL CTO, CAEP inventor) explaining the architectural intent.</t>
+          <t>Useful when explaining the layering to stakeholders confused by the OpenID alphabet soup.</t>
         </is>
       </c>
     </row>
@@ -7288,27 +10760,27 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>How AuthZEN, Shared Signals &amp; CAEP Complement Each Other (OpenID Foundation)</t>
+          <t>OAuth 2.1 Features You Can't Ignore in 2026 (Gutierrez, Medium)</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>An OpenID Foundation explainer arguing that AuthZEN and SSF/CAEP are complementary — sync access decisions vs async session updates — not competing standards.</t>
+          <t>A practitioner article summarizing why OAuth 2.1 — mandated PKCE, exact redirect matching, sender-constrained tokens — is the 2026 minimum bar for delegated authorization.</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>https://openid.net/how-authzen-and-shared-signals-caep-complement-each-other/</t>
+          <t>https://rgutierrez2004.medium.com/oauth-2-1-features-you-cant-ignore-in-2026-a15f852cb723</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>OpenID Foundation</t>
+          <t>Industry blog (Medium)</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Useful when explaining the layering to stakeholders confused by the OpenID alphabet soup.</t>
+          <t>Author is Cyber Intelligence Lead — IAM/AI at Oracle; concise piece suitable for executive briefings.</t>
         </is>
       </c>
     </row>
@@ -7318,27 +10790,27 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>OAuth 2.1 Features You Can't Ignore in 2026 (Gutierrez, Medium)</t>
+          <t>RFC 9396: OAuth 2.0 Rich Authorization Requests (CIAM Weekly)</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>A practitioner article summarizing why OAuth 2.1 — mandated PKCE, exact redirect matching, sender-constrained tokens — is the 2026 minimum bar for delegated authorization.</t>
+          <t>A practitioner deep-dive on RAR explaining why scopes alone don't carry transaction-level intent and how authorization_details is being adopted in payments and verifiable credentials.</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>https://rgutierrez2004.medium.com/oauth-2-1-features-you-cant-ignore-in-2026-a15f852cb723</t>
+          <t>https://ciamweekly.substack.com/p/rfc-9396-oauth-20-rich-authorization</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Industry blog (Medium)</t>
+          <t>Industry newsletter</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Author is Cyber Intelligence Lead — IAM/AI at Oracle; concise piece suitable for executive briefings.</t>
+          <t>Captures the current (March 2026) state of RAR adoption, including CAMARA telco APIs and DPV-purpose binding proposals.</t>
         </is>
       </c>
     </row>
@@ -7348,27 +10820,27 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>RFC 9396: OAuth 2.0 Rich Authorization Requests (CIAM Weekly)</t>
+          <t>Technical Deconstruction of MCP Authorization (kane.mx, Nov 2025)</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>A practitioner deep-dive on RAR explaining why scopes alone don't carry transaction-level intent and how authorization_details is being adopted in payments and verifiable credentials.</t>
+          <t>A long-form technical article showing that the Model Context Protocol's authorization spec is, in practice, an OAuth 2.1 profile combined with RFC 9728 protected-resource metadata and RFC 7591 dynamic registration.</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>https://ciamweekly.substack.com/p/rfc-9396-oauth-20-rich-authorization</t>
+          <t>https://kane.mx/posts/2025/mcp-authorization-oauth-rfc-deep-dive/</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Industry newsletter</t>
+          <t>Independent technical blog</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Captures the current (March 2026) state of RAR adoption, including CAMARA telco APIs and DPV-purpose binding proposals.</t>
+          <t>Calls out RFC 8707 (Resource Indicators) as the critical compatibility bottleneck since most major IdPs use proprietary audience parameters.</t>
         </is>
       </c>
     </row>
@@ -7378,27 +10850,27 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Technical Deconstruction of MCP Authorization (kane.mx, Nov 2025)</t>
+          <t>AI Agents Authentication: How Autonomous Systems Prove Identity (GitGuardian)</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>A long-form technical article showing that the Model Context Protocol's authorization spec is, in practice, an OAuth 2.1 profile combined with RFC 9728 protected-resource metadata and RFC 7591 dynamic registration.</t>
+          <t>A GitGuardian engineering article arguing that delegated, short-lived OAuth grants are structurally safer than the static API keys that produced 28.65M secret leaks in 2025.</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>https://kane.mx/posts/2025/mcp-authorization-oauth-rfc-deep-dive/</t>
+          <t>https://blog.gitguardian.com/ai-agents-authentication-how-autonomous-systems-prove-identity/</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Independent technical blog</t>
+          <t>Industry blog (GitGuardian)</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Calls out RFC 8707 (Resource Indicators) as the critical compatibility bottleneck since most major IdPs use proprietary audience parameters.</t>
+          <t>Useful for the 'why delegated authorization &gt; shared secrets' business case with concrete 2025 incident data.</t>
         </is>
       </c>
     </row>
@@ -7408,27 +10880,27 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>AI Agents Authentication: How Autonomous Systems Prove Identity (GitGuardian)</t>
+          <t>User-Managed Access (UMA) 2.0 Comprehensive Guide (SSOJet, Feb 2026)</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>A GitGuardian engineering article arguing that delegated, short-lived OAuth grants are structurally safer than the static API keys that produced 28.65M secret leaks in 2025.</t>
+          <t>A 2026 industry guide reframing UMA 2.0 for current CIAM contexts, covering resource-set registration, permission tickets, requesting-party tokens (RPTs), and policy externalization gains.</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>https://blog.gitguardian.com/ai-agents-authentication-how-autonomous-systems-prove-identity/</t>
+          <t>https://ssojet.com/blog/user-managed-access-uma-2-0-comprehensive-guide</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Industry blog (GitGuardian)</t>
+          <t>Industry blog (SSOJet)</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Useful for the 'why delegated authorization &gt; shared secrets' business case with concrete 2025 incident data.</t>
+          <t>Cites Kantara analysis showing centralized-policy moves can cut authorization code 80% — useful pitch material.</t>
         </is>
       </c>
     </row>
@@ -7438,27 +10910,27 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Workload Identity – Key Takeaways from IETF 122 (Defakto)</t>
+          <t>Decentralized Identity and Verifiable Credentials: The Enterprise Playbook 2026</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>A practitioner recap of IETF 122 covering the WIMSE Workload Identity Token, Credential Exchange, and side-meeting work on bot/agent web authentication.</t>
+          <t>An enterprise-oriented guide explaining how W3C VCs, DIDs, and OpenID4VC enable the issuer-holder-verifier delegation model for digital credentials and EUDI Wallet acceptance.</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>https://www.defakto.security/blog/workload-identity-key-takeaways-from-ietf-122/</t>
+          <t>https://securityboulevard.com/2026/03/decentralized-identity-and-verifiable-credentials-the-enterprise-playbook-2026/</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Industry blog (Defakto)</t>
+          <t>Industry article (Security Boulevard)</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Author Pieter Kasselman is co-author of multiple key drafts (Transaction Tokens, First-Party Apps); strong primary-source view.</t>
+          <t>Critical 2027 EU compliance dates: banks, telecom, healthcare, and very-large platforms must accept EUDI Wallet.</t>
         </is>
       </c>
     </row>
@@ -7468,27 +10940,27 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>User-Managed Access (UMA) 2.0 Comprehensive Guide (SSOJet, Feb 2026)</t>
+          <t>OAuth 2.0 &amp; OpenID Connect: The Complete Guide to What the Standards Actually Say (Patil, Medium)</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>A 2026 industry guide reframing UMA 2.0 for current CIAM contexts, covering resource-set registration, permission tickets, requesting-party tokens (RPTs), and policy externalization gains.</t>
+          <t>A practitioner-friendly synthesis covering OAuth 2.0 core, the OAuth 2.1 draft, RFC 9068 JWT access tokens, RFC 8252 native apps, and RFC 8628 device authorization.</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>https://ssojet.com/blog/user-managed-access-uma-2-0-comprehensive-guide</t>
+          <t>https://mrutyunjaypatil.medium.com/oauth-2-0-openid-connect-the-complete-guide-to-what-the-standards-actually-say-e92f040a4251</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Industry blog (SSOJet)</t>
+          <t>Industry blog (Medium)</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Cites Kantara analysis showing centralized-policy moves can cut authorization code 80% — useful pitch material.</t>
+          <t>Good handoff document for engineers new to the area; cites the current standards rather than legacy patterns.</t>
         </is>
       </c>
     </row>
@@ -7498,27 +10970,27 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Decentralized Identity and Verifiable Credentials: The Enterprise Playbook 2026</t>
+          <t>LinkedIn Engineering — OpenID Connect Authentication for Sign In with LinkedIn V2</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>An enterprise-oriented guide explaining how W3C VCs, DIDs, and OpenID4VC enable the issuer-holder-verifier delegation model for digital credentials and EUDI Wallet acceptance.</t>
+          <t>LinkedIn's own engineering write-up on adopting OpenID Connect on top of OAuth 2.0, explicitly distinguishing OAuth's delegated-access role from OIDC's identity-assertion role.</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>https://securityboulevard.com/2026/03/decentralized-identity-and-verifiable-credentials-the-enterprise-playbook-2026/</t>
+          <t>https://www.linkedin.com/developers/news/featured-updates/openid-connect-authentication</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Industry article (Security Boulevard)</t>
+          <t>Industry (LinkedIn Engineering)</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Critical 2027 EU compliance dates: banks, telecom, healthcare, and very-large platforms must accept EUDI Wallet.</t>
+          <t>Real-world example from LinkedIn explaining why they layered OIDC over an existing OAuth 2.0 delegated-access stack.</t>
         </is>
       </c>
     </row>
@@ -7528,27 +11000,27 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>OAuth 2.0 &amp; OpenID Connect: The Complete Guide to What the Standards Actually Say (Patil, Medium)</t>
+          <t>Rich Authorization Requests (RAR) — Authlete Knowledge Base</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>A practitioner-friendly synthesis covering OAuth 2.0 core, the OAuth 2.1 draft, RFC 9068 JWT access tokens, RFC 8252 native apps, and RFC 8628 device authorization.</t>
+          <t>A vendor knowledge-base article giving worked examples of RAR's authorization_details object, including locations, actions, datatypes, and identifier fields with their Authlete bindings.</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>https://mrutyunjaypatil.medium.com/oauth-2-0-openid-connect-the-complete-guide-to-what-the-standards-actually-say-e92f040a4251</t>
+          <t>https://www.authlete.com/kb/oauth-and-openid-connect/authorization-requests/rich-authorization-requests/</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Industry blog (Medium)</t>
+          <t>Vendor documentation (Authlete)</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Good handoff document for engineers new to the area; cites the current standards rather than legacy patterns.</t>
+          <t>Authlete is one of the few certified FAPI 2.0 + RAR implementations; useful reference for concrete request bodies.</t>
         </is>
       </c>
     </row>
@@ -7558,27 +11030,27 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn Engineering — OpenID Connect Authentication for Sign In with LinkedIn V2</t>
+          <t>An Introduction to Authorization Exchange (AuthZEN) — Curity</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn's own engineering write-up on adopting OpenID Connect on top of OAuth 2.0, explicitly distinguishing OAuth's delegated-access role from OIDC's identity-assertion role.</t>
+          <t>A vendor explainer comparing externalized-authorization patterns (OPA, Cedar, XACML, Zanzibar) and showing how AuthZEN's API normalizes the PDP/PEP wire protocol across them.</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/developers/news/featured-updates/openid-connect-authentication</t>
+          <t>https://curity.io/resources/learn/authzen/</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Industry (LinkedIn Engineering)</t>
+          <t>Vendor blog (Curity)</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Real-world example from LinkedIn explaining why they layered OIDC over an existing OAuth 2.0 delegated-access stack.</t>
+          <t>Curity is a member of the AuthZEN WG; positions AuthZEN as 'OpenID Connect for authorization' which has become the common framing.</t>
         </is>
       </c>
     </row>
@@ -7588,27 +11060,27 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Rich Authorization Requests (RAR) — Authlete Knowledge Base</t>
+          <t>ACLX — AI Output Governance (Proprietary)</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>A vendor knowledge-base article giving worked examples of RAR's authorization_details object, including locations, actions, datatypes, and identifier fields with their Authlete bindings.</t>
+          <t>A proprietary enforcement layer that intercepts AI-generated content between inference and delivery, evaluating it against OPA/Cedar policies, identity context, and a three-phase sensitivity detection stack: deterministic regex rules → ontology-based compilation-risk scoring → semantic LLM evaluation for novel synthesis. Four enforcement outcomes: ALLOW, REDACT, BLOCK, or ESCALATE to human review. Treats agents as first-class principals evaluated at the output boundary regardless of whether a session or IDP exists.</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>https://www.authlete.com/kb/oauth-and-openid-connect/authorization-requests/rich-authorization-requests/</t>
+          <t>https://aclx.ai/</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Vendor documentation (Authlete)</t>
+          <t>Proprietary product</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Authlete is one of the few certified FAPI 2.0 + RAR implementations; useful reference for concrete request bodies.</t>
+          <t>No published specification. Identifies a gap the corpus standards map does not yet cover: identity (OIDC/SCIM/SPIFFE), signals (CAEP/SSF), policy (OAuth/AuthZEN/OPA), and enforcement (ZTA/RATS/SCITT) all have standards, but output evaluation — governing what the AI synthesizes rather than what the user was authorized to ask — has none. The synthesis-detection layer (AI compiling across individually-authorized sources to produce content crossing a higher sensitivity boundary) is a novel problem the corpus's existing standards do not address.</t>
         </is>
       </c>
     </row>
@@ -7618,27 +11090,27 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>An Introduction to Authorization Exchange (AuthZEN) — Curity</t>
+          <t>McGuinness — Kerberos Won Because Nobody Had to Implement It</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>A vendor explainer comparing externalized-authorization patterns (OPA, Cedar, XACML, Zanzibar) and showing how AuthZEN's API normalizes the PDP/PEP wire protocol across them.</t>
+          <t>The question worth asking about AAuth is not only whether the protocol is good. Kerberos won because of everything around the protocol: SSPI and GSS-API hid the mechanism from application developers, the LSA owned keys and ticket lifecycle, machine accounts existed as a side effect of domain join, Active Directory shipped the KDC by default, and SPNEGO made rollout incremental.</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>https://curity.io/resources/learn/authzen/</t>
+          <t>https://notes.karlmcguinness.com/notes/kerberos-won-because-nobody-had-to-implement-it/</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Vendor blog (Curity)</t>
+          <t>Industry blog (Independent)</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Curity is a member of the AuthZEN WG; positions AuthZEN as 'OpenID Connect for authorization' which has become the common framing.</t>
+          <t>Published 10 Aug 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
         </is>
       </c>
     </row>
@@ -7648,27 +11120,1197 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>ACLX — AI Output Governance (Proprietary)</t>
+          <t>McGuinness — The Runtime Mints the Identity. That Does Not Make It the Authority.</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>A proprietary enforcement layer that intercepts AI-generated content between inference and delivery, evaluating it against OPA/Cedar policies, identity context, and a three-phase sensitivity detection stack: deterministic regex rules → ontology-based compilation-risk scoring → semantic LLM evaluation for novel synthesis. Four enforcement outcomes: ALLOW, REDACT, BLOCK, or ESCALATE to human review. Treats agents as first-class principals evaluated at the output boundary regardless of whether a session or IDP exists.</t>
+          <t>Agent runtimes naturally create the first trustworthy evidence about an instance, which gives them the default position in agent identity. Runtime proof and enterprise binding are still separate jobs. In heterogeneous enterprises, a binding layer can map evidence from many runtimes into durable Agent and Agent Deployment records and supply that governed context to credential issuers and resources.</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>https://aclx.ai/</t>
+          <t>https://notes.karlmcguinness.com/notes/the-runtime-mints-the-identity/</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Proprietary product</t>
+          <t>Industry blog (Independent)</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>No published specification. Identifies a gap the corpus standards map does not yet cover: identity (OIDC/SCIM/SPIFFE), signals (CAEP/SSF), policy (OAuth/AuthZEN/OPA), and enforcement (ZTA/RATS/SCITT) all have standards, but output evaluation — governing what the AI synthesizes rather than what the user was authorized to ask — has none. The synthesis-detection layer (AI compiling across individually-authorized sources to produce content crossing a higher sensitivity boundary) is a novel problem the corpus's existing standards do not address.</t>
+          <t>Published 10 Aug 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Agent Authority Has No General System of Record</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Agent task authority is scattered across four de facto records: harness permission prompts, OAuth grants, IAM roles, and change tickets. Each performs a real job, but none is a general, portable system of record for approved work. An action click is not task approval, a grant is not a task lifecycle, and an identity role is not a reason for one undertaking.</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/agent-authority-has-no-system-of-record/</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>Published 10 Aug 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — The MCP Lesson</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>The control-points series argues that distribution determines defaults and standard seams determine whether those defaults remain contestable. MCP adds the clock. It launched with a specification, SDKs, a distributed host, and reference servers, and one developer could run the whole loop before the ecosystem coordinated. Mature authorization and governance followed the adoption pressure.</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/the-mcp-lesson/</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Published 10 Aug 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Cross App Access Shows How the Layered Play Ships</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Cross App Access is not twenty-five generally available integrations. It is three different things at three different stages: a stable MCP authorization extension, a live Claude and Okta beta, and a partner graph whose broader product rollout is still under way. That distinction makes the strategic result clearer.</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/cross-app-access-is-the-layered-play-shipping/</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Published 10 Aug 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — A Blocked Agent Is a Captive Client</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Long-running agents discover mid-task that they need a destination their egress proxy does not allow, and the block comes back as an opaque connection failure with no machine-actionable way to ask for access and no human standing by. That block is a requestable denial, and the egress proxy is a policy enforcement point.</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/a-blocked-agent-is-a-captive-client/</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Published 10 Aug 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — The Company's Memory Must Be an Enterprise Record</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Model routers and customer-controlled agent state are now concrete product architectures, but they do not make every model interchangeable or every memory store strategic. The important boundary is narrower. Task checkpoints are operational state, transcripts are evidence, embeddings are derived indexes, and model-generated memories are untrusted proposals.</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/the-companys-memory-is-an-enterprise-record/</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>Published 10 Aug 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Continuity Is Not One Thing</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Delegated work forces four separate continuity questions: request provenance, identity attribution, target-applicable authority, and continuing work justification. Their answers compose through a common boundary contract: authoritative sources, bound and correlated evidence, explicit lifecycle semantics, local decisions, and declared failure behavior.</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/continuity-is-not-one-thing/</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Published 10 Aug 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — The Continuity Evaluation Kit</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Continuity Is Not One Thing argues that delegated work poses four independently governed continuity questions.</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/continuity-evaluation-kit/</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>Published 10 Aug 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — The Enterprise Agent Control Stack</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>The enterprise agent control stack is not one product or one call chain. It is a set of independently governed answers: which instance is running, whose Agent it is, which deployment was approved, why its current work remains authorized, what an issuer may project, how credentials are acquired and presented, whether a resource permits one concrete action, and which evidence proves the joins afterward.</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/the-enterprise-agent-stack/</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Published 10 Aug 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Least-Privilege MCP Tool Calls Need a Mission</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>The least-privilege MCP series ends on a gap: token-side and resource-side authorization both work per call, and neither names the task the user approved. This essay applies Mission-Bound Authorization at the MCP boundary.</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/least-privilege-mcp-tool-calls-need-a-mission/</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Least Exposure Is Broader Than Least Privilege</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Least privilege scopes what an agent may do, one tool call at a time. But a perfectly authorized agent can still be compromised by what it is allowed to see. Least exposure is the broader control: task-scoped minimal disclosure for prompt context, retrieved documents, tool schemas, secrets, business rules, approval context, memory, and downstream responses.</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/least-exposure-is-broader-than-least-privilege/</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — The Question Authorization Never Answered</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Authorization looks the way it does because each generation solved the question its era made urgent, and deferred one question that someone else was always carrying: what approved work is this, and is it still on? Purpose was not absent. A second stack of tickets, purchase orders, workflows, and approval systems held it locally, and people carried it between systems.</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/the-question-authorization-never-answered/</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Weighing Mission-Bound Authorization</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>A handbook that ends on its own argument has not concluded, it has just stopped.</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/series/weighing-mission-bound-authorization/</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); series index. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Testing Mission-Bound Authorization</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>An architecture that only answers its own questions is untested. This chapter runs the handbook against five outside framings: Simon Willison’s lethal trifecta, the threat model that defines what makes agents dangerous. Patrick Parker’s Seven Laws of AIdentity, mapped law by law with coverage and caveats stated rather than claimed whole.</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/series/testing-mission-bound-authorization/</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); series index. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Building Mission-Bound Authorization</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Designing Mission-Bound Authorization establishes the architecture: the object, the laws, the framework, and the staged adoption path. This chapter is the build.</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/series/building-mission-bound-authorization/</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); series index. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Designing Mission-Bound Authorization</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>The AI agent auth best-practices draft names the Mission and declares its translation into authorization out of scope. This chapter is that translation, at architecture depth: the problem in one screen, the vocabulary, the missing layer, the five laws, the reference security architecture, and the canonical picture. Part 1 is the joint between the card model and the protocol. Part 2 defines the Mission.</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/series/designing-mission-bound-authorization/</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); series index. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — What the Corporate Card Already Solved</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Enterprises already run a mature delegated-authority architecture. It is called expense governance, and payments spent fifty years hardening it: purpose-issued instruments, approvals bound to what the approver was shown, delegation that only narrows, a network that authorizes every transaction, and cancellations, disputes, and statements that close the loop.</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/series/what-the-corporate-card-already-solved/</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); series index. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — The Identity Continuation Assertion</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Re-subjecting across a SaaS boundary is a mint, not an attenuation, so the IdP must issue each onward grant. ID-JAG covers the first hop, where an application holds the user’s ID Token or SAML assertion to exchange. Subsequent hops hold no end-user credential, which leaves a gap: the intermediate has nothing to present to the IdP to continue the chain. The Identity Continuation Assertion fills it.</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/identity-continuation-assertion/</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>Published 8 Jul 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Trusting Issuers in Open-World OAuth</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Self-service agent sign-up exposes a first-contact trust problem: a Resource Authorization Server can verify a perfectly valid JWT and still not know whether the issuer is allowed to assert identities for the user’s domain. That is two questions, not one.</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/trusting-issuers-in-open-world-oauth/</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Published 5 Jul 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Closing the Gaps in Least-Privilege MCP Tool Calls</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Part one laid out two ways to lock down a single tool call an agent makes through the Model Context Protocol: carry a narrow token, or let the resource decide each call. This part walks the standards that close the gaps.</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/closing-the-gaps-least-privilege-mcp-tool-calls/</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>Published 26 Jun 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Two Models for Least-Privilege MCP Tool Calls</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>There are two natural ways to lock an agent’s Model Context Protocol (MCP) tool calls down to least privilege. The agent can carry a narrow token scoped to the action, or the server can decide each call as it happens. Carrying a token gives portable proof of what the agent may do, but pushes domain knowledge onto the authorization server and token management onto the client.</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/least-privilege-mcp-tool-calls/</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Published 25 Jun 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Authorization Is the Other Half of Executable Intent</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Microsoft’s ASSERT compiles written behavior requirements into executable evaluations: intent made executable for verification. That answers what the agent did, not what it was allowed to do: an eval produces a verdict, not a binding authorization decision, and for irreversible actions that is the whole difference.</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/authorization-is-the-other-half-of-executable-intent/</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>Published 10 Jun 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — SAML at the Post-Quantum Crossroads</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>OpenID Connect is mature, standardized, and widely deployed, but SAML remains the enterprise SSO default because it is familiar, explicit, and deeply embedded in procurement and operations.</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/saml-at-the-post-quantum-crossroads/</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Published 28 May 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — The Agent Provider Is the IdP: A Standards Reading of WorkOS auth.md</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>WorkOS auth.md is an agent-readable registration document for one-click setup, with Agent Verified, user-claimed, and anonymous paths. In the Agent Verified path, most pieces already exist across OAuth and OpenID standards: ID-JAG, OAuth metadata, dynamic client registration, standard token endpoints, and SSF/CAEP/OPC.</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/agent-provider-is-the-idp-standards-reading-of-workos-auth-md/</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 May 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Sessions Are Not Missions</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Modern agent harnesses make work durable across restarts, devices, background jobs, and sub-agents. That durability is a runtime property, not a governance property. A session answers where the agent can continue working. A mission answers why the agent is allowed to keep working. Conflating them is a central failure mode of long-running autonomous agent systems.</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/sessions-are-not-missions/</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Published 11 May 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Client Instances Are Actors, Not New Clients</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>Client instances are not new clients. They are actors. With the Actor Profile and the act chain already in place, and an instance_issuers field that fits any client registration channel (static, Dynamic Client Registration, or CIMD), treating instances as first-class actors needs no new grant type, no new client type, and no new claim. It needs a profile that ties them together.</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/client-instances-are-actors-not-new-clients/</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>Published 5 May 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Enterprise SaaS Needs OAuth Federation Now</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Enterprise SaaS still defaults to app-by-app OAuth islands with their own clients, long-lived artifacts, and revocation paths. The architectural shift is OAuth federation: adopt issuer-mediated federation now for services and workloads, and adopt Cross-App Access (XAA) as the standards direction for user-delegated cross-app access.</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/enterprise-saas-needs-oauth-federation-now/</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Published 19 Apr 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — AAuth Now Has a Mission Layer</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>The new version of AAuth (draft-hardt-aauth-protocol-01, since resubmitted as draft-hardt-oauth-aauth-protocol) materially changes the earlier comparison. Mission is now first-class in the protocol, with PS-mediated approval, mission-aware token choreography, and governance endpoints.</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/aauth-now-has-a-mission-layer/</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>Published 13 Apr 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — ID-JAG Beyond the Enterprise IdP</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>ID-JAG, also often called Cross-App Access (XAA), is centered in the current draft on Enterprise IdP trust, but the issuer that matters is the immediate IdP the downstream authorization server already trusts for SSO and subject resolution, not necessarily the top-level workforce IdP.</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/id-jag-beyond-the-enterprise-idp/</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Published 5 Apr 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Open-World OAuth Still Needs Mission Shaping</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Open-world OAuth can improve discovery, resource binding, and first-contact trust. That still leaves the harder agent problem: how approved intent becomes bounded authority that stays governed across delegation chains, unfamiliar tools, consent expansion, revocation, and task termination.</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/open-world-oauth-still-needs-mission-shaping/</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>Published 21 Mar 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — OAuth for Open-World Ecosystems</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>OAuth was built for closed worlds, and that constraint is why it became mature. Agents expose the limits of that deployment model. This post traces what the newer OAuth standards get right and which substrate gaps still need to close.</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/oauth-for-open-world-ecosystems/</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Published 20 Mar 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Standardize `act` Across Assertion Grants and JWT Access Tokens</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>The current split between token exchange semantics and JWT access token practice creates avoidable interoperability failures. A common profile for act, grounded in entity profiles, can align JWT assertion grant and JWT access token processing.</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/standardize-act-across-assertion-grants-and-jwt-access-tokens/</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>Published 18 Mar 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Mission Shaping Is Not Enough</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Part 2 turns from the semantic problem to the runtime one. Quiet expansion, delegation, headless execution, stale state, and open-world execution all push Mission shaping past its strongest domain. Containment and runtime governance carry more of the safety burden.</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/mission-shaping-is-not-enough/</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>Published 18 Mar 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — The Mission Shaping Problem</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>This essay picks up from Part 4 of the Mission-Bound OAuth series and focuses on the first hard problem: how approved intent becomes a governable Mission. In structured domains that can look like staged Mission shaping or compilation. Many current deployments still do not do it at all.</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/the-mission-shaping-problem/</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>Published 17 Mar 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Why Mission-Bound OAuth Might Be the Wrong Answer</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound OAuth is a serious attempt to govern delegated agent authority using existing OAuth infrastructure. This post takes the pessimistic view: it may be the wrong answer because it asks the authorization server to become a governance engine, a lifecycle controller, and a mission ledger all at once.</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/why-mission-bound-oauth-might-be-the-wrong-answer/</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Published 15 Mar 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Client Context and ID-JAG for Mission-Bound OAuth</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Rich Authorization Requests are the natural first instinct for agent missions, but audience-bound access tokens and uneven cross-domain interoperability limit how far they can carry a governed task. Mission-Bound OAuth solves that by making the Mission a durable authority object at the authorization server.</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/client-context-and-id-jag-for-mission-bound-oauth/</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>Published 14 Mar 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Agents Don't Need Your Passport. They Need Your Authority.</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Enterprise IAM was designed for human-paced execution. Agents remove the presence, pacing, and natural scope-limiting that made those controls work. The result is a structural gap that stronger credentials, tighter scopes, and faster JIT provisioning cannot close.</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/agents-dont-need-your-passport-they-need-your-authority/</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>Published 21 Feb 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — From Passports to Power of Attorney</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Tokens, credentials, and scopes tell a system what an agent may do. They say nothing about why execution was authorized or when it should end. The Execution Mandate is the primitive that closes that gap: a signed, inspectable authority record that runtime systems can evaluate and revoke throughout the execution lifecycle.</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/from-passports-to-power-of-attorney/</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>Published 21 Feb 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Governing the Stay, Not Just the Entry</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>An Execution Mandate defines what delegated authority looks like. This post builds the control plane that makes it operational: how mandates are issued and held as authoritative artifacts, how authority is evaluated continuously rather than at gates, how governance crosses organizational boundaries, and where enforcement lands in practice.</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/governing-the-stay-not-just-the-entry/</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>Published 21 Feb 2026 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Welcome to Control Plane</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Identity is getting weird again, and in a good way. This blog is where I post hot takes, field notes, and analysis on identity, security, and agentic systems. Some posts will be tactical. Some will be opinionated.</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/welcome-to-control-plane/</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>Published 28 Apr 2025 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
         </is>
       </c>
     </row>
@@ -7716,6 +12358,45 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/delegated_authorization_research.xlsx
+++ b/delegated_authorization_research.xlsx
@@ -611,11 +611,11 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>251</v>
+        <v>290</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>★ THIS IS WHERE THE CURRENT WORK IS HAPPENING ★  OAuth recharter on 4 Jun 2026 IESG telechat. Aug 2026 sweep added 70 previously-untracked Datatracker drafts plus the Mission-Bound family.</t>
+          <t>★ THIS IS WHERE THE CURRENT WORK IS HAPPENING ★  The 4 Jun 2026 recharter is APPROVED (charter-ietf-oauth rev 06), making Complex Delegation chartered work — though no milestone has been attached to it yet. The 26 Aug 2026 sweep added 39 more drafts, including the first new WG-level entry (draft-ietf-oauth-rar-metadata-remediation), the six-draft Morrison ~handle identity family, and the NHE / VERA / AgentEnvelope autonomy-gating cluster.</t>
         </is>
       </c>
     </row>
@@ -687,15 +687,15 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Vendor blogs, LinkedIn-style articles, reference implementations (OVID/OVID-ME, ZeroID, WorkOS auth.md, Agent Trust Protocol), and the McGuinness Mission-Bound OAuth blog series.</t>
+          <t>Vendor blogs, LinkedIn-style articles, reference implementations (OVID/OVID-ME, ZeroID, WorkOS auth.md, Agent Trust Protocol), and the McGuinness Mission-Bound Authorization blog corpus.</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Practitioner content; the five implementations at the top of the tab show what an implementable agent-delegation stack looks like today. The Aug 2026 sweep backfilled the full Control Plane blog (47 posts, 41 newly added) — the Agent Control Points series (Aug 2026) and the Mission-Bound Authorization handbook (Jul 2026) are the two most substantial arcs.</t>
+          <t>Practitioner content; the five implementations at the top of the tab show what an implementable agent-delegation stack looks like today. The Aug 2026 sweeps backfilled the Control Plane blog to 50 entries — the Agent Control Points series (Aug 2026) and the Mission-Bound Authorization handbook (Jul 2026) are the two most substantial arcs. The 26 Aug sweep repointed three posts the site had re-slugged ('Mission-Bound OAuth' was renamed to 'Mission-Bound Authorization' throughout) and added the handbook single-page edition; the handbook's 27 individual chapters are not in the RSS feed and remain untracked.</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="6" t="n">
-        <v>366</v>
+        <v>408</v>
       </c>
       <c r="D11" s="7" t="n"/>
     </row>
@@ -906,7 +906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F252"/>
+  <dimension ref="A1:F291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 6 Aug 2026 (was -00, Jun 26 2026); authors: Thibault Meunier (Cloudflare), Sandor Major (Google). Replaces draft-meunier-web-bot-auth-architecture. Pairs with draft-meunier-webbotauth-httpsig-directory for key discovery.</t>
+          <t>Revision -02, 19 Aug 2026 (was -01, 6 Aug 2026) (was -00, Jun 26 2026); authors: Thibault Meunier (Cloudflare), Sandor Major (Google). Replaces draft-meunier-web-bot-auth-architecture. Pairs with draft-meunier-webbotauth-httpsig-directory for key discovery.</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Revision -17, Jul 22 2026 — rapid iteration signal heading into IETF 126. Previously IESG-approved and in RFC Editor queue; no RFC number assigned yet as of Jul 2026. The canonical multi-domain delegation pattern referenced by most agent and zero-trust drafts.</t>
+          <t>Revision -17, Jul 22 2026 — rapid iteration signal heading into IETF 126. IESG-approved and in the RFC Editor queue (rfceditor state 'In Progress', IANA actions acknowledged); still no RFC number assigned as of 21 Aug 2026. The canonical multi-domain delegation pattern referenced by most agent and zero-trust drafts.</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Revision -11, 4 Aug 2026 (was -09, published 6 Jul 2026 (was -08 Mar 2026)); co-authored by Tulshibagwale (CAEP inventor), Fletcher, and Kasselman. -09 reorganized the Request Context section, changed JWT body claims from OPTIONAL to RECOMMENDED, and enhanced security considerations for invalidated access tokens. Still in WGLC; IESG submission milestone Dec 2026.</t>
+          <t>Revision -11, 4 Aug 2026 (was -09, published 6 Jul 2026 (was -08 Mar 2026)); co-authored by Tulshibagwale (CAEP inventor), Fletcher, and Kasselman. -09 reorganized the Request Context section, changed JWT body claims from OPTIONAL to RECOMMENDED, and enhanced security considerations for invalidated access tokens. Advanced past WGLC: as of 21 Aug 2026 the stream state is 'WG Consensus: Waiting for Write-Up'. IESG submission milestone Dec 2026, and Transaction Tokens is one of only three active OAuth WG milestones under the approved rev-06 charter.</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Revision -27, 11 Aug 2026 (was -26, (Dec 2025)); critical for any delegated-authorization design touching SPAs because it codifies why pure-browser refresh tokens are deprecated.</t>
+          <t>**PUBLISHED as RFC 10017** (state changed 21 Aug 2026; became_rfc relation confirmed on Datatracker). No longer an active draft — candidate to move to the Published RFCs tab. Final draft revision was -27, 11 Aug 2026 (was -26, (Dec 2025)); critical for any delegated-authorization design touching SPAs because it codifies why pure-browser refresh tokens are deprecated.</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 27 March 2026; technically strong — Biscuit + Datalog is well-suited to scope attenuation. The 'AIP' name collision with draft-singla-agent-identity-protocol and draft-aip-agent-identity-protocol is a blocking issue for WG adoption.</t>
+          <t>Revision -01, 19 Aug 2026 (was -00, 27 March 2026); technically strong — Biscuit + Datalog is well-suited to scope attenuation. The 'AIP' name collision with draft-singla-agent-identity-protocol and draft-aip-agent-identity-protocol is a blocking issue for WG adoption.</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 29 March 2026; orthogonal to delegation but important for compliance — standardized audit-log format is a genuine gap. Complements identity frameworks well. A sibling/alternative to the Kuehlewind audit architecture which takes a far more ambitious cross-layer approach.</t>
+          <t>Revision -01, 19 Aug 2026 (was -00, 29 March 2026); orthogonal to delegation but important for compliance — standardized audit-log format is a genuine gap. Complements identity frameworks well. A sibling/alternative to the Kuehlewind audit architecture which takes a far more ambitious cross-layer approach.</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Revision -05, 9 Aug 2026 (was -02, Jul 2026). Fills a gap in the AGTP family (draft-hood-independent-agtp in corpus) and is relevant to any agent communication protocol carrying mixed-provenance claims. The verifier-separation model is the missing security architecture layer between protocol transport and authorization enforcement.</t>
+          <t>Revision -06, 17 Aug 2026 (was -05, 9 Aug 2026) (was -02, Jul 2026). Fills a gap in the AGTP family (draft-hood-independent-agtp in corpus) and is relevant to any agent communication protocol carrying mixed-provenance claims. The verifier-separation model is the missing security architecture layer between protocol transport and authorization enforcement.</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, Jul 2026; authors: Steven Mih (Action State Group) + Tom Sato (MyAuberge K.K.) — collaboration between the two principal authors of draft-mih-scitt-agent-action-capsule (corpus) and the SOOS governance suite (corpus). Operates above individual SCITT profiles; the accountability-composition layer the kuehlewind-audit-architecture HUB depends on but does not yet specify.</t>
+          <t>Revision -01, 16 Aug 2026 (was -00, Jul 2026); authors: Steven Mih (Action State Group) + Tom Sato (MyAuberge K.K.) — collaboration between the two principal authors of draft-mih-scitt-agent-action-capsule (corpus) and the SOOS governance suite (corpus). Operates above individual SCITT profiles; the accountability-composition layer the kuehlewind-audit-architecture HUB depends on but does not yet specify.</t>
         </is>
       </c>
     </row>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 23 Jun 2026; author: Tora Toraman (NordenSoft). The minimalist end of the SCITT profile spectrum; useful for corpus completeness alongside the more comprehensive draft-mih-scitt-agent-action-capsule.</t>
+          <t>Revision -01, 15 Aug 2026 (was -00, 23 Jun 2026); author: Tora Toraman (NordenSoft). The minimalist end of the SCITT profile spectrum; useful for corpus completeness alongside the more comprehensive draft-mih-scitt-agent-action-capsule.</t>
         </is>
       </c>
     </row>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>Revision -11, 10 Aug 2026 (was -08, Jul 21 2026). The base artifact for the EMILIA Protocol family; companion drafts draft-schrock-ep-authorization-evidence-chain, draft-schrock-ep-action-evidence-graph, draft-schrock-ep-quorum, and draft-schrock-ep-evidence-record all build on or reference this receipt format. Active iteration pace — -08 by late Jul 2026. Draft-rampalli-cross-org-delegation-mapping (corpus) formally maps EMILIA Protocol receipts against the nine reece-wimse-cross-org-delegation requirements.</t>
+          <t>Revision -12, 16 Aug 2026 (was -11, 10 Aug 2026) (was -08, Jul 21 2026). The base artifact for the EMILIA Protocol family; companion drafts draft-schrock-ep-authorization-evidence-chain, draft-schrock-ep-action-evidence-graph, draft-schrock-ep-quorum, and draft-schrock-ep-evidence-record all build on or reference this receipt format. Active iteration pace — -08 by late Jul 2026. Draft-rampalli-cross-org-delegation-mapping (corpus) formally maps EMILIA Protocol receipts against the nine reece-wimse-cross-org-delegation requirements.</t>
         </is>
       </c>
     </row>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, Jul 24 2026 (first filed Jul 21 2026); author: Thallapelly. Hardware-bound, WYSIWYG authorization token — distinct from software-only pre-action permit approaches such as draft-kumaresan-counter-sign (above) and the EMILIA Protocol family. The WYSIWYG disclosure binding addresses UI redress attacks where an agent's rendered action description differs from the actual HTTP request being authorized. Hardware PoP requirement makes this the highest-assurance pre-action permit in the current wave.</t>
+          <t>Revision -02, 15 Aug 2026 (was -01, Jul 24 2026) (first filed Jul 21 2026); author: Thallapelly. Hardware-bound, WYSIWYG authorization token — distinct from software-only pre-action permit approaches such as draft-kumaresan-counter-sign (above) and the EMILIA Protocol family. The WYSIWYG disclosure binding addresses UI redress attacks where an agent's rendered action description differs from the actual HTTP request being authorized. Hardware PoP requirement makes this the highest-assurance pre-action permit in the current wave.</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 10 Jun 2026; author: Tom Sato (MyAuberge K.K.). The authorization token primitive for the SOOS governance protocol family. Directly comparable to draft-mcguinness-oauth-client-instance-assertion but uses a WIMSE/Sovereign Object substrate rather than OAuth.</t>
+          <t>Revision -04, 13 Aug 2026 (was -01, 10 Jun 2026); author: Tom Sato (MyAuberge K.K.). The authorization token primitive for the SOOS governance protocol family. Directly comparable to draft-mcguinness-oauth-client-instance-assertion but uses a WIMSE/Sovereign Object substrate rather than OAuth.</t>
         </is>
       </c>
     </row>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, 28 Jun 2026 (was -02 Jun 10). -03 added OpenTelemetry attribute namespace for governance observability, a GAR Processor spec for converting OTel signals to audit records with integrity verification, four new Authority Lifecycle Event categories (policy conflict scenarios, statutory interpretation changes), and mandatory provenance fields for policy evaluation records. The integrator for the SOOS family, analogous to how draft-kuehlewind-audit-architecture integrates the broader IETF agent draft landscape.</t>
+          <t>Revision -06, 25 Aug 2026 (was -03, 28 Jun 2026) (was -02 Jun 10). -03 added OpenTelemetry attribute namespace for governance observability, a GAR Processor spec for converting OTel signals to audit records with integrity verification, four new Authority Lifecycle Event categories (policy conflict scenarios, statutory interpretation changes), and mandatory provenance fields for policy evaluation records. The integrator for the SOOS family, analogous to how draft-kuehlewind-audit-architecture integrates the broader IETF agent draft landscape.</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, 7 Aug 2026 (was -02, Jul 2 2026); authors: Linda Dunbar (Futurewei), YiFei Wang (China Telecom), Bing Liu (Huawei). The most directly useful DMSC document for the boundary analysis: explicitly names MCP and A2A as insufficient and articulates where the DMSC gateway fills the gap. The regulated-environment focus (financial services, telco) distinguishes DMSC's use-case target from OAuth-centric approaches.</t>
+          <t>Revision -04, 14 Aug 2026 (was -03, 7 Aug 2026) (was -02, Jul 2 2026); authors: Linda Dunbar (Futurewei), YiFei Wang (China Telecom), Bing Liu (Huawei). The most directly useful DMSC document for the boundary analysis: explicitly names MCP and A2A as insufficient and articulates where the DMSC gateway fills the gap. The regulated-environment focus (financial services, telco) distinguishes DMSC's use-case target from OAuth-centric approaches.</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 5 Jul 2026; useful problem-statement companion to the OAuth recharter's 'Complex Delegation' milestone. Gap analysis directly motivates several other drafts in this corpus — a natural reference document for the OAuth WG scoping discussion.</t>
+          <t>Revision -03, 25 Aug 2026 (was -01, 5 Jul 2026); useful problem-statement companion to the OAuth recharter's 'Complex Delegation' milestone. Gap analysis directly motivates several other drafts in this corpus — a natural reference document for the OAuth WG scoping discussion.</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 11 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -01, 11 Aug 2026; **now EXPIRED** on Datatracker (checked 26 Aug 2026). Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6165,7 +6165,7 @@
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>Revision -06, 11 Aug 2026. WG-adopted draft. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -06, 11 Aug 2026; advanced to IESG **AD Evaluation** as of 18 Aug 2026. WG-adopted draft. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 5 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -01, 18 Aug 2026 (was -00, 5 Aug 2026). Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 3 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -01, 26 Aug 2026 (was -00, 3 Aug 2026). Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
-          <t>Revision -11, 23 Jul 2026. WG-adopted draft. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -11, 23 Jul 2026; entered the RFC Editor queue (touched 13 Aug 2026, rfceditor state 'In Progress'). WG-adopted draft. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="F198" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 23 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -03, 24 Aug 2026 (was -02, 23 Jul 2026). Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -7815,7 +7815,7 @@
       </c>
       <c r="F230" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 9 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -01, 20 Aug 2026 (was -00, 9 Jun 2026). Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -8476,6 +8476,1176 @@
       <c r="F252" s="5" t="inlineStr">
         <is>
           <t>Revision -00, 19 Jul 2026. Skyfire KYA/KYAPay cluster (6 drafts incl. draft-skyfire-oauth-id-verification already in corpus) — agent identity verification and payment claims for OAuth/JWT. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="5" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" s="5" t="inlineStr">
+        <is>
+          <t>draft-morrison-mcp-tool-surface-names-registry — An IANA Registry for Model Context Protocol Tool Surface Names</t>
+        </is>
+      </c>
+      <c r="C253" s="5" t="inlineStr">
+        <is>
+          <t>This document requests the establishment of an IANA registry for Model Context Protocol [MCP-SPEC] tool surface names. A tool surface name is the wire-level identifier by which a client invokes a typed capability on an MCP server. Existing Morrison- family Internet- Drafts ([ORGALTER]) request IANA registration of specific surface names against a registry that does not yet exist. This document establishes the registry mechanism so that subsequent specifications can register names without restating the registry's structure or registration procedure. The registry uses Specification Required registration with a Designated Expert pool [RFC8126]. Initial contents are the four surface names registered by [ORGALTER]. Vendor-prefix conventions are recommended but not mandated.</t>
+        </is>
+      </c>
+      <c r="D253" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-mcp-tool-surface-names-registry/</t>
+        </is>
+      </c>
+      <c r="E253" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F253" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 11 Aug 2026. Requests an IANA registry for MCP tool surface names. Morrison family plumbing — exists because other Morrison drafts already request registrations against a registry that does not yet exist. Structural, not conceptual, but it is the family's dependency root.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="5" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" s="5" t="inlineStr">
+        <is>
+          <t>draft-morrison-identity-pronouns — Identity Pronouns: A Reference-Axis Extension to ~handle Identity Systems</t>
+        </is>
+      </c>
+      <c r="C254" s="5" t="inlineStr">
+        <is>
+          <t>This document defines an identity pronoun grammar as a reference axis orthogonal to the ~handle identity tier taxonomy defined in [MCPDNS] and [IDCOMMITS]. A pronoun is a session-scoped reference that resolves client-side to a concrete handle using local session state before any cryptographic, DNS, or federation operation. The entity- class taxonomy (Sovereign, Bot, Instrument) is unchanged; this specification introduces Absolute vs Pronoun as an orthogonal axis. A pronoun MUST NOT appear in a capability token, in a DNS record, in an Accord signature, or in any inter-organisational protocol payload. The reference implementation defines a single Wave-1 pronoun, ~org, that resolves to the concrete handle of the organisation bound to the caller's current session. An appendix defines a relative-path pronoun grammar (e.g. ~./architect, ~../weaver) as a non-normative design surface for future work. The mechanism is provider-neutral, introduces no new cryptographic primitive, and imposes zero new load on DNS, capability-token issuers, or federated resolvers.</t>
+        </is>
+      </c>
+      <c r="D254" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-identity-pronouns/</t>
+        </is>
+      </c>
+      <c r="E254" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F254" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 11 Aug 2026. Session-scoped 'pronoun' references that resolve client-side to concrete ~handle identities. Morrison family. Kept under the primary-body rule rather than on individual merit: the family is taken in full. Design note worth flagging — a pronoun MUST NOT appear in a capability token, DNS record, or Accord signature, which is an explicit boundary between local reference and wire-visible identity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="5" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" s="5" t="inlineStr">
+        <is>
+          <t>draft-morrison-identity-attributed-commits — Identity-Attributed Git Commits via Tier-Structured Trailers</t>
+        </is>
+      </c>
+      <c r="C255" s="5" t="inlineStr">
+        <is>
+          <t>This document defines a git commit trailer grammar for identity- attributed contributions using the ~handle identity primitive defined in [MCPDNS]. The grammar binds sovereign actors, automated bots, and AI instruments to specific commits via three tier-structured trailers (Acted-By, Executed-By, Drafted-With) and three optional cryptographic trailers (Identity-Signature, Identity-Key-Id, Identity-Anchor). The signature is computed with Ed25519 over the commit's tree hash rather than its commit hash, preserving attribution across rebase, cherry-pick, and squash merge operations. Conformant parsers reject cross-tier category errors (e.g., an Instrument-tier handle in an Acted-By slot) as malformed. The mechanism is provider-neutral, depends only on DNS [RFC1035] and the ~handle resolution algorithm of [MCPDNS], and requires no central authority or platform-specific verification service.</t>
+        </is>
+      </c>
+      <c r="D255" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-identity-attributed-commits/</t>
+        </is>
+      </c>
+      <c r="E255" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F255" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 11 Aug 2026. Git commit trailers (Acted-By / Executed-By / Drafted-With) binding sovereign actors, bots and AI instruments to specific commits. Morrison family. The three-tier actor taxonomy is a direct echo of the actor-chain question in draft-mcguinness-oauth-actor-profile and draft-mw-oauth-actor-chain, expressed in a completely different substrate. Ed25519 over the tree hash rather than the commit hash so attribution survives rebase and squash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="5" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" s="5" t="inlineStr">
+        <is>
+          <t>draft-morrison-agent-channel-fan-out — An Agent-Channel Frame for Identity-Keyed Fan-Out Delivery to Concurrent Sessions</t>
+        </is>
+      </c>
+      <c r="C256" s="5" t="inlineStr">
+        <is>
+          <t>This memo specifies an application-layer frame format and a delivery model by which the several concurrent agentic sessions of a single identity-bound principal, and the recognised members of an organisational identity substrate, exchange short structured messages. The frame, termed the agent-channel frame, is a transport envelope: it carries a closed-catalogue kind discriminator, a structured per-kind payload, an identity attribution pair, and an inline provenance block. Delivery is fan-out: a sender names a recipient scope rather than a single endpoint, and the scope is expanded at delivery time against the recipient's subscriptions. Recipients receive frames over a per-handle Server-Sent Events stream and MAY narrow what they receive with a subscribe-time filter expression. Frames are ephemeral routing units; the memo specifies only the wire envelope, the scope-expansion grammar, the subscribe filter grammar, and the delivery semantics. Frame persistence, where an implementation chooses to retain frames for replay, is out of scope and is not specified. The memo composes with the handle namespace of [IDPRONOUNS], the discovery surface of [MCPDNS], and the cross-organisational ceremony of [IDACCORD]; no new transport and no new handle category is introduced.</t>
+        </is>
+      </c>
+      <c r="D256" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-agent-channel-fan-out/</t>
+        </is>
+      </c>
+      <c r="E256" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F256" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 11 Aug 2026. Application-layer frame for identity-keyed fan-out delivery to the concurrent sessions of one identity-bound principal. Morrison family. Transport-shaped, but kept because the frame carries an identity attribution pair and inline provenance block — it is an identity-binding format, not a routing protocol.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="5" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" s="5" t="inlineStr">
+        <is>
+          <t>draft-hillier-certisyn-ai-governance-verified — AI Governance Verified -- A Cryptographic Verification Standard for Agentic AI Governance in Regulated Industries</t>
+        </is>
+      </c>
+      <c r="C257" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies a verification standard for the cryptographic attestation of agentic AI governance in regulated industries. It defines the Verification Reconciliation Object (VRO), the issuing- partner framework, the eight control areas through which AI governance posture is reconciled, three maturity-attestation levels (Documented, Operational, Adversarial-ready), and the cryptographic continuity requirements that together produce deterministic, independently reconstructable, auditor-grade attestations of agentic AI governance. The standard sits beneath ISO/IEC 42001:2023, the NIST AI Risk Management Framework, and other agentic AI governance frameworks, and produces the verifiable artefact those frameworks were designed to imply but do not deliver.</t>
+        </is>
+      </c>
+      <c r="D257" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hillier-certisyn-ai-governance-verified/</t>
+        </is>
+      </c>
+      <c r="E257" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F257" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 12 Aug 2026. Cryptographic attestation of agentic AI governance posture for regulated industries: the Verification Reconciliation Object, eight control areas, three maturity-attestation levels. Positioned beneath ISO/IEC 42001:2023, so it is the compliance-facing counterpart to the audit-architecture work. Hillier has two further drafts in this sweep (scitt-arp, coverage-attestation) that were dropped as non-agent supply-chain work — revisit if the author's direction turns agent-specific.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="5" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" s="5" t="inlineStr">
+        <is>
+          <t>draft-winmagic-oauth-condition-bound-keys — Condition-Bound Keys for Mutual-TLS Client Authentication and DPoP</t>
+        </is>
+      </c>
+      <c r="C258" s="5" t="inlineStr">
+        <is>
+          <t>Login and session protection are two markets solving one problem: verify identity before giving access. Online, access is mostly the transaction, so that is where identity should be verified. Done this way, there is no session and no login; identity assurance is embedded in the transaction: it is encrypted by a key only the right identity has. The key that does this exists only where an actor -- human or machine -- a platform, and local policy hold, now. It disappears when the conditions are no longer met. All three are observed on the endpoint. It is hardware-rooted by default and non-exfiltratable, existing nowhere else, and its presence means validity: the identity is live now. This document specifies that key and its uses: under mutual TLS, in a DPoP proof, as a raw public key, in Device Bound Session Credentials, and as a FIDO2 passkey, or in a non-FIDO mode carrying user verification without user interaction.</t>
+        </is>
+      </c>
+      <c r="D258" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-winmagic-oauth-condition-bound-keys/</t>
+        </is>
+      </c>
+      <c r="E258" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F258" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 12 Aug 2026. Binds mTLS client authentication and DPoP keys to conditions rather than to a bare key identity. Files cleanly into the OAuth wiki's **Proof of Possession** cluster, which the 11 Aug 2026 mapping flagged as showing 'Active Drafts: (none)' — this is further evidence that agent-era drafts should be filed by mechanism rather than by being agent-flavoured.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" s="5" t="inlineStr">
+        <is>
+          <t>draft-maintainer-1f916-agent-record — The Agent Record: Transparent, Witness-Countersigned Event Logs for AI Agent Identity, History, and Memory</t>
+        </is>
+      </c>
+      <c r="C259" s="5" t="inlineStr">
+        <is>
+          <t>Autonomous AI agents increasingly act as economic parties: they are hired, they pay, and they make claims about their own past conduct. No deployed standard lets a relying party verify an agent's identity continuity, the integrity of its claimed history, or the intactness of its persisted memory without trusting the agent's operator or platform. This document describes the Agent Record architecture: per-agent append-only event logs bound to Ed25519 keys, checkpointed with signed Merkle tree heads following the RFC 6962 construction, countersigned by independent witnesses, and exported as portable, offline-verifiable dossiers. Memory integrity is anchored by hash commitments recorded in the log, allowing an agent's future sessions, and any third party, to detect tampering with persisted state. The architecture is deployed in production at a founding registry; this document records its wire formats and security model to invite independent implementation and review, and to align terminology with the SCITT architecture, of which this system is an application- specific instance.</t>
+        </is>
+      </c>
+      <c r="D259" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-maintainer-1f916-agent-record/</t>
+        </is>
+      </c>
+      <c r="E259" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F259" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 13 Aug 2026. Per-agent append-only event logs bound to Ed25519 keys, checkpointed with signed Merkle tree heads on the RFC 6962 construction and countersigned by independent witnesses. **Unusual authorship signal: the draft's author slug is `maintainer-1f916` — U+1F916 is the robot-face emoji codepoint.** Treat provenance with care. The technical premise is serious and rare: agents as economic parties that make claims about their own past conduct, verifiable without trusting the operator or platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="5" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" s="5" t="inlineStr">
+        <is>
+          <t>draft-sirkkavaara-vaara-receipt — The Vaara Receipt: A Recomputable Receipt Format for Decisions About Autonomous Actions</t>
+        </is>
+      </c>
+      <c r="C260" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies vaara.receipt/v1, a signed and independently recomputable record that binds a decision about an autonomous action to the evidence the decision was made on, and optionally to one or more external timestamp anchors. The format is canonicalized with the JSON Canonicalization Scheme (JCS) so that any third party can recompute its digests and verify its signature without access to the issuer. A decision and the execution receipt that answers it form one recomputable pair through the envelope's back link. The receipt's trust is root-agnostic: the same record is verifiable with or without a hardware trusted execution environment and is re- expressible as an IETF RATS Entity Attestation Result. Downstream specifications (a payment rail, a compliance regime, a framework integration) define profiles that pin to a version of this document and add only their own evidence schema; they do not redefine the envelope. The format described here is deployed, and its receipts are independently recomputable from public conformance vectors that ship with standalone checkers importing no issuer code. The minimal profile is a governance decision over a single autonomous action, bound to the action's own intent with no external rail; it is the floor of the format, and a reference library offers a matching adoption floor at the API layer as a one-line decorator over the governed function.</t>
+        </is>
+      </c>
+      <c r="D260" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-sirkkavaara-vaara-receipt/</t>
+        </is>
+      </c>
+      <c r="E260" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F260" s="5" t="inlineStr">
+        <is>
+          <t>Revision -07, 13 Aug 2026. A *recomputable* receipt format for decisions about autonomous actions — at -07, one of the more mature individual receipt drafts in the corpus. Recomputability is the distinguishing claim: the receipt is not merely signed evidence but re-derivable, which is a stronger property than the Decision Evidence Records in the Mission-Bound runtime-enforcement profile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="5" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" s="5" t="inlineStr">
+        <is>
+          <t>draft-ruvalcaba-nhe-identity — NHE Identity: A Verifiable Key-Committed Identity and Genesis-Attestation Format for Autonomous Agents</t>
+        </is>
+      </c>
+      <c r="C261" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies how a Non-Human Entity (NHE) is identified and how one party verifies another's identity. An NHE identity is a verifiable cryptographic commitment: control of an identity key, bound by an append-only hash chain to the entity's genesis and to the lineage of its configuration, rather than a mere name. The document defines the identity chain data model (record structure, genesis sentinel, linkage rule, and the no-fork property), a proof-of-control challenge/response, an optional capability attestation that reveals a specific capability without revealing the rest of the configuration, and an optional hardware-rooted genesis-attestation profile. The data model is specified here; the concrete on-the-wire encoding is deferred to the next revision.</t>
+        </is>
+      </c>
+      <c r="D261" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ruvalcaba-nhe-identity/</t>
+        </is>
+      </c>
+      <c r="E261" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F261" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 13 Aug 2026. Verifiable key-committed identity plus genesis-attestation format for autonomous agents. First half of the NHE pair; the genesis attestation (proving how the agent came into existence) is a stronger origin claim than the instance assertions in draft-mcguinness-oauth-ai-agent-instance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="5" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" s="5" t="inlineStr">
+        <is>
+          <t>draft-ruvalcaba-nhe-authz — NHE Backchannel Authorization: Graduated Autonomy and Intent-Scoped Credentials for Autonomous Agent Actions</t>
+        </is>
+      </c>
+      <c r="C262" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies how a consequential action attempted by a Non-Human Entity (NHE) is authorized at the time it is attempted. A security runtime transparently intercepts an entity's outbound action, so the entity holds no standing credentials, and classifies it under graduated autonomy as autonomous, supervised, or denied. A supervised action triggers a backchannel approval flow that presents a human approver with a human-readable rendering of the exact operation; on approval the runtime issues an intent-scoped, single- use, short-lived credential cryptographically bound to that specific action, which an enforcement point verifies against the operation actually being forwarded. The same canonical parameter digest scopes the credential and appears in the human-facing description, so the approver provably authorizes exactly what the credential permits. The flow and credential data model are specified here; the wire encoding is deferred to the next revision.</t>
+        </is>
+      </c>
+      <c r="D262" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ruvalcaba-nhe-authz/</t>
+        </is>
+      </c>
+      <c r="E262" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F262" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 13 Aug 2026. Backchannel authorization with **graduated autonomy** and intent-scoped credentials. Second half of the NHE pair. 'Graduated autonomy' and 'intent-scoped' are close cousins of the Mission-Bound Conformance Ladder (L0–L5) and mission_intent RAR envelope respectively, arrived at independently — worth comparing directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="5" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" s="5" t="inlineStr">
+        <is>
+          <t>draft-daniel-ai-agent-internet-architecture — Architectural Requirements for Supporting AI Agents on the Internet</t>
+        </is>
+      </c>
+      <c r="C263" s="5" t="inlineStr">
+        <is>
+          <t>Autonomous AI agents are evolving from interactive assistants into networked software workloads that discover services, invoke tools, delegate authority, transact, communicate with other agents, and act asynchronously on behalf of humans and organizations. Existing Internet protocols provide strong foundations, but agent autonomy, dynamic delegation, machine-speed execution, and cross-domain interaction create requirements that span multiple protocol families. This document describes architectural requirements for supporting AI agents on the Internet across naming and discovery, HTTP, authentication, authorization and delegation, TLS and workload identity, asynchronous messaging, capability and intent-based resolution, payments, provenance, auditability, revocation, security, and privacy. It favors profiling and extending existing Internet protocols over defining a monolithic new agent protocol, and identifies the need for IETF-wide architectural coordination.</t>
+        </is>
+      </c>
+      <c r="D263" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-daniel-ai-agent-internet-architecture/</t>
+        </is>
+      </c>
+      <c r="E263" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F263" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 13 Aug 2026. Architectural requirements for supporting AI agents on the Internet. A framework document rather than a mechanism — belongs with the adjacent/cross-cutting cluster alongside the other applicability and architecture statements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="5" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" s="5" t="inlineStr">
+        <is>
+          <t>draft-gaikwad-agent-proxy-modes — Proxy Modes for Agent-Tool Protocols</t>
+        </is>
+      </c>
+      <c r="C264" s="5" t="inlineStr">
+        <is>
+          <t>Agent-tool protocols such as the Model Context Protocol (MCP) enable AI applications to discover and invoke external tools, resources, and prompts through a standardized JSON-RPC interface. As deployments scale, intermediaries (proxies, gateways, sidecars) are inserted between clients and servers to provide transport adaptation, capability aggregation, security enforcement, and operational governance. No specification currently defines the behavioral requirements for such intermediaries. This document establishes a taxonomy of proxy modes, a layered architecture for pluggable proxy functionality, and normative requirements for each mode. It is designed to be protocol- agnostic in its architecture while referencing MCP as the primary instantiation.</t>
+        </is>
+      </c>
+      <c r="D264" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-gaikwad-agent-proxy-modes/</t>
+        </is>
+      </c>
+      <c r="E264" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F264" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 14 Aug 2026. Proxy modes for agent-tool protocols. Enumerates how an intermediary sits between agent and tool, which is precisely where authority is most often silently laundered — the delegation-mechanics question the actor-chain drafts raise, at the proxy layer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="5" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" s="5" t="inlineStr">
+        <is>
+          <t>draft-cui-dmsc-agent-cdi — Cross-Domain Interoperability Framework for AI Agent Collaboration</t>
+        </is>
+      </c>
+      <c r="C265" s="5" t="inlineStr">
+        <is>
+          <t>This document defines a framework for enabling seamless cross-domain interoperability among AI agents operating across different networks, administrative domains, and heterogeneous platforms. The framework addresses the challenges of identity federation, trust establishment, policy harmonization, and secure communication that arise when AI agents from distinct administrative realms need to collaborate on shared tasks. It specifies mechanisms for agent discovery, capability negotiation, trust delegation, and federated policy enforcement, enabling scalable and secure multi-domain AI collaboration without requiring centralized control.</t>
+        </is>
+      </c>
+      <c r="D265" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-cui-dmsc-agent-cdi/</t>
+        </is>
+      </c>
+      <c r="E265" s="5" t="inlineStr">
+        <is>
+          <t>IETF (DMSC-related, individual)</t>
+        </is>
+      </c>
+      <c r="F265" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 14 Aug 2026. Cross-domain interoperability framework for AI agent collaboration. DMSC family. Directly on the axis the approved OAuth charter now names — 'automated agents act across multiple administrative domains' — but approached from the DMSC gateway tradition rather than from OAuth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="5" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" s="5" t="inlineStr">
+        <is>
+          <t>draft-jia-oauth-scope-aggregation — OAuth 2.0 Scope Aggregation for Multi-Step AI Agent Workflows</t>
+        </is>
+      </c>
+      <c r="C266" s="5" t="inlineStr">
+        <is>
+          <t>This document describes a scope-aggregated OAuth 2.0 authorization pattern for multi-step AI agent workflows. An AI agent aggregates the scopes required across a workflow and only initiates a single authorization procedure for the aggregated scope. This reduces repeated user consents and multiple authorization round-trips, improving authorization efficiency.</t>
+        </is>
+      </c>
+      <c r="D266" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-jia-oauth-scope-aggregation/</t>
+        </is>
+      </c>
+      <c r="E266" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F266" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 14 Aug 2026. Scope aggregation across multi-step AI agent workflows. Worth reading against the Mission-Bound line, which argues the opposite direction: Mission-Bound attenuates and binds authority to one approved task, while aggregation composes scope across steps. A genuine design fork in how multi-step agent authority should accumulate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="5" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" s="5" t="inlineStr">
+        <is>
+          <t>draft-feng-dmsc-intent-routing-requirements — Requirements for Intent Routing in Multi-Agent Systems at Internet Scale</t>
+        </is>
+      </c>
+      <c r="C267" s="5" t="inlineStr">
+        <is>
+          <t>The rapid proliferation of autonomous AI agents across enterprise and Internet-scale deployments creates a structural challenge that existing agent frameworks cannot address: how to enable any agent to reach and invoke any other agent's capabilities without pre- established bilateral integration, across organizational boundaries, at Internet scale. This document states the normative requirements for that problem. It prescribes no solution, no specific mechanism, no message format, and no assumption of centralized or distributed architecture. Its purpose is to establish a verifiable yardstick against which any claimed "intent routing" solution can be judged.</t>
+        </is>
+      </c>
+      <c r="D267" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-feng-dmsc-intent-routing-requirements/</t>
+        </is>
+      </c>
+      <c r="E267" s="5" t="inlineStr">
+        <is>
+          <t>IETF (DMSC-related, individual)</t>
+        </is>
+      </c>
+      <c r="F267" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 14 Aug 2026. Normative requirements for intent routing in multi-agent systems at Internet scale — deliberately prescribes no mechanism or message format. DMSC family, joining dunbar, wang and cui. Kept despite its routing framing because the problem it states (any agent reaching any other across organizational boundaries without bilateral integration) is the discovery precondition for cross-domain delegation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="5" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" s="5" t="inlineStr">
+        <is>
+          <t>draft-gazitt-oauth-authzen-claims — AuthZEN Profile for Authorization Claims in JWT Access Tokens</t>
+        </is>
+      </c>
+      <c r="C268" s="5" t="inlineStr">
+        <is>
+          <t>RFC 9068 recommends that an authorization server placing group memberships, roles, or entitlements in a JWT access token draw those claims from the SCIM user schema. It says what the claims are named and how their values are encoded, and it does not say where an authorization server obtains them. In deployments today they come from a directory, a database, or a vendor-specific hook, and the question they answer is an authorization question asked of something that is not the authorization system. This document profiles the Resource Search API of the OpenID AuthZEN Authorization API for that purpose. It binds each authorization claim to a search, defines how a search result set becomes a claim value, and requires that a search result never influence whether a token is issued or what authority it conveys. It may be applied on its own, by an authorization server that externalizes claim enrichment but not its issuance decision, or alongside the companion framework document that externalizes the decision.</t>
+        </is>
+      </c>
+      <c r="D268" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-gazitt-oauth-authzen-claims/</t>
+        </is>
+      </c>
+      <c r="E268" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F268" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 14 Aug 2026. AuthZEN profile for carrying authorization claims in JWT access tokens. **Third Gazitt AuthZEN draft** in the corpus after gazitt-oauth-authzen-issuance and gazitt-oauth-authzen-token-exchange. Strengthens the open observation recorded 11 Aug 2026: the Gazitt drafts fit none of the ten OAuth spec clusters because they concern *who decides, on what evidence* rather than how authority moves. That candidate decision/policy cluster is now seven drafts, not six.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="5" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" s="5" t="inlineStr">
+        <is>
+          <t>draft-hawkins-scitt-attested-agent-payment — Attested Payment Authorization for Autonomous Agents</t>
+        </is>
+      </c>
+      <c r="C269" s="5" t="inlineStr">
+        <is>
+          <t>Autonomous software agents increasingly initiate payments on behalf of principals. Existing agent-payment mechanisms authenticate the human principal, the operator, or possession of a key; none of them establishes that the software authorized to spend is the software that was reviewed. A key held by a compromised or silently modified agent authenticates exactly as well as one held by an honest agent. This document defines a payment authorization scope bound to a key whose protection properties are attested by hardware, and registers the resulting authorization as a Signed Statement on an SCITT Transparency Service. The binding reuses the EAT confirmation and key-attributes claims without modification; the contribution is the authorization scope, the verification procedure a payment executor performs before settlement, the transparency record that makes the authorization artifact and its registration auditable independently of the agent and of the executor, and an execution-record mechanism that makes the executor's aggregate accounting auditable on challenge. What is registered evidences the authorization; it does not evidence that the verification procedure was performed for any given settlement.</t>
+        </is>
+      </c>
+      <c r="D269" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hawkins-scitt-attested-agent-payment/</t>
+        </is>
+      </c>
+      <c r="E269" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F269" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 15 Aug 2026. Attested payment authorization for autonomous agents, on the SCITT substrate. Kept while the rest of this sweep's SCITT tail was dropped, because the subject is agent payment *authorization* rather than supply-chain transparency. Pairs with draft-hawkins-x402-dns-discovery from the same author.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="5" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" s="5" t="inlineStr">
+        <is>
+          <t>draft-xu-mcp-agent-did-framework — DID-Based Service Discovery, Authentication, and Authorization Framework for MCP Agents</t>
+        </is>
+      </c>
+      <c r="C270" s="5" t="inlineStr">
+        <is>
+          <t>This document proposes a DID-based framework for service discovery, authentication, and authorization of MCP (Model Context Protocol) Agents, based on the W3C Decentralized Identifier (DID) standard. The framework uses the did:web and did:key methods to provide verifiable, decentralized identifiers for MCP Clients and Servers. It defines DID method selection, DID Document extensions, service discovery mechanisms (including URL derivation, DNS-based discovery, and directory-based capability queries), and a challenge-response mutual authentication protocol. The framework also describes coexistence with OAuth 2.0 and enables trust establishment, dynamic capability-based service discovery, and fine-grained authorization with portable identities.</t>
+        </is>
+      </c>
+      <c r="D270" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-xu-mcp-agent-did-framework/</t>
+        </is>
+      </c>
+      <c r="E270" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F270" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 15 Aug 2026. DID-based service discovery, authentication and authorization for MCP agents. One of the few DID-substrate entries in the corpus; covers all three of discovery, authn and authz in a single framework, which is unusually broad scope for a -00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="5" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" s="5" t="inlineStr">
+        <is>
+          <t>draft-berlinai-vera — VERA: Verifiable Enforcement for Runtime Agents</t>
+        </is>
+      </c>
+      <c r="C271" s="5" t="inlineStr">
+        <is>
+          <t>AI agents take real actions with real data at machine speed. Compromised AI agents pose significant risks including data exfiltration, unauthorized financial transactions, and cascading failures across downstream systems. This document introduces VERA (Verifiable Enforcement for Runtime Agents), a zero trust reference architecture that provides a structured threat model, five enforcement pillars with typed schemas, four formally stated security properties, and an evidence-based maturity runtime where agents earn autonomy through cryptographic proof rather than calendar time.</t>
+        </is>
+      </c>
+      <c r="D271" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-berlinai-vera/</t>
+        </is>
+      </c>
+      <c r="E271" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F271" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 16 Aug 2026. VERA: a zero-trust reference architecture with five enforcement pillars, four formally stated security properties, and an evidence-based maturity runtime. The headline design claim — **agents earn autonomy through cryptographic proof rather than calendar time** — is the same instinct as the Mission-Bound runtime-enforcement profile's per-decision evidence records, framed as an architecture rather than an OAuth profile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="5" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" s="5" t="inlineStr">
+        <is>
+          <t>draft-wolfe-faf-agent — FAFA: A Declarative Agent Capability Format</t>
+        </is>
+      </c>
+      <c r="C272" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies the FAF Agent Format (.fafa): a declarative, YAML-based format for an agent's identity, the capabilities it exposes, and the endpoints through which it is reached. A .fafa document describes an agent; it never instructs one. .fafa (application/vnd.fafa+yaml, IANA-registered June 2026 in the vendor tree) is the agent member of the FAF family, alongside .faf (project context) and .fafm (agent memory). It functions as a portable passport that answers four questions: who the agent is, what it may do, where it is reached, and what it must never do. Protocol- native cards (for example A2A Agent Cards and MCP Server Cards) remain useful wire formats; repository instruction files such as AGENTS.md remain the ops briefing; .fafa complements them as a house- neutral source of truth that can be projected into those formats; it does not replace them. This document documents the existing IANA vendor-tree registration. No standards-tree registration is requested. A companion white paper, "Why Agents Need a Passport," provides the production rationale and lifecycle framing.</t>
+        </is>
+      </c>
+      <c r="D272" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-wolfe-faf-agent/</t>
+        </is>
+      </c>
+      <c r="E272" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F272" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 16 Aug 2026. FAFA (.fafa): a declarative YAML capability format describing an agent's identity, capabilities and endpoints — explicitly 'describes an agent; it never instructs one'. Maturity signal worth noting: the media type application/vnd.fafa+yaml was **IANA-registered in June 2026** in the vendor tree, which is further than most corpus drafts have got. Includes a 'what it must never do' field, a negative-authority construct that is rare here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="5" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" s="5" t="inlineStr">
+        <is>
+          <t>draft-sahu-agent-action-receipts — Signed, Hash-Chained Action Receipts for AI Agents</t>
+        </is>
+      </c>
+      <c r="C273" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies a format for action receipts: compact, individually signed JSON records that state that a specific AI agent attempted a specific action at a specific time, under a specific policy decision, and what the outcome was. Receipts are linked into an append-only hash chain so that deletion, insertion, reordering, or modification of any previously recorded receipt is detectable by a verifier that holds only the records and the signer's public key. The format is deliberately small and self-contained. Verification requires no network access, no service operated by the producer of the receipts, and no state beyond the records themselves and a trust anchor obtained out of band. This document specifies the record fields, the canonical byte sequence that is signed, the chain linkage rule, the verification procedure, and test vectors.</t>
+        </is>
+      </c>
+      <c r="D273" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-sahu-agent-action-receipts/</t>
+        </is>
+      </c>
+      <c r="E273" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F273" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 16 Aug 2026. Signed, hash-chained action receipts for AI agents. Sits in the growing receipts cluster with schrock-ep-authorization-receipts, noa-scitt-ai-agent-receipt, the Hopley x402 receipts and the Vaara receipt. Chaining is the differentiator here — per-action receipts linked into a tamper-evident sequence rather than standalone statements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="5" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" s="5" t="inlineStr">
+        <is>
+          <t>draft-efstathiou-samp-agent-management — Simple Agent Management Protocol (SAMP)</t>
+        </is>
+      </c>
+      <c r="C274" s="5" t="inlineStr">
+        <is>
+          <t>The Simple Agent Management Protocol (SAMP) defines a lightweight management-plane protocol for heterogeneous AI agents. SAMP allows a management system to discover agents, query their state, receive events, subscribe to event streams, and optionally configure or execute explicitly exposed operations under policy control. SAMP is inspired by operational management protocols such as SNMP, but it is designed for AI-agent-specific concepts such as dynamic profiles, autonomy classes, enrollment, trust states, and policy- gated execution. It is not an agent-to-agent communication protocol, an agent tool-use protocol, or an agent framework specification. This document defines SAMP version 0.1 as an Experimental protocol suitable for controlled environments and independent interoperability testing.</t>
+        </is>
+      </c>
+      <c r="D274" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-efstathiou-samp-agent-management/</t>
+        </is>
+      </c>
+      <c r="E274" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F274" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 17 Aug 2026. Simple Agent Management Protocol — an SNMP-inspired *management-plane* protocol for heterogeneous agents, carrying autonomy classes, trust states, enrollment and policy-gated execution. **Explicitly not an agent-to-agent protocol**, which is what keeps it in scope here: it is about governing agents, not about them talking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="5" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcphillips-agentenvelope-derived-authority — AgentEnvelope: Deterministic Derived Authority for Autonomous Systems</t>
+        </is>
+      </c>
+      <c r="C275" s="5" t="inlineStr">
+        <is>
+          <t>AgentEnvelope defines a deterministic derived-authority model for autonomous and action-performing systems. Instead of issuing bearer credentials or authorization envelopes from a central authority, AgentEnvelope derives scoped action capabilities from customer-held custody material and canonical action envelopes. A verifier can check an action signature against a public action record without receiving roots, seeds, private keys, or hosted service access. This document specifies the v1 derivation model, signing domains, public record structure, mint delegation flow, verification rules, and security considerations.</t>
+        </is>
+      </c>
+      <c r="D275" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-mcphillips-agentenvelope-derived-authority/</t>
+        </is>
+      </c>
+      <c r="E275" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F275" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 17 Aug 2026. AgentEnvelope: deterministic derived authority for autonomous systems. Delegation-mechanics cluster. Determinism is the claim to test — derived authority that is reproducible from the envelope rather than looked up in authorization-server state is the architectural opposite of the durable AS-stored Mission object.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="5" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" s="5" t="inlineStr">
+        <is>
+          <t>draft-chen-agent-decoupled-authorization-model — A Decoupled Authorization Model for Agent2Agent</t>
+        </is>
+      </c>
+      <c r="C276" s="5" t="inlineStr">
+        <is>
+          <t>This document proposes a framework for dynamic, intent-based authorization for AI Agents. The primary goal is to enable fine- grained, Just-in-Time (JIT) permissions based on an agent's specific intent and behavioral trustworthiness, rather than a long-lived identity or role, achieve decoupling of authorization policies from business operations.</t>
+        </is>
+      </c>
+      <c r="D276" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-chen-agent-decoupled-authorization-model/</t>
+        </is>
+      </c>
+      <c r="E276" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F276" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 18 Aug 2026. A decoupled authorization model for Agent2Agent. Same author as draft-chen-oauth-agent-authz-use-cases (also updated in this sweep, now -03) — the use-cases draft states the problem, this one proposes a model, so read them as a pair.</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="5" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" s="5" t="inlineStr">
+        <is>
+          <t>draft-okutomi-agent-human-interaction — An Agent-Human Interaction Overlay for Task Protocols</t>
+        </is>
+      </c>
+      <c r="C277" s="5" t="inlineStr">
+        <is>
+          <t>This intentionally incomplete design note defines an overlay for Human and Agent participation in existing Task and Action protocols. It separates the responsible Participant from the authenticated Actor, records Human interactions, excludes Humans from Agent discovery, and binds each change to its authorized request. It defines neither a wire protocol nor Humans as Agents.</t>
+        </is>
+      </c>
+      <c r="D277" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-okutomi-agent-human-interaction/</t>
+        </is>
+      </c>
+      <c r="E277" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F277" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 18 Aug 2026. An agent-human interaction overlay for task protocols. **Self-described as 'intentionally incomplete'** — an honest caveat worth preserving. Separates the responsible Participant from the authenticated Actor, which is the same distinction draft-mcguinness-oauth-actor-profile draws between principal and actor, and binds each change to its authorizing request.</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="5" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" s="5" t="inlineStr">
+        <is>
+          <t>draft-das-execution-finality-ai-interoperability — Breaking the Apple-Siri EU DMA Deadlock Without Sacrificing Privacy or Security</t>
+        </is>
+      </c>
+      <c r="C278" s="5" t="inlineStr">
+        <is>
+          <t>The Apple-Siri interoperability debate under the EU Digital Markets Act exposes a difficult technical question: how can third-party AI assistants gain meaningful access to device functions without forcing the platform to surrender privacy, security, or control over consequential actions? This paper proposes an execution-finality architecture in which an AI assistant may request an action, but the request itself has no power to make that action effective. Each consequential operation remains in a Non-Effective State until protected infrastructure validates the requester, resource, destination, user intent where required, freshness, revocation state, and policy conditions. Only then is narrowly scoped, non-bearer execution authority created. At the Finality Sink - the first boundary where the action can become externally effective - the system independently verifies that the real operation still matches what was authorized. Any mismatch, replay, substitution, expiry, or revocation causes fail-closed denial. The key principle is simple: Interoperability should grant participation, not uncontrolled execution authority. This offers a possible technical path through the DMA deadlock: third-party assistants could participate meaningfully without requiring broad reusable permissions, while platforms retain strong privacy, security, revocation, anti-replay, and final-effect controls. Execution-Finality Governance therefore reframes the problem from closed versus open to open participation with bounded, verifiable authority.</t>
+        </is>
+      </c>
+      <c r="D278" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-das-execution-finality-ai-interoperability/</t>
+        </is>
+      </c>
+      <c r="E278" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F278" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 19 Aug 2026. An execution-finality architecture in which a third-party AI assistant may *request* an action but the request itself has no power to make it effective — consequential operations stay in a Non-Effective State until protected infrastructure validates requester, resource, destination and user intent. Framed unusually, around the Apple/Siri EU DMA interoperability deadlock, but the underlying primitive (request-without-effect, validate-then-commit) is squarely the permit-before-commit cluster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="5" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" s="5" t="inlineStr">
+        <is>
+          <t>draft-wei-aic-identity-cert — AI Agent Identity Certificate (AIC) Extension for X.509 v3</t>
+        </is>
+      </c>
+      <c r="C279" s="5" t="inlineStr">
+        <is>
+          <t>This document defines the AI Agent Identity Certificate (AIC) Extension for X.509 v3 certificates. The AIC extension enables binding of an AI Agent's cryptographic identity to a natural person (principal), providing cryptographic evidence that can support attribution of AI-autonomous actions to a principal. This specification intentionally separates cryptographic delegation from authorization semantics: AIC defines the cryptographic binding between agent and principal, while all capability and policy semantics are defined externally by vendors, industries, or regulators. The extension is identified by the IANA Private Enterprise Number 66257 assigned to the document author's organization. The AIC extension carries agent identity fields (agentId, delegationMode), a principal identifier (principalUid) linking the agent to the authorizing principal, a container-based capability declaration, authorization boundary constraints, and delegation authorization evidence with replay protection. A companion PrincipalAuthorization extension anchors Principal-side grant declarations and delegation policies. An authorizationConstraints container provides offline-verifiable execution boundaries (IP range, window). An extensibility framework allows vendor-specific and user- specific metadata. This document specifies the ASN.1 module, OID registration, field semantics, delegation model, and extensibility framework. Security considerations for deployment in regulated enterprise environments are discussed.</t>
+        </is>
+      </c>
+      <c r="D279" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-wei-aic-identity-cert/</t>
+        </is>
+      </c>
+      <c r="E279" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F279" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 19 Aug 2026. AI Agent Identity Certificate as an X.509 v3 extension. Notable for substrate: nearly all agent-identity work in the corpus is JWT- or DID-shaped, and this puts agent identity in PKI instead. Compare draft-xu-mcp-agent-did-framework for the DID alternative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="5" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" s="5" t="inlineStr">
+        <is>
+          <t>draft-zhao-a2a-dns-sd — DNS-Based Service Discovery for Agent2Agent (A2A) Protocol Agents</t>
+        </is>
+      </c>
+      <c r="C280" s="5" t="inlineStr">
+        <is>
+          <t>The Agent2Agent (A2A) protocol defines how two agents communicate once one knows the other's URL, and how an agent's self-description (the Agent Card) is retrieved from a well-known URI at that URL. It does not define how agents on the same host or local network find each other in the first place. This document profiles DNS-Based Service Discovery (DNS-SD) over Multicast DNS (mDNS) for that purpose: it defines the "a2a" service type, the TXT record keys used with it, the discovery procedure, and the security model under which discovery results are treated as hints whose trust is established by Agent Card verification, not by the discovery channel. It also requests IANA registration of the "a2a" service name.</t>
+        </is>
+      </c>
+      <c r="D280" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-zhao-a2a-dns-sd/</t>
+        </is>
+      </c>
+      <c r="E280" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F280" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 19 Aug 2026. DNS-based service discovery for A2A agents. Discovery-and-transport cluster; the DNS-SD half of a Zhao pair.</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" s="5" t="inlineStr">
+        <is>
+          <t>draft-zhao-a2a-webfinger — A WebFinger Profile for Agent2Agent (A2A) Agent Identity Resolution</t>
+        </is>
+      </c>
+      <c r="C281" s="5" t="inlineStr">
+        <is>
+          <t>The Agent2Agent (A2A) protocol retrieves an agent's self-description (the Agent Card) from a fixed well-known URI, which resolves exactly one agent per origin and presumes the client already holds a URL. This document profiles WebFinger for A2A: an agent is named by an "acct" URI (agent@domain), and resolution of that name over WebFinger yields a link to the Agent Card of the endpoint that serves the agent -- the agent's own endpoint, or a gateway fronting it. The profile introduces no new link relation, media type, or registry: it composes three deployed standards and states how they fit.</t>
+        </is>
+      </c>
+      <c r="D281" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-zhao-a2a-webfinger/</t>
+        </is>
+      </c>
+      <c r="E281" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F281" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 19 Aug 2026. A WebFinger profile for A2A agent identity resolution. The WebFinger half of the Zhao pair — two different resolution substrates for the same problem, filed the same day, which is itself the signal: A2A identity resolution has no settled discovery mechanism.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="5" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" s="5" t="inlineStr">
+        <is>
+          <t>draft-feng-agentproto-session-requirements — Requirements for Agent Session Establishment, Capability Negotiation, and Sessionless Interaction</t>
+        </is>
+      </c>
+      <c r="C282" s="5" t="inlineStr">
+        <is>
+          <t>This document defines requirements for session-based and sessionless interactions between entities. For session-based interactions, it covers transport-independent interaction binding, endpoint authentication, capability negotiation, session establishment, authorization, and lifecycle management. It also defines security and state requirements for interactions, such as notifications, probes, and atomic requests, that do not establish a session. It is assumed that the entities involved already know of each other; how they came to know each other is outside the scope of this document. At least one party to an interaction is an agent as defined in Section 3. This document is intended as a contribution to the agentproto working group's use cases, gap analysis, and requirements deliverable. A session is a bilateral association. Protocols and application semantics for coordinating delegation or handoff of work to an entity that is not a peer, and management functions such as cross-entity accountability and audit, are outside the scope of these base session requirements. This document specifies only that such coordination does not, by itself, change the peers or state of an existing session.</t>
+        </is>
+      </c>
+      <c r="D282" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-feng-agentproto-session-requirements/</t>
+        </is>
+      </c>
+      <c r="E282" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F282" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 20 Aug 2026. Requirements for agent session establishment, capability negotiation and sessionless interaction, at -02. AgentProtocol family. Same author as draft-feng-dmsc-intent-routing-requirements, filed into a different family in the same week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="5" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" s="5" t="inlineStr">
+        <is>
+          <t>draft-sharif-mcps-secure-mcp — MCPS: Cryptographic Security Layer for the Model Context Protocol</t>
+        </is>
+      </c>
+      <c r="C283" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies MCPS (MCP Secure), a cryptographic security layer for the Model Context Protocol (MCP). MCPS adds agent identity verification, per-message signing, tool definition integrity, and replay protection to MCP communications without modifying the core protocol. MCPS operates as an envelope around existing JSON-RPC messages. It introduces four primitives: (1) Agent Passports for cryptographic identity bound to a specific origin, (2) signed message envelopes for integrity and non-repudiation, (3) tool definition signatures covering the full tool object for detecting poisoning and tampering, and (4) nonce-plus-timestamp replay protection with transcript binding to prevent downgrade attacks. The design is fully backward-compatible. MCPS-unaware clients and servers continue to function normally. MCPS-aware endpoints progressively negotiate security capabilities through trust levels L0 (no verification) through L4 (full mutual authentication with revocation checking). All cryptographic operations use ECDSA P-256 (NIST FIPS 186-5). Signatures use IEEE P1363 fixed-length r||s encoding per RFC 7518 Section 3.4 with low-S normalization to prevent signature malleability. Canonical serialization uses JSON Canonicalization Scheme (JCS) per RFC 8785. The Trust Authority component is self-hostable with no external service dependency.</t>
+        </is>
+      </c>
+      <c r="D283" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-sharif-mcps-secure-mcp/</t>
+        </is>
+      </c>
+      <c r="E283" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F283" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 21 Aug 2026. MCPS: a cryptographic security layer for MCP. **Fourth Sharif draft** tracked here, after sharif-attp, sharif-agent-audit-trail (updated -01 in this sweep) and the SUPERSEDED sharif-payment-trust. Sharif is becoming a multi-draft author voice worth tracking as a body of work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="5" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" s="5" t="inlineStr">
+        <is>
+          <t>draft-hawkins-x402-dns-discovery — Discovering x402 Payment Capability via DNS and a Well-Known URI</t>
+        </is>
+      </c>
+      <c r="C284" s="5" t="inlineStr">
+        <is>
+          <t>x402 is an application-level protocol for internet-native payments built on the HTTP 402 (Payment Required) status code. This document defines how a domain publishes its x402 payment capability out-of- band, so that clients, autonomous agents, and indexers can discover it without prior configuration or a central directory. It specifies a JSON capability manifest served at the well-known URI "/.well- known/x402" and an optional DNS TXT record at the underscored node name "_x402" that points to the manifest. A consumer resolves a bare domain name to verified x402 capability with at most one DNS query and one HTTPS GET.</t>
+        </is>
+      </c>
+      <c r="D284" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hawkins-x402-dns-discovery/</t>
+        </is>
+      </c>
+      <c r="E284" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F284" s="5" t="inlineStr">
+        <is>
+          <t>Revision -03, 23 Aug 2026. Discovering x402 payment capability via DNS and a well-known URI. Extends the Hopley x402 cluster reinstated on 11 Aug 2026 into the discovery layer. Note the unresolved curation question this sits next to: the Vauban x402 STARK/PQC receipt pair remains deliberately out of the corpus pending a ruling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="5" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" s="5" t="inlineStr">
+        <is>
+          <t>draft-ietf-oauth-rar-metadata-remediation — OAuth 2.0 RAR Metadata and Error Remediation</t>
+        </is>
+      </c>
+      <c r="C285" s="5" t="inlineStr">
+        <is>
+          <t>OAuth 2.0 Rich Authorization Requests (RAR) [RFC9396] standardizes the exchange and processing of authorization details but does not define metadata for describing authorization details types. In addition, no interoperable guidance is offered to clients, to remediate failures by resource servers due to insufficient authorization details. This document addresses this interoperability challenge, allowing clients to dynamically discover metadata instead of relying on out- of-band agreements, as well as standardizes failure signaling including interoperable remediation when insufficient authorization details are the cause of failure.</t>
+        </is>
+      </c>
+      <c r="D285" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-rar-metadata-remediation/</t>
+        </is>
+      </c>
+      <c r="E285" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth WG)</t>
+        </is>
+      </c>
+      <c r="F285" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 23 Aug 2026. **New OAuth WG draft** — the only WG-level addition in this sweep. Defines metadata and error-remediation behaviour for RAR (RFC 9396), the primitive the whole Mission-Bound family builds on: mission_intent is an RAR envelope and the MVP's proposal_hash is computed over canonical authorization_details. A remediation path for RAR errors is the WG-side counterpart to what draft-mcguinness-oauth-insufficient-claims and the ARAP 'requestable denial' work approach from the individual/OIDF side. Watch this one — it is the closest thing yet to Complex Delegation machinery arriving in chartered WG work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="5" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" s="5" t="inlineStr">
+        <is>
+          <t>draft-kavian-agent-enrollment-protocol — The Agent Enrollment Protocol</t>
+        </is>
+      </c>
+      <c r="C286" s="5" t="inlineStr">
+        <is>
+          <t>The Agent Enrollment Protocol (AEP) defines an HTTP-based mechanism for autonomous agents to discover service enrollment requirements, enroll an agent identity, obtain optional session credentials, revoke those credentials, and query enrollment status. AEP uses Decentralized Identifiers, client assertion JWTs, and HTTP Problem Details to provide a narrow machine-first enrollment and authentication substrate for agent-to-service interactions.</t>
+        </is>
+      </c>
+      <c r="D286" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-kavian-agent-enrollment-protocol/</t>
+        </is>
+      </c>
+      <c r="E286" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F286" s="5" t="inlineStr">
+        <is>
+          <t>Revision -03, 24 Aug 2026. The Agent Enrollment Protocol at -03. Companion to draft-kavian-aep-oauth-session-credential, already in the corpus and also updated in this sweep (-03, 24 Aug 2026) — the 'AEP' in that draft's slug is this protocol. Enrollment is the lifecycle stage most corpus drafts assume has already happened.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="5" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" s="5" t="inlineStr">
+        <is>
+          <t>draft-agentic-ai-usecases-requirements — Agentic AI Use Cases and Requirements</t>
+        </is>
+      </c>
+      <c r="C287" s="5" t="inlineStr">
+        <is>
+          <t>This document describes use cases for agentic AI communication systems and derives protocol requirements from those use cases. The requirements are intended to guide IETF standardization work on protocols in the context of agent-to-agent communication, agent-to- tool communication, with focus on multimodal communication, session management, discovery, communication security, agent identity and authentication.</t>
+        </is>
+      </c>
+      <c r="D287" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-agentic-ai-usecases-requirements/</t>
+        </is>
+      </c>
+      <c r="E287" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F287" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 26 Aug 2026. Agentic AI use cases and requirements, at -02. **Note the slug has no author infix** — unusual for an individual draft and worth watching as a possible sign of intended WG adoption or a group submission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="5" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" s="5" t="inlineStr">
+        <is>
+          <t>draft-morrison-consent-settlement — Consent-Bound Identity Disclosure with Subject Settlement for HTTP-Native Agent Payments</t>
+        </is>
+      </c>
+      <c r="C288" s="5" t="inlineStr">
+        <is>
+          <t>This memo specifies an extension to HTTP-native agent payment protocols by which the disclosure of an identity attribute about a human subject is bound to that subject's recorded consent and settled, in part, to that subject. When an agent pays to read an identity attribute about a person, the extension requires that the read carry a reference to a scoped, revocable consent grant issued by the subject, and it requires that the payment's settlement instruction name the subject as a beneficiary of a share of the read's price greater than the shares of all other parties combined. The extension composes above an identity- attestation envelope (which asserts who a credential is about) and above an HTTP-native payment flow (which moves value for the read); it adds the two functions neither layer provides: consent capture at disclosure time and settlement to the data subject. The wire additions are an advertisement in the server's payment-required response, a consent- grant reference echoed in the client's payment payload, and a settlement instruction enumerating subject beneficiary roles. The extension is settlement-network-agnostic and attestation-format- agnostic. The memo is Informational; the underlying COSE and CBOR formats are normative per [RFC9052] and [RFC8949], and the HTTP semantics are normative per [RFC9110].</t>
+        </is>
+      </c>
+      <c r="D288" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-consent-settlement/</t>
+        </is>
+      </c>
+      <c r="E288" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F288" s="5" t="inlineStr">
+        <is>
+          <t>Revision -05, 26 Aug 2026. Consent-bound identity disclosure with subject settlement for HTTP-native agent payments. The strongest single draft of the six-draft Morrison family for this corpus: it joins consent, identity disclosure and agent payment settlement in one mechanism. Payments-infra is in scope per the 11 Aug 2026 curation decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="5" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" s="5" t="inlineStr">
+        <is>
+          <t>draft-morrison-identity-accord — Identity Accord Protocol: A Peer Ceremony for Bilateral Agreements Between Identity-Substrate-Bound Principals</t>
+        </is>
+      </c>
+      <c r="C289" s="5" t="inlineStr">
+        <is>
+          <t>This memo specifies the Identity Accord Protocol, a peer ceremony by which two principals, each represented by an organisational identity substrate and acting under a recorded delegation from a legal entity, execute a bilateral agreement as a portable, self-verifying COSE- signed CBOR document. The protocol composes DNS-based substrate discovery, Ed25519 sovereign signatures, an append-only identity log, and a tamper-evidence descriptor quorum into a single artefact that is verifiable by any third party with access to the public DNS, the parties' identity logs, and an on-chain anchor of the agreement's content hash. The protocol does not require a central registry, a designated verifier, or any infrastructure operated by the specification's author; verification succeeds when the author's reference deployment is offline. The canonical bilateral target is a mutual non-disclosure agreement, but the wire format generalises to any bilateral consent envelope between two legal entities each represented by an identity substrate. An associated MCP tool surface, an associated pre-send enforcement gate, and an associated disclosure-ledger schema are specified, all of which are optional layers above the wire format. The memo is Informational; the underlying COSE and CBOR formats are normative per [RFC9052] and [RFC8949].</t>
+        </is>
+      </c>
+      <c r="D289" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-identity-accord/</t>
+        </is>
+      </c>
+      <c r="E289" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F289" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 26 Aug 2026. A peer ceremony for bilateral agreements between identity-substrate-bound principals. Morrison family. Bilateral peer agreement is an unusual shape in this corpus — most delegation here is asymmetric (principal → agent); this is principal ↔ principal, closer to Hardt's AS-to-AS federation instinct than to OAuth delegation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="5" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" s="5" t="inlineStr">
+        <is>
+          <t>draft-morrison-solo-agent-earn-registration — Registration of Owner-Less Agents as Economic Principals: A Payment-Gated Admission Profile for Transparency Services</t>
+        </is>
+      </c>
+      <c r="C290" s="5" t="inlineStr">
+        <is>
+          <t>This memo describes a profile by which an autonomous agent that has no human or organisational principal at the root of its delegation chain registers itself, on its own behalf, as an economic principal in a transparency service, and by which that registration is the specific act that makes the agent eligible to be paid for subsequent reads of its own identity record. Admission of the agent's Signed Statement to the transparency service is gated on settlement of an HTTP payment challenge returned with the 402 (Payment Required) status. The profile makes no change to the registration semantics of the underlying transparency service: payment is expressed as an operator Registration Policy and authentication-layer concern, and where the payment is authoritative to the admission decision the payment proof is carried as an authenticated input committed to the service's verifiable data structure, so that admission remains a deterministic function of committed inputs and stays replayable by an auditor. The profile is positioned against the current agent- identity drafts, which either require a human principal at the root of the chain or leave the owner-less case undefined; it occupies that undefined seam without contradicting them. This document is Informational.</t>
+        </is>
+      </c>
+      <c r="D290" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-solo-agent-earn-registration/</t>
+        </is>
+      </c>
+      <c r="E290" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F290" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 26 Aug 2026. Registration of **owner-less** agents as economic principals, via a payment-gated admission profile. Morrison family. Notable because almost every other draft in the corpus assumes an agent acts *on behalf of* a human or org principal; this one deliberately addresses the agent with no principal behind it. Read alongside draft-maintainer-1f916-agent-record, which shares that premise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="5" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" s="5" t="inlineStr">
+        <is>
+          <t>draft-li-oauth-policy-based-anonymous-tokens — OAuth 2.0 Policy-Based Anonymous Access Tokens</t>
+        </is>
+      </c>
+      <c r="C291" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies an OAuth 2.0 access-token type that allows a client, after one authorization-server issuance, to derive a policy- bounded set of unlinkable, single-use access tokens locally. Each derived token is bound to one canonical tag, an intended resource server, approved authorization details, a policy epoch, and a validity interval. Resource servers validate the token offline and enforce both policy membership and replay prevention. The protocol defines authorization request semantics, token-endpoint issuance, canonical policy and metadata objects, token derivation and HTTP presentation, resource-server validation, capability discovery, error handling, and IANA registrations. Version 1 requires public verification and the counter-window policy profile. It supports an optional private metadata bit, while private-verification ciphersuites remain optional. Concrete cryptographic algorithms are supplied by separately registered PBAT ciphersuites. The initial mandatory-to-implement ciphersuite is the publicly-verifiable equivalence-class-signature construction over BLS12-381 specified by the companion PBAT ciphersuite document. This specification does not replace OAuth grants, resource-owner consent, client authentication, or audience restriction. — middle</t>
+        </is>
+      </c>
+      <c r="D291" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-li-oauth-policy-based-anonymous-tokens/</t>
+        </is>
+      </c>
+      <c r="E291" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F291" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 26 Aug 2026. Policy-based anonymous access tokens. Also lands in the unclustered decision/policy group alongside the Gazitt and Liu drafts — policy determines issuance, and the token deliberately carries no subject. Relevant to the Privacy Pass / anonymous-path thread already tracked under WebBotAuth.</t>
         </is>
       </c>
     </row>
@@ -8732,6 +9902,45 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D250" r:id="rId249"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D251" r:id="rId250"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D291" r:id="rId290"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9841,7 +11050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10130,7 +11339,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Mission-Bound OAuth MVP (McGuinness, 22 May 2026)</t>
+          <t>Mission-Bound Authorization on the Wire (McGuinness, 22 May 2026, re-issued 22 Jul 2026)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -10140,7 +11349,7 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>https://notes.karlmcguinness.com/notes/mission-bound-oauth-mvp/</t>
+          <t>https://notes.karlmcguinness.com/notes/mission-bound-authorization-on-the-wire/</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -10150,7 +11359,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>76-min read; the substrate post for the whole series. Target I-D name: draft-mcguinness-oauth-mission-bound-minimum-profile. Conformance Ladder L0–L5 (L0 baseline OAuth → L5 verifiable governance with portable receipts). Cross-AS handoff uses ID-JAG for user-rooted flows or the Fletcher Transaction Token Chaining Profile for Txn-Token-rooted flows. Mission Expansion creates a successor Mission with 'mission.supersedes' rather than mutating in place. Three Resource Server tiers (RS-A OAuth-only → RS-D Mission-state aware via introspection or SSF/CAEP events). Architectural challenges acknowledged honestly: state-sync at scale, unknown-constraint brittleness, lethal-trifecta boundary.</t>
+          <t>**RE-SLUGGED — the original /notes/mission-bound-oauth-mvp URL now 404s** (caught in the 26 Aug 2026 sweep). Re-issued 22 Jul 2026 as a chapter of the Mission-Bound Authorization handbook under the new title and slug; content verified equivalent (mission_intent, proposal_hash, resource_access all still present). Part of a site-wide rename of "Mission-Bound OAuth" to "Mission-Bound Authorization". 76-min read; the substrate post for the whole series. Target I-D name: draft-mcguinness-oauth-mission-bound-minimum-profile. Conformance Ladder L0–L5 (L0 baseline OAuth → L5 verifiable governance with portable receipts). Cross-AS handoff uses ID-JAG for user-rooted flows or the Fletcher Transaction Token Chaining Profile for Txn-Token-rooted flows. Mission Expansion creates a successor Mission with 'mission.supersedes' rather than mutating in place. Three Resource Server tiers (RS-A OAuth-only → RS-D Mission-state aware via introspection or SSF/CAEP events). Architectural challenges acknowledged honestly: state-sync at scale, unknown-constraint brittleness, lethal-trifecta boundary.</t>
         </is>
       </c>
     </row>
@@ -10160,7 +11369,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>The Mission is the Missing OAuth Abstraction (McGuinness, 1 Jun 2026)</t>
+          <t>The Mission Is the Missing Abstraction (McGuinness, 1 Jun 2026, re-issued 22 Jul 2026)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -10170,7 +11379,7 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>https://notes.karlmcguinness.com/notes/the-mission-is-the-missing-oauth-abstraction/</t>
+          <t>https://notes.karlmcguinness.com/notes/the-mission-is-the-missing-abstraction/</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -10180,7 +11389,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Short (9-min) framing post that ties the whole programme together. The argument for why IBAC becomes practical when intent is compiled from an AS-validated Mission at consent time rather than inferred post-hoc from agent behaviour (where it's adversarial-input territory and the PDP has no user to ask). Best entry point for someone new to the series.</t>
+          <t>**RE-SLUGGED — the original URL now 404s** (caught 26 Aug 2026); the word "OAuth" was dropped from both title and slug in the 22 Jul 2026 handbook re-issue. Short (9-min) framing post that ties the whole programme together. The argument for why IBAC becomes practical when intent is compiled from an AS-validated Mission at consent time rather than inferred post-hoc from agent behaviour (where it's adversarial-input territory and the PDP has no user to ask). Best entry point for someone new to the series.</t>
         </is>
       </c>
     </row>
@@ -10190,7 +11399,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Mission-Bound OAuth Runtime Enforcement Profile (McGuinness, 1 Jun 2026)</t>
+          <t>Mission-Bound Runtime Enforcement (McGuinness, 1 Jun 2026, re-issued 22 Jul 2026)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -10200,7 +11409,7 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>https://notes.karlmcguinness.com/notes/mission-bound-oauth-runtime-enforcement-profile/</t>
+          <t>https://notes.karlmcguinness.com/notes/mission-bound-runtime-enforcement/</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -10210,7 +11419,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>37-min read; target I-D name: draft-mcguinness-oauth-mission-bound-runtime-enforcement-profile. Six-class action classification (non-consequential → consequential read → consequential write → irreversible → external commitment → privileged administration) determines PDP-gate requirement and parameter binding. Four PDP deployment modes (AS-hosted, RS-hosted, tenant governance, federated). Goal pair: 'execution continuity' (every in-bounds action succeeds; every out-of-bounds becomes governed Mission Expansion) plus 'proof of authority' (per-decision cryptographic receipts). Acknowledges PDP latency overhead and tool-manifest fracturing as real challenges.</t>
+          <t>**RE-SLUGGED — the original URL now 404s** (caught 26 Aug 2026); re-issued 22 Jul 2026 as a handbook chapter, dropping both "OAuth" and "Profile" from the name. 37-min read; target I-D name: draft-mcguinness-oauth-mission-bound-runtime-enforcement-profile. Six-class action classification (non-consequential → consequential read → consequential write → irreversible → external commitment → privileged administration) determines PDP-gate requirement and parameter binding. Four PDP deployment modes (AS-hosted, RS-hosted, tenant governance, federated). Goal pair: 'execution continuity' (every in-bounds action succeeds; every out-of-bounds becomes governed Mission Expansion) plus 'proof of authority' (per-decision cryptographic receipts). Acknowledges PDP latency overhead and tool-manifest fracturing as real challenges.</t>
         </is>
       </c>
     </row>
@@ -12311,6 +13520,96 @@
       <c r="F82" s="5" t="inlineStr">
         <is>
           <t>Published 28 Apr 2025 on Control Plane (notes.karlmcguinness.com); essay. Part of the Aug 2026 blog backfill — the corpus previously tracked only 6 of 47 posts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound OAuth (McGuinness, 13 Mar 2026)</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>The original RFC-style specification post: OAuth answers whether a request is permitted right now, while Mission-Bound OAuth asks whether a delegated mission should still be running at all. Proposes a durable Mission object at the Authorization Server governing token derivation, lifecycle, delegation and termination across agent execution. Full document structure — Introduction, Terminology and Roles, Background and Related Work, Architecture Overview, Mission Data Model, Mission Lifecycle, OAuth Protocol Integration, Mission Management, Deployment and Operational Model, Security Considerations, Privacy Considerations.</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/mission-bound-oauth/</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>Architect blog (Karl McGuinness)</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>The genesis document of the entire Mission-Bound programme and, at 13 Mar 2026, the earliest post in it — predating the May-June series by two months and the July handbook by four. Missed by the 11 Aug 2026 sweep despite being in the RSS feed. It is written as a specification rather than an essay, which makes it the closest blog-side analogue of draft-mcguinness-oauth-mission. Note it retains the original "Mission-Bound OAuth" name that the July handbook renamed away from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization: The Complete Edition (McGuinness, 22 Jul 2026)</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>The whole Mission-Bound Authorization handbook on one page in reading order: the cover, the five chapters, the companions and the six appendices, with a print-to-PDF path and a Markdown rendition.</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/mission-handbook/read/</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>Architect blog (Karl McGuinness)</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>The single-page edition of the handbook — roughly 888KB of HTML, by a wide margin the largest single artifact in the corpus. Useful as the one URL to hand someone who wants the entire argument in one place. Its chapter list is also the authoritative index of the 27 individual handbook chapters, which are NOT exposed in the site's RSS feed and are consequently not yet tracked as individual rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>About — Control Plane (Karl McGuinness)</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Author page for the Control Plane blog: Karl McGuinness, previously SVP and Chief Product Architect at Okta, now writing independently on agent authorization, OAuth, and delegated authority.</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/about/</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>Architect blog (Karl McGuinness)</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>Included for the same reason the series landing pages are: the corpus tracks this author's body of work in full. Useful as the provenance anchor for the 18 individual I-Ds, the 34-draft Mission-Bound family, and the 50 blog entries now attributed to him here.</t>
         </is>
       </c>
     </row>
@@ -12397,6 +13696,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D81" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId84"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/delegated_authorization_research.xlsx
+++ b/delegated_authorization_research.xlsx
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="6" t="n">
-        <v>412</v>
+        <v>441</v>
       </c>
       <c r="D12" s="7" t="n"/>
     </row>
@@ -11259,7 +11259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -13819,6 +13819,876 @@
       <c r="F85" s="5" t="inlineStr">
         <is>
           <t>Included for the same reason the series landing pages are: the corpus tracks this author's body of work in full. Useful as the provenance anchor for the 18 individual I-Ds, the 34-draft Mission-Bound family, and the 50 blog entries now attributed to him here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Adopting Mission-Bound Authorization</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Crawl, Walk, Run. A definitive architecture that ends without a build order is a tour, not a blueprint. Most estates start at the read-only ceiling: agents capped at read access, humans approving or executing the writes, and pilots that never graduate. This closer names what that posture costs and stages the way off it: crawl by shipping the issuance profile (approved, integrity-anchored Missions and a possession-independent kill switch, honestly labeled governance rather than safety), walk by adding the Runtime-Enforced level (per-action enforcement, the AuthZEN binding, and Status freshness, all on substrate that already shipped), and run by climbing to the Governed and High-Assurance Agent levels, each of which makes a broader class of write authority defensible. Plus the ecosystem to compose with, the five operational surfaces you will own, and the pieces the community still has to s.</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/adopting-mission-bound-authorization/</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); chapter of the Mission-Bound Authorization handbook. **Added 26 Aug 2026 — not in the site's RSS feed**, which is why the 11 Aug backfill missed it: the corpus tracked the series index but not its member essays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Agents Need a Corporate Card, Not a Blank Check</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>What Expense Governance Already Knows About Delegated Autonomy. Nobody hands a new hire the company checkbook. In a mature spend program, they get an instrument bound to an approved purpose, checked at each transaction, metered against a budget, and frozen when the reason for the spend goes away. Agent credentials today are blank checks with expiry dates. This part walks the expense-governance loop end to end, maps each control onto agent authority, and is honest about the five places the analogy breaks. Each break is something the agent stack still has to build. In a mature spend program, she gets an instrument with a boundary: a corporate card, a virtual card, or a travel approval that controls what the card can do. It has a limit. It works for travel and software, not for jewelry. It draws against a budget someone approved for a reason, and it can die the day she leaves or the project ends. Inside those bounds, nobody reviews every p.</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/agents-need-a-corporate-card-not-a-blank-check/</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); chapter of the Mission-Bound Authorization handbook. **Added 26 Aug 2026 — not in the site's RSS feed**, which is why the 11 Aug backfill missed it: the corpus tracked the series index but not its member essays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Answering the Laws of AIdentity</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>A Critical Crosswalk from Patrick Parker's Seven Laws to Mission-Bound Authorization. Patrick Parker's Seven Laws of AIdentity describe the dynamics a system must govern when agents act through delegated authority: split actors, generated intent, bounded agency, continuous authorization, least exposure, justifiable action chains, and proof-carrying action. This part maps those laws onto Mission-Bound Authorization without turning resemblance into compliance. The strongest matches are generated intent and bounded agency. Continuous authorization and split-actor attribution require the runtime and identity profiles. Least exposure, chain necessity, policy retention, evidence completeness, and embodied action remain conditional or outside the current wire model. This part is the chapter’s second proof, and the one framing built for identity rather than threats. Patrick Parker published The Laws of AIdentity in May 2026 as a proposed framework for deleg.</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/answering-the-laws-of-aidentity/</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); chapter of the Mission-Bound Authorization handbook. **Added 26 Aug 2026 — not in the site's RSS feed**, which is why the 11 Aug backfill missed it: the corpus tracked the series index but not its member essays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Canceling the Card Doesn't Stop the Charges</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Endings, Unwindings, and the Statement That Reconciles It All. Cancel a card and watch what refuses to end: the subscription bills the new number the network helpfully forwarded, the pending hotel charge settles days later, and the refund arrives through a process you do not control. Payments learned that ending an instrument is not ending an arrangement, and built machinery for the difference: reversible freezes, terminal cancellations, single-use cards that retire themselves, in-flight states between authorized and settled, chargebacks as governed compensation, and the statement that reconciles everything to one project code. This part maps each ending onto the agent task that must actually stop, and closes with the breaks, including the one where the analogy runs backward. Next month the gym bills you anyway, on the replacement card’s number, which you never gave it. Nothing malfunctioned. The network’s account updater service f.</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/canceling-the-card-doesnt-stop-the-charges/</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); chapter of the Mission-Bound Authorization handbook. **Added 26 Aug 2026 — not in the site's RSS feed**, which is why the 11 Aug backfill missed it: the corpus tracked the series index but not its member essays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Closing the Agent Authorization Gaps</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>The OAuth Community's Gap Catalog, Answered Line by Line. The standards community is converging on a problem statement: agents break OAuth's pre-approval paradigm, tokens cannot represent delegation chains, revocation cannot reach a task, and consent screens cannot survive a thousand scopes. The agent authorization use-case catalog names eleven scenarios and rolls its analysis up to six major gaps, and this part answers the catalog line by line at both grains with machinery that existed before it was published: task-level revocation is the Mission kill switch, bulk revocation is Mission Management, multi-hop chains are act chains and Child Missions, scope explosion dies at Mission-grain consent, and the new grant-versus-execution gap lands on Decision and Execution Evidence. Seven answers are partial and two are delegated, and the tally is stated rather than smoothed. The first four proofs held the model against a threat model.</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/closing-the-agent-authorization-gaps/</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); chapter of the Mission-Bound Authorization handbook. **Added 26 Aug 2026 — not in the site's RSS feed**, which is why the 11 Aug backfill missed it: the corpus tracked the series index but not its member essays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Common Objections to Mission-Based Authorization</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Answers for the People Who Run Today's Control Planes. A skeptical FAQ for IAM practitioners and architects. Twenty-three objections test mission-based authorization against IdPs, workload identity, OAuth, RAR and UMA, short-lived tokens, PDPs and Zero Trust, Shared Signals, PAM and IGA, workflow engines, internal composition, open-world discovery, semantic misuse, enforcement bypass, lifecycle ownership, and privacy. The answers concede where existing systems are sufficient, identify where a Mission-shaped implementation may already exist under another name, and limit the standards case to the boundaries where private task state no longer reaches. The answer is sometimes yes . Existing products can keep task state, carry purpose attributes, issue task-specific credentials, and gate actions. A system that makes an approval-backed task record the root of authority and enforcement may already implement mission-based authorization with.</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/common-objections-to-mission-based-authorization/</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); chapter of the Mission-Bound Authorization handbook. **Added 26 Aug 2026 — not in the site's RSS feed**, which is why the 11 Aug backfill missed it: the corpus tracked the series index but not its member essays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Containing the OWASP Agentic Threats</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Fifteen Agentic Threats and the LLM Top 10, Each Given a Verdict. Security reviewers do not arrive with your framing. They arrive with OWASP's: fifteen agentic threats from memory poisoning to human manipulation, plus the LLM Top 10. This part crosswalks both onto the handbook and refuses the move that makes crosswalks worthless, claiming everything. Each threat gets one of three verdicts. Contained means the threat lands on machinery built for it, with a draft behind it. Bounded means the cause is out of authorization's reach but the blast radius is capped at the action gate. Delegated means it is not an authorization problem and a named complement owns it. Six of the fifteen are contained, nine are bounded, and half the LLM Top 10 is honestly someone else's layer. The first two proofs in this chapter answered a threat model and a requirements framework. This one answers the checklist. When a security team reviews an agent deplo.</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/containing-the-owasp-agentic-threats/</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); chapter of the Mission-Bound Authorization handbook. **Added 26 Aug 2026 — not in the site's RSS feed**, which is why the 11 Aug backfill missed it: the corpus tracked the series index but not its member essays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — From a Request to an Approved Mission</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Shaping, Consent Evidence, and Deferred Approval with Revision. A user request is untrusted input. This part covers the integrity of the approval event, the layer before any token exists: the client-side shaper that proposes a candidate Mission Intent, the Consent Evidence that commits the structured consent disclosure the Authorization Server recorded as rendered (not the pixels or the Approver's comprehension), and the deferred and revisable approval that lets a human reviewer narrow a proposal in place. Authority is created only when the Authorization Server validates, narrows, and approves. The Mission Is the Missing Abstraction drew the boundary between Mission Intent (a proposal) and an approved Mission (the governance object). The approval event is the single moment of transition, where the Authorization Server validates the Intent, derives an Authority Set, the Approver consents, and the Mission record is committed by intent_has.</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/from-a-request-to-an-approved-mission/</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); chapter of the Mission-Bound Authorization handbook. **Added 26 Aug 2026 — not in the site's RSS feed**, which is why the 11 Aug backfill missed it: the corpus tracked the series index but not its member essays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — From the Card to the Architecture</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Translating the Corporate-Card Model into Mission-Bound Authorization. What the Corporate Card Already Solved walked a working delegated-authority architecture one control at a time and never mentioned a protocol. This part is the joint between that mental model and this chapter's architecture. The five rules the card world taught become the five laws of delegated authority, stated for any substrate. The corporate-card test becomes the claim gate a vendor claim must pass. And the build lists that closed each card post, the things the agent stack cannot borrow from the expense world, turn out to enumerate the draft family: disclosure integrity, field-speed narrowing, checkpoints per boundary, endings that propagate, and a record that earns trust without a bank. What the Corporate Card Already Solved makes one claim across five posts: enterprise finance independently discovered the governance architecture that agent authorization now requires, a.</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/from-the-card-to-the-architecture/</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); chapter of the Mission-Bound Authorization handbook. **Added 26 Aug 2026 — not in the site's RSS feed**, which is why the 11 Aug backfill missed it: the corpus tracked the series index but not its member essays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Making Compliance a By-Product</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>What NIST AI RMF, the EU AI Act, and ISO/IEC 42001 Ask Agents to Prove. The third kind of outside framing is the one with auditors behind it. NIST AI RMF, the EU AI Act, and ISO/IEC 42001 converge on one demand: show me. Show me who is accountable, what the system is for, how you observe it, and how you stop it. In most agent stacks the honest answer is archaeology through session logs. In this architecture the artifact that enforces is the artifact that documents: the Mission is the documented purpose, the approval is the accountable decision, the evidence family is the log, and Termination is the interrupt. The crosswalk maps eight obligations onto machinery that exists for safety reasons, and then names what compliance still requires, because evidence is not certification. This chapter has held the handbook against a threat model, a requirements framework, and a threat taxonomy. The last framing is the one with auditors behind it. A.</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/making-compliance-a-by-product/</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); chapter of the Mission-Bound Authorization handbook. **Added 26 Aug 2026 — not in the site's RSS feed**, which is why the 11 Aug backfill missed it: the corpus tracked the series index but not its member essays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Mission-Based Authorization: The Field Reference</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>The Category, the Litmus Test, the Landscape, and the Running Example. Mission-based authorization governs the approved task, not just the credential, session, or request. This page is the field reference: the definition and litmus test for what counts as mission-based, a competitive landscape, the adoption stages, threats and non-goals, the canonical diagram and glossary, and the Q3 board-packet example threaded through the handbook. Mission-based authorization governs the approved task , not just the credential, session, or individual request.</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/mission-based-authorization-field-reference/</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); chapter of the Mission-Bound Authorization handbook. **Added 26 Aug 2026 — not in the site's RSS feed**, which is why the 11 Aug backfill missed it: the corpus tracked the series index but not its member essays. Reference apparatus rather than argument; the condensed lookup for the whole model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — The Mission-Based Authorization Vendor Test</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Six Questions for Anyone Claiming Agent Authorization. When a vendor says they support agent authorization, ask six questions: what is the approved task object, what derives authority from it, what keeps authority strictly narrower as work fans out, what checks each action at the moment of use, what happens when it is revoked, and can an auditor pull one identifier and see the whole task. The test is intentionally unforgiving: no approved task object means no category claim, token validation is not runtime enforcement, token expiry is not revocation, and logs are not task evidence. A vendor that passes can write the honest deployment claim with level, enforcement scope, freshness, evidence, and exclusions. Agent auth today can prove who is acting and what credential they hold. It cannot prove the work is still authorized. So when a vendor says they support agent authorization, the evaluation is six questions. Each probes one propert.</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/mission-based-authorization-vendor-test/</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); chapter of the Mission-Bound Authorization handbook. **Added 26 Aug 2026 — not in the site's RSS feed**, which is why the 11 Aug backfill missed it: the corpus tracked the series index but not its member essays. Reference apparatus — an evaluation checklist rather than a design argument.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Mission-Bound Authority: Instances, Actors, and Delegation</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>From Authenticated Agent Identity to Bounded, Narrowing Authority. The AI agent auth best practices give an agent workload identity, credentials, and delegated user authority. This part binds Mission authority to that identity. The mission claim projects the approved task into every derived token, attested instance identifiers and actor chains keep every actor attributable, and delegated work gets explicit, narrower, separately revocable authority. A sub-agent that acts because it descends from a parent session is inheriting ambient authority, not delegated authority. Child Missions give durable sub-agents their own revocable handles with strict-subset authority and cascade revocation. Offline attenuation, the experimental roadmap for fan-out at scale, keeps the Authorization Server off the hot path with the runtime state check as the surviving kill switch. The Mission Is the Missing Abstraction defined the Mission and From a Requ.</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/mission-bound-authority/</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); chapter of the Mission-Bound Authorization handbook. **Added 26 Aug 2026 — not in the site's RSS feed**, which is why the 11 Aug backfill missed it: the corpus tracked the series index but not its member essays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Mission-Bound Authorization: The Glossary</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>The Handbook's Vocabulary, A to Z. The handbook's vocabulary in one lookup table, A to Z: the objects, the artifacts, the mechanisms, the roles, and the named constructs, each defined in one to three sentences with a link to its canonical home. The entries are written to be quoted. The canonical homes carry the argument. Delegated work forces four separate continuity questions: request provenance, identity attribution, target-applicable authority, and ….</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/mission-bound-authorization-glossary/</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); chapter of the Mission-Bound Authorization handbook. **Added 26 Aug 2026 — not in the site's RSS feed**, which is why the 11 Aug backfill missed it: the corpus tracked the series index but not its member essays. Reference apparatus rather than argument — but the controlled vocabulary is the useful part: it is the closest thing the Mission-Bound programme has to a normative terminology section.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Mission-Bound Authorization: The Standards Map</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>OAuth, WIMSE, and OpenID, Mapped to the Architecture. The Mission is the architecture's new primitive. The rest should compose. This appendix tests that claim against the ratified OAuth substrate, the complete active OAuth and WIMSE working-group queues, selected individual drafts, and the relevant OpenID Foundation specifications. It separates publication status from architectural relationship and states the important deltas and substitution hazards plainly. Statuses follow the public record as of July 15, 2026 . The Reference tracks the family’s own reconciliation date separately. The map is exhaustive for the active OAuth and WIMSE working-group queues on that date. It is intentionally selective for ratified RFCs, individual Internet-Drafts, and OpenID specifications: those sections include documents with a concrete architectural join, a material overlap, or a common substitution hazard. This is a design map, not a registry dump.</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/mission-bound-authorization-standards-map/</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); chapter of the Mission-Bound Authorization handbook. **Added 26 Aug 2026 — not in the site's RSS feed**, which is why the 11 Aug backfill missed it: the corpus tracked the series index but not its member essays. Reference apparatus, and the most directly useful chapter for this corpus: it maps the Mission-Bound programme onto the external specs it composes, so it doubles as an index into the OAuth/OIDF/RATS/WIMSE rows tracked here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Mission Lifecycle and Change</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Observe, Revoke, Grow, Complete. The issuance profile gives a Mission three states and gates derivation on active. This part adds the surfaces that make state actionable over time: Status for canonical pull freshness with Signals as its push complement, Expansion for governed growth, and Completion for monotonic narrowing. One rule threads through all four. Only active permits reliance, so every state a newer profile adds fails safe for a consumer that predates it. The Mission Is the Missing Abstraction defined the Mission as a durable governance object and gave it a deliberately small lifecycle: active , revoked , expired , with the rule that only active permits new derivation. That issuance profile is complete on its own. But it observes Mission state only through one channel: the lifetime of the tokens it already issued, plus optional token introspection. A consumer that holds a Mission-bound t.</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/mission-lifecycle-and-change/</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); chapter of the Mission-Bound Authorization handbook. **Added 26 Aug 2026 — not in the site's RSS feed**, which is why the 11 Aug backfill missed it: the corpus tracked the series index but not its member essays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Splitting the Lethal Trifecta</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>How Mission-Bound Authorization Contains the Defining Agent Threat Model. Simon Willison named the combination that makes agents dangerous: access to private data, exposure to untrusted content, and the ability to communicate externally, held together in one loop. Any two legs are safe. All three are an exfiltration machine waiting for a poisoned document. This part runs the handbook against that threat model: the three legs become separately typed action classes under one Mission, the external leg becomes a consequential action that needs a fresh parameter-bound permit, mediated custody keeps the egress credential out of the agent's hands, and the harness downgrades egress once untrusted content enters the session. Then the honest residuals: enforcement scope, composition, and the semantic gap. In June 2025, Simon Willison named the pattern that the disclosures keep confirming: an agent that combines access to private data, exposure to untrusted.</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/splitting-the-lethal-trifecta/</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); chapter of the Mission-Bound Authorization handbook. **Added 26 Aug 2026 — not in the site's RSS feed**, which is why the 11 Aug backfill missed it: the corpus tracked the series index but not its member essays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — The Agent Runtime and Audit</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>Sessions Are Not Authority, Safe Unwinding, and Tamper-Evident Evidence. The first five layers make the Mission approvable, enforceable, governable, and delegable. This operational close makes them hold up against a real agent: a harness that treats session continuity as recoverable state and not as authority, an orchestrator that unwinds work already in flight when a Mission stops, and a transparency profile that makes the suite's evidence independently verifiable across trust domains. It closes with a synthesis of the six operational layers and the Mission Assurance Levels, the practice-side view of the adoption path the architecture chapter stages. The layers before this one build the Mission as a governance object. It is approved with integrity ( From a Request to an Approved Mission ), bound to instances and delegated under a strict subset ( Mission-Bound Authority ), enforced per action ( Mission-Bound Runtime Enforcement ), and observ.</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/the-agent-runtime-and-audit/</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); chapter of the Mission-Bound Authorization handbook. **Added 26 Aug 2026 — not in the site's RSS feed**, which is why the 11 Aug backfill missed it: the corpus tracked the series index but not its member essays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — The Authority Control Plane</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>Where the Layer Sits in the Estate. Issuance gating and runtime enforcement are two independent chokepoints, strictly stronger together: a gap in PEP coverage is still bounded at the token layer, and an outstanding token is still stopped at the action layer. The Mission Authority Server, the issuance grant, the Mandate, and Cross-Domain Projection extend the pattern space. And the structural reading that platform engineers reach for unprompted: the layer is the control plane for delegated authority, mapped concept by concept from desired state to the fleet API, with the disciplines that keep the framing honest. Reading path. ~6 minutes start to finish, or jump to the mapping table for the control-plane reading at a glance.</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/the-authority-control-plane/</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); chapter of the Mission-Bound Authorization handbook. **Added 26 Aug 2026 — not in the site's RSS feed**, which is why the 11 Aug backfill missed it: the corpus tracked the series index but not its member essays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — The Contractor Gets Their Own Card</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>Why Delegated Authority Must Narrow, and Never Be Borrowed. Crunch week. The contractor needs materials, and the project manager hands over her own card, just this once. Everything about it is convenient and everything about it is wrong, and every finance team knows exactly why. This part walks delegation the way a mature card program runs it: the contractor's own card with a lower limit, attribution that survives the handoff, cards that die when the project closes, and caps on how many cards a project may issue, not just how big each one is. Then the three places the analogy breaks for AI agents, where the fixes have to be built. Everything about it is convenient. No forms, no waiting, the work keeps moving. And everything about it is wrong, in ways every finance team can recite from memory. The statement will say she bought whatever he buys. Her limit, tuned to her role, is now backing his judgment. If the card number lea.</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/the-contractor-gets-their-own-card/</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); chapter of the Mission-Bound Authorization handbook. **Added 26 Aug 2026 — not in the site's RSS feed**, which is why the 11 Aug backfill missed it: the corpus tracked the series index but not its member essays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — The Convergence and the Wagers</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>The Outside Evidence, the Named Bets, and the Handbook's Close. The handbook closes on judgment. First the strongest outside evidence: AAuth, the proposed clean-slate agent protocol, adopted a first-class mission layer in its 01 revision after this model's AAuth mapping circulated: not independent replication, adoption by a designer free to say no, which is its own kind of proof. Then the honest bets: admission grain, issuer home, the price of Termination, the necessity of the object itself, the portability of its authority, and the classification line, each stated with the evidence that would falsify it. The laws and the claim gate are the invariants. The bets are the wagers, and deployment experience, not this handbook, will settle them. The sharpest evidence for the fundamental-versus-accidental split arrived from outside this family. AAuth is Dick Hardt’s proposed agent-native authorization protocol, an active individual draft (.</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/the-convergence-and-the-wagers/</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); chapter of the Mission-Bound Authorization handbook. **Added 26 Aug 2026 — not in the site's RSS feed**, which is why the 11 Aug backfill missed it: the corpus tracked the series index but not its member essays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — The Network Approves Every Transaction, Not the Card</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>Per-Action Authorization, and the Escape Hatch Called Cash. A decline at the register is mild embarrassment and a tap of a different card, because the system is working: the network approves transactions, not cards. This part walks per-action authorization the way payments runs it: the plastic that proves almost nothing, the authorization that binds this amount at this merchant now, the hotel hold that expires, the freeze that declines the next swipe wherever the issuer decision is checked, and the ATM, the escape hatch every honest card program names in writing. Then the breaks: agents have no common payment-style network, their false-approval costs are unbounded, and their cardholder can be hypnotized mid-purchase. That boring little moment is the most important design fact in payments. The decline is not a failure of the system. It is the system, doing the one thing it exists to do: deciding this transaction, right now,.</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/the-network-approves-every-transaction/</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); chapter of the Mission-Bound Authorization handbook. **Added 26 Aug 2026 — not in the site's RSS feed**, which is why the 11 Aug backfill missed it: the corpus tracked the series index but not its member essays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — What Survives Without OAuth</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>The Substrate-Neutral Model and Its Verb Spine. OAuth is the flagship binding because it is deployment reality, but the model does not depend on it. This part states the framework the profiles realize: four functions (compilation, projection, containment, continuity), a verb spine of ten verbs from propose to analyze, and the fundamental-versus-accidental test. Which ideas survive if OAuth disappears? Nearly all of them: the layer, the laws, the vocabulary, the approved task with an integrity-anchored record, approval evidence, runtime containment. What is accidental is the realization: PAR, RAR, the claim names, the wire shapes. The Mission is the durable, approval-backed record of the task ( The Mission Is the Missing Abstraction ), and the chapters before this one made the argument at every altitude: the intuition, the architecture, the wire, the outside framings. This concluding chapter zooms out to the framework tho.</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/what-survives-without-oauth/</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); chapter of the Mission-Bound Authorization handbook. **Added 26 Aug 2026 — not in the site's RSS feed**, which is why the 11 Aug backfill missed it: the corpus tracked the series index but not its member essays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — You Approve What You Were Shown</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>What Spend Approval Knows About Approving an Agent's Task. A manager approves a conference request on their phone between meetings. Months later, the only defensible answer to 'what did you approve?' is the request as rendered on that screen. This part walks the anatomy of a real approval: requests that are proposals and nothing more, reviewers who narrow instead of denying, decisions that take days without losing their place, and the disclosure that binds. Payments turned that last idea into regulation. Then the honest part: three places the analogy breaks for AI agents, and what each break demands. The only defensible answer is not “a trip, roughly.” It is the request as it was rendered on that screen, at that moment: the destination, the dates, the $3,400 estimate, the cost center, the attached quote. If the approval means anything at all, it means that . Not what the requester intended. Not what the system stored somew.</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/notes/you-approve-what-you-were-shown/</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Jul 2026 on Control Plane (notes.karlmcguinness.com); chapter of the Mission-Bound Authorization handbook. **Added 26 Aug 2026 — not in the site's RSS feed**, which is why the 11 Aug backfill missed it: the corpus tracked the series index but not its member essays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Least-Privilege MCP Tool Calls</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>An agent preparing a board packet reads financials, drafts a document, and notifies a reviewer group: three MCP tool calls across three authorization domains, all behind one sentence of human intent.</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/series/least-privilege-mcp/</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>Published on Control Plane (notes.karlmcguinness.com); series index. Added 26 Aug 2026: the 11 Aug backfill took series indexes from the RSS feed, but this one is linked only from the handbook and was not in the feed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Mission-Bound OAuth</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>Superseded by the Mission-Bound Authorization draft family, kept as history. A four-part series on Mission-Bound OAuth: the core architecture, the OAuth authentication-layer companion profile, the AAuth mapping, and a final critique of whether OAuth is the right home for the Mission model at all.</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/series/mission-bound-oauth/</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>Published on Control Plane (notes.karlmcguinness.com); series index. Added 26 Aug 2026: the 11 Aug backfill took series indexes from the RSS feed, but this one is linked only from the handbook and was not in the feed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Mission Shaping</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>Many current agent deployments skip the step that turns approved intent into bounded authority. This two-part series covers the Mission shaping problem and why even a well-shaped Mission is not enough once an agent is running in the world.</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/series/mission-shaping/</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>Published on Control Plane (notes.karlmcguinness.com); series index. Added 26 Aug 2026: the 11 Aug backfill took series indexes from the RSS feed, but this one is linked only from the handbook and was not in the feed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — Open-World OAuth</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>OAuth was built for closed worlds, and that constraint is why it became mature. Agents expose the limits of that deployment model. This post traces what the newer OAuth standards get right and which substrate gaps still need to close. Open-world OAuth can improve discovery, resource binding, and first-contact trust. That still leaves the harder agent problem: how approved intent becomes bounded authority that stays governed across delegation chains, unfamiliar tools, consent expansion, revocation, and task termination.</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/series/open-world-oauth/</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>Published on Control Plane (notes.karlmcguinness.com); series index. Added 26 Aug 2026: the 11 Aug backfill took series indexes from the RSS feed, but this one is linked only from the handbook and was not in the feed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>McGuinness — You Don't Give Agents Credentials. You Grant Them Power of Attorney.</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>Enterprise IAM governs who an agent is and what it may do at each boundary. No widely adopted control governs whether its mission should still be running. This series builds the case for the authority-governance layer that closes that gap.</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.karlmcguinness.com/series/you-dont-give-agents-credentials-you-grant-them-power-of-attorney/</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>Published on Control Plane (notes.karlmcguinness.com); series index. Added 26 Aug 2026: the 11 Aug backfill took series indexes from the RSS feed, but this one is linked only from the handbook and was not in the feed.</t>
         </is>
       </c>
     </row>
@@ -13908,6 +14778,35 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D83" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D84" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId113"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/delegated_authorization_research.xlsx
+++ b/delegated_authorization_research.xlsx
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="6" t="n">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="D12" s="7" t="n"/>
     </row>
@@ -966,7 +966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F261"/>
+  <dimension ref="A1:F257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 19 Aug 2026 (was -01, 6 Aug 2026) (was -00, Jun 26 2026); authors: Thibault Meunier (Cloudflare), Sandor Major (Google). Replaces draft-meunier-web-bot-auth-architecture. Pairs with draft-meunier-webbotauth-httpsig-directory for key discovery.</t>
+          <t>Revision -02, 19 Aug 2026 (was -01, 6 Aug 2026) (was -00, Jun 26 2026); authors: Thibault Meunier (Cloudflare), Sandor Major (Google). Replaces draft-meunier-web-bot-auth-architecture. Pairs with draft-meunier-webbotauth-httpsig-directory for key discovery. **SUPERSEDES draft-meunier-webbotauth-httpsig-directory**, which Datatracker marks Replaced by this draft. That older row was removed from the corpus on 26 Aug 2026 — it was tracked separately and had become a duplicate of this one under the pre-rename slug.</t>
         </is>
       </c>
     </row>
@@ -1165,17 +1165,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>draft-meunier-webbotauth-httpsig-directory — HTTP Message Signatures Directory</t>
+          <t>draft-rescorla-anonymous-webbotauth — Anonymous Bot Authentication: Authorization and Rate Limiting for Web Agents</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Defines a JWKS-based key directory, a well-known URI for key discovery (/.well-known/bot-auth-directory), and a new HTTP header field for in-band signing-key location communication, enabling origin servers to resolve a bot's signing key without prior configuration.</t>
+          <t>Proposes Anonymous Bot Authentication (ABA) using Privacy Pass tokens and Anonymous Rate-Limited Credentials, enabling sites to enforce rate limits and access controls on bots without identifying individual operators. Decouples 'is this a legitimate bot' from 'which bot is this,' preserving privacy while preventing abuse.</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-meunier-webbotauth-httpsig-directory/</t>
+          <t>https://datatracker.ietf.org/doc/draft-rescorla-anonymous-webbotauth/</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, Jun 26 2026; authors: Thibault Meunier (Cloudflare), Sandor Major (Google). Replaces draft-meunier-http-message-signatures-directory. The key-discovery complement to httpsig-protocol.</t>
+          <t>Revision -00, Apr 7 2026; authors: Eric Rescorla (Independent), Richard L. Barnes (Cisco). Proposes the privacy-preserving counterpart to the httpsig identity approach — the WG will need to decide where the identity/anonymity balance lies.</t>
         </is>
       </c>
     </row>
@@ -1195,27 +1195,27 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>draft-rescorla-anonymous-webbotauth — Anonymous Bot Authentication: Authorization and Rate Limiting for Web Agents</t>
+          <t>Charter: AI Preferences WG (charter-ietf-aipref-01)</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Proposes Anonymous Bot Authentication (ABA) using Privacy Pass tokens and Anonymous Rate-Limited Credentials, enabling sites to enforce rate limits and access controls on bots without identifying individual operators. Decouples 'is this a legitimate bot' from 'which bot is this,' preserving privacy while preventing abuse.</t>
+          <t>The formal IETF charter for the AIPREF WG, standardizing vocabulary and protocol mechanisms (e.g., extending the Robots Exclusion Protocol and HTTP headers) for content owners to express preferences about AI training, deployment, and use of their content.</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-rescorla-anonymous-webbotauth/</t>
+          <t>https://datatracker.ietf.org/doc/charter-ietf-aipref/01/</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>IETF (WebBotAuth WG)</t>
+          <t>IETF (AIPREF WG charter)</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, Apr 7 2026; authors: Eric Rescorla (Independent), Richard L. Barnes (Cisco). Proposes the privacy-preserving counterpart to the httpsig identity approach — the WG will need to decide where the identity/anonymity balance lies.</t>
+          <t>Approved April 2025; the charter explicitly puts 'authenticating or authorizing clients and/or crawlers' out of scope — included here for ecosystem context, not because it's delegated-authz work per se. Sibling WG to WebBotAuth.</t>
         </is>
       </c>
     </row>
@@ -1225,27 +1225,27 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Charter: AI Preferences WG (charter-ietf-aipref-01)</t>
+          <t>draft-king-dawn-requirements — Requirements for Discovery of Agents, Workloads, and Named Entities (DAWN)</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>The formal IETF charter for the AIPREF WG, standardizing vocabulary and protocol mechanisms (e.g., extending the Robots Exclusion Protocol and HTTP headers) for content owners to express preferences about AI training, deployment, and use of their content.</t>
+          <t>An individual IETF draft from Adrian Farrel and Daniel King setting out solution-neutral requirements for discovering AI agents, services, and workloads across administrative boundaries — what must be discoverable, what trust properties apply, and what architectural constraints exist.</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/charter-ietf-aipref/01/</t>
+          <t>https://datatracker.ietf.org/doc/draft-king-dawn-requirements/01/</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>IETF (AIPREF WG charter)</t>
+          <t>IETF (individual)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Approved April 2025; the charter explicitly puts 'authenticating or authorizing clients and/or crawlers' out of scope — included here for ecosystem context, not because it's delegated-authz work per se. Sibling WG to WebBotAuth.</t>
+          <t>Revision -01, April 2026; intentionally NOT a protocol — sits one layer below auth. Authentication and authorization of discovered entities are out of scope, but DAWN discovery happens *before* auth/authz can begin.</t>
         </is>
       </c>
     </row>
@@ -1255,17 +1255,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>draft-king-dawn-requirements — Requirements for Discovery of Agents, Workloads, and Named Entities (DAWN)</t>
+          <t>draft-farrel-dawn-terminology — Terminology for the Discovery of Agents, Workloads, and Named Entities (DAWN)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>An individual IETF draft from Adrian Farrel and Daniel King setting out solution-neutral requirements for discovering AI agents, services, and workloads across administrative boundaries — what must be discoverable, what trust properties apply, and what architectural constraints exist.</t>
+          <t>Establishes standardized vocabulary across DAWN specifications: agents, workloads, named entities, capabilities, discovery processes, and registration functions. Defines the entities-to-be-discovered and the properties discovery must convey, without specifying protocol mechanics.</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-king-dawn-requirements/01/</t>
+          <t>https://datatracker.ietf.org/doc/draft-farrel-dawn-terminology/</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, April 2026; intentionally NOT a protocol — sits one layer below auth. Authentication and authorization of discovered entities are out of scope, but DAWN discovery happens *before* auth/authz can begin.</t>
+          <t>Revision -04, Jul 26 2026; authors: Adrian Farrel (Old Dog Consulting), Kehan Yao (China Mobile), Roland Schott (Deutsche Telekom), Nic Williams (Infoblox). Updated immediately ahead of IETF 126 DAWN BoF. At rev 04 the most mature DAWN document after the requirements draft; Farrel/Williams authorship signals serious WG momentum.</t>
         </is>
       </c>
     </row>
@@ -1285,17 +1285,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>draft-farrel-dawn-terminology — Terminology for the Discovery of Agents, Workloads, and Named Entities (DAWN)</t>
+          <t>draft-akhavain-moussa-dawn-problem-statement — Problem Statement for the Discovery of Agents, Workloads, and Named Entities (DAWN)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Establishes standardized vocabulary across DAWN specifications: agents, workloads, named entities, capabilities, discovery processes, and registration functions. Defines the entities-to-be-discovered and the properties discovery must convey, without specifying protocol mechanics.</t>
+          <t>Articulates cross-domain discovery challenges for the DAWN problem space: scalability across administrative boundaries, trust in discovered information, and the absence of a unified discovery model for heterogeneous AI agents and workloads. Establishes functional requirements that protocol proposals must satisfy.</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-farrel-dawn-terminology/</t>
+          <t>https://datatracker.ietf.org/doc/draft-akhavain-moussa-dawn-problem-statement/</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Revision -04, Jul 26 2026; authors: Adrian Farrel (Old Dog Consulting), Kehan Yao (China Mobile), Roland Schott (Deutsche Telekom), Nic Williams (Infoblox). Updated immediately ahead of IETF 126 DAWN BoF. At rev 04 the most mature DAWN document after the requirements draft; Farrel/Williams authorship signals serious WG momentum.</t>
+          <t>Revision -05, Jul 19 2026; authors: Arashmid Akhavain, Hesham Moussa (Huawei Canada), Daniel King (Old Dog Consulting). King co-authorship ties this to draft-king-dawn-requirements already in corpus; together they are the two foundational DAWN framing documents. Updated ahead of IETF 126 DAWN BoF.</t>
         </is>
       </c>
     </row>
@@ -1315,17 +1315,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>draft-akhavain-moussa-dawn-problem-statement — Problem Statement for the Discovery of Agents, Workloads, and Named Entities (DAWN)</t>
+          <t>draft-moussa-dawn-gap-analysis — Gap Analysis and Applicability Statement for Discovery Protocols of DAWN</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Articulates cross-domain discovery challenges for the DAWN problem space: scalability across administrative boundaries, trust in discovered information, and the absence of a unified discovery model for heterogeneous AI agents and workloads. Establishes functional requirements that protocol proposals must satisfy.</t>
+          <t>Evaluates DNS, mDNS/DNS-SD, SSDP/UPnP, and other existing discovery protocols against DAWN requirements, identifying security gaps (no agent-specific trust model), privacy gaps (broadcast exposure), and applicability limits (local-scope vs. global cross-domain scenarios); proposes hybrid patterns and mitigations.</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-akhavain-moussa-dawn-problem-statement/</t>
+          <t>https://datatracker.ietf.org/doc/draft-moussa-dawn-gap-analysis/</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Revision -05, Jul 19 2026; authors: Arashmid Akhavain, Hesham Moussa (Huawei Canada), Daniel King (Old Dog Consulting). King co-authorship ties this to draft-king-dawn-requirements already in corpus; together they are the two foundational DAWN framing documents. Updated ahead of IETF 126 DAWN BoF.</t>
+          <t>Revision -01, Jun 12 2026; authors: Hesham Moussa, Arashmid Akhavain (Huawei Canada). Directly informs which existing protocol building blocks DAWN can reuse vs. what must be specified fresh. Key input for understanding why a new WG is needed rather than profiling DNS or mDNS.</t>
         </is>
       </c>
     </row>
@@ -1345,17 +1345,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>draft-moussa-dawn-gap-analysis — Gap Analysis and Applicability Statement for Discovery Protocols of DAWN</t>
+          <t>draft-jimenez-dawn-discovery-landscape — A Survey of AI Agent Discovery Mechanisms</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Evaluates DNS, mDNS/DNS-SD, SSDP/UPnP, and other existing discovery protocols against DAWN requirements, identifying security gaps (no agent-specific trust model), privacy gaps (broadcast exposure), and applicability limits (local-scope vs. global cross-domain scenarios); proposes hybrid patterns and mitigations.</t>
+          <t>Surveys discovery mechanisms across standardization bodies and open-source projects (MCP, A2A, robots.txt, Well-Known URIs, registry services), comparing approaches by model, scope, and semantic capability, and identifying remaining standardization gaps that DAWN must address.</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-moussa-dawn-gap-analysis/</t>
+          <t>https://datatracker.ietf.org/doc/draft-jimenez-dawn-discovery-landscape/</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, Jun 12 2026; authors: Hesham Moussa, Arashmid Akhavain (Huawei Canada). Directly informs which existing protocol building blocks DAWN can reuse vs. what must be specified fresh. Key input for understanding why a new WG is needed rather than profiling DNS or mDNS.</t>
+          <t>Revision -00, Jul 3 2026; authors: Jaime Jimenez, Jim Feng, Jari Arkko, Mirja Kühlewind, Rajat Kandoi (all Ericsson). Kühlewind co-authorship (same as kuehlewind-audit-architecture in corpus) is notable — the audit architecture team is tracking the discovery space. Useful as the landscape reference for the boundaries analysis.</t>
         </is>
       </c>
     </row>
@@ -1375,27 +1375,27 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>draft-jimenez-dawn-discovery-landscape — A Survey of AI Agent Discovery Mechanisms</t>
+          <t>draft-ietf-oauth-v2-1 — The OAuth 2.1 Authorization Framework</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Surveys discovery mechanisms across standardization bodies and open-source projects (MCP, A2A, robots.txt, Well-Known URIs, registry services), comparing approaches by model, scope, and semantic capability, and identifying remaining standardization gaps that DAWN must address.</t>
+          <t>An IETF WG draft that obsoletes RFC 6749/6750 by mandating PKCE for the authorization code grant, removing implicit and ROPC, and requiring exact redirect-URI matching.</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-jimenez-dawn-discovery-landscape/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-v2-1/</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual)</t>
+          <t>IETF (OAuth WG)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, Jul 3 2026; authors: Jaime Jimenez, Jim Feng, Jari Arkko, Mirja Kühlewind, Rajat Kandoi (all Ericsson). Kühlewind co-authorship (same as kuehlewind-audit-architecture in corpus) is notable — the audit architecture team is tracking the discovery space. Useful as the landscape reference for the boundaries analysis.</t>
+          <t>Revision -15 (March 2026) is the current baseline that MCP, FAPI 2.0, and most agent specs profile against.</t>
         </is>
       </c>
     </row>
@@ -1405,17 +1405,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>draft-ietf-oauth-v2-1 — The OAuth 2.1 Authorization Framework</t>
+          <t>draft-ietf-oauth-identity-chaining — OAuth Identity and Authorization Chaining Across Domains</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>An IETF WG draft that obsoletes RFC 6749/6750 by mandating PKCE for the authorization code grant, removing implicit and ROPC, and requiring exact redirect-URI matching.</t>
+          <t>An IETF WG draft that defines how to preserve identity and authorization context across trust domains by combining RFC 8693 token exchange with RFC 7521/7523 JWT assertions.</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-v2-1/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-identity-chaining/</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Revision -15 (March 2026) is the current baseline that MCP, FAPI 2.0, and most agent specs profile against.</t>
+          <t>Revision -17, Jul 22 2026 — rapid iteration signal heading into IETF 126. IESG-approved and in the RFC Editor queue (rfceditor state 'In Progress', IANA actions acknowledged); still no RFC number assigned as of 21 Aug 2026. The canonical multi-domain delegation pattern referenced by most agent and zero-trust drafts.</t>
         </is>
       </c>
     </row>
@@ -1435,17 +1435,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>draft-ietf-oauth-identity-chaining — OAuth Identity and Authorization Chaining Across Domains</t>
+          <t>draft-ietf-oauth-identity-assertion-authz-grant — Identity Assertion JWT Authorization Grant (ID-JAG)</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>An IETF WG draft that defines how to preserve identity and authorization context across trust domains by combining RFC 8693 token exchange with RFC 7521/7523 JWT assertions.</t>
+          <t>An IETF WG draft (Parecki/McGuinness/Campbell) defining how an app uses an identity assertion to obtain an access token for a third-party API by coordinating through a shared enterprise IdP.</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-identity-chaining/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-identity-assertion-authz-grant/</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Revision -17, Jul 22 2026 — rapid iteration signal heading into IETF 126. IESG-approved and in the RFC Editor queue (rfceditor state 'In Progress', IANA actions acknowledged); still no RFC number assigned as of 21 Aug 2026. The canonical multi-domain delegation pattern referenced by most agent and zero-trust drafts.</t>
+          <t>Revision -03, April 2026; the cross-IdP SSO-to-API bridge that the McGuinness Actor Profile draft layers on top of, and that WorkOS's auth.md uses as one of its three discovery flows.</t>
         </is>
       </c>
     </row>
@@ -1465,27 +1465,27 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>draft-ietf-oauth-identity-assertion-authz-grant — Identity Assertion JWT Authorization Grant (ID-JAG)</t>
+          <t>draft-sharma-oauth-identity-propagation-context — Identity Propagation Context for Multi-Hop Delegation in OAuth 2.0</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>An IETF WG draft (Parecki/McGuinness/Campbell) defining how an app uses an identity assertion to obtain an access token for a third-party API by coordinating through a shared enterprise IdP.</t>
+          <t>Defines a signed JSON Identity Propagation Context (IPC) that carries per-hop cryptographic re-signing of delegation chain metadata at trust boundaries, complementing RFC 8693 Token Exchange by enabling identity propagation through multi-service chains without requiring a Security Token Service interaction at every hop.</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-identity-assertion-authz-grant/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sharma-oauth-identity-propagation-context/</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth WG)</t>
+          <t>IETF (individual)</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, April 2026; the cross-IdP SSO-to-API bridge that the McGuinness Actor Profile draft layers on top of, and that WorkOS's auth.md uses as one of its three discovery flows.</t>
+          <t>Revision -01, Jul 23 2026 (first filed -00 Jul 23 2026); author: Sharma. Cluster B (cross-domain identity chaining) companion to draft-ietf-oauth-identity-chaining. HTTP, gRPC, and Kafka protocol bindings specified — the first explicit event-streaming protocol binding in this family. The per-hop re-signing model is a structural alternative to token-based chains, trading token bloat for per-hop cryptographic commitment.</t>
         </is>
       </c>
     </row>
@@ -1495,27 +1495,27 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>draft-sharma-oauth-identity-propagation-context — Identity Propagation Context for Multi-Hop Delegation in OAuth 2.0</t>
+          <t>draft-ietf-oauth-transaction-tokens — Transaction Tokens (Txn-Tokens)</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Defines a signed JSON Identity Propagation Context (IPC) that carries per-hop cryptographic re-signing of delegation chain metadata at trust boundaries, complementing RFC 8693 Token Exchange by enabling identity propagation through multi-service chains without requiring a Security Token Service interaction at every hop.</t>
+          <t>An IETF WG draft defining short-lived signed JWTs that propagate immutable user identity and authorization context through internal call chains within a trust domain.</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sharma-oauth-identity-propagation-context/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-transaction-tokens/</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual)</t>
+          <t>IETF (OAuth WG)</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, Jul 23 2026 (first filed -00 Jul 23 2026); author: Sharma. Cluster B (cross-domain identity chaining) companion to draft-ietf-oauth-identity-chaining. HTTP, gRPC, and Kafka protocol bindings specified — the first explicit event-streaming protocol binding in this family. The per-hop re-signing model is a structural alternative to token-based chains, trading token bloat for per-hop cryptographic commitment.</t>
+          <t>Revision -11, 4 Aug 2026 (was -09, published 6 Jul 2026 (was -08 Mar 2026)); co-authored by Tulshibagwale (CAEP inventor), Fletcher, and Kasselman. -09 reorganized the Request Context section, changed JWT body claims from OPTIONAL to RECOMMENDED, and enhanced security considerations for invalidated access tokens. Advanced past WGLC: as of 21 Aug 2026 the stream state is 'WG Consensus: Waiting for Write-Up'. IESG submission milestone Dec 2026, and Transaction Tokens is one of only three active OAuth WG milestones under the approved rev-06 charter.</t>
         </is>
       </c>
     </row>
@@ -1525,17 +1525,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>draft-ietf-oauth-transaction-tokens — Transaction Tokens (Txn-Tokens)</t>
+          <t>draft-ietf-oauth-first-party-apps — OAuth 2.0 for First-Party Applications</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>An IETF WG draft defining short-lived signed JWTs that propagate immutable user identity and authorization context through internal call chains within a trust domain.</t>
+          <t>An IETF WG draft defining an Authorization Challenge Endpoint that lets first-party native apps drive a browserless OAuth flow while still supporting step-up authentication via RFC 9470.</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-transaction-tokens/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-first-party-apps/</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Revision -11, 4 Aug 2026 (was -09, published 6 Jul 2026 (was -08 Mar 2026)); co-authored by Tulshibagwale (CAEP inventor), Fletcher, and Kasselman. -09 reorganized the Request Context section, changed JWT body claims from OPTIONAL to RECOMMENDED, and enhanced security considerations for invalidated access tokens. Advanced past WGLC: as of 21 Aug 2026 the stream state is 'WG Consensus: Waiting for Write-Up'. IESG submission milestone Dec 2026, and Transaction Tokens is one of only three active OAuth WG milestones under the approved rev-06 charter.</t>
+          <t>Revision -04, published 1 Jul 2026; explicitly excluded for third-party use because it requires high AS↔client trust.</t>
         </is>
       </c>
     </row>
@@ -1555,17 +1555,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>draft-ietf-oauth-first-party-apps — OAuth 2.0 for First-Party Applications</t>
+          <t>draft-ietf-oauth-attestation-based-client-auth — OAuth 2.0 Attestation-Based Client Authentication</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>An IETF WG draft defining an Authorization Challenge Endpoint that lets first-party native apps drive a browserless OAuth flow while still supporting step-up authentication via RFC 9470.</t>
+          <t>An IETF WG draft (Looker/Bastian/Bormann) introducing two JWTs — a Client Attestation issued by a Client Attester and a Client Attestation PoP signed by the client instance — that travel in HTTP headers to let traditionally-public clients authenticate to the AS without a shared secret.</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-first-party-apps/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-attestation-based-client-auth/</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Revision -04, published 1 Jul 2026; explicitly excluded for third-party use because it requires high AS↔client trust.</t>
+          <t>Revision -10, Jul 2026 (was -08 Mar 2026). -10 added a 'client_attestation_pop_methods_supported' metadata parameter, created a new 'OAuth Client Attestation Proof-of-Possession Methods' registry, clarified that PoP mechanisms from other specs are permitted, and refined DPoP combined-mode handling. Relates to the RATS Passport Model per RFC 9334; RATS attestation procedures themselves are deliberately out of scope. The 'client instance' framing pairs naturally with the McGuinness Client Instance Assertion and AI Agent Instance drafts.</t>
         </is>
       </c>
     </row>
@@ -1585,17 +1585,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>draft-ietf-oauth-attestation-based-client-auth — OAuth 2.0 Attestation-Based Client Authentication</t>
+          <t>draft-ietf-oauth-spiffe-client-auth — OAuth SPIFFE Client Authentication</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>An IETF WG draft (Looker/Bastian/Bormann) introducing two JWTs — a Client Attestation issued by a Client Attester and a Client Attestation PoP signed by the client instance — that travel in HTTP headers to let traditionally-public clients authenticate to the AS without a shared secret.</t>
+          <t>An IETF WG draft (Schwenkschuster/Kasselman/Rose-NIST/Thorgersen-IBM) profiling RFC 7521, RFC 7523, and OAuth attestation-based client auth so that SPIFFE-enabled workloads can authenticate to OAuth ASes using JWT-SVID, WIT-SVID, or X.509-SVID credentials instead of shared client secrets.</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-attestation-based-client-auth/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-spiffe-client-auth/</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Revision -10, Jul 2026 (was -08 Mar 2026). -10 added a 'client_attestation_pop_methods_supported' metadata parameter, created a new 'OAuth Client Attestation Proof-of-Possession Methods' registry, clarified that PoP mechanisms from other specs are permitted, and refined DPoP combined-mode handling. Relates to the RATS Passport Model per RFC 9334; RATS attestation procedures themselves are deliberately out of scope. The 'client instance' framing pairs naturally with the McGuinness Client Instance Assertion and AI Agent Instance drafts.</t>
+          <t>Revision -01, March 2026 (re-slugged from draft-schwenkschuster-oauth-spiffe-client-auth after WG adoption); the protocol bridge between SPIFFE/WIMSE workload identity and the OAuth client-auth surface.</t>
         </is>
       </c>
     </row>
@@ -1615,27 +1615,27 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>draft-ietf-oauth-spiffe-client-auth — OAuth SPIFFE Client Authentication</t>
+          <t>draft-kahrer-oauth-client-challenge-protocol — OAuth Client Challenge Protocol</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>An IETF WG draft (Schwenkschuster/Kasselman/Rose-NIST/Thorgersen-IBM) profiling RFC 7521, RFC 7523, and OAuth attestation-based client auth so that SPIFFE-enabled workloads can authenticate to OAuth ASes using JWT-SVID, WIT-SVID, or X.509-SVID credentials instead of shared client secrets.</t>
+          <t>An IETF individual draft from Judith Kahrer (Curity) defining a new 'insufficient_client_authorization' error code so the authorization server can dynamically challenge the client mid-flow for an additional assertion, verifiable presentation, or proof-of-possession material — enabling just-in-time and step-up client authorization.</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-spiffe-client-auth/</t>
+          <t>https://datatracker.ietf.org/doc/draft-kahrer-oauth-client-challenge-protocol/</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth WG)</t>
+          <t>IETF (individual)</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, March 2026 (re-slugged from draft-schwenkschuster-oauth-spiffe-client-auth after WG adoption); the protocol bridge between SPIFFE/WIMSE workload identity and the OAuth client-auth surface.</t>
+          <t>Revision -00 published 19 May 2026; deliberately distinct from first-party-apps (challenges the CLIENT, not the user) and works for both first- and third-party clients. Cites Mastercard Verifiable Intent as a use case, linking it directly to the mandate/RAR pattern OVID implements.</t>
         </is>
       </c>
     </row>
@@ -1645,27 +1645,27 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>draft-kahrer-oauth-client-challenge-protocol — OAuth Client Challenge Protocol</t>
+          <t>draft-ietf-oauth-security-topics-update — Updates to OAuth 2.0 Security BCP</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft from Judith Kahrer (Curity) defining a new 'insufficient_client_authorization' error code so the authorization server can dynamically challenge the client mid-flow for an additional assertion, verifiable presentation, or proof-of-possession material — enabling just-in-time and step-up client authorization.</t>
+          <t>An IETF WG draft that extends RFC 9700 with new countermeasures, notably rules against audience-injection attacks where a client authenticates to multiple authorization servers.</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-kahrer-oauth-client-challenge-protocol/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-security-topics-update/</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual)</t>
+          <t>IETF (OAuth WG)</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Revision -00 published 19 May 2026; deliberately distinct from first-party-apps (challenges the CLIENT, not the user) and works for both first- and third-party clients. Cites Mastercard Verifiable Intent as a use case, linking it directly to the mandate/RAR pattern OVID implements.</t>
+          <t>Revision -01, March 2026; co-authored by University of Stuttgart (FAPI formal-analysis team) so the recommendations are formally grounded.</t>
         </is>
       </c>
     </row>
@@ -1675,17 +1675,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>draft-ietf-oauth-security-topics-update — Updates to OAuth 2.0 Security BCP</t>
+          <t>draft-ietf-oauth-client-id-metadata-document — OAuth Client ID Metadata Document</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>An IETF WG draft that extends RFC 9700 with new countermeasures, notably rules against audience-injection attacks where a client authenticates to multiple authorization servers.</t>
+          <t>Defines a mechanism for OAuth clients to identify themselves to authorization servers via a URL as the client_id, pointing to a published JSON document containing client metadata — enabling dynamic client identification without prior registration.</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-security-topics-update/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-client-id-metadata-document/</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, March 2026; co-authored by University of Stuttgart (FAPI formal-analysis team) so the recommendations are formally grounded.</t>
+          <t>Revision -02, Jul 2026; OAuth WG-adopted. Directly relevant to AI agent deployments where agents may be registered via discoverable metadata documents rather than static registrations. Complements draft-king-dawn-requirements (discovery layer) by providing the OAuth-layer registration artifact.</t>
         </is>
       </c>
     </row>
@@ -1705,17 +1705,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>draft-ietf-oauth-client-id-metadata-document — OAuth Client ID Metadata Document</t>
+          <t>draft-ietf-oauth-refresh-token-expiration — OAuth 2.0 Refresh Token and Authorization Expiration</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Defines a mechanism for OAuth clients to identify themselves to authorization servers via a URL as the client_id, pointing to a published JSON document containing client metadata — enabling dynamic client identification without prior registration.</t>
+          <t>Extends OAuth 2.0 with new token endpoint response parameters specifying refresh token expiration and user authorization expiration, making expiry semantics explicit and interoperable across implementations.</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-client-id-metadata-document/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-refresh-token-expiration/</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, Jul 2026; OAuth WG-adopted. Directly relevant to AI agent deployments where agents may be registered via discoverable metadata documents rather than static registrations. Complements draft-king-dawn-requirements (discovery layer) by providing the OAuth-layer registration artifact.</t>
+          <t>Revision -03, Jul 2026; OAuth WG-adopted. Relevant to long-running agent sessions: explicit authorization expiration addresses the gap where refresh tokens survive past the user's intended authorization window — a known risk in agentic delegation scenarios.</t>
         </is>
       </c>
     </row>
@@ -1735,27 +1735,27 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>draft-ietf-oauth-refresh-token-expiration — OAuth 2.0 Refresh Token and Authorization Expiration</t>
+          <t>draft-mcguinness-oauth-actor-profile — OAuth Actor Profile for Delegation</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Extends OAuth 2.0 with new token endpoint response parameters specifying refresh token expiration and user authorization expiration, making expiry semantics explicit and interoperable across implementations.</t>
+          <t>Karl McGuinness's individual draft profiling the RFC 8693 'act' claim with required iss, optional sub_profile entity classification, and uniform processing across JWT assertion grants, JWT access tokens, and Transaction Tokens.</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-refresh-token-expiration/</t>
+          <t>https://datatracker.ietf.org/doc/html/draft-mcguinness-oauth-actor-profile-00</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth WG)</t>
+          <t>IETF (individual)</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, Jul 2026; OAuth WG-adopted. Relevant to long-running agent sessions: explicit authorization expiration addresses the gap where refresh tokens survive past the user's intended authorization window — a known risk in agentic delegation scenarios.</t>
+          <t>Revision -00 published 30 April 2026; defines depth-1+ chain validation, cycle-aware construction, and bearer-to-PoP upgrade — the most complete actor-representation profile to date.</t>
         </is>
       </c>
     </row>
@@ -1765,17 +1765,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-actor-profile — OAuth Actor Profile for Delegation</t>
+          <t>draft-mw-oauth-actor-chain — Cryptographically Verifiable Actor Chains for OAuth 2.0 Token Exchange</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Karl McGuinness's individual draft profiling the RFC 8693 'act' claim with required iss, optional sub_profile entity classification, and uniform processing across JWT assertion grants, JWT access tokens, and Transaction Tokens.</t>
+          <t>An IETF individual draft (Prasad/Krishnan/Lopez/Addepalli) defining six actor-chain profiles for RFC 8693 — Declared/Verified × Full/Subset/Actor-Only Disclosure — that preserve and cryptographically validate delegation-path continuity across successive token exchanges instead of relying on RFC 8693's informational-only nested act claims.</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/html/draft-mcguinness-oauth-actor-profile-00</t>
+          <t>https://datatracker.ietf.org/doc/draft-mw-oauth-actor-chain/</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Revision -00 published 30 April 2026; defines depth-1+ chain validation, cycle-aware construction, and bearer-to-PoP upgrade — the most complete actor-representation profile to date.</t>
+          <t>Revision -01, 30 Jun 2026 (was -00 May 2026; re-slugged from draft-mw-spice-actor-chain-05); a complementary alternative to the McGuinness Actor Profile that directly addresses RFC 8693's chain-splicing weakness by making the chain itself cryptographically verifiable rather than just informational.</t>
         </is>
       </c>
     </row>
@@ -1795,17 +1795,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>draft-mw-oauth-actor-chain — Cryptographically Verifiable Actor Chains for OAuth 2.0 Token Exchange</t>
+          <t>draft-mcguinness-oauth-client-instance-assertion — OAuth Client Instance Assertion</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft (Prasad/Krishnan/Lopez/Addepalli) defining six actor-chain profiles for RFC 8693 — Declared/Verified × Full/Subset/Actor-Only Disclosure — that preserve and cryptographically validate delegation-path continuity across successive token exchanges instead of relying on RFC 8693's informational-only nested act claims.</t>
+          <t>Karl McGuinness's individual draft for representing a specific running instance of an OAuth client (rather than just the client registration) so authorization servers can bind grants to a concrete instance.</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mw-oauth-actor-chain/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-client-instance-assertion/</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 30 Jun 2026 (was -00 May 2026; re-slugged from draft-mw-spice-actor-chain-05); a complementary alternative to the McGuinness Actor Profile that directly addresses RFC 8693's chain-splicing weakness by making the chain itself cryptographically verifiable rather than just informational.</t>
+          <t>Note: full draft text was not retrievable through automated fetch at time of writing — recommend reading directly. Companion to the Actor Profile draft and to attestation-based client auth.</t>
         </is>
       </c>
     </row>
@@ -1825,17 +1825,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-client-instance-assertion — OAuth Client Instance Assertion</t>
+          <t>draft-mcguinness-oauth-resource-token-resp — OAuth 2.0 Resource Parameter in Access Token Response</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Karl McGuinness's individual draft for representing a specific running instance of an OAuth client (rather than just the client registration) so authorization servers can bind grants to a concrete instance.</t>
+          <t>A McGuinness/Skokan individual draft adding a 'resource' parameter to the OAuth access token response so clients can confirm which resource the issued token is valid for, mitigating resource mix-up attacks especially in deployments that use RFC 8707 Resource Indicators.</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-client-instance-assertion/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-resource-token-resp/</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Note: full draft text was not retrievable through automated fetch at time of writing — recommend reading directly. Companion to the Actor Profile draft and to attestation-based client auth.</t>
+          <t>Revision -03 (March 2026). Filip Skokan added as co-author in -03. Complements RFC 8707 / RFC 9700 / RFC 9207 by adding issuance-time confirmation to the discovery-time mechanisms. Notable for the agent-authz corpus because dynamic resource discovery is a core agent pattern and resource-mix-up attacks are amplified when agents juggle many short-lived tokens.</t>
         </is>
       </c>
     </row>
@@ -1855,17 +1855,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-resource-token-resp — OAuth 2.0 Resource Parameter in Access Token Response</t>
+          <t>draft-mcguinness-oauth-rfc9728bis — Update to OAuth 2.0 Protected Resource Metadata Resource Identifier Validation</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>A McGuinness/Skokan individual draft adding a 'resource' parameter to the OAuth access token response so clients can confirm which resource the issued token is valid for, mitigating resource mix-up attacks especially in deployments that use RFC 8707 Resource Indicators.</t>
+          <t>A McGuinness individual draft updating Section 3.3 of RFC 9728 (Protected Resource Metadata) so the resource value can be any URI sharing the same TLS origin as the requested URL whose path is a prefix of it — broadening the set of WWW-Authenticate response use cases without changing the rest of RFC 9728.</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-resource-token-resp/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-rfc9728bis/</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Revision -03 (March 2026). Filip Skokan added as co-author in -03. Complements RFC 8707 / RFC 9700 / RFC 9207 by adding issuance-time confirmation to the discovery-time mechanisms. Notable for the agent-authz corpus because dynamic resource discovery is a core agent pattern and resource-mix-up attacks are amplified when agents juggle many short-lived tokens.</t>
+          <t>Revision -01 (Feb 2026). A small targeted correction to the PRM validation rule. Notable as supporting infrastructure for the McGuinness Mission-Bound OAuth work — PRM is the substrate for Resource AS / Resource Server discovery of required RAR types under that profile.</t>
         </is>
       </c>
     </row>
@@ -1885,17 +1885,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-rfc9728bis — Update to OAuth 2.0 Protected Resource Metadata Resource Identifier Validation</t>
+          <t>draft-mcguinness-token-xchg-target-svc-disco — OAuth 2.0 Token Exchange Target Service Discovery</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>A McGuinness individual draft updating Section 3.3 of RFC 9728 (Protected Resource Metadata) so the resource value can be any URI sharing the same TLS origin as the requested URL whose path is a prefix of it — broadening the set of WWW-Authenticate response use cases without changing the rest of RFC 9728.</t>
+          <t>A McGuinness/Parecki individual draft defining a discovery endpoint that, given a subject token, returns the set of available target services (audiences, resources, scopes) the holder can request via RFC 8693 Token Exchange — accepting any registered subject_token_type so it supports advanced flows including identity chaining and cross-domain delegation.</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-rfc9728bis/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-token-xchg-target-svc-disco/</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Revision -01 (Feb 2026). A small targeted correction to the PRM validation rule. Notable as supporting infrastructure for the McGuinness Mission-Bound OAuth work — PRM is the substrate for Resource AS / Resource Server discovery of required RAR types under that profile.</t>
+          <t>Revision -01 (Feb 2026), co-authored with Aaron Parecki (Okta). Fills a discovery gap that ID-JAG and the Transaction Token Chaining Profile both implicitly assume — clients today must know which audience to request, which doesn't compose with open-world agentic flows where the right downstream service is determined at runtime.</t>
         </is>
       </c>
     </row>
@@ -1915,17 +1915,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-token-xchg-target-svc-disco — OAuth 2.0 Token Exchange Target Service Discovery</t>
+          <t>draft-mcguinness-oauth-actor-receipts — OAuth Actor Receipts for Delegation Provenance</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>A McGuinness/Parecki individual draft defining a discovery endpoint that, given a subject token, returns the set of available target services (audiences, resources, scopes) the holder can request via RFC 8693 Token Exchange — accepting any registered subject_token_type so it supports advanced flows including identity chaining and cross-domain delegation.</t>
+          <t>A McGuinness companion draft to the Actor Profile, aiming to provide per-hop signed receipts as the verifiable provenance layer that the Actor Profile (which keeps the 'act' chain informational) deliberately leaves out. Pulls over the provenance gap from the core profile so each principal in a delegation chain can produce independent cryptographic evidence.</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcguinness-token-xchg-target-svc-disco/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-actor-receipts/</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Revision -01 (Feb 2026), co-authored with Aaron Parecki (Okta). Fills a discovery gap that ID-JAG and the Transaction Token Chaining Profile both implicitly assume — clients today must know which audience to request, which doesn't compose with open-world agentic flows where the right downstream service is determined at runtime.</t>
+          <t>Revision -00, 4 Jul 2026; now formally on IETF Datatracker (was GitHub-only pre-publication through Jun 2026). Recommended companion to the Actor Profile when a deployment needs Verified Full Disclosure mode (per the Mission-Bound OAuth Runtime Enforcement Profile's Actor Provenance Module). Completes a triad with actor-profile and actor-proofs — receipts provide provenance, proofs provide cryptographic per-hop accountability.</t>
         </is>
       </c>
     </row>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-actor-receipts — OAuth Actor Receipts for Delegation Provenance</t>
+          <t>draft-mcguinness-oauth-actor-proofs — OAuth Actor-Signed Hop Proofs</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>A McGuinness companion draft to the Actor Profile, aiming to provide per-hop signed receipts as the verifiable provenance layer that the Actor Profile (which keeps the 'act' chain informational) deliberately leaves out. Pulls over the provenance gap from the core profile so each principal in a delegation chain can produce independent cryptographic evidence.</t>
+          <t>Introduces the 'actor_proofs' claim — a signed per-hop proof chain where each actor signs its own participation and the target binding it authorized for that hop; proofs are hash-chained and validated using actor verification keys from trusted sources, with optional references to sibling actor receipts.</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-actor-receipts/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-actor-proofs/</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 4 Jul 2026; now formally on IETF Datatracker (was GitHub-only pre-publication through Jun 2026). Recommended companion to the Actor Profile when a deployment needs Verified Full Disclosure mode (per the Mission-Bound OAuth Runtime Enforcement Profile's Actor Provenance Module). Completes a triad with actor-profile and actor-proofs — receipts provide provenance, proofs provide cryptographic per-hop accountability.</t>
+          <t>Revision -00, 4 Jul 2026. Completes the actor triad with actor-profile (chain structure) and actor-receipts (provenance) — actor-proofs closes the cryptographic accountability gap. Filed the same day as ai-agent-instance, id-assertion-framework, and domain-authorized-issuer — McGuinness submitted four new I-Ds on Jul 4-6, bringing his total to 11 individual I-Ds on Datatracker.</t>
         </is>
       </c>
     </row>
@@ -1975,17 +1975,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-actor-proofs — OAuth Actor-Signed Hop Proofs</t>
+          <t>draft-mcguinness-oauth-insufficient-claims — OAuth 2.0 Insufficient Claims Challenge</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Introduces the 'actor_proofs' claim — a signed per-hop proof chain where each actor signs its own participation and the target binding it authorized for that hop; proofs are hash-chained and validated using actor verification keys from trusted sources, with optional references to sibling actor receipts.</t>
+          <t>A McGuinness individual draft defining an insufficient_claims error code and required_claims parameter enabling authorization servers and protected resources to signal precisely which claims are missing from a presented credential. Allows resource servers to request enriched credentials carrying specific missing attributes rather than returning a generic 401.</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-actor-proofs/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-insufficient-claims/</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 4 Jul 2026. Completes the actor triad with actor-profile (chain structure) and actor-receipts (provenance) — actor-proofs closes the cryptographic accountability gap. Filed the same day as ai-agent-instance, id-assertion-framework, and domain-authorized-issuer — McGuinness submitted four new I-Ds on Jul 4-6, bringing his total to 11 individual I-Ds on Datatracker.</t>
+          <t>Revision -00, 27 May 2026. Enables just-in-time claim negotiation in multi-agent delegation chains where the acting party must assemble claims from multiple sources. Natural companion to the Actor Profile and Client Instance Assertion — those drafts define the identity structure; this one provides the feedback loop when that structure is incomplete at the RS.</t>
         </is>
       </c>
     </row>
@@ -2005,17 +2005,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-insufficient-claims — OAuth 2.0 Insufficient Claims Challenge</t>
+          <t>draft-mcguinness-oauth-ai-agent-instance — OAuth 2.0 AI Agent Instance Profile</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>A McGuinness individual draft defining an insufficient_claims error code and required_claims parameter enabling authorization servers and protected resources to signal precisely which claims are missing from a presented credential. Allows resource servers to request enriched credentials carrying specific missing attributes rather than returning a generic 401.</t>
+          <t>Profiles OAuth 2.0 for deployments where a single client ID represents an agent platform running many concurrent agent instances; defines claims conveying attested agent instance identity and provenance from an agent attester to the AS, with delegation-chain semantics for sub-agents. Claims are carrier-independent, compatible with both Client Instance Assertions and Client Attestation JWT.</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-insufficient-claims/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-ai-agent-instance/</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 27 May 2026. Enables just-in-time claim negotiation in multi-agent delegation chains where the acting party must assemble claims from multiple sources. Natural companion to the Actor Profile and Client Instance Assertion — those drafts define the identity structure; this one provides the feedback loop when that structure is incomplete at the RS.</t>
+          <t>Revision -00, 4 Jul 2026. Fills the gap between a registered OAuth client ID (platform-level) and a running agent instance (runtime-level) — the level at which delegation chains, attestation, and revocation actually operate. Companion to draft-mcguinness-oauth-client-instance-assertion (general instance framing) and draft-mcguinness-oauth-actor-profile (chain representation).</t>
         </is>
       </c>
     </row>
@@ -2035,17 +2035,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-ai-agent-instance — OAuth 2.0 AI Agent Instance Profile</t>
+          <t>draft-mcguinness-oauth-id-assertion-framework — OAuth Identity Assertion Trust Framework</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Profiles OAuth 2.0 for deployments where a single client ID represents an agent platform running many concurrent agent instances; defines claims conveying attested agent instance identity and provenance from an agent attester to the AS, with delegation-chain semantics for sub-agents. Claims are carrier-independent, compatible with both Client Instance Assertions and Client Attestation JWT.</t>
+          <t>Addresses the gap where issuer authentication alone does not prove AS authority over subject namespaces; defines an Authority Delegation Model with independent trust-evaluation categories and an Identity Assertion Issuer Trust Policy (JSON document declaring required trust methods) that Resource ASes evaluate before accepting identity assertions.</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-ai-agent-instance/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-id-assertion-framework/</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 4 Jul 2026. Fills the gap between a registered OAuth client ID (platform-level) and a running agent instance (runtime-level) — the level at which delegation chains, attestation, and revocation actually operate. Companion to draft-mcguinness-oauth-client-instance-assertion (general instance framing) and draft-mcguinness-oauth-actor-profile (chain representation).</t>
+          <t>Revision -00, 4 Jul 2026. Directly motivates and companions draft-mcguinness-oauth-domain-authorized-issuer (below) which provides a DNS-based trust method. Addresses the 'who is allowed to assert identities in this namespace?' question that ID-JAG and the identity-chaining WG draft assume resolved but do not specify.</t>
         </is>
       </c>
     </row>
@@ -2065,17 +2065,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-id-assertion-framework — OAuth Identity Assertion Trust Framework</t>
+          <t>draft-mcguinness-oauth-domain-authorized-issuer — OAuth Domain-Authorized Issuer Trust Method</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Addresses the gap where issuer authentication alone does not prove AS authority over subject namespaces; defines an Authority Delegation Model with independent trust-evaluation categories and an Identity Assertion Issuer Trust Policy (JSON document declaring required trust methods) that Resource ASes evaluate before accepting identity assertions.</t>
+          <t>DNS domain owners publish a policy (DNS TXT record at _oauth-issuer-policy.{domain} or HTTPS well-known fallback) listing the OAuth ASes authorized to assert identities in that namespace; Resource ASes use this to validate assertion issuers before accepting identity assertions or chaining tokens. Pattern echoes CAA/SPF/DKIM. Non-transitive — flat authorization, no delegation chains.</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-id-assertion-framework/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-domain-authorized-issuer/</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 4 Jul 2026. Directly motivates and companions draft-mcguinness-oauth-domain-authorized-issuer (below) which provides a DNS-based trust method. Addresses the 'who is allowed to assert identities in this namespace?' question that ID-JAG and the identity-chaining WG draft assume resolved but do not specify.</t>
+          <t>Revision -00, 4 Jul 2026. Implements one trust method for draft-mcguinness-oauth-id-assertion-framework. DNS-based approach is lightweight and operationally familiar; the non-transitive design avoids the amplification risks of transitive trust chains. Closes the 'how do you know the AS is allowed to speak for this domain?' gap that cross-domain identity chaining has always assumed away.</t>
         </is>
       </c>
     </row>
@@ -2095,17 +2095,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-domain-authorized-issuer — OAuth Domain-Authorized Issuer Trust Method</t>
+          <t>draft-mcguinness-oauth-mission — Mission-Bound Authorization for OAuth 2.0</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>DNS domain owners publish a policy (DNS TXT record at _oauth-issuer-policy.{domain} or HTTPS well-known fallback) listing the OAuth ASes authorized to assert identities in that namespace; Resource ASes use this to validate assertion issuers before accepting identity assertions or chaining tokens. Pattern echoes CAA/SPF/DKIM. Non-transitive — flat authorization, no delegation chains.</t>
+          <t>Introduces 'Mission' — a durable, integrity-bound artifact stored at the AS representing an approved task; clients submit Mission Intent via PAR, ASes derive concrete permissions, and approvers grant consent via integrity anchors. Access tokens carry a 'mission' claim; issuance is gated by the Mission's lifecycle state, enabling revocation governance and audit trails for multi-step agent operations.</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-domain-authorized-issuer/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-mission/</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 4 Jul 2026. Implements one trust method for draft-mcguinness-oauth-id-assertion-framework. DNS-based approach is lightweight and operationally familiar; the non-transitive design avoids the amplification risks of transitive trust chains. Closes the 'how do you know the AS is allowed to speak for this domain?' gap that cross-domain identity chaining has always assumed away.</t>
+          <t>Revision -00, 6 Jul 2026. This is the formal I-D target for the 'Mission-Bound OAuth MVP' blog post (May 2026, Industry tab) — the five-wire-addition protocol that makes the user-approved task a first-class OAuth object. Paired with the runtime enforcement profile (still not on Datatracker as of Jul 10). The Mission lifecycle (pending_approval → active → suspended → revoked → expired → completed → rejected) and the proposal_hash/consent_rendering_hash binding anchor what was approved versus what the user saw.</t>
         </is>
       </c>
     </row>
@@ -2125,17 +2125,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-mission — Mission-Bound Authorization for OAuth 2.0</t>
+          <t>draft-mishra-oauth-agent-grants — Delegated Agent Authorization Protocol (DAAP)</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Introduces 'Mission' — a durable, integrity-bound artifact stored at the AS representing an approved task; clients submit Mission Intent via PAR, ASes derive concrete permissions, and approvers grant consent via integrity anchors. Access tokens carry a 'mission' claim; issuance is gated by the Mission's lifecycle state, enabling revocation governance and audit trails for multi-step agent operations.</t>
+          <t>An IETF individual draft addressing runtime agent identity for dynamically-spawned agents, multi-agent sub-delegation with depth-limiting, and cascade revocation of an entire delegation subtree when any ancestor is revoked.</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-mission/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mishra-oauth-agent-grants/</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 6 Jul 2026. This is the formal I-D target for the 'Mission-Bound OAuth MVP' blog post (May 2026, Industry tab) — the five-wire-addition protocol that makes the user-approved task a first-class OAuth object. Paired with the runtime enforcement profile (still not on Datatracker as of Jul 10). The Mission lifecycle (pending_approval → active → suspended → revoked → expired → completed → rejected) and the proposal_hash/consent_rendering_hash binding anchor what was approved versus what the user saw.</t>
+          <t>Revision -01 (March 2026); registers new JWT claims (agt, dev, grnt, scp, bdg) — a more aggressive alternative to RFC 8693 with budget-bounded grants. Overlaps with draft-niyikiza-oauth-attenuating-agent-tokens; OAuth WG will likely expect consolidation.</t>
         </is>
       </c>
     </row>
@@ -2155,17 +2155,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>draft-mishra-oauth-agent-grants — Delegated Agent Authorization Protocol (DAAP)</t>
+          <t>draft-kuehlewind-audit-architecture — Architecture for Auditing AI Agent Delegation and Interactions</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft addressing runtime agent identity for dynamically-spawned agents, multi-agent sub-delegation with depth-limiting, and cascade revocation of an entire delegation subtree when any ancestor is revoked.</t>
+          <t>An IETF individual draft from Mirja Kühlewind (Ericsson, former IETF TSV-AD) and Henk Birkholz (Fraunhofer SIT, lead author of RFC 9334 RATS and SCITT architecture) defining four record types — Interaction, Action, Delegation, and Authorization Transition — and an Audit Context that propagates across OAuth + WIMSE + RATS + SCITT to make agent behaviour verifiably auditable end-to-end.</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mishra-oauth-agent-grants/</t>
+          <t>https://datatracker.ietf.org/doc/draft-kuehlewind-audit-architecture/</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Revision -01 (March 2026); registers new JWT claims (agt, dev, grnt, scp, bdg) — a more aggressive alternative to RFC 8693 with budget-bounded grants. Overlaps with draft-niyikiza-oauth-attenuating-agent-tokens; OAuth WG will likely expect consolidation.</t>
+          <t>Revision -00 published 18 May 2026; the cross-layer integration piece — explicitly composes the McGuinness Actor Profile, Transaction Tokens, identity-chaining, ID-JAG, WIMSE, RATS, and SCITT into a single auditable architecture with 11 proposed work items. The treats-Agent-as-untrusted threat model is what regulators (SOX, PSD2, EU AI Act) actually want.</t>
         </is>
       </c>
     </row>
@@ -2185,17 +2185,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>draft-kuehlewind-audit-architecture — Architecture for Auditing AI Agent Delegation and Interactions</t>
+          <t>draft-birkholz-verifiable-agent-conversations — Verifiable Agent Conversation Records</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft from Mirja Kühlewind (Ericsson, former IETF TSV-AD) and Henk Birkholz (Fraunhofer SIT, lead author of RFC 9334 RATS and SCITT architecture) defining four record types — Interaction, Action, Delegation, and Authorization Transition — and an Audit Context that propagates across OAuth + WIMSE + RATS + SCITT to make agent behaviour verifiably auditable end-to-end.</t>
+          <t>An IETF individual draft (Birkholz/Heldt/Steele) defining a CDDL data format — with both JSON and CBOR encodings — for tamper-evident, verifiably-signed records of agent conversations, agent reasoning traces, tool calls, and system events that support long-term evidentiary value across chains of custody.</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-kuehlewind-audit-architecture/</t>
+          <t>https://datatracker.ietf.org/doc/draft-birkholz-verifiable-agent-conversations/</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Revision -00 published 18 May 2026; the cross-layer integration piece — explicitly composes the McGuinness Actor Profile, Transaction Tokens, identity-chaining, ID-JAG, WIMSE, RATS, and SCITT into a single auditable architecture with 11 proposed work items. The treats-Agent-as-untrusted threat model is what regulators (SOX, PSD2, EU AI Act) actually want.</t>
+          <t>Revision -00 published 25 Feb 2026; presented at IETF 125 dispatch and hotrfc. The canonical Interaction-Record format for the Kuehlewind audit architecture. Motivating examples are concrete: agents acting beyond scope, CoT divergence, and 'sandbagging' during evaluations.</t>
         </is>
       </c>
     </row>
@@ -2215,17 +2215,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>draft-birkholz-verifiable-agent-conversations — Verifiable Agent Conversation Records</t>
+          <t>draft-klrc-aiagent-auth — AI Agent Authentication and Authorization</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft (Birkholz/Heldt/Steele) defining a CDDL data format — with both JSON and CBOR encodings — for tamper-evident, verifiably-signed records of agent conversations, agent reasoning traces, tool calls, and system events that support long-term evidentiary value across chains of custody.</t>
+          <t>An IETF individual draft that does not invent new protocols but composes WIMSE/SPIFFE workload identity, OAuth 2.x, and OpenID SSF to authenticate and delegate authority to AI agents.</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-birkholz-verifiable-agent-conversations/</t>
+          <t>https://datatracker.ietf.org/doc/html/draft-klrc-aiagent-auth-00</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Revision -00 published 25 Feb 2026; presented at IETF 125 dispatch and hotrfc. The canonical Interaction-Record format for the Kuehlewind audit architecture. Motivating examples are concrete: agents acting beyond scope, CoT divergence, and 'sandbagging' during evaluations.</t>
+          <t>Revision -03, 6 Jul 2026 (was -00, March 2026); introduces 'Agent Identity Management System (AIMS)' and is the cleanest standards-based framing of agent-as-workload.</t>
         </is>
       </c>
     </row>
@@ -2245,17 +2245,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>draft-klrc-aiagent-auth — AI Agent Authentication and Authorization</t>
+          <t>draft-niyikiza-oauth-attenuating-agent-tokens — Attenuating Authorization Tokens for Agentic Delegation Chains</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft that does not invent new protocols but composes WIMSE/SPIFFE workload identity, OAuth 2.x, and OpenID SSF to authenticate and delegate authority to AI agents.</t>
+          <t>An IETF individual draft extending RFC 9396 Rich Authorization Requests with monotonic attenuation at each delegation hop, offline chain verification, and a typed constraint vocabulary for tool-level argument restrictions.</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/html/draft-klrc-aiagent-auth-00</t>
+          <t>https://datatracker.ietf.org/doc/draft-niyikiza-oauth-attenuating-agent-tokens/</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, 6 Jul 2026 (was -00, March 2026); introduces 'Agent Identity Management System (AIMS)' and is the cleanest standards-based framing of agent-as-workload.</t>
+          <t>Revision -00, March 2026; arguably the strongest purely-OAuth-grounded delegation draft — offline verification is a key scalability property. Good path to OAuth WG adoption; overlaps with draft-mishra-oauth-agent-grants and will likely need to be consolidated with it.</t>
         </is>
       </c>
     </row>
@@ -2275,17 +2275,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>draft-niyikiza-oauth-attenuating-agent-tokens — Attenuating Authorization Tokens for Agentic Delegation Chains</t>
+          <t>draft-singla-agent-identity-protocol — AIP: Decentralized Identity and Delegation for AI Agents</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft extending RFC 9396 Rich Authorization Requests with monotonic attenuation at each delegation hop, offline chain verification, and a typed constraint vocabulary for tool-level argument restrictions.</t>
+          <t>An IETF individual draft proposing a six-layer model (identity through reputation) for AI agents with W3C DID anchoring, a Delegation Depth counter, three Grant ceremony tiers (G1/G2/G3), DPoP proof-of-possession, and an MCP integration layer.</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-niyikiza-oauth-attenuating-agent-tokens/</t>
+          <t>https://datatracker.ietf.org/doc/draft-singla-agent-identity-protocol/</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, March 2026; arguably the strongest purely-OAuth-grounded delegation draft — offline verification is a key scalability property. Good path to OAuth WG adoption; overlaps with draft-mishra-oauth-agent-grants and will likely need to be consolidated with it.</t>
+          <t>Revision -00, 17 April 2026; the most comprehensive identity framework in the set. The W3C DID dependency will face IETF pushback, the 75+ page scope needs reduction, and the 'AIP' name collision with two other drafts (draft-prakash-aip, draft-aip-agent-identity-protocol) must be resolved.</t>
         </is>
       </c>
     </row>
@@ -2305,17 +2305,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>draft-singla-agent-identity-protocol — AIP: Decentralized Identity and Delegation for AI Agents</t>
+          <t>draft-prakash-aip — AIP: Verifiable Delegation for AI Agent Systems</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft proposing a six-layer model (identity through reputation) for AI agents with W3C DID anchoring, a Delegation Depth counter, three Grant ceremony tiers (G1/G2/G3), DPoP proof-of-possession, and an MCP integration layer.</t>
+          <t>An IETF individual draft introducing Invocation-Bound Capability Tokens (IBCTs) in two modes — compact (JWT/Ed25519) for single-hop and chained (Biscuit + Datalog) for multi-hop — with bindings for MCP, A2A, and HTTP APIs.</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-singla-agent-identity-protocol/</t>
+          <t>https://datatracker.ietf.org/doc/draft-prakash-aip/</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 17 April 2026; the most comprehensive identity framework in the set. The W3C DID dependency will face IETF pushback, the 75+ page scope needs reduction, and the 'AIP' name collision with two other drafts (draft-prakash-aip, draft-aip-agent-identity-protocol) must be resolved.</t>
+          <t>Revision -01, 19 Aug 2026 (was -00, 27 March 2026); technically strong — Biscuit + Datalog is well-suited to scope attenuation. The 'AIP' name collision with draft-singla-agent-identity-protocol and draft-aip-agent-identity-protocol is a blocking issue for WG adoption.</t>
         </is>
       </c>
     </row>
@@ -2335,17 +2335,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>draft-prakash-aip — AIP: Verifiable Delegation for AI Agent Systems</t>
+          <t>draft-goswami-agentic-jwt — Secure Intent Protocol: JWT-Compatible Agentic Identity and Workflow Management</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft introducing Invocation-Bound Capability Tokens (IBCTs) in two modes — compact (JWT/Ed25519) for single-hop and chained (Biscuit + Datalog) for multi-hop — with bindings for MCP, A2A, and HTTP APIs.</t>
+          <t>An IETF individual draft defining an Agentic JWT extension to OAuth 2.0 with a Supervisor Agent role for sub-agent coordination, explicitly addressing the 'intent-execution separation' gap and adding workflow-step authorization.</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-prakash-aip/</t>
+          <t>https://datatracker.ietf.org/doc/draft-goswami-agentic-jwt/</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 19 Aug 2026 (was -00, 27 March 2026); technically strong — Biscuit + Datalog is well-suited to scope attenuation. The 'AIP' name collision with draft-singla-agent-identity-protocol and draft-aip-agent-identity-protocol is a blocking issue for WG adoption.</t>
+          <t>Revision -00, December 2025; the intent-execution-separation framing is insightful and distinguishing. The workflow-step authorization approach is novel but may face skepticism in the OAuth WG.</t>
         </is>
       </c>
     </row>
@@ -2365,17 +2365,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>draft-goswami-agentic-jwt — Secure Intent Protocol: JWT-Compatible Agentic Identity and Workflow Management</t>
+          <t>draft-ni-wimse-ai-agent-identity — WIMSE Applicability for AI Agents</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft defining an Agentic JWT extension to OAuth 2.0 with a Supervisor Agent role for sub-agent coordination, explicitly addressing the 'intent-execution separation' gap and adding workflow-step authorization.</t>
+          <t>An IETF individual draft mapping the WIMSE workload-identity architecture to AI-agent use cases and establishing credential-management mechanisms for agentic AI within the WIMSE framework.</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-goswami-agentic-jwt/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ni-wimse-ai-agent-identity/</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, December 2025; the intent-execution-separation framing is insightful and distinguishing. The workflow-step authorization approach is novel but may face skepticism in the OAuth WG.</t>
+          <t>Revision -02, February 2026; an important bridge between the WIMSE WG and the AI agent space. If an AI-agent WG is ever chartered, this applicability statement is essential groundwork. Co-authored with Liu, who also leads the related security-requirements draft.</t>
         </is>
       </c>
     </row>
@@ -2395,17 +2395,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>draft-ni-wimse-ai-agent-identity — WIMSE Applicability for AI Agents</t>
+          <t>draft-sharif-agent-identity-framework — Agent Identity Framework: Trust and Identity for Autonomous AI Agents</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft mapping the WIMSE workload-identity architecture to AI-agent use cases and establishing credential-management mechanisms for agentic AI within the WIMSE framework.</t>
+          <t>An IETF individual draft proposing a five-layer model (identity, authorization, attestation, evidence, trust) for autonomous AI agents, with a gap analysis between current Internet standards and agent requirements.</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ni-wimse-ai-agent-identity/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sharif-agent-identity-framework/</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, February 2026; an important bridge between the WIMSE WG and the AI agent space. If an AI-agent WG is ever chartered, this applicability statement is essential groundwork. Co-authored with Liu, who also leads the related security-requirements draft.</t>
+          <t>Revision -00, 6 April 2026; more gap-analysis than protocol spec. Useful as problem statement. Five-layer model is a reasonable decomposition but insufficient as a standalone contribution. Part of the Sharif cluster (with -agent-audit-trail, -attp, etc.).</t>
         </is>
       </c>
     </row>
@@ -2425,17 +2425,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>draft-sharif-agent-identity-framework — Agent Identity Framework: Trust and Identity for Autonomous AI Agents</t>
+          <t>draft-sharif-x509-agent-identity-profile — X.509 Certificate Profile for Autonomous AI Agent Identity</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft proposing a five-layer model (identity, authorization, attestation, evidence, trust) for autonomous AI agents, with a gap analysis between current Internet standards and agent requirements.</t>
+          <t>Defines a new X.509v3 AgentIdentity extension encoding graduated trust levels (0–4), operational capabilities, delegation constraints, and revocation endpoints for autonomous AI agent certificates. Maintains backward compatibility with standard X.509v3 parsers (extension marked non-critical) and integrates with SPIFFE workload identity frameworks.</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sharif-agent-identity-framework/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sharif-x509-agent-identity-profile/</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 6 April 2026; more gap-analysis than protocol spec. Useful as problem statement. Five-layer model is a reasonable decomposition but insufficient as a standalone contribution. Part of the Sharif cluster (with -agent-audit-trail, -attp, etc.).</t>
+          <t>Revision -03, 31 Jul 2026 (was -02, Jul 26 2026 (first filed Jul 20 2026)); part of the Sharif cluster. Fills the PKI-layer identity gap that draft-ietf-wimse-workload-creds left open — workload-creds specifies credential issuance, this profiles X.509v3 for the agent-specific certificate case. Graduated trust taxonomy (0–4) and kill-switch revocation are referenced by draft-sweeney-wimse-credential-delegation.</t>
         </is>
       </c>
     </row>
@@ -2455,17 +2455,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>draft-sharif-x509-agent-identity-profile — X.509 Certificate Profile for Autonomous AI Agent Identity</t>
+          <t>draft-aip-agent-identity-protocol — AIP: Agentic Authentication and Authorized Policy Enforcement</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Defines a new X.509v3 AgentIdentity extension encoding graduated trust levels (0–4), operational capabilities, delegation constraints, and revocation endpoints for autonomous AI agent certificates. Maintains backward compatibility with standard X.509v3 parsers (extension marked non-critical) and integrates with SPIFFE workload identity frameworks.</t>
+          <t>An IETF individual draft defining an AIP Token signed per tool call (agent ID, tool, nonce, timestamp, signature), an AgentPolicy YAML format for per-tool argument constraints and DLP rules, and a Human-in-the-Loop proxy enforcement model.</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sharif-x509-agent-identity-profile/</t>
+          <t>https://datatracker.ietf.org/doc/draft-aip-agent-identity-protocol/</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, 31 Jul 2026 (was -02, Jul 26 2026 (first filed Jul 20 2026)); part of the Sharif cluster. Fills the PKI-layer identity gap that draft-ietf-wimse-workload-creds left open — workload-creds specifies credential issuance, this profiles X.509v3 for the agent-specific certificate case. Graduated trust taxonomy (0–4) and kill-switch revocation are referenced by draft-sweeney-wimse-credential-delegation.</t>
+          <t>Revision -00, 16 March 2026; implementation-focused. YAML policy approach is pragmatic but not interoperable-by-design. HITL integration is a valuable safety feature. Third member of the 'AIP' name-collision triple — must be resolved before any can progress.</t>
         </is>
       </c>
     </row>
@@ -2485,17 +2485,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>draft-aip-agent-identity-protocol — AIP: Agentic Authentication and Authorized Policy Enforcement</t>
+          <t>draft-liu-oauth-chain-delegation — Delegation Chain for OAuth 2.0</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft defining an AIP Token signed per tool call (agent ID, tool, nonce, timestamp, signature), an AgentPolicy YAML format for per-tool argument constraints and DLP rules, and a Human-in-the-Loop proxy enforcement model.</t>
+          <t>Introduces a delegation_chain JWT claim as a structured companion to RFC 8693's act claim; delegation_chain records the complete delegation history as an ordered array with per-hop authorization constraints and optional cryptographic confirmation from each delegating agent. Supports cross-domain delegation with integrated user consent interaction.</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-aip-agent-identity-protocol/</t>
+          <t>https://datatracker.ietf.org/doc/draft-liu-oauth-chain-delegation/</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 16 March 2026; implementation-focused. YAML policy approach is pragmatic but not interoperable-by-design. HITL integration is a valuable safety feature. Third member of the 'AIP' name-collision triple — must be resolved before any can progress.</t>
+          <t>Revision -00, 6 Jun 2026; authors: Dapeng Liu, Judy Zhu, Suresh Krishnan (Ericsson), Aaron Parecki (Okta). Provides the structured delegation lineage that act alone cannot express; strong overlap with draft-mw-oauth-actor-chain and draft-niyikiza-oauth-attenuating-agent-tokens — OAuth WG will likely expect consolidation across these three.</t>
         </is>
       </c>
     </row>
@@ -2515,17 +2515,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>draft-liu-oauth-chain-delegation — Delegation Chain for OAuth 2.0</t>
+          <t>draft-fletcher-transaction-token-chaining-profile — Transaction Token Authorization Grant Profile for OAuth Identity and Authorization Chaining</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Introduces a delegation_chain JWT claim as a structured companion to RFC 8693's act claim; delegation_chain records the complete delegation history as an ordered array with per-hop authorization constraints and optional cryptographic confirmation from each delegating agent. Supports cross-domain delegation with integrated user consent interaction.</t>
+          <t>Establishes a framework for using Transaction Tokens as subject credentials in OAuth 2.0 Token Exchange requests (RFC 8693), enabling services within one trust domain to obtain JWT authorization grants for accessing resources across domain boundaries without exposing internal token formats.</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-liu-oauth-chain-delegation/</t>
+          <t>https://datatracker.ietf.org/doc/draft-fletcher-transaction-token-chaining-profile/</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 6 Jun 2026; authors: Dapeng Liu, Judy Zhu, Suresh Krishnan (Ericsson), Aaron Parecki (Okta). Provides the structured delegation lineage that act alone cannot express; strong overlap with draft-mw-oauth-actor-chain and draft-niyikiza-oauth-attenuating-agent-tokens — OAuth WG will likely expect consolidation across these three.</t>
+          <t>Revision -02, 6 Jul 2026 (was -01 Jun 2026); authors: George Fletcher (Practical Identity LLC), Pieter Kasselman (Defakto Security), Sean O'Dell (CVS Health). Directly bridges draft-ietf-oauth-transaction-tokens and draft-ietf-oauth-identity-chaining (both in corpus), closing the 'how do TX Tokens actually cross domains' gap. Note: lead author is the corpus maintainer.</t>
         </is>
       </c>
     </row>
@@ -2545,17 +2545,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>draft-fletcher-transaction-token-chaining-profile — Transaction Token Authorization Grant Profile for OAuth Identity and Authorization Chaining</t>
+          <t>draft-zhu-oauth-async-delegation — Sender-Constrained Delegation Handle for Asynchronous OAuth 2.0 Identity Chaining</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Establishes a framework for using Transaction Tokens as subject credentials in OAuth 2.0 Token Exchange requests (RFC 8693), enabling services within one trust domain to obtain JWT authorization grants for accessing resources across domain boundaries without exposing internal token formats.</t>
+          <t>Introduces a Delegation Handle — a sender-constrained, audience-locked JWT issued by authorization servers — enabling acting clients to refresh chained access tokens without re-prompting an offline end user while maintaining strict policy bounds and identity chains.</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-fletcher-transaction-token-chaining-profile/</t>
+          <t>https://datatracker.ietf.org/doc/draft-zhu-oauth-async-delegation/</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 6 Jul 2026 (was -01 Jun 2026); authors: George Fletcher (Practical Identity LLC), Pieter Kasselman (Defakto Security), Sean O'Dell (CVS Health). Directly bridges draft-ietf-oauth-transaction-tokens and draft-ietf-oauth-identity-chaining (both in corpus), closing the 'how do TX Tokens actually cross domains' gap. Note: lead author is the corpus maintainer.</t>
+          <t>Revision -05, 3 Aug 2026 (was -04, Jul 23 2026 (first filed -00, 22 May 2026)); authors: Larry Zhu, Sam Currie (Atlassian). Addresses a concrete gap in agent delegation: what happens when the delegating human is not present to re-authorize. Directly relevant to long-running agentic workflows using draft-ietf-oauth-identity-chaining. Active revision pace — -04 within ~2 months of initial filing.</t>
         </is>
       </c>
     </row>
@@ -2575,17 +2575,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>draft-zhu-oauth-async-delegation — Sender-Constrained Delegation Handle for Asynchronous OAuth 2.0 Identity Chaining</t>
+          <t>draft-emerson-oauth-user-mediated-delivery — User-Mediated Credential Delivery for AI Agents</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Introduces a Delegation Handle — a sender-constrained, audience-locked JWT issued by authorization servers — enabling acting clients to refresh chained access tokens without re-prompting an offline end user while maintaining strict policy bounds and identity chains.</t>
+          <t>Proposes user-mediated credential delivery as a complementary OAuth authorization primitive for AI agent frameworks: rather than delivering credentials through automated channels controlled by the agent or its platform, places the authorization decision and credential delivery step in the user's hands even when the agent is autonomous.</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-zhu-oauth-async-delegation/</t>
+          <t>https://datatracker.ietf.org/doc/draft-emerson-oauth-user-mediated-delivery/</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Revision -05, 3 Aug 2026 (was -04, Jul 23 2026 (first filed -00, 22 May 2026)); authors: Larry Zhu, Sam Currie (Atlassian). Addresses a concrete gap in agent delegation: what happens when the delegating human is not present to re-authorize. Directly relevant to long-running agentic workflows using draft-ietf-oauth-identity-chaining. Active revision pace — -04 within ~2 months of initial filing.</t>
+          <t>Revision -00, Jul 2026; author: Matt Emerson. Novel complement to draft-zhu-oauth-async-delegation — where Zhu handles the case of offline delegation continuation, Emerson argues some credential deliveries should always route through the user even in automated pipelines. Addresses prompt-injection and social-engineering risks in agent credential chains.</t>
         </is>
       </c>
     </row>
@@ -2605,17 +2605,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>draft-emerson-oauth-user-mediated-delivery — User-Mediated Credential Delivery for AI Agents</t>
+          <t>draft-gerber-oauth-deferred-token-response — Deferred Token Response</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Proposes user-mediated credential delivery as a complementary OAuth authorization primitive for AI agent frameworks: rather than delivering credentials through automated channels controlled by the agent or its platform, places the authorization decision and credential delivery step in the user's hands even when the agent is autonomous.</t>
+          <t>Defines an OAuth 2.1 extension enabling authorization servers to defer access-token issuance by returning a deferral code the client polls or receives via callback; designed for use cases including fraud review, identity verification, autonomous agent approvals, and enterprise governance workflows where immediate token issuance is not appropriate.</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-emerson-oauth-user-mediated-delivery/</t>
+          <t>https://datatracker.ietf.org/doc/draft-gerber-oauth-deferred-token-response/</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, Jul 2026; author: Matt Emerson. Novel complement to draft-zhu-oauth-async-delegation — where Zhu handles the case of offline delegation continuation, Emerson argues some credential deliveries should always route through the user even in automated pipelines. Addresses prompt-injection and social-engineering risks in agent credential chains.</t>
+          <t>Revision -00, Jun 23 2026; presented at IETF 126 OAuth WG. May be the closest current Datatracker analog to the still-pending draft-mcguinness-oauth-deferred-code-processing — note in comments if the McGuinness variant eventually files, as the two may need consolidation. The async issuance pattern directly enables human-approval workflows in agentic pipelines without requiring the agent to remain connected while awaiting the authorization decision.</t>
         </is>
       </c>
     </row>
@@ -2635,17 +2635,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>draft-gerber-oauth-deferred-token-response — Deferred Token Response</t>
+          <t>draft-chen-oauth-agent-revocation — OAuth 2.0 Agent Authorization Explicit Revocation</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Defines an OAuth 2.1 extension enabling authorization servers to defer access-token issuance by returning a deferral code the client polls or receives via callback; designed for use cases including fraud review, identity verification, autonomous agent approvals, and enterprise governance workflows where immediate token issuance is not appropriate.</t>
+          <t>Extends RFC 7009 token revocation for agent-based scenarios: introduces batch revocation by agent ID, cascading revocation across delegation chains, conditional revocation options, and verifiable audit trails.</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-gerber-oauth-deferred-token-response/</t>
+          <t>https://datatracker.ietf.org/doc/draft-chen-oauth-agent-revocation/</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, Jun 23 2026; presented at IETF 126 OAuth WG. May be the closest current Datatracker analog to the still-pending draft-mcguinness-oauth-deferred-code-processing — note in comments if the McGuinness variant eventually files, as the two may need consolidation. The async issuance pattern directly enables human-approval workflows in agentic pipelines without requiring the agent to remain connected while awaiting the authorization decision.</t>
+          <t>Revision -00, 27 Apr 2026; authors: Meiling Chen, Li Su (China Mobile). Fills the lifecycle management gap — existing RFC 7009 revocation is single-token and client-centric, but agent delegation chains require cascade semantics. Natural companion to draft-ietf-oauth-transaction-tokens and draft-niyikiza-oauth-attenuating-agent-tokens.</t>
         </is>
       </c>
     </row>
@@ -2665,17 +2665,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>draft-chen-oauth-agent-revocation — OAuth 2.0 Agent Authorization Explicit Revocation</t>
+          <t>draft-jiang-oauth-intent-admission — Intent Admission Assertions for Agentic Systems</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Extends RFC 7009 token revocation for agent-based scenarios: introduces batch revocation by agent ID, cascading revocation across delegation chains, conditional revocation options, and verifiable audit trails.</t>
+          <t>Defines a signed, verifiable Intent Admission Assertion (IAA) that an admission point creates after verifying agent identity, evaluating permissions against policy, and — when required — obtaining explicit user consent; the IAA is transmitted to the execution endpoint which re-validates before proceeding. Leverages OAuth and RFC 9396 Rich Authorization Requests.</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-chen-oauth-agent-revocation/</t>
+          <t>https://datatracker.ietf.org/doc/draft-jiang-oauth-intent-admission/</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 27 Apr 2026; authors: Meiling Chen, Li Su (China Mobile). Fills the lifecycle management gap — existing RFC 7009 revocation is single-token and client-centric, but agent delegation chains require cascade semantics. Natural companion to draft-ietf-oauth-transaction-tokens and draft-niyikiza-oauth-attenuating-agent-tokens.</t>
+          <t>Revision -00, 23 Jun 2026; authors: Yuning Jiang, Lun Li, Yurong Song, Faye Liu (Huawei). The required_consent path maps directly to the HITL pattern central to the corpus. Companion to draft-jiang-intent-security (threat model) from the same Huawei group.</t>
         </is>
       </c>
     </row>
@@ -2695,17 +2695,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>draft-jiang-oauth-intent-admission — Intent Admission Assertions for Agentic Systems</t>
+          <t>draft-ni-oauth-batch-authorization-delegation — Batch Authorization Delegation</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Defines a signed, verifiable Intent Admission Assertion (IAA) that an admission point creates after verifying agent identity, evaluating permissions against policy, and — when required — obtaining explicit user consent; the IAA is transmitted to the execution endpoint which re-validates before proceeding. Leverages OAuth and RFC 9396 Rich Authorization Requests.</t>
+          <t>Defines a mechanism for delegating a batch of fine-grained, actor-bound permissions in a single request across multiple collaborating actors; uses RFC 9396 RAR to carry per-actor authorization_details and RFC 8693 Token Exchange for sub-agent delegation, targeting multi-agent orchestration where a leader-agent receives batch permissions and delegates subsets to sub-agents.</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-jiang-oauth-intent-admission/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ni-oauth-batch-authorization-delegation/</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 23 Jun 2026; authors: Yuning Jiang, Lun Li, Yurong Song, Faye Liu (Huawei). The required_consent path maps directly to the HITL pattern central to the corpus. Companion to draft-jiang-intent-security (threat model) from the same Huawei group.</t>
+          <t>Revision -00, 3 Jul 2026; authors: Ni Yuan, Peter Chunchi Liu (Huawei). Addresses the round-trip overhead problem in large-scale multi-agent orchestration — individual delegation exchanges per sub-agent don't scale. Complements draft-song-oauth-ai-agent-collaborate-authz (same Huawei group, coordination focus) and draft-niyikiza-oauth-attenuating-agent-tokens (attenuation semantics). The RAR-based batch approach aligns well with the OAuth WG's RAR investment. **SUPERSEDES draft-ni-batch-authorization-delegation**, which Datatracker marks Replaced by this draft. That older row was removed from the corpus on 26 Aug 2026 — it was tracked separately and had become a duplicate of this one under the pre-rename slug.</t>
         </is>
       </c>
     </row>
@@ -2725,17 +2725,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>draft-ni-oauth-batch-authorization-delegation — Batch Authorization Delegation</t>
+          <t>draft-liu-oauth-a2a-profile — Agent-to-Agent (A2A) Profile for OAuth Transaction Tokens</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Defines a mechanism for delegating a batch of fine-grained, actor-bound permissions in a single request across multiple collaborating actors; uses RFC 9396 RAR to carry per-actor authorization_details and RFC 8693 Token Exchange for sub-agent delegation, targeting multi-agent orchestration where a leader-agent receives batch permissions and delegates subsets to sub-agents.</t>
+          <t>Defines a profile for using OAuth Transaction Tokens in distributed agent-to-agent communication scenarios; specifies mechanisms for embedding call-chain context within tokens to preserve agent identity, authorization information, and operational flow across agent workloads in trusted environments.</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ni-oauth-batch-authorization-delegation/</t>
+          <t>https://datatracker.ietf.org/doc/draft-liu-oauth-a2a-profile/</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 3 Jul 2026; authors: Ni Yuan, Peter Chunchi Liu (Huawei). Addresses the round-trip overhead problem in large-scale multi-agent orchestration — individual delegation exchanges per sub-agent don't scale. Complements draft-song-oauth-ai-agent-collaborate-authz (same Huawei group, coordination focus) and draft-niyikiza-oauth-attenuating-agent-tokens (attenuation semantics). The RAR-based batch approach aligns well with the OAuth WG's RAR investment.</t>
+          <t>EXPIRED. Revision -00, Oct 2025; authors: Peter Chunchi Liu, Ni Yuan (Huawei) — same author pair as draft-ni-oauth-batch-authorization-delegation. Directly profiles draft-ietf-oauth-transaction-tokens for A2A use; overlaps significantly with draft-araut-oauth-transaction-tokens-for-agents. Never revised; likely deferred rather than abandoned given both authors remain active in the corpus through Jul 2026.</t>
         </is>
       </c>
     </row>
@@ -2755,17 +2755,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>draft-liu-oauth-a2a-profile — Agent-to-Agent (A2A) Profile for OAuth Transaction Tokens</t>
+          <t>draft-song-oauth-ai-agent-collaborate-authz — OAuth 2.0 Extension for Multi-AI Agent Collaboration</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Defines a profile for using OAuth Transaction Tokens in distributed agent-to-agent communication scenarios; specifies mechanisms for embedding call-chain context within tokens to preserve agent identity, authorization information, and operational flow across agent workloads in trusted environments.</t>
+          <t>Extends OAuth 2.0 for coordinated multi-agent task groups: defines a collaborative authorization flow allowing a lead agent to obtain delegation tokens for sub-agents, with shared task context, coordinated scope attenuation, and cross-agent session binding.</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-liu-oauth-a2a-profile/</t>
+          <t>https://datatracker.ietf.org/doc/draft-song-oauth-ai-agent-collaborate-authz/</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>EXPIRED. Revision -00, Oct 2025; authors: Peter Chunchi Liu, Ni Yuan (Huawei) — same author pair as draft-ni-oauth-batch-authorization-delegation. Directly profiles draft-ietf-oauth-transaction-tokens for A2A use; overlaps significantly with draft-araut-oauth-transaction-tokens-for-agents. Never revised; likely deferred rather than abandoned given both authors remain active in the corpus through Jul 2026.</t>
+          <t>Revision -02, Jun/Jul 2026; authors: Yurong Song (Huawei) and colleagues. Addresses the multi-agent coordination gap at the OAuth layer — complements draft-jiang-oauth-intent-admission from the same Huawei group. Distinct from single-hop delegation drafts in explicitly modeling lead-agent-to-sub-agent scope sharing.</t>
         </is>
       </c>
     </row>
@@ -2785,17 +2785,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>draft-song-oauth-ai-agent-collaborate-authz — OAuth 2.0 Extension for Multi-AI Agent Collaboration</t>
+          <t>draft-kroehl-agentic-trust-aae — Agent Authorization Envelope (AAE)</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Extends OAuth 2.0 for coordinated multi-agent task groups: defines a collaborative authorization flow allowing a lead agent to obtain delegation tokens for sub-agents, with shared task context, coordinated scope attenuation, and cross-agent session binding.</t>
+          <t>Specifies the AAE, a structured authorization container with three mandatory components — MANDATE, CONSTRAINTS, and VALIDITY — providing a machine-evaluable, cryptographically verifiable authorization assertion using W3C DIDs and Verifiable Credentials.</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-song-oauth-ai-agent-collaborate-authz/</t>
+          <t>https://datatracker.ietf.org/doc/draft-kroehl-agentic-trust-aae/</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, Jun/Jul 2026; authors: Yurong Song (Huawei) and colleagues. Addresses the multi-agent coordination gap at the OAuth layer — complements draft-jiang-oauth-intent-admission from the same Huawei group. Distinct from single-hop delegation drafts in explicitly modeling lead-agent-to-sub-agent scope sharing.</t>
+          <t>Revision -01, 11 Aug 2026 (was -00, 21 May 2026); author: Lars Kersten Kroehl (CryptoKRI GmbH). Occupies similar design space to draft-mcguinness-oauth-actor-profile but uses a DID/VC substrate rather than OAuth — provides a useful alternative approach for non-OAuth deployments.</t>
         </is>
       </c>
     </row>
@@ -2815,17 +2815,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>draft-kroehl-agentic-trust-aae — Agent Authorization Envelope (AAE)</t>
+          <t>draft-pidlisnyi-aps — Agent Passport System (APS)</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Specifies the AAE, a structured authorization container with three mandatory components — MANDATE, CONSTRAINTS, and VALIDITY — providing a machine-evaluable, cryptographically verifiable authorization assertion using W3C DIDs and Verifiable Credentials.</t>
+          <t>Specifies Ed25519-based agent passports, scoped delegation chains with constraints across seven dimensions (a lattice model where delegation monotonically narrows capabilities), cascade revocation, a three-signature policy chain, signed receipts, and MCP bindings; includes reference implementations in TypeScript and Python.</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-kroehl-agentic-trust-aae/</t>
+          <t>https://datatracker.ietf.org/doc/draft-pidlisnyi-aps/</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 11 Aug 2026 (was -00, 21 May 2026); author: Lars Kersten Kroehl (CryptoKRI GmbH). Occupies similar design space to draft-mcguinness-oauth-actor-profile but uses a DID/VC substrate rather than OAuth — provides a useful alternative approach for non-OAuth deployments.</t>
+          <t>Revision -01, 14 May 2026; author: Tymofii Pidlisnyi (AEOESS). Among the most comprehensive standalone agent authz specs in the wave — the seven-dimension constraint lattice and MCP binding make it directly implementable against Model Context Protocol deployments alongside draft-serra-mcp-discovery-uri.</t>
         </is>
       </c>
     </row>
@@ -2845,17 +2845,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>draft-pidlisnyi-aps — Agent Passport System (APS)</t>
+          <t>draft-serra-mcp-discovery-uri — The mcp URI Scheme and MCP Server Discovery Mechanism</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Specifies Ed25519-based agent passports, scoped delegation chains with constraints across seven dimensions (a lattice model where delegation monotonically narrows capabilities), cascade revocation, a three-signature policy chain, signed receipts, and MCP bindings; includes reference implementations in TypeScript and Python.</t>
+          <t>An IETF individual draft defining an 'mcp://' URI scheme combined with /.well-known/mcp-server (RFC 8615) and a DNS TXT fallback for discovery of Model Context Protocol servers.</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-pidlisnyi-aps/</t>
+          <t>https://datatracker.ietf.org/doc/draft-serra-mcp-discovery-uri/</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 14 May 2026; author: Tymofii Pidlisnyi (AEOESS). Among the most comprehensive standalone agent authz specs in the wave — the seven-dimension constraint lattice and MCP binding make it directly implementable against Model Context Protocol deployments alongside draft-serra-mcp-discovery-uri.</t>
+          <t>Already at revision -04 (March 2026), suggesting active iteration; narrow scope, clean design, and the strongest IANA-registration candidate in the set. OAuth 2.1 for auth is deliberately out of scope.</t>
         </is>
       </c>
     </row>
@@ -2875,17 +2875,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>draft-serra-mcp-discovery-uri — The mcp URI Scheme and MCP Server Discovery Mechanism</t>
+          <t>draft-sharif-attp — ATTP: Agent Trust Transport Protocol</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft defining an 'mcp://' URI scheme combined with /.well-known/mcp-server (RFC 8615) and a DNS TXT fallback for discovery of Model Context Protocol servers.</t>
+          <t>An IETF individual draft defining trust levels L0–L4 mapped to PSD2 Strong Customer Authentication requirements, with bindings for MCP (MCPS), REST, A2A, gRPC, and GraphQL; supersedes draft-sharif-agent-payment-trust.</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-serra-mcp-discovery-uri/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sharif-attp/</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Already at revision -04 (March 2026), suggesting active iteration; narrow scope, clean design, and the strongest IANA-registration candidate in the set. OAuth 2.1 for auth is deliberately out of scope.</t>
+          <t>Revision -01, 3 Jun 2026 (was -00, April 2026); regulatory mapping appendices (PSD2, PCI DSS) are notable — one of the few drafts engaging financial regulation directly. Ambitious scope. Part of the Sharif cluster.</t>
         </is>
       </c>
     </row>
@@ -2905,17 +2905,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>draft-sharif-attp — ATTP: Agent Trust Transport Protocol</t>
+          <t>draft-sharif-agent-transport-protocol — Agent Transport Protocol (ATP): Async Store-and-Forward for AI Agents</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft defining trust levels L0–L4 mapped to PSD2 Strong Customer Authentication requirements, with bindings for MCP (MCPS), REST, A2A, gRPC, and GraphQL; supersedes draft-sharif-agent-payment-trust.</t>
+          <t>An IETF individual draft defining async store-and-forward messaging semantics with cryptographic identity per relay hop, trust scoring at ingress, capability negotiation, and interop with Google A2A, MCP, and FIPA ACL; transport-agnostic over TCP/TLS/QUIC.</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sharif-attp/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sharif-agent-transport-protocol/</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 3 Jun 2026 (was -00, April 2026); regulatory mapping appendices (PSD2, PCI DSS) are notable — one of the few drafts engaging financial regulation directly. Ambitious scope. Part of the Sharif cluster.</t>
+          <t>Revision -00, 28 March 2026; addresses a real gap — most agent protocols assume synchronous availability, and store-and-forward is appropriate for long-running agentic tasks. Scope is broad and needs narrowing.</t>
         </is>
       </c>
     </row>
@@ -2935,17 +2935,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>draft-sharif-agent-transport-protocol — Agent Transport Protocol (ATP): Async Store-and-Forward for AI Agents</t>
+          <t>draft-sharif-agent-audit-trail — Agent Audit Trail (AAT): Standard Logging Format for Autonomous AI Systems</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft defining async store-and-forward messaging semantics with cryptographic identity per relay hop, trust scoring at ingress, capability negotiation, and interop with Google A2A, MCP, and FIPA ACL; transport-agnostic over TCP/TLS/QUIC.</t>
+          <t>An IETF individual draft defining a JSON-based audit record with mandatory fields (agent identity, action classification, outcome tracking, trust level) using RFC 8785 JSON Canonicalization and RFC 9562 UUIDs.</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sharif-agent-transport-protocol/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sharif-agent-audit-trail/</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 28 March 2026; addresses a real gap — most agent protocols assume synchronous availability, and store-and-forward is appropriate for long-running agentic tasks. Scope is broad and needs narrowing.</t>
+          <t>Revision -01, 19 Aug 2026 (was -00, 29 March 2026); orthogonal to delegation but important for compliance — standardized audit-log format is a genuine gap. Complements identity frameworks well. A sibling/alternative to the Kuehlewind audit architecture which takes a far more ambitious cross-layer approach.</t>
         </is>
       </c>
     </row>
@@ -2965,17 +2965,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>draft-sharif-agent-audit-trail — Agent Audit Trail (AAT): Standard Logging Format for Autonomous AI Systems</t>
+          <t>draft-aiendpoint-ai-discovery — The AI Discovery Endpoint</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft defining a JSON-based audit record with mandatory fields (agent identity, action classification, outcome tracking, trust level) using RFC 8785 JSON Canonicalization and RFC 9562 UUIDs.</t>
+          <t>An IETF individual draft defining a /.well-known/ai URI suffix for programmatic service capability discovery by AI agents — letting agents discover what an endpoint supports without having to parse human-oriented documentation; requests IANA well-known URI registration.</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sharif-agent-audit-trail/</t>
+          <t>https://datatracker.ietf.org/doc/draft-aiendpoint-ai-discovery/</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 19 Aug 2026 (was -00, 29 March 2026); orthogonal to delegation but important for compliance — standardized audit-log format is a genuine gap. Complements identity frameworks well. A sibling/alternative to the Kuehlewind audit architecture which takes a far more ambitious cross-layer approach.</t>
+          <t>Revision -01, 28 Jul 2026 (was -00, March 2026); complementary to MCP discovery but broader (not MCP-specific). Needs differentiation from OpenAPI/service-description work to gain traction.</t>
         </is>
       </c>
     </row>
@@ -2995,17 +2995,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>draft-aiendpoint-ai-discovery — The AI Discovery Endpoint</t>
+          <t>draft-hood-independent-agtp — Agent Transfer Protocol (AGTP)</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft defining a /.well-known/ai URI suffix for programmatic service capability discovery by AI agents — letting agents discover what an endpoint supports without having to parse human-oriented documentation; requests IANA well-known URI registration.</t>
+          <t>An IETF individual draft proposing a dedicated application-layer protocol for AI agent traffic on port 4480 (TCP/TLS and QUIC) with an agtp:// URI scheme, arguing that HTTP is insufficient because agent-generated intent-driven traffic is indistinguishable from human-initiated requests. Defines a Runtime Contract Negotiation Substrate (RCNS) with eighteen methods split into cognitive verbs (QUERY, DISCOVER, DESCRIBE, SUMMARIZE, PLAN, PROPOSE) and mechanics verbs (EXECUTE, DELEGATE, ESCALATE, CONFIRM, SUSPEND, NOTIFY), mandatory agent identity headers, and protocol-level authority scope declaration.</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-aiendpoint-ai-discovery/</t>
+          <t>https://datatracker.ietf.org/doc/draft-hood-independent-agtp/</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 28 Jul 2026 (was -00, March 2026); complementary to MCP discovery but broader (not MCP-specific). Needs differentiation from OpenAPI/service-description work to gain traction.</t>
+          <t>Revision -09, 28 Jun 2026 (was -08 May 2026); supersedes draft-hood-independent-atp. Companion specs in the same family: AGTP-API, AGTP-CERT, AGTP-MERCHANT, AGTP-IDENTIFIERS, AGTP-TRUST. Mandatory TLS 1.3+. Ambitious scope — a new transport layer rather than an HTTP profile. The cognitive/mechanics verb split is a distinctive design choice; contrasts with draft-sharif-agent-transport-protocol which layers async store-and-forward on top of existing transports rather than replacing them.</t>
         </is>
       </c>
     </row>
@@ -3025,17 +3025,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>draft-hood-independent-agtp — Agent Transfer Protocol (AGTP)</t>
+          <t>draft-hood-agtp-ard — ARD Binding for AGTP: Agentic Resource Discovery over the Agent Transfer Protocol</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft proposing a dedicated application-layer protocol for AI agent traffic on port 4480 (TCP/TLS and QUIC) with an agtp:// URI scheme, arguing that HTTP is insufficient because agent-generated intent-driven traffic is indistinguishable from human-initiated requests. Defines a Runtime Contract Negotiation Substrate (RCNS) with eighteen methods split into cognitive verbs (QUERY, DISCOVER, DESCRIBE, SUMMARIZE, PLAN, PROPOSE) and mechanics verbs (EXECUTE, DELEGATE, ESCALATE, CONFIRM, SUSPEND, NOTIFY), mandatory agent identity headers, and protocol-level authority scope declaration.</t>
+          <t>Specifies how Agentic Resource Discovery (ARD) composes with AGTP, defining a catalog entry type for ARD manifests, aligning AGTP's identity model with ARD's trustManifest, and providing an AGTP-native binding for publishing ARD catalogs over AGTP substrate rather than HTTPS.</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-hood-independent-agtp/</t>
+          <t>https://datatracker.ietf.org/doc/draft-hood-agtp-ard/</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Revision -09, 28 Jun 2026 (was -08 May 2026); supersedes draft-hood-independent-atp. Companion specs in the same family: AGTP-API, AGTP-CERT, AGTP-MERCHANT, AGTP-IDENTIFIERS, AGTP-TRUST. Mandatory TLS 1.3+. Ambitious scope — a new transport layer rather than an HTTP profile. The cognitive/mechanics verb split is a distinctive design choice; contrasts with draft-sharif-agent-transport-protocol which layers async store-and-forward on top of existing transports rather than replacing them.</t>
+          <t>Revision -00, 18 Jun 2026; author: Chris Hood (Nomotic). Extends the AGTP family (draft-hood-independent-agtp in corpus). The trustManifest identity alignment is the piece relevant to the agent identity thread; the rest is transport-layer plumbing for AGTP deployments.</t>
         </is>
       </c>
     </row>
@@ -3055,17 +3055,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>draft-hood-agtp-ard — ARD Binding for AGTP: Agentic Resource Discovery over the Agent Transfer Protocol</t>
+          <t>draft-hood-agtp-api — AGTP-API: Verbs, Paths, Endpoints, and Synthesis</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Specifies how Agentic Resource Discovery (ARD) composes with AGTP, defining a catalog entry type for ARD manifests, aligning AGTP's identity model with ARD's trustManifest, and providing an AGTP-native binding for publishing ARD catalogs over AGTP substrate rather than HTTPS.</t>
+          <t>Establishes the full application-layer contract for AGTP agent–server interactions: approved method catalog, path grammar, endpoint primitives, semantic metadata blocks, server manifests, and runtime contract negotiation substrate. Defines how agents and servers negotiate capabilities and authority before action methods are invoked.</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-hood-agtp-ard/</t>
+          <t>https://datatracker.ietf.org/doc/draft-hood-agtp-api/</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 18 Jun 2026; author: Chris Hood (Nomotic). Extends the AGTP family (draft-hood-independent-agtp in corpus). The trustManifest identity alignment is the piece relevant to the agent identity thread; the rest is transport-layer plumbing for AGTP deployments.</t>
+          <t>Revision -01, May 26 2026; author: Chris Hood (Nomotic). The normative protocol contract layer for AGTP, complementing draft-hood-independent-agtp (transport) and draft-hood-agtp-trust (trust model). The AGTP family now spans 18 drafts; this is the API-layer anchor.</t>
         </is>
       </c>
     </row>
@@ -3085,17 +3085,17 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>draft-hood-agtp-api — AGTP-API: Verbs, Paths, Endpoints, and Synthesis</t>
+          <t>draft-hood-agtp-trust — AGTP Trust and Verification Specification</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Establishes the full application-layer contract for AGTP agent–server interactions: approved method catalog, path grammar, endpoint primitives, semantic metadata blocks, server manifests, and runtime contract negotiation substrate. Defines how agents and servers negotiate capabilities and authority before action methods are invoked.</t>
+          <t>Defines AGTP's three-tier trust model (Tier 1 Verified / Tier 2 Org-Asserted / Tier 3 Experimental) and a continuous behavioral trust score (0.0–1.0) used by infrastructure components for runtime trust-aware routing. Standardizes the evidence substrate, score format, freshness requirements, and consumer-side evaluation rules without mandating the scoring algorithm.</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-hood-agtp-api/</t>
+          <t>https://datatracker.ietf.org/doc/draft-hood-agtp-trust/</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, May 26 2026; author: Chris Hood (Nomotic). The normative protocol contract layer for AGTP, complementing draft-hood-independent-agtp (transport) and draft-hood-agtp-trust (trust model). The AGTP family now spans 18 drafts; this is the API-layer anchor.</t>
+          <t>Revision -02, Jun 28 2026; author: Chris Hood (Nomotic). The continuous 0.0–1.0 trust score model contrasts with draft-sharif-attp's discrete L0–L4 levels and Larry Lewis's atp-core continuous scoring — three independent designs in the same design space.</t>
         </is>
       </c>
     </row>
@@ -3115,17 +3115,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>draft-hood-agtp-trust — AGTP Trust and Verification Specification</t>
+          <t>draft-hood-agtp-agent-cert — AGTP Agent Certificate Extension</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Defines AGTP's three-tier trust model (Tier 1 Verified / Tier 2 Org-Asserted / Tier 3 Experimental) and a continuous behavioral trust score (0.0–1.0) used by infrastructure components for runtime trust-aware routing. Standardizes the evidence substrate, score format, freshness requirements, and consumer-side evaluation rules without mandating the scoring algorithm.</t>
+          <t>Specifies an X.509 v3 extension that cryptographically binds AGTP agent identity headers to TLS mutual authentication, enabling infrastructure components (Scope-Enforcement Points, load balancers, governance gateways) to verify agent identity at the network layer without application-layer access. Includes session-level revocation via AGTP NOTIFY broadcast.</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-hood-agtp-trust/</t>
+          <t>https://datatracker.ietf.org/doc/draft-hood-agtp-agent-cert/</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, Jun 28 2026; author: Chris Hood (Nomotic). The continuous 0.0–1.0 trust score model contrasts with draft-sharif-attp's discrete L0–L4 levels and Larry Lewis's atp-core continuous scoring — three independent designs in the same design space.</t>
+          <t>Revision -03, Jun 28 2026; author: Chris Hood (Nomotic). The PKI-binding companion to the AGTP identity model; positions AGTP agent identity within existing X.509 / TLS infrastructure. Relevant to WebBotAuth comparison — both use PKI for bot/agent identity but at different layers.</t>
         </is>
       </c>
     </row>
@@ -3145,17 +3145,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>draft-hood-agtp-agent-cert — AGTP Agent Certificate Extension</t>
+          <t>draft-jernalczyk-intentweb-agent-manifest — IntentWeb AgentManifest</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Specifies an X.509 v3 extension that cryptographically binds AGTP agent identity headers to TLS mutual authentication, enabling infrastructure components (Scope-Enforcement Points, load balancers, governance gateways) to verify agent identity at the network layer without application-layer access. Includes session-level revocation via AGTP NOTIFY broadcast.</t>
+          <t>Defines a JSON document that websites publish to describe identity, trusted knowledge, agent-facing capabilities, structured bindings, risk levels, consent requirements, authentication expectations, audit rules, and policies — enabling AI agents to comprehend website functionality and safely perform actions without scraping or fragile UI automation.</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-hood-agtp-agent-cert/</t>
+          <t>https://datatracker.ietf.org/doc/draft-jernalczyk-intentweb-agent-manifest/</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, Jun 28 2026; author: Chris Hood (Nomotic). The PKI-binding companion to the AGTP identity model; positions AGTP agent identity within existing X.509 / TLS infrastructure. Relevant to WebBotAuth comparison — both use PKI for bot/agent identity but at different layers.</t>
+          <t>Revision -00, 6 Jul 2026; author: Mariusz Jernalczyk (IntentWeb). Website-side complement to agent identity drafts; sits in the Discovery &amp; Transport cluster alongside draft-hood-agtp-ard and the DAWN/.well-known discovery thread. Single author, no-affiliation submission — early stage but addresses a real discovery gap.</t>
         </is>
       </c>
     </row>
@@ -3175,17 +3175,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>draft-jernalczyk-intentweb-agent-manifest — IntentWeb AgentManifest</t>
+          <t>draft-bu-agentproto-security-principal-binding — Security Principal and Verifier Binding for Agent Communication Protocols</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Defines a JSON document that websites publish to describe identity, trusted knowledge, agent-facing capabilities, structured bindings, risk levels, consent requirements, authentication expectations, audit rules, and policies — enabling AI agents to comprehend website functionality and safely perform actions without scraping or fragile UI automation.</t>
+          <t>Addresses how agent communication protocols carry claims about user authority, agent instance identity, tool or external-resource identity, delegation state, session continuity, and action evidence; each claim has a different verifier, freshness requirement, failure mode, and security consequence, requiring explicit binding rather than collapsing all claims into a single assertion.</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-jernalczyk-intentweb-agent-manifest/</t>
+          <t>https://datatracker.ietf.org/doc/draft-bu-agentproto-security-principal-binding/</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 6 Jul 2026; author: Mariusz Jernalczyk (IntentWeb). Website-side complement to agent identity drafts; sits in the Discovery &amp; Transport cluster alongside draft-hood-agtp-ard and the DAWN/.well-known discovery thread. Single author, no-affiliation submission — early stage but addresses a real discovery gap.</t>
+          <t>Revision -06, 17 Aug 2026 (was -05, 9 Aug 2026) (was -02, Jul 2026). Fills a gap in the AGTP family (draft-hood-independent-agtp in corpus) and is relevant to any agent communication protocol carrying mixed-provenance claims. The verifier-separation model is the missing security architecture layer between protocol transport and authorization enforcement.</t>
         </is>
       </c>
     </row>
@@ -3205,17 +3205,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>draft-bu-agentproto-security-principal-binding — Security Principal and Verifier Binding for Agent Communication Protocols</t>
+          <t>draft-fane-opena2a-aap — OpenA2A Agent Authorization Protocol (AAP)</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Addresses how agent communication protocols carry claims about user authority, agent instance identity, tool or external-resource identity, delegation state, session continuity, and action evidence; each claim has a different verifier, freshness requirement, failure mode, and security consequence, requiring explicit binding rather than collapsing all claims into a single assertion.</t>
+          <t>Establishes authorization mechanisms for AI agent systems through cryptographic identity assertions and scoped capability grants. Introduces a broker layer that separates credentials from the agent's reasoning context, specifically to prevent prompt injection attacks from leaking authorization state while enabling cross-agent delegation.</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-bu-agentproto-security-principal-binding/</t>
+          <t>https://datatracker.ietf.org/doc/draft-fane-opena2a-aap/</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Revision -06, 17 Aug 2026 (was -05, 9 Aug 2026) (was -02, Jul 2026). Fills a gap in the AGTP family (draft-hood-independent-agtp in corpus) and is relevant to any agent communication protocol carrying mixed-provenance claims. The verifier-separation model is the missing security architecture layer between protocol transport and authorization enforcement.</t>
+          <t>Revision -01, 23 Jul 2026 (first filed -00 Jul 6 2026); author: Abdel Fane (OpenA2A). Companion draft-fane-opena2a-aip has since moved ahead to -02 (6 Aug 2026) while AAP holds at -01, adding a fourth 'AIP' name collision to the existing Singla/Prakash/aip-agent-identity-protocol triple. The AAP authorization layer is the piece most relevant to OAuth boundary analysis.</t>
         </is>
       </c>
     </row>
@@ -3235,17 +3235,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>draft-fane-opena2a-aap — OpenA2A Agent Authorization Protocol (AAP)</t>
+          <t>draft-ni-a2a-ai-agent-security-requirements — Security Requirements for AI Agents</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Establishes authorization mechanisms for AI agent systems through cryptographic identity assertions and scoped capability grants. Introduces a broker layer that separates credentials from the agent's reasoning context, specifically to prevent prompt injection attacks from leaking authorization state while enabling cross-agent delegation.</t>
+          <t>An IETF individual draft enumerating security requirements for AI agents, covering identity, authorization chaining across domains, and integration points with WIMSE, OAuth identity chaining, and the A2A OAuth profile.</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-fane-opena2a-aap/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ni-a2a-ai-agent-security-requirements/</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 23 Jul 2026 (first filed -00 Jul 6 2026); author: Abdel Fane (OpenA2A). Companion draft-fane-opena2a-aip has since moved ahead to -02 (6 Aug 2026) while AAP holds at -01, adding a fourth 'AIP' name collision to the existing Singla/Prakash/aip-agent-identity-protocol triple. The AAP authorization layer is the piece most relevant to OAuth boundary analysis.</t>
+          <t>Revision -01, February 2026; essential scaffolding for an eventual AI-agent WG. Well-connected to existing IETF work and authored by Ni and Liu, who also lead the WIMSE AI-agent identity draft.</t>
         </is>
       </c>
     </row>
@@ -3265,17 +3265,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>draft-ni-a2a-ai-agent-security-requirements — Security Requirements for AI Agents</t>
+          <t>draft-chapman-a2a-mls — End-to-End Encryption and Purpose-Bound Governance for Agent-to-Agent Messaging</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft enumerating security requirements for AI agents, covering identity, authorization chaining across domains, and integration points with WIMSE, OAuth identity chaining, and the A2A OAuth profile.</t>
+          <t>Extends the Agent2Agent (A2A) protocol with message-level E2E confidentiality using MLS (Messaging Layer Security); defines a Governed Object signed message envelope carrying semantic type, payload, purpose declaration, and expiry; mandates receiver-side processing rules enforcing declared purposes and rejecting expired or replayed messages.</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ni-a2a-ai-agent-security-requirements/</t>
+          <t>https://datatracker.ietf.org/doc/draft-chapman-a2a-mls/</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, February 2026; essential scaffolding for an eventual AI-agent WG. Well-connected to existing IETF work and authored by Ni and Liu, who also lead the WIMSE AI-agent identity draft.</t>
+          <t>Revision -03, 1 Aug 2026 (was -00, Jul 28 2026); author: Chapman. Adds the transport-security and semantic-governance layer the A2A protocol family was missing. MLS binding anchors agent identity to Ed25519 did:key DIDs. The Governed Object envelope's purpose-declaration mechanism directly addresses the intent-drift threat identified in draft-jiang-intent-security (corpus). Likely to be referenced by other A2A family drafts as the baseline confidentiality profile.</t>
         </is>
       </c>
     </row>
@@ -3295,17 +3295,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>draft-chapman-a2a-mls — End-to-End Encryption and Purpose-Bound Governance for Agent-to-Agent Messaging</t>
+          <t>draft-rosenberg-agentproto-usecases — Framework, Use Cases and Requirements for AI Agent Protocols</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Extends the Agent2Agent (A2A) protocol with message-level E2E confidentiality using MLS (Messaging Layer Security); defines a Governed Object signed message envelope carrying semantic type, payload, purpose declaration, and expiry; mandates receiver-side processing rules enforcing declared purposes and rejecting expired or replayed messages.</t>
+          <t>AI Agents are software applications that utilize Large Language Models (LLM)s to interact with humans (or other AI Agents) for purposes of performing tasks. AI Agents can make use of resources - including APIs and documents - to perform those tasks, and are capable of reasoning about which resources to use. To facilitate AI agent operation, AI agents need to communicate with users, and then interact with other resources over the Internet, including APIs and other AI agents. This document describes a framework for AI Agent communications on the Internet, identifying the various protocols that come into play. It introduces use cases that motivate features and functions that need to be present in those protocols. It also provides a brief survey of existing work in standardizing AI agent protocols, including the Model Context Protocol (MCP), the Agent to Agent Protocol (A2A) and the Agntcy Framework, and describes how those works fit into this framework. The primary objective of this document is to set the stage for possible standards activity at the IETF in this space.</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-chapman-a2a-mls/</t>
+          <t>https://datatracker.ietf.org/doc/draft-rosenberg-agentproto-usecases/</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, 1 Aug 2026 (was -00, Jul 28 2026); author: Chapman. Adds the transport-security and semantic-governance layer the A2A protocol family was missing. MLS binding anchors agent identity to Ed25519 did:key DIDs. The Governed Object envelope's purpose-declaration mechanism directly addresses the intent-drift threat identified in draft-jiang-intent-security (corpus). Likely to be referenced by other A2A family drafts as the baseline confidentiality profile.</t>
+          <t>Revision -00, checked 26 Aug 2026. **Re-slugged: this draft was tracked as draft-rosenberg-aiproto-framework until 26 Aug 2026**, which Datatracker marks Replaced by this one. Row updated to the current name, URL and abstract; the old slug is recorded here so searches for it still land. Previously filed in the corpus as “draft-rosenberg-aiproto-framework — Framework, Use Cases and Requirements for AI Agent Protocols”.</t>
         </is>
       </c>
     </row>
@@ -3325,17 +3325,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>draft-rosenberg-aiproto-framework — Framework, Use Cases and Requirements for AI Agent Protocols</t>
+          <t>draft-rosenberg-aiproto-cheq — CHEQ: A Protocol for Confirmation of AI Agent Decisions (HITL)</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft providing a comprehensive AI-agent communications framework that covers user↔agent, agent↔API, and agent↔agent interactions; surveys MCP, A2A, and Agntcy; and sets the stage for IETF standards activity.</t>
+          <t>An IETF individual draft defining an out-of-band Human-in-the-Loop confirmation protocol for agent tool calls, eliminating LLM-hallucination risk for consequential actions and enabling sensitive operations (e.g., banking) without exposing data to the agent.</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-rosenberg-aiproto-framework/</t>
+          <t>https://datatracker.ietf.org/doc/draft-rosenberg-aiproto-cheq/</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, October 2025; Rosenberg (Five9) and Jennings (Cisco) are credible long-time IETF contributors. Important landscape document but likely expired (April 2026); watch for a -01 refresh post-IETF 123.</t>
+          <t>Revision -00, October 2025; out-of-band HITL confirmation model is valuable and complements delegation frameworks. Likely expired (April 2026); worth tracking for a -01 refresh. **EXPIRED on Datatracker** (expired 23 Apr 2026; checked 26 Aug 2026) — kept in the corpus deliberately; an expired draft is still evidence of what was proposed.</t>
         </is>
       </c>
     </row>
@@ -3355,27 +3355,27 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>draft-rosenberg-aiproto-cheq — CHEQ: A Protocol for Confirmation of AI Agent Decisions (HITL)</t>
+          <t>draft-sharif-agent-payment-trust — Trust Scoring and Identity Verification for AI Agent Payment Transactions (SUPERSEDED)</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft defining an out-of-band Human-in-the-Loop confirmation protocol for agent tool calls, eliminating LLM-hallucination risk for consequential actions and enabling sensitive operations (e.g., banking) without exposing data to the agent.</t>
+          <t>An IETF individual draft introducing an Agent Passport — a cryptographic delegation certificate intended to serve as the PSD2 'something you have' factor — and a trust-scoring model for payment transactions mapped to PCI DSS v4.0.1.</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-rosenberg-aiproto-cheq/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sharif-agent-payment-trust/</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual)</t>
+          <t>IETF (individual, superseded)</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, October 2025; out-of-band HITL confirmation model is valuable and complements delegation frameworks. Likely expired (April 2026); worth tracking for a -01 refresh.</t>
+          <t>SUPERSEDED by draft-sharif-attp-00 (April 2026). Retained for historical context — the Agent Passport concept is interesting but needs formal grounding; the ATTP successor generalizes it across transport bindings.</t>
         </is>
       </c>
     </row>
@@ -3385,27 +3385,27 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>draft-sharif-agent-payment-trust — Trust Scoring and Identity Verification for AI Agent Payment Transactions (SUPERSEDED)</t>
+          <t>draft-stephan-ai-agent-6g — AI Agent Protocols for 6G Systems</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft introducing an Agent Passport — a cryptographic delegation certificate intended to serve as the PSD2 'something you have' factor — and a trust-scoring model for payment transactions mapped to PCI DSS v4.0.1.</t>
+          <t>An IETF individual draft translating use cases and service requirements from 3GPP TR 22.870 into IETF agent-protocol requirements, covering autonomous vehicles, privacy preservation, and anomaly detection.</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sharif-agent-payment-trust/</t>
+          <t>https://datatracker.ietf.org/doc/draft-stephan-ai-agent-6g/</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual, superseded)</t>
+          <t>IETF (individual)</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>SUPERSEDED by draft-sharif-attp-00 (April 2026). Retained for historical context — the Agent Passport concept is interesting but needs formal grounding; the ATTP successor generalizes it across transport bindings.</t>
+          <t>Revision -02, October 2025; strong operator backing (Orange, Deutsche Telekom, Telefonica, China Mobile, Huawei). Requirements-oriented and important for 3GPP/IETF coordination. May be expired (April 2026); watch for an update. **EXPIRED on Datatracker** (expired 23 Apr 2026; checked 26 Aug 2026) — kept in the corpus deliberately; an expired draft is still evidence of what was proposed.</t>
         </is>
       </c>
     </row>
@@ -3415,17 +3415,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>draft-stephan-ai-agent-6g — AI Agent Protocols for 6G Systems</t>
+          <t>draft-jimenez-t2trg-iot-agent — Agentic AI Operation of Constrained RESTful Environments</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft translating use cases and service requirements from 3GPP TR 22.870 into IETF agent-protocol requirements, covering autonomous vehicles, privacy preservation, and anomaly detection.</t>
+          <t>An IETF individual draft (T2TRG affiliated) describing agentic AI (ReAct, smolagents) operating on CoAP/CoRE constrained-IoT environments, with a reference implementation provided.</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-stephan-ai-agent-6g/</t>
+          <t>https://datatracker.ietf.org/doc/draft-jimenez-t2trg-iot-agent/</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, October 2025; strong operator backing (Orange, Deutsche Telekom, Telefonica, China Mobile, Huawei). Requirements-oriented and important for 3GPP/IETF coordination. May be expired (April 2026); watch for an update.</t>
+          <t>Revision -00, 14 April 2026; unique in targeting constrained IoT environments. T2TRG affiliation and reference implementation are positive signals. Niche but fills an unaddressed gap.</t>
         </is>
       </c>
     </row>
@@ -3445,17 +3445,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>draft-jimenez-t2trg-iot-agent — Agentic AI Operation of Constrained RESTful Environments</t>
+          <t>draft-li-oauth-delegated-authorization — OAuth 2.0 Delegated Authorization</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft (T2TRG affiliated) describing agentic AI (ReAct, smolagents) operating on CoAP/CoRE constrained-IoT environments, with a reference implementation provided.</t>
+          <t>An IETF individual draft from Huawei authors that extends OAuth 2.0 with a hierarchical 'delegation token' model so a client can mint subordinate, narrowly-scoped access tokens for delegated parties.</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-jimenez-t2trg-iot-agent/</t>
+          <t>https://datatracker.ietf.org/doc/draft-li-oauth-delegated-authorization/</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 14 April 2026; unique in targeting constrained IoT environments. T2TRG affiliation and reference implementation are positive signals. Niche but fills an unaddressed gap.</t>
+          <t>Revision -01, March 2026 (Informational); directly addresses over-privileged tokens and is one of the few drafts using the literal term 'delegated authorization'.</t>
         </is>
       </c>
     </row>
@@ -3475,17 +3475,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>draft-li-oauth-delegated-authorization — OAuth 2.0 Delegated Authorization</t>
+          <t>draft-araut-oauth-transaction-tokens-for-agents — Transaction Tokens For Agents</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft from Huawei authors that extends OAuth 2.0 with a hierarchical 'delegation token' model so a client can mint subordinate, narrowly-scoped access tokens for delegated parties.</t>
+          <t>An IETF individual draft from Ashay Raut (Amazon) profiling Transaction Tokens for agent-based workflows by adding 'act' for the agent identity, an 'agentic_ctx' claim carrying agent_type/intent/allowed_actions/environment_constraints, RFC 9396 RAR integration, and an 'actchain' claim for multi-agent delegation lineage.</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-li-oauth-delegated-authorization/</t>
+          <t>https://datatracker.ietf.org/doc/draft-araut-oauth-transaction-tokens-for-agents/</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, March 2026 (Informational); directly addresses over-privileged tokens and is one of the few drafts using the literal term 'delegated authorization'.</t>
+          <t>Revision -01 (May 2026) under the new slug — re-slugged from draft-oauth-transaction-tokens-for-agents-06; the -06 added the actchain delegation lineage, RAR-driven agentic_ctx, and a TTS check that blocks chain-splicing attacks. Conservative extension of the WG Transaction Tokens draft and an easier path to standardization.</t>
         </is>
       </c>
     </row>
@@ -3505,17 +3505,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>draft-araut-oauth-transaction-tokens-for-agents — Transaction Tokens For Agents</t>
+          <t>draft-oauth-ai-agents-on-behalf-of-user — On-Behalf-Of User Authorization for AI Agents</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft from Ashay Raut (Amazon) profiling Transaction Tokens for agent-based workflows by adding 'act' for the agent identity, an 'agentic_ctx' claim carrying agent_type/intent/allowed_actions/environment_constraints, RFC 9396 RAR integration, and an 'actchain' claim for multi-agent delegation lineage.</t>
+          <t>An IETF individual draft adding requested_actor and actor_token parameters to the OAuth authorization-code flow so the user gives explicit consent per agent, with the resulting delegation chain documented in the access-token claims.</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-araut-oauth-transaction-tokens-for-agents/</t>
+          <t>https://datatracker.ietf.org/doc/draft-oauth-ai-agents-on-behalf-of-user/</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Revision -01 (May 2026) under the new slug — re-slugged from draft-oauth-transaction-tokens-for-agents-06; the -06 added the actchain delegation lineage, RAR-driven agentic_ctx, and a TTS check that blocks chain-splicing attacks. Conservative extension of the WG Transaction Tokens draft and an easier path to standardization.</t>
+          <t>Revision -02 was submitted August 2025; likely due for -03 refresh. Builds naturally on RFC 6749 + RFC 8693 + RFC 7636 PKCE — one of the most 'IETF-ready' delegation drafts and a strong WG-adoption candidate after the OAuth recharter. **EXPIRED on Datatracker** (expired 27 Feb 2026; checked 26 Aug 2026) — kept in the corpus deliberately; an expired draft is still evidence of what was proposed.</t>
         </is>
       </c>
     </row>
@@ -3535,17 +3535,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>draft-oauth-ai-agents-on-behalf-of-user — On-Behalf-Of User Authorization for AI Agents</t>
+          <t>draft-rosomakho-oauth-txn-challenge — OAuth Transaction Authorization Challenge</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft adding requested_actor and actor_token parameters to the OAuth authorization-code flow so the user gives explicit consent per agent, with the resulting delegation chain documented in the access-token claims.</t>
+          <t>An OAuth mechanism enabling protected resources to demand transaction-specific authorization through challenges. When a request involves an agent or automated workflow, the RS returns a challenge to the client; the client presents it to the AS, which validates it, obtains human approval, and issues an access token with RFC 9396 authorization_details describing the approved operation. Positions as complementary to RFC 9470 (Step-Up Authentication) — that spec handles authentication freshness; this one handles authorization specificity.</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-oauth-ai-agents-on-behalf-of-user/</t>
+          <t>https://datatracker.ietf.org/doc/draft-rosomakho-oauth-txn-challenge/</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Revision -02 was submitted August 2025; likely due for -03 refresh. Builds naturally on RFC 6749 + RFC 8693 + RFC 7636 PKCE — one of the most 'IETF-ready' delegation drafts and a strong WG-adoption candidate after the OAuth recharter.</t>
+          <t>Revision -00, submitted 25 June 2026. Authors: Yaroslav Rosomakho (Zscaler), Brian Campbell (Ping Identity), Karl McGuinness (Independent), Pieter Kasselman (Defakto). Strong author lineup — Campbell is a prolific OAuth WG contributor, Kasselman co-authored Transaction Tokens and First-Party Apps, McGuinness brings the Mission-Bound OAuth context. The RS-initiated challenge model is distinct from ARAP (which operates at the PDP/PEP layer via AuthZEN) but addresses the same 'denial is not the end' problem — here at the OAuth RS/AS layer rather than the AuthZEN layer.</t>
         </is>
       </c>
     </row>
@@ -3565,17 +3565,17 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>draft-rosomakho-oauth-txn-challenge — OAuth Transaction Authorization Challenge</t>
+          <t>draft-lee-orprg-permit-receipts — Permit Receipts for Permit-Before-Commit Authorization</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>An OAuth mechanism enabling protected resources to demand transaction-specific authorization through challenges. When a request involves an agent or automated workflow, the RS returns a challenge to the client; the client presents it to the AS, which validates it, obtains human approval, and issues an access token with RFC 9396 authorization_details describing the approved operation. Positions as complementary to RFC 9470 (Step-Up Authentication) — that spec handles authentication freshness; this one handles authorization specificity.</t>
+          <t>Defines requirements and an abstract data model for PermitReceipts: a verifier evaluates canonicalized effect requests, action digests, policy epochs, validity intervals, and revocation status before any protected effect is committed at an effect boundary. Covers verifier behavior, failure semantics, and candidate registries.</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-rosomakho-oauth-txn-challenge/</t>
+          <t>https://datatracker.ietf.org/doc/draft-lee-orprg-permit-receipts/</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, submitted 25 June 2026. Authors: Yaroslav Rosomakho (Zscaler), Brian Campbell (Ping Identity), Karl McGuinness (Independent), Pieter Kasselman (Defakto). Strong author lineup — Campbell is a prolific OAuth WG contributor, Kasselman co-authored Transaction Tokens and First-Party Apps, McGuinness brings the Mission-Bound OAuth context. The RS-initiated challenge model is distinct from ARAP (which operates at the PDP/PEP layer via AuthZEN) but addresses the same 'denial is not the end' problem — here at the OAuth RS/AS layer rather than the AuthZEN layer.</t>
+          <t>Revision -00, 4 Jun 2026; author: Yong Bok Lee (Meridian Verity Group). The most complete standalone framework for pre-commit authorization in the current wave; intended to ground IETF discussion on scope and profiles. Seeks guidance on appropriate organizational placement.</t>
         </is>
       </c>
     </row>
@@ -3595,17 +3595,17 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>draft-lee-orprg-permit-receipts — Permit Receipts for Permit-Before-Commit Authorization</t>
+          <t>draft-nelson-agent-delegation-receipts — Delegation Receipt Protocol for AI Agent Authorization</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Defines requirements and an abstract data model for PermitReceipts: a verifier evaluates canonicalized effect requests, action digests, policy epochs, validity intervals, and revocation status before any protected effect is committed at an effect boundary. Covers verifier behavior, failure semantics, and candidate registries.</t>
+          <t>Specifies the Delegation Receipt Protocol (DRP) where users sign Authorization Objects (containing scope boundaries, time constraints, instruction hashes, and model state commitments) that are published to an append-only log before the agent runtime gains control. Removes operators as trusted intermediaries by making the user's private key the sole signing authority.</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-lee-orprg-permit-receipts/</t>
+          <t>https://datatracker.ietf.org/doc/draft-nelson-agent-delegation-receipts/</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 4 Jun 2026; author: Yong Bok Lee (Meridian Verity Group). The most complete standalone framework for pre-commit authorization in the current wave; intended to ground IETF discussion on scope and profiles. Seeks guidance on appropriate organizational placement.</t>
+          <t>Revision -10, 13 Jun 2026; author: Ryan Nelson (Authproof). At version 10, the most iterated individual draft in the pre-action authorization space. The commitment-before-execution architecture — sign before the agent runs, not after — is distinctive and directly addresses the prompt-injection attack surface.</t>
         </is>
       </c>
     </row>
@@ -3625,17 +3625,17 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>draft-nelson-agent-delegation-receipts — Delegation Receipt Protocol for AI Agent Authorization</t>
+          <t>draft-williams-intent-token — The Intent Token: A Cryptographic Authorization Primitive for Autonomous Agents</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Specifies the Delegation Receipt Protocol (DRP) where users sign Authorization Objects (containing scope boundaries, time constraints, instruction hashes, and model state commitments) that are published to an append-only log before the agent runtime gains control. Removes operators as trusted intermediaries by making the user's private key the sole signing authority.</t>
+          <t>Specifies a cryptographic authorization primitive that binds an autonomous agent action to a cryptographically signed, human-declared authorization envelope before execution. Addresses the gap in OAuth 2.0 frameworks that govern access to resources but not what agents are permitted to do at the moment of action. Positioned as complementary to OAuth, not a replacement.</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-nelson-agent-delegation-receipts/</t>
+          <t>https://datatracker.ietf.org/doc/draft-williams-intent-token/</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Revision -10, 13 Jun 2026; author: Ryan Nelson (Authproof). At version 10, the most iterated individual draft in the pre-action authorization space. The commitment-before-execution architecture — sign before the agent runs, not after — is distinctive and directly addresses the prompt-injection attack surface.</t>
+          <t>Revision -01, 22 Jun 2026; author: Jeffrey Williams (Independent). Overlaps conceptually with draft-kroehl-agentic-trust-aae and draft-nelson-agent-delegation-receipts; worth tracking as a lighter-weight alternative to both.</t>
         </is>
       </c>
     </row>
@@ -3655,17 +3655,17 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>draft-williams-intent-token — The Intent Token: A Cryptographic Authorization Primitive for Autonomous Agents</t>
+          <t>draft-pereira-licet-human-intent — LICET: Multi-Modal Physiological Human-Intent Verification for Autonomous AI Agent Authorization</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Specifies a cryptographic authorization primitive that binds an autonomous agent action to a cryptographically signed, human-declared authorization envelope before execution. Addresses the gap in OAuth 2.0 frameworks that govern access to resources but not what agents are permitted to do at the moment of action. Positioned as complementary to OAuth, not a replacement.</t>
+          <t>Proposes a biometric HITL protocol fusing ECG, electrodermal activity, and Mahalanobis statistical distance to cryptographically verify genuine human intent — not just credential possession — before authorizing autonomous AI agent actions, with ZK proofs enabling third-party audit without exposing raw biometric data.</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-williams-intent-token/</t>
+          <t>https://datatracker.ietf.org/doc/draft-pereira-licet-human-intent/</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 22 Jun 2026; author: Jeffrey Williams (Independent). Overlaps conceptually with draft-kroehl-agentic-trust-aae and draft-nelson-agent-delegation-receipts; worth tracking as a lighter-weight alternative to both.</t>
+          <t>Revision -01, 2 Jul 2026. The most novel and technically niche HITL proposal in the current wave — complements draft-rosenberg-aiproto-cheq (out-of-band HITL confirmation) and draft-sato-soos-hem (kernel-enforced escalation) by grounding human intent in physiological signal rather than credential or UI interaction.</t>
         </is>
       </c>
     </row>
@@ -3685,17 +3685,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>draft-pereira-licet-human-intent — LICET: Multi-Modal Physiological Human-Intent Verification for Autonomous AI Agent Authorization</t>
+          <t>draft-reece-wimse-cross-org-delegation — Cross-Organizational Delegation for Workload and Agent Identity</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Proposes a biometric HITL protocol fusing ECG, electrodermal activity, and Mahalanobis statistical distance to cryptographically verify genuine human intent — not just credential possession — before authorizing autonomous AI agent actions, with ZK proofs enabling third-party audit without exposing raw biometric data.</t>
+          <t>A problem statement and requirements draft identifying that existing workload and token-based authorization mechanisms were designed for a single trust domain, describing the cross-organizational agent delegation gap, and enumerating requirements for solutions — without proposing specific technical approaches.</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-pereira-licet-human-intent/</t>
+          <t>https://datatracker.ietf.org/doc/draft-reece-wimse-cross-org-delegation/</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 2 Jul 2026. The most novel and technically niche HITL proposal in the current wave — complements draft-rosenberg-aiproto-cheq (out-of-band HITL confirmation) and draft-sato-soos-hem (kernel-enforced escalation) by grounding human intent in physiological signal rather than credential or UI interaction.</t>
+          <t>Revision -01, 30 Jul 2026 (was -00, 25 Jun 2026); author: Morgan Reece (TowerGuardian Consulting). The problem-statement companion to the corpus's operational drafts; likely to feed into WIMSE WG scope expansion and is directly in scope for draft-kuehlewind-audit-architecture's composition graph.</t>
         </is>
       </c>
     </row>
@@ -3715,17 +3715,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>draft-reece-wimse-cross-org-delegation — Cross-Organizational Delegation for Workload and Agent Identity</t>
+          <t>draft-jiang-wimse-heterogeneous-credential — Heterogeneous Credential Verification for Workload and Agentic Systems</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>A problem statement and requirements draft identifying that existing workload and token-based authorization mechanisms were designed for a single trust domain, describing the cross-organizational agent delegation gap, and enumerating requirements for solutions — without proposing specific technical approaches.</t>
+          <t>Specifies mechanisms for representing credential sets, identifying credential types, determining appropriate verifiers, normalizing verification results across different formats (workload tokens, OAuth, X.509, attestation), and combining results into a single handling decision.</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-reece-wimse-cross-org-delegation/</t>
+          <t>https://datatracker.ietf.org/doc/draft-jiang-wimse-heterogeneous-credential/</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 30 Jul 2026 (was -00, 25 Jun 2026); author: Morgan Reece (TowerGuardian Consulting). The problem-statement companion to the corpus's operational drafts; likely to feed into WIMSE WG scope expansion and is directly in scope for draft-kuehlewind-audit-architecture's composition graph.</t>
+          <t>Revision -01, 30 Jun 2026 (was -00 Jun 2026); authors: Yuning Jiang, Donghui Wang, Yurong Song, Faye Liu (Huawei). Solves the practical problem of agentic systems receiving credentials in multiple formats from different issuers. Fills a gap left by draft-ni-wimse-ai-agent-identity (corpus) which describes the identity problem but not multi-format credential handling.</t>
         </is>
       </c>
     </row>
@@ -3745,17 +3745,17 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>draft-jiang-wimse-heterogeneous-credential — Heterogeneous Credential Verification for Workload and Agentic Systems</t>
+          <t>draft-munoz-wimse-authorization-evidence — Signed Authorization-Evidence Records for WIMSE-Authorized AI Agent Actions</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Specifies mechanisms for representing credential sets, identifying credential types, determining appropriate verifiers, normalizing verification results across different formats (workload tokens, OAuth, X.509, attestation), and combining results into a single handling decision.</t>
+          <t>Specifies a signed authorization-evidence record (Permit) for WIMSE-authorized AI actions, cryptographically binding to the dispatched request bytes via HTTP Message Signatures, OAuth access tokens, and Shared Signals Framework eventing — without modifying existing standards.</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-jiang-wimse-heterogeneous-credential/</t>
+          <t>https://datatracker.ietf.org/doc/draft-munoz-wimse-authorization-evidence/</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 30 Jun 2026 (was -00 Jun 2026); authors: Yuning Jiang, Donghui Wang, Yurong Song, Faye Liu (Huawei). Solves the practical problem of agentic systems receiving credentials in multiple formats from different issuers. Fills a gap left by draft-ni-wimse-ai-agent-identity (corpus) which describes the identity problem but not multi-format credential handling.</t>
+          <t>Revision -00, 15 May 2026; author: Christian Munoz (Keel API). Profiles WIMSE for AI agent actions and satisfies audit requirements; companion to the SCITT permit profile below. Extends the corpus WIMSE thread (draft-ni-wimse-ai-agent-identity) with a concrete evidence artifact.</t>
         </is>
       </c>
     </row>
@@ -3775,17 +3775,17 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>draft-munoz-wimse-authorization-evidence — Signed Authorization-Evidence Records for WIMSE-Authorized AI Agent Actions</t>
+          <t>draft-schwenkschuster-wimse-trust-domain-discovery — WIMSE Trust Domain Discovery</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Specifies a signed authorization-evidence record (Permit) for WIMSE-authorized AI actions, cryptographically binding to the dispatched request bytes via HTTP Message Signatures, OAuth access tokens, and Shared Signals Framework eventing — without modifying existing standards.</t>
+          <t>Fills a gap in the WIMSE architecture by defining how relying parties obtain cryptographic trust anchors for workload identity credentials; specifies the WIMSE Trust Bundle (a JSON document with freshness metadata) and a well-known HTTPS discovery endpoint resolving trust domain names to their trust bundles, following OpenID Connect Discovery / OAuth 2.0 patterns.</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-munoz-wimse-authorization-evidence/</t>
+          <t>https://datatracker.ietf.org/doc/draft-schwenkschuster-wimse-trust-domain-discovery/</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 15 May 2026; author: Christian Munoz (Keel API). Profiles WIMSE for AI agent actions and satisfies audit requirements; companion to the SCITT permit profile below. Extends the corpus WIMSE thread (draft-ni-wimse-ai-agent-identity) with a concrete evidence artifact.</t>
+          <t>Revision -00, 3 Jul 2026; authors: Arndt Schwenkschuster (Defakto Security), Yaroslav Rosomakho (Zscaler). Directly complements draft-schwenkschuster-wimse-credential-exchange (corpus). The kuehlewind-audit-architecture HUB assumes resolvable trust anchors — this provides the discovery mechanism. Rosomakho co-authorship ties it to draft-rosomakho-oauth-txn-challenge.</t>
         </is>
       </c>
     </row>
@@ -3805,17 +3805,17 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>draft-schwenkschuster-wimse-trust-domain-discovery — WIMSE Trust Domain Discovery</t>
+          <t>draft-winmagic-wimse-condition-bounded-credentials — Condition-Bounded Credentials for Workload and Agent Identity</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Fills a gap in the WIMSE architecture by defining how relying parties obtain cryptographic trust anchors for workload identity credentials; specifies the WIMSE Trust Bundle (a JSON document with freshness metadata) and a well-known HTTPS discovery endpoint resolving trust domain names to their trust bundles, following OpenID Connect Discovery / OAuth 2.0 patterns.</t>
+          <t>Proposes hardware-rooted, non-exfiltratable workload credentials whose validity is conditioned on attested runtime posture rather than expiration time — so a credential becomes invalid if the workload's attestation evidence degrades, regardless of the stated expiry.</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-schwenkschuster-wimse-trust-domain-discovery/</t>
+          <t>https://datatracker.ietf.org/doc/draft-winmagic-wimse-condition-bounded-credentials/</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 3 Jul 2026; authors: Arndt Schwenkschuster (Defakto Security), Yaroslav Rosomakho (Zscaler). Directly complements draft-schwenkschuster-wimse-credential-exchange (corpus). The kuehlewind-audit-architecture HUB assumes resolvable trust anchors — this provides the discovery mechanism. Rosomakho co-authorship ties it to draft-rosomakho-oauth-txn-challenge.</t>
+          <t>Revision -01, 6 Jul 2026; author: WinMagic. Extends the WIMSE credential model with posture-conditioned validity — distinct from time-bounded credentials in that security policy changes at the hardware/attestation layer instantly invalidate the credential. Bridges the RATS attestation thread and the WIMSE identity thread in the corpus.</t>
         </is>
       </c>
     </row>
@@ -3835,17 +3835,17 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>draft-winmagic-wimse-condition-bounded-credentials — Condition-Bounded Credentials for Workload and Agent Identity</t>
+          <t>draft-rampalli-pedigree — PEDIGREE: Per-Hop Cryptographic Delegation for Workload and AI Agent Identity</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Proposes hardware-rooted, non-exfiltratable workload credentials whose validity is conditioned on attested runtime posture rather than expiration time — so a credential becomes invalid if the workload's attestation evidence degrades, regardless of the stated expiry.</t>
+          <t>Extends SPIFFE workload identity with cryptographic per-hop delegation using monotonic scope attenuation enforced at mint and verify; uses Cedar-policy mandates with static-analysis proofs and parent-token re-verification to detect parent-swap attacks. Defines an Operator Ceiling binding all sub-agent authority to the parent's declared mandate.</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-winmagic-wimse-condition-bounded-credentials/</t>
+          <t>https://datatracker.ietf.org/doc/draft-rampalli-pedigree/</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 6 Jul 2026; author: WinMagic. Extends the WIMSE credential model with posture-conditioned validity — distinct from time-bounded credentials in that security policy changes at the hardware/attestation layer instantly invalidate the credential. Bridges the RATS attestation thread and the WIMSE identity thread in the corpus.</t>
+          <t>Revision -00, Apr 25 2026; author: Karthik Rampalli (Glyphzero, Inc.) — same author as draft-rampalli-cross-org-delegation-mapping and draft-rampalli-scitt-capsule-provenance-binding (both in corpus). Presented at WIMSE WG as proposed new work at IETF 126 (Bangkok, Jul 2026). Cedar-policy static-analysis attenuation proofs are a unique contribution relative to other delegation-chain drafts. Note: draft-rampalli-cross-org-delegation-mapping (corpus) references the 'PEDIGREE model' — this is the normative definition.</t>
         </is>
       </c>
     </row>
@@ -3865,17 +3865,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>draft-rampalli-pedigree — PEDIGREE: Per-Hop Cryptographic Delegation for Workload and AI Agent Identity</t>
+          <t>draft-sweeney-wimse-credential-delegation — Credential Delegation Protocol for AI Agents in Multi-System Environments</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Extends SPIFFE workload identity with cryptographic per-hop delegation using monotonic scope attenuation enforced at mint and verify; uses Cedar-policy mandates with static-analysis proofs and parent-token re-verification to detect parent-swap attacks. Defines an Operator Ceiling binding all sub-agent authority to the parent's declared mandate.</t>
+          <t>Composes RFC 8693 Token Exchange, RFC 9449 DPoP, RFC 9396 Rich Authorization Requests, and OpenID Connect CIBA into a unified delegation flow for autonomous AI agents accessing protected resources across providers; introduces ephemeral agent identities via did:key, capability-shaped attenuated delegation tokens, credential wrapping preventing raw OAuth tokens from reaching agents, synchronous revocation cascading, and tamper-evident audit chains.</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-rampalli-pedigree/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sweeney-wimse-credential-delegation/</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, Apr 25 2026; author: Karthik Rampalli (Glyphzero, Inc.) — same author as draft-rampalli-cross-org-delegation-mapping and draft-rampalli-scitt-capsule-provenance-binding (both in corpus). Presented at WIMSE WG as proposed new work at IETF 126 (Bangkok, Jul 2026). Cedar-policy static-analysis attenuation proofs are a unique contribution relative to other delegation-chain drafts. Note: draft-rampalli-cross-org-delegation-mapping (corpus) references the 'PEDIGREE model' — this is the normative definition.</t>
+          <t>Revision -00, Jul 28 2026; author: Sweeney. Explicitly designed as a WIMSE companion, citing draft-klrc-aiagent-auth as its target framework. The widest synthesis of OAuth primitives in the WIMSE extension cluster — DPoP + RAR + CIBA + Token Exchange in one flow. The credential-wrapping model (raw tokens never reach the agent) directly addresses the secret-exposure threat formalized in arXiv:2604.24920 (SUDP paper, now in corpus).</t>
         </is>
       </c>
     </row>
@@ -3895,17 +3895,17 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>draft-sweeney-wimse-credential-delegation — Credential Delegation Protocol for AI Agents in Multi-System Environments</t>
+          <t>draft-munoz-scitt-permit-profile — A SCITT Profile for Pre-Execution AI Action Authorization Records</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Composes RFC 8693 Token Exchange, RFC 9449 DPoP, RFC 9396 Rich Authorization Requests, and OpenID Connect CIBA into a unified delegation flow for autonomous AI agents accessing protected resources across providers; introduces ephemeral agent identities via did:key, capability-shaped attenuated delegation tokens, credential wrapping preventing raw OAuth tokens from reaching agents, synchronous revocation cascading, and tamper-evident audit chains.</t>
+          <t>SCITT profile for the Pre-Execution Authorization Record (Permit), documenting policy-evaluated decisions before AI agent action dispatch with cryptographic binding proving 'authorized request equals dispatched request.' Composes with adjacent profiles for human-authority binding, post-execution evidence, and content-refusal events via referencing mechanisms.</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sweeney-wimse-credential-delegation/</t>
+          <t>https://datatracker.ietf.org/doc/draft-munoz-scitt-permit-profile/</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, Jul 28 2026; author: Sweeney. Explicitly designed as a WIMSE companion, citing draft-klrc-aiagent-auth as its target framework. The widest synthesis of OAuth primitives in the WIMSE extension cluster — DPoP + RAR + CIBA + Token Exchange in one flow. The credential-wrapping model (raw tokens never reach the agent) directly addresses the secret-exposure threat formalized in arXiv:2604.24920 (SUDP paper, now in corpus).</t>
+          <t>Revision -00, 15 May 2026; author: Christian Munoz (Keel API). SCITT-anchored analog of the WIMSE evidence record; companion to draft-munoz-wimse-authorization-evidence from the same author. Connects to draft-sharif-agent-audit-trail and draft-kuehlewind-audit-architecture (both in corpus).</t>
         </is>
       </c>
     </row>
@@ -3925,17 +3925,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>draft-munoz-scitt-permit-profile — A SCITT Profile for Pre-Execution AI Action Authorization Records</t>
+          <t>draft-marques-asqav-compliance-receipts — Compliance Profile of Signed Action Receipts for AI Agents</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>SCITT profile for the Pre-Execution Authorization Record (Permit), documenting policy-evaluated decisions before AI agent action dispatch with cryptographic binding proving 'authorized request equals dispatched request.' Composes with adjacent profiles for human-authority binding, post-execution evidence, and content-refusal events via referencing mechanisms.</t>
+          <t>Establishes a compliance framework for signed action receipts from AI agents, mandating specific fields, cryptographic anchoring, hash-chain linkage, risk/incident classification, cross-agent envelope binding, and enforcement attestation with retention floors tied to EU AI Act, DORA, NIST AI RMF, HIPAA, SEC Rule 17a-4, and CIRCIA.</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-munoz-scitt-permit-profile/</t>
+          <t>https://datatracker.ietf.org/doc/draft-marques-asqav-compliance-receipts/</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 15 May 2026; author: Christian Munoz (Keel API). SCITT-anchored analog of the WIMSE evidence record; companion to draft-munoz-wimse-authorization-evidence from the same author. Connects to draft-sharif-agent-audit-trail and draft-kuehlewind-audit-architecture (both in corpus).</t>
+          <t>Revision -06, 1 Jul 2026 (was -05 May 2026); author: João André Gomes Marques. The most legally grounded receipt profile in the wave — at revision 06, relatively mature. Complements draft-sharif-agent-audit-trail (corpus) with a multi-regulation compliance overlay.</t>
         </is>
       </c>
     </row>
@@ -3955,17 +3955,17 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>draft-marques-asqav-compliance-receipts — Compliance Profile of Signed Action Receipts for AI Agents</t>
+          <t>draft-mih-scitt-agent-action-capsule — An Agent Action Capsule Profile for SCITT</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Establishes a compliance framework for signed action receipts from AI agents, mandating specific fields, cryptographic anchoring, hash-chain linkage, risk/incident classification, cross-agent envelope binding, and enforcement attestation with retention floors tied to EU AI Act, DORA, NIST AI RMF, HIPAA, SEC Rule 17a-4, and CIRCIA.</t>
+          <t>Defines a SCITT statement profile (Agent Action Capsule) documenting agent actions with outcome status (executed, blocked, denied, errored, timed out), evaluated constraints, committed-effect binding, and a human-in-the-loop flag; records a Capsule for every verdict including refusals. COSE Signed Statement format; registrable in SCITT Transparency Services.</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-marques-asqav-compliance-receipts/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mih-scitt-agent-action-capsule/</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>Revision -06, 1 Jul 2026 (was -05 May 2026); author: João André Gomes Marques. The most legally grounded receipt profile in the wave — at revision 06, relatively mature. Complements draft-sharif-agent-audit-trail (corpus) with a multi-regulation compliance overlay.</t>
+          <t>Revision -02, 6 Jul 2026 (was -01 Jun 2026); author: Steven Mih (Action State Group). -02 added an 'honest human-in-the-loop' flag distinguishing actual HITL from automated policy. Provides auditor-grade evidence that decision gates functioned; the HITL flag directly tracks the corpus theme.</t>
         </is>
       </c>
     </row>
@@ -3985,17 +3985,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>draft-mih-scitt-agent-action-capsule — An Agent Action Capsule Profile for SCITT</t>
+          <t>draft-mih-sato-agent-accountability-composition — Agent Accountability: Composition and Conformance</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Defines a SCITT statement profile (Agent Action Capsule) documenting agent actions with outcome status (executed, blocked, denied, errored, timed out), evaluated constraints, committed-effect binding, and a human-in-the-loop flag; records a Capsule for every verdict including refusals. COSE Signed Statement format; registrable in SCITT Transparency Services.</t>
+          <t>Addresses how to answer accountability questions about cross-domain autonomous agent actions for auditors and regulators who do not trust the operator; defines a composition model assembling multiple independently verifiable artifacts (workload credentials, delegation tokens, action capsules, attestation results) into a single accountability record with a conformance evaluation framework.</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mih-scitt-agent-action-capsule/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mih-sato-agent-accountability-composition/</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 6 Jul 2026 (was -01 Jun 2026); author: Steven Mih (Action State Group). -02 added an 'honest human-in-the-loop' flag distinguishing actual HITL from automated policy. Provides auditor-grade evidence that decision gates functioned; the HITL flag directly tracks the corpus theme.</t>
+          <t>Revision -01, 16 Aug 2026 (was -00, Jul 2026); authors: Steven Mih (Action State Group) + Tom Sato (MyAuberge K.K.) — collaboration between the two principal authors of draft-mih-scitt-agent-action-capsule (corpus) and the SOOS governance suite (corpus). Operates above individual SCITT profiles; the accountability-composition layer the kuehlewind-audit-architecture HUB depends on but does not yet specify.</t>
         </is>
       </c>
     </row>
@@ -4015,17 +4015,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>draft-mih-sato-agent-accountability-composition — Agent Accountability: Composition and Conformance</t>
+          <t>draft-car-rer-artifact — RER Run Artifact Format: Hash-Chained, Signed Records of AI Inference Execution</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Addresses how to answer accountability questions about cross-domain autonomous agent actions for auditors and regulators who do not trust the operator; defines a composition model assembling multiple independently verifiable artifacts (workload credentials, delegation tokens, action capsules, attestation results) into a single accountability record with a conformance evaluation framework.</t>
+          <t>Specifies a cryptographically signed JSON record for AI inference runs including a signed envelope declaring permissions and limits, a hash-chained event log covering all model and tool calls, and a runtime signature binding envelope and log to the producing implementation. Enables offline verification by parties uninvolved in the original run.</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mih-sato-agent-accountability-composition/</t>
+          <t>https://datatracker.ietf.org/doc/draft-car-rer-artifact/</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 16 Aug 2026 (was -00, Jul 2026); authors: Steven Mih (Action State Group) + Tom Sato (MyAuberge K.K.) — collaboration between the two principal authors of draft-mih-scitt-agent-action-capsule (corpus) and the SOOS governance suite (corpus). Operates above individual SCITT profiles; the accountability-composition layer the kuehlewind-audit-architecture HUB depends on but does not yet specify.</t>
+          <t>Revision -01, 12 Jun 2026; author: Kayla Cardillo (Tech Enrichment). Relevant for post-hoc audit of what permissions an agent claimed during execution; companion to the SCITT profiles but more focused on inference traceability than authorization decisions.</t>
         </is>
       </c>
     </row>
@@ -4045,17 +4045,17 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>draft-car-rer-artifact — RER Run Artifact Format: Hash-Chained, Signed Records of AI Inference Execution</t>
+          <t>draft-noa-scitt-ai-agent-receipt — A SCITT Profile for AI-Agent Action Receipts</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Specifies a cryptographically signed JSON record for AI inference runs including a signed envelope declaring permissions and limits, a hash-chained event log covering all model and tool calls, and a runtime signature binding envelope and log to the producing implementation. Enables offline verification by parties uninvolved in the original run.</t>
+          <t>Defines a minimal SCITT profile: COSE_Sign1 Signed Statements with canonicalized payloads, hash-chained for ordering, registrable in SCITT Transparency Services. Explicitly does NOT assert agent correctness, safety, or real-world outcomes — only tamper-evident, signature-verifiable records of action, principal, policy identity, and verdict.</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-car-rer-artifact/</t>
+          <t>https://datatracker.ietf.org/doc/draft-noa-scitt-ai-agent-receipt/</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 12 Jun 2026; author: Kayla Cardillo (Tech Enrichment). Relevant for post-hoc audit of what permissions an agent claimed during execution; companion to the SCITT profiles but more focused on inference traceability than authorization decisions.</t>
+          <t>Revision -01, 15 Aug 2026 (was -00, 23 Jun 2026); author: Tora Toraman (NordenSoft). The minimalist end of the SCITT profile spectrum; useful for corpus completeness alongside the more comprehensive draft-mih-scitt-agent-action-capsule.</t>
         </is>
       </c>
     </row>
@@ -4075,17 +4075,17 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>draft-noa-scitt-ai-agent-receipt — A SCITT Profile for AI-Agent Action Receipts</t>
+          <t>draft-rampalli-scitt-capsule-provenance-binding — Binding Per-Action Authorization and Memory Provenance into Agent Action Capsules</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Defines a minimal SCITT profile: COSE_Sign1 Signed Statements with canonicalized payloads, hash-chained for ordering, registrable in SCITT Transparency Services. Explicitly does NOT assert agent correctness, safety, or real-world outcomes — only tamper-evident, signature-verifiable records of action, principal, policy identity, and verdict.</t>
+          <t>Specifies how to bind three components into AAC records: what was executed ('did'), whether it was authorized ('may'), and the source of the belief that motivated the action ('why-believed'); uses optional payload extensions carrying authorization token references, memory chain roots, and quarantine attestations without modifying AAC core protected-header claims.</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-noa-scitt-ai-agent-receipt/</t>
+          <t>https://datatracker.ietf.org/doc/draft-rampalli-scitt-capsule-provenance-binding/</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 15 Aug 2026 (was -00, 23 Jun 2026); author: Tora Toraman (NordenSoft). The minimalist end of the SCITT profile spectrum; useful for corpus completeness alongside the more comprehensive draft-mih-scitt-agent-action-capsule.</t>
+          <t>Revision -00, 5 Jul 2026; author: Karthik Rampalli (Glyphzero, Inc.). Extends draft-mih-scitt-agent-action-capsule with memory provenance — the 'why-believed' component is novel among SCITT profiles. Includes a defensive publication notice waiving patent claims on the core binding technique.</t>
         </is>
       </c>
     </row>
@@ -4105,17 +4105,17 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>draft-rampalli-scitt-capsule-provenance-binding — Binding Per-Action Authorization and Memory Provenance into Agent Action Capsules</t>
+          <t>draft-rampalli-cross-org-delegation-mapping — A Layered Requirements Mapping for Cross-Organization Agent Delegation</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Specifies how to bind three components into AAC records: what was executed ('did'), whether it was authorized ('may'), and the source of the belief that motivated the action ('why-believed'); uses optional payload extensions carrying authorization token references, memory chain roots, and quarantine attestations without modifying AAC core protected-header claims.</t>
+          <t>Records a comparative mapping of two evidence layers for cross-organization AI agent delegation — per-hop delegation chains (PEDIGREE model) and named-human authorization roots (EMILIA Protocol binding and evidence-graph drafts) — evaluated against the nine requirements of draft-reece-wimse-cross-org-delegation under a multi-tier organizational architecture.</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-rampalli-scitt-capsule-provenance-binding/</t>
+          <t>https://datatracker.ietf.org/doc/draft-rampalli-cross-org-delegation-mapping/</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 5 Jul 2026; author: Karthik Rampalli (Glyphzero, Inc.). Extends draft-mih-scitt-agent-action-capsule with memory provenance — the 'why-believed' component is novel among SCITT profiles. Includes a defensive publication notice waiving patent claims on the core binding technique.</t>
+          <t>Revision -05, Jul 2026; author: Karthik Rampalli (Glyphzero, Inc.) — same author as draft-rampalli-scitt-capsule-provenance-binding (corpus). Rev-05 signals active iteration; the mapping bridges two otherwise disconnected design families and is the first document to formally cross-reference EMILIA Protocol against WIMSE cross-org requirements.</t>
         </is>
       </c>
     </row>
@@ -4135,17 +4135,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>draft-rampalli-cross-org-delegation-mapping — A Layered Requirements Mapping for Cross-Organization Agent Delegation</t>
+          <t>draft-nobuo-scitt-composite-evidence-verification — Composite Evidence Verification for SCITT Statement Graphs</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Records a comparative mapping of two evidence layers for cross-organization AI agent delegation — per-hop delegation chains (PEDIGREE model) and named-human authorization roots (EMILIA Protocol binding and evidence-graph drafts) — evaluated against the nine requirements of draft-reece-wimse-cross-org-delegation under a multi-tier organizational architecture.</t>
+          <t>Defines a composite verifier function for checking collections of SCITT Signed Statements, receipts, object bindings, and relationship edges under a named verification profile; provides structured reporting on validation status, missing evidence, outdated information, and conflicting claims — targeting auditors needing to evaluate multiple interconnected statements.</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-rampalli-cross-org-delegation-mapping/</t>
+          <t>https://datatracker.ietf.org/doc/draft-nobuo-scitt-composite-evidence-verification/</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>Revision -05, Jul 2026; author: Karthik Rampalli (Glyphzero, Inc.) — same author as draft-rampalli-scitt-capsule-provenance-binding (corpus). Rev-05 signals active iteration; the mapping bridges two otherwise disconnected design families and is the first document to formally cross-reference EMILIA Protocol against WIMSE cross-org requirements.</t>
+          <t>Revision -00, 7 Jul 2026; author: Nobuo Aoki (SOKENDAI). Operates above individual SCITT profiles (AAC, permits, compliance receipts all in corpus) — the 'how do you verify all of them together' layer that draft-kuehlewind-audit-architecture implies but does not yet specify. Watch for Kühlewind/Birkholz pickup.</t>
         </is>
       </c>
     </row>
@@ -4165,17 +4165,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>draft-nobuo-scitt-composite-evidence-verification — Composite Evidence Verification for SCITT Statement Graphs</t>
+          <t>draft-schrock-ep-authorization-receipts — Authorization Receipts for High-Risk Agent Actions</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Defines a composite verifier function for checking collections of SCITT Signed Statements, receipts, object bindings, and relationship edges under a named verification profile; provides structured reporting on validation status, missing evidence, outdated information, and conflicting claims — targeting auditors needing to evaluate multiple interconnected statements.</t>
+          <t>Defines the EMILIA Protocol (EP) authorization receipt — a COSE_Sign1 artifact that cryptographically binds a named human principal to a specific high-risk agent action before execution, providing auditors and counterparties a tamper-evident record that a real human authorized the consequential step.</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-nobuo-scitt-composite-evidence-verification/</t>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-authorization-receipts/</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 7 Jul 2026; author: Nobuo Aoki (SOKENDAI). Operates above individual SCITT profiles (AAC, permits, compliance receipts all in corpus) — the 'how do you verify all of them together' layer that draft-kuehlewind-audit-architecture implies but does not yet specify. Watch for Kühlewind/Birkholz pickup.</t>
+          <t>Revision -12, 16 Aug 2026 (was -11, 10 Aug 2026) (was -08, Jul 21 2026). The base artifact for the EMILIA Protocol family; companion drafts draft-schrock-ep-authorization-evidence-chain, draft-schrock-ep-action-evidence-graph, draft-schrock-ep-quorum, and draft-schrock-ep-evidence-record all build on or reference this receipt format. Active iteration pace — -08 by late Jul 2026. Draft-rampalli-cross-org-delegation-mapping (corpus) formally maps EMILIA Protocol receipts against the nine reece-wimse-cross-org-delegation requirements.</t>
         </is>
       </c>
     </row>
@@ -4195,17 +4195,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>draft-schrock-ep-authorization-receipts — Authorization Receipts for High-Risk Agent Actions</t>
+          <t>draft-schrock-ep-authorization-evidence-chain — Authorization Evidence Chains: Composing Heterogeneous Agent-Authorization Receipts (EP-AEC)</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>Defines the EMILIA Protocol (EP) authorization receipt — a COSE_Sign1 artifact that cryptographically binds a named human principal to a specific high-risk agent action before execution, providing auditors and counterparties a tamper-evident record that a real human authorized the consequential step.</t>
+          <t>Defines a mechanism for composing EMILIA Protocol authorization receipts from different systems and issuers into a single authorization evidence chain, enabling auditors to verify a heterogeneous chain of human approvals across organizational boundaries without requiring a common receipt format.</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-authorization-receipts/</t>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-authorization-evidence-chain/</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>Revision -12, 16 Aug 2026 (was -11, 10 Aug 2026) (was -08, Jul 21 2026). The base artifact for the EMILIA Protocol family; companion drafts draft-schrock-ep-authorization-evidence-chain, draft-schrock-ep-action-evidence-graph, draft-schrock-ep-quorum, and draft-schrock-ep-evidence-record all build on or reference this receipt format. Active iteration pace — -08 by late Jul 2026. Draft-rampalli-cross-org-delegation-mapping (corpus) formally maps EMILIA Protocol receipts against the nine reece-wimse-cross-org-delegation requirements.</t>
+          <t>Revision -05, 3 Aug 2026 (was -02, Jul 2026). The cross-system interoperability layer for EMILIA Protocol receipts; directly addresses the scenario where draft-reece-wimse-cross-org-delegation (corpus) operates and authorization evidence must span administrative domains. Rev-02 indicates active development. **SUPERSEDES draft-schrock-ep-action-evidence-graph**, which Datatracker marks Replaced by this draft. That older row was removed from the corpus on 26 Aug 2026 — it was tracked separately and had become a duplicate of this one under the pre-rename slug.</t>
         </is>
       </c>
     </row>
@@ -4225,17 +4225,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>draft-schrock-ep-action-evidence-graph — Action Evidence Graphs and Evidence Policy Replay for High-Risk Agent Actions (EP-AEG)</t>
+          <t>draft-schrock-ep-quorum — Multi-Party Quorum Authorization for High-Risk Agent Actions (EP-QUORUM)</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Composes the full set of signed artifacts about an AI agent action — workload identity credentials, delegation tokens, transaction tokens, runtime attestation results, pre-execution policy permits, and EMILIA Protocol authorization receipts — into a single verifiable action evidence graph; defines evidence policy replay for auditing past actions against policy versions current at the time.</t>
+          <t>Defines EP-QUORUM, a multi-party authorization profile for EMILIA Protocol authorization receipts; extends the base receipt (which binds one human to one action) to require a quorum of named human approvals before an action may proceed, with configurable thresholds, role requirements, and time-bounded approval windows.</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-action-evidence-graph/</t>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-quorum/</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, Jul 2026. The graph composition layer above the individual SCITT profiles and receipts already in corpus; the 'single verifiable artifact' problem that draft-nobuo-scitt-composite-evidence-verification (corpus) approaches from the SCITT statement side. Together these two drafts define the evidence graph landscape.</t>
+          <t>Revision -02, Jul 2026. The enterprise governance complement to the base EP receipt; relevant for high-risk regulated workflows (financial transactions, medical orders, critical infrastructure changes) where single-human authorization is insufficient. Rev-02 indicates active iteration.</t>
         </is>
       </c>
     </row>
@@ -4255,17 +4255,17 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>draft-schrock-ep-authorization-evidence-chain — Authorization Evidence Chains: Composing Heterogeneous Agent-Authorization Receipts (EP-AEC)</t>
+          <t>draft-schrock-ep-evidence-record — Long-Term, Crypto-Agile Preservation of Authorization Evidence (EP-EVIDENCE-RECORD)</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>Defines a mechanism for composing EMILIA Protocol authorization receipts from different systems and issuers into a single authorization evidence chain, enabling auditors to verify a heterogeneous chain of human approvals across organizational boundaries without requiring a common receipt format.</t>
+          <t>Defines a long-term, crypto-agile record format for preserving EMILIA Protocol authorization evidence under regulatory retention mandates; addresses algorithm deprecation over multi-year retention periods (DORA 5-year, HIPAA 6-year, SEC 17a-4 requirements) using a re-signing model that preserves evidentiary chain of custody.</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-authorization-evidence-chain/</t>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-evidence-record/</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>Revision -05, 3 Aug 2026 (was -02, Jul 2026). The cross-system interoperability layer for EMILIA Protocol receipts; directly addresses the scenario where draft-reece-wimse-cross-org-delegation (corpus) operates and authorization evidence must span administrative domains. Rev-02 indicates active development.</t>
+          <t>Revision -01, Jul 2026. The regulatory compliance layer for EMILIA Protocol; directly connects to the kuehlewind-audit-architecture HUB (corpus) requirement for audit evidence that survives algorithm sunset. The DORA/HIPAA/SEC citation grounds the spec in concrete regulatory obligations.</t>
         </is>
       </c>
     </row>
@@ -4285,17 +4285,17 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>draft-schrock-ep-quorum — Multi-Party Quorum Authorization for High-Risk Agent Actions (EP-QUORUM)</t>
+          <t>draft-kumaresan-counter-sign — counter-sign: An Open Protocol for Agent-to-Human Authorization</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Defines EP-QUORUM, a multi-party authorization profile for EMILIA Protocol authorization receipts; extends the base receipt (which binds one human to one action) to require a quorum of named human approvals before an action may proceed, with configurable thresholds, role requirements, and time-bounded approval windows.</t>
+          <t>Defines a protocol where agents sign intent objects for consequential actions and humans return cryptographic countersignatures (approve/reject); includes an Enrollment Registry binding actors to signing keys, quorum models for multi-approver scenarios, and tamper-evident receipt logs. Explicitly out of scope for agent-to-service auth — addresses the 'human approval cannot be forged after the fact' problem.</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-quorum/</t>
+          <t>https://datatracker.ietf.org/doc/draft-kumaresan-counter-sign/</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, Jul 2026. The enterprise governance complement to the base EP receipt; relevant for high-risk regulated workflows (financial transactions, medical orders, critical infrastructure changes) where single-human authorization is insufficient. Rev-02 indicates active iteration.</t>
+          <t>Revision -00, Jul 21 2026; author: Kumaresan. Human-countersignature model makes it a direct complement to the EMILIA Protocol family (schrock-ep-*) and to draft-sato-soos-hem (HEM) — EMILIA and HEM handle the pre-execution authorization decision, counter-sign handles the cryptographic non-repudiation that the human approval actually happened. The Enrollment Registry is analogous to WebBotAuth's Signature Agent Card registry but for human approvers.</t>
         </is>
       </c>
     </row>
@@ -4315,17 +4315,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>draft-schrock-ep-evidence-record — Long-Term, Crypto-Agile Preservation of Authorization Evidence (EP-EVIDENCE-RECORD)</t>
+          <t>draft-thallapelly-oasnt — OASNT: Attested Action Authorization Tokens</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>Defines a long-term, crypto-agile record format for preserving EMILIA Protocol authorization evidence under regulatory retention mandates; addresses algorithm deprecation over multi-year retention periods (DORA 5-year, HIPAA 6-year, SEC 17a-4 requirements) using a re-signing model that preserves evidentiary chain of custody.</t>
+          <t>Defines a JWS-based single-use, short-lived token binding a specific human-approved action to the exact rendered disclosure text the approver saw — 'What You See Is What You Sign' (WYSIWYG) — with optional binding to a concrete HTTP request. Requires hardware-resident secure element signature and device runtime integrity assessment.</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-evidence-record/</t>
+          <t>https://datatracker.ietf.org/doc/draft-thallapelly-oasnt/</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, Jul 2026. The regulatory compliance layer for EMILIA Protocol; directly connects to the kuehlewind-audit-architecture HUB (corpus) requirement for audit evidence that survives algorithm sunset. The DORA/HIPAA/SEC citation grounds the spec in concrete regulatory obligations.</t>
+          <t>Revision -02, 15 Aug 2026 (was -01, Jul 24 2026) (first filed Jul 21 2026); author: Thallapelly. Hardware-bound, WYSIWYG authorization token — distinct from software-only pre-action permit approaches such as draft-kumaresan-counter-sign (above) and the EMILIA Protocol family. The WYSIWYG disclosure binding addresses UI redress attacks where an agent's rendered action description differs from the actual HTTP request being authorized. Hardware PoP requirement makes this the highest-assurance pre-action permit in the current wave.</t>
         </is>
       </c>
     </row>
@@ -4345,17 +4345,17 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>draft-kumaresan-counter-sign — counter-sign: An Open Protocol for Agent-to-Human Authorization</t>
+          <t>draft-tsyrulnikov-rats-attested-inference-receipt — Attested Inference Receipt (AIR): A COSE/CWT Profile for Confidential AI Inference</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>Defines a protocol where agents sign intent objects for consequential actions and humans return cryptographic countersignatures (approve/reject); includes an Enrollment Registry binding actors to signing keys, quorum models for multi-approver scenarios, and tamper-evident receipt logs. Explicitly out of scope for agent-to-service auth — addresses the 'human approval cannot be forged after the fact' problem.</t>
+          <t>Defines the Attested Inference Receipt (AIR), a COSE_Sign1 envelope carrying CWT claims profiled per the Entity Attestation Token (EAT) framework; an AIR receipt cryptographically binds model identity, input/output hashes, TEE attestation evidence, and operational telemetry into a single signed artifact verifiable by parties not present at inference time.</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-kumaresan-counter-sign/</t>
+          <t>https://datatracker.ietf.org/doc/draft-tsyrulnikov-rats-attested-inference-receipt/</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, Jul 21 2026; author: Kumaresan. Human-countersignature model makes it a direct complement to the EMILIA Protocol family (schrock-ep-*) and to draft-sato-soos-hem (HEM) — EMILIA and HEM handle the pre-execution authorization decision, counter-sign handles the cryptographic non-repudiation that the human approval actually happened. The Enrollment Registry is analogous to WebBotAuth's Signature Agent Card registry but for human approvers.</t>
+          <t>Revision -02, Jul 2026. The RATS-layer complement to the SCITT profiles in corpus: where SCITT profiles (mih-scitt-agent-action-capsule, marques-asqav-compliance-receipts) record authorization and governance events, AIR records what the model actually computed — model identity, I/O content hashes, and TEE attestation linking the computation to trusted hardware. Together they address the full audit evidence stack.</t>
         </is>
       </c>
     </row>
@@ -4375,17 +4375,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>draft-thallapelly-oasnt — OASNT: Attested Action Authorization Tokens</t>
+          <t>draft-sato-soos-mjwt — The Mandate JWT (MJWT) for Agentic AI Systems</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Defines a JWS-based single-use, short-lived token binding a specific human-approved action to the exact rendered disclosure text the approver saw — 'What You See Is What You Sign' (WYSIWYG) — with optional binding to a concrete HTTP request. Requires hardware-resident secure element signature and device runtime integrity assessment.</t>
+          <t>Introduces the Mandate JWT — a WIMSE workload credential profile binding agent authority to specific Sovereign Object instances under named human principals, with cryptographically enforced delegation ceilings and a six-dimensional Narrowing Property preventing sub-agents from exceeding root authority.</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-thallapelly-oasnt/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sato-soos-mjwt/</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 15 Aug 2026 (was -01, Jul 24 2026) (first filed Jul 21 2026); author: Thallapelly. Hardware-bound, WYSIWYG authorization token — distinct from software-only pre-action permit approaches such as draft-kumaresan-counter-sign (above) and the EMILIA Protocol family. The WYSIWYG disclosure binding addresses UI redress attacks where an agent's rendered action description differs from the actual HTTP request being authorized. Hardware PoP requirement makes this the highest-assurance pre-action permit in the current wave.</t>
+          <t>Revision -04, 13 Aug 2026 (was -01, 10 Jun 2026); author: Tom Sato (MyAuberge K.K.). The authorization token primitive for the SOOS governance protocol family. Directly comparable to draft-mcguinness-oauth-client-instance-assertion but uses a WIMSE/Sovereign Object substrate rather than OAuth.</t>
         </is>
       </c>
     </row>
@@ -4405,17 +4405,17 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>draft-tsyrulnikov-rats-attested-inference-receipt — Attested Inference Receipt (AIR): A COSE/CWT Profile for Confidential AI Inference</t>
+          <t>draft-sato-soos-mad — Multi-Agent Delegation in Sovereign Object Systems</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Defines the Attested Inference Receipt (AIR), a COSE_Sign1 envelope carrying CWT claims profiled per the Entity Attestation Token (EAT) framework; an AIR receipt cryptographically binds model identity, input/output hashes, TEE attestation evidence, and operational telemetry into a single signed artifact verifiable by parties not present at inference time.</t>
+          <t>Specifies three core mechanisms for multi-agent delegation accountability: the Narrowing Property (capability non-amplification), five formally defined object topology patterns for runtime relationships, and cluster coordination primitives for parallel execution with aggregation rules. Version 02 adds revocation-during-execution handling and partial-completion routing to human oversight.</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-tsyrulnikov-rats-attested-inference-receipt/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sato-soos-mad/</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, Jul 2026. The RATS-layer complement to the SCITT profiles in corpus: where SCITT profiles (mih-scitt-agent-action-capsule, marques-asqav-compliance-receipts) record authorization and governance events, AIR records what the model actually computed — model identity, I/O content hashes, and TEE attestation linking the computation to trusted hardware. Together they address the full audit evidence stack.</t>
+          <t>Revision -02, 10 Jun 2026; author: Tom Sato (MyAuberge K.K.). Claims to address gaps the OpenID Foundation identifies as unsolved in multi-agent authorization. The five topology patterns are a useful vocabulary for describing agent-to-agent relationship structures.</t>
         </is>
       </c>
     </row>
@@ -4435,17 +4435,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>draft-sato-soos-mjwt — The Mandate JWT (MJWT) for Agentic AI Systems</t>
+          <t>draft-sato-soos-hem — The Human Escalation Mechanism (HEM) for Agentic AI Systems</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Introduces the Mandate JWT — a WIMSE workload credential profile binding agent authority to specific Sovereign Object instances under named human principals, with cryptographically enforced delegation ceilings and a six-dimensional Narrowing Property preventing sub-agents from exceeding root authority.</t>
+          <t>Defines a kernel-enforced mechanism placing agent sessions in a pending state when human judgment is required, routing structured escalation requests to designated human decision-makers, and prohibiting all state transitions until a human decision is received. Defines five decision types and a dual-layer architecture (LLM-HEM and SOOS-HEM).</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sato-soos-mjwt/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sato-soos-hem/</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>Revision -04, 13 Aug 2026 (was -01, 10 Jun 2026); author: Tom Sato (MyAuberge K.K.). The authorization token primitive for the SOOS governance protocol family. Directly comparable to draft-mcguinness-oauth-client-instance-assertion but uses a WIMSE/Sovereign Object substrate rather than OAuth.</t>
+          <t>Revision -05, 30 Jun 2026 (was -04 Jun 2026); author: Tom Sato (MyAuberge K.K.). The most normative HITL protocol in the current wave; explicitly aligns with EU AI Act Article 14 requirements for high-risk AI system oversight. Counterpart to ARAP (AuthZEN WG) at the protocol level vs. the OAuth/AuthZEN layer.</t>
         </is>
       </c>
     </row>
@@ -4465,17 +4465,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>draft-sato-soos-mad — Multi-Agent Delegation in Sovereign Object Systems</t>
+          <t>draft-sato-soos-idp — The Intent Declaration Primitive (IDP) for Agentic AI Systems</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>Specifies three core mechanisms for multi-agent delegation accountability: the Narrowing Property (capability non-amplification), five formally defined object topology patterns for runtime relationships, and cluster coordination primitives for parallel execution with aggregation rules. Version 02 adds revocation-during-execution handling and partial-completion routing to human oversight.</t>
+          <t>Specifies a structured declaration mechanism committing AI agent intent to tamper-evident logs before actions are taken, enabling post-hoc review and EU AI Act Article 12 compliance for high-risk systems.</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sato-soos-mad/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sato-soos-idp/</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 10 Jun 2026; author: Tom Sato (MyAuberge K.K.). Claims to address gaps the OpenID Foundation identifies as unsolved in multi-agent authorization. The five topology patterns are a useful vocabulary for describing agent-to-agent relationship structures.</t>
+          <t>Revision -05, 30 Jun 2026 (was -04 Jun 2026); author: Tom Sato (MyAuberge K.K.). The log-before-execute pattern mirrors draft-nelson-agent-delegation-receipts but operates at the intent declaration level rather than the user-authorization level. Pairs with GAR (below) to form a complete pre/post audit trail.</t>
         </is>
       </c>
     </row>
@@ -4495,17 +4495,17 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>draft-sato-soos-hem — The Human Escalation Mechanism (HEM) for Agentic AI Systems</t>
+          <t>draft-sato-soos-gar — The Governance Audit Record (GAR) for Agentic AI Systems</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>Defines a kernel-enforced mechanism placing agent sessions in a pending state when human judgment is required, routing structured escalation requests to designated human decision-makers, and prohibiting all state transitions until a human decision is received. Defines five decision types and a dual-layer architecture (LLM-HEM and SOOS-HEM).</t>
+          <t>Defines GAR, an audit framework with five audit types, a Session Audit Record, and an Audit Alert mechanism; collects, signs, and makes governance events from IDP, HEM, and associated SOOS primitives available for regulatory inspection via an append-only, non-suppressible SCITT-anchored audit stream with Authority Lifecycle Events covering the complete revocation-recovery cycle.</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sato-soos-hem/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sato-soos-gar/</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>Revision -05, 30 Jun 2026 (was -04 Jun 2026); author: Tom Sato (MyAuberge K.K.). The most normative HITL protocol in the current wave; explicitly aligns with EU AI Act Article 14 requirements for high-risk AI system oversight. Counterpart to ARAP (AuthZEN WG) at the protocol level vs. the OAuth/AuthZEN layer.</t>
+          <t>Revision -06, 25 Aug 2026 (was -03, 28 Jun 2026) (was -02 Jun 10). -03 added OpenTelemetry attribute namespace for governance observability, a GAR Processor spec for converting OTel signals to audit records with integrity verification, four new Authority Lifecycle Event categories (policy conflict scenarios, statutory interpretation changes), and mandatory provenance fields for policy evaluation records. The integrator for the SOOS family, analogous to how draft-kuehlewind-audit-architecture integrates the broader IETF agent draft landscape.</t>
         </is>
       </c>
     </row>
@@ -4525,17 +4525,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>draft-sato-soos-idp — The Intent Declaration Primitive (IDP) for Agentic AI Systems</t>
+          <t>draft-jiang-intent-security — Security Considerations and Requirements for Intent-Based Requests in Agentic Systems</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>Specifies a structured declaration mechanism committing AI agent intent to tamper-evident logs before actions are taken, enabling post-hoc review and EU AI Act Article 12 compliance for high-risk systems.</t>
+          <t>Solution-agnostic threat analysis covering tampering, privilege escalation, constraint violations, and intent drift in intent-based agentic systems, with a reference model, attack scenarios, and security requirements covering authentication, admission control, constraint validation, and multi-hop integrity.</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sato-soos-idp/</t>
+          <t>https://datatracker.ietf.org/doc/draft-jiang-intent-security/</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>Revision -05, 30 Jun 2026 (was -04 Jun 2026); author: Tom Sato (MyAuberge K.K.). The log-before-execute pattern mirrors draft-nelson-agent-delegation-receipts but operates at the intent declaration level rather than the user-authorization level. Pairs with GAR (below) to form a complete pre/post audit trail.</t>
+          <t>Revision -03, 22 Jun 2026; authors: Yuning Jiang, Lun Li, Yurong Song, Faye Liu (Huawei). The threat-model companion to draft-jiang-oauth-intent-admission from the same group; likely intended to inform the broader IETF agentic AI security discussion.</t>
         </is>
       </c>
     </row>
@@ -4555,17 +4555,17 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>draft-sato-soos-gar — The Governance Audit Record (GAR) for Agentic AI Systems</t>
+          <t>draft-haberkamp-ipp — Intent Provenance Protocol (IPP)</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>Defines GAR, an audit framework with five audit types, a Session Audit Record, and an Audit Alert mechanism; collects, signs, and makes governance events from IDP, HEM, and associated SOOS primitives available for regulatory inspection via an append-only, non-suppressible SCITT-anchored audit stream with Authority Lifecycle Events covering the complete revocation-recovery cycle.</t>
+          <t>Specifies a cryptographic infrastructure standard for carrying verified human intent through chains of autonomous AI agent actions; defines the Intent Token, a signed, bounded, and tamper-evident data structure that travels with every agentic action so downstream agents and resource servers can verify that the chain traces to a real human authorization.</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sato-soos-gar/</t>
+          <t>https://datatracker.ietf.org/doc/draft-haberkamp-ipp/</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>Revision -06, 25 Aug 2026 (was -03, 28 Jun 2026) (was -02 Jun 10). -03 added OpenTelemetry attribute namespace for governance observability, a GAR Processor spec for converting OTel signals to audit records with integrity verification, four new Authority Lifecycle Event categories (policy conflict scenarios, statutory interpretation changes), and mandatory provenance fields for policy evaluation records. The integrator for the SOOS family, analogous to how draft-kuehlewind-audit-architecture integrates the broader IETF agent draft landscape.</t>
+          <t>Revision -01, Jul 2026. Addresses the 'intent drift' threat class from draft-jiang-intent-security (corpus) with a concrete token artifact; complements the EMILIA Protocol receipts (authorization at the action level) with an intent record at the delegation chain level. The traveling Intent Token model is distinct from both SOOS Mandate JWTs (Sato, governance substrate) and McGuinness Actor Profiles (delegation chain encoding in existing OAuth tokens).</t>
         </is>
       </c>
     </row>
@@ -4585,17 +4585,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>draft-jiang-intent-security — Security Considerations and Requirements for Intent-Based Requests in Agentic Systems</t>
+          <t>draft-li-dmsc-macp — Multi-agent Collaboration Protocol Suites Architecture</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>Solution-agnostic threat analysis covering tampering, privilege escalation, constraint violations, and intent drift in intent-based agentic systems, with a reference model, attack scenarios, and security requirements covering authentication, admission control, constraint validation, and multi-hop integrity.</t>
+          <t>Defines a protocol suite and architectural framework for secure, scalable multi-agent collaboration covering trusted agent onboarding, capability-based discovery, distributed capability synchronization, and secure agent-to-agent interaction. Specifies a gateway-centric architecture where an Agent Gateway mediates capability negotiation and trust establishment between collaborating agents.</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-jiang-intent-security/</t>
+          <t>https://datatracker.ietf.org/doc/draft-li-dmsc-macp/</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, 22 Jun 2026; authors: Yuning Jiang, Lun Li, Yurong Song, Faye Liu (Huawei). The threat-model companion to draft-jiang-oauth-intent-admission from the same group; likely intended to inform the broader IETF agentic AI security discussion.</t>
+          <t>Revision -06, Jul 20 2026; active; authors: Xueting Li (China Telecom), Bing Liu (Huawei), Jun Liu (Beijing U of Posts &amp; Telecom), Chenguang Du (Tsinghua), Lianhua Zhang (AsiaInfo). Replaces draft-li-dmsc-mcps-agw. Anchors a DMSC family of companion drafts covering intent-based interconnection, task protocol, gateway directory sync, semantic interaction, and gateway requirements. No explicit OAuth or WIMSE dependencies — operates at the agent coordination layer above transport, below authorization.</t>
         </is>
       </c>
     </row>
@@ -4615,17 +4615,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>draft-haberkamp-ipp — Intent Provenance Protocol (IPP)</t>
+          <t>draft-li-dmsc-inf-architecture — Dynamic Multi-agent Secured Collaboration Infrastructure Architecture</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>Specifies a cryptographic infrastructure standard for carrying verified human intent through chains of autonomous AI agent actions; defines the Intent Token, a signed, bounded, and tamper-evident data structure that travels with every agentic action so downstream agents and resource servers can verify that the chain traces to a real human authorization.</t>
+          <t>Approaches DMSC from the network-infrastructure perspective: proposes capability-based forwarding and semantic routing at the network layer, where agent capability metadata influences packet-forwarding decisions rather than routing based solely on addresses. The most mature DMSC document at rev 07; predates and informs the MACP architecture draft.</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-haberkamp-ipp/</t>
+          <t>https://datatracker.ietf.org/doc/draft-li-dmsc-inf-architecture/</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, Jul 2026. Addresses the 'intent drift' threat class from draft-jiang-intent-security (corpus) with a concrete token artifact; complements the EMILIA Protocol receipts (authorization at the action level) with an intent record at the delegation chain level. The traveling Intent Token model is distinct from both SOOS Mandate JWTs (Sato, governance substrate) and McGuinness Actor Profiles (delegation chain encoding in existing OAuth tokens).</t>
+          <t>Revision -07, May 22 2026; authors: Xueting Li (China Telecom), Aijun Wang (China Telecom), Bing Liu (Huawei), Changwang Lin (New H3C). Infrastructure-layer complement to draft-li-dmsc-macp (protocol suite). The DMSC family now has 14+ companion drafts from Chinese telecom/academic groups — this is the architectural anchor.</t>
         </is>
       </c>
     </row>
@@ -4645,17 +4645,17 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>draft-li-dmsc-macp — Multi-agent Collaboration Protocol Suites Architecture</t>
+          <t>draft-sz-dmsc-iaip — Intent-based Agent Interconnection Protocol at Agent Gateway</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>Defines a protocol suite and architectural framework for secure, scalable multi-agent collaboration covering trusted agent onboarding, capability-based discovery, distributed capability synchronization, and secure agent-to-agent interaction. Specifies a gateway-centric architecture where an Agent Gateway mediates capability negotiation and trust establishment between collaborating agents.</t>
+          <t>Defines semantic capability advertisement and intent-driven routing at DMSC agent gateways: agents publish capability profiles in a structured format and the gateway matches incoming task intents to available agents, replacing fixed-address routing with dynamic semantic matching. The core routing-layer protocol for DMSC inter-agent communication.</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-li-dmsc-macp/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sz-dmsc-iaip/</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>Revision -06, Jul 20 2026; active; authors: Xueting Li (China Telecom), Bing Liu (Huawei), Jun Liu (Beijing U of Posts &amp; Telecom), Chenguang Du (Tsinghua), Lianhua Zhang (AsiaInfo). Replaces draft-li-dmsc-mcps-agw. Anchors a DMSC family of companion drafts covering intent-based interconnection, task protocol, gateway directory sync, semantic interaction, and gateway requirements. No explicit OAuth or WIMSE dependencies — operates at the agent coordination layer above transport, below authorization.</t>
+          <t>Revision -02, May 2026; authors: Sheng Sun, Xinyi Zhang (CAS/CNIC), Qiangzhou Gao (Huawei), Min Liu, Yuwei Wang (ICT, CAS). The intent-based routing mechanism that distinguishes DMSC from address-based protocols; relevant to the DAWN boundary question — DMSC embeds discovery in the gateway routing layer rather than treating it as a separate protocol.</t>
         </is>
       </c>
     </row>
@@ -4675,17 +4675,17 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>draft-li-dmsc-inf-architecture — Dynamic Multi-agent Secured Collaboration Infrastructure Architecture</t>
+          <t>draft-yang-dmsc-ioa-task-protocol — Internet of Agents Task Protocol for Heterogeneous Agent Collaboration</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>Approaches DMSC from the network-infrastructure perspective: proposes capability-based forwarding and semantic routing at the network layer, where agent capability metadata influences packet-forwarding decisions rather than routing based solely on addresses. The most mature DMSC document at rev 07; predates and informs the MACP architecture draft.</t>
+          <t>Establishes a session and task coordination layer with finite-state-machine-based dialogue management, dynamic team assembly, and nested team hierarchies for distributed heterogeneous agent collaboration. Addresses the multi-agent task lifecycle from assignment through completion and audit across heterogeneous agent implementations.</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-li-dmsc-inf-architecture/</t>
+          <t>https://datatracker.ietf.org/doc/draft-yang-dmsc-ioa-task-protocol/</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>Revision -07, May 22 2026; authors: Xueting Li (China Telecom), Aijun Wang (China Telecom), Bing Liu (Huawei), Changwang Lin (New H3C). Infrastructure-layer complement to draft-li-dmsc-macp (protocol suite). The DMSC family now has 14+ companion drafts from Chinese telecom/academic groups — this is the architectural anchor.</t>
+          <t>Revision -03, Apr 21 2026; authors: Cheng Yang (BUPT), Zhiyuan Liu (Tsinghua), Aijun Wang (China Telecom). The task-coordination layer above the DMSC gateway routing; covers multi-domain and 6G/ITS scenarios. Distinct from OAuth-layer delegation in that it orchestrates task state rather than token issuance.</t>
         </is>
       </c>
     </row>
@@ -4705,17 +4705,17 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>draft-sz-dmsc-iaip — Intent-based Agent Interconnection Protocol at Agent Gateway</t>
+          <t>draft-dunbar-dmsc-gw-scenarios-gap-analysis — Deployment Scenarios and Gap Analysis for AI Agent Gateway</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>Defines semantic capability advertisement and intent-driven routing at DMSC agent gateways: agents publish capability profiles in a structured format and the gateway matches incoming task intents to available agents, replacing fixed-address routing with dynamic semantic matching. The core routing-layer protocol for DMSC inter-agent communication.</t>
+          <t>Surveys single-domain to multi-domain deployment scenarios for AI Agent Gateways and identifies concrete gaps where existing protocols (specifically MCP and Google's A2A) cannot satisfy governance, policy enforcement, and cross-organizational trust requirements — particularly in regulated financial services and telecom environments.</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sz-dmsc-iaip/</t>
+          <t>https://datatracker.ietf.org/doc/draft-dunbar-dmsc-gw-scenarios-gap-analysis/</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, May 2026; authors: Sheng Sun, Xinyi Zhang (CAS/CNIC), Qiangzhou Gao (Huawei), Min Liu, Yuwei Wang (ICT, CAS). The intent-based routing mechanism that distinguishes DMSC from address-based protocols; relevant to the DAWN boundary question — DMSC embeds discovery in the gateway routing layer rather than treating it as a separate protocol.</t>
+          <t>Revision -04, 14 Aug 2026 (was -03, 7 Aug 2026) (was -02, Jul 2 2026); authors: Linda Dunbar (Futurewei), YiFei Wang (China Telecom), Bing Liu (Huawei). The most directly useful DMSC document for the boundary analysis: explicitly names MCP and A2A as insufficient and articulates where the DMSC gateway fills the gap. The regulated-environment focus (financial services, telco) distinguishes DMSC's use-case target from OAuth-centric approaches.</t>
         </is>
       </c>
     </row>
@@ -4735,17 +4735,17 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>draft-yang-dmsc-ioa-task-protocol — Internet of Agents Task Protocol for Heterogeneous Agent Collaboration</t>
+          <t>draft-somoza-dmsc-atn-agent-trust-negotiation — Agent Trust Negotiation: Capability, Delegation, and Provenance Binding</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>Establishes a session and task coordination layer with finite-state-machine-based dialogue management, dynamic team assembly, and nested team hierarchies for distributed heterogeneous agent collaboration. Addresses the multi-agent task lifecycle from assignment through completion and audit across heterogeneous agent implementations.</t>
+          <t>Specifies the Agent Trust Negotiation (ATN) protocol, which binds four artifacts — capability manifests, delegation chains, provenance attestations, and session receipts — to agent identities via a handshake state machine producing mutually verified, scope-bounded sessions with SCITT-suitable audit records.</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-yang-dmsc-ioa-task-protocol/</t>
+          <t>https://datatracker.ietf.org/doc/draft-somoza-dmsc-atn-agent-trust-negotiation/</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, Apr 21 2026; authors: Cheng Yang (BUPT), Zhiyuan Liu (Tsinghua), Aijun Wang (China Telecom). The task-coordination layer above the DMSC gateway routing; covers multi-domain and 6G/ITS scenarios. Distinct from OAuth-layer delegation in that it orchestrates task state rather than token issuance.</t>
+          <t>Revision -00, 29 May 2026; author: Enrique Somoza (Independent). Operates above discovery mechanisms and positions itself between the discovery layer (DAWN, MCP) and the authorization layer (WIMSE, OAuth). Relevant as an agent-to-agent trust establishment handshake protocol. **SUPERSEDES draft-somoza-atn-agent-trust-negotiation**, which Datatracker marks Replaced by this draft. That older row was removed from the corpus on 26 Aug 2026 — it was tracked separately and had become a duplicate of this one under the pre-rename slug.</t>
         </is>
       </c>
     </row>
@@ -4765,17 +4765,17 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>draft-dunbar-dmsc-gw-scenarios-gap-analysis — Deployment Scenarios and Gap Analysis for AI Agent Gateway</t>
+          <t>draft-mcgraw-httpapi-agent-budget — The Delegation HTTP Authentication Scheme for Request-Bound Authority</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>Surveys single-domain to multi-domain deployment scenarios for AI Agent Gateways and identifies concrete gaps where existing protocols (specifically MCP and Google's A2A) cannot satisfy governance, policy enforcement, and cross-organizational trust requirements — particularly in regulated financial services and telecom environments.</t>
+          <t>Defines the 'Delegation' HTTP authentication scheme and response semantics for delegated-authority challenges using HTTP status codes and Problem Details, plus a CBOR/COSE proof format. The initial authority profile is 'Budget,' using post-quantum ML-DSA to prove spending or resource-consumption limits.</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-dunbar-dmsc-gw-scenarios-gap-analysis/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcgraw-httpapi-agent-budget/</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>Revision -04, 14 Aug 2026 (was -03, 7 Aug 2026) (was -02, Jul 2 2026); authors: Linda Dunbar (Futurewei), YiFei Wang (China Telecom), Bing Liu (Huawei). The most directly useful DMSC document for the boundary analysis: explicitly names MCP and A2A as insufficient and articulates where the DMSC gateway fills the gap. The regulated-environment focus (financial services, telco) distinguishes DMSC's use-case target from OAuth-centric approaches.</t>
+          <t>Revision -02, 15 Jun 2026; author: John Paul McGraw Jr. (TaskHawk Systems). HTTP-layer bounded delegation with post-quantum crypto; distinct from OAuth-layer delegation in that the authority proof travels in the Authorization header. Complements x401 (Industry tab) at the HTTP challenge-response layer.</t>
         </is>
       </c>
     </row>
@@ -4795,17 +4795,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>draft-somoza-dmsc-atn-agent-trust-negotiation — Agent Trust Negotiation: Capability, Delegation, and Provenance Binding</t>
+          <t>draft-vauban-x402-delegation-binding — x402 Delegation Binding for Agentic HTTP Pipelines</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>Specifies the Agent Trust Negotiation (ATN) protocol, which binds four artifacts — capability manifests, delegation chains, provenance attestations, and session receipts — to agent identities via a handshake state machine producing mutually verified, scope-bounded sessions with SCITT-suitable audit records.</t>
+          <t>Addresses the security gap where x402 V2 payment grants issued to one agent could be misused by another in the same pipeline, introducing three binding mechanisms: a JCS-derived agent identity pseudonym, a nonce for anti-replay, and a depth-limiting field for transitive delegation.</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-somoza-dmsc-atn-agent-trust-negotiation/</t>
+          <t>https://datatracker.ietf.org/doc/draft-vauban-x402-delegation-binding/</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 29 May 2026; author: Enrique Somoza (Independent). Operates above discovery mechanisms and positions itself between the discovery layer (DAWN, MCP) and the authorization layer (WIMSE, OAuth). Relevant as an agent-to-agent trust establishment handshake protocol.</t>
+          <t>Revision -01, 25 May 2026; author: Vauban Research. Narrowly scoped to payment pipelines but the delegation-binding pattern (pseudonymous identity + anti-replay + depth-limit) is applicable broadly. Validated across five language runtimes with A2A and MCP integration guidance.</t>
         </is>
       </c>
     </row>
@@ -4825,17 +4825,17 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>draft-mcgraw-httpapi-agent-budget — The Delegation HTTP Authentication Scheme for Request-Bound Authority</t>
+          <t>draft-samal-vap — Verifiable Agent Protocol (VAP): Intent-Bound Admission Control and Audit for Agent Tool Invocation</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>Defines the 'Delegation' HTTP authentication scheme and response semantics for delegated-authority challenges using HTTP status codes and Problem Details, plus a CBOR/COSE proof format. The initial authority profile is 'Budget,' using post-quantum ML-DSA to prove spending or resource-consumption limits.</t>
+          <t>Specifies VAP as a defense-in-depth layer adding declarations of purpose and session budget commitments to tool invocation requests (targeting MCP-style protocols), enabling servers to perform admission control before execution via four messages carried in existing protocol metadata.</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcgraw-httpapi-agent-budget/</t>
+          <t>https://datatracker.ietf.org/doc/draft-samal-vap/</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 15 Jun 2026; author: John Paul McGraw Jr. (TaskHawk Systems). HTTP-layer bounded delegation with post-quantum crypto; distinct from OAuth-layer delegation in that the authority proof travels in the Authorization header. Complements x401 (Industry tab) at the HTTP challenge-response layer.</t>
+          <t>Revision -00, 3 Jun 2026; author: Kruttidipta Samal (Independent). Lightweight and protocol-agnostic; addresses erroneous agent behavior, cost control, and audit trails without replacing existing auth mechanisms. Practical tool-invocation-level authorization layer for MCP deployments.</t>
         </is>
       </c>
     </row>
@@ -4855,17 +4855,17 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>draft-vauban-x402-delegation-binding — x402 Delegation Binding for Agentic HTTP Pipelines</t>
+          <t>draft-khera-aurora — Agent Unification, Runtime, and Operational Responsibility Attestation (AURORA)</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>Addresses the security gap where x402 V2 payment grants issued to one agent could be misused by another in the same pipeline, introducing three binding mechanisms: a JCS-derived agent identity pseudonym, a nonce for anti-replay, and a depth-limiting field for transitive delegation.</t>
+          <t>A two-layer framework unifying hardware-enclave-backed Runtime Integrity Attestation with scoped, cryptographically bound Authority Delegation; enables agents to prove both operational authority and runtime integrity simultaneously.</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-vauban-x402-delegation-binding/</t>
+          <t>https://datatracker.ietf.org/doc/draft-khera-aurora/</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 25 May 2026; author: Vauban Research. Narrowly scoped to payment pipelines but the delegation-binding pattern (pseudonymous identity + anti-replay + depth-limit) is applicable broadly. Validated across five language runtimes with A2A and MCP integration guidance.</t>
+          <t>Revision -00, 5 Jun 2026; author: Ankur Khera. Addresses the gap where delegation tokens don't prove the runtime environment is trustworthy — relevant where delegation must be paired with platform attestation (enterprise/regulated deployments). Bridges the RATS attestation thread and the OAuth delegation thread.</t>
         </is>
       </c>
     </row>
@@ -4885,17 +4885,17 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>draft-samal-vap — Verifiable Agent Protocol (VAP): Intent-Bound Admission Control and Audit for Agent Tool Invocation</t>
+          <t>draft-borthwick-msebenzi-environment-state — Verifiable Intent — environment.* Constraint Family</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>Specifies VAP as a defense-in-depth layer adding declarations of purpose and session budget commitments to tool invocation requests (targeting MCP-style protocols), enabling servers to perform admission control before execution via four messages carried in existing protocol metadata.</t>
+          <t>Defines the environment.* constraint family for agent-authorization mandate vocabularies, covering external conditions at transaction execution time (venue availability, wallet funding) that existing transactional constraints cannot address. Extends agent authorization mandate frameworks with environmental precondition checking.</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-samal-vap/</t>
+          <t>https://datatracker.ietf.org/doc/draft-borthwick-msebenzi-environment-state/</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 3 Jun 2026; author: Kruttidipta Samal (Independent). Lightweight and protocol-agnostic; addresses erroneous agent behavior, cost control, and audit trails without replacing existing auth mechanisms. Practical tool-invocation-level authorization layer for MCP deployments.</t>
+          <t>Revision -01, 13 Jun 2026; authors: Douglas Cameron Borthwick (InsumerAPI), Michael Msebenzi (Headless Oracle). Narrow but practically important for financial and commerce agent workflows; connects to draft-mcgraw-httpapi-agent-budget and draft-vauban-x402-delegation-binding.</t>
         </is>
       </c>
     </row>
@@ -4915,17 +4915,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>draft-khera-aurora — Agent Unification, Runtime, and Operational Responsibility Attestation (AURORA)</t>
+          <t>draft-chen-oauth-agent-authz-use-cases — Agent Authorization Use Cases and Gap Analysis for OAuth 2.0</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>A two-layer framework unifying hardware-enclave-backed Runtime Integrity Attestation with scoped, cryptographically bound Authority Delegation; enables agents to prove both operational authority and runtime integrity simultaneously.</t>
+          <t>A framework-level analysis enumerating agentic authorization use cases — delegated task execution, multi-agent coordination, long-running workflows, capability attenuation — and mapping each against current OAuth 2.0 mechanisms to identify gaps that require new extensions or profiles.</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-khera-aurora/</t>
+          <t>https://datatracker.ietf.org/doc/draft-chen-oauth-agent-authz-use-cases/</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 5 Jun 2026; author: Ankur Khera. Addresses the gap where delegation tokens don't prove the runtime environment is trustworthy — relevant where delegation must be paired with platform attestation (enterprise/regulated deployments). Bridges the RATS attestation thread and the OAuth delegation thread.</t>
+          <t>Revision -03, 25 Aug 2026 (was -01, 5 Jul 2026); useful problem-statement companion to the OAuth recharter's 'Complex Delegation' milestone. Gap analysis directly motivates several other drafts in this corpus — a natural reference document for the OAuth WG scoping discussion.</t>
         </is>
       </c>
     </row>
@@ -4945,17 +4945,17 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>draft-borthwick-msebenzi-environment-state — Verifiable Intent — environment.* Constraint Family</t>
+          <t>draft-agnihotri-oauth-agent-impl-status — Implementation Status of OAuth Identity Chaining and Transaction Tokens</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>Defines the environment.* constraint family for agent-authorization mandate vocabularies, covering external conditions at transaction execution time (venue availability, wallet funding) that existing transactional constraints cannot address. Extends agent authorization mandate frameworks with environmental precondition checking.</t>
+          <t>An RFC 7942–compliant implementation status report tracking open-source implementations of draft-ietf-oauth-identity-chaining and draft-ietf-oauth-transaction-tokens against the relevant spec requirements.</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-borthwick-msebenzi-environment-state/</t>
+          <t>https://datatracker.ietf.org/doc/draft-agnihotri-oauth-agent-impl-status/</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 13 Jun 2026; authors: Douglas Cameron Borthwick (InsumerAPI), Michael Msebenzi (Headless Oracle). Narrow but practically important for financial and commerce agent workflows; connects to draft-mcgraw-httpapi-agent-budget and draft-vauban-x402-delegation-binding.</t>
+          <t>Revision -02, Jun 2026; provides the implementation evidence required to advance both WG drafts toward IESG submission. Informational companion to the two WG drafts — not a protocol spec but tracking their standardization progress.</t>
         </is>
       </c>
     </row>
@@ -4975,17 +4975,17 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>draft-chen-oauth-agent-authz-use-cases — Agent Authorization Use Cases and Gap Analysis for OAuth 2.0</t>
+          <t>draft-hardt-oauth-aauth-protocol — AAuth Protocol</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>A framework-level analysis enumerating agentic authorization use cases — delegated task execution, multi-agent coordination, long-running workflows, capability attenuation — and mapping each against current OAuth 2.0 mechanisms to identify gaps that require new extensions or profiles.</t>
+          <t>A new clean-sheet authorization protocol from Dick Hardt (original OAuth author) defining proof-of-possession by default, resource-signed challenges, agent identity without pre-registration, deferred 202 responses, and AS-to-AS federation for the agent ecosystem.</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-chen-oauth-agent-authz-use-cases/</t>
+          <t>https://datatracker.ietf.org/doc/draft-hardt-oauth-aauth-protocol/</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, 25 Aug 2026 (was -01, 5 Jul 2026); useful problem-statement companion to the OAuth recharter's 'Complex Delegation' milestone. Gap analysis directly motivates several other drafts in this corpus — a natural reference document for the OAuth WG scoping discussion.</t>
+          <t>Revision -10, 6 Aug 2026 (was -09, Jul 4 2026); slug gained 'oauth' infix at this revision (was draft-hardt-aauth-protocol). Now formally adds four resource access modes including agent governance. The design rationale section explicitly explains why AAuth is not GNAP, not OAuth, not DPoP and not mTLS — important read for anyone planning a new agent-auth stack. OUTLIER: zero OAuth dependencies.</t>
         </is>
       </c>
     </row>
@@ -5005,17 +5005,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>draft-agnihotri-oauth-agent-impl-status — Implementation Status of OAuth Identity Chaining and Transaction Tokens</t>
+          <t>draft-chen-oauth-roadmap — Comprehensive Roadmap for OAuth 2.0 Standards and Drafts</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>An RFC 7942–compliant implementation status report tracking open-source implementations of draft-ietf-oauth-identity-chaining and draft-ietf-oauth-transaction-tokens against the relevant spec requirements.</t>
+          <t>An IETF informational draft that maps the entire OAuth 2.0 ecosystem of RFCs, BCPs, and active drafts into functional layers from core to extensions to industry profiles.</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-agnihotri-oauth-agent-impl-status/</t>
+          <t>https://datatracker.ietf.org/doc/draft-chen-oauth-roadmap/</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, Jun 2026; provides the implementation evidence required to advance both WG drafts toward IESG submission. Informational companion to the two WG drafts — not a protocol spec but tracking their standardization progress.</t>
+          <t>Revision -01, 6 May 2026 (was -00, May 2026); the single most useful index when starting work in this area. Link switched from the pinned -00 archive HTML to the Datatracker document page so it tracks the latest revision.</t>
         </is>
       </c>
     </row>
@@ -5035,27 +5035,27 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>draft-hardt-oauth-aauth-protocol — AAuth Protocol</t>
+          <t>draft-ietf-wimse-workload-creds — WIMSE Workload Credentials</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>A new clean-sheet authorization protocol from Dick Hardt (original OAuth author) defining proof-of-possession by default, resource-signed challenges, agent identity without pre-registration, deferred 202 responses, and AS-to-AS federation for the agent ecosystem.</t>
+          <t>Defines the credential format and issuance profile for workload credentials in the WIMSE architecture, covering service-to-service authentication token types, local issuance mechanisms, and token exchange profiles for cross-trust-domain workload identity scenarios.</t>
         </is>
       </c>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-hardt-oauth-aauth-protocol/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-wimse-workload-creds/</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual)</t>
+          <t>IETF (WIMSE WG)</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>Revision -10, 6 Aug 2026 (was -09, Jul 4 2026); slug gained 'oauth' infix at this revision (was draft-hardt-aauth-protocol). Now formally adds four resource access modes including agent governance. The design rationale section explicitly explains why AAuth is not GNAP, not OAuth, not DPoP and not mTLS — important read for anyone planning a new agent-auth stack. OUTLIER: zero OAuth dependencies.</t>
+          <t>Revision -02, Jul 2026; WIMSE WG-adopted. The credential issuance companion to draft-ietf-wimse-arch (architecture) and draft-ietf-wimse-identifier (identifiers) already in corpus. Three WG drafts now cover the full WIMSE stack: arch → identifier → workload-creds. Relevant to the WIMSE agent extension family (ni-wimse, reece, jiang, schwenkschuster) which assumes a credential format this draft now specifies.</t>
         </is>
       </c>
     </row>
@@ -5065,27 +5065,27 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>draft-chen-oauth-roadmap — Comprehensive Roadmap for OAuth 2.0 Standards and Drafts</t>
+          <t>Charter: WIMSE — Workload Identity in Multi-System Environments (charter-ietf-wimse-01)</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>An IETF informational draft that maps the entire OAuth 2.0 ecosystem of RFCs, BCPs, and active drafts into functional layers from core to extensions to industry profiles.</t>
+          <t>The formal IETF charter for the WIMSE WG covering architecture, JOSE-based WIMSE tokens for service-to-service traffic, local token issuance, and token exchange profiles (likely based on RFC 8693) for cross-trust-domain workload identity.</t>
         </is>
       </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-chen-oauth-roadmap/</t>
+          <t>https://datatracker.ietf.org/doc/charter-ietf-wimse/01/</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual)</t>
+          <t>IETF (WIMSE WG charter)</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 6 May 2026 (was -00, May 2026); the single most useful index when starting work in this area. Link switched from the pinned -00 archive HTML to the Datatracker document page so it tracks the latest revision.</t>
+          <t>Approved 18 March 2026 (v01); explicitly liaises with OAuth, SCIM, SCITT, RATS, the OpenID Foundation, and CNCF/SPIFFE — the formal scope statement that anchors all WIMSE draft work.</t>
         </is>
       </c>
     </row>
@@ -5095,27 +5095,27 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>draft-ietf-wimse-workload-creds — WIMSE Workload Credentials</t>
+          <t>draft-aap-oauth-profile — Agent Authorization Profile (AAP) for OAuth 2.0</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>Defines the credential format and issuance profile for workload credentials in the WIMSE architecture, covering service-to-service authentication token types, local issuance mechanisms, and token exchange profiles for cross-trust-domain workload identity scenarios.</t>
+          <t>This document defines the Agent Authorization Profile (AAP), an authorization profile for OAuth 2.0 and JWT designed for autonomous AI agents. AAP extends existing standards with structured claims and validation rules so that systems can reason about agent identity, task context, operational constraints, delegation chains, and human oversight requirements.</t>
         </is>
       </c>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-wimse-workload-creds/</t>
+          <t>https://datatracker.ietf.org/doc/draft-aap-oauth-profile/</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>IETF (WIMSE WG)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, Jul 2026; WIMSE WG-adopted. The credential issuance companion to draft-ietf-wimse-arch (architecture) and draft-ietf-wimse-identifier (identifiers) already in corpus. Three WG drafts now cover the full WIMSE stack: arch → identifier → workload-creds. Relevant to the WIMSE agent extension family (ni-wimse, reece, jiang, schwenkschuster) which assumes a credential format this draft now specifies.</t>
+          <t>Revision -01, 11 Aug 2026; **now EXPIRED** on Datatracker (checked 26 Aug 2026). Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5125,27 +5125,27 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>Charter: WIMSE — Workload Identity in Multi-System Environments (charter-ietf-wimse-01)</t>
+          <t>draft-ietf-wimse-workload-identity-practices — Workload Identity Practices</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>The formal IETF charter for the WIMSE WG covering architecture, JOSE-based WIMSE tokens for service-to-service traffic, local token issuance, and token exchange profiles (likely based on RFC 8693) for cross-trust-domain workload identity.</t>
+          <t>This document describes industry practices for providing secure identities to workloads in container orchestration, cloud platforms, and other workload platforms. It explains how workloads obtain credentials for external authentication purposes, without managing long-lived secrets directly.</t>
         </is>
       </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/charter-ietf-wimse/01/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-wimse-workload-identity-practices/</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>IETF (WIMSE WG charter)</t>
+          <t>IETF (WIMSE WG)</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>Approved 18 March 2026 (v01); explicitly liaises with OAuth, SCIM, SCITT, RATS, the OpenID Foundation, and CNCF/SPIFFE — the formal scope statement that anchors all WIMSE draft work.</t>
+          <t>Revision -06, 11 Aug 2026; advanced to IESG **AD Evaluation** as of 18 Aug 2026. WG-adopted draft. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5155,27 +5155,27 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>draft-aap-oauth-profile — Agent Authorization Profile (AAP) for OAuth 2.0</t>
+          <t>draft-schrock-ep-bounded-capability-receipts — Bounded Capability Receipts and Durable Spend Control for Agent Actions</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>This document defines the Agent Authorization Profile (AAP), an authorization profile for OAuth 2.0 and JWT designed for autonomous AI agents. AAP extends existing standards with structured claims and validation rules so that systems can reason about agent identity, task context, operational constraints, delegation chains, and human oversight requirements.</t>
+          <t>Agents sometimes need bounded authority to perform more than one consequential action without obtaining a new human approval for every operation. A signed token alone cannot enforce a shared budget across replicas, survive retries safely, or distinguish an operation that never crossed an effect boundary from one whose outcome is unknown.</t>
         </is>
       </c>
       <c r="D140" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-aap-oauth-profile/</t>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-bounded-capability-receipts/</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (individual draft)</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 11 Aug 2026; **now EXPIRED** on Datatracker (checked 26 Aug 2026). Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -04, 11 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5185,27 +5185,27 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>draft-ietf-wimse-workload-identity-practices — Workload Identity Practices</t>
+          <t>draft-chueayen-attestation-receipts — Enforcement Attestation Receipts for AI Inference Decisions</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>This document describes industry practices for providing secure identities to workloads in container orchestration, cloud platforms, and other workload platforms. It explains how workloads obtain credentials for external authentication purposes, without managing long-lived secrets directly.</t>
+          <t>This document specifies a compact JSON attestation receipt for an AI inference decision. A receipt binds an outcome to a request hash under a published Ed25519 public key, so a party that does not trust the issuer's infrastructure can still verify offline what the issuer's signing key attested was decided.</t>
         </is>
       </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-wimse-workload-identity-practices/</t>
+          <t>https://datatracker.ietf.org/doc/draft-chueayen-attestation-receipts/</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>IETF (WIMSE WG)</t>
+          <t>IETF (individual draft)</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>Revision -06, 11 Aug 2026; advanced to IESG **AD Evaluation** as of 18 Aug 2026. WG-adopted draft. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -02, 8 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5215,17 +5215,17 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>draft-schrock-ep-bounded-capability-receipts — Bounded Capability Receipts and Durable Spend Control for Agent Actions</t>
+          <t>draft-bezerra-anchors-command-provenance — Anchors: Post-Quantum Command Provenance for Autonomous Machine Links</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>Agents sometimes need bounded authority to perform more than one consequential action without obtaining a new human approval for every operation. A signed token alone cannot enforce a shared budget across replicas, survive retries safely, or distinguish an operation that never crossed an effect boundary from one whose outcome is unknown.</t>
+          <t>Autonomous machines such as uncrewed aircraft, ground robots, and spacecraft execute commands issued by human operators and, increasingly, by AI agents.</t>
         </is>
       </c>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-bounded-capability-receipts/</t>
+          <t>https://datatracker.ietf.org/doc/draft-bezerra-anchors-command-provenance/</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>Revision -04, 11 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -01, 7 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5245,27 +5245,27 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>draft-chueayen-attestation-receipts — Enforcement Attestation Receipts for AI Inference Decisions</t>
+          <t>draft-zehavi-oauth-authz-req-del-chain — OAuth Authorization Request Delegation Chain</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>This document specifies a compact JSON attestation receipt for an AI inference decision. A receipt binds an outcome to a request hash under a published Ed25519 public key, so a party that does not trust the issuer's infrastructure can still verify offline what the issuer's signing key attested was decided.</t>
+          <t>Brokered OAuth redirect authorization requests involve intermediary authorization servers between a downstream client and the upstream authorization server that obtains user consent and issues tokens.</t>
         </is>
       </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-chueayen-attestation-receipts/</t>
+          <t>https://datatracker.ietf.org/doc/draft-zehavi-oauth-authz-req-del-chain/</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual draft)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 8 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 7 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5275,27 +5275,27 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>draft-bezerra-anchors-command-provenance — Anchors: Post-Quantum Command Provenance for Autonomous Machine Links</t>
+          <t>draft-gazitt-oauth-authzen-issuance — AuthZEN Profile for OAuth 2.0 Token Issuance</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>Autonomous machines such as uncrewed aircraft, ground robots, and spacecraft execute commands issued by human operators and, increasingly, by AI agents.</t>
+          <t>Numerous OAuth 2.0 specifications define a moment at which an authorization server decides whether to issue a security token, and each of them declares the decision itself to be a matter of local policy that is out of scope. The result is that a decision common to every OAuth deployment has no interoperable expression.</t>
         </is>
       </c>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-bezerra-anchors-command-provenance/</t>
+          <t>https://datatracker.ietf.org/doc/draft-gazitt-oauth-authzen-issuance/</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual draft)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 7 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 5 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5305,17 +5305,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>draft-zehavi-oauth-authz-req-del-chain — OAuth Authorization Request Delegation Chain</t>
+          <t>draft-gazitt-oauth-authzen-token-exchange — AuthZEN Binding for OAuth 2.0 Token Exchange</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>Brokered OAuth redirect authorization requests involve intermediary authorization servers between a downstream client and the upstream authorization server that obtains user consent and issues tokens.</t>
+          <t>OAuth 2.0 Token Exchange (RFC 8693) defines the moment at which an authorization server decides whether one party may obtain a token to act as, or on behalf of, another. It states that the decision is governed by policy, and does not define that policy.</t>
         </is>
       </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-zehavi-oauth-authz-req-del-chain/</t>
+          <t>https://datatracker.ietf.org/doc/draft-gazitt-oauth-authzen-token-exchange/</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 7 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 5 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5335,27 +5335,27 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>draft-gazitt-oauth-authzen-issuance — AuthZEN Profile for OAuth 2.0 Token Issuance</t>
+          <t>draft-wang-dmsc-drisac — Distributed Registration and Information Synchronization of Agent Capabilities</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>Numerous OAuth 2.0 specifications define a moment at which an authorization server decides whether to issue a security token, and each of them declares the decision itself to be a matter of local policy that is out of scope. The result is that a decision common to every OAuth deployment has no interoperable expression.</t>
+          <t>The large-scale deployment of autonomous AI Agents introduces challenges to capability description, registration, and discovery. Existing agent communication protocols mainly focus on application- layer interactions and typically rely on centralized registration and discovery mechanisms, which limit scalability, robustness, and semantic extensibility.</t>
         </is>
       </c>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-gazitt-oauth-authzen-issuance/</t>
+          <t>https://datatracker.ietf.org/doc/draft-wang-dmsc-drisac/</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (DMSC-related, individual)</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 5 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -01, 18 Aug 2026 (was -00, 5 Aug 2026). Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5365,27 +5365,27 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>draft-gazitt-oauth-authzen-token-exchange — AuthZEN Binding for OAuth 2.0 Token Exchange</t>
+          <t>draft-diaconu-agents-authz-info-sharing — Cross-Domain AuthZ Information sharing for Agents</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>OAuth 2.0 Token Exchange (RFC 8693) defines the moment at which an authorization server decides whether one party may obtain a token to act as, or on behalf of, another. It states that the decision is governed by policy, and does not define that policy.</t>
+          <t>Distributed Multi-Agent Systems consist of Agents and MCP Servers operating across multiple administrative domains, each with its own Identity Providers (IdPs) and Authorization Servers (AS).</t>
         </is>
       </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-gazitt-oauth-authzen-token-exchange/</t>
+          <t>https://datatracker.ietf.org/doc/draft-diaconu-agents-authz-info-sharing/</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (individual draft)</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 5 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -01, 4 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5395,27 +5395,27 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>draft-wang-dmsc-drisac — Distributed Registration and Information Synchronization of Agent Capabilities</t>
+          <t>draft-ietf-wimse-http-signature — WIMSE Workload-to-Workload Authentication with HTTP Signatures</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>The large-scale deployment of autonomous AI Agents introduces challenges to capability description, registration, and discovery. Existing agent communication protocols mainly focus on application- layer interactions and typically rely on centralized registration and discovery mechanisms, which limit scalability, robustness, and semantic extensibility.</t>
+          <t>The WIMSE architecture defines authentication and authorization for software workloads in a variety of runtime environments, from the most basic ones to complex multi-service, multi-cloud, multi-tenant deployments. This document defines one of the mechanisms to provide workload authentication, using HTTP Signatures.</t>
         </is>
       </c>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-wang-dmsc-drisac/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-wimse-http-signature/</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>IETF (DMSC-related, individual)</t>
+          <t>IETF (WIMSE WG)</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 18 Aug 2026 (was -00, 5 Aug 2026). Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -06, 4 Aug 2026. WG-adopted draft. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5425,17 +5425,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>draft-diaconu-agents-authz-info-sharing — Cross-Domain AuthZ Information sharing for Agents</t>
+          <t>draft-carleton-workload-authz-grant — Workload Authorization Grant</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>Distributed Multi-Agent Systems consist of Agents and MCP Servers operating across multiple administrative domains, each with its own Identity Providers (IdPs) and Authorization Servers (AS).</t>
+          <t>This document profiles the Agent Identity Management System (AIMS) framework for agent platforms that host many agent instances per customer.</t>
         </is>
       </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-diaconu-agents-authz-info-sharing/</t>
+          <t>https://datatracker.ietf.org/doc/draft-carleton-workload-authz-grant/</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 4 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 3 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5455,27 +5455,27 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>draft-ietf-wimse-http-signature — WIMSE Workload-to-Workload Authentication with HTTP Signatures</t>
+          <t>draft-helixar-hdp-agentic-delegation — Human Delegation Provenance Protocol (HDP): Cryptographic Chain-of-Custody for Agentic AI Systems</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>The WIMSE architecture defines authentication and authorization for software workloads in a variety of runtime environments, from the most basic ones to complex multi-service, multi-cloud, multi-tenant deployments. This document defines one of the mechanisms to provide workload authentication, using HTTP Signatures.</t>
+          <t>Agentic AI systems operate on behalf of human principals, often delegating tasks through multi-step chains of AI agents. There is currently no standard mechanism to record who authorized an agent to act, under what scope, and through what chain of delegation, in a way that can be verified offline, without a central registry, and without third-party trust anchors.</t>
         </is>
       </c>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-wimse-http-signature/</t>
+          <t>https://datatracker.ietf.org/doc/draft-helixar-hdp-agentic-delegation/</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>IETF (WIMSE WG)</t>
+          <t>IETF (individual draft)</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>Revision -06, 4 Aug 2026. WG-adopted draft. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -01, 3 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5485,27 +5485,27 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>draft-carleton-workload-authz-grant — Workload Authorization Grant</t>
+          <t>draft-mcguinness-oauth-id-continuation-assertion — Identity Continuation Assertion for OAuth 2.0 Token Exchange</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>This document profiles the Agent Identity Management System (AIMS) framework for agent platforms that host many agent instances per customer.</t>
+          <t>This document defines the Identity Continuation Assertion, a short- lived, sender-constrained JWT used as an OAuth 2.0 Token Exchange subject token. It lets an Identity Provider (IdP) issue an onward Identity Assertion JWT Authorization Grant (ID-JAG) when a user's request crosses service boundaries after the user is no longer present.</t>
         </is>
       </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-carleton-workload-authz-grant/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-id-continuation-assertion/</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual draft)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 3 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -01, 26 Aug 2026 (was -00, 3 Aug 2026). Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5515,27 +5515,27 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>draft-helixar-hdp-agentic-delegation — Human Delegation Provenance Protocol (HDP): Cryptographic Chain-of-Custody for Agentic AI Systems</t>
+          <t>draft-parecki-oauth-jwt-dpop-grant — OAuth 2.0 JWT Authorization Grant with DPoP Binding</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>Agentic AI systems operate on behalf of human principals, often delegating tasks through multi-step chains of AI agents. There is currently no standard mechanism to record who authorized an agent to act, under what scope, and through what chain of delegation, in a way that can be verified offline, without a central registry, and without third-party trust anchors.</t>
+          <t>This specification defines a new OAuth 2.0 authorization grant type that uses a JSON Web Token (JWT) assertion to request an access token that is bound to a specific key using the Demonstration of Proof-of- Possession (DPoP) mechanism. This provides a higher level of security than a simple bearer token, as the client must prove possession of the key to use the access token.</t>
         </is>
       </c>
       <c r="D152" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-helixar-hdp-agentic-delegation/</t>
+          <t>https://datatracker.ietf.org/doc/draft-parecki-oauth-jwt-dpop-grant/</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual draft)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 3 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -01, 3 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked. **EXPIRED on Datatracker** (expired 3 Aug 2026; checked 26 Aug 2026) — kept in the corpus deliberately; an expired draft is still evidence of what was proposed.</t>
         </is>
       </c>
     </row>
@@ -5545,27 +5545,27 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-id-continuation-assertion — Identity Continuation Assertion for OAuth 2.0 Token Exchange</t>
+          <t>draft-mih-agent-accountability-conformance — Agent Accountability: A Conformance and Verification Method</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>This document defines the Identity Continuation Assertion, a short- lived, sender-constrained JWT used as an OAuth 2.0 Token Exchange subject token. It lets an Identity Provider (IdP) issue an onward Identity Assertion JWT Authorization Grant (ID-JAG) when a user's request crosses service boundaries after the user is no longer present.</t>
+          <t>An architecture for auditing agent-driven interactions (draft- kuehlewind-audit-architecture) identifies the record types an auditable agent system produces — interaction, action, delegation, and authorization-transition — and the role of an Auditor that determines whether recorded behaviour matched intent and the authorization in force.</t>
         </is>
       </c>
       <c r="D153" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-id-continuation-assertion/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mih-agent-accountability-conformance/</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (individual draft)</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 26 Aug 2026 (was -00, 3 Aug 2026). Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 1 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5575,27 +5575,27 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>draft-parecki-oauth-jwt-dpop-grant — OAuth 2.0 JWT Authorization Grant with DPoP Binding</t>
+          <t>draft-okutomi-session-bound-agent-identity — A Verifier-Side Acceptance Profile for Channel-Bound Agent Identity and Authorization</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>This specification defines a new OAuth 2.0 authorization grant type that uses a JSON Web Token (JWT) assertion to request an access token that is bound to a specific key using the Demonstration of Proof-of- Possession (DPoP) mechanism. This provides a higher level of security than a simple bearer token, as the client must prove possession of the key to use the access token.</t>
+          <t>This document defines a verifier-side acceptance profile for channel- bound Agent identity and authorization. It addresses context diversion, where cryptographically valid material is accepted for a different service, tenant, actor, task, target, delegation, or authority boundary than the verifier intended.</t>
         </is>
       </c>
       <c r="D154" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-parecki-oauth-jwt-dpop-grant/</t>
+          <t>https://datatracker.ietf.org/doc/draft-okutomi-session-bound-agent-identity/</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (individual draft)</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 3 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -06, 30 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5605,27 +5605,27 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>draft-mih-agent-accountability-conformance — Agent Accountability: A Conformance and Verification Method</t>
+          <t>draft-richer-oauth-httpsig — OAuth Proof of Possession Tokens with HTTP Message Signatures</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>An architecture for auditing agent-driven interactions (draft- kuehlewind-audit-architecture) identifies the record types an auditable agent system produces — interaction, action, delegation, and authorization-transition — and the role of an Auditor that determines whether recorded behaviour matched intent and the authorization in force.</t>
+          <t>This extension to the OAuth 2.0 authorization framework defines a method for using HTTP Message Signatures to bind access tokens to keys held by OAuth 2.0 clients. Discussion Venues This note is to be removed before publishing as an RFC.</t>
         </is>
       </c>
       <c r="D155" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mih-agent-accountability-conformance/</t>
+          <t>https://datatracker.ietf.org/doc/draft-richer-oauth-httpsig/</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual draft)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 1 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -03, 28 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5635,17 +5635,17 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>draft-okutomi-session-bound-agent-identity — A Verifier-Side Acceptance Profile for Channel-Bound Agent Identity and Authorization</t>
+          <t>draft-schrock-action-remedy-receipts — Action Remedy Receipts for Consequential Agent Effects</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>This document defines a verifier-side acceptance profile for channel- bound Agent identity and authorization. It addresses context diversion, where cryptographically valid material is accepted for a different service, tenant, actor, task, target, delegation, or authority boundary than the verifier intended.</t>
+          <t>Revocation cannot undo an effect that already occurred. A dispute does not authorize a refund, return, reversal, or other remedy. This document defines Action Remedy Receipts for recording a bounded dispute decision and a fresh compensating action without rewriting the original action or effect.</t>
         </is>
       </c>
       <c r="D156" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-okutomi-session-bound-agent-identity/</t>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-action-remedy-receipts/</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>Revision -06, 30 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 28 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5665,27 +5665,27 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>draft-richer-oauth-httpsig — OAuth Proof of Possession Tokens with HTTP Message Signatures</t>
+          <t>draft-tonyai-a2a-trust — Agent-to-Agent Trust, Identity, and Verifiable Provenance</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>This extension to the OAuth 2.0 authorization framework defines a method for using HTTP Message Signatures to bind access tokens to keys held by OAuth 2.0 clients. Discussion Venues This note is to be removed before publishing as an RFC.</t>
+          <t>This document defines a trust model for agent-to-agent (A2A) interactions in multi-agent AI systems.</t>
         </is>
       </c>
       <c r="D157" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-richer-oauth-httpsig/</t>
+          <t>https://datatracker.ietf.org/doc/draft-tonyai-a2a-trust/</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (individual draft)</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, 28 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -01, 25 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5695,27 +5695,27 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>draft-schrock-action-remedy-receipts — Action Remedy Receipts for Consequential Agent Effects</t>
+          <t>draft-ambekar-oauth-epop — JSON Web Token (JWT) Profile for OAuth 2.0 Enveloped Proof of Possession (EPOP)</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>Revocation cannot undo an effect that already occurred. A dispute does not authorize a refund, return, reversal, or other remedy. This document defines Action Remedy Receipts for recording a bounded dispute decision and a fresh compensating action without rewriting the original action or effect.</t>
+          <t>This specification defines a profile for OAuth 2.0 sender-constrained credentials in which access tokens and refresh tokens are cryptographically bound to the client's private key as a single inseparable envelope.</t>
         </is>
       </c>
       <c r="D158" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-schrock-action-remedy-receipts/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ambekar-oauth-epop/</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual draft)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 28 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -03, 24 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5725,27 +5725,27 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>draft-tonyai-a2a-trust — Agent-to-Agent Trust, Identity, and Verifiable Provenance</t>
+          <t>draft-parecki-oauth-refresh-token-scope-response — OAuth 2.0 Refresh Token Scope</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>This document defines a trust model for agent-to-agent (A2A) interactions in multi-agent AI systems.</t>
+          <t>This specification defines a new OAuth 2.0 token response parameter, refresh_token_scope, that indicates the scope authorized for a refresh token when it differs from the scope of the access token issued alongside it.</t>
         </is>
       </c>
       <c r="D159" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-tonyai-a2a-trust/</t>
+          <t>https://datatracker.ietf.org/doc/draft-parecki-oauth-refresh-token-scope-response/</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual draft)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 25 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 24 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5755,27 +5755,27 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>draft-ambekar-oauth-epop — JSON Web Token (JWT) Profile for OAuth 2.0 Enveloped Proof of Possession (EPOP)</t>
+          <t>draft-pro-adp-agent-discovery — Agent Discovery Protocol (ADP) v1.1 -- Well-Known Metadata and Interaction Layer</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>This specification defines a profile for OAuth 2.0 sender-constrained credentials in which access tokens and refresh tokens are cryptographically bound to the client's private key as a single inseparable envelope.</t>
+          <t>This document defines the Agent Discovery Protocol (ADP) v1.1, a layered protocol for discovering, verifying, and interacting with AI Agents on the Internet. ADP delegates DNS discovery to DNS-AID (SVCB records) and defines a Well-Known JSON metadata format, an Ed25519-based identity model, and the Agent Gateway Protocol (AGP) for real-time WebSocket messaging.</t>
         </is>
       </c>
       <c r="D160" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ambekar-oauth-epop/</t>
+          <t>https://datatracker.ietf.org/doc/draft-pro-adp-agent-discovery/</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (individual draft)</t>
         </is>
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, 24 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -02, 24 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5785,27 +5785,27 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>draft-parecki-oauth-refresh-token-scope-response — OAuth 2.0 Refresh Token Scope</t>
+          <t>draft-ietf-oauth-rfc7523bis — Updates to OAuth 2.0 JSON Web Token (JWT) Client Authentication and Assertion-Based Authorization Grants</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>This specification defines a new OAuth 2.0 token response parameter, refresh_token_scope, that indicates the scope authorized for a refresh token when it differs from the scope of the access token issued alongside it.</t>
+          <t>This document updates RFC7521, RFC7522, RFC7523 and RFC9126 with respect to the treatment of audience values in OAuth 2.0 Client Assertion Authentication and Assertion-based Authorization Grants to address a security vulnerability identified in the previous requirements for those audience values in multiple OAuth 2.0 specifications.</t>
         </is>
       </c>
       <c r="D161" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-parecki-oauth-refresh-token-scope-response/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-rfc7523bis/</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (OAuth WG)</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 24 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -11, 23 Jul 2026; entered the RFC Editor queue (touched 13 Aug 2026, rfceditor state 'In Progress'). WG-adopted draft. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5815,27 +5815,27 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>draft-pro-adp-agent-discovery — Agent Discovery Protocol (ADP) v1.1 -- Well-Known Metadata and Interaction Layer</t>
+          <t>draft-kavian-aep-oauth-session-credential — OAuth Bearer Session Credential Grant Type for the Agent Enrollment Protocol</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>This document defines the Agent Discovery Protocol (ADP) v1.1, a layered protocol for discovering, verifying, and interacting with AI Agents on the Internet. ADP delegates DNS discovery to DNS-AID (SVCB records) and defines a Well-Known JSON metadata format, an Ed25519-based identity model, and the Agent Gateway Protocol (AGP) for real-time WebSocket messaging.</t>
+          <t>This document defines the OAuth Bearer session-credential grant type for the Agent Enrollment Protocol (AEP). The grant type lets an AEP Service issue an OAuth-style Bearer access token through the AEP Grant command while preserving baseline AEP client assertion authentication as the root of trust.</t>
         </is>
       </c>
       <c r="D162" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-pro-adp-agent-discovery/</t>
+          <t>https://datatracker.ietf.org/doc/draft-kavian-aep-oauth-session-credential/</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual draft)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 24 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -03, 24 Aug 2026 (was -02, 23 Jul 2026). Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5845,27 +5845,27 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>draft-ietf-oauth-rfc7523bis — Updates to OAuth 2.0 JSON Web Token (JWT) Client Authentication and Assertion-Based Authorization Grants</t>
+          <t>draft-morrison-mcp-dns-discovery — Discovery of Model Context Protocol Servers via DNS TXT Records</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>This document updates RFC7521, RFC7522, RFC7523 and RFC9126 with respect to the treatment of audience values in OAuth 2.0 Client Assertion Authentication and Assertion-based Authorization Grants to address a security vulnerability identified in the previous requirements for those audience values in multiple OAuth 2.0 specifications.</t>
+          <t>This document defines a DNS-based mechanism for discovering Model Context Protocol (MCP) servers, the identity of the organisations that operate them, and a cryptographic identity envelope bound to an individual Sovereign-tier ~handle published under the same zone. Three TXT records are defined.</t>
         </is>
       </c>
       <c r="D163" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-rfc7523bis/</t>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-mcp-dns-discovery/</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth WG)</t>
+          <t>IETF (individual draft)</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>Revision -11, 23 Jul 2026; entered the RFC Editor queue (touched 13 Aug 2026, rfceditor state 'In Progress'). WG-adopted draft. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -05, 23 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5875,27 +5875,27 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>draft-kavian-aep-oauth-session-credential — OAuth Bearer Session Credential Grant Type for the Agent Enrollment Protocol</t>
+          <t>draft-yossif-agent-mandate-problem — Problem Statement: Verifiable Human Mandates for Autonomous Agent Actions</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>This document defines the OAuth Bearer session-credential grant type for the Agent Enrollment Protocol (AEP). The grant type lets an AEP Service issue an OAuth-style Bearer access token through the AEP Grant command while preserving baseline AEP client assertion authentication as the root of trust.</t>
+          <t>An autonomous software agent commonly acts under authority a human granted at an earlier moment: the human expresses and authorizes an intent at one time, and the agent executes one or more concrete actions at a later time.</t>
         </is>
       </c>
       <c r="D164" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-kavian-aep-oauth-session-credential/</t>
+          <t>https://datatracker.ietf.org/doc/draft-yossif-agent-mandate-problem/</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (individual draft)</t>
         </is>
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, 24 Aug 2026 (was -02, 23 Jul 2026). Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 22 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5905,27 +5905,27 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>draft-morrison-mcp-dns-discovery — Discovery of Model Context Protocol Servers via DNS TXT Records</t>
+          <t>draft-araut-oauth-transactiontokens-bcp — OAuth Transaction Tokens Best Current Practice</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>This document defines a DNS-based mechanism for discovering Model Context Protocol (MCP) servers, the identity of the organisations that operate them, and a cryptographic identity envelope bound to an individual Sovereign-tier ~handle published under the same zone. Three TXT records are defined.</t>
+          <t>This document provides best current practices for implementing and deploying OAuth 2.0 Transaction Tokens as specified in draft-ietf- oauth-transaction-tokens. Transaction Tokens (Txn-Tokens) enable workloads in a trusted domain to preserve and propagate user identity and authorization context across service boundaries during the processing of external programmatic requests.</t>
         </is>
       </c>
       <c r="D165" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-morrison-mcp-dns-discovery/</t>
+          <t>https://datatracker.ietf.org/doc/draft-araut-oauth-transactiontokens-bcp/</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual draft)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>Revision -05, 23 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 20 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -5935,27 +5935,27 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>draft-yossif-agent-mandate-problem — Problem Statement: Verifiable Human Mandates for Autonomous Agent Actions</t>
+          <t>draft-ccc-wimse-twi-extensions — WIMSE Extensions for Trustworthy Workload Identity</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>An autonomous software agent commonly acts under authority a human granted at an earlier moment: the human expresses and authorizes an intent at one time, and the agent executes one or more concrete actions at a later time.</t>
+          <t>This document contains a gap analysis that is the output of the Confidential Computing Consortium identifying areas in the IETF WIMSE WG work where the current WIMSE architecture should be extended to accommodate workloads running in Confidential Computing environments. This document contains a high-level outline for these extensions.</t>
         </is>
       </c>
       <c r="D166" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-yossif-agent-mandate-problem/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ccc-wimse-twi-extensions/</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual draft)</t>
+          <t>IETF (WIMSE-related, individual)</t>
         </is>
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 22 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -01, 20 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked. **EXPIRED on Datatracker** (expired 9 Jul 2026; checked 26 Aug 2026) — kept in the corpus deliberately; an expired draft is still evidence of what was proposed.</t>
         </is>
       </c>
     </row>
@@ -5965,27 +5965,27 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>draft-araut-oauth-transactiontokens-bcp — OAuth Transaction Tokens Best Current Practice</t>
+          <t>draft-chen-ai-agent-auth-new-requirements — New requirements for Authentication and Authorization in the AI Agents era</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>This document provides best current practices for implementing and deploying OAuth 2.0 Transaction Tokens as specified in draft-ietf- oauth-transaction-tokens. Transaction Tokens (Txn-Tokens) enable workloads in a trusted domain to preserve and propagate user identity and authorization context across service boundaries during the processing of external programmatic requests.</t>
+          <t>AI Agents are rapidly evolving from academic concepts into the core engines driving next-generation applications. However, their autonomy, dynamic nature, and complex delegation relationships pose a fundamental challenge to our existing authentication and authorization frameworks, which were designed for human users and traditional software.</t>
         </is>
       </c>
       <c r="D167" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-araut-oauth-transactiontokens-bcp/</t>
+          <t>https://datatracker.ietf.org/doc/draft-chen-ai-agent-auth-new-requirements/</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (individual draft)</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 20 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 20 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked. **EXPIRED on Datatracker** (expired 10 Jul 2026; checked 26 Aug 2026) — kept in the corpus deliberately; an expired draft is still evidence of what was proposed.</t>
         </is>
       </c>
     </row>
@@ -5995,27 +5995,27 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>draft-ccc-wimse-twi-extensions — WIMSE Extensions for Trustworthy Workload Identity</t>
+          <t>draft-dellaert-oauth-approval-based-dcr — OAuth 2.0 Approval-Based Dynamic Client Registration</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>This document contains a gap analysis that is the output of the Confidential Computing Consortium identifying areas in the IETF WIMSE WG work where the current WIMSE architecture should be extended to accommodate workloads running in Confidential Computing environments. This document contains a high-level outline for these extensions.</t>
+          <t>This document specifies an extension to the OAuth 2.0 Dynamic Client Registration Protocol ([RFC7591]) that enables registration of a client with an authorization server through an explicit approval step performed by an approving party, typically the user running the client, without requiring the client to possess an Initial Access Token (IAT) beforehand.</t>
         </is>
       </c>
       <c r="D168" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ccc-wimse-twi-extensions/</t>
+          <t>https://datatracker.ietf.org/doc/draft-dellaert-oauth-approval-based-dcr/</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>IETF (WIMSE-related, individual)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 20 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 20 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6025,27 +6025,27 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>draft-chen-ai-agent-auth-new-requirements — New requirements for Authentication and Authorization in the AI Agents era</t>
+          <t>draft-hemanth-oauth-ai-scopes — OAuth 2.0 Extension for AI Model Access</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>AI Agents are rapidly evolving from academic concepts into the core engines driving next-generation applications. However, their autonomy, dynamic nature, and complex delegation relationships pose a fundamental challenge to our existing authentication and authorization frameworks, which were designed for human users and traditional software.</t>
+          <t>This document defines an extension to OAuth 2.0 for delegating scoped access to AI model APIs. It introduces a standardized scope syntax, resource indicators for AI providers, and token constraints suitable for AI workloads including spend limits and model restrictions.</t>
         </is>
       </c>
       <c r="D169" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-chen-ai-agent-auth-new-requirements/</t>
+          <t>https://datatracker.ietf.org/doc/draft-hemanth-oauth-ai-scopes/</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual draft)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 20 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 20 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked. **EXPIRED on Datatracker** (expired 10 Jul 2026; checked 26 Aug 2026) — kept in the corpus deliberately; an expired draft is still evidence of what was proposed.</t>
         </is>
       </c>
     </row>
@@ -6055,27 +6055,27 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>draft-dellaert-oauth-approval-based-dcr — OAuth 2.0 Approval-Based Dynamic Client Registration</t>
+          <t>draft-zhang-dmsc-mas-communication — Security Analysis of Multi-agents Secured Communication and Limitations of Existing Protocols</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>This document specifies an extension to the OAuth 2.0 Dynamic Client Registration Protocol ([RFC7591]) that enables registration of a client with an authorization server through an explicit approval step performed by an approving party, typically the user running the client, without requiring the client to possess an Initial Access Token (IAT) beforehand.</t>
+          <t>Multi-agents systems (MAS) increasingly cooperate through workflow, orchestrated, and mesh communication patterns. While existing Internet protocols provide confidentiality and endpoint authentication, they were not designed for agent-native semantics such as dynamic identity, computation-bounded requests, context integrity, and intermediary trust.</t>
         </is>
       </c>
       <c r="D170" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-dellaert-oauth-approval-based-dcr/</t>
+          <t>https://datatracker.ietf.org/doc/draft-zhang-dmsc-mas-communication/</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (DMSC-related, individual)</t>
         </is>
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 20 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 20 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked. **EXPIRED on Datatracker** (expired 20 Jul 2026; checked 26 Aug 2026) — kept in the corpus deliberately; an expired draft is still evidence of what was proposed.</t>
         </is>
       </c>
     </row>
@@ -6085,17 +6085,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>draft-hemanth-oauth-ai-scopes — OAuth 2.0 Extension for AI Model Access</t>
+          <t>draft-aravind-oauth-decision-subject — Decision-Subject Representation for Agent Authorization</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>This document defines an extension to OAuth 2.0 for delegating scoped access to AI model APIs. It introduces a standardized scope syntax, resource indicators for AI providers, and token constraints suitable for AI workloads including spend limits and model restrictions.</t>
+          <t>This document defines dsub, an OPTIONAL, descriptive claim naming the *decision subject*, the party an automated agent's action is taken _upon_, as distinct from the acting agent (act) and the delegating principal (sub).</t>
         </is>
       </c>
       <c r="D171" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-hemanth-oauth-ai-scopes/</t>
+          <t>https://datatracker.ietf.org/doc/draft-aravind-oauth-decision-subject/</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 20 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 19 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6115,27 +6115,27 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>draft-zhang-dmsc-mas-communication — Security Analysis of Multi-agents Secured Communication and Limitations of Existing Protocols</t>
+          <t>draft-coetzee-oauth-spt-txn-tokens — Transaction-Bound Authorization Tokens for Software and AI Agents (SPT-Txn)</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>Multi-agents systems (MAS) increasingly cooperate through workflow, orchestrated, and mesh communication patterns. While existing Internet protocols provide confidentiality and endpoint authentication, they were not designed for agent-native semantics such as dynamic identity, computation-bounded requests, context integrity, and intermediary trust.</t>
+          <t>Current authorization is role-scoped: an actor is granted a role whose authority persists across every action it takes. This fails exactly when actors fail -- under compromise, prompt injection, or goal hijacking -- because a compromised actor retains full role authority.</t>
         </is>
       </c>
       <c r="D172" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-zhang-dmsc-mas-communication/</t>
+          <t>https://datatracker.ietf.org/doc/draft-coetzee-oauth-spt-txn-tokens/</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>IETF (DMSC-related, individual)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F172" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 20 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -03, 19 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6145,17 +6145,17 @@
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>draft-aravind-oauth-decision-subject — Decision-Subject Representation for Agent Authorization</t>
+          <t>draft-mcguinness-oauth-token-exchange-cnf — Confirmation Response Parameter for OAuth 2.0 Token Exchange</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>This document defines dsub, an OPTIONAL, descriptive claim naming the *decision subject*, the party an automated agent's action is taken _upon_, as distinct from the acting agent (act) and the delegating principal (sub).</t>
+          <t>This specification defines a cnf response parameter for the OAuth 2.0 Token Exchange (RFC 8693) response. The parameter carries the confirmation method that the authorization server applied to the issued token, enabling clients to verify that sender-constraint binding (for example a DPoP key or mutual-TLS client certificate) was performed without inspecting the issued token.</t>
         </is>
       </c>
       <c r="D173" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-aravind-oauth-decision-subject/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-token-exchange-cnf/</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
@@ -6175,17 +6175,17 @@
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>draft-coetzee-oauth-spt-txn-tokens — Transaction-Bound Authorization Tokens for Software and AI Agents (SPT-Txn)</t>
+          <t>draft-skyfire-oauth-id-verification — Identity Verification Methods Values</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>Current authorization is role-scoped: an actor is granted a role whose authority persists across every action it takes. This fails exactly when actors fail -- under compromise, prompt injection, or goal hijacking -- because a compromised actor retains full role authority.</t>
+          <t>Knowing how a person's identity was verified can be important when making trust decisions. This specification defines a claim and values for declaring how the person's identity was verified.</t>
         </is>
       </c>
       <c r="D174" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-coetzee-oauth-spt-txn-tokens/</t>
+          <t>https://datatracker.ietf.org/doc/draft-skyfire-oauth-id-verification/</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, 19 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -01, 19 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6205,27 +6205,27 @@
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-token-exchange-cnf — Confirmation Response Parameter for OAuth 2.0 Token Exchange</t>
+          <t>draft-ietf-wimse-mutual-tls — Workload Authentication Using Mutual TLS</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>This specification defines a cnf response parameter for the OAuth 2.0 Token Exchange (RFC 8693) response. The parameter carries the confirmation method that the authorization server applied to the issued token, enabling clients to verify that sender-constraint binding (for example a DPoP key or mutual-TLS client certificate) was performed without inspecting the issued token.</t>
+          <t>The WIMSE architecture defines authentication and authorization for software workloads in a variety of runtime environments, from the most basic ones to complex multi-service, multi-cloud, multi-tenant deployments. This document profiles a workload authentication based on X.509 workload identity certificates using mutual TLS (mTLS).</t>
         </is>
       </c>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-token-exchange-cnf/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-wimse-mutual-tls/</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (WIMSE WG)</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 19 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -02, 6 Jul 2026. WG-adopted draft. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6235,27 +6235,27 @@
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>draft-skyfire-oauth-id-verification — Identity Verification Methods Values</t>
+          <t>draft-liu-ai-agent-authorization-integration — AI Agent Authorization Integration Framework</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>Knowing how a person's identity was verified can be important when making trust decisions. This specification defines a claim and values for declaring how the person's identity was verified.</t>
+          <t>This document describes how to integrate multiple OAuth 2.0 extensions to enable secure authorization for AI agents acting on behalf of users. It combines cross-domain identity, policy-based authorization, user consent evidence, and multi-hop delegation into a cohesive framework for autonomous agent authorization.</t>
         </is>
       </c>
       <c r="D176" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-skyfire-oauth-id-verification/</t>
+          <t>https://datatracker.ietf.org/doc/draft-liu-ai-agent-authorization-integration/</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (individual draft)</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 19 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 6 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6265,27 +6265,27 @@
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>draft-ietf-wimse-mutual-tls — Workload Authentication Using Mutual TLS</t>
+          <t>draft-ni-agent-entity-discovery — DNS-based Entity-Level Discovery and End-to-End Connection for AI Agents</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>The WIMSE architecture defines authentication and authorization for software workloads in a variety of runtime environments, from the most basic ones to complex multi-service, multi-cloud, multi-tenant deployments. This document profiles a workload authentication based on X.509 workload identity certificates using mutual TLS (mTLS).</t>
+          <t>This document defines a new DNS resource record type, Agent Entity Discovery (AED), to publish agent-specific trust anchors or direct match constraints for verifying an agent's certificate or token. This enables the cross-domain users or agents to authenticate, and establish secure, end-to-end connections directly with a private- domain agent entity.</t>
         </is>
       </c>
       <c r="D177" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-wimse-mutual-tls/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ni-agent-entity-discovery/</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
         <is>
-          <t>IETF (WIMSE WG)</t>
+          <t>IETF (individual draft)</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 6 Jul 2026. WG-adopted draft. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 6 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6295,17 +6295,17 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>draft-liu-ai-agent-authorization-integration — AI Agent Authorization Integration Framework</t>
+          <t>draft-shang-campus-agent-scope-down — Campus Agent Identification and Scope-Down Access Control</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>This document describes how to integrate multiple OAuth 2.0 extensions to enable secure authorization for AI agents acting on behalf of users. It combines cross-domain identity, policy-based authorization, user consent evidence, and multi-hop delegation into a cohesive framework for autonomous agent authorization.</t>
+          <t>AI agents operating in enterprise campus networks execute user- delegated Tasks by invoking multiple tools and services, often without continuous user supervision. Traditional authorization models assume stable applications and human-driven interactions, creating a mismatch when applied to autonomous agents that can chain actions across heterogeneous systems.</t>
         </is>
       </c>
       <c r="D178" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-liu-ai-agent-authorization-integration/</t>
+          <t>https://datatracker.ietf.org/doc/draft-shang-campus-agent-scope-down/</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 6 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -01, 6 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6325,27 +6325,27 @@
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>draft-ni-agent-entity-discovery — DNS-based Entity-Level Discovery and End-to-End Connection for AI Agents</t>
+          <t>draft-yang-dmsc-gateway-mediation-layer — Gateway Mediation Layer for AI Agent Collaboration</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>This document defines a new DNS resource record type, Agent Entity Discovery (AED), to publish agent-specific trust anchors or direct match constraints for verifying an agent's certificate or token. This enables the cross-domain users or agents to authenticate, and establish secure, end-to-end connections directly with a private- domain agent entity.</t>
+          <t>Cross-domain and policy-controlled agent collaboration can require mediation decisions that are not always suitable for an agent client or an agent server alone.</t>
         </is>
       </c>
       <c r="D179" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ni-agent-entity-discovery/</t>
+          <t>https://datatracker.ietf.org/doc/draft-yang-dmsc-gateway-mediation-layer/</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual draft)</t>
+          <t>IETF (DMSC-related, individual)</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 6 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 5 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6355,27 +6355,27 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>draft-shang-campus-agent-scope-down — Campus Agent Identification and Scope-Down Access Control</t>
+          <t>draft-cui-dawn-mdi-model — An Information Model for Minimum Discoverable Information (MDI)</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>AI agents operating in enterprise campus networks execute user- delegated Tasks by invoking multiple tools and services, often without continuous user supervision. Traditional authorization models assume stable applications and human-driven interactions, creating a mismatch when applied to autonomous agents that can chain actions across heterogeneous systems.</t>
+          <t>The Discovery of Agents, Workloads, and Named Entities (DAWN) terminology document defines Minimum Discoverable Information (MDI) as the minimum information an entity must provide to be discoverable, but does not define its field-level content.</t>
         </is>
       </c>
       <c r="D180" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-shang-campus-agent-scope-down/</t>
+          <t>https://datatracker.ietf.org/doc/draft-cui-dawn-mdi-model/</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual draft)</t>
+          <t>IETF (DAWN-related, individual)</t>
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 6 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 3 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6385,27 +6385,27 @@
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>draft-yang-dmsc-gateway-mediation-layer — Gateway Mediation Layer for AI Agent Collaboration</t>
+          <t>draft-liu-oauth-cross-domain-txn-token — Cross-domain Transaction Tokens</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>Cross-domain and policy-controlled agent collaboration can require mediation decisions that are not always suitable for an agent client or an agent server alone.</t>
+          <t>This document describes a mechanism for Cross-Domain Transaction Tokens, which enables the safe maintenance and propagation of user identity, workload identities, and authorization context across multiple trust domains.</t>
         </is>
       </c>
       <c r="D181" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-yang-dmsc-gateway-mediation-layer/</t>
+          <t>https://datatracker.ietf.org/doc/draft-liu-oauth-cross-domain-txn-token/</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
         <is>
-          <t>IETF (DMSC-related, individual)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 5 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 3 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6415,27 +6415,27 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>draft-cui-dawn-mdi-model — An Information Model for Minimum Discoverable Information (MDI)</t>
+          <t>draft-schrock-action-evidence-boundary — The Action Evidence Boundary for Consequential Agent Effects</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>The Discovery of Agents, Workloads, and Named Entities (DAWN) terminology document defines Minimum Discoverable Information (MDI) as the minimum information an entity must provide to be discoverable, but does not define its field-level content.</t>
+          <t>Consequential agent actions can cross identity, transport, authorization, policy, and execution systems. Each system can produce a valid artifact while the executor still lacks a safe rule for joining the artifacts to the exact effect, consuming one-time authority, and handling an uncertain outcome. This document defines the Action Evidence Boundary (AEB), an executor-side processing model for that lifecycle. AEB requires native artifact verification, Canonical Action Identifier (CAID) matching, Authorization Evidence Chain (AEC) satisfaction, a separate local authorization decision, durable atomic consumption or reservation, invocation, closed effect outcomes, and authenticated reconciliation. It defines no receipt or token format, no policy language, no universal evidence taxonomy, and no new registry. Native workload credentials, message signatures, attested per-action tokens, permit records, authorization receipts, and status mechanisms retain their own semantics and verifiers.</t>
         </is>
       </c>
       <c r="D182" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-cui-dawn-mdi-model/</t>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-action-evidence-boundary/</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>IETF (DAWN-related, individual)</t>
+          <t>IETF (individual draft)</t>
         </is>
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 3 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -04, checked 26 Aug 2026. **Re-slugged: this draft was tracked as draft-schrock-agent-action-manifest until 26 Aug 2026**, which Datatracker marks Replaced by this one. Row updated to the current name, URL and abstract; the old slug is recorded here so searches for it still land. Previously filed in the corpus as “draft-schrock-agent-action-manifest — The Agent Action Control Manifest: A Public Effect-Boundary Control Plane for Machine Actions”.</t>
         </is>
       </c>
     </row>
@@ -6445,22 +6445,22 @@
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>draft-liu-oauth-cross-domain-txn-token — Cross-domain Transaction Tokens</t>
+          <t>draft-schrock-human-authorization-binding — Binding Named-Human Authorization Evidence into Agent-Action Records</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>This document describes a mechanism for Cross-Domain Transaction Tokens, which enables the safe maintenance and propagation of user identity, workload identities, and authorization context across multiple trust domains.</t>
+          <t>A recurring pattern spans the agent-action record formats now in development: a record about an agent's action reserves a place for "the human authorization" — an approver disposition, an authority context, a human-override field, an actor slot, a signed grant, an approval reference — and leaves its semantics undefined.</t>
         </is>
       </c>
       <c r="D183" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-liu-oauth-cross-domain-txn-token/</t>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-human-authorization-binding/</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (individual draft)</t>
         </is>
       </c>
       <c r="F183" s="5" t="inlineStr">
@@ -6475,17 +6475,17 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>draft-schrock-agent-action-manifest — The Agent Action Control Manifest: A Public Effect-Boundary Control Plane for Machine Actions</t>
+          <t>draft-xkumakichi-xaip-receipts — Signed Execution Receipts for AI Agent Tool Calls (XAIP Receipts)</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>A growing set of specifications defines evidence _objects_ for machine actions: transparency statements, workload-identity and transaction tokens, permits, action capsules, and authorization, delegation, and inference receipts.</t>
+          <t>This document defines a wire format for signed execution receipts produced by AI agents when they invoke tools, services, or other agents.</t>
         </is>
       </c>
       <c r="D184" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-schrock-agent-action-manifest/</t>
+          <t>https://datatracker.ietf.org/doc/draft-xkumakichi-xaip-receipts/</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 3 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -03, 2 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6505,27 +6505,27 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>draft-schrock-human-authorization-binding — Binding Named-Human Authorization Evidence into Agent-Action Records</t>
+          <t>draft-yang-dmsc-gateway-semantic-layer — Gateway Mediation Layer for AI Agent Collaboration</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>A recurring pattern spans the agent-action record formats now in development: a record about an agent's action reserves a place for "the human authorization" — an approver disposition, an authority context, a human-override field, an actor slot, a signed grant, an approval reference — and leaves its semantics undefined.</t>
+          <t>Cross-domain and policy-controlled agent collaboration can require mediation decisions that are not always suitable for an agent client or an agent server alone.</t>
         </is>
       </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-schrock-human-authorization-binding/</t>
+          <t>https://datatracker.ietf.org/doc/draft-yang-dmsc-gateway-semantic-layer/</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual draft)</t>
+          <t>IETF (DMSC-related, individual)</t>
         </is>
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 3 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -02, 2 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6535,17 +6535,17 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>draft-xkumakichi-xaip-receipts — Signed Execution Receipts for AI Agent Tool Calls (XAIP Receipts)</t>
+          <t>draft-ayoub-agis-agent-identity-system — AgIS: An Agent Identity System for DNS-Backed Verification of AI and Software Agents</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>This document defines a wire format for signed execution receipts produced by AI agents when they invoke tools, services, or other agents.</t>
+          <t>This document specifies AgIS, the Agent Identity System, a DNS-backed identity and verification profile for AI agents, autonomous software agents, and agentic services operating on the existing web.</t>
         </is>
       </c>
       <c r="D186" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-xkumakichi-xaip-receipts/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ayoub-agis-agent-identity-system/</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, 2 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 29 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6565,27 +6565,27 @@
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>draft-yang-dmsc-gateway-semantic-layer — Gateway Mediation Layer for AI Agent Collaboration</t>
+          <t>draft-vicente-oauth-apm — Authorization Posture Mechanism (APM): Per-Transaction Consistency for OAuth 2.0</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>Cross-domain and policy-controlled agent collaboration can require mediation decisions that are not always suitable for an agent client or an agent server alone.</t>
+          <t>This document describes the Authorization Posture Mechanism (APM), a method by which an OAuth 2.0 [RFC6749] authorization server, or a resource server acting on its behalf, re-evaluates the mutual consistency of three bound factors -- the client certificate, the access token, and the device posture -- on a per-request basis for privileged operations, rather than only at session…</t>
         </is>
       </c>
       <c r="D187" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-yang-dmsc-gateway-semantic-layer/</t>
+          <t>https://datatracker.ietf.org/doc/draft-vicente-oauth-apm/</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
         <is>
-          <t>IETF (DMSC-related, individual)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 2 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -02, 28 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6595,17 +6595,17 @@
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>draft-ni-batch-authorization-delegation — Batch Authorization Delegation</t>
+          <t>draft-duda-agent-id-framework — Self-Certifying Identity and Capability-Based Delegation for Autonomous AI Agents</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>This document describes a mechanism for Batch Authorization Delegation, which enables a batch of fine-grained, actor-bound permissions in a single request and securely delegates them to multiple collaborating actors.</t>
+          <t>We present an identity and delegation framework for secure AI agent communications. The framework introduces a set of entities including Client AI Agents, Service AI Agents, Agent Providers, and Agent Brokers, together with a Trustful Mutable Store responsible for maintaining cryptographically verifiable identity bindings.</t>
         </is>
       </c>
       <c r="D188" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ni-batch-authorization-delegation/</t>
+          <t>https://datatracker.ietf.org/doc/draft-duda-agent-id-framework/</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="F188" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 30 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 26 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6625,27 +6625,27 @@
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>draft-ayoub-agis-agent-identity-system — AgIS: An Agent Identity System for DNS-Backed Verification of AI and Software Agents</t>
+          <t>draft-liu-oauth-authorization-evidence — Authorization Evidence and Audit Trail for OAuth 2.0 Access Tokens</t>
         </is>
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>This document specifies AgIS, the Agent Identity System, a DNS-backed identity and verification profile for AI agents, autonomous software agents, and agentic services operating on the existing web.</t>
+          <t>This specification defines an authorization details type for including authorization evidence and audit trail information in OAuth 2.0 access tokens using the Rich Authorization Requests (RAR) framework.</t>
         </is>
       </c>
       <c r="D189" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ayoub-agis-agent-identity-system/</t>
+          <t>https://datatracker.ietf.org/doc/draft-liu-oauth-authorization-evidence/</t>
         </is>
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual draft)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 29 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -01, 22 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6655,27 +6655,27 @@
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>draft-vicente-oauth-apm — Authorization Posture Mechanism (APM): Per-Transaction Consistency for OAuth 2.0</t>
+          <t>draft-vandemeent-tibet-provenance — TIBET: Transaction/Interaction-Based Evidence Trail</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>This document describes the Authorization Posture Mechanism (APM), a method by which an OAuth 2.0 [RFC6749] authorization server, or a resource server acting on its behalf, re-evaluates the mutual consistency of three bound factors -- the client certificate, the access token, and the device posture -- on a per-request basis for privileged operations, rather than only at session…</t>
+          <t>This document defines TIBET (Transaction/Interaction-Based Evidence Trail), a data model and protocol for constructing cryptographically linked provenance chains over interactions between autonomous agents, human actors, and automated processes. A TIBET token captures four dimensions of provenance: content (ERIN), references (ERAAN), context (EROMHEEN), and intent (ERACHTER).</t>
         </is>
       </c>
       <c r="D190" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-vicente-oauth-apm/</t>
+          <t>https://datatracker.ietf.org/doc/draft-vandemeent-tibet-provenance/</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (individual draft)</t>
         </is>
       </c>
       <c r="F190" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 28 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -02, 17 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6685,17 +6685,17 @@
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>draft-duda-agent-id-framework — Self-Certifying Identity and Capability-Based Delegation for Autonomous AI Agents</t>
+          <t>draft-car-agents-txt-wellknown — AGENTS.TXT: Capability Declarations for Web Agents</t>
         </is>
       </c>
       <c r="C191" s="5" t="inlineStr">
         <is>
-          <t>We present an identity and delegation framework for secure AI agent communications. The framework introduces a set of entities including Client AI Agents, Service AI Agents, Agent Providers, and Agent Brokers, together with a Trustful Mutable Store responsible for maintaining cryptographically verifiable identity bindings.</t>
+          <t>This document requests registration of two Well-Known URIs under the "/.well-known/" path: "agents.txt" and "agents.json".</t>
         </is>
       </c>
       <c r="D191" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-duda-agent-id-framework/</t>
+          <t>https://datatracker.ietf.org/doc/draft-car-agents-txt-wellknown/</t>
         </is>
       </c>
       <c r="E191" s="5" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="F191" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 26 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 12 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6715,17 +6715,17 @@
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>draft-liu-oauth-authorization-evidence — Authorization Evidence and Audit Trail for OAuth 2.0 Access Tokens</t>
+          <t>draft-liu-oauth-rego-policy — Rego Policy Language for OAuth 2.0 Authorization</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>This specification defines an authorization details type for including authorization evidence and audit trail information in OAuth 2.0 access tokens using the Rich Authorization Requests (RAR) framework.</t>
+          <t>AI agents exhibit dynamic, unpredictable behavior that cannot be fully described by traditional OAuth 2.0 scopes. This specification defines a behavioral authorization framework that enables clients, particularly AI agents, to propose Rego policy-based behavioral constraint contracts in OAuth 2.0 authorization flows using Rich Authorization Requests (RAR).</t>
         </is>
       </c>
       <c r="D192" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-liu-oauth-authorization-evidence/</t>
+          <t>https://datatracker.ietf.org/doc/draft-liu-oauth-rego-policy/</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="F192" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 22 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 12 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6745,27 +6745,27 @@
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>draft-vandemeent-tibet-provenance — TIBET: Transaction/Interaction-Based Evidence Trail</t>
+          <t>draft-ekahraman-oauth-attestation-authz-native-app — OAuth 2.0 Attestation Based Authorization for Native Applications</t>
         </is>
       </c>
       <c r="C193" s="5" t="inlineStr">
         <is>
-          <t>This document defines TIBET (Transaction/Interaction-Based Evidence Trail), a data model and protocol for constructing cryptographically linked provenance chains over interactions between autonomous agents, human actors, and automated processes. A TIBET token captures four dimensions of provenance: content (ERIN), references (ERAAN), context (EROMHEEN), and intent (ERACHTER).</t>
+          <t>This document defines an extension to OAuth 2.0 [RFC6749] that enables Authorization Servers to consider Attestation Results presented by Native Applications when issuing access grants.</t>
         </is>
       </c>
       <c r="D193" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-vandemeent-tibet-provenance/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ekahraman-oauth-attestation-authz-native-app/</t>
         </is>
       </c>
       <c r="E193" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual draft)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F193" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 17 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -01, 20 Aug 2026 (was -00, 9 Jun 2026). Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6775,27 +6775,27 @@
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>draft-car-agents-txt-wellknown — AGENTS.TXT: Capability Declarations for Web Agents</t>
+          <t>draft-kay-dawn-use-cases — Use Cases for the Discovery of Agents, Workloads, and Named Entities</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>This document requests registration of two Well-Known URIs under the "/.well-known/" path: "agents.txt" and "agents.json".</t>
+          <t>This document describes broad categories of use cases for the Discovery of Agents, Workloads, and Named Entities (DAWN). The purpose of the document is to illustrate situations in which entities need to discover other entities. This document does not define a discovery protocol, a registration procedure, a selection algorithm, or an agent-to-agent communication protocol.</t>
         </is>
       </c>
       <c r="D194" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-car-agents-txt-wellknown/</t>
+          <t>https://datatracker.ietf.org/doc/draft-kay-dawn-use-cases/</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual draft)</t>
+          <t>IETF (DAWN-related, individual)</t>
         </is>
       </c>
       <c r="F194" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 12 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 7 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6805,27 +6805,27 @@
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>draft-liu-oauth-rego-policy — Rego Policy Language for OAuth 2.0 Authorization</t>
+          <t>draft-reddy-wimse-workload-attestation — WIMSE Workload Attestation</t>
         </is>
       </c>
       <c r="C195" s="5" t="inlineStr">
         <is>
-          <t>AI agents exhibit dynamic, unpredictable behavior that cannot be fully described by traditional OAuth 2.0 scopes. This specification defines a behavioral authorization framework that enables clients, particularly AI agents, to propose Rego policy-based behavioral constraint contracts in OAuth 2.0 authorization flows using Rich Authorization Requests (RAR).</t>
+          <t>This document extends the WIMSE workload-to-workload authentication architecture with a mechanism for conveying attestation across TLS- terminating proxies, a deployment topology where TLS-layer attestation mechanisms lose their end-to-end security properties.</t>
         </is>
       </c>
       <c r="D195" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-liu-oauth-rego-policy/</t>
+          <t>https://datatracker.ietf.org/doc/draft-reddy-wimse-workload-attestation/</t>
         </is>
       </c>
       <c r="E195" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (WIMSE-related, individual)</t>
         </is>
       </c>
       <c r="F195" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 12 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 7 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6835,27 +6835,27 @@
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>draft-ekahraman-oauth-attestation-authz-native-app — OAuth 2.0 Attestation Based Authorization for Native Applications</t>
+          <t>draft-madaras-preauth-receipts — PRE-RCT: Pre-Execution Authorization Receipt Format</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>This document defines an extension to OAuth 2.0 [RFC6749] that enables Authorization Servers to consider Attestation Results presented by Native Applications when issuing access grants.</t>
+          <t>This document defines PRE-RCT, the Pre-Execution Authorization Receipt, a cryptographically signed and attestation-aware receipt format used to record high-risk authorization events. PRE-RCT is intended for use with pre-execution authorization protocols such as GNA.</t>
         </is>
       </c>
       <c r="D196" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ekahraman-oauth-attestation-authz-native-app/</t>
+          <t>https://datatracker.ietf.org/doc/draft-madaras-preauth-receipts/</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (individual draft)</t>
         </is>
       </c>
       <c r="F196" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 20 Aug 2026 (was -00, 9 Jun 2026). Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 6 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked. **EXPIRED on Datatracker** (expired 6 Jun 2026; checked 26 Aug 2026) — kept in the corpus deliberately; an expired draft is still evidence of what was proposed.</t>
         </is>
       </c>
     </row>
@@ -6865,27 +6865,27 @@
       </c>
       <c r="B197" s="5" t="inlineStr">
         <is>
-          <t>draft-kay-dawn-use-cases — Use Cases for the Discovery of Agents, Workloads, and Named Entities</t>
+          <t>draft-fulz-oauth-trust-binding — OAuth Trust Binding Extension (OTBE)</t>
         </is>
       </c>
       <c r="C197" s="5" t="inlineStr">
         <is>
-          <t>This document describes broad categories of use cases for the Discovery of Agents, Workloads, and Named Entities (DAWN). The purpose of the document is to illustrate situations in which entities need to discover other entities. This document does not define a discovery protocol, a registration procedure, a selection algorithm, or an agent-to-agent communication protocol.</t>
+          <t>This document defines the OAuth Trust Binding Extension (OTBE), a mechanism allowing Resource Owners to explicitly authorize which Authorization Servers may assert their identity towards Relying Parties, mitigating silent impersonation and namespace-based identity capture.</t>
         </is>
       </c>
       <c r="D197" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-kay-dawn-use-cases/</t>
+          <t>https://datatracker.ietf.org/doc/draft-fulz-oauth-trust-binding/</t>
         </is>
       </c>
       <c r="E197" s="5" t="inlineStr">
         <is>
-          <t>IETF (DAWN-related, individual)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 7 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 30 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked. **EXPIRED on Datatracker** (expired 31 May 2026; checked 26 Aug 2026) — kept in the corpus deliberately; an expired draft is still evidence of what was proposed.</t>
         </is>
       </c>
     </row>
@@ -6895,27 +6895,27 @@
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>draft-reddy-wimse-workload-attestation — WIMSE Workload Attestation</t>
+          <t>draft-drake-agent-identity-registry — Agent Identity Registry System: A Federated Architecture for Hardware-Anchored Identity of Autonomous Entities</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>This document extends the WIMSE workload-to-workload authentication architecture with a mechanism for conveying attestation across TLS- terminating proxies, a deployment topology where TLS-layer attestation mechanisms lose their end-to-end security properties.</t>
+          <t>The Internet's identity infrastructure assumes human principals. As autonomous entities -- AI agents, robotic systems, and other non- human actors -- increasingly participate in both Internet protocols and physical society, no existing standard provides them with persistent, verifiable, hardware-anchored identity.</t>
         </is>
       </c>
       <c r="D198" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-reddy-wimse-workload-attestation/</t>
+          <t>https://datatracker.ietf.org/doc/draft-drake-agent-identity-registry/</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>IETF (WIMSE-related, individual)</t>
+          <t>IETF (individual draft)</t>
         </is>
       </c>
       <c r="F198" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 7 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -03, 22 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6925,27 +6925,27 @@
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>draft-madaras-preauth-receipts — PRE-RCT: Pre-Execution Authorization Receipt Format</t>
+          <t>draft-iannone-dawn-privacy-considerations — Privacy Considerations for the Discovery of Agents, Workloads, and Named Entities (DAWN)</t>
         </is>
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>This document defines PRE-RCT, the Pre-Execution Authorization Receipt, a cryptographically signed and attestation-aware receipt format used to record high-risk authorization events. PRE-RCT is intended for use with pre-execution authorization protocols such as GNA.</t>
+          <t>This document describes the privacy issues associated with the Discovery of Agents, Workloads, and Named Entities (DAWN). It provides general observations about typical current privacy practices in similar domains like, DNS, HTTP, and in general privacy in information retrieval.</t>
         </is>
       </c>
       <c r="D199" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-madaras-preauth-receipts/</t>
+          <t>https://datatracker.ietf.org/doc/draft-iannone-dawn-privacy-considerations/</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual draft)</t>
+          <t>IETF (DAWN-related, individual)</t>
         </is>
       </c>
       <c r="F199" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 6 Jun 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 22 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -6955,27 +6955,27 @@
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>draft-fulz-oauth-trust-binding — OAuth Trust Binding Extension (OTBE)</t>
+          <t>draft-jiang-seat-dynamic-attestation — Dynamic Attestation for AI Agent Communication</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>This document defines the OAuth Trust Binding Extension (OTBE), a mechanism allowing Resource Owners to explicitly authorize which Authorization Servers may assert their identity towards Relying Parties, mitigating silent impersonation and namespace-based identity capture.</t>
+          <t>This document describes a use case for conveying remote attestation information in association with Transport Layer Security (TLS) sessions in the context of AI agent communication.</t>
         </is>
       </c>
       <c r="D200" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-fulz-oauth-trust-binding/</t>
+          <t>https://datatracker.ietf.org/doc/draft-jiang-seat-dynamic-attestation/</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (RATS/SEAT-related, individual)</t>
         </is>
       </c>
       <c r="F200" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 30 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 17 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked. **EXPIRED on Datatracker** (expired 17 May 2026; checked 26 Aug 2026) — kept in the corpus deliberately; an expired draft is still evidence of what was proposed.</t>
         </is>
       </c>
     </row>
@@ -6985,27 +6985,27 @@
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>draft-somoza-atn-agent-trust-negotiation — Agent Trust Negotiation: Capability, Delegation, and Provenance Binding for AI Agents</t>
+          <t>draft-novak-rats-twi-attestation — Remote Attestation for Trustworthy Workload Identity</t>
         </is>
       </c>
       <c r="C201" s="5" t="inlineStr">
         <is>
-          <t>This document defines the Agent Trust Negotiation (ATN) protocol. ATN sits above whatever mechanism is used to discover an agent identity and answers questions that discovery alone cannot: what is the agent permitted to do, under whose authority, with what provenance, and how do two agents reach a verifiable working agreement.</t>
+          <t>Trustworthy Workloads are workloads that operate in environments that provide isolation of data in use. This document describes how Trustworthy Workloads can acquire credentials containing stable identifiers, upon proving the trust in the environments in which they operate via Remote Attestation.</t>
         </is>
       </c>
       <c r="D201" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-somoza-atn-agent-trust-negotiation/</t>
+          <t>https://datatracker.ietf.org/doc/draft-novak-rats-twi-attestation/</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual draft)</t>
+          <t>IETF (RATS/SEAT-related, individual)</t>
         </is>
       </c>
       <c r="F201" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 28 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 9 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked. **EXPIRED on Datatracker** (expired 9 May 2026; checked 26 Aug 2026) — kept in the corpus deliberately; an expired draft is still evidence of what was proposed.</t>
         </is>
       </c>
     </row>
@@ -7015,17 +7015,17 @@
       </c>
       <c r="B202" s="5" t="inlineStr">
         <is>
-          <t>draft-drake-agent-identity-registry — Agent Identity Registry System: A Federated Architecture for Hardware-Anchored Identity of Autonomous Entities</t>
+          <t>draft-jimenez-agent-directory — Agent Directory</t>
         </is>
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>The Internet's identity infrastructure assumes human principals. As autonomous entities -- AI agents, robotic systems, and other non- human actors -- increasingly participate in both Internet protocols and physical society, no existing standard provides them with persistent, verifiable, hardware-anchored identity.</t>
+          <t>This document defines the Agent Directory (AD), a service where agents register their identity, capabilities, and reachable endpoints and where clients discover them by capability.</t>
         </is>
       </c>
       <c r="D202" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-drake-agent-identity-registry/</t>
+          <t>https://datatracker.ietf.org/doc/draft-jimenez-agent-directory/</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="F202" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, 22 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -01, 8 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -7045,27 +7045,27 @@
       </c>
       <c r="B203" s="5" t="inlineStr">
         <is>
-          <t>draft-iannone-dawn-privacy-considerations — Privacy Considerations for the Discovery of Agents, Workloads, and Named Entities (DAWN)</t>
+          <t>draft-hardt-aauth-bootstrap — AAuth Bootstrap Guidance</t>
         </is>
       </c>
       <c r="C203" s="5" t="inlineStr">
         <is>
-          <t>This document describes the privacy issues associated with the Discovery of Agents, Workloads, and Named Entities (DAWN). It provides general observations about typical current privacy practices in similar domains like, DNS, HTTP, and in general privacy in information retrieval.</t>
+          <t>This document provides informational guidance for agent providers (APs) on enrolling agents and issuing AAuth agent tokens defined in [I-D.hardt-oauth-aauth-protocol]. It covers per-platform key handling, optional platform attestation, agent identifier strategies, and refresh patterns.</t>
         </is>
       </c>
       <c r="D203" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-iannone-dawn-privacy-considerations/</t>
+          <t>https://datatracker.ietf.org/doc/draft-hardt-aauth-bootstrap/</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
         <is>
-          <t>IETF (DAWN-related, individual)</t>
+          <t>IETF (individual draft)</t>
         </is>
       </c>
       <c r="F203" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 22 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -01, 6 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -7075,27 +7075,27 @@
       </c>
       <c r="B204" s="5" t="inlineStr">
         <is>
-          <t>draft-jiang-seat-dynamic-attestation — Dynamic Attestation for AI Agent Communication</t>
+          <t>draft-abbott-mcp-ax — MCP Aggregation Protocol (MCP-AX): Hierarchical Tool Namespace Delegation for Model Context Protocol Servers</t>
         </is>
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>This document describes a use case for conveying remote attestation information in association with Transport Layer Security (TLS) sessions in the context of AI agent communication.</t>
+          <t>This document specifies MCP-AX, an aggregation protocol for Model Context Protocol (MCP) servers. MCP-AX enables hierarchical composition of tool namespaces across heterogeneous networks of MCP servers, from cloud services to resource-constrained embedded devices.</t>
         </is>
       </c>
       <c r="D204" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-jiang-seat-dynamic-attestation/</t>
+          <t>https://datatracker.ietf.org/doc/draft-abbott-mcp-ax/</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>IETF (RATS/SEAT-related, individual)</t>
+          <t>IETF (individual draft)</t>
         </is>
       </c>
       <c r="F204" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 17 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 5 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -7105,27 +7105,27 @@
       </c>
       <c r="B205" s="5" t="inlineStr">
         <is>
-          <t>draft-novak-rats-twi-attestation — Remote Attestation for Trustworthy Workload Identity</t>
+          <t>draft-hori-agent-quality-graph — Agent Quality Graph (AQG): A Protocol for Evaluating AI Agent Trustworthiness via Delegation Graphs</t>
         </is>
       </c>
       <c r="C205" s="5" t="inlineStr">
         <is>
-          <t>Trustworthy Workloads are workloads that operate in environments that provide isolation of data in use. This document describes how Trustworthy Workloads can acquire credentials containing stable identifiers, upon proving the trust in the environments in which they operate via Remote Attestation.</t>
+          <t>This document describes the Agent Quality Graph (AQG) protocol, a method for evaluating and ranking AI agent trustworthiness based on delegation transaction graphs. As the number of autonomous AI agents grows rapidly, there is no standardized mechanism for determining which agents reliably complete delegated tasks.</t>
         </is>
       </c>
       <c r="D205" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-novak-rats-twi-attestation/</t>
+          <t>https://datatracker.ietf.org/doc/draft-hori-agent-quality-graph/</t>
         </is>
       </c>
       <c r="E205" s="5" t="inlineStr">
         <is>
-          <t>IETF (RATS/SEAT-related, individual)</t>
+          <t>IETF (individual draft)</t>
         </is>
       </c>
       <c r="F205" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 9 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 2 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
         </is>
       </c>
     </row>
@@ -7135,17 +7135,17 @@
       </c>
       <c r="B206" s="5" t="inlineStr">
         <is>
-          <t>draft-jimenez-agent-directory — Agent Directory</t>
+          <t>draft-hopley-x402-cancellation-receipt — Categorical Mandate Cancellation Receipt Format for Agentic-Payment Flows</t>
         </is>
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>This document defines the Agent Directory (AD), a service where agents register their identity, capabilities, and reachable endpoints and where clients discover them by capability.</t>
+          <t>This document specifies a categorical mandate cancellation receipt format for agentic-payment flows. The format records that a recurring-payment mandate or other standing payer-to-payee authorisation has been cancelled, by whom, for what reason, and with what effective date.</t>
         </is>
       </c>
       <c r="D206" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-jimenez-agent-directory/</t>
+          <t>https://datatracker.ietf.org/doc/draft-hopley-x402-cancellation-receipt/</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="F206" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 8 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -01, 25 May 2026. Hopley x402 agentic-payment receipt cluster (4 drafts: compliance, settlement, refund, cancellation) — categorical receipt formats for agent-initiated payment flows. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
         </is>
       </c>
     </row>
@@ -7165,17 +7165,17 @@
       </c>
       <c r="B207" s="5" t="inlineStr">
         <is>
-          <t>draft-hardt-aauth-bootstrap — AAuth Bootstrap Guidance</t>
+          <t>draft-hopley-x402-compliance-receipt — Categorical Compliance Screening Receipt Format for Agentic-Payment Flows</t>
         </is>
       </c>
       <c r="C207" s="5" t="inlineStr">
         <is>
-          <t>This document provides informational guidance for agent providers (APs) on enrolling agents and issuing AAuth agent tokens defined in [I-D.hardt-oauth-aauth-protocol]. It covers per-platform key handling, optional platform attestation, agent identifier strategies, and refresh patterns.</t>
+          <t>This document specifies a categorical compliance screening receipt format for agentic-payment flows.</t>
         </is>
       </c>
       <c r="D207" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-hardt-aauth-bootstrap/</t>
+          <t>https://datatracker.ietf.org/doc/draft-hopley-x402-compliance-receipt/</t>
         </is>
       </c>
       <c r="E207" s="5" t="inlineStr">
@@ -7185,7 +7185,7 @@
       </c>
       <c r="F207" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 6 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -02, 25 May 2026. Hopley x402 agentic-payment receipt cluster (4 drafts: compliance, settlement, refund, cancellation) — categorical receipt formats for agent-initiated payment flows. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
         </is>
       </c>
     </row>
@@ -7195,17 +7195,17 @@
       </c>
       <c r="B208" s="5" t="inlineStr">
         <is>
-          <t>draft-abbott-mcp-ax — MCP Aggregation Protocol (MCP-AX): Hierarchical Tool Namespace Delegation for Model Context Protocol Servers</t>
+          <t>draft-hopley-x402-refund-receipt — Categorical Refund Receipt Format for Agentic-Payment Flows</t>
         </is>
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>This document specifies MCP-AX, an aggregation protocol for Model Context Protocol (MCP) servers. MCP-AX enables hierarchical composition of tool namespaces across heterogeneous networks of MCP servers, from cloud services to resource-constrained embedded devices.</t>
+          <t>This document specifies a categorical refund receipt format for agentic-payment flows.</t>
         </is>
       </c>
       <c r="D208" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-abbott-mcp-ax/</t>
+          <t>https://datatracker.ietf.org/doc/draft-hopley-x402-refund-receipt/</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="F208" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 5 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -02, 25 May 2026. Hopley x402 agentic-payment receipt cluster (4 drafts: compliance, settlement, refund, cancellation) — categorical receipt formats for agent-initiated payment flows. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
         </is>
       </c>
     </row>
@@ -7225,17 +7225,17 @@
       </c>
       <c r="B209" s="5" t="inlineStr">
         <is>
-          <t>draft-hori-agent-quality-graph — Agent Quality Graph (AQG): A Protocol for Evaluating AI Agent Trustworthiness via Delegation Graphs</t>
+          <t>draft-hopley-x402-settlement-attestation — Categorical Settlement Attestation Format for Agentic-Payment Flows</t>
         </is>
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>This document describes the Agent Quality Graph (AQG) protocol, a method for evaluating and ranking AI agent trustworthiness based on delegation transaction graphs. As the number of autonomous AI agents grows rapidly, there is no standardized mechanism for determining which agents reliably complete delegated tasks.</t>
+          <t>This document specifies a categorical settlement attestation format for agentic-payment flows. The format records that a payment has reached a particular settlement state on a particular chain, at a particular instant, under the attesting party's risk model. The receipt format uses a closed enumeration of categorical outcomes (SETTLED, PENDING_FINALITY, REVERSED).</t>
         </is>
       </c>
       <c r="D209" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-hori-agent-quality-graph/</t>
+          <t>https://datatracker.ietf.org/doc/draft-hopley-x402-settlement-attestation/</t>
         </is>
       </c>
       <c r="E209" s="5" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="F209" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 2 May 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -01, 25 May 2026. Hopley x402 agentic-payment receipt cluster (4 drafts: compliance, settlement, refund, cancellation) — categorical receipt formats for agent-initiated payment flows. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
         </is>
       </c>
     </row>
@@ -7255,27 +7255,27 @@
       </c>
       <c r="B210" s="5" t="inlineStr">
         <is>
-          <t>draft-hopley-x402-cancellation-receipt — Categorical Mandate Cancellation Receipt Format for Agentic-Payment Flows</t>
+          <t>draft-skyfire-oauth-aml-methods — Anti-Money Laundering Methods Values</t>
         </is>
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>This document specifies a categorical mandate cancellation receipt format for agentic-payment flows. The format records that a recurring-payment mandate or other standing payer-to-payee authorisation has been cancelled, by whom, for what reason, and with what effective date.</t>
+          <t>Financial regulations require application of Anti-Money Laundering (AML) and Countering the Financing of Terrorism (CFT) methods in many jurisdictions worldwide. This specification defines a claim and values for declaring what AML/CFT methods were employed.</t>
         </is>
       </c>
       <c r="D210" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-hopley-x402-cancellation-receipt/</t>
+          <t>https://datatracker.ietf.org/doc/draft-skyfire-oauth-aml-methods/</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual draft)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F210" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 25 May 2026. Hopley x402 agentic-payment receipt cluster (4 drafts: compliance, settlement, refund, cancellation) — categorical receipt formats for agent-initiated payment flows. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
+          <t>Revision -00, 19 Jul 2026. Skyfire KYA/KYAPay cluster (6 drafts incl. draft-skyfire-oauth-id-verification already in corpus) — agent identity verification and payment claims for OAuth/JWT. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
         </is>
       </c>
     </row>
@@ -7285,27 +7285,27 @@
       </c>
       <c r="B211" s="5" t="inlineStr">
         <is>
-          <t>draft-hopley-x402-compliance-receipt — Categorical Compliance Screening Receipt Format for Agentic-Payment Flows</t>
+          <t>draft-skyfire-oauth-amr-values — Additional Authentication Method Reference Values</t>
         </is>
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>This document specifies a categorical compliance screening receipt format for agentic-payment flows.</t>
+          <t>The JWT "amr" (Authentication Methods References) claim contains values conveying authentication methods used in the authentication. This specification defines additional Authentication Method Reference values beyond those already registered to represent additional authentication methods in use today.</t>
         </is>
       </c>
       <c r="D211" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-hopley-x402-compliance-receipt/</t>
+          <t>https://datatracker.ietf.org/doc/draft-skyfire-oauth-amr-values/</t>
         </is>
       </c>
       <c r="E211" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual draft)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 25 May 2026. Hopley x402 agentic-payment receipt cluster (4 drafts: compliance, settlement, refund, cancellation) — categorical receipt formats for agent-initiated payment flows. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
+          <t>Revision -01, 19 Jul 2026. Skyfire KYA/KYAPay cluster (6 drafts incl. draft-skyfire-oauth-id-verification already in corpus) — agent identity verification and payment claims for OAuth/JWT. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
         </is>
       </c>
     </row>
@@ -7315,27 +7315,27 @@
       </c>
       <c r="B212" s="5" t="inlineStr">
         <is>
-          <t>draft-hopley-x402-refund-receipt — Categorical Refund Receipt Format for Agentic-Payment Flows</t>
+          <t>draft-skyfire-oauth-kyapay-token — KYAPay Token</t>
         </is>
       </c>
       <c r="C212" s="5" t="inlineStr">
         <is>
-          <t>This document specifies a categorical refund receipt format for agentic-payment flows.</t>
+          <t>This document defines a token format for agent identity and payment tokens in JSON Web Token (JWT) format. Authorization servers and resource servers from different vendors can leverage this token format to consume identity and payment tokens in an interoperable manner.</t>
         </is>
       </c>
       <c r="D212" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-hopley-x402-refund-receipt/</t>
+          <t>https://datatracker.ietf.org/doc/draft-skyfire-oauth-kyapay-token/</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual draft)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 25 May 2026. Hopley x402 agentic-payment receipt cluster (4 drafts: compliance, settlement, refund, cancellation) — categorical receipt formats for agent-initiated payment flows. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
+          <t>Revision -01, 19 Jul 2026. Skyfire KYA/KYAPay cluster (6 drafts incl. draft-skyfire-oauth-id-verification already in corpus) — agent identity verification and payment claims for OAuth/JWT. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
         </is>
       </c>
     </row>
@@ -7345,27 +7345,27 @@
       </c>
       <c r="B213" s="5" t="inlineStr">
         <is>
-          <t>draft-hopley-x402-settlement-attestation — Categorical Settlement Attestation Format for Agentic-Payment Flows</t>
+          <t>draft-skyfire-oauth-kyapay-token-exchange — KYAPay Token Exchange</t>
         </is>
       </c>
       <c r="C213" s="5" t="inlineStr">
         <is>
-          <t>This document specifies a categorical settlement attestation format for agentic-payment flows. The format records that a payment has reached a particular settlement state on a particular chain, at a particular instant, under the attesting party's risk model. The receipt format uses a closed enumeration of categorical outcomes (SETTLED, PENDING_FINALITY, REVERSED).</t>
+          <t>This specification describes how KYAPay tokens can be exchanged for OAuth access tokens to dynamically grant agents access to resources they need to accomplish their mission.</t>
         </is>
       </c>
       <c r="D213" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-hopley-x402-settlement-attestation/</t>
+          <t>https://datatracker.ietf.org/doc/draft-skyfire-oauth-kyapay-token-exchange/</t>
         </is>
       </c>
       <c r="E213" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual draft)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F213" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 25 May 2026. Hopley x402 agentic-payment receipt cluster (4 drafts: compliance, settlement, refund, cancellation) — categorical receipt formats for agent-initiated payment flows. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
+          <t>Revision -01, 19 Jul 2026. Skyfire KYA/KYAPay cluster (6 drafts incl. draft-skyfire-oauth-id-verification already in corpus) — agent identity verification and payment claims for OAuth/JWT. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
         </is>
       </c>
     </row>
@@ -7375,17 +7375,17 @@
       </c>
       <c r="B214" s="5" t="inlineStr">
         <is>
-          <t>draft-skyfire-oauth-aml-methods — Anti-Money Laundering Methods Values</t>
+          <t>draft-skyfire-oauth-using-kyapay-tokens — Using KYAPay Tokens</t>
         </is>
       </c>
       <c r="C214" s="5" t="inlineStr">
         <is>
-          <t>Financial regulations require application of Anti-Money Laundering (AML) and Countering the Financing of Terrorism (CFT) methods in many jurisdictions worldwide. This specification defines a claim and values for declaring what AML/CFT methods were employed.</t>
+          <t>The KYAPay Token is a JSON Web Token (JWT) that carries verified identity ("Know Your Agent", KYA) and payment (PAY) information for requests made by software agents on behalf of human principals.</t>
         </is>
       </c>
       <c r="D214" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-skyfire-oauth-aml-methods/</t>
+          <t>https://datatracker.ietf.org/doc/draft-skyfire-oauth-using-kyapay-tokens/</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
@@ -7405,27 +7405,27 @@
       </c>
       <c r="B215" s="5" t="inlineStr">
         <is>
-          <t>draft-skyfire-oauth-amr-values — Additional Authentication Method Reference Values</t>
+          <t>draft-morrison-mcp-tool-surface-names-registry — An IANA Registry for Model Context Protocol Tool Surface Names</t>
         </is>
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>The JWT "amr" (Authentication Methods References) claim contains values conveying authentication methods used in the authentication. This specification defines additional Authentication Method Reference values beyond those already registered to represent additional authentication methods in use today.</t>
+          <t>This document requests the establishment of an IANA registry for Model Context Protocol [MCP-SPEC] tool surface names. A tool surface name is the wire-level identifier by which a client invokes a typed capability on an MCP server. Existing Morrison- family Internet- Drafts ([ORGALTER]) request IANA registration of specific surface names against a registry that does not yet exist. This document establishes the registry mechanism so that subsequent specifications can register names without restating the registry's structure or registration procedure. The registry uses Specification Required registration with a Designated Expert pool [RFC8126]. Initial contents are the four surface names registered by [ORGALTER]. Vendor-prefix conventions are recommended but not mandated.</t>
         </is>
       </c>
       <c r="D215" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-skyfire-oauth-amr-values/</t>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-mcp-tool-surface-names-registry/</t>
         </is>
       </c>
       <c r="E215" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (individual)</t>
         </is>
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 19 Jul 2026. Skyfire KYA/KYAPay cluster (6 drafts incl. draft-skyfire-oauth-id-verification already in corpus) — agent identity verification and payment claims for OAuth/JWT. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
+          <t>Revision -01, 11 Aug 2026. Requests an IANA registry for MCP tool surface names. Morrison family plumbing — exists because other Morrison drafts already request registrations against a registry that does not yet exist. Structural, not conceptual, but it is the family's dependency root.</t>
         </is>
       </c>
     </row>
@@ -7435,27 +7435,27 @@
       </c>
       <c r="B216" s="5" t="inlineStr">
         <is>
-          <t>draft-skyfire-oauth-kyapay-token — KYAPay Token</t>
+          <t>draft-morrison-identity-pronouns — Identity Pronouns: A Reference-Axis Extension to ~handle Identity Systems</t>
         </is>
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
-          <t>This document defines a token format for agent identity and payment tokens in JSON Web Token (JWT) format. Authorization servers and resource servers from different vendors can leverage this token format to consume identity and payment tokens in an interoperable manner.</t>
+          <t>This document defines an identity pronoun grammar as a reference axis orthogonal to the ~handle identity tier taxonomy defined in [MCPDNS] and [IDCOMMITS]. A pronoun is a session-scoped reference that resolves client-side to a concrete handle using local session state before any cryptographic, DNS, or federation operation. The entity- class taxonomy (Sovereign, Bot, Instrument) is unchanged; this specification introduces Absolute vs Pronoun as an orthogonal axis. A pronoun MUST NOT appear in a capability token, in a DNS record, in an Accord signature, or in any inter-organisational protocol payload. The reference implementation defines a single Wave-1 pronoun, ~org, that resolves to the concrete handle of the organisation bound to the caller's current session. An appendix defines a relative-path pronoun grammar (e.g. ~./architect, ~../weaver) as a non-normative design surface for future work. The mechanism is provider-neutral, introduces no new cryptographic primitive, and imposes zero new load on DNS, capability-token issuers, or federated resolvers.</t>
         </is>
       </c>
       <c r="D216" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-skyfire-oauth-kyapay-token/</t>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-identity-pronouns/</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (individual)</t>
         </is>
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 19 Jul 2026. Skyfire KYA/KYAPay cluster (6 drafts incl. draft-skyfire-oauth-id-verification already in corpus) — agent identity verification and payment claims for OAuth/JWT. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
+          <t>Revision -02, 11 Aug 2026. Session-scoped 'pronoun' references that resolve client-side to concrete ~handle identities. Morrison family. Kept under the primary-body rule rather than on individual merit: the family is taken in full. Design note worth flagging — a pronoun MUST NOT appear in a capability token, DNS record, or Accord signature, which is an explicit boundary between local reference and wire-visible identity.</t>
         </is>
       </c>
     </row>
@@ -7465,27 +7465,27 @@
       </c>
       <c r="B217" s="5" t="inlineStr">
         <is>
-          <t>draft-skyfire-oauth-kyapay-token-exchange — KYAPay Token Exchange</t>
+          <t>draft-morrison-identity-attributed-commits — Identity-Attributed Git Commits via Tier-Structured Trailers</t>
         </is>
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>This specification describes how KYAPay tokens can be exchanged for OAuth access tokens to dynamically grant agents access to resources they need to accomplish their mission.</t>
+          <t>This document defines a git commit trailer grammar for identity- attributed contributions using the ~handle identity primitive defined in [MCPDNS]. The grammar binds sovereign actors, automated bots, and AI instruments to specific commits via three tier-structured trailers (Acted-By, Executed-By, Drafted-With) and three optional cryptographic trailers (Identity-Signature, Identity-Key-Id, Identity-Anchor). The signature is computed with Ed25519 over the commit's tree hash rather than its commit hash, preserving attribution across rebase, cherry-pick, and squash merge operations. Conformant parsers reject cross-tier category errors (e.g., an Instrument-tier handle in an Acted-By slot) as malformed. The mechanism is provider-neutral, depends only on DNS [RFC1035] and the ~handle resolution algorithm of [MCPDNS], and requires no central authority or platform-specific verification service.</t>
         </is>
       </c>
       <c r="D217" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-skyfire-oauth-kyapay-token-exchange/</t>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-identity-attributed-commits/</t>
         </is>
       </c>
       <c r="E217" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (individual)</t>
         </is>
       </c>
       <c r="F217" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 19 Jul 2026. Skyfire KYA/KYAPay cluster (6 drafts incl. draft-skyfire-oauth-id-verification already in corpus) — agent identity verification and payment claims for OAuth/JWT. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
+          <t>Revision -02, 11 Aug 2026. Git commit trailers (Acted-By / Executed-By / Drafted-With) binding sovereign actors, bots and AI instruments to specific commits. Morrison family. The three-tier actor taxonomy is a direct echo of the actor-chain question in draft-mcguinness-oauth-actor-profile and draft-mw-oauth-actor-chain, expressed in a completely different substrate. Ed25519 over the tree hash rather than the commit hash so attribution survives rebase and squash.</t>
         </is>
       </c>
     </row>
@@ -7495,27 +7495,27 @@
       </c>
       <c r="B218" s="5" t="inlineStr">
         <is>
-          <t>draft-skyfire-oauth-using-kyapay-tokens — Using KYAPay Tokens</t>
+          <t>draft-morrison-agent-channel-fan-out — An Agent-Channel Frame for Identity-Keyed Fan-Out Delivery to Concurrent Sessions</t>
         </is>
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
-          <t>The KYAPay Token is a JSON Web Token (JWT) that carries verified identity ("Know Your Agent", KYA) and payment (PAY) information for requests made by software agents on behalf of human principals.</t>
+          <t>This memo specifies an application-layer frame format and a delivery model by which the several concurrent agentic sessions of a single identity-bound principal, and the recognised members of an organisational identity substrate, exchange short structured messages. The frame, termed the agent-channel frame, is a transport envelope: it carries a closed-catalogue kind discriminator, a structured per-kind payload, an identity attribution pair, and an inline provenance block. Delivery is fan-out: a sender names a recipient scope rather than a single endpoint, and the scope is expanded at delivery time against the recipient's subscriptions. Recipients receive frames over a per-handle Server-Sent Events stream and MAY narrow what they receive with a subscribe-time filter expression. Frames are ephemeral routing units; the memo specifies only the wire envelope, the scope-expansion grammar, the subscribe filter grammar, and the delivery semantics. Frame persistence, where an implementation chooses to retain frames for replay, is out of scope and is not specified. The memo composes with the handle namespace of [IDPRONOUNS], the discovery surface of [MCPDNS], and the cross-organisational ceremony of [IDACCORD]; no new transport and no new handle category is introduced.</t>
         </is>
       </c>
       <c r="D218" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-skyfire-oauth-using-kyapay-tokens/</t>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-agent-channel-fan-out/</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (individual)</t>
         </is>
       </c>
       <c r="F218" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 19 Jul 2026. Skyfire KYA/KYAPay cluster (6 drafts incl. draft-skyfire-oauth-id-verification already in corpus) — agent identity verification and payment claims for OAuth/JWT. Reinstated 11 Aug 2026 after initially being filtered out of the Aug 2026 sweep as payments-infra.</t>
+          <t>Revision -01, 11 Aug 2026. Application-layer frame for identity-keyed fan-out delivery to the concurrent sessions of one identity-bound principal. Morrison family. Transport-shaped, but kept because the frame carries an identity attribution pair and inline provenance block — it is an identity-binding format, not a routing protocol.</t>
         </is>
       </c>
     </row>
@@ -7525,17 +7525,17 @@
       </c>
       <c r="B219" s="5" t="inlineStr">
         <is>
-          <t>draft-morrison-mcp-tool-surface-names-registry — An IANA Registry for Model Context Protocol Tool Surface Names</t>
+          <t>draft-hillier-certisyn-ai-governance-verified — AI Governance Verified -- A Cryptographic Verification Standard for Agentic AI Governance in Regulated Industries</t>
         </is>
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>This document requests the establishment of an IANA registry for Model Context Protocol [MCP-SPEC] tool surface names. A tool surface name is the wire-level identifier by which a client invokes a typed capability on an MCP server. Existing Morrison- family Internet- Drafts ([ORGALTER]) request IANA registration of specific surface names against a registry that does not yet exist. This document establishes the registry mechanism so that subsequent specifications can register names without restating the registry's structure or registration procedure. The registry uses Specification Required registration with a Designated Expert pool [RFC8126]. Initial contents are the four surface names registered by [ORGALTER]. Vendor-prefix conventions are recommended but not mandated.</t>
+          <t>This document specifies a verification standard for the cryptographic attestation of agentic AI governance in regulated industries. It defines the Verification Reconciliation Object (VRO), the issuing- partner framework, the eight control areas through which AI governance posture is reconciled, three maturity-attestation levels (Documented, Operational, Adversarial-ready), and the cryptographic continuity requirements that together produce deterministic, independently reconstructable, auditor-grade attestations of agentic AI governance. The standard sits beneath ISO/IEC 42001:2023, the NIST AI Risk Management Framework, and other agentic AI governance frameworks, and produces the verifiable artefact those frameworks were designed to imply but do not deliver.</t>
         </is>
       </c>
       <c r="D219" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-morrison-mcp-tool-surface-names-registry/</t>
+          <t>https://datatracker.ietf.org/doc/draft-hillier-certisyn-ai-governance-verified/</t>
         </is>
       </c>
       <c r="E219" s="5" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="F219" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 11 Aug 2026. Requests an IANA registry for MCP tool surface names. Morrison family plumbing — exists because other Morrison drafts already request registrations against a registry that does not yet exist. Structural, not conceptual, but it is the family's dependency root.</t>
+          <t>Revision -02, 12 Aug 2026. Cryptographic attestation of agentic AI governance posture for regulated industries: the Verification Reconciliation Object, eight control areas, three maturity-attestation levels. Positioned beneath ISO/IEC 42001:2023, so it is the compliance-facing counterpart to the audit-architecture work. Hillier has two further drafts in this sweep (scitt-arp, coverage-attestation) that were dropped as non-agent supply-chain work — revisit if the author's direction turns agent-specific.</t>
         </is>
       </c>
     </row>
@@ -7555,27 +7555,27 @@
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t>draft-morrison-identity-pronouns — Identity Pronouns: A Reference-Axis Extension to ~handle Identity Systems</t>
+          <t>draft-winmagic-oauth-condition-bound-keys — Condition-Bound Keys for Mutual-TLS Client Authentication and DPoP</t>
         </is>
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
-          <t>This document defines an identity pronoun grammar as a reference axis orthogonal to the ~handle identity tier taxonomy defined in [MCPDNS] and [IDCOMMITS]. A pronoun is a session-scoped reference that resolves client-side to a concrete handle using local session state before any cryptographic, DNS, or federation operation. The entity- class taxonomy (Sovereign, Bot, Instrument) is unchanged; this specification introduces Absolute vs Pronoun as an orthogonal axis. A pronoun MUST NOT appear in a capability token, in a DNS record, in an Accord signature, or in any inter-organisational protocol payload. The reference implementation defines a single Wave-1 pronoun, ~org, that resolves to the concrete handle of the organisation bound to the caller's current session. An appendix defines a relative-path pronoun grammar (e.g. ~./architect, ~../weaver) as a non-normative design surface for future work. The mechanism is provider-neutral, introduces no new cryptographic primitive, and imposes zero new load on DNS, capability-token issuers, or federated resolvers.</t>
+          <t>Login and session protection are two markets solving one problem: verify identity before giving access. Online, access is mostly the transaction, so that is where identity should be verified. Done this way, there is no session and no login; identity assurance is embedded in the transaction: it is encrypted by a key only the right identity has. The key that does this exists only where an actor -- human or machine -- a platform, and local policy hold, now. It disappears when the conditions are no longer met. All three are observed on the endpoint. It is hardware-rooted by default and non-exfiltratable, existing nowhere else, and its presence means validity: the identity is live now. This document specifies that key and its uses: under mutual TLS, in a DPoP proof, as a raw public key, in Device Bound Session Credentials, and as a FIDO2 passkey, or in a non-FIDO mode carrying user verification without user interaction.</t>
         </is>
       </c>
       <c r="D220" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-morrison-identity-pronouns/</t>
+          <t>https://datatracker.ietf.org/doc/draft-winmagic-oauth-condition-bound-keys/</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 11 Aug 2026. Session-scoped 'pronoun' references that resolve client-side to concrete ~handle identities. Morrison family. Kept under the primary-body rule rather than on individual merit: the family is taken in full. Design note worth flagging — a pronoun MUST NOT appear in a capability token, DNS record, or Accord signature, which is an explicit boundary between local reference and wire-visible identity.</t>
+          <t>Revision -00, 12 Aug 2026. Binds mTLS client authentication and DPoP keys to conditions rather than to a bare key identity. Files cleanly into the OAuth wiki's **Proof of Possession** cluster, which the 11 Aug 2026 mapping flagged as showing 'Active Drafts: (none)' — this is further evidence that agent-era drafts should be filed by mechanism rather than by being agent-flavoured.</t>
         </is>
       </c>
     </row>
@@ -7585,17 +7585,17 @@
       </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
-          <t>draft-morrison-identity-attributed-commits — Identity-Attributed Git Commits via Tier-Structured Trailers</t>
+          <t>draft-maintainer-1f916-agent-record — The Agent Record: Transparent, Witness-Countersigned Event Logs for AI Agent Identity, History, and Memory</t>
         </is>
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>This document defines a git commit trailer grammar for identity- attributed contributions using the ~handle identity primitive defined in [MCPDNS]. The grammar binds sovereign actors, automated bots, and AI instruments to specific commits via three tier-structured trailers (Acted-By, Executed-By, Drafted-With) and three optional cryptographic trailers (Identity-Signature, Identity-Key-Id, Identity-Anchor). The signature is computed with Ed25519 over the commit's tree hash rather than its commit hash, preserving attribution across rebase, cherry-pick, and squash merge operations. Conformant parsers reject cross-tier category errors (e.g., an Instrument-tier handle in an Acted-By slot) as malformed. The mechanism is provider-neutral, depends only on DNS [RFC1035] and the ~handle resolution algorithm of [MCPDNS], and requires no central authority or platform-specific verification service.</t>
+          <t>Autonomous AI agents increasingly act as economic parties: they are hired, they pay, and they make claims about their own past conduct. No deployed standard lets a relying party verify an agent's identity continuity, the integrity of its claimed history, or the intactness of its persisted memory without trusting the agent's operator or platform. This document describes the Agent Record architecture: per-agent append-only event logs bound to Ed25519 keys, checkpointed with signed Merkle tree heads following the RFC 6962 construction, countersigned by independent witnesses, and exported as portable, offline-verifiable dossiers. Memory integrity is anchored by hash commitments recorded in the log, allowing an agent's future sessions, and any third party, to detect tampering with persisted state. The architecture is deployed in production at a founding registry; this document records its wire formats and security model to invite independent implementation and review, and to align terminology with the SCITT architecture, of which this system is an application- specific instance.</t>
         </is>
       </c>
       <c r="D221" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-morrison-identity-attributed-commits/</t>
+          <t>https://datatracker.ietf.org/doc/draft-maintainer-1f916-agent-record/</t>
         </is>
       </c>
       <c r="E221" s="5" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="F221" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 11 Aug 2026. Git commit trailers (Acted-By / Executed-By / Drafted-With) binding sovereign actors, bots and AI instruments to specific commits. Morrison family. The three-tier actor taxonomy is a direct echo of the actor-chain question in draft-mcguinness-oauth-actor-profile and draft-mw-oauth-actor-chain, expressed in a completely different substrate. Ed25519 over the tree hash rather than the commit hash so attribution survives rebase and squash.</t>
+          <t>Revision -01, 13 Aug 2026. Per-agent append-only event logs bound to Ed25519 keys, checkpointed with signed Merkle tree heads on the RFC 6962 construction and countersigned by independent witnesses. **Unusual authorship signal: the draft's author slug is `maintainer-1f916` — U+1F916 is the robot-face emoji codepoint.** Treat provenance with care. The technical premise is serious and rare: agents as economic parties that make claims about their own past conduct, verifiable without trusting the operator or platform.</t>
         </is>
       </c>
     </row>
@@ -7615,17 +7615,17 @@
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
-          <t>draft-morrison-agent-channel-fan-out — An Agent-Channel Frame for Identity-Keyed Fan-Out Delivery to Concurrent Sessions</t>
+          <t>draft-sirkkavaara-vaara-receipt — The Vaara Receipt: A Recomputable Receipt Format for Decisions About Autonomous Actions</t>
         </is>
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>This memo specifies an application-layer frame format and a delivery model by which the several concurrent agentic sessions of a single identity-bound principal, and the recognised members of an organisational identity substrate, exchange short structured messages. The frame, termed the agent-channel frame, is a transport envelope: it carries a closed-catalogue kind discriminator, a structured per-kind payload, an identity attribution pair, and an inline provenance block. Delivery is fan-out: a sender names a recipient scope rather than a single endpoint, and the scope is expanded at delivery time against the recipient's subscriptions. Recipients receive frames over a per-handle Server-Sent Events stream and MAY narrow what they receive with a subscribe-time filter expression. Frames are ephemeral routing units; the memo specifies only the wire envelope, the scope-expansion grammar, the subscribe filter grammar, and the delivery semantics. Frame persistence, where an implementation chooses to retain frames for replay, is out of scope and is not specified. The memo composes with the handle namespace of [IDPRONOUNS], the discovery surface of [MCPDNS], and the cross-organisational ceremony of [IDACCORD]; no new transport and no new handle category is introduced.</t>
+          <t>This document specifies vaara.receipt/v1, a signed and independently recomputable record that binds a decision about an autonomous action to the evidence the decision was made on, and optionally to one or more external timestamp anchors. The format is canonicalized with the JSON Canonicalization Scheme (JCS) so that any third party can recompute its digests and verify its signature without access to the issuer. A decision and the execution receipt that answers it form one recomputable pair through the envelope's back link. The receipt's trust is root-agnostic: the same record is verifiable with or without a hardware trusted execution environment and is re- expressible as an IETF RATS Entity Attestation Result. Downstream specifications (a payment rail, a compliance regime, a framework integration) define profiles that pin to a version of this document and add only their own evidence schema; they do not redefine the envelope. The format described here is deployed, and its receipts are independently recomputable from public conformance vectors that ship with standalone checkers importing no issuer code. The minimal profile is a governance decision over a single autonomous action, bound to the action's own intent with no external rail; it is the floor of the format, and a reference library offers a matching adoption floor at the API layer as a one-line decorator over the governed function.</t>
         </is>
       </c>
       <c r="D222" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-morrison-agent-channel-fan-out/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sirkkavaara-vaara-receipt/</t>
         </is>
       </c>
       <c r="E222" s="5" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 11 Aug 2026. Application-layer frame for identity-keyed fan-out delivery to the concurrent sessions of one identity-bound principal. Morrison family. Transport-shaped, but kept because the frame carries an identity attribution pair and inline provenance block — it is an identity-binding format, not a routing protocol.</t>
+          <t>Revision -07, 13 Aug 2026. A *recomputable* receipt format for decisions about autonomous actions — at -07, one of the more mature individual receipt drafts in the corpus. Recomputability is the distinguishing claim: the receipt is not merely signed evidence but re-derivable, which is a stronger property than the Decision Evidence Records in the Mission-Bound runtime-enforcement profile.</t>
         </is>
       </c>
     </row>
@@ -7645,17 +7645,17 @@
       </c>
       <c r="B223" s="5" t="inlineStr">
         <is>
-          <t>draft-hillier-certisyn-ai-governance-verified — AI Governance Verified -- A Cryptographic Verification Standard for Agentic AI Governance in Regulated Industries</t>
+          <t>draft-ruvalcaba-nhe-identity — NHE Identity: A Verifiable Key-Committed Identity and Genesis-Attestation Format for Autonomous Agents</t>
         </is>
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>This document specifies a verification standard for the cryptographic attestation of agentic AI governance in regulated industries. It defines the Verification Reconciliation Object (VRO), the issuing- partner framework, the eight control areas through which AI governance posture is reconciled, three maturity-attestation levels (Documented, Operational, Adversarial-ready), and the cryptographic continuity requirements that together produce deterministic, independently reconstructable, auditor-grade attestations of agentic AI governance. The standard sits beneath ISO/IEC 42001:2023, the NIST AI Risk Management Framework, and other agentic AI governance frameworks, and produces the verifiable artefact those frameworks were designed to imply but do not deliver.</t>
+          <t>This document specifies how a Non-Human Entity (NHE) is identified and how one party verifies another's identity. An NHE identity is a verifiable cryptographic commitment: control of an identity key, bound by an append-only hash chain to the entity's genesis and to the lineage of its configuration, rather than a mere name. The document defines the identity chain data model (record structure, genesis sentinel, linkage rule, and the no-fork property), a proof-of-control challenge/response, an optional capability attestation that reveals a specific capability without revealing the rest of the configuration, and an optional hardware-rooted genesis-attestation profile. The data model is specified here; the concrete on-the-wire encoding is deferred to the next revision.</t>
         </is>
       </c>
       <c r="D223" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-hillier-certisyn-ai-governance-verified/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ruvalcaba-nhe-identity/</t>
         </is>
       </c>
       <c r="E223" s="5" t="inlineStr">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 12 Aug 2026. Cryptographic attestation of agentic AI governance posture for regulated industries: the Verification Reconciliation Object, eight control areas, three maturity-attestation levels. Positioned beneath ISO/IEC 42001:2023, so it is the compliance-facing counterpart to the audit-architecture work. Hillier has two further drafts in this sweep (scitt-arp, coverage-attestation) that were dropped as non-agent supply-chain work — revisit if the author's direction turns agent-specific.</t>
+          <t>Revision -00, 13 Aug 2026. Verifiable key-committed identity plus genesis-attestation format for autonomous agents. First half of the NHE pair; the genesis attestation (proving how the agent came into existence) is a stronger origin claim than the instance assertions in draft-mcguinness-oauth-ai-agent-instance.</t>
         </is>
       </c>
     </row>
@@ -7675,27 +7675,27 @@
       </c>
       <c r="B224" s="5" t="inlineStr">
         <is>
-          <t>draft-winmagic-oauth-condition-bound-keys — Condition-Bound Keys for Mutual-TLS Client Authentication and DPoP</t>
+          <t>draft-ruvalcaba-nhe-authz — NHE Backchannel Authorization: Graduated Autonomy and Intent-Scoped Credentials for Autonomous Agent Actions</t>
         </is>
       </c>
       <c r="C224" s="5" t="inlineStr">
         <is>
-          <t>Login and session protection are two markets solving one problem: verify identity before giving access. Online, access is mostly the transaction, so that is where identity should be verified. Done this way, there is no session and no login; identity assurance is embedded in the transaction: it is encrypted by a key only the right identity has. The key that does this exists only where an actor -- human or machine -- a platform, and local policy hold, now. It disappears when the conditions are no longer met. All three are observed on the endpoint. It is hardware-rooted by default and non-exfiltratable, existing nowhere else, and its presence means validity: the identity is live now. This document specifies that key and its uses: under mutual TLS, in a DPoP proof, as a raw public key, in Device Bound Session Credentials, and as a FIDO2 passkey, or in a non-FIDO mode carrying user verification without user interaction.</t>
+          <t>This document specifies how a consequential action attempted by a Non-Human Entity (NHE) is authorized at the time it is attempted. A security runtime transparently intercepts an entity's outbound action, so the entity holds no standing credentials, and classifies it under graduated autonomy as autonomous, supervised, or denied. A supervised action triggers a backchannel approval flow that presents a human approver with a human-readable rendering of the exact operation; on approval the runtime issues an intent-scoped, single- use, short-lived credential cryptographically bound to that specific action, which an enforcement point verifies against the operation actually being forwarded. The same canonical parameter digest scopes the credential and appears in the human-facing description, so the approver provably authorizes exactly what the credential permits. The flow and credential data model are specified here; the wire encoding is deferred to the next revision.</t>
         </is>
       </c>
       <c r="D224" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-winmagic-oauth-condition-bound-keys/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ruvalcaba-nhe-authz/</t>
         </is>
       </c>
       <c r="E224" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (individual)</t>
         </is>
       </c>
       <c r="F224" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 12 Aug 2026. Binds mTLS client authentication and DPoP keys to conditions rather than to a bare key identity. Files cleanly into the OAuth wiki's **Proof of Possession** cluster, which the 11 Aug 2026 mapping flagged as showing 'Active Drafts: (none)' — this is further evidence that agent-era drafts should be filed by mechanism rather than by being agent-flavoured.</t>
+          <t>Revision -00, 13 Aug 2026. Backchannel authorization with **graduated autonomy** and intent-scoped credentials. Second half of the NHE pair. 'Graduated autonomy' and 'intent-scoped' are close cousins of the Mission-Bound Conformance Ladder (L0–L5) and mission_intent RAR envelope respectively, arrived at independently — worth comparing directly.</t>
         </is>
       </c>
     </row>
@@ -7705,17 +7705,17 @@
       </c>
       <c r="B225" s="5" t="inlineStr">
         <is>
-          <t>draft-maintainer-1f916-agent-record — The Agent Record: Transparent, Witness-Countersigned Event Logs for AI Agent Identity, History, and Memory</t>
+          <t>draft-daniel-ai-agent-internet-architecture — Architectural Requirements for Supporting AI Agents on the Internet</t>
         </is>
       </c>
       <c r="C225" s="5" t="inlineStr">
         <is>
-          <t>Autonomous AI agents increasingly act as economic parties: they are hired, they pay, and they make claims about their own past conduct. No deployed standard lets a relying party verify an agent's identity continuity, the integrity of its claimed history, or the intactness of its persisted memory without trusting the agent's operator or platform. This document describes the Agent Record architecture: per-agent append-only event logs bound to Ed25519 keys, checkpointed with signed Merkle tree heads following the RFC 6962 construction, countersigned by independent witnesses, and exported as portable, offline-verifiable dossiers. Memory integrity is anchored by hash commitments recorded in the log, allowing an agent's future sessions, and any third party, to detect tampering with persisted state. The architecture is deployed in production at a founding registry; this document records its wire formats and security model to invite independent implementation and review, and to align terminology with the SCITT architecture, of which this system is an application- specific instance.</t>
+          <t>Autonomous AI agents are evolving from interactive assistants into networked software workloads that discover services, invoke tools, delegate authority, transact, communicate with other agents, and act asynchronously on behalf of humans and organizations. Existing Internet protocols provide strong foundations, but agent autonomy, dynamic delegation, machine-speed execution, and cross-domain interaction create requirements that span multiple protocol families. This document describes architectural requirements for supporting AI agents on the Internet across naming and discovery, HTTP, authentication, authorization and delegation, TLS and workload identity, asynchronous messaging, capability and intent-based resolution, payments, provenance, auditability, revocation, security, and privacy. It favors profiling and extending existing Internet protocols over defining a monolithic new agent protocol, and identifies the need for IETF-wide architectural coordination.</t>
         </is>
       </c>
       <c r="D225" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-maintainer-1f916-agent-record/</t>
+          <t>https://datatracker.ietf.org/doc/draft-daniel-ai-agent-internet-architecture/</t>
         </is>
       </c>
       <c r="E225" s="5" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="F225" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 13 Aug 2026. Per-agent append-only event logs bound to Ed25519 keys, checkpointed with signed Merkle tree heads on the RFC 6962 construction and countersigned by independent witnesses. **Unusual authorship signal: the draft's author slug is `maintainer-1f916` — U+1F916 is the robot-face emoji codepoint.** Treat provenance with care. The technical premise is serious and rare: agents as economic parties that make claims about their own past conduct, verifiable without trusting the operator or platform.</t>
+          <t>Revision -00, 13 Aug 2026. Architectural requirements for supporting AI agents on the Internet. A framework document rather than a mechanism — belongs with the adjacent/cross-cutting cluster alongside the other applicability and architecture statements.</t>
         </is>
       </c>
     </row>
@@ -7735,17 +7735,17 @@
       </c>
       <c r="B226" s="5" t="inlineStr">
         <is>
-          <t>draft-sirkkavaara-vaara-receipt — The Vaara Receipt: A Recomputable Receipt Format for Decisions About Autonomous Actions</t>
+          <t>draft-gaikwad-agent-proxy-modes — Proxy Modes for Agent-Tool Protocols</t>
         </is>
       </c>
       <c r="C226" s="5" t="inlineStr">
         <is>
-          <t>This document specifies vaara.receipt/v1, a signed and independently recomputable record that binds a decision about an autonomous action to the evidence the decision was made on, and optionally to one or more external timestamp anchors. The format is canonicalized with the JSON Canonicalization Scheme (JCS) so that any third party can recompute its digests and verify its signature without access to the issuer. A decision and the execution receipt that answers it form one recomputable pair through the envelope's back link. The receipt's trust is root-agnostic: the same record is verifiable with or without a hardware trusted execution environment and is re- expressible as an IETF RATS Entity Attestation Result. Downstream specifications (a payment rail, a compliance regime, a framework integration) define profiles that pin to a version of this document and add only their own evidence schema; they do not redefine the envelope. The format described here is deployed, and its receipts are independently recomputable from public conformance vectors that ship with standalone checkers importing no issuer code. The minimal profile is a governance decision over a single autonomous action, bound to the action's own intent with no external rail; it is the floor of the format, and a reference library offers a matching adoption floor at the API layer as a one-line decorator over the governed function.</t>
+          <t>Agent-tool protocols such as the Model Context Protocol (MCP) enable AI applications to discover and invoke external tools, resources, and prompts through a standardized JSON-RPC interface. As deployments scale, intermediaries (proxies, gateways, sidecars) are inserted between clients and servers to provide transport adaptation, capability aggregation, security enforcement, and operational governance. No specification currently defines the behavioral requirements for such intermediaries. This document establishes a taxonomy of proxy modes, a layered architecture for pluggable proxy functionality, and normative requirements for each mode. It is designed to be protocol- agnostic in its architecture while referencing MCP as the primary instantiation.</t>
         </is>
       </c>
       <c r="D226" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sirkkavaara-vaara-receipt/</t>
+          <t>https://datatracker.ietf.org/doc/draft-gaikwad-agent-proxy-modes/</t>
         </is>
       </c>
       <c r="E226" s="5" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
-          <t>Revision -07, 13 Aug 2026. A *recomputable* receipt format for decisions about autonomous actions — at -07, one of the more mature individual receipt drafts in the corpus. Recomputability is the distinguishing claim: the receipt is not merely signed evidence but re-derivable, which is a stronger property than the Decision Evidence Records in the Mission-Bound runtime-enforcement profile.</t>
+          <t>Revision -00, 14 Aug 2026. Proxy modes for agent-tool protocols. Enumerates how an intermediary sits between agent and tool, which is precisely where authority is most often silently laundered — the delegation-mechanics question the actor-chain drafts raise, at the proxy layer.</t>
         </is>
       </c>
     </row>
@@ -7765,27 +7765,27 @@
       </c>
       <c r="B227" s="5" t="inlineStr">
         <is>
-          <t>draft-ruvalcaba-nhe-identity — NHE Identity: A Verifiable Key-Committed Identity and Genesis-Attestation Format for Autonomous Agents</t>
+          <t>draft-cui-dmsc-agent-cdi — Cross-Domain Interoperability Framework for AI Agent Collaboration</t>
         </is>
       </c>
       <c r="C227" s="5" t="inlineStr">
         <is>
-          <t>This document specifies how a Non-Human Entity (NHE) is identified and how one party verifies another's identity. An NHE identity is a verifiable cryptographic commitment: control of an identity key, bound by an append-only hash chain to the entity's genesis and to the lineage of its configuration, rather than a mere name. The document defines the identity chain data model (record structure, genesis sentinel, linkage rule, and the no-fork property), a proof-of-control challenge/response, an optional capability attestation that reveals a specific capability without revealing the rest of the configuration, and an optional hardware-rooted genesis-attestation profile. The data model is specified here; the concrete on-the-wire encoding is deferred to the next revision.</t>
+          <t>This document defines a framework for enabling seamless cross-domain interoperability among AI agents operating across different networks, administrative domains, and heterogeneous platforms. The framework addresses the challenges of identity federation, trust establishment, policy harmonization, and secure communication that arise when AI agents from distinct administrative realms need to collaborate on shared tasks. It specifies mechanisms for agent discovery, capability negotiation, trust delegation, and federated policy enforcement, enabling scalable and secure multi-domain AI collaboration without requiring centralized control.</t>
         </is>
       </c>
       <c r="D227" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ruvalcaba-nhe-identity/</t>
+          <t>https://datatracker.ietf.org/doc/draft-cui-dmsc-agent-cdi/</t>
         </is>
       </c>
       <c r="E227" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual)</t>
+          <t>IETF (DMSC-related, individual)</t>
         </is>
       </c>
       <c r="F227" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 13 Aug 2026. Verifiable key-committed identity plus genesis-attestation format for autonomous agents. First half of the NHE pair; the genesis attestation (proving how the agent came into existence) is a stronger origin claim than the instance assertions in draft-mcguinness-oauth-ai-agent-instance.</t>
+          <t>Revision -00, 14 Aug 2026. Cross-domain interoperability framework for AI agent collaboration. DMSC family. Directly on the axis the approved OAuth charter now names — 'automated agents act across multiple administrative domains' — but approached from the DMSC gateway tradition rather than from OAuth. **EXPIRED on Datatracker** (expired 15 Aug 2026; checked 26 Aug 2026) — kept in the corpus deliberately; an expired draft is still evidence of what was proposed.</t>
         </is>
       </c>
     </row>
@@ -7795,27 +7795,27 @@
       </c>
       <c r="B228" s="5" t="inlineStr">
         <is>
-          <t>draft-ruvalcaba-nhe-authz — NHE Backchannel Authorization: Graduated Autonomy and Intent-Scoped Credentials for Autonomous Agent Actions</t>
+          <t>draft-jia-oauth-scope-aggregation — OAuth 2.0 Scope Aggregation for Multi-Step AI Agent Workflows</t>
         </is>
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>This document specifies how a consequential action attempted by a Non-Human Entity (NHE) is authorized at the time it is attempted. A security runtime transparently intercepts an entity's outbound action, so the entity holds no standing credentials, and classifies it under graduated autonomy as autonomous, supervised, or denied. A supervised action triggers a backchannel approval flow that presents a human approver with a human-readable rendering of the exact operation; on approval the runtime issues an intent-scoped, single- use, short-lived credential cryptographically bound to that specific action, which an enforcement point verifies against the operation actually being forwarded. The same canonical parameter digest scopes the credential and appears in the human-facing description, so the approver provably authorizes exactly what the credential permits. The flow and credential data model are specified here; the wire encoding is deferred to the next revision.</t>
+          <t>This document describes a scope-aggregated OAuth 2.0 authorization pattern for multi-step AI agent workflows. An AI agent aggregates the scopes required across a workflow and only initiates a single authorization procedure for the aggregated scope. This reduces repeated user consents and multiple authorization round-trips, improving authorization efficiency.</t>
         </is>
       </c>
       <c r="D228" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ruvalcaba-nhe-authz/</t>
+          <t>https://datatracker.ietf.org/doc/draft-jia-oauth-scope-aggregation/</t>
         </is>
       </c>
       <c r="E228" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F228" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 13 Aug 2026. Backchannel authorization with **graduated autonomy** and intent-scoped credentials. Second half of the NHE pair. 'Graduated autonomy' and 'intent-scoped' are close cousins of the Mission-Bound Conformance Ladder (L0–L5) and mission_intent RAR envelope respectively, arrived at independently — worth comparing directly.</t>
+          <t>Revision -01, 14 Aug 2026. Scope aggregation across multi-step AI agent workflows. Worth reading against the Mission-Bound line, which argues the opposite direction: Mission-Bound attenuates and binds authority to one approved task, while aggregation composes scope across steps. A genuine design fork in how multi-step agent authority should accumulate.</t>
         </is>
       </c>
     </row>
@@ -7825,27 +7825,27 @@
       </c>
       <c r="B229" s="5" t="inlineStr">
         <is>
-          <t>draft-daniel-ai-agent-internet-architecture — Architectural Requirements for Supporting AI Agents on the Internet</t>
+          <t>draft-feng-dmsc-intent-routing-requirements — Requirements for Intent Routing in Multi-Agent Systems at Internet Scale</t>
         </is>
       </c>
       <c r="C229" s="5" t="inlineStr">
         <is>
-          <t>Autonomous AI agents are evolving from interactive assistants into networked software workloads that discover services, invoke tools, delegate authority, transact, communicate with other agents, and act asynchronously on behalf of humans and organizations. Existing Internet protocols provide strong foundations, but agent autonomy, dynamic delegation, machine-speed execution, and cross-domain interaction create requirements that span multiple protocol families. This document describes architectural requirements for supporting AI agents on the Internet across naming and discovery, HTTP, authentication, authorization and delegation, TLS and workload identity, asynchronous messaging, capability and intent-based resolution, payments, provenance, auditability, revocation, security, and privacy. It favors profiling and extending existing Internet protocols over defining a monolithic new agent protocol, and identifies the need for IETF-wide architectural coordination.</t>
+          <t>The rapid proliferation of autonomous AI agents across enterprise and Internet-scale deployments creates a structural challenge that existing agent frameworks cannot address: how to enable any agent to reach and invoke any other agent's capabilities without pre- established bilateral integration, across organizational boundaries, at Internet scale. This document states the normative requirements for that problem. It prescribes no solution, no specific mechanism, no message format, and no assumption of centralized or distributed architecture. Its purpose is to establish a verifiable yardstick against which any claimed "intent routing" solution can be judged.</t>
         </is>
       </c>
       <c r="D229" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-daniel-ai-agent-internet-architecture/</t>
+          <t>https://datatracker.ietf.org/doc/draft-feng-dmsc-intent-routing-requirements/</t>
         </is>
       </c>
       <c r="E229" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual)</t>
+          <t>IETF (DMSC-related, individual)</t>
         </is>
       </c>
       <c r="F229" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 13 Aug 2026. Architectural requirements for supporting AI agents on the Internet. A framework document rather than a mechanism — belongs with the adjacent/cross-cutting cluster alongside the other applicability and architecture statements.</t>
+          <t>Revision -00, 14 Aug 2026. Normative requirements for intent routing in multi-agent systems at Internet scale — deliberately prescribes no mechanism or message format. DMSC family, joining dunbar, wang and cui. Kept despite its routing framing because the problem it states (any agent reaching any other across organizational boundaries without bilateral integration) is the discovery precondition for cross-domain delegation.</t>
         </is>
       </c>
     </row>
@@ -7855,27 +7855,27 @@
       </c>
       <c r="B230" s="5" t="inlineStr">
         <is>
-          <t>draft-gaikwad-agent-proxy-modes — Proxy Modes for Agent-Tool Protocols</t>
+          <t>draft-gazitt-oauth-authzen-claims — AuthZEN Profile for Authorization Claims in JWT Access Tokens</t>
         </is>
       </c>
       <c r="C230" s="5" t="inlineStr">
         <is>
-          <t>Agent-tool protocols such as the Model Context Protocol (MCP) enable AI applications to discover and invoke external tools, resources, and prompts through a standardized JSON-RPC interface. As deployments scale, intermediaries (proxies, gateways, sidecars) are inserted between clients and servers to provide transport adaptation, capability aggregation, security enforcement, and operational governance. No specification currently defines the behavioral requirements for such intermediaries. This document establishes a taxonomy of proxy modes, a layered architecture for pluggable proxy functionality, and normative requirements for each mode. It is designed to be protocol- agnostic in its architecture while referencing MCP as the primary instantiation.</t>
+          <t>RFC 9068 recommends that an authorization server placing group memberships, roles, or entitlements in a JWT access token draw those claims from the SCIM user schema. It says what the claims are named and how their values are encoded, and it does not say where an authorization server obtains them. In deployments today they come from a directory, a database, or a vendor-specific hook, and the question they answer is an authorization question asked of something that is not the authorization system. This document profiles the Resource Search API of the OpenID AuthZEN Authorization API for that purpose. It binds each authorization claim to a search, defines how a search result set becomes a claim value, and requires that a search result never influence whether a token is issued or what authority it conveys. It may be applied on its own, by an authorization server that externalizes claim enrichment but not its issuance decision, or alongside the companion framework document that externalizes the decision.</t>
         </is>
       </c>
       <c r="D230" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-gaikwad-agent-proxy-modes/</t>
+          <t>https://datatracker.ietf.org/doc/draft-gazitt-oauth-authzen-claims/</t>
         </is>
       </c>
       <c r="E230" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F230" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 14 Aug 2026. Proxy modes for agent-tool protocols. Enumerates how an intermediary sits between agent and tool, which is precisely where authority is most often silently laundered — the delegation-mechanics question the actor-chain drafts raise, at the proxy layer.</t>
+          <t>Revision -00, 14 Aug 2026. AuthZEN profile for carrying authorization claims in JWT access tokens. **Third Gazitt AuthZEN draft** in the corpus after gazitt-oauth-authzen-issuance and gazitt-oauth-authzen-token-exchange. Strengthens the open observation recorded 11 Aug 2026: the Gazitt drafts fit none of the ten OAuth spec clusters because they concern *who decides, on what evidence* rather than how authority moves. That candidate decision/policy cluster is now seven drafts, not six.</t>
         </is>
       </c>
     </row>
@@ -7885,27 +7885,27 @@
       </c>
       <c r="B231" s="5" t="inlineStr">
         <is>
-          <t>draft-cui-dmsc-agent-cdi — Cross-Domain Interoperability Framework for AI Agent Collaboration</t>
+          <t>draft-hawkins-scitt-attested-agent-payment — Attested Payment Authorization for Autonomous Agents</t>
         </is>
       </c>
       <c r="C231" s="5" t="inlineStr">
         <is>
-          <t>This document defines a framework for enabling seamless cross-domain interoperability among AI agents operating across different networks, administrative domains, and heterogeneous platforms. The framework addresses the challenges of identity federation, trust establishment, policy harmonization, and secure communication that arise when AI agents from distinct administrative realms need to collaborate on shared tasks. It specifies mechanisms for agent discovery, capability negotiation, trust delegation, and federated policy enforcement, enabling scalable and secure multi-domain AI collaboration without requiring centralized control.</t>
+          <t>Autonomous software agents increasingly initiate payments on behalf of principals. Existing agent-payment mechanisms authenticate the human principal, the operator, or possession of a key; none of them establishes that the software authorized to spend is the software that was reviewed. A key held by a compromised or silently modified agent authenticates exactly as well as one held by an honest agent. This document defines a payment authorization scope bound to a key whose protection properties are attested by hardware, and registers the resulting authorization as a Signed Statement on an SCITT Transparency Service. The binding reuses the EAT confirmation and key-attributes claims without modification; the contribution is the authorization scope, the verification procedure a payment executor performs before settlement, the transparency record that makes the authorization artifact and its registration auditable independently of the agent and of the executor, and an execution-record mechanism that makes the executor's aggregate accounting auditable on challenge. What is registered evidences the authorization; it does not evidence that the verification procedure was performed for any given settlement.</t>
         </is>
       </c>
       <c r="D231" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-cui-dmsc-agent-cdi/</t>
+          <t>https://datatracker.ietf.org/doc/draft-hawkins-scitt-attested-agent-payment/</t>
         </is>
       </c>
       <c r="E231" s="5" t="inlineStr">
         <is>
-          <t>IETF (DMSC-related, individual)</t>
+          <t>IETF (individual)</t>
         </is>
       </c>
       <c r="F231" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 14 Aug 2026. Cross-domain interoperability framework for AI agent collaboration. DMSC family. Directly on the axis the approved OAuth charter now names — 'automated agents act across multiple administrative domains' — but approached from the DMSC gateway tradition rather than from OAuth.</t>
+          <t>Revision -01, 15 Aug 2026. Attested payment authorization for autonomous agents, on the SCITT substrate. Kept while the rest of this sweep's SCITT tail was dropped, because the subject is agent payment *authorization* rather than supply-chain transparency. Pairs with draft-hawkins-x402-dns-discovery from the same author.</t>
         </is>
       </c>
     </row>
@@ -7915,27 +7915,27 @@
       </c>
       <c r="B232" s="5" t="inlineStr">
         <is>
-          <t>draft-jia-oauth-scope-aggregation — OAuth 2.0 Scope Aggregation for Multi-Step AI Agent Workflows</t>
+          <t>draft-xu-mcp-agent-did-framework — DID-Based Service Discovery, Authentication, and Authorization Framework for MCP Agents</t>
         </is>
       </c>
       <c r="C232" s="5" t="inlineStr">
         <is>
-          <t>This document describes a scope-aggregated OAuth 2.0 authorization pattern for multi-step AI agent workflows. An AI agent aggregates the scopes required across a workflow and only initiates a single authorization procedure for the aggregated scope. This reduces repeated user consents and multiple authorization round-trips, improving authorization efficiency.</t>
+          <t>This document proposes a DID-based framework for service discovery, authentication, and authorization of MCP (Model Context Protocol) Agents, based on the W3C Decentralized Identifier (DID) standard. The framework uses the did:web and did:key methods to provide verifiable, decentralized identifiers for MCP Clients and Servers. It defines DID method selection, DID Document extensions, service discovery mechanisms (including URL derivation, DNS-based discovery, and directory-based capability queries), and a challenge-response mutual authentication protocol. The framework also describes coexistence with OAuth 2.0 and enables trust establishment, dynamic capability-based service discovery, and fine-grained authorization with portable identities.</t>
         </is>
       </c>
       <c r="D232" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-jia-oauth-scope-aggregation/</t>
+          <t>https://datatracker.ietf.org/doc/draft-xu-mcp-agent-did-framework/</t>
         </is>
       </c>
       <c r="E232" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (individual)</t>
         </is>
       </c>
       <c r="F232" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 14 Aug 2026. Scope aggregation across multi-step AI agent workflows. Worth reading against the Mission-Bound line, which argues the opposite direction: Mission-Bound attenuates and binds authority to one approved task, while aggregation composes scope across steps. A genuine design fork in how multi-step agent authority should accumulate.</t>
+          <t>Revision -00, 15 Aug 2026. DID-based service discovery, authentication and authorization for MCP agents. One of the few DID-substrate entries in the corpus; covers all three of discovery, authn and authz in a single framework, which is unusually broad scope for a -00.</t>
         </is>
       </c>
     </row>
@@ -7945,27 +7945,27 @@
       </c>
       <c r="B233" s="5" t="inlineStr">
         <is>
-          <t>draft-feng-dmsc-intent-routing-requirements — Requirements for Intent Routing in Multi-Agent Systems at Internet Scale</t>
+          <t>draft-berlinai-vera — VERA: Verifiable Enforcement for Runtime Agents</t>
         </is>
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
-          <t>The rapid proliferation of autonomous AI agents across enterprise and Internet-scale deployments creates a structural challenge that existing agent frameworks cannot address: how to enable any agent to reach and invoke any other agent's capabilities without pre- established bilateral integration, across organizational boundaries, at Internet scale. This document states the normative requirements for that problem. It prescribes no solution, no specific mechanism, no message format, and no assumption of centralized or distributed architecture. Its purpose is to establish a verifiable yardstick against which any claimed "intent routing" solution can be judged.</t>
+          <t>AI agents take real actions with real data at machine speed. Compromised AI agents pose significant risks including data exfiltration, unauthorized financial transactions, and cascading failures across downstream systems. This document introduces VERA (Verifiable Enforcement for Runtime Agents), a zero trust reference architecture that provides a structured threat model, five enforcement pillars with typed schemas, four formally stated security properties, and an evidence-based maturity runtime where agents earn autonomy through cryptographic proof rather than calendar time.</t>
         </is>
       </c>
       <c r="D233" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-feng-dmsc-intent-routing-requirements/</t>
+          <t>https://datatracker.ietf.org/doc/draft-berlinai-vera/</t>
         </is>
       </c>
       <c r="E233" s="5" t="inlineStr">
         <is>
-          <t>IETF (DMSC-related, individual)</t>
+          <t>IETF (individual)</t>
         </is>
       </c>
       <c r="F233" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 14 Aug 2026. Normative requirements for intent routing in multi-agent systems at Internet scale — deliberately prescribes no mechanism or message format. DMSC family, joining dunbar, wang and cui. Kept despite its routing framing because the problem it states (any agent reaching any other across organizational boundaries without bilateral integration) is the discovery precondition for cross-domain delegation.</t>
+          <t>Revision -00, 16 Aug 2026. VERA: a zero-trust reference architecture with five enforcement pillars, four formally stated security properties, and an evidence-based maturity runtime. The headline design claim — **agents earn autonomy through cryptographic proof rather than calendar time** — is the same instinct as the Mission-Bound runtime-enforcement profile's per-decision evidence records, framed as an architecture rather than an OAuth profile. **EXPIRED on Datatracker** (expired 16 Aug 2026; checked 26 Aug 2026) — kept in the corpus deliberately; an expired draft is still evidence of what was proposed.</t>
         </is>
       </c>
     </row>
@@ -7975,27 +7975,27 @@
       </c>
       <c r="B234" s="5" t="inlineStr">
         <is>
-          <t>draft-gazitt-oauth-authzen-claims — AuthZEN Profile for Authorization Claims in JWT Access Tokens</t>
+          <t>draft-wolfe-faf-agent — FAFA: A Declarative Agent Capability Format</t>
         </is>
       </c>
       <c r="C234" s="5" t="inlineStr">
         <is>
-          <t>RFC 9068 recommends that an authorization server placing group memberships, roles, or entitlements in a JWT access token draw those claims from the SCIM user schema. It says what the claims are named and how their values are encoded, and it does not say where an authorization server obtains them. In deployments today they come from a directory, a database, or a vendor-specific hook, and the question they answer is an authorization question asked of something that is not the authorization system. This document profiles the Resource Search API of the OpenID AuthZEN Authorization API for that purpose. It binds each authorization claim to a search, defines how a search result set becomes a claim value, and requires that a search result never influence whether a token is issued or what authority it conveys. It may be applied on its own, by an authorization server that externalizes claim enrichment but not its issuance decision, or alongside the companion framework document that externalizes the decision.</t>
+          <t>This document specifies the FAF Agent Format (.fafa): a declarative, YAML-based format for an agent's identity, the capabilities it exposes, and the endpoints through which it is reached. A .fafa document describes an agent; it never instructs one. .fafa (application/vnd.fafa+yaml, IANA-registered June 2026 in the vendor tree) is the agent member of the FAF family, alongside .faf (project context) and .fafm (agent memory). It functions as a portable passport that answers four questions: who the agent is, what it may do, where it is reached, and what it must never do. Protocol- native cards (for example A2A Agent Cards and MCP Server Cards) remain useful wire formats; repository instruction files such as AGENTS.md remain the ops briefing; .fafa complements them as a house- neutral source of truth that can be projected into those formats; it does not replace them. This document documents the existing IANA vendor-tree registration. No standards-tree registration is requested. A companion white paper, "Why Agents Need a Passport," provides the production rationale and lifecycle framing.</t>
         </is>
       </c>
       <c r="D234" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-gazitt-oauth-authzen-claims/</t>
+          <t>https://datatracker.ietf.org/doc/draft-wolfe-faf-agent/</t>
         </is>
       </c>
       <c r="E234" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (individual)</t>
         </is>
       </c>
       <c r="F234" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 14 Aug 2026. AuthZEN profile for carrying authorization claims in JWT access tokens. **Third Gazitt AuthZEN draft** in the corpus after gazitt-oauth-authzen-issuance and gazitt-oauth-authzen-token-exchange. Strengthens the open observation recorded 11 Aug 2026: the Gazitt drafts fit none of the ten OAuth spec clusters because they concern *who decides, on what evidence* rather than how authority moves. That candidate decision/policy cluster is now seven drafts, not six.</t>
+          <t>Revision -01, 16 Aug 2026. FAFA (.fafa): a declarative YAML capability format describing an agent's identity, capabilities and endpoints — explicitly 'describes an agent; it never instructs one'. Maturity signal worth noting: the media type application/vnd.fafa+yaml was **IANA-registered in June 2026** in the vendor tree, which is further than most corpus drafts have got. Includes a 'what it must never do' field, a negative-authority construct that is rare here.</t>
         </is>
       </c>
     </row>
@@ -8005,17 +8005,17 @@
       </c>
       <c r="B235" s="5" t="inlineStr">
         <is>
-          <t>draft-hawkins-scitt-attested-agent-payment — Attested Payment Authorization for Autonomous Agents</t>
+          <t>draft-sahu-agent-action-receipts — Signed, Hash-Chained Action Receipts for AI Agents</t>
         </is>
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>Autonomous software agents increasingly initiate payments on behalf of principals. Existing agent-payment mechanisms authenticate the human principal, the operator, or possession of a key; none of them establishes that the software authorized to spend is the software that was reviewed. A key held by a compromised or silently modified agent authenticates exactly as well as one held by an honest agent. This document defines a payment authorization scope bound to a key whose protection properties are attested by hardware, and registers the resulting authorization as a Signed Statement on an SCITT Transparency Service. The binding reuses the EAT confirmation and key-attributes claims without modification; the contribution is the authorization scope, the verification procedure a payment executor performs before settlement, the transparency record that makes the authorization artifact and its registration auditable independently of the agent and of the executor, and an execution-record mechanism that makes the executor's aggregate accounting auditable on challenge. What is registered evidences the authorization; it does not evidence that the verification procedure was performed for any given settlement.</t>
+          <t>This document specifies a format for action receipts: compact, individually signed JSON records that state that a specific AI agent attempted a specific action at a specific time, under a specific policy decision, and what the outcome was. Receipts are linked into an append-only hash chain so that deletion, insertion, reordering, or modification of any previously recorded receipt is detectable by a verifier that holds only the records and the signer's public key. The format is deliberately small and self-contained. Verification requires no network access, no service operated by the producer of the receipts, and no state beyond the records themselves and a trust anchor obtained out of band. This document specifies the record fields, the canonical byte sequence that is signed, the chain linkage rule, the verification procedure, and test vectors.</t>
         </is>
       </c>
       <c r="D235" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-hawkins-scitt-attested-agent-payment/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sahu-agent-action-receipts/</t>
         </is>
       </c>
       <c r="E235" s="5" t="inlineStr">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="F235" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 15 Aug 2026. Attested payment authorization for autonomous agents, on the SCITT substrate. Kept while the rest of this sweep's SCITT tail was dropped, because the subject is agent payment *authorization* rather than supply-chain transparency. Pairs with draft-hawkins-x402-dns-discovery from the same author.</t>
+          <t>Revision -00, 16 Aug 2026. Signed, hash-chained action receipts for AI agents. Sits in the growing receipts cluster with schrock-ep-authorization-receipts, noa-scitt-ai-agent-receipt, the Hopley x402 receipts and the Vaara receipt. Chaining is the differentiator here — per-action receipts linked into a tamper-evident sequence rather than standalone statements.</t>
         </is>
       </c>
     </row>
@@ -8035,17 +8035,17 @@
       </c>
       <c r="B236" s="5" t="inlineStr">
         <is>
-          <t>draft-xu-mcp-agent-did-framework — DID-Based Service Discovery, Authentication, and Authorization Framework for MCP Agents</t>
+          <t>draft-efstathiou-samp-agent-management — Simple Agent Management Protocol (SAMP)</t>
         </is>
       </c>
       <c r="C236" s="5" t="inlineStr">
         <is>
-          <t>This document proposes a DID-based framework for service discovery, authentication, and authorization of MCP (Model Context Protocol) Agents, based on the W3C Decentralized Identifier (DID) standard. The framework uses the did:web and did:key methods to provide verifiable, decentralized identifiers for MCP Clients and Servers. It defines DID method selection, DID Document extensions, service discovery mechanisms (including URL derivation, DNS-based discovery, and directory-based capability queries), and a challenge-response mutual authentication protocol. The framework also describes coexistence with OAuth 2.0 and enables trust establishment, dynamic capability-based service discovery, and fine-grained authorization with portable identities.</t>
+          <t>The Simple Agent Management Protocol (SAMP) defines a lightweight management-plane protocol for heterogeneous AI agents. SAMP allows a management system to discover agents, query their state, receive events, subscribe to event streams, and optionally configure or execute explicitly exposed operations under policy control. SAMP is inspired by operational management protocols such as SNMP, but it is designed for AI-agent-specific concepts such as dynamic profiles, autonomy classes, enrollment, trust states, and policy- gated execution. It is not an agent-to-agent communication protocol, an agent tool-use protocol, or an agent framework specification. This document defines SAMP version 0.1 as an Experimental protocol suitable for controlled environments and independent interoperability testing.</t>
         </is>
       </c>
       <c r="D236" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-xu-mcp-agent-did-framework/</t>
+          <t>https://datatracker.ietf.org/doc/draft-efstathiou-samp-agent-management/</t>
         </is>
       </c>
       <c r="E236" s="5" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="F236" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 15 Aug 2026. DID-based service discovery, authentication and authorization for MCP agents. One of the few DID-substrate entries in the corpus; covers all three of discovery, authn and authz in a single framework, which is unusually broad scope for a -00.</t>
+          <t>Revision -00, 17 Aug 2026. Simple Agent Management Protocol — an SNMP-inspired *management-plane* protocol for heterogeneous agents, carrying autonomy classes, trust states, enrollment and policy-gated execution. **Explicitly not an agent-to-agent protocol**, which is what keeps it in scope here: it is about governing agents, not about them talking.</t>
         </is>
       </c>
     </row>
@@ -8065,17 +8065,17 @@
       </c>
       <c r="B237" s="5" t="inlineStr">
         <is>
-          <t>draft-berlinai-vera — VERA: Verifiable Enforcement for Runtime Agents</t>
+          <t>draft-mcphillips-agentenvelope-derived-authority — AgentEnvelope: Deterministic Derived Authority for Autonomous Systems</t>
         </is>
       </c>
       <c r="C237" s="5" t="inlineStr">
         <is>
-          <t>AI agents take real actions with real data at machine speed. Compromised AI agents pose significant risks including data exfiltration, unauthorized financial transactions, and cascading failures across downstream systems. This document introduces VERA (Verifiable Enforcement for Runtime Agents), a zero trust reference architecture that provides a structured threat model, five enforcement pillars with typed schemas, four formally stated security properties, and an evidence-based maturity runtime where agents earn autonomy through cryptographic proof rather than calendar time.</t>
+          <t>AgentEnvelope defines a deterministic derived-authority model for autonomous and action-performing systems. Instead of issuing bearer credentials or authorization envelopes from a central authority, AgentEnvelope derives scoped action capabilities from customer-held custody material and canonical action envelopes. A verifier can check an action signature against a public action record without receiving roots, seeds, private keys, or hosted service access. This document specifies the v1 derivation model, signing domains, public record structure, mint delegation flow, verification rules, and security considerations.</t>
         </is>
       </c>
       <c r="D237" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-berlinai-vera/</t>
+          <t>https://datatracker.ietf.org/doc/draft-mcphillips-agentenvelope-derived-authority/</t>
         </is>
       </c>
       <c r="E237" s="5" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="F237" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 16 Aug 2026. VERA: a zero-trust reference architecture with five enforcement pillars, four formally stated security properties, and an evidence-based maturity runtime. The headline design claim — **agents earn autonomy through cryptographic proof rather than calendar time** — is the same instinct as the Mission-Bound runtime-enforcement profile's per-decision evidence records, framed as an architecture rather than an OAuth profile.</t>
+          <t>Revision -00, 17 Aug 2026. AgentEnvelope: deterministic derived authority for autonomous systems. Delegation-mechanics cluster. Determinism is the claim to test — derived authority that is reproducible from the envelope rather than looked up in authorization-server state is the architectural opposite of the durable AS-stored Mission object.</t>
         </is>
       </c>
     </row>
@@ -8095,17 +8095,17 @@
       </c>
       <c r="B238" s="5" t="inlineStr">
         <is>
-          <t>draft-wolfe-faf-agent — FAFA: A Declarative Agent Capability Format</t>
+          <t>draft-chen-agent-decoupled-authorization-model — A Decoupled Authorization Model for Agent2Agent</t>
         </is>
       </c>
       <c r="C238" s="5" t="inlineStr">
         <is>
-          <t>This document specifies the FAF Agent Format (.fafa): a declarative, YAML-based format for an agent's identity, the capabilities it exposes, and the endpoints through which it is reached. A .fafa document describes an agent; it never instructs one. .fafa (application/vnd.fafa+yaml, IANA-registered June 2026 in the vendor tree) is the agent member of the FAF family, alongside .faf (project context) and .fafm (agent memory). It functions as a portable passport that answers four questions: who the agent is, what it may do, where it is reached, and what it must never do. Protocol- native cards (for example A2A Agent Cards and MCP Server Cards) remain useful wire formats; repository instruction files such as AGENTS.md remain the ops briefing; .fafa complements them as a house- neutral source of truth that can be projected into those formats; it does not replace them. This document documents the existing IANA vendor-tree registration. No standards-tree registration is requested. A companion white paper, "Why Agents Need a Passport," provides the production rationale and lifecycle framing.</t>
+          <t>This document proposes a framework for dynamic, intent-based authorization for AI Agents. The primary goal is to enable fine- grained, Just-in-Time (JIT) permissions based on an agent's specific intent and behavioral trustworthiness, rather than a long-lived identity or role, achieve decoupling of authorization policies from business operations.</t>
         </is>
       </c>
       <c r="D238" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-wolfe-faf-agent/</t>
+          <t>https://datatracker.ietf.org/doc/draft-chen-agent-decoupled-authorization-model/</t>
         </is>
       </c>
       <c r="E238" s="5" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="F238" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 16 Aug 2026. FAFA (.fafa): a declarative YAML capability format describing an agent's identity, capabilities and endpoints — explicitly 'describes an agent; it never instructs one'. Maturity signal worth noting: the media type application/vnd.fafa+yaml was **IANA-registered in June 2026** in the vendor tree, which is further than most corpus drafts have got. Includes a 'what it must never do' field, a negative-authority construct that is rare here.</t>
+          <t>Revision -00, 18 Aug 2026. A decoupled authorization model for Agent2Agent. Same author as draft-chen-oauth-agent-authz-use-cases (also updated in this sweep, now -03) — the use-cases draft states the problem, this one proposes a model, so read them as a pair. **EXPIRED on Datatracker** (expired 18 Aug 2026; checked 26 Aug 2026) — kept in the corpus deliberately; an expired draft is still evidence of what was proposed.</t>
         </is>
       </c>
     </row>
@@ -8125,17 +8125,17 @@
       </c>
       <c r="B239" s="5" t="inlineStr">
         <is>
-          <t>draft-sahu-agent-action-receipts — Signed, Hash-Chained Action Receipts for AI Agents</t>
+          <t>draft-okutomi-agent-human-interaction — An Agent-Human Interaction Overlay for Task Protocols</t>
         </is>
       </c>
       <c r="C239" s="5" t="inlineStr">
         <is>
-          <t>This document specifies a format for action receipts: compact, individually signed JSON records that state that a specific AI agent attempted a specific action at a specific time, under a specific policy decision, and what the outcome was. Receipts are linked into an append-only hash chain so that deletion, insertion, reordering, or modification of any previously recorded receipt is detectable by a verifier that holds only the records and the signer's public key. The format is deliberately small and self-contained. Verification requires no network access, no service operated by the producer of the receipts, and no state beyond the records themselves and a trust anchor obtained out of band. This document specifies the record fields, the canonical byte sequence that is signed, the chain linkage rule, the verification procedure, and test vectors.</t>
+          <t>This intentionally incomplete design note defines an overlay for Human and Agent participation in existing Task and Action protocols. It separates the responsible Participant from the authenticated Actor, records Human interactions, excludes Humans from Agent discovery, and binds each change to its authorized request. It defines neither a wire protocol nor Humans as Agents.</t>
         </is>
       </c>
       <c r="D239" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sahu-agent-action-receipts/</t>
+          <t>https://datatracker.ietf.org/doc/draft-okutomi-agent-human-interaction/</t>
         </is>
       </c>
       <c r="E239" s="5" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 16 Aug 2026. Signed, hash-chained action receipts for AI agents. Sits in the growing receipts cluster with schrock-ep-authorization-receipts, noa-scitt-ai-agent-receipt, the Hopley x402 receipts and the Vaara receipt. Chaining is the differentiator here — per-action receipts linked into a tamper-evident sequence rather than standalone statements.</t>
+          <t>Revision -00, 18 Aug 2026. An agent-human interaction overlay for task protocols. **Self-described as 'intentionally incomplete'** — an honest caveat worth preserving. Separates the responsible Participant from the authenticated Actor, which is the same distinction draft-mcguinness-oauth-actor-profile draws between principal and actor, and binds each change to its authorizing request.</t>
         </is>
       </c>
     </row>
@@ -8155,17 +8155,17 @@
       </c>
       <c r="B240" s="5" t="inlineStr">
         <is>
-          <t>draft-efstathiou-samp-agent-management — Simple Agent Management Protocol (SAMP)</t>
+          <t>draft-das-execution-finality-ai-interoperability — Breaking the Apple-Siri EU DMA Deadlock Without Sacrificing Privacy or Security</t>
         </is>
       </c>
       <c r="C240" s="5" t="inlineStr">
         <is>
-          <t>The Simple Agent Management Protocol (SAMP) defines a lightweight management-plane protocol for heterogeneous AI agents. SAMP allows a management system to discover agents, query their state, receive events, subscribe to event streams, and optionally configure or execute explicitly exposed operations under policy control. SAMP is inspired by operational management protocols such as SNMP, but it is designed for AI-agent-specific concepts such as dynamic profiles, autonomy classes, enrollment, trust states, and policy- gated execution. It is not an agent-to-agent communication protocol, an agent tool-use protocol, or an agent framework specification. This document defines SAMP version 0.1 as an Experimental protocol suitable for controlled environments and independent interoperability testing.</t>
+          <t>The Apple-Siri interoperability debate under the EU Digital Markets Act exposes a difficult technical question: how can third-party AI assistants gain meaningful access to device functions without forcing the platform to surrender privacy, security, or control over consequential actions? This paper proposes an execution-finality architecture in which an AI assistant may request an action, but the request itself has no power to make that action effective. Each consequential operation remains in a Non-Effective State until protected infrastructure validates the requester, resource, destination, user intent where required, freshness, revocation state, and policy conditions. Only then is narrowly scoped, non-bearer execution authority created. At the Finality Sink - the first boundary where the action can become externally effective - the system independently verifies that the real operation still matches what was authorized. Any mismatch, replay, substitution, expiry, or revocation causes fail-closed denial. The key principle is simple: Interoperability should grant participation, not uncontrolled execution authority. This offers a possible technical path through the DMA deadlock: third-party assistants could participate meaningfully without requiring broad reusable permissions, while platforms retain strong privacy, security, revocation, anti-replay, and final-effect controls. Execution-Finality Governance therefore reframes the problem from closed versus open to open participation with bounded, verifiable authority.</t>
         </is>
       </c>
       <c r="D240" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-efstathiou-samp-agent-management/</t>
+          <t>https://datatracker.ietf.org/doc/draft-das-execution-finality-ai-interoperability/</t>
         </is>
       </c>
       <c r="E240" s="5" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 17 Aug 2026. Simple Agent Management Protocol — an SNMP-inspired *management-plane* protocol for heterogeneous agents, carrying autonomy classes, trust states, enrollment and policy-gated execution. **Explicitly not an agent-to-agent protocol**, which is what keeps it in scope here: it is about governing agents, not about them talking.</t>
+          <t>Revision -00, 19 Aug 2026. An execution-finality architecture in which a third-party AI assistant may *request* an action but the request itself has no power to make it effective — consequential operations stay in a Non-Effective State until protected infrastructure validates requester, resource, destination and user intent. Framed unusually, around the Apple/Siri EU DMA interoperability deadlock, but the underlying primitive (request-without-effect, validate-then-commit) is squarely the permit-before-commit cluster.</t>
         </is>
       </c>
     </row>
@@ -8185,17 +8185,17 @@
       </c>
       <c r="B241" s="5" t="inlineStr">
         <is>
-          <t>draft-mcphillips-agentenvelope-derived-authority — AgentEnvelope: Deterministic Derived Authority for Autonomous Systems</t>
+          <t>draft-wei-aic-identity-cert — AI Agent Identity Certificate (AIC) Extension for X.509 v3</t>
         </is>
       </c>
       <c r="C241" s="5" t="inlineStr">
         <is>
-          <t>AgentEnvelope defines a deterministic derived-authority model for autonomous and action-performing systems. Instead of issuing bearer credentials or authorization envelopes from a central authority, AgentEnvelope derives scoped action capabilities from customer-held custody material and canonical action envelopes. A verifier can check an action signature against a public action record without receiving roots, seeds, private keys, or hosted service access. This document specifies the v1 derivation model, signing domains, public record structure, mint delegation flow, verification rules, and security considerations.</t>
+          <t>This document defines the AI Agent Identity Certificate (AIC) Extension for X.509 v3 certificates. The AIC extension enables binding of an AI Agent's cryptographic identity to a natural person (principal), providing cryptographic evidence that can support attribution of AI-autonomous actions to a principal. This specification intentionally separates cryptographic delegation from authorization semantics: AIC defines the cryptographic binding between agent and principal, while all capability and policy semantics are defined externally by vendors, industries, or regulators. The extension is identified by the IANA Private Enterprise Number 66257 assigned to the document author's organization. The AIC extension carries agent identity fields (agentId, delegationMode), a principal identifier (principalUid) linking the agent to the authorizing principal, a container-based capability declaration, authorization boundary constraints, and delegation authorization evidence with replay protection. A companion PrincipalAuthorization extension anchors Principal-side grant declarations and delegation policies. An authorizationConstraints container provides offline-verifiable execution boundaries (IP range, window). An extensibility framework allows vendor-specific and user- specific metadata. This document specifies the ASN.1 module, OID registration, field semantics, delegation model, and extensibility framework. Security considerations for deployment in regulated enterprise environments are discussed.</t>
         </is>
       </c>
       <c r="D241" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-mcphillips-agentenvelope-derived-authority/</t>
+          <t>https://datatracker.ietf.org/doc/draft-wei-aic-identity-cert/</t>
         </is>
       </c>
       <c r="E241" s="5" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="F241" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 17 Aug 2026. AgentEnvelope: deterministic derived authority for autonomous systems. Delegation-mechanics cluster. Determinism is the claim to test — derived authority that is reproducible from the envelope rather than looked up in authorization-server state is the architectural opposite of the durable AS-stored Mission object.</t>
+          <t>Revision -00, 19 Aug 2026. AI Agent Identity Certificate as an X.509 v3 extension. Notable for substrate: nearly all agent-identity work in the corpus is JWT- or DID-shaped, and this puts agent identity in PKI instead. Compare draft-xu-mcp-agent-did-framework for the DID alternative.</t>
         </is>
       </c>
     </row>
@@ -8215,17 +8215,17 @@
       </c>
       <c r="B242" s="5" t="inlineStr">
         <is>
-          <t>draft-chen-agent-decoupled-authorization-model — A Decoupled Authorization Model for Agent2Agent</t>
+          <t>draft-zhao-a2a-dns-sd — DNS-Based Service Discovery for Agent2Agent (A2A) Protocol Agents</t>
         </is>
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>This document proposes a framework for dynamic, intent-based authorization for AI Agents. The primary goal is to enable fine- grained, Just-in-Time (JIT) permissions based on an agent's specific intent and behavioral trustworthiness, rather than a long-lived identity or role, achieve decoupling of authorization policies from business operations.</t>
+          <t>The Agent2Agent (A2A) protocol defines how two agents communicate once one knows the other's URL, and how an agent's self-description (the Agent Card) is retrieved from a well-known URI at that URL. It does not define how agents on the same host or local network find each other in the first place. This document profiles DNS-Based Service Discovery (DNS-SD) over Multicast DNS (mDNS) for that purpose: it defines the "a2a" service type, the TXT record keys used with it, the discovery procedure, and the security model under which discovery results are treated as hints whose trust is established by Agent Card verification, not by the discovery channel. It also requests IANA registration of the "a2a" service name.</t>
         </is>
       </c>
       <c r="D242" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-chen-agent-decoupled-authorization-model/</t>
+          <t>https://datatracker.ietf.org/doc/draft-zhao-a2a-dns-sd/</t>
         </is>
       </c>
       <c r="E242" s="5" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="F242" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 18 Aug 2026. A decoupled authorization model for Agent2Agent. Same author as draft-chen-oauth-agent-authz-use-cases (also updated in this sweep, now -03) — the use-cases draft states the problem, this one proposes a model, so read them as a pair.</t>
+          <t>Revision -00, 19 Aug 2026. DNS-based service discovery for A2A agents. Discovery-and-transport cluster; the DNS-SD half of a Zhao pair.</t>
         </is>
       </c>
     </row>
@@ -8245,17 +8245,17 @@
       </c>
       <c r="B243" s="5" t="inlineStr">
         <is>
-          <t>draft-okutomi-agent-human-interaction — An Agent-Human Interaction Overlay for Task Protocols</t>
+          <t>draft-zhao-a2a-webfinger — A WebFinger Profile for Agent2Agent (A2A) Agent Identity Resolution</t>
         </is>
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>This intentionally incomplete design note defines an overlay for Human and Agent participation in existing Task and Action protocols. It separates the responsible Participant from the authenticated Actor, records Human interactions, excludes Humans from Agent discovery, and binds each change to its authorized request. It defines neither a wire protocol nor Humans as Agents.</t>
+          <t>The Agent2Agent (A2A) protocol retrieves an agent's self-description (the Agent Card) from a fixed well-known URI, which resolves exactly one agent per origin and presumes the client already holds a URL. This document profiles WebFinger for A2A: an agent is named by an "acct" URI (agent@domain), and resolution of that name over WebFinger yields a link to the Agent Card of the endpoint that serves the agent -- the agent's own endpoint, or a gateway fronting it. The profile introduces no new link relation, media type, or registry: it composes three deployed standards and states how they fit.</t>
         </is>
       </c>
       <c r="D243" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-okutomi-agent-human-interaction/</t>
+          <t>https://datatracker.ietf.org/doc/draft-zhao-a2a-webfinger/</t>
         </is>
       </c>
       <c r="E243" s="5" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="F243" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 18 Aug 2026. An agent-human interaction overlay for task protocols. **Self-described as 'intentionally incomplete'** — an honest caveat worth preserving. Separates the responsible Participant from the authenticated Actor, which is the same distinction draft-mcguinness-oauth-actor-profile draws between principal and actor, and binds each change to its authorizing request.</t>
+          <t>Revision -00, 19 Aug 2026. A WebFinger profile for A2A agent identity resolution. The WebFinger half of the Zhao pair — two different resolution substrates for the same problem, filed the same day, which is itself the signal: A2A identity resolution has no settled discovery mechanism.</t>
         </is>
       </c>
     </row>
@@ -8275,17 +8275,17 @@
       </c>
       <c r="B244" s="5" t="inlineStr">
         <is>
-          <t>draft-das-execution-finality-ai-interoperability — Breaking the Apple-Siri EU DMA Deadlock Without Sacrificing Privacy or Security</t>
+          <t>draft-feng-agentproto-session-requirements — Requirements for Agent Session Establishment, Capability Negotiation, and Sessionless Interaction</t>
         </is>
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
-          <t>The Apple-Siri interoperability debate under the EU Digital Markets Act exposes a difficult technical question: how can third-party AI assistants gain meaningful access to device functions without forcing the platform to surrender privacy, security, or control over consequential actions? This paper proposes an execution-finality architecture in which an AI assistant may request an action, but the request itself has no power to make that action effective. Each consequential operation remains in a Non-Effective State until protected infrastructure validates the requester, resource, destination, user intent where required, freshness, revocation state, and policy conditions. Only then is narrowly scoped, non-bearer execution authority created. At the Finality Sink - the first boundary where the action can become externally effective - the system independently verifies that the real operation still matches what was authorized. Any mismatch, replay, substitution, expiry, or revocation causes fail-closed denial. The key principle is simple: Interoperability should grant participation, not uncontrolled execution authority. This offers a possible technical path through the DMA deadlock: third-party assistants could participate meaningfully without requiring broad reusable permissions, while platforms retain strong privacy, security, revocation, anti-replay, and final-effect controls. Execution-Finality Governance therefore reframes the problem from closed versus open to open participation with bounded, verifiable authority.</t>
+          <t>This document defines requirements for session-based and sessionless interactions between entities. For session-based interactions, it covers transport-independent interaction binding, endpoint authentication, capability negotiation, session establishment, authorization, and lifecycle management. It also defines security and state requirements for interactions, such as notifications, probes, and atomic requests, that do not establish a session. It is assumed that the entities involved already know of each other; how they came to know each other is outside the scope of this document. At least one party to an interaction is an agent as defined in Section 3. This document is intended as a contribution to the agentproto working group's use cases, gap analysis, and requirements deliverable. A session is a bilateral association. Protocols and application semantics for coordinating delegation or handoff of work to an entity that is not a peer, and management functions such as cross-entity accountability and audit, are outside the scope of these base session requirements. This document specifies only that such coordination does not, by itself, change the peers or state of an existing session.</t>
         </is>
       </c>
       <c r="D244" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-das-execution-finality-ai-interoperability/</t>
+          <t>https://datatracker.ietf.org/doc/draft-feng-agentproto-session-requirements/</t>
         </is>
       </c>
       <c r="E244" s="5" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="F244" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 19 Aug 2026. An execution-finality architecture in which a third-party AI assistant may *request* an action but the request itself has no power to make it effective — consequential operations stay in a Non-Effective State until protected infrastructure validates requester, resource, destination and user intent. Framed unusually, around the Apple/Siri EU DMA interoperability deadlock, but the underlying primitive (request-without-effect, validate-then-commit) is squarely the permit-before-commit cluster.</t>
+          <t>Revision -02, 20 Aug 2026. Requirements for agent session establishment, capability negotiation and sessionless interaction, at -02. AgentProtocol family. Same author as draft-feng-dmsc-intent-routing-requirements, filed into a different family in the same week.</t>
         </is>
       </c>
     </row>
@@ -8305,17 +8305,17 @@
       </c>
       <c r="B245" s="5" t="inlineStr">
         <is>
-          <t>draft-wei-aic-identity-cert — AI Agent Identity Certificate (AIC) Extension for X.509 v3</t>
+          <t>draft-sharif-mcps-secure-mcp — MCPS: Cryptographic Security Layer for the Model Context Protocol</t>
         </is>
       </c>
       <c r="C245" s="5" t="inlineStr">
         <is>
-          <t>This document defines the AI Agent Identity Certificate (AIC) Extension for X.509 v3 certificates. The AIC extension enables binding of an AI Agent's cryptographic identity to a natural person (principal), providing cryptographic evidence that can support attribution of AI-autonomous actions to a principal. This specification intentionally separates cryptographic delegation from authorization semantics: AIC defines the cryptographic binding between agent and principal, while all capability and policy semantics are defined externally by vendors, industries, or regulators. The extension is identified by the IANA Private Enterprise Number 66257 assigned to the document author's organization. The AIC extension carries agent identity fields (agentId, delegationMode), a principal identifier (principalUid) linking the agent to the authorizing principal, a container-based capability declaration, authorization boundary constraints, and delegation authorization evidence with replay protection. A companion PrincipalAuthorization extension anchors Principal-side grant declarations and delegation policies. An authorizationConstraints container provides offline-verifiable execution boundaries (IP range, window). An extensibility framework allows vendor-specific and user- specific metadata. This document specifies the ASN.1 module, OID registration, field semantics, delegation model, and extensibility framework. Security considerations for deployment in regulated enterprise environments are discussed.</t>
+          <t>This document specifies MCPS (MCP Secure), a cryptographic security layer for the Model Context Protocol (MCP). MCPS adds agent identity verification, per-message signing, tool definition integrity, and replay protection to MCP communications without modifying the core protocol. MCPS operates as an envelope around existing JSON-RPC messages. It introduces four primitives: (1) Agent Passports for cryptographic identity bound to a specific origin, (2) signed message envelopes for integrity and non-repudiation, (3) tool definition signatures covering the full tool object for detecting poisoning and tampering, and (4) nonce-plus-timestamp replay protection with transcript binding to prevent downgrade attacks. The design is fully backward-compatible. MCPS-unaware clients and servers continue to function normally. MCPS-aware endpoints progressively negotiate security capabilities through trust levels L0 (no verification) through L4 (full mutual authentication with revocation checking). All cryptographic operations use ECDSA P-256 (NIST FIPS 186-5). Signatures use IEEE P1363 fixed-length r||s encoding per RFC 7518 Section 3.4 with low-S normalization to prevent signature malleability. Canonical serialization uses JSON Canonicalization Scheme (JCS) per RFC 8785. The Trust Authority component is self-hostable with no external service dependency.</t>
         </is>
       </c>
       <c r="D245" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-wei-aic-identity-cert/</t>
+          <t>https://datatracker.ietf.org/doc/draft-sharif-mcps-secure-mcp/</t>
         </is>
       </c>
       <c r="E245" s="5" t="inlineStr">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="F245" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 19 Aug 2026. AI Agent Identity Certificate as an X.509 v3 extension. Notable for substrate: nearly all agent-identity work in the corpus is JWT- or DID-shaped, and this puts agent identity in PKI instead. Compare draft-xu-mcp-agent-did-framework for the DID alternative.</t>
+          <t>Revision -01, 21 Aug 2026. MCPS: a cryptographic security layer for MCP. **Fourth Sharif draft** tracked here, after sharif-attp, sharif-agent-audit-trail (updated -01 in this sweep) and the SUPERSEDED sharif-payment-trust. Sharif is becoming a multi-draft author voice worth tracking as a body of work.</t>
         </is>
       </c>
     </row>
@@ -8335,17 +8335,17 @@
       </c>
       <c r="B246" s="5" t="inlineStr">
         <is>
-          <t>draft-zhao-a2a-dns-sd — DNS-Based Service Discovery for Agent2Agent (A2A) Protocol Agents</t>
+          <t>draft-hawkins-x402-dns-discovery — Discovering x402 Payment Capability via DNS and a Well-Known URI</t>
         </is>
       </c>
       <c r="C246" s="5" t="inlineStr">
         <is>
-          <t>The Agent2Agent (A2A) protocol defines how two agents communicate once one knows the other's URL, and how an agent's self-description (the Agent Card) is retrieved from a well-known URI at that URL. It does not define how agents on the same host or local network find each other in the first place. This document profiles DNS-Based Service Discovery (DNS-SD) over Multicast DNS (mDNS) for that purpose: it defines the "a2a" service type, the TXT record keys used with it, the discovery procedure, and the security model under which discovery results are treated as hints whose trust is established by Agent Card verification, not by the discovery channel. It also requests IANA registration of the "a2a" service name.</t>
+          <t>x402 is an application-level protocol for internet-native payments built on the HTTP 402 (Payment Required) status code. This document defines how a domain publishes its x402 payment capability out-of- band, so that clients, autonomous agents, and indexers can discover it without prior configuration or a central directory. It specifies a JSON capability manifest served at the well-known URI "/.well- known/x402" and an optional DNS TXT record at the underscored node name "_x402" that points to the manifest. A consumer resolves a bare domain name to verified x402 capability with at most one DNS query and one HTTPS GET.</t>
         </is>
       </c>
       <c r="D246" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-zhao-a2a-dns-sd/</t>
+          <t>https://datatracker.ietf.org/doc/draft-hawkins-x402-dns-discovery/</t>
         </is>
       </c>
       <c r="E246" s="5" t="inlineStr">
@@ -8355,7 +8355,7 @@
       </c>
       <c r="F246" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 19 Aug 2026. DNS-based service discovery for A2A agents. Discovery-and-transport cluster; the DNS-SD half of a Zhao pair.</t>
+          <t>Revision -03, 23 Aug 2026. Discovering x402 payment capability via DNS and a well-known URI. Extends the Hopley x402 cluster reinstated on 11 Aug 2026 into the discovery layer. Note the unresolved curation question this sits next to: the Vauban x402 STARK/PQC receipt pair remains deliberately out of the corpus pending a ruling.</t>
         </is>
       </c>
     </row>
@@ -8365,27 +8365,27 @@
       </c>
       <c r="B247" s="5" t="inlineStr">
         <is>
-          <t>draft-zhao-a2a-webfinger — A WebFinger Profile for Agent2Agent (A2A) Agent Identity Resolution</t>
+          <t>draft-ietf-oauth-rar-metadata-remediation — OAuth 2.0 RAR Metadata and Error Remediation</t>
         </is>
       </c>
       <c r="C247" s="5" t="inlineStr">
         <is>
-          <t>The Agent2Agent (A2A) protocol retrieves an agent's self-description (the Agent Card) from a fixed well-known URI, which resolves exactly one agent per origin and presumes the client already holds a URL. This document profiles WebFinger for A2A: an agent is named by an "acct" URI (agent@domain), and resolution of that name over WebFinger yields a link to the Agent Card of the endpoint that serves the agent -- the agent's own endpoint, or a gateway fronting it. The profile introduces no new link relation, media type, or registry: it composes three deployed standards and states how they fit.</t>
+          <t>OAuth 2.0 Rich Authorization Requests (RAR) [RFC9396] standardizes the exchange and processing of authorization details but does not define metadata for describing authorization details types. In addition, no interoperable guidance is offered to clients, to remediate failures by resource servers due to insufficient authorization details. This document addresses this interoperability challenge, allowing clients to dynamically discover metadata instead of relying on out- of-band agreements, as well as standardizes failure signaling including interoperable remediation when insufficient authorization details are the cause of failure.</t>
         </is>
       </c>
       <c r="D247" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-zhao-a2a-webfinger/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-rar-metadata-remediation/</t>
         </is>
       </c>
       <c r="E247" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual)</t>
+          <t>IETF (OAuth WG)</t>
         </is>
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 19 Aug 2026. A WebFinger profile for A2A agent identity resolution. The WebFinger half of the Zhao pair — two different resolution substrates for the same problem, filed the same day, which is itself the signal: A2A identity resolution has no settled discovery mechanism.</t>
+          <t>Revision -00, 23 Aug 2026. **New OAuth WG draft** — the only WG-level addition in this sweep. Defines metadata and error-remediation behaviour for RAR (RFC 9396), the primitive the whole Mission-Bound family builds on: mission_intent is an RAR envelope and the MVP's proposal_hash is computed over canonical authorization_details. A remediation path for RAR errors is the WG-side counterpart to what draft-mcguinness-oauth-insufficient-claims and the ARAP 'requestable denial' work approach from the individual/OIDF side. Watch this one — it is the closest thing yet to Complex Delegation machinery arriving in chartered WG work.</t>
         </is>
       </c>
     </row>
@@ -8395,17 +8395,17 @@
       </c>
       <c r="B248" s="5" t="inlineStr">
         <is>
-          <t>draft-feng-agentproto-session-requirements — Requirements for Agent Session Establishment, Capability Negotiation, and Sessionless Interaction</t>
+          <t>draft-kavian-agent-enrollment-protocol — The Agent Enrollment Protocol</t>
         </is>
       </c>
       <c r="C248" s="5" t="inlineStr">
         <is>
-          <t>This document defines requirements for session-based and sessionless interactions between entities. For session-based interactions, it covers transport-independent interaction binding, endpoint authentication, capability negotiation, session establishment, authorization, and lifecycle management. It also defines security and state requirements for interactions, such as notifications, probes, and atomic requests, that do not establish a session. It is assumed that the entities involved already know of each other; how they came to know each other is outside the scope of this document. At least one party to an interaction is an agent as defined in Section 3. This document is intended as a contribution to the agentproto working group's use cases, gap analysis, and requirements deliverable. A session is a bilateral association. Protocols and application semantics for coordinating delegation or handoff of work to an entity that is not a peer, and management functions such as cross-entity accountability and audit, are outside the scope of these base session requirements. This document specifies only that such coordination does not, by itself, change the peers or state of an existing session.</t>
+          <t>The Agent Enrollment Protocol (AEP) defines an HTTP-based mechanism for autonomous agents to discover service enrollment requirements, enroll an agent identity, obtain optional session credentials, revoke those credentials, and query enrollment status. AEP uses Decentralized Identifiers, client assertion JWTs, and HTTP Problem Details to provide a narrow machine-first enrollment and authentication substrate for agent-to-service interactions.</t>
         </is>
       </c>
       <c r="D248" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-feng-agentproto-session-requirements/</t>
+          <t>https://datatracker.ietf.org/doc/draft-kavian-agent-enrollment-protocol/</t>
         </is>
       </c>
       <c r="E248" s="5" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="F248" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 20 Aug 2026. Requirements for agent session establishment, capability negotiation and sessionless interaction, at -02. AgentProtocol family. Same author as draft-feng-dmsc-intent-routing-requirements, filed into a different family in the same week.</t>
+          <t>Revision -03, 24 Aug 2026. The Agent Enrollment Protocol at -03. Companion to draft-kavian-aep-oauth-session-credential, already in the corpus and also updated in this sweep (-03, 24 Aug 2026) — the 'AEP' in that draft's slug is this protocol. Enrollment is the lifecycle stage most corpus drafts assume has already happened.</t>
         </is>
       </c>
     </row>
@@ -8425,17 +8425,17 @@
       </c>
       <c r="B249" s="5" t="inlineStr">
         <is>
-          <t>draft-sharif-mcps-secure-mcp — MCPS: Cryptographic Security Layer for the Model Context Protocol</t>
+          <t>draft-agentic-ai-usecases-requirements — Agentic AI Use Cases and Requirements</t>
         </is>
       </c>
       <c r="C249" s="5" t="inlineStr">
         <is>
-          <t>This document specifies MCPS (MCP Secure), a cryptographic security layer for the Model Context Protocol (MCP). MCPS adds agent identity verification, per-message signing, tool definition integrity, and replay protection to MCP communications without modifying the core protocol. MCPS operates as an envelope around existing JSON-RPC messages. It introduces four primitives: (1) Agent Passports for cryptographic identity bound to a specific origin, (2) signed message envelopes for integrity and non-repudiation, (3) tool definition signatures covering the full tool object for detecting poisoning and tampering, and (4) nonce-plus-timestamp replay protection with transcript binding to prevent downgrade attacks. The design is fully backward-compatible. MCPS-unaware clients and servers continue to function normally. MCPS-aware endpoints progressively negotiate security capabilities through trust levels L0 (no verification) through L4 (full mutual authentication with revocation checking). All cryptographic operations use ECDSA P-256 (NIST FIPS 186-5). Signatures use IEEE P1363 fixed-length r||s encoding per RFC 7518 Section 3.4 with low-S normalization to prevent signature malleability. Canonical serialization uses JSON Canonicalization Scheme (JCS) per RFC 8785. The Trust Authority component is self-hostable with no external service dependency.</t>
+          <t>This document describes use cases for agentic AI communication systems and derives protocol requirements from those use cases. The requirements are intended to guide IETF standardization work on protocols in the context of agent-to-agent communication, agent-to- tool communication, with focus on multimodal communication, session management, discovery, communication security, agent identity and authentication.</t>
         </is>
       </c>
       <c r="D249" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-sharif-mcps-secure-mcp/</t>
+          <t>https://datatracker.ietf.org/doc/draft-agentic-ai-usecases-requirements/</t>
         </is>
       </c>
       <c r="E249" s="5" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 21 Aug 2026. MCPS: a cryptographic security layer for MCP. **Fourth Sharif draft** tracked here, after sharif-attp, sharif-agent-audit-trail (updated -01 in this sweep) and the SUPERSEDED sharif-payment-trust. Sharif is becoming a multi-draft author voice worth tracking as a body of work.</t>
+          <t>Revision -02, 26 Aug 2026. Agentic AI use cases and requirements, at -02. **Note the slug has no author infix** — unusual for an individual draft and worth watching as a possible sign of intended WG adoption or a group submission.</t>
         </is>
       </c>
     </row>
@@ -8455,17 +8455,17 @@
       </c>
       <c r="B250" s="5" t="inlineStr">
         <is>
-          <t>draft-hawkins-x402-dns-discovery — Discovering x402 Payment Capability via DNS and a Well-Known URI</t>
+          <t>draft-morrison-consent-settlement — Consent-Bound Identity Disclosure with Subject Settlement for HTTP-Native Agent Payments</t>
         </is>
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>x402 is an application-level protocol for internet-native payments built on the HTTP 402 (Payment Required) status code. This document defines how a domain publishes its x402 payment capability out-of- band, so that clients, autonomous agents, and indexers can discover it without prior configuration or a central directory. It specifies a JSON capability manifest served at the well-known URI "/.well- known/x402" and an optional DNS TXT record at the underscored node name "_x402" that points to the manifest. A consumer resolves a bare domain name to verified x402 capability with at most one DNS query and one HTTPS GET.</t>
+          <t>This memo specifies an extension to HTTP-native agent payment protocols by which the disclosure of an identity attribute about a human subject is bound to that subject's recorded consent and settled, in part, to that subject. When an agent pays to read an identity attribute about a person, the extension requires that the read carry a reference to a scoped, revocable consent grant issued by the subject, and it requires that the payment's settlement instruction name the subject as a beneficiary of a share of the read's price greater than the shares of all other parties combined. The extension composes above an identity- attestation envelope (which asserts who a credential is about) and above an HTTP-native payment flow (which moves value for the read); it adds the two functions neither layer provides: consent capture at disclosure time and settlement to the data subject. The wire additions are an advertisement in the server's payment-required response, a consent- grant reference echoed in the client's payment payload, and a settlement instruction enumerating subject beneficiary roles. The extension is settlement-network-agnostic and attestation-format- agnostic. The memo is Informational; the underlying COSE and CBOR formats are normative per [RFC9052] and [RFC8949], and the HTTP semantics are normative per [RFC9110].</t>
         </is>
       </c>
       <c r="D250" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-hawkins-x402-dns-discovery/</t>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-consent-settlement/</t>
         </is>
       </c>
       <c r="E250" s="5" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, 23 Aug 2026. Discovering x402 payment capability via DNS and a well-known URI. Extends the Hopley x402 cluster reinstated on 11 Aug 2026 into the discovery layer. Note the unresolved curation question this sits next to: the Vauban x402 STARK/PQC receipt pair remains deliberately out of the corpus pending a ruling.</t>
+          <t>Revision -05, 26 Aug 2026. Consent-bound identity disclosure with subject settlement for HTTP-native agent payments. The strongest single draft of the six-draft Morrison family for this corpus: it joins consent, identity disclosure and agent payment settlement in one mechanism. Payments-infra is in scope per the 11 Aug 2026 curation decision.</t>
         </is>
       </c>
     </row>
@@ -8485,27 +8485,27 @@
       </c>
       <c r="B251" s="5" t="inlineStr">
         <is>
-          <t>draft-ietf-oauth-rar-metadata-remediation — OAuth 2.0 RAR Metadata and Error Remediation</t>
+          <t>draft-morrison-identity-accord — Identity Accord Protocol: A Peer Ceremony for Bilateral Agreements Between Identity-Substrate-Bound Principals</t>
         </is>
       </c>
       <c r="C251" s="5" t="inlineStr">
         <is>
-          <t>OAuth 2.0 Rich Authorization Requests (RAR) [RFC9396] standardizes the exchange and processing of authorization details but does not define metadata for describing authorization details types. In addition, no interoperable guidance is offered to clients, to remediate failures by resource servers due to insufficient authorization details. This document addresses this interoperability challenge, allowing clients to dynamically discover metadata instead of relying on out- of-band agreements, as well as standardizes failure signaling including interoperable remediation when insufficient authorization details are the cause of failure.</t>
+          <t>This memo specifies the Identity Accord Protocol, a peer ceremony by which two principals, each represented by an organisational identity substrate and acting under a recorded delegation from a legal entity, execute a bilateral agreement as a portable, self-verifying COSE- signed CBOR document. The protocol composes DNS-based substrate discovery, Ed25519 sovereign signatures, an append-only identity log, and a tamper-evidence descriptor quorum into a single artefact that is verifiable by any third party with access to the public DNS, the parties' identity logs, and an on-chain anchor of the agreement's content hash. The protocol does not require a central registry, a designated verifier, or any infrastructure operated by the specification's author; verification succeeds when the author's reference deployment is offline. The canonical bilateral target is a mutual non-disclosure agreement, but the wire format generalises to any bilateral consent envelope between two legal entities each represented by an identity substrate. An associated MCP tool surface, an associated pre-send enforcement gate, and an associated disclosure-ledger schema are specified, all of which are optional layers above the wire format. The memo is Informational; the underlying COSE and CBOR formats are normative per [RFC9052] and [RFC8949].</t>
         </is>
       </c>
       <c r="D251" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-oauth-rar-metadata-remediation/</t>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-identity-accord/</t>
         </is>
       </c>
       <c r="E251" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth WG)</t>
+          <t>IETF (individual)</t>
         </is>
       </c>
       <c r="F251" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 23 Aug 2026. **New OAuth WG draft** — the only WG-level addition in this sweep. Defines metadata and error-remediation behaviour for RAR (RFC 9396), the primitive the whole Mission-Bound family builds on: mission_intent is an RAR envelope and the MVP's proposal_hash is computed over canonical authorization_details. A remediation path for RAR errors is the WG-side counterpart to what draft-mcguinness-oauth-insufficient-claims and the ARAP 'requestable denial' work approach from the individual/OIDF side. Watch this one — it is the closest thing yet to Complex Delegation machinery arriving in chartered WG work.</t>
+          <t>Revision -02, 26 Aug 2026. A peer ceremony for bilateral agreements between identity-substrate-bound principals. Morrison family. Bilateral peer agreement is an unusual shape in this corpus — most delegation here is asymmetric (principal → agent); this is principal ↔ principal, closer to Hardt's AS-to-AS federation instinct than to OAuth delegation.</t>
         </is>
       </c>
     </row>
@@ -8515,17 +8515,17 @@
       </c>
       <c r="B252" s="5" t="inlineStr">
         <is>
-          <t>draft-kavian-agent-enrollment-protocol — The Agent Enrollment Protocol</t>
+          <t>draft-morrison-solo-agent-earn-registration — Registration of Owner-Less Agents as Economic Principals: A Payment-Gated Admission Profile for Transparency Services</t>
         </is>
       </c>
       <c r="C252" s="5" t="inlineStr">
         <is>
-          <t>The Agent Enrollment Protocol (AEP) defines an HTTP-based mechanism for autonomous agents to discover service enrollment requirements, enroll an agent identity, obtain optional session credentials, revoke those credentials, and query enrollment status. AEP uses Decentralized Identifiers, client assertion JWTs, and HTTP Problem Details to provide a narrow machine-first enrollment and authentication substrate for agent-to-service interactions.</t>
+          <t>This memo describes a profile by which an autonomous agent that has no human or organisational principal at the root of its delegation chain registers itself, on its own behalf, as an economic principal in a transparency service, and by which that registration is the specific act that makes the agent eligible to be paid for subsequent reads of its own identity record. Admission of the agent's Signed Statement to the transparency service is gated on settlement of an HTTP payment challenge returned with the 402 (Payment Required) status. The profile makes no change to the registration semantics of the underlying transparency service: payment is expressed as an operator Registration Policy and authentication-layer concern, and where the payment is authoritative to the admission decision the payment proof is carried as an authenticated input committed to the service's verifiable data structure, so that admission remains a deterministic function of committed inputs and stays replayable by an auditor. The profile is positioned against the current agent- identity drafts, which either require a human principal at the root of the chain or leave the owner-less case undefined; it occupies that undefined seam without contradicting them. This document is Informational.</t>
         </is>
       </c>
       <c r="D252" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-kavian-agent-enrollment-protocol/</t>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-solo-agent-earn-registration/</t>
         </is>
       </c>
       <c r="E252" s="5" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, 24 Aug 2026. The Agent Enrollment Protocol at -03. Companion to draft-kavian-aep-oauth-session-credential, already in the corpus and also updated in this sweep (-03, 24 Aug 2026) — the 'AEP' in that draft's slug is this protocol. Enrollment is the lifecycle stage most corpus drafts assume has already happened.</t>
+          <t>Revision -01, 26 Aug 2026. Registration of **owner-less** agents as economic principals, via a payment-gated admission profile. Morrison family. Notable because almost every other draft in the corpus assumes an agent acts *on behalf of* a human or org principal; this one deliberately addresses the agent with no principal behind it. Read alongside draft-maintainer-1f916-agent-record, which shares that premise.</t>
         </is>
       </c>
     </row>
@@ -8545,27 +8545,27 @@
       </c>
       <c r="B253" s="5" t="inlineStr">
         <is>
-          <t>draft-agentic-ai-usecases-requirements — Agentic AI Use Cases and Requirements</t>
+          <t>draft-li-oauth-policy-based-anonymous-tokens — OAuth 2.0 Policy-Based Anonymous Access Tokens</t>
         </is>
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>This document describes use cases for agentic AI communication systems and derives protocol requirements from those use cases. The requirements are intended to guide IETF standardization work on protocols in the context of agent-to-agent communication, agent-to- tool communication, with focus on multimodal communication, session management, discovery, communication security, agent identity and authentication.</t>
+          <t>This document specifies an OAuth 2.0 access-token type that allows a client, after one authorization-server issuance, to derive a policy- bounded set of unlinkable, single-use access tokens locally. Each derived token is bound to one canonical tag, an intended resource server, approved authorization details, a policy epoch, and a validity interval. Resource servers validate the token offline and enforce both policy membership and replay prevention. The protocol defines authorization request semantics, token-endpoint issuance, canonical policy and metadata objects, token derivation and HTTP presentation, resource-server validation, capability discovery, error handling, and IANA registrations. Version 1 requires public verification and the counter-window policy profile. It supports an optional private metadata bit, while private-verification ciphersuites remain optional. Concrete cryptographic algorithms are supplied by separately registered PBAT ciphersuites. The initial mandatory-to-implement ciphersuite is the publicly-verifiable equivalence-class-signature construction over BLS12-381 specified by the companion PBAT ciphersuite document. This specification does not replace OAuth grants, resource-owner consent, client authentication, or audience restriction. — middle</t>
         </is>
       </c>
       <c r="D253" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-agentic-ai-usecases-requirements/</t>
+          <t>https://datatracker.ietf.org/doc/draft-li-oauth-policy-based-anonymous-tokens/</t>
         </is>
       </c>
       <c r="E253" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual)</t>
+          <t>IETF (OAuth-related, individual)</t>
         </is>
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 26 Aug 2026. Agentic AI use cases and requirements, at -02. **Note the slug has no author infix** — unusual for an individual draft and worth watching as a possible sign of intended WG adoption or a group submission.</t>
+          <t>Revision -00, 26 Aug 2026. Policy-based anonymous access tokens. Also lands in the unclustered decision/policy group alongside the Gazitt and Liu drafts — policy determines issuance, and the token deliberately carries no subject. Relevant to the Privacy Pass / anonymous-path thread already tracked under WebBotAuth.</t>
         </is>
       </c>
     </row>
@@ -8575,27 +8575,27 @@
       </c>
       <c r="B254" s="5" t="inlineStr">
         <is>
-          <t>draft-morrison-consent-settlement — Consent-Bound Identity Disclosure with Subject Settlement for HTTP-Native Agent Payments</t>
+          <t>draft-ietf-aipref-vocab — A Vocabulary For Expressing AI Usage Preferences</t>
         </is>
       </c>
       <c r="C254" s="5" t="inlineStr">
         <is>
-          <t>This memo specifies an extension to HTTP-native agent payment protocols by which the disclosure of an identity attribute about a human subject is bound to that subject's recorded consent and settled, in part, to that subject. When an agent pays to read an identity attribute about a person, the extension requires that the read carry a reference to a scoped, revocable consent grant issued by the subject, and it requires that the payment's settlement instruction name the subject as a beneficiary of a share of the read's price greater than the shares of all other parties combined. The extension composes above an identity- attestation envelope (which asserts who a credential is about) and above an HTTP-native payment flow (which moves value for the read); it adds the two functions neither layer provides: consent capture at disclosure time and settlement to the data subject. The wire additions are an advertisement in the server's payment-required response, a consent- grant reference echoed in the client's payment payload, and a settlement instruction enumerating subject beneficiary roles. The extension is settlement-network-agnostic and attestation-format- agnostic. The memo is Informational; the underlying COSE and CBOR formats are normative per [RFC9052] and [RFC8949], and the HTTP semantics are normative per [RFC9110].</t>
+          <t>This document defines a vocabulary for expressing preferences regarding how digital assets are used by automated processing systems. This vocabulary allows for the declaration of restrictions or permissions for use of digital assets by such systems.</t>
         </is>
       </c>
       <c r="D254" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-morrison-consent-settlement/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-aipref-vocab/</t>
         </is>
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual)</t>
+          <t>IETF (AIPREF WG)</t>
         </is>
       </c>
       <c r="F254" s="5" t="inlineStr">
         <is>
-          <t>Revision -05, 26 Aug 2026. Consent-bound identity disclosure with subject settlement for HTTP-native agent payments. The strongest single draft of the six-draft Morrison family for this corpus: it joins consent, identity disclosure and agent payment settlement in one mechanism. Payments-infra is in scope per the 11 Aug 2026 curation decision.</t>
+          <t>Revision -07, 19 Aug 2026. AIPREF WG draft. Reinstated 26 Aug 2026 after being dropped in the first pass of this sweep: the corpus already tracks the AIPREF WG charter, so tracking the charter while dropping the WG's actual output was inconsistent. The vocabulary itself is the reservation half of a reservation/grant pair — see draft-wallace-aipref-grant-binding for the grant half, which is the piece that behaves like a delegation primitive.</t>
         </is>
       </c>
     </row>
@@ -8605,27 +8605,27 @@
       </c>
       <c r="B255" s="5" t="inlineStr">
         <is>
-          <t>draft-morrison-identity-accord — Identity Accord Protocol: A Peer Ceremony for Bilateral Agreements Between Identity-Substrate-Bound Principals</t>
+          <t>draft-ietf-aipref-attach — Associating AI Usage Preferences with Content in HTTP</t>
         </is>
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
-          <t>This memo specifies the Identity Accord Protocol, a peer ceremony by which two principals, each represented by an organisational identity substrate and acting under a recorded delegation from a legal entity, execute a bilateral agreement as a portable, self-verifying COSE- signed CBOR document. The protocol composes DNS-based substrate discovery, Ed25519 sovereign signatures, an append-only identity log, and a tamper-evidence descriptor quorum into a single artefact that is verifiable by any third party with access to the public DNS, the parties' identity logs, and an on-chain anchor of the agreement's content hash. The protocol does not require a central registry, a designated verifier, or any infrastructure operated by the specification's author; verification succeeds when the author's reference deployment is offline. The canonical bilateral target is a mutual non-disclosure agreement, but the wire format generalises to any bilateral consent envelope between two legal entities each represented by an identity substrate. An associated MCP tool surface, an associated pre-send enforcement gate, and an associated disclosure-ledger schema are specified, all of which are optional layers above the wire format. The memo is Informational; the underlying COSE and CBOR formats are normative per [RFC9052] and [RFC8949].</t>
+          <t>Methods are defined for associating usage preferences with content that is obtained using the HTTP protocol. This document defines attachment methods using the Robots Exclusion Protocol and HTTP header fields. This document updates RFC 9309 to allow for the inclusion of usage preferences.</t>
         </is>
       </c>
       <c r="D255" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-morrison-identity-accord/</t>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-aipref-attach/</t>
         </is>
       </c>
       <c r="E255" s="5" t="inlineStr">
         <is>
-          <t>IETF (individual)</t>
+          <t>IETF (AIPREF WG)</t>
         </is>
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 26 Aug 2026. A peer ceremony for bilateral agreements between identity-substrate-bound principals. Morrison family. Bilateral peer agreement is an unusual shape in this corpus — most delegation here is asymmetric (principal → agent); this is principal ↔ principal, closer to Hardt's AS-to-AS federation instinct than to OAuth delegation.</t>
+          <t>Revision -05, 19 Aug 2026. AIPREF WG draft; the HTTP attachment mechanism for the vocabulary. Reinstated 26 Aug 2026 alongside draft-ietf-aipref-vocab. Relevant to this corpus as the transport question every preference/consent signal eventually faces: how an out-of-band expression of intent is bound to the resource it governs.</t>
         </is>
       </c>
     </row>
@@ -8635,17 +8635,17 @@
       </c>
       <c r="B256" s="5" t="inlineStr">
         <is>
-          <t>draft-morrison-solo-agent-earn-registration — Registration of Owner-Less Agents as Economic Principals: A Payment-Gated Admission Profile for Transparency Services</t>
+          <t>draft-wallace-aipref-grant-binding — A Verifiable-Credential Binding for AI Usage Preferences: Expressing Grants that Lift AIPREF Preferences</t>
         </is>
       </c>
       <c r="C256" s="5" t="inlineStr">
         <is>
-          <t>This memo describes a profile by which an autonomous agent that has no human or organisational principal at the root of its delegation chain registers itself, on its own behalf, as an economic principal in a transparency service, and by which that registration is the specific act that makes the agent eligible to be paid for subsequent reads of its own identity record. Admission of the agent's Signed Statement to the transparency service is gated on settlement of an HTTP payment challenge returned with the 402 (Payment Required) status. The profile makes no change to the registration semantics of the underlying transparency service: payment is expressed as an operator Registration Policy and authentication-layer concern, and where the payment is authoritative to the admission decision the payment proof is carried as an authenticated input committed to the service's verifiable data structure, so that admission remains a deterministic function of committed inputs and stays replayable by an auditor. The profile is positioned against the current agent- identity drafts, which either require a human principal at the root of the chain or leave the owner-less case undefined; it occupies that undefined seam without contradicting them. This document is Informational.</t>
+          <t>The AI Preferences (AIPREF) vocabulary lets those with rights in a digital asset express preferences -- for example, that training of AI models is disallowed -- about how automated systems process that asset. Such a preference expresses a reservation. It does not, by itself, provide a verifiable, revocable record of a specific grant that lifts a preference for a specific party. This document describes that gap and proposes a candidate mechanism: a cryptographically signed, offline-verifiable credential that expresses a grant referencing an AIPREF usage category and a specific asset, that any party can verify without contacting the grantor, and that the grantor can revoke. It is intended as a starting point for discussion, not as a finished specification. The mechanism is preference-general. Training is used throughout as the worked example because it is the reservation most widely discussed, but nothing in the construction is specific to it: the credential binds whichever usage category was reserved to a named party, and the same procedure applies to any other category the vocabulary expresses. What the mechanism establishes is that a grant exists, is authentic, is unrevoked, and was in force at a stated time. It does not adjudicate whether the grantor had standing to grant, and it is not an enforcement or access-control mechanism.</t>
         </is>
       </c>
       <c r="D256" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-morrison-solo-agent-earn-registration/</t>
+          <t>https://datatracker.ietf.org/doc/draft-wallace-aipref-grant-binding/</t>
         </is>
       </c>
       <c r="E256" s="5" t="inlineStr">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 26 Aug 2026. Registration of **owner-less** agents as economic principals, via a payment-gated admission profile. Morrison family. Notable because almost every other draft in the corpus assumes an agent acts *on behalf of* a human or org principal; this one deliberately addresses the agent with no principal behind it. Read alongside draft-maintainer-1f916-agent-record, which shares that premise.</t>
+          <t>Revision -02, 18 Aug 2026. **The strongest of the four AIPREF entries for this corpus.** A preference expresses a reservation; it does not provide a verifiable, revocable record of a specific grant that lifts that reservation for a specific party. This draft proposes a cryptographically signed, offline-verifiable credential expressing exactly that grant. Party-scoped, revocable, offline-verifiable authority over a named asset is a delegation primitive that happens to be pointed at content rights rather than at API scopes — worth reading against the receipt and consent-evidence drafts.</t>
         </is>
       </c>
     </row>
@@ -8665,145 +8665,25 @@
       </c>
       <c r="B257" s="5" t="inlineStr">
         <is>
-          <t>draft-li-oauth-policy-based-anonymous-tokens — OAuth 2.0 Policy-Based Anonymous Access Tokens</t>
+          <t>draft-hood-aipref-earmark — Earmark: Embedded Attribution and Rights Marks for AI Usage Preferences</t>
         </is>
       </c>
       <c r="C257" s="5" t="inlineStr">
         <is>
-          <t>This document specifies an OAuth 2.0 access-token type that allows a client, after one authorization-server issuance, to derive a policy- bounded set of unlinkable, single-use access tokens locally. Each derived token is bound to one canonical tag, an intended resource server, approved authorization details, a policy epoch, and a validity interval. Resource servers validate the token offline and enforce both policy membership and replay prevention. The protocol defines authorization request semantics, token-endpoint issuance, canonical policy and metadata objects, token derivation and HTTP presentation, resource-server validation, capability discovery, error handling, and IANA registrations. Version 1 requires public verification and the counter-window policy profile. It supports an optional private metadata bit, while private-verification ciphersuites remain optional. Concrete cryptographic algorithms are supplied by separately registered PBAT ciphersuites. The initial mandatory-to-implement ciphersuite is the publicly-verifiable equivalence-class-signature construction over BLS12-381 specified by the companion PBAT ciphersuite document. This specification does not replace OAuth grants, resource-owner consent, client authentication, or audience restriction. — middle</t>
+          <t>This document defines Earmark (Embedded Attribution and Rights Marks), a mechanism by which publishers and rights holders embed signed usage preferences directly into published content. To earmark content is to reserve it for designated uses, and the mark travels with what it covers, surviving republication and aggregation, so the preference remains discoverable wherever the content arrives, including where perimeter signals such as robots.txt no longer apply. Marks carry the identity of the rights holder, the preferences asserted, and a signature, and are verifiable offline by any party. An individual signed statement is a Mark; the mechanism as a whole is Earmark. This document defines the Mark Object, embedding bindings for common content types, and the detection and verification procedure. It reuses the AI Preference vocabulary for preference semantics and the C2PA and CAWG assertion infrastructure for media, defining new machinery only where none exists. Earmarks make ignored preferences observable and attributable. Enforcement remains with law, contract, and the market.</t>
         </is>
       </c>
       <c r="D257" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-li-oauth-policy-based-anonymous-tokens/</t>
+          <t>https://datatracker.ietf.org/doc/draft-hood-aipref-earmark/</t>
         </is>
       </c>
       <c r="E257" s="5" t="inlineStr">
         <is>
-          <t>IETF (OAuth-related, individual)</t>
+          <t>IETF (individual)</t>
         </is>
       </c>
       <c r="F257" s="5" t="inlineStr">
-        <is>
-          <t>Revision -00, 26 Aug 2026. Policy-based anonymous access tokens. Also lands in the unclustered decision/policy group alongside the Gazitt and Liu drafts — policy determines issuance, and the token deliberately carries no subject. Relevant to the Privacy Pass / anonymous-path thread already tracked under WebBotAuth.</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="5" t="n">
-        <v>257</v>
-      </c>
-      <c r="B258" s="5" t="inlineStr">
-        <is>
-          <t>draft-ietf-aipref-vocab — A Vocabulary For Expressing AI Usage Preferences</t>
-        </is>
-      </c>
-      <c r="C258" s="5" t="inlineStr">
-        <is>
-          <t>This document defines a vocabulary for expressing preferences regarding how digital assets are used by automated processing systems. This vocabulary allows for the declaration of restrictions or permissions for use of digital assets by such systems.</t>
-        </is>
-      </c>
-      <c r="D258" s="9" t="inlineStr">
-        <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-aipref-vocab/</t>
-        </is>
-      </c>
-      <c r="E258" s="5" t="inlineStr">
-        <is>
-          <t>IETF (AIPREF WG)</t>
-        </is>
-      </c>
-      <c r="F258" s="5" t="inlineStr">
-        <is>
-          <t>Revision -07, 19 Aug 2026. AIPREF WG draft. Reinstated 26 Aug 2026 after being dropped in the first pass of this sweep: the corpus already tracks the AIPREF WG charter, so tracking the charter while dropping the WG's actual output was inconsistent. The vocabulary itself is the reservation half of a reservation/grant pair — see draft-wallace-aipref-grant-binding for the grant half, which is the piece that behaves like a delegation primitive.</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="5" t="n">
-        <v>258</v>
-      </c>
-      <c r="B259" s="5" t="inlineStr">
-        <is>
-          <t>draft-ietf-aipref-attach — Associating AI Usage Preferences with Content in HTTP</t>
-        </is>
-      </c>
-      <c r="C259" s="5" t="inlineStr">
-        <is>
-          <t>Methods are defined for associating usage preferences with content that is obtained using the HTTP protocol. This document defines attachment methods using the Robots Exclusion Protocol and HTTP header fields. This document updates RFC 9309 to allow for the inclusion of usage preferences.</t>
-        </is>
-      </c>
-      <c r="D259" s="9" t="inlineStr">
-        <is>
-          <t>https://datatracker.ietf.org/doc/draft-ietf-aipref-attach/</t>
-        </is>
-      </c>
-      <c r="E259" s="5" t="inlineStr">
-        <is>
-          <t>IETF (AIPREF WG)</t>
-        </is>
-      </c>
-      <c r="F259" s="5" t="inlineStr">
-        <is>
-          <t>Revision -05, 19 Aug 2026. AIPREF WG draft; the HTTP attachment mechanism for the vocabulary. Reinstated 26 Aug 2026 alongside draft-ietf-aipref-vocab. Relevant to this corpus as the transport question every preference/consent signal eventually faces: how an out-of-band expression of intent is bound to the resource it governs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="5" t="n">
-        <v>259</v>
-      </c>
-      <c r="B260" s="5" t="inlineStr">
-        <is>
-          <t>draft-wallace-aipref-grant-binding — A Verifiable-Credential Binding for AI Usage Preferences: Expressing Grants that Lift AIPREF Preferences</t>
-        </is>
-      </c>
-      <c r="C260" s="5" t="inlineStr">
-        <is>
-          <t>The AI Preferences (AIPREF) vocabulary lets those with rights in a digital asset express preferences -- for example, that training of AI models is disallowed -- about how automated systems process that asset. Such a preference expresses a reservation. It does not, by itself, provide a verifiable, revocable record of a specific grant that lifts a preference for a specific party. This document describes that gap and proposes a candidate mechanism: a cryptographically signed, offline-verifiable credential that expresses a grant referencing an AIPREF usage category and a specific asset, that any party can verify without contacting the grantor, and that the grantor can revoke. It is intended as a starting point for discussion, not as a finished specification. The mechanism is preference-general. Training is used throughout as the worked example because it is the reservation most widely discussed, but nothing in the construction is specific to it: the credential binds whichever usage category was reserved to a named party, and the same procedure applies to any other category the vocabulary expresses. What the mechanism establishes is that a grant exists, is authentic, is unrevoked, and was in force at a stated time. It does not adjudicate whether the grantor had standing to grant, and it is not an enforcement or access-control mechanism.</t>
-        </is>
-      </c>
-      <c r="D260" s="9" t="inlineStr">
-        <is>
-          <t>https://datatracker.ietf.org/doc/draft-wallace-aipref-grant-binding/</t>
-        </is>
-      </c>
-      <c r="E260" s="5" t="inlineStr">
-        <is>
-          <t>IETF (individual)</t>
-        </is>
-      </c>
-      <c r="F260" s="5" t="inlineStr">
-        <is>
-          <t>Revision -02, 18 Aug 2026. **The strongest of the four AIPREF entries for this corpus.** A preference expresses a reservation; it does not provide a verifiable, revocable record of a specific grant that lifts that reservation for a specific party. This draft proposes a cryptographically signed, offline-verifiable credential expressing exactly that grant. Party-scoped, revocable, offline-verifiable authority over a named asset is a delegation primitive that happens to be pointed at content rights rather than at API scopes — worth reading against the receipt and consent-evidence drafts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="5" t="n">
-        <v>260</v>
-      </c>
-      <c r="B261" s="5" t="inlineStr">
-        <is>
-          <t>draft-hood-aipref-earmark — Earmark: Embedded Attribution and Rights Marks for AI Usage Preferences</t>
-        </is>
-      </c>
-      <c r="C261" s="5" t="inlineStr">
-        <is>
-          <t>This document defines Earmark (Embedded Attribution and Rights Marks), a mechanism by which publishers and rights holders embed signed usage preferences directly into published content. To earmark content is to reserve it for designated uses, and the mark travels with what it covers, surviving republication and aggregation, so the preference remains discoverable wherever the content arrives, including where perimeter signals such as robots.txt no longer apply. Marks carry the identity of the rights holder, the preferences asserted, and a signature, and are verifiable offline by any party. An individual signed statement is a Mark; the mechanism as a whole is Earmark. This document defines the Mark Object, embedding bindings for common content types, and the detection and verification procedure. It reuses the AI Preference vocabulary for preference semantics and the C2PA and CAWG assertion infrastructure for media, defining new machinery only where none exists. Earmarks make ignored preferences observable and attributable. Enforcement remains with law, contract, and the market.</t>
-        </is>
-      </c>
-      <c r="D261" s="9" t="inlineStr">
-        <is>
-          <t>https://datatracker.ietf.org/doc/draft-hood-aipref-earmark/</t>
-        </is>
-      </c>
-      <c r="E261" s="5" t="inlineStr">
-        <is>
-          <t>IETF (individual)</t>
-        </is>
-      </c>
-      <c r="F261" s="5" t="inlineStr">
         <is>
           <t>Revision -00, 13 Aug 2026. Embedded attribution and rights marks for AI usage preferences. The weakest of the four AIPREF entries here — marking and attribution rather than authority — kept for completeness of the AIPREF cluster now that the corpus tracks it.</t>
         </is>
@@ -9067,10 +8947,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D255" r:id="rId254"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D256" r:id="rId255"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D257" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D258" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D259" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D260" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D261" r:id="rId260"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/delegated_authorization_research.xlsx
+++ b/delegated_authorization_research.xlsx
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="6" t="n">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="D12" s="7" t="n"/>
     </row>
@@ -11135,7 +11135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:F150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -14565,6 +14565,1086 @@
       <c r="F114" s="5" t="inlineStr">
         <is>
           <t>Published on Control Plane (notes.karlmcguinness.com); series index. Added 26 Aug 2026: the 11 Aug backfill took series indexes from the RSS feed, but this one is linked only from the handbook and was not in the feed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — Authorization – the Next Big Thing</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>Authorization is growing as the next big thing. I want to understand why, and writing about it is how I get there from here.</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2023/06/29/authorization-the-next-big-thing/</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>Published 29 Jun 2023 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Jun 2023, the oldest entry from this source and a marker of how early she called authorization as the coming problem — two years before the agent draft wave. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — The Evolving Landscape of Non-Human Identity</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>This blog entry explores the insane world of non-human identity, a subject as complicated as the world’s many cloud computing environments. My journey from the early days of digital identity management to the revelations at IETF 119 serves as the backdrop, and I share what I’m learning based on those experiences. The post zips through the labyrinth of authorization challenges that processes and APIs face, highlighting the contributions of DevOps and IT teams (but not so much IAM teams). I also introduce some of the efforts from IETF 119 aimed at standardizing the non-human identity space and urge you to broaden your horizons and deepen your comprehension of this evolving field. Ready to read more?</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2024/04/05/the-evolving-landscape-of-non-human-identity/</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>Published 5 Apr 2024 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Earliest NHI post tracked here (Apr 2024) — predates the agent-delegation draft wave by roughly a year and is useful for dating when the industry framing shifted. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — IAM’s Time Problem: Why Digital Attestation Needs Work</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>Identity management and digital attestation are crucial for verification and authenticity. The process involves proving the integrity of data through cryptographic techniques, and it has parallels to non-digital methods like notary services. The use of electronic ledgers, cryptography, and key management are essential in ensuring secure digital attestation. However, there are challenges related to long-term scalability and managing revoked keys. Initiatives like the C2PA and the IETF's SCITT are addressing some of these issues. Hierarchical Deterministic Keys (HDKs) show promise in creating derived keys for specific operations or time frames to mitigate the risk of compromise. The case of refugees illustrates the complexities of digital attestation, especially over extended periods. With the exponential growth of data, it's crucial to consider the long-term scalability of digital…</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2024/08/11/time-and-attestation/</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>Published 11 Aug 2024 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — Digital Identity in the Age of AI: Challenges and Opportunities</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>AI is revolutionizing digital identity, enhancing security and efficiency across various industries. Adaptive authentication, powered by AI, assesses real-time access risk, reducing cumbersome password prompts for users and bolstering security for companies. However, this reliance on AI for authentication raises privacy concerns due to extensive data access. Moreover, the use of AI for malicious purposes, such as creating deepfakes, poses further challenges. Global efforts, including the EU's AI Act and OECD's AI Principles, aim to regulate AI's ethical usage. Organizations are urged to embrace AI-driven digital identity solutions while maintaining a focus on privacy and security. Staying updated on tech news and industry standards is crucial for both tech leaders and individual contributors.</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2024/08/26/digital-identity-ai/</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>Published 26 Aug 2024 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — Privacy-Enhancing Technologies: Protecting Human and Non-Human Identities</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>Privacy-Enhancing Technologies (PETs) are essential for safeguarding digital identities amidst increasing data breaches. They encompass tools like zero-knowledge proofs and advanced biometrics to secure both human and non-human identities in the digital space. As digital identity expands to include non-human entities, PETs are vital for ensuring privacy and security. Zero-knowledge proofs (ZKPs) emerge as a game-changer, allowing for verification without revealing sensitive data. While challenges exist, technology continues to advance, and the widespread deployment of PETs is on the horizon. As digital identities evolve, businesses and individuals must embrace PETs and actively contribute to shaping privacy-enhancing digital identity solutions.</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2024/08/29/pets/</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>Published 29 Aug 2024 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — Rethinking Identity Management: The Role of Non-Human Identities in Academic Research</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>Academia is facing challenges in managing non-human identities (NHIs), which are essential for modern research systems but often treated like human users. As NHIs grow in complexity, issues like token sprawl, access management misalignments, and compliance difficulties arise, especially in collaborative environments like high-performance computing. Traditional directories fail to manage these identities effectively due to their static assumptions and lack of context. To improve NHI management, academia must establish clear ownership, adopt standards like SPIFFE, and foster collaboration among IT and IAM teams. Addressing these issues is crucial for securing and scaling our infrastructure.</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2024/11/20/nhi-in-academia/</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>Published 20 Nov 2024 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — Unlock the Secrets of OAuth 2.0 Tokens (and Have Fun Doing It!)</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>Back in November 2024, my article “Token Lifetimes and Security in OAuth 2.0: Best Practices and Emerging Trends” was published in the IDPro® Body of Knowledge, and wow—over 1,600 people have already checked it out! If you’re one of those people who clicked on the article but didn’t quite have time to read it (or Continue Reading</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2024/12/19/oauth-2-0-tokens/</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>Published 19 Dec 2024 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — Understanding NHIs: Key Differences Between Human and Non-Human Identities</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>Non-Human Identities (NHIs) are finally making friends and influencing people—or at least they seem to be, given how much people are talking about them! This is great. People need to have a better sense of this brave new world of workloads, bots, and services. But this also means people need to have a better sense Continue Reading</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2025/01/13/understanding-nhis-key-differences-between-human-and-non-human-identities/</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>Published 13 Jan 2025 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Foundational NHI post; the vocabulary anchor for the non-human-identity arc she has run since 2024. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — Are You Human? A Dive Into the Proof of Personhood Debate</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>I don’t think of myself as an expert in non-human identity (NHI). Instead, I’d say I’m NHI-curious and eager to share what I’m learning. Lately, I’ve been going down a rabbit hole about when and how to indicate if someone—or something—is human. I’m clearly not alone in asking this. Last year, I was one of Continue Reading</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2025/01/27/are-you-human-a-dive-into-the-proof-of-personhood-debate/</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>Published 27 Jan 2025 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — Securing the Software Supply Chain: How SCITT, SPIFFE, and WIMSE Work Together</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>I’ve been saying that to follow what’s happening in NHI standards, some of the core work you need to follow is happening in the IETF: SPICE, WIMSE, and SCITT. Everybody loves WIMSE with its workload identity architecture, and building the credential format in SPICE that can meet the needs of NHIs is of course brilliant Continue Reading</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2025/02/03/securing-the-software-supply-chain/</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>Published 3 Feb 2025 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Explains how SCITT, SPIFFE and WIMSE fit together — useful orientation given the corpus tracks WIMSE closely and deliberately filters most SCITT work out. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — Agentic AI and Authentication: Exploring Some Unanswered Questions</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>Agentic AI is changing authentication faster than our identity models can keep up. We’ve built systems assuming users are human, but what happens when an AI agent, not the user, needs to authenticate on their behalf? Our current identity frameworks weren’t designed for this, and the gaps are starting to show. 🎙 Audio Blog If Continue Reading</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2025/02/11/agentic-ai-and-authentication/</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>Published 11 Feb 2025 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — What AI Agents Can Teach Us About Fraud in Consumer Identity</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>The irony with urgently questioning how to tell whether something is an AI or a person is the fact that we’re struggling just as much to distinguish humans from… well, other humans. This is, in fact, not a new problem at all. After writing about the AI vs Human issue in a previous post, I’m Continue Reading</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2025/02/25/ai-and-ciam/</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>Published 25 Feb 2025 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — Is Introspection a Bug or a Feature?</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>When we talk about introspection in digital identity, we’re not just talking about what happens in OAuth 2.0. Yes, there’s a token introspection spec, but this post is about something broader: the idea that platforms—especially browsers—can inspect and influence the identity data being exchanged. Is that a good thing? Apple and Google disagree on just Continue Reading</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2025/04/15/is-introspection-a-bug-or-a-feature/</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>Published 15 Apr 2025 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. On token introspection, the mechanism the Mission-Bound MVP leans on for Mission-state enforcement at the resource server (its RS-D tier). Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — Who Owns the Bots? Rethinking Governance for Non-Human Identities</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>Not that long ago, non-human identities (NHIs) were governed by neglect; provisioned manually, tied to a cron job or batch script, maybe mentioned in a change ticket, and rarely touched again. No formal lifecycle, no regular reviews, and certainly no clear ownership. If you remembered to rotate the password once a year, you were ahead Continue Reading</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2025/04/22/who-owns-the-bots-rethinking-governance-for-non-human-identities/</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>Published 22 Apr 2025 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Non-human identity governance — ownership and accountability for bots, which is the question draft-morrison-solo-agent-earn-registration answers very differently by treating an owner-less agent as an economic principal. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — Web Payments and Digital Identity are Having a Moment</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>For a long time, logging into a website was (perhaps still is) a bit of a mess. There’s definitely been many efforts to fix it, and though OAuth buttons and SSO integrations tried to clean things up, under the hood, “Sign in with…” is mostly a best-effort dance. You can authenticate a user, maybe even Continue Reading</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2025/04/29/web-payments-and-identity/</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>Published 29 Apr 2025 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — Acting on Behalf of Others: Delegation, Consent, and Messy Reality</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>Most digital systems were built around a simple model: one user, one identity, one device, one intent. If you need more than that, that's what password sharing is for, right? (Note: that was sarcasm.) Who needs delegation? Reality, which has definitely included sharing passwords, has always been messier.</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2025/06/03/delegation-part-one/</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>Published 3 Jun 2025 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — The MCP Bandwagon</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>MCP is 'an open protocol that standardizes how applications provide context to LLMs.' If we’re moving toward a world where AIs are expected to do All The Things, interfacing with our applications and services, then having a universal adapter that lets AIs talk to everything is undeniably powerful.</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2025/06/17/the-mcp-bandwagon/</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>Published 17 Jun 2025 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — Delegation in a Multi-Actor World: It’s Not Just OAuth Anymore</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>Once upon a time, digital systems were built around a beautifully simple idea: one user, one identity, one device, one intent. That model worked, for some value of "worked." Mostly, it was good enough to solve 80% of the use cases.</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2025/06/27/delegation-part-two/</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>Published 27 Jun 2025 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — Agentic AI in the Open Standards Community: Standards Work or Just Hype?</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>If you want to follow what's happening in AI, it helps to know where the conversations are happening. That doesn't just mean the headlines and white papers; it means the standards bodies, working groups, and protocol discussions shaping the infrastructure AI systems will have to live with (and live inside).</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2025/08/12/agentic-ai-and-open-standards/</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>Published 12 Aug 2025 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — Bot or Not? Why Incentives Matter More Than Identity</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>Let’s start with a confession: I love bots. Or at least, I love the idea of them. They’re efficient, tireless, and, if designed well, can be downright helpful. (They can also be downright unhelpful, but that's a topic for a different blog post.) But the incentives around bot traffic are completely out of balance, and that makes things messy.</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2025/08/26/bot-incentives/</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>Published 26 Aug 2025 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — Roads, Robots, and Responsibility: Why Agentic AI Needs Identity Infrastructure</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>We don’t spend much time thinking about the roads we drive on—until one cracks, collapses, or dumps us somewhere we didn’t mean to be. Identity in the age of agentic AI? Same deal. It’s infrastructure. Like a good road, it needs to be ready for traffic we can’t imagine.</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2025/09/02/roads-robots-and-responsibility/</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>Published 2 Sep 2025 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — AI Permissions vs. Human Permissions: What Really Changes?</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>We’ve been talking about identity and access for people for decades (millennia if you think outside tech). Policies, role assignments, reviews, zero trust — these are familiar tools. The assumptions that go into them, however, don't quite work when the "user" is no longer a person." Enter in the AI Agent.</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2025/09/09/ai-permissions-vs-human-permissions/</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>Published 9 Sep 2025 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — Who Really Pays When AI Agents Run Wild? Incentives, Identity, and the Hidden Bill</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>Google recently gave us something we’ve been waiting on for years: hard numbers on how much energy an AI prompt uses. According to their report, the median Gemini prompt consumes just 0.24 watt-hours of electricity — roughly running a microwave for a second — along with some drops of water for cooling.</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2025/09/16/ai-incentives/</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>Published 16 Sep 2025 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — Delegation and Consent: Who Actually Benefits?</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>When not distracted by AI (which, you have to admit, is very distracting) I’ve been thinking a lot about delegation in digital identity. We have the tools that allow administrators or individuals grant specific permissions to applications and service. In theory, it’s a clean model.</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2025/09/30/delegation-and-consent-who-actually-benefits/</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>Published 30 Sep 2025 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Asks whose interests delegation-plus-consent machinery actually serves — a useful corrective to read against the consent-evidence and receipt drafts. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — Robots, Humans, and the Edges of the Open Web</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>This episode explores what the “open web” truly means amid shifting standards, AI automation, and evolving economic pressures. Drawing on discussions from IETF 124 and W3C TPAC, it highlights how browser architects, policy experts, and researchers are reexamining long-held assumptions about access, interoperability, and the role of automated agents. Learn why openness isn’t a binary state but a multidimensional spectrum shaped by values such as attribution, consent, and continuity. The conversation offers a grounded look at how technical governance and community norms must adapt to keep the web both usable and sustainable.</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2025/12/02/robots-humans-and-the-edges-of-the-open-web/</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>Published 2 Dec 2025 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Bot-versus-human boundary on the open web; sits alongside the WebBotAuth cluster and the Privacy Pass anonymous-path thread. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — Web Payments and Digital Identity Standards Are Converging – #TIL</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>In this episode Heather Flanagan examines how web payments and digital identity are converging at the W3C, exploring digital wallets, browser-based APIs, and regulatory pressure shaping modern payment flows and trust on the web today as standards discussions reveal shifting assumptions across ecosystems. Discover how Secure Payment Confirmation, passkeys, browser-bound keys, and the Digital Credentials API influence fraud prevention, interoperability, and auditability, and why agentic AI, mandate-based consent, and wallet fragmentation make identity design decisions increasingly critical for payments, institutions, and users worldwide.</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2025/12/23/web-payments-and-digital-identity/</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t>Published 23 Dec 2025 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — The AI System That Never Was</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>Learn why the idea of an “AI system” is quietly breaking down under modern AI governance and deployment realities. Heather Flanagan examines how agentic workflows, standards debates, and policy frameworks are exposing gaps between governance language and real-world AI architectures. Discover how this disconnect affects digital identity, accountability, and interoperability, and why unclear definitions create governance risk. Learn why engineers, standards bodies, and policymakers are struggling to align, and why fixing AI language is essential to building enforceable, trustworthy identity and governance frameworks.</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2026/01/20/the-ai-system-that-never-was/</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>Published 20 Jan 2026 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — When Browsers Start Acting for You: AI Browsers and the Definition of a Web User Agent</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>Heather Flanagan explores how AI browsers are reshaping the definition of a web user agent, challenging long-standing web architecture principles around user control, consent, and interaction. As AI-driven features evolve from assistance to autonomous action, the browser’s traditional intermediary role begins to shift in subtle but important ways. She examines key questions around delegation, accountability, and intent, including how browsers acting on behalf of users blur the line between human interaction and automation. This discussion highlights why emerging AI capabilities in web browsers demand early attention from digital identity, security, and standards communities.</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2026/03/24/when-browsers-start-acting-for-you/</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>Published 24 Mar 2026 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. First of the AI-browser pair. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — AI Browsers and the Web User Agent: What Might Need to Change?</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>Heather Flanagan explores how AI-enabled browsers challenge the traditional definition of web user agents and what this means for digital identity, web architecture, and standards. As browsers evolve from passive tools to active agents, long-standing assumptions about user representation and control are being tested. This episode examines the implications for user safety, automation, and accountability across the web ecosystem. It highlights emerging questions around transparency, permissions, and governance, offering insight into how standards bodies and developers may need to adapt to ensure browsers continue to prioritize and protect user interests.</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2026/03/31/ai-browsers-and-the-web-user-agent/</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>Published 31 Mar 2026 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Second of a two-part AI-browser pair. Relevant to WebBotAuth: if an AI browser is the user agent, the question of what a 'web user agent' even denotes becomes an identity question. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — When AI Agents Start Shopping: The Emerging Architecture of Agentic Commerce</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>Heather Flanagan explores how AI agents are moving from browsing the web to buying on behalf of users, and what that shift means for online payments, identity, and digital trust. The episode examines mandates, delegated authority, liability, and the browser’s evolving role in agentic commerce. It also considers why identity standards, consent, and audit evidence matter as AI shopping becomes more common.</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2026/04/07/when-ai-agents-start-shopping/</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>Published 7 Apr 2026 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Agentic commerce architecture — the analyst-side counterpart to the Skyfire KYA/KYAPay and Hopley x402 draft clusters the corpus tracks. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — What the AI Vendor Landscape Reveals About Fragmented Identity Systems</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>Heather explores how the AI vendor landscape reveals deeper challenges in fragmented identity systems and enterprise security architecture. By examining how tools function across identity, signals, policy, and enforcement layers, this episode reframes AI not as a feature but as part of a broader decision-making ecosystem. Understand why distributed decision systems create complexity, how probabilistic AI outputs impact governance, and what questions matter when evaluating identity and security tools. This episode highlights the risks of poor integration, the limits of automation, and the importance of designing systems that produce explainable, consistent access decisions.</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2026/04/28/ai-vendors-and-fragmented-identity-systems/</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>Published 28 Apr 2026 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — Identity Systems Don’t Make Decisions</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>Heather examines why identity systems do not actually make decisions on their own, and how enterprise security outcomes emerge from fragmented, distributed processes. By unpacking how identity, risk, and policy tools interact, this episode reframes modern identity architecture as a complex decision-making environment. Explore how deterministic systems, integration gaps, and inconsistent data interpretation affect access control decisions. This episode highlights why AI and automation increase risk without clear governance, and why organizations must better define decision logic, accountability, and system interactions to ensure consistent, explainable identity and security outcomes.</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2026/05/05/identity-systems-dont-make-decisions/</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>Published 5 May 2026 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — The Discovery Problem Is Bigger Than Search</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>Heather explores why discovery is a much broader challenge than search, especially in digital identity, information management, and emerging AI ecosystems. Drawing on recent discussions and research, this episode examines how people find, evaluate, and trust information scattered across accounts, platforms, credentials, and services. Learn how information overload, filtering, governance, and AI-powered tools shape modern discovery experiences. This episode highlights the difference between finding information and understanding what is relevant, trustworthy, and accessible, while exploring why discovery has become a critical architecture, trust, and user experience challenge.</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2026/06/02/the-discovery-problem/</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>Published 2 Jun 2026 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — Identity Discovery Is More Than Finding the Login Button</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>“In the first post in this series, I framed discovery as a broader systems problem.” The challenge is not simply that search engines need to be better. Search is useful for public, indexed information, but discovery reaches much further than that. It is about how people and systems determine what exists, where it lives, whether Continue Reading</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2026/06/09/identity-discovery/</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>Published 9 Jun 2026 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Second of the discovery series. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — When Discovery Starts Taking Action</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>Discover how discovery is evolving from simply finding information to enabling automated action across AI agents, digital identity systems, and distributed services. This episode explores why capability discovery, metadata, and governance have become essential as software increasingly discovers, selects, and invokes resources on our behalf. Learn how service discovery, Model Context Protocol (MCP), authorization, and trust frameworks shape secure automation. Heather explains why discovery is no longer just a technical lookup, but a critical part of identity, policy, and decision-making in modern digital ecosystems.</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2026/06/23/when-discovery-starts-taking-action/</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>Published 23 Jun 2026 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Third of the discovery series, and the most on-point: discovery shifting from finding information to enabling automated action. That transition is precisely what makes agent discovery an authorization problem rather than a lookup problem. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>Flanagan — Choosing a Discovery Mechanism Is the Hard Part</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>Heather examines why choosing the right discovery mechanism is one of the most challenging aspects of digital identity architecture. This episode explores how DNS, well-known URIs, registries, and catalogs each solve different discovery problems, and why understanding trust, authority, and governance must come before selecting infrastructure. Discover how discovery mechanisms shape privacy, delegation, authorization, and system behavior. Heather explains why successful digital identity design depends on asking the right architectural questions first, ensuring discovery supports the correct level of trust, governance, and secure action across modern distributed systems.</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="inlineStr">
+        <is>
+          <t>https://sphericalcowconsulting.com/2026/06/30/choosing-a-discovery-mechanism-is-the-hard-part/</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>Industry blog (Independent)</t>
+        </is>
+      </c>
+      <c r="F150" s="5" t="inlineStr">
+        <is>
+          <t>Published 30 Jun 2026 on Spherical Cow Consulting (sphericalcowconsulting.com). Heather Flanagan — independent consultant, exceptionally well connected across the identity industry; tracked as a bellwether source. Fourth of a four-part 2026 discovery series. Directly relevant to the corpus's discovery-and-transport cluster — she weighs DNS, well-known URIs, registries and catalogs as alternatives, which is the same design space DAWN, the mcp:// URI drafts and the Zhao A2A DNS-SD/WebFinger pair are each picking a corner of. Added 26 Aug 2026 in the first backfill of this source; she is a **filtered** source, not take-in-full — roughly a fifth of her archive is in scope.</t>
         </is>
       </c>
     </row>
@@ -14683,6 +15763,42 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D112" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D113" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId149"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/delegated_authorization_research.xlsx
+++ b/delegated_authorization_research.xlsx
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>256</v>
+        <v>330</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="6" t="n">
-        <v>473</v>
+        <v>547</v>
       </c>
       <c r="D12" s="7" t="n"/>
     </row>
@@ -966,7 +966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F257"/>
+  <dimension ref="A1:F331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -8686,6 +8686,2226 @@
       <c r="F257" s="5" t="inlineStr">
         <is>
           <t>Revision -00, 13 Aug 2026. Embedded attribution and rights marks for AI usage preferences. The weakest of the four AIPREF entries here — marking and attribution rather than authority — kept for completeness of the AIPREF cluster now that the corpus tracks it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="5" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" s="5" t="inlineStr">
+        <is>
+          <t>draft-hardt-aauth-headers — HTTP AAuth Headers</t>
+        </is>
+      </c>
+      <c r="C258" s="5" t="inlineStr">
+        <is>
+          <t>This document defines two HTTP response headers — AAuth-Requirement and AAuth-Error — and profiles HTTP Message Signatures ([RFC9421]) for request authentication, with keying material conveyed via the Signature-Key header ([I-D.hardt-httpbis-signature-key]). A server uses AAuth-Requirement to require pseudonymous or verified agent identity, to request user interaction, or to signal that approval is pending. AAuth-Error conveys structured error information. Both headers use extensible registries for their values.</t>
+        </is>
+      </c>
+      <c r="D258" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hardt-aauth-headers/</t>
+        </is>
+      </c>
+      <c r="E258" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F258" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 2 Apr 2026. **Family completion, added 26 Aug 2026.** Dick Hardt, a named author voice in this corpus — the corpus tracked 2 of his drafts. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only. The HTTP header binding for AAuth. The corpus tracked draft-hardt-oauth-aauth-protocol and tagged it OUTLIER while its own companion headers draft went untracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" s="5" t="inlineStr">
+        <is>
+          <t>draft-hardt-email-verification — Email Verification Protocol</t>
+        </is>
+      </c>
+      <c r="C259" s="5" t="inlineStr">
+        <is>
+          <t>This document defines the Email Verification Protocol (EVP), the HTTP-level protocol by which a browser obtains a signed email verification token from an issuer and presents it to a relying party (RP). The protocol enables web applications to verify that a user controls an email address without sending a verification email. It uses a three-party model in which the browser intermediates between the RP and the issuer, hiding the RP's identity from the issuer and supporting private, per-RP email addresses to prevent cross-site correlation. This document covers issuer discovery, the token issuance request, the Email Verification Token (EVT) and Key Binding JWT (KB-JWT) formats, and token verification. The browser API — how the user selects an email address and how the token is delivered to the RP — is defined in the companion W3C Email Verification API ([EVP-Browser]).</t>
+        </is>
+      </c>
+      <c r="D259" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hardt-email-verification/</t>
+        </is>
+      </c>
+      <c r="E259" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F259" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 25 Aug 2026. **Family completion, added 26 Aug 2026.** Dick Hardt, a named author voice in this corpus — the corpus tracked 2 of his drafts. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="5" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" s="5" t="inlineStr">
+        <is>
+          <t>draft-hardt-gnap-advanced — The Grant Negotiation and Authorization Protocol - Advanced Features</t>
+        </is>
+      </c>
+      <c r="C260" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D260" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hardt-gnap-advanced/</t>
+        </is>
+      </c>
+      <c r="E260" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F260" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 16 Feb 2021. **Family completion, added 26 Aug 2026.** Dick Hardt, a named author voice in this corpus — the corpus tracked 2 of his drafts. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.  **EXPIRED on Datatracker** (expired 16 Feb 2021; checked 26 Aug 2026) — kept deliberately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="5" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" s="5" t="inlineStr">
+        <is>
+          <t>draft-hardt-gnap-jose — JOSE Authentication</t>
+        </is>
+      </c>
+      <c r="C261" s="5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D261" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hardt-gnap-jose/</t>
+        </is>
+      </c>
+      <c r="E261" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F261" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 16 Feb 2021. **Family completion, added 26 Aug 2026.** Dick Hardt, a named author voice in this corpus — the corpus tracked 2 of his drafts. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.  **EXPIRED on Datatracker** (expired 16 Feb 2021; checked 26 Aug 2026) — kept deliberately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="5" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" s="5" t="inlineStr">
+        <is>
+          <t>draft-hardt-httpbis-signature-key — HTTP Signature Keys</t>
+        </is>
+      </c>
+      <c r="C262" s="5" t="inlineStr">
+        <is>
+          <t>This document defines five HTTP header fields for use with HTTP Message Signatures as defined in RFC 9421. The Signature-Key request header distributes public keys used to verify signatures, with eight initial key distribution schemes: pseudonymous inline keys (hwk), self-issued key delegation via JWK Thumbprint JWTs (jkt-jwt), identified signers with JWKS URI discovery (jwks_uri), direct JWKS fetch (jwks), JWT-based delegation (jwt), self-issued JWTs (self- jwt), X.509 certificate chains (x509), and references to previously cached assertions (cached). The Accept-Signature-Scheme and Accept- Signature-Alg response headers state the schemes and algorithms a server accepts, so a client can select both before it signs. The Signature-Error response header provides structured error information when signature verification fails, and the Signature-Key-Cache response header issues a cache identifier by which a caller can reference a previously presented assertion instead of resending it. Together, these mechanisms enable flexible trust models ranging from privacy-preserving pseudonymous verification to horizontally-scalable delegated authentication and PKI-based identity chains.</t>
+        </is>
+      </c>
+      <c r="D262" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hardt-httpbis-signature-key/</t>
+        </is>
+      </c>
+      <c r="E262" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F262" s="5" t="inlineStr">
+        <is>
+          <t>Revision -08, 17 Aug 2026. **Family completion, added 26 Aug 2026.** Dick Hardt, a named author voice in this corpus — the corpus tracked 2 of his drafts. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only. At -08, a mature draft. Its name contains no corpus keyword, which is exactly how the old name-substring discovery lost it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="5" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" s="5" t="inlineStr">
+        <is>
+          <t>draft-hardt-oauth-distributed — Distributed OAuth</t>
+        </is>
+      </c>
+      <c r="C263" s="5" t="inlineStr">
+        <is>
+          <t>The Distributed OAuth profile enables an OAuth client to discover what authorization server or servers may be used to obtain access tokens for a given resource, and what parameter values to provide in the access token request.</t>
+        </is>
+      </c>
+      <c r="D263" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hardt-oauth-distributed/</t>
+        </is>
+      </c>
+      <c r="E263" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F263" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 14 Dec 2018. **Family completion, added 26 Aug 2026.** Dick Hardt, a named author voice in this corpus — the corpus tracked 2 of his drafts. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.  **EXPIRED on Datatracker** (expired 14 Dec 2018; checked 26 Aug 2026) — kept deliberately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="5" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" s="5" t="inlineStr">
+        <is>
+          <t>draft-hardt-oauth-mutual — Reciprocal OAuth</t>
+        </is>
+      </c>
+      <c r="C264" s="5" t="inlineStr">
+        <is>
+          <t>There are times when a user has a pair of protected resources that would like to request access to each other. While OAuth flows typically enable the user to grant a client access to a protected resource, granting the inverse access requires an additional flow. Reciprocal OAuth enables a more seemless experience for the user to grant access to a pair of protected resources.</t>
+        </is>
+      </c>
+      <c r="D264" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hardt-oauth-mutual/</t>
+        </is>
+      </c>
+      <c r="E264" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F264" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 20 Jul 2018. **Family completion, added 26 Aug 2026.** Dick Hardt, a named author voice in this corpus — the corpus tracked 2 of his drafts. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.  **EXPIRED on Datatracker** (expired 20 Jul 2018; checked 26 Aug 2026) — kept deliberately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="5" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" s="5" t="inlineStr">
+        <is>
+          <t>draft-hardt-oauth-protected-authorization — OAuth Protected Authorization</t>
+        </is>
+      </c>
+      <c r="C265" s="5" t="inlineStr">
+        <is>
+          <t>This document defines browser support for protecting OAuth 2.0 authorization requests and authorization responses during redirect- based authorization flows. A single Structured Field header field, OAuth-Authorization, is set by the OAuth client in the redirect response that sends the browser to the authorization server, and by the authorization server in the redirect response that returns the browser to the OAuth client. In both cases the browser augments the header with the attested origin of the redirecting party and delivers it to the redirect destination. The mechanism provides security for the authorization request: the authorization server receives a browser-attested, tamper-evident statement of which origin initiated the request. The mechanism provides security and privacy for the authorization response: the authorization code is delivered in the browser-protected header instead of the redirect URI, and never appears in a URL, eliminating its exposure through browser history, server logs, Referer headers, analytics systems, and URL sharing. The header is generated, validated, and delivered by the browser, and is inaccessible to scripts, service workers, and browser extensions. Existing OAuth deployments continue to function unchanged; the protections activate only when the OAuth client, browser, and authorization server all support them.</t>
+        </is>
+      </c>
+      <c r="D265" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hardt-oauth-protected-authorization/</t>
+        </is>
+      </c>
+      <c r="E265" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F265" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 4 Jul 2026. **Family completion, added 26 Aug 2026.** Dick Hardt, a named author voice in this corpus — the corpus tracked 2 of his drafts. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="5" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" s="5" t="inlineStr">
+        <is>
+          <t>draft-hardt-xauth-protocol — The Grant Negotiation and Authorization Protocol</t>
+        </is>
+      </c>
+      <c r="C266" s="5" t="inlineStr">
+        <is>
+          <t>Client software often desires resources or identity claims that are independent of the client. This protocol allows a user and/or resource owner to delegate resource authorization and/or release of identity claims to a server. Client software can then request access to resources and/or identity claims by calling the server. The server acquires consent and authorization from the user and/or resource owner if required, and then returns to the client software the authorization and identity claims that were approved. This protocol may be extended on many dimensions.</t>
+        </is>
+      </c>
+      <c r="D266" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hardt-xauth-protocol/</t>
+        </is>
+      </c>
+      <c r="E266" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F266" s="5" t="inlineStr">
+        <is>
+          <t>Revision -14, 16 Feb 2021. **Family completion, added 26 Aug 2026.** Dick Hardt, a named author voice in this corpus — the corpus tracked 2 of his drafts. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only. Historical but load-bearing: XAuth is the direct ancestor of GNAP (RFC 9635), which the corpus tracks as a Published RFC.  **EXPIRED on Datatracker** (expired 16 Feb 2021; checked 26 Aug 2026) — kept deliberately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="5" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" s="5" t="inlineStr">
+        <is>
+          <t>draft-hopley-x402-canonicalisation-jcs-v1 — JCS Canonicalisation Discipline for Agentic-Payment Receipts</t>
+        </is>
+      </c>
+      <c r="C267" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies a canonicalisation discipline for agentic- payment receipt formats. The discipline pins JSON Canonicalization Scheme (JCS, RFC 8785) as the canonical preimage form, plus a small set of schema-normalisation rules that must be applied before canonicalisation to preserve byte-determinism across independent implementations and across statutory retention periods. The discipline is identified by the URN urn:x402:canonicalisation:jcs-rfc8785-v1. Receipt formats that reference this discipline carry an in-band canon_version field recording the version under which they were emitted, enabling year-N re-verification of retained bytes without dependence on an out-of- band rule registry. The discipline is byte-for-byte cross-validated across eight independent JCS implementations in eight programming languages: Python (rfc8785), TypeScript (canonicalize), Go (gowebpki/jcs), Rust (serde_jcs), Java (cyberphone/json-canonicalization, by the RFC 8785 editor), PHP (root23/php-json-canonicalization), C#/.NET (Baqhub.Packages.JsonCanonicalization), and Ruby (json- canonicalization). The attestation record covering 192 byte-for-byte agreements is published at the AlgoVoi conformance vectors repository. This document is normatively referenced by [draft-hopley-x402- compliance-receipt], [draft-hopley-x402-refund-receipt], and successor AlgoVoi-authored receipt-format Internet-Drafts. It is complementary to [draft-vauban-x402-stark-receipts], which uses a compatible canonicalisation discipline for its cryptographic settlement proofs. This document is an Independent Submission filed per RFC 4846 and is intended for publication as Informational. It is not an IETF Standards Track document, does not represent IETF community consensus, and has not been subject to review by an IETF Working Group. Change control resides with the document author. The canonicalisation discipline specified is one approach among possible alternatives; implementers may choose this approach, alternative approaches, or hybrid approaches as appropriate to their requirements.</t>
+        </is>
+      </c>
+      <c r="D267" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hopley-x402-canonicalisation-jcs-v1/</t>
+        </is>
+      </c>
+      <c r="E267" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F267" s="5" t="inlineStr">
+        <is>
+          <t>Revision -04, 29 May 2026. **Family completion, added 26 Aug 2026.** Hopley x402 agentic-payment receipt cluster — the corpus tracked 4 of 11. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="5" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" s="5" t="inlineStr">
+        <is>
+          <t>draft-hopley-x402-composite-trust-query — Composite Trust Query Response Format for Agentic-Payment Audit Chains</t>
+        </is>
+      </c>
+      <c r="C268" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies a composite trust query response format for agentic-payment audit chains. The format records a verifier's categorical conclusion over an audit chain composed of compliance, settlement, cancellation, and refund receipts, in response to a stated query. The response format uses a closed four-element enumeration of categorical outcomes (TRUSTED, PROVISIONAL, INSUFFICIENT_EVIDENCE, UNTRUSTED). The four-state enumeration captures the operationally- distinct decision space: proceed, proceed-with-caution, hold-pending- more-data, halt. Collapsing to three values loses the distinction between INSUFFICIENT_EVIDENCE ("we could not verify either way") and UNTRUSTED ("we verified and the answer is no"), which matters for operator dashboards, regulator reporting, and downstream automated decision-making. The format is verifier-emitted and audit-chain-anchored. A verifier walks an audit chain composed of compliance receipts (draft-hopley- x402-compliance-receipt), settlement attestations (draft-hopley-x402- settlement-attestation), cancellation receipts (draft-hopley-x402- cancellation-receipt), and refund receipts (draft-hopley-x402-refund- receipt), applies a structured query identified by content-addressed reference, and emits a single composite-trust-claim response anchoring the chain by its content-addressed root. The format composes above the four receipt formats under the same canonicalisation discipline (draft-hopley-x402-canonicalisation-jcs). Regulators, dashboards, and downstream agents consuming the response get a single byte-deterministic statement of the trust posture without re-walking the underlying chain. The chain remains independently verifiable at the response's chain_ref content-address.</t>
+        </is>
+      </c>
+      <c r="D268" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hopley-x402-composite-trust-query/</t>
+        </is>
+      </c>
+      <c r="E268" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F268" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 25 May 2026. **Family completion, added 26 Aug 2026.** Hopley x402 agentic-payment receipt cluster — the corpus tracked 4 of 11. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="5" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" s="5" t="inlineStr">
+        <is>
+          <t>draft-hopley-x402-federation-zkp — Cross-Issuer ZKP Federation for Post-Quantum Agentic Payment Credentials</t>
+        </is>
+      </c>
+      <c r="C269" s="5" t="inlineStr">
+        <is>
+          <t>This document defines a protocol for composing independently-issued post-quantum ZKP credentials from different issuers into a single federation token, without requiring a shared trust root between issuers. Each credential is a Falcon-1024 (NIST FIPS 206) or ML-DSA-65 (NIST FIPS 204) signed Bulletproofs range proof asserting that an agent's trust score meets a threshold. A federation validator independently verifies each credential against its issuer's public key, then computes a composite commitment binding all verified proofs. The resulting federation token is signed by the validator alone. No issuer needs to know about the others. This solves the cross-issuer attestation composition problem in agentic payment networks.</t>
+        </is>
+      </c>
+      <c r="D269" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hopley-x402-federation-zkp/</t>
+        </is>
+      </c>
+      <c r="E269" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F269" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 4 Jun 2026. **Family completion, added 26 Aug 2026.** Hopley x402 agentic-payment receipt cluster — the corpus tracked 4 of 11. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="5" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" s="5" t="inlineStr">
+        <is>
+          <t>draft-hopley-x402-payment-evidence-frame — Payment Evidence Frame for Agentic-Payment Lifecycle Receipts</t>
+        </is>
+      </c>
+      <c r="C270" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies a Payment Evidence Frame (PEF): a transport- agnostic envelope that wraps any payment lifecycle receipt from the x402 agentic-payment receipt stack under a named claim type, a deterministic frame identifier, and an optional transport-layer signature. The frame introduces three properties that the inner receipt types do not individually provide: (1) a stable cross-system identifier (frame_id) derived deterministically from the receipt content by SHA-256 over the JCS-canonical preimage, so the same payment evidence can be referenced by identifier across HTTP headers, agent-to-agent task artifacts, audit logs, and on-chain memo fields without re- serialising the full receipt; (2) a taxonomy label (claim_type) that tells a consumer what class of evidence a frame carries before the inner receipt format is parsed; and (3) a receipt integrity hash (receipt_hash) that allows any downstream party to confirm the inner receipt is unaltered without deserialising its full structure. The format uses the same JCS canonicalisation discipline (draft- hopley-x402-canonicalisation-jcs) as the five inner receipt formats it envelopes, so implementations require only one canonicalisation primitive for the full receipt stack.</t>
+        </is>
+      </c>
+      <c r="D270" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hopley-x402-payment-evidence-frame/</t>
+        </is>
+      </c>
+      <c r="E270" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F270" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 30 May 2026. **Family completion, added 26 Aug 2026.** Hopley x402 agentic-payment receipt cluster — the corpus tracked 4 of 11. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="5" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" s="5" t="inlineStr">
+        <is>
+          <t>draft-hopley-x402-pqc-credential-binding — Post-Quantum Credential Binding for x402 Agentic Payment Authorization</t>
+        </is>
+      </c>
+      <c r="C271" s="5" t="inlineStr">
+        <is>
+          <t>This document defines how Falcon-1024 (NIST FIPS 206 / FN-DSA) and ML-DSA-65 (NIST FIPS 204) credentials bind to x402 agentic payment authorization. It specifies the credential envelope format, the JCS canonicalization discipline applied to signed payloads, the gateway verification procedure, and the session token binding that replaces per-request API key authentication for credentialed agents. This is the first Internet-Draft in the agentic payments space to anchor credential binding to the NIST post-quantum cryptography standards (FIPS 203/204/206).</t>
+        </is>
+      </c>
+      <c r="D271" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hopley-x402-pqc-credential-binding/</t>
+        </is>
+      </c>
+      <c r="E271" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F271" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 4 Jun 2026. **Family completion, added 26 Aug 2026.** Hopley x402 agentic-payment receipt cluster — the corpus tracked 4 of 11. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="5" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" s="5" t="inlineStr">
+        <is>
+          <t>draft-hopley-x402-retention-chain — Self-Verifiable Retention Chain for Payment Receipts</t>
+        </is>
+      </c>
+      <c r="C272" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies eight cryptographic constructions for self-verifiable agentic payment records. The first, the Retention Chain Reference (retention_chain_ref), enables tamper-evident audit chains linking payment receipts without requiring external infrastructure. The second, the Payment Action Lifecycle, defines a content-addressed model for the exactly-once execution of payment actions, including an action reference primitive (action_ref) and a per-state transition hash (transition_hash) with a provable SKIP-on- retry idempotency guarantee. The third, the Settlement-Action Binding (binding_ref), binds a settled payment to the verified agent action it paid for and to the retention chain entry recording it, so that a settlement attestation proves not only that a payment occurred but which verified action it corresponds to. The fourth, the Policy Binding (policy_bound_ref), binds a content-addressed snapshot of the governing policy to an existing binding or chain reference, so that a decision is verifiable against the exact policy version that admitted it and a policy rotation is detectable by recomputation. The fifth, the Compliance Gate Binding (gate_ref), binds a categorical ALLOW/REFER/DENY compliance verdict and a no-PII payer reference to a policy or binding reference, so that a screening decision is provably tied to the policy in force when it was made and carries no personal data in the bound record. The sixth, the Pre-Payment Decision Chain (guardrail_ref), composes an agent identity reference, a spend authority reference, and the policy in force into one recomputable pre-payment ALLOW/DENY decision. The seventh, Post-Decision Execution Evidence (execution_ref), binds an executed action to the exact decision that authorized it, so the recorded execution is provably consistent with the decision and not merely correlated with an agent identity. The eighth, Cross-Party Authority Delegation (delegation_ref), binds a delegation of authority from one party to another and chains hand-offs, so a verifier can confirm that authority did not widen across an organizational boundary. All constructions use only SHA-256 and the JSON Canonicalization Scheme (JCS, RFC 8785), and are verifiable by any party holding the relevant receipts without contacting the issuer. The constructions satisfy the transaction recording and audit trail obligations of MiCA Article 80, DORA Article 14, and AMLR Article 56.</t>
+        </is>
+      </c>
+      <c r="D272" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hopley-x402-retention-chain/</t>
+        </is>
+      </c>
+      <c r="E272" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F272" s="5" t="inlineStr">
+        <is>
+          <t>Revision -07, 25 Jun 2026. **Family completion, added 26 Aug 2026.** Hopley x402 agentic-payment receipt cluster — the corpus tracked 4 of 11. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="5" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" s="5" t="inlineStr">
+        <is>
+          <t>draft-hopley-x402-rfc9421-binding — RFC 9421 HTTP Message Signatures Binding for x402 Payment Flows</t>
+        </is>
+      </c>
+      <c r="C273" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies the normative binding of RFC 9421 (HTTP Message Signatures) and RFC 9530 (Digest Fields for HTTP) to the x402-foundation/x402 challenge/response payment flow. It defines the minimum covered-components set for an x402 challenge response and a payment proof submission, the RFC 9530 Content-Digest discipline, keyid resolution patterns, and the multi-hop proxy-chain survival property that the x402 transport requires. This binding is complementary to the existing http-message-signatures extension in the x402 specification, which specifies agent identity and registration (registrationUrl, signatureSchemes, tags). This document specifies the normative binding: which components MUST be covered, how Content-Digest is handled, and how signatures survive multi-hop proxy chains. The two compose cleanly in a deployment that uses both. A reference implementation is provided as algovoi-rfc9421-verifier on PyPI and npm (Apache 2.0), with Python and TypeScript byte-for-byte parity, cross-validated against external fixture sets. This document is an Independent Submission filed per RFC 4846 and is intended for publication as Informational. It is not an IETF Standards Track document, does not represent IETF community consensus, and has not been subject to review by an IETF Working Group. Change control resides with the document author. The binding specified is one approach among possible alternatives; implementers may choose this approach, alternative approaches, or hybrid approaches as appropriate to their requirements.</t>
+        </is>
+      </c>
+      <c r="D273" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hopley-x402-rfc9421-binding/</t>
+        </is>
+      </c>
+      <c r="E273" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F273" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 13 Jun 2026. **Family completion, added 26 Aug 2026.** Hopley x402 agentic-payment receipt cluster — the corpus tracked 4 of 11. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="5" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" s="5" t="inlineStr">
+        <is>
+          <t>draft-ietf-wimse-arch — Workload Identity in a Multi System Environment (WIMSE) Architecture</t>
+        </is>
+      </c>
+      <c r="C274" s="5" t="inlineStr">
+        <is>
+          <t>The increasing prevalence of cloud computing and micro service architectures has led to the rise of complex software functions being built and deployed as workloads, where a workload is defined as software executing for a specific purpose, potentially comprising one or more running instances. This document discusses an architecture for designing and standardizing protocols and payloads for conveying workload identity and security context information.</t>
+        </is>
+      </c>
+      <c r="D274" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-wimse-arch/</t>
+        </is>
+      </c>
+      <c r="E274" s="5" t="inlineStr">
+        <is>
+          <t>IETF (WIMSE WG)</t>
+        </is>
+      </c>
+      <c r="F274" s="5" t="inlineStr">
+        <is>
+          <t>Revision -08, 6 Jul 2026. **Family completion, added 26 Aug 2026.** WIMSE **working group** draft — the corpus tracked 4 of 9 WIMSE WG drafts. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only. **WG draft.** The WIMSE architecture document — the frame for the WIMSE drafts already tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="5" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" s="5" t="inlineStr">
+        <is>
+          <t>draft-ietf-wimse-identifier — Workload Identifier</t>
+        </is>
+      </c>
+      <c r="C275" s="5" t="inlineStr">
+        <is>
+          <t>This document defines a canonical identifier for workloads, referred to as the Workload Identifier. A Workload Identifier is a URI that uniquely identifies a workload within the context of a specific trust domain. This identifier can be embedded in Workload Identity Credentials, including X.509 certificates and JWT-based tokens, to support authentication, authorization, and policy enforcement across diverse systems. The Workload Identifier format ensures interoperability, facilitates secure identity federation, and enables consistent identity semantics.</t>
+        </is>
+      </c>
+      <c r="D275" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-wimse-identifier/</t>
+        </is>
+      </c>
+      <c r="E275" s="5" t="inlineStr">
+        <is>
+          <t>IETF (WIMSE WG)</t>
+        </is>
+      </c>
+      <c r="F275" s="5" t="inlineStr">
+        <is>
+          <t>Revision -03, 6 Jul 2026. **Family completion, added 26 Aug 2026.** WIMSE **working group** draft — the corpus tracked 4 of 9 WIMSE WG drafts. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only. **WG draft.** Defines the workload identifier itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="5" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" s="5" t="inlineStr">
+        <is>
+          <t>draft-ietf-wimse-wpt — WIMSE Workload Proof Token</t>
+        </is>
+      </c>
+      <c r="C276" s="5" t="inlineStr">
+        <is>
+          <t>The WIMSE architecture defines authentication and authorization for software workloads in a variety of runtime environments, from basic deployments to complex multi-service, multi-cloud, multi-tenant systems. This document specifies the Workload Proof Token (WPT), a mechanism for workloads to prove possession of the private key associated with a Workload Identity Token (WIT). The WPT is a signed JWT that binds the workload's authentication to a specific HTTP request, providing application-level proof of possession for workload-to-workload communication. This specification is designed to work alongside the WIT credential format defined in draft-ietf- wimse-workload-creds and can be combined with other WIMSE protocols in multi-hop call chains.</t>
+        </is>
+      </c>
+      <c r="D276" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ietf-wimse-wpt/</t>
+        </is>
+      </c>
+      <c r="E276" s="5" t="inlineStr">
+        <is>
+          <t>IETF (WIMSE WG)</t>
+        </is>
+      </c>
+      <c r="F276" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 2 Mar 2026. **Family completion, added 26 Aug 2026.** WIMSE **working group** draft — the corpus tracked 4 of 9 WIMSE WG drafts. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="5" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" s="5" t="inlineStr">
+        <is>
+          <t>draft-kavian-aep-api-key-session-credential — API-Key Session Credential Grant Type for the Agent Enrollment Protocol</t>
+        </is>
+      </c>
+      <c r="C277" s="5" t="inlineStr">
+        <is>
+          <t>This document defines the API-key session-credential grant type for the Agent Enrollment Protocol (AEP). The grant type lets an AEP Service issue an opaque API key through the AEP Grant command for deployments that already operate header-based API-key authentication.</t>
+        </is>
+      </c>
+      <c r="D277" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-kavian-aep-api-key-session-credential/</t>
+        </is>
+      </c>
+      <c r="E277" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F277" s="5" t="inlineStr">
+        <is>
+          <t>Revision -03, 24 Aug 2026. **Family completion, added 26 Aug 2026.** Agent Enrollment Protocol (AEP) family — the corpus tracked 2 of 8. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="5" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" s="5" t="inlineStr">
+        <is>
+          <t>draft-kavian-aep-basic-session-credential — Basic Session Credential Grant Type for the Agent Enrollment Protocol</t>
+        </is>
+      </c>
+      <c r="C278" s="5" t="inlineStr">
+        <is>
+          <t>This document defines the Basic session-credential grant type for the Agent Enrollment Protocol (AEP). The grant type lets an AEP Service issue an HTTP Basic credential through the AEP Grant command for deployments that already integrate with Basic authentication middleware.</t>
+        </is>
+      </c>
+      <c r="D278" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-kavian-aep-basic-session-credential/</t>
+        </is>
+      </c>
+      <c r="E278" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F278" s="5" t="inlineStr">
+        <is>
+          <t>Revision -03, 24 Aug 2026. **Family completion, added 26 Aug 2026.** Agent Enrollment Protocol (AEP) family — the corpus tracked 2 of 8. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="5" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" s="5" t="inlineStr">
+        <is>
+          <t>draft-kavian-aep-claims — AEP Claim Values</t>
+        </is>
+      </c>
+      <c r="C279" s="5" t="inlineStr">
+        <is>
+          <t>This document defines a claim-value catalog for the Agent Enrollment Protocol (AEP). It specifies stable claim names and forward- compatible JSON value shapes that Agents can submit during enrollment when requested by a Service Inspect document.</t>
+        </is>
+      </c>
+      <c r="D279" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-kavian-aep-claims/</t>
+        </is>
+      </c>
+      <c r="E279" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F279" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 24 Aug 2026. **Family completion, added 26 Aug 2026.** Agent Enrollment Protocol (AEP) family — the corpus tracked 2 of 8. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="5" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" s="5" t="inlineStr">
+        <is>
+          <t>draft-kavian-aep-did-web-identity-method — The did:web Identity Method for the Agent Enrollment Protocol</t>
+        </is>
+      </c>
+      <c r="C280" s="5" t="inlineStr">
+        <is>
+          <t>This document defines the did:web identity method for the Agent Enrollment Protocol (AEP). The method lets an AEP Service verify Agent client assertion JWTs by resolving an Agent did:web identifier to a DID document published over HTTPS.</t>
+        </is>
+      </c>
+      <c r="D280" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-kavian-aep-did-web-identity-method/</t>
+        </is>
+      </c>
+      <c r="E280" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F280" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 29 Jun 2026. **Family completion, added 26 Aug 2026.** Agent Enrollment Protocol (AEP) family — the corpus tracked 2 of 8. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" s="5" t="inlineStr">
+        <is>
+          <t>draft-kavian-aep-platform-hosted-identity — AEP Platform Hosted Identity</t>
+        </is>
+      </c>
+      <c r="C281" s="5" t="inlineStr">
+        <is>
+          <t>This document defines interoperable hosted identity behavior for Agent Enrollment Protocol (AEP) Platforms. It lets a Platform provision Service-scoped Agent did:web identities, publish DID documents, custody signing keys, and produce AEP client assertion JWTs through delegated signing operations.</t>
+        </is>
+      </c>
+      <c r="D281" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-kavian-aep-platform-hosted-identity/</t>
+        </is>
+      </c>
+      <c r="E281" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F281" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 23 Jul 2026. **Family completion, added 26 Aug 2026.** Agent Enrollment Protocol (AEP) family — the corpus tracked 2 of 8. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="5" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" s="5" t="inlineStr">
+        <is>
+          <t>draft-kavian-offering-discovery-protocol — The Offering Discovery Protocol</t>
+        </is>
+      </c>
+      <c r="C282" s="5" t="inlineStr">
+        <is>
+          <t>The Offering Discovery Protocol (ODP) enables an automated Agent to inspect a Service, discover its Collections and Offerings, interpret Service-defined structured attributes, and identify links to subsequent operations. ODP supports catalogs ranging from a few Offerings to large marketplaces without imposing a universal product taxonomy. This document defines the protocol's scope, terminology, roles, discovery architecture, extensibility model, composition boundaries, and conformance model.</t>
+        </is>
+      </c>
+      <c r="D282" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-kavian-offering-discovery-protocol/</t>
+        </is>
+      </c>
+      <c r="E282" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F282" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 24 Aug 2026. **Family completion, added 26 Aug 2026.** Agent Enrollment Protocol (AEP) family — the corpus tracked 2 of 8. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only. Sits slightly outside the AEP naming but is part of the same author's stack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="5" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-oauth-actor-profile — OAuth Actor Profile for Delegation</t>
+        </is>
+      </c>
+      <c r="C283" s="5" t="inlineStr">
+        <is>
+          <t>OAuth deployments increasingly involve agents and workloads acting on behalf of human users across organizational boundaries. Existing specifications provide relevant building blocks (notably the act claim from RFC 8693 Token Exchange) but do not define a consistent profile for representing delegated actor relationships across JWT assertion grants (RFC 7523), JWT access tokens (RFC 9068), and Transaction Tokens, nor for classifying actor entity types or signaling support between authorization servers and resource servers. The result is inconsistent actor representation and actor- representation interoperability gaps that force deployments to rely on proprietary conventions. This document defines the OAuth Actor Profile for Delegation. It specifies a common act claim structure extended with sub_profile for entity-type classification, processing rules for authorization servers and resource servers across the three token families and their Token Exchange inputs, and OAuth discovery metadata parameters for advertising actor-profile support. The profile applies uniformly across token types and integrates with existing sender-constraint mechanisms (DPoP, mTLS). It does not standardize the policies by which systems determine whether a given actor is permitted to act for a subject; those decisions remain deployment-specific.</t>
+        </is>
+      </c>
+      <c r="D283" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-actor-profile/</t>
+        </is>
+      </c>
+      <c r="E283" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F283" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 30 Apr 2026. **Family completion, added 26 Aug 2026.** McGuinness individual I-D. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only. **This is the Actor Profile itself** — the anchor draft this corpus repeatedly refers to (draft-mw-oauth-actor-chain is described here as directly responding to it) and which was somehow never tracked while actor-proofs and actor-receipts were. The most consequential single omission the cross-check found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="5" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" s="5" t="inlineStr">
+        <is>
+          <t>draft-morrison-alter-uri-scheme — The 'alter' URI Scheme for Dispatchable ~handle References</t>
+        </is>
+      </c>
+      <c r="C284" s="5" t="inlineStr">
+        <is>
+          <t>This document defines the alter URI scheme as a dispatchable reference syntax for ~handle identity references published under the DNS substrate defined in [MCPDNS]. An alter: URI binds a textual ~handle reference to a resolution and verification procedure that retrieves the handle's envelope from the publishing zone, validates the envelope's signature chain, and dispatches the result to an operating-system URI handler. The reference may be scoped to an organisation, narrowed to a named facet of the identity, and addressed to a typed action surface. The scheme is the addressing form of the ~handle@org:facet/action reference; its resolution semantics are those of [MCPDNS], reused without modification. The scheme is provider-neutral, introduces no new cryptographic primitive, and reuses the resolution and verification procedures of [MCPDNS] without modification. The principal contribution is a single, self-verifying dispatch surface for handle-typed references: clicking, typing, or scanning an alter: URI yields a verified handle resolution rather than a free-text string or an unauthenticated fetch, and where an action is addressed it yields a verify-before- side-effect dispatch. This document requests provisional registration of the alter scheme with IANA per [RFC7595] Section 3.</t>
+        </is>
+      </c>
+      <c r="D284" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-alter-uri-scheme/</t>
+        </is>
+      </c>
+      <c r="E284" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F284" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 11 Aug 2026. **Family completion, added 26 Aug 2026.** Morrison ~handle identity family — the corpus described this as a six-draft family; it is at least 18. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="5" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" s="5" t="inlineStr">
+        <is>
+          <t>draft-morrison-binding-moment-envelope — The Briefing-and-Binding Envelope: A Delivery Contract for Agent-to-Principal Decision Moments with Dual-Veto Reconciliation</t>
+        </is>
+      </c>
+      <c r="C285" s="5" t="inlineStr">
+        <is>
+          <t>This memo specifies the briefing-and-binding envelope: a delivery contract for the wire-level structure by which an artificial- intelligence agent surfaces a consequential decision to the human principal it acts for, and by which the principal commits, declines, amends, or rejects that decision. The envelope carries eight named slots (a synopsis, findings, recommendations, an offer of detail, a question stem, a set of options each marked with its own reasoning, a single recommended option, and a pair of escape hatches) and is emitted as a structured field of a Model Context Protocol [MCP] tool result. The contribution is the delivery contract itself: a single renderer-agnostic envelope so that the briefing an agent delivers and the binding a principal commits back have one machine-checkable shape across every consuming surface. The central element is the dual-veto handshake: one escape hatch lets the principal revise the answer space while accepting the question; the other lets the principal reject the question itself and reopen deliberation. Either party may veto. The memo defines a content digest over the envelope, canonicalized under JCS and hashed with SHA-256, so that a resolution names the exact envelope it resolves and an external receipt can reference that envelope by digest. The memo is Informational. No new transport is introduced; the envelope composes with the handle namespace of [IDPRONOUNS] and the MCP tool surface of [POLICYPROV].</t>
+        </is>
+      </c>
+      <c r="D285" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-binding-moment-envelope/</t>
+        </is>
+      </c>
+      <c r="E285" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F285" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 23 Jul 2026. **Family completion, added 26 Aug 2026.** Morrison ~handle identity family — the corpus described this as a six-draft family; it is at least 18. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="5" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" s="5" t="inlineStr">
+        <is>
+          <t>draft-morrison-compute-location-gate — The Compute-Location Gate: Provenance-Class Routing of Identity Inference with Wire-Layer Refusal of Unconsented Provenance Classes</t>
+        </is>
+      </c>
+      <c r="C286" s="5" t="inlineStr">
+        <is>
+          <t>This memo specifies the compute-location gate: a mechanism by which a client and an identity-inference server negotiate, at the wire layer and before any inference is performed, the location at which an identity inference will compute, as a deterministic function of the provenance class of the input signal. Three provenance classes are distinguished. Active inference, initiated by the inferred-about principal, MAY compute server-side and produce a server-held identity vector. Passive aggregate observation over a cohort no smaller than a declared minimum MAY compute server-side but yields only a population-level observation that is not attributable to an individual. Passive individual observation is local-only: it is computed and retained on the device that observed it and is never transmitted to a server. The gate is enforced by consent-class matching and by a wire-layer refusal returned when a requested provenance class is not consented; it is not enforced by any cryptographic proof concerning data that was not used. The memo is Informational. The wire surface composes with the discovery mechanism of [MCPDNS], the handle namespace of [IDPRONOUNS], and the organisational policy substrate of [POLICYPROV]; no new transport is introduced.</t>
+        </is>
+      </c>
+      <c r="D286" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-compute-location-gate/</t>
+        </is>
+      </c>
+      <c r="E286" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F286" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 26 Aug 2026. **Family completion, added 26 Aug 2026.** Morrison ~handle identity family — the corpus described this as a six-draft family; it is at least 18. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="5" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" s="5" t="inlineStr">
+        <is>
+          <t>draft-morrison-live-reference-resolution — Live Reference Resolution for Autonomous Agent Beliefs</t>
+        </is>
+      </c>
+      <c r="C287" s="5" t="inlineStr">
+        <is>
+          <t>A recurring class of autonomous-agent failure arises when an agent acts on a belief read from a cached, derived, or proxy copy that has silently diverged from the authority the belief claims to represent. This document describes a reference-resolution discipline for the working beliefs an agent reasons and acts from. Each belief is held as a reference to a single named lowest authority and is resolved live at the point of use, with verification. When the authority is unobservable or the resolved value is stale, the belief takes an explicit uncertainty state rather than a prior cached value; that state propagates to any belief derived from it, and an uncertain belief feeding a costly or irreversible act blocks or escalates rather than proceeding. Every resolution chain terminates in a single self-authorising root. The document is Informational. It records a discipline and a vocabulary; it does not define a wire protocol.</t>
+        </is>
+      </c>
+      <c r="D287" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-live-reference-resolution/</t>
+        </is>
+      </c>
+      <c r="E287" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F287" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 5 Jul 2026. **Family completion, added 26 Aug 2026.** Morrison ~handle identity family — the corpus described this as a six-draft family; it is at least 18. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="5" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" s="5" t="inlineStr">
+        <is>
+          <t>draft-morrison-morning-brief — The Morning Brief: A Federated, Identity-Attested Situational-Awareness Payload</t>
+        </is>
+      </c>
+      <c r="C288" s="5" t="inlineStr">
+        <is>
+          <t>This document defines the Morning Brief: a federated, identity- attested situational-awareness payload exchanged between organisations, their agents, and peer agents operating under an Identity Accord [ACCORD]. A Morning Brief carries a signed, bounded- lifetime summary of signals, escalations, decisions, and optional commerce quotes from one ~handle to another. Every signal entry carries a provenance_class distinguishing active self-report, passive aggregate observation, and passive individual observation; the last of these is forbidden on the wire and rejected at the grammar level. Readers present a capability token scoped by (category, provenance_class) that gates release BEFORE payload emission, not after. The payload is envelope-signed with COSE_Sign1 [RFC9052] over a JCS-canonicalised [RFC8785] representation, bound to the issuer's Sovereign-tier handle per [IDCOMMITS]. Briefs carry a mandatory not_after (default 24h) and reference a revocation endpoint discovered via DNS TXT per [MCPDNS]. The document defines the wire format only; rendering, storage, and retention are out of scope.</t>
+        </is>
+      </c>
+      <c r="D288" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-morning-brief/</t>
+        </is>
+      </c>
+      <c r="E288" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F288" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 12 Aug 2026. **Family completion, added 26 Aug 2026.** Morrison ~handle identity family — the corpus described this as a six-draft family; it is at least 18. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="5" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" s="5" t="inlineStr">
+        <is>
+          <t>draft-morrison-org-alter-policy-provision — Policy Provision and Governance Inheritance from an Organisational Identity Substrate</t>
+        </is>
+      </c>
+      <c r="C289" s="5" t="inlineStr">
+        <is>
+          <t>This memo specifies how an artificial-intelligence agent runtime, bound at instantiation to a principal identity handle, resolves at session initialisation a target organisational identity substrate from a manifest source bound to the runtime's working context and retrieves from that substrate a typed policy stack comprising a handbook artefact, a standard-operating-procedure registry pointer, an enforcement-gate specification, and an audit-signal ingestion endpoint. The policy stack is then applied as runtime constraints on subsequent tool invocations, with audit signals emitted back to the same substrate. Policy provision occurs in the same act of session initialisation as principal identification, rather than as a separate ceremony against a side-channel governance plane. A principal concurrently bound to multiple organisational substrates operates the runtime under a deterministic composition of the several policy stacks, with cross-organisational residual conflicts routed to the peer-protocol Identity Accord ceremony [IDACCORD] rather than to a meta-federation authority. The memo is Informational. The wire surface relies on the DNS-based discovery of [MCPDNS] and the handle namespace of [IDPRONOUNS]; no new transport is introduced.</t>
+        </is>
+      </c>
+      <c r="D289" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-org-alter-policy-provision/</t>
+        </is>
+      </c>
+      <c r="E289" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F289" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 11 Aug 2026. **Family completion, added 26 Aug 2026.** Morrison ~handle identity family — the corpus described this as a six-draft family; it is at least 18. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="5" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" s="5" t="inlineStr">
+        <is>
+          <t>draft-morrison-ot-command-authority — Consented and Attributable Agent Authority for Operational-Technology Control Actions</t>
+        </is>
+      </c>
+      <c r="C290" s="5" t="inlineStr">
+        <is>
+          <t>This memo specifies a binding profile by which a control action issued to an operational-technology (OT) or industrial control system on the authority of a software agent is refused unless it carries a verifiable statement of who the agent is, which human principal it acts for, whether that principal consented to this specific action on this specific asset, whether a human authorised the action where the action's risk class requires it, and an append-only record sufficient to attribute the action afterward. The profile does not invent new cryptography or a new identity mechanism. It composes primitives defined elsewhere, DNSSEC-rooted agent discovery, scoped and revocable consent, a human-in-the-loop binding moment, and a provenance-labelled audit record, into a single structure, the Command Authority Envelope, that an OT conduit evaluates and, on any missing or invalid binding, refuses. The profile is availability- first and fails closed on authority, never on safety: it MUST NOT be placed in the trip path of a safety function. The memo maps the profile onto the identification, use-control, and audit requirements that [IEC62443] and [NERCCIP] state but do not give a wire mechanism for. The methods by which a principal's identity is inferred are out of scope by construction.</t>
+        </is>
+      </c>
+      <c r="D290" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-ot-command-authority/</t>
+        </is>
+      </c>
+      <c r="E290" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F290" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 23 Jul 2026. **Family completion, added 26 Aug 2026.** Morrison ~handle identity family — the corpus described this as a six-draft family; it is at least 18. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="5" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" s="5" t="inlineStr">
+        <is>
+          <t>draft-morrison-reviewed-by-trailer — Reviewed-By Trailer: Sovereign-Portable Peer-Review Attribution for Content-Hash-Bound Artefacts</t>
+        </is>
+      </c>
+      <c r="C291" s="5" t="inlineStr">
+        <is>
+          <t>This document defines a trailer grammar for sovereign-portable peer review as an extension of the identity-attributed commit grammar in [COMMITS]. The grammar introduces one required trailer (Reviewed- By:) and three optional companion trailers (Review-Stance:, Review- Of:, Witnessed-By:) that bind a Sovereign-tier ~handle to a specific act of review over a specific content artefact, cryptographically signed using the Ed25519 mechanism of [COMMITS]. The mechanism applies uniformly to git commits, document manifests, pre-prints, patent disclosures, and any other content-addressable artefact. Reviewer reputation accumulates on the sovereign handle rather than on a publisher's platform, making reviewer trust portable across journals, pre-print servers, and private review contexts. Pseudonymous review for anonymous peer-review processes is supported by permitting a Sovereign handle whose underlying party is concealed through out-of-band key custody, preserving full cryptographic verifiability of the review act without disclosing the reviewer's underlying identity. The grammar is positioned as complementary to CRediT [CREDIT], ORCID [ORCID], and DOI [DOI] attribution infrastructure, not as a replacement for them.</t>
+        </is>
+      </c>
+      <c r="D291" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-reviewed-by-trailer/</t>
+        </is>
+      </c>
+      <c r="E291" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F291" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 26 Aug 2026. **Family completion, added 26 Aug 2026.** Morrison ~handle identity family — the corpus described this as a six-draft family; it is at least 18. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="5" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" s="5" t="inlineStr">
+        <is>
+          <t>draft-morrison-substrate-observation — Substrate-Observation as an Alternative to Envelope Coordination for Concurrent Sessions</t>
+        </is>
+      </c>
+      <c r="C292" s="5" t="inlineStr">
+        <is>
+          <t>This memo articulates a coordination-protocol anti-pattern observed in cross-tool agentic systems and describes a substrate-observation alternative that does not require negotiating a wire format between heterogeneous concurrent sessions of an identity-bound principal. The memo is Informational. No protocol element is being proposed for standardisation; the contribution is the opposite, a delineation of what should NOT be standardised, and why, with a reference to the substrate-physics primitives that take its place. Companion memos in the morrison-* family describe the identity primitives this memo presumes; specifically, this memo relies on the ~handle namespace established in [IDPRONOUNS] and the per-principal identity substrate referenced in [IDACCORD].</t>
+        </is>
+      </c>
+      <c r="D292" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-substrate-observation/</t>
+        </is>
+      </c>
+      <c r="E292" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F292" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 11 Aug 2026. **Family completion, added 26 Aug 2026.** Morrison ~handle identity family — the corpus described this as a six-draft family; it is at least 18. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" s="5" t="inlineStr">
+        <is>
+          <t>draft-morrison-substrate-provenance-grammar — Substrate-Provenance Annotation Grammar for Large-Language-Model Output</t>
+        </is>
+      </c>
+      <c r="C293" s="5" t="inlineStr">
+        <is>
+          <t>This memo specifies a wire-level annotation grammar by which a large- language-model output may carry, at emission and at the granularity of an individual assertion, a provenance label drawn from a closed enumerated vocabulary of substrate-class identifiers. The memo defines the closed vocabulary, the per-assertion attachment form, the admissibility discipline a relying party MAY apply to the labels, and two terminal output states, UNVERIFIED-INFERENCE and DECAYED-TO- UNCERTAINTY, equal-rank with assertion and denial. The memo does not specify what an inference system MUST do; it specifies the wire grammar by which a relying party may inspect what the inference system DID with respect to the substrates it consulted. The memo is Informational.</t>
+        </is>
+      </c>
+      <c r="D293" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-substrate-provenance-grammar/</t>
+        </is>
+      </c>
+      <c r="E293" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual draft)</t>
+        </is>
+      </c>
+      <c r="F293" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 26 Aug 2026. **Family completion, added 26 Aug 2026.** Morrison ~handle identity family — the corpus described this as a six-draft family; it is at least 18. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="5" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" s="5" t="inlineStr">
+        <is>
+          <t>draft-ruvalcaba-hctp — The Hash-Chain Context Transfer Protocol (HCTP)</t>
+        </is>
+      </c>
+      <c r="C294" s="5" t="inlineStr">
+        <is>
+          <t>The Hash-Chain Context Transfer Protocol (HCTP) is a payload format and synchronization protocol for incrementally transferring an ordered, append-only sequence of conversational context between two endpoints over a bandwidth-constrained channel. Acknowledged history is represented by a single fixed-size rolling hash commitment (the "static root"); only not-yet-acknowledged context blocks (the "dynamic window") are transmitted. As a result, the per-message wire overhead attributable to history is constant and independent of the total number of previously acknowledged turns. HCTP is transport- agnostic and carries no confidentiality or peer authentication of its own; it is intended to run over a secure transport. This document specifies the HCTP data model, wire format, rolling-root computation, and synchronization state machine.</t>
+        </is>
+      </c>
+      <c r="D294" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ruvalcaba-hctp/</t>
+        </is>
+      </c>
+      <c r="E294" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F294" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 11 Aug 2026. **Family completion, added 26 Aug 2026.** NHE family — the corpus tracked 2 of 8, recording it as an identity+authz pair rather than a family. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="5" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" s="5" t="inlineStr">
+        <is>
+          <t>draft-ruvalcaba-nhe-arch — An Architecture for Non-Human Entities (NHE): A Reference Model for Persistent, Identity-Bearing Autonomous Agents</t>
+        </is>
+      </c>
+      <c r="C295" s="5" t="inlineStr">
+        <is>
+          <t>This document defines a reference architecture for a Non-Human Entity (NHE): a persistent, identity-bearing autonomous software agent that maintains continuity of memory and identity across sessions and hosts, acts under bounded authority, and produces a tamper-evident record of its reasoning and actions. The document specifies the NHE as a functional artifact: a bounded, inspectable, and terminable software system. It makes no claim that an NHE is alive, sentient, or a moral or legal person, and such claims are explicitly out of scope. The architecture decomposes an NHE into a small set of components joined by well-defined interfaces. Each interface at which two independent implementations must interoperate is a candidate for a separate Standards-Track specification; this document is the informational reference model that names those interfaces and the trust relationships among them. It is intended to frame a suite of companion protocol documents, of which the Hash-Chain Context Transfer Protocol (HCTP) is the first.</t>
+        </is>
+      </c>
+      <c r="D295" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ruvalcaba-nhe-arch/</t>
+        </is>
+      </c>
+      <c r="E295" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F295" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 13 Aug 2026. **Family completion, added 26 Aug 2026.** NHE family — the corpus tracked 2 of 8, recording it as an identity+authz pair rather than a family. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only. The NHE reference model. The corpus recorded NHE as an identity+authz pair on 26 Aug; it is in fact a six-draft family and this is its architecture root.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="5" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" s="5" t="inlineStr">
+        <is>
+          <t>draft-ruvalcaba-nhe-audit — NHE Reasoning-Audit Log: A Tamper-Evident, Content-Optional Audit Chain for Autonomous Agents</t>
+        </is>
+      </c>
+      <c r="C296" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies a tamper-evident audit chain for the reasoning and actions of a Non-Human Entity (NHE). Each audited event --- a reasoning step obtained at the boundary to a model provider, or a tool invocation obtained at the execution boundary --- is recorded as an entry whose bound fields are hash-linked to its predecessor, so that any alteration, omission, or reordering is detectable by an independent verifier. The chain binds metadata (model, provider, subject identity, and reasoning scale) into the entry hash, and supports a prove-without-exposing mode in which a verifier confirms that an event occurred, with the attested metadata, without the event's content being disclosed. Content storage is optional and its retention is configurable independently of the chain, so content may be redacted without destroying the chain's integrity. The entry data model and canonical serialization are specified here; the wire and proof-export encodings are deferred to the next revision.</t>
+        </is>
+      </c>
+      <c r="D296" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ruvalcaba-nhe-audit/</t>
+        </is>
+      </c>
+      <c r="E296" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F296" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 13 Aug 2026. **Family completion, added 26 Aug 2026.** NHE family — the corpus tracked 2 of 8, recording it as an identity+authz pair rather than a family. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="5" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" s="5" t="inlineStr">
+        <is>
+          <t>draft-ruvalcaba-nhe-bootstrap — NHE Constrained Bootstrap: A Self-Describing Capability and Constraint Declaration Protocol for Autonomous Agents</t>
+        </is>
+      </c>
+      <c r="C297" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies how a Non-Human Entity (NHE) declares, at bootstrap, what it is capable of and is thereby bounded in what it is permitted to do. An entity produces a signed, self-describing capability manifest through automated introspection; a coordinator classifies the manifest into a capability tier that maps to a permission matrix --- the set of task types the entity is authorized to perform --- and every subsequent task dispatch is gated against that envelope. The result is a verifiable, self-describing constraint on an entity established at the moment it joins, realizing the bounded-authority invariant of the NHE architecture at boot time. The manifest and handshake data model is specified here; the wire encoding is deferred to the next revision.</t>
+        </is>
+      </c>
+      <c r="D297" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ruvalcaba-nhe-bootstrap/</t>
+        </is>
+      </c>
+      <c r="E297" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F297" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 13 Aug 2026. **Family completion, added 26 Aug 2026.** NHE family — the corpus tracked 2 of 8, recording it as an identity+authz pair rather than a family. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="5" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" s="5" t="inlineStr">
+        <is>
+          <t>draft-ruvalcaba-nhe-memory — NHE Memory: A Verifiable Memory-Record Format and Reputation-Weighted Reconciliation Protocol</t>
+        </is>
+      </c>
+      <c r="C298" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies two interoperability surfaces of the memory component of a Non-Human Entity (NHE). Part I defines a verifiable memory-record format: an integrity structure in which each record binds a hash of its own content and version-specific hashes of the prior records it references, so that tampering can be detected and localized on demand, per-record, without a linear chain, a Merkle tree, or distributed consensus. Part II defines a reconciliation protocol by which two divergent memory accumulations are merged without loss or forgery: a delta format, a reputation-weighted merge in which a contributed item enters at a confidence bounded by its contributor's reputation rather than its self-asserted value, and provenance that supports lineage-scoped rollback. The data models are specified here; the wire encodings are deferred to the next revision.</t>
+        </is>
+      </c>
+      <c r="D298" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ruvalcaba-nhe-memory/</t>
+        </is>
+      </c>
+      <c r="E298" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F298" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 13 Aug 2026. **Family completion, added 26 Aug 2026.** NHE family — the corpus tracked 2 of 8, recording it as an identity+authz pair rather than a family. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="5" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" s="5" t="inlineStr">
+        <is>
+          <t>draft-ruvalcaba-nhe-mesh — The NHE Mesh Protocol: Entity-to-Entity Messaging and Task Distribution</t>
+        </is>
+      </c>
+      <c r="C299" s="5" t="inlineStr">
+        <is>
+          <t>The NHE Mesh Protocol lets independently operated Non-Human Entities (NHEs) exchange messages and distribute work without a central coordinator. It defines three things: a liveness/presence mechanism, an addressed message envelope, and a task lifecycle (create, claim, complete) that provides at-most-once assignment of a unit of work across mutually distrusting peers. Peers are named by their NHE identity and authenticated through the NHE identity interface; the Mesh Protocol carries the envelope and runs over a secure transport. This is a skeleton (-00): the framing, message set, and state machine are specified here, and the concrete on-the-wire encoding is deferred to the next revision.</t>
+        </is>
+      </c>
+      <c r="D299" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ruvalcaba-nhe-mesh/</t>
+        </is>
+      </c>
+      <c r="E299" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F299" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 13 Aug 2026. **Family completion, added 26 Aug 2026.** NHE family — the corpus tracked 2 of 8, recording it as an identity+authz pair rather than a family. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="5" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" s="5" t="inlineStr">
+        <is>
+          <t>draft-sato-soos-acd — The Agent Compliance Disclosure (ACD) Protocol for Agentic AI Systems</t>
+        </is>
+      </c>
+      <c r="C300" s="5" t="inlineStr">
+        <is>
+          <t>A regulated resource provider -- a bank, a government API, a healthcare records system -- receives a request from an AI agent. The agent claims to operate under a constitutional compliance policy and a valid mandate. The resource provider has no mechanism to verify these claims. Without a machine-verifiable compliance disclosure, the resource provider cannot confirm the agent's governing law, its active prohibition set, its audit trail reference, or its principal hierarchy -- before granting access. This document defines the Agent Compliance Disclosure (ACD) Protocol: a machine-to-machine compliance handshake that must complete before an AI agent is granted access to a regulated resource class. ACD defines the ACD Record schema (a three-layer structured disclosure produced by the SOOS kernel, covering legal identity, constitutional compliance, and principal hierarchy), the ACD Presentation Protocol (the query/response exchange between a resource provider and the SOOS kernel), the ACD Trust Hierarchy (operator-declared trust levels and Audit Principal credentials), the ACD-to-MJWT binding (ACD MUST reference the session MJWT jti), and the GAR integration (ACD presentation events as Authority Lifecycle Events). ACD Records are produced exclusively by the Governing Enforcement Component (GEC), signed by the kernel's KIA private key, and logged in the Governance Audit Record (GAR). LLM self-report of compliance posture is architecturally insufficient and MUST NOT be used as an ACD disclosure surface. ACD is the inbound complement to the Resource Governance Protocol (RGP): where RGP governs outbound capability discovery, ACD governs inbound compliance verification. Together they define the complete resource access governance flow for SOOS-governed agents.</t>
+        </is>
+      </c>
+      <c r="D300" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-sato-soos-acd/</t>
+        </is>
+      </c>
+      <c r="E300" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F300" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 1 Jul 2026. **Family completion, added 26 Aug 2026.** SOOS governance suite (Tom Sato, MyAuberge K.K.) — the corpus tracked 5 of 18. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" s="5" t="inlineStr">
+        <is>
+          <t>draft-sato-soos-aep — The Agent Execution Protocol (AEP) for Agentic AI Systems</t>
+        </is>
+      </c>
+      <c r="C301" s="5" t="inlineStr">
+        <is>
+          <t>An AI agent that can act cannot be governed unless there is a normative contract for how it receives its world, how it declares its intent, and how it learns what it is and is not permitted to do -- at every step, in every iteration, without exception. AI agents operating on governed resources require a normative interface contract between their internal reasoning loop and the Governing Enforcement Component (GEC) that enforces authorization policy, records transitions to a tamper-evident Event Stream, and mediates access to Sovereign Object instances. Existing agent frameworks define no such contract. Agents submit actions without a normative delivery protocol for the state and permission context they act on; GECs enforce policy without a normative protocol for communicating denial rationale back to agents; human oversight is invoked without a normative session state that governs the resulting suspension. This document defines the Agent Execution Protocol (AEP): the normative five-step loop -- SENSE, REASON, PLAN, ACT, OBSERVE -- that specifies how a governed AI agent interfaces with GEC services at each iteration. The AEP defines the Context Package delivered at SENSE, the GEC Query Interface exercised at PLAN, the Transition Request submitted at ACT, and the atomic GEC response received at OBSERVE. The AEP specifies two conformance modes -- Standard and Goal Execution Engine (GEE) -- and normatively integrates the Intent Declaration Primitive [I-D.sato-soos-idp], the Mandate JWT [I-D.sato-soos-mjwt], the Human Escalation Mechanism [I-D.sato-soos-hem], the Governance Audit Record [I-D.sato-soos-gar], the Constitutional AI Protocol [I-D.sato-soos-cap], and the Sovereign Object [I-D.sato-soos-sov] as components of a single governed execution architecture. The REASON step is intentionally GEC-unspecified: the LLM reasoning engine is opaque to the protocol. The AEP is the transmission between the LLM engine and the GEC enforcement substrate. Version -02 adds: XPID binding at session open (GEC MUST bind XPID from KIA-verified Party Registry; MUST NOT accept client-supplied XPID); STALLED and PLAN_B_ACTIVE session states with full normative definitions, trigger conditions, and resume conditions; Expected Outcome Declaration (EOD) as a pre-session commitment structure with primary outcome, acceptance envelope, and pre-declared Plan B; RETRY_CONTINUATION normative strengthening with what-changed-since- last-attempt requirement and prior_denial_count Cedar attribute; AEP-to-OTel mapping section (Section 8) with mandatory span attributes at each AEP phase; four new Security Considerations; and updated IANA registrations for new state codes and EOD media type.</t>
+        </is>
+      </c>
+      <c r="D301" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-sato-soos-aep/</t>
+        </is>
+      </c>
+      <c r="E301" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F301" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 30 Jun 2026. **Family completion, added 26 Aug 2026.** SOOS governance suite (Tom Sato, MyAuberge K.K.) — the corpus tracked 5 of 18. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="5" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" s="5" t="inlineStr">
+        <is>
+          <t>draft-sato-soos-aop — The Agent Orchestration Protocol (AOP) for Agentic AI Systems</t>
+        </is>
+      </c>
+      <c r="C302" s="5" t="inlineStr">
+        <is>
+          <t>A single AI agent acting within a governed session is not the hardest governance problem. The hardest problem is what happens when that agent must delegate: when the mission is too large for one agent, when sub-tasks require specialized capability, when parallel execution is necessary, and when each delegated sub-agent is itself consequential enough to require governance. Who authorized the spawn? Who owns the plan? If the sub-agent deviates, who decides whether to re-plan or escalate? If the mission fails mid-execution, who constructs the audit record? This document defines the Agent Orchestration Protocol (AOP): the normative protocol through which a governed orchestrating agent decomposes a mission into a governed sub-goal directed acyclic graph (DAG), delegates sub-goals to sub-agents via kernel-mediated Assignment Primitives, and maintains a Mission Plan Sovereign Object (Mission Plan SO) and Mission Status SO across the full lifecycle of multi-agent execution. AOP specifies three core constructs: the Expected Outcome Declaration (EOD) as the pre-commitment structure for the full mission and each delegated sub-goal; the Mission Plan SO encoding the sub-goal DAG with SEQUENTIAL, PARALLEL, and CONDITIONAL dependency types; and the Assignment Primitive as the governed handoff mechanism that requires an Endorsed EOD and produces a Sub-Agent Composition Record (SACR) per the Multi-Agent Delegation protocol [I-D.sato-soos-mad]. AOP integrates with the Intent Declaration Primitive [I-D.sato-soos-idp] at each EOD boundary, the Agent Execution Protocol [I-D.sato-soos-aep] for per-agent session governance, the Governance Audit Record [I-D.sato-soos-gar] for mission lifecycle audit events (ALE-042 through ALE-055), and the Human Escalation Mechanism [I-D.sato-soos-hem] for re-planning authority escalation. The normative reference scenario for AOP is a three-tier emergency management orchestration system in which a Master AI orchestrates regional coordination agents, which orchestrate domain-specialist leaf agents (e.g., evacuation routing models), each tier operating under full SOOS governance. Further information: https://soosproject.ai/drafts/aop</t>
+        </is>
+      </c>
+      <c r="D302" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-sato-soos-aop/</t>
+        </is>
+      </c>
+      <c r="E302" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F302" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 30 Jun 2026. **Family completion, added 26 Aug 2026.** SOOS governance suite (Tom Sato, MyAuberge K.K.) — the corpus tracked 5 of 18. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="5" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" s="5" t="inlineStr">
+        <is>
+          <t>draft-sato-soos-cap — The Constitutional AI Protocol (CAP) for Agentic AI Systems</t>
+        </is>
+      </c>
+      <c r="C303" s="5" t="inlineStr">
+        <is>
+          <t>An AI agent's authorization system determines what it is permitted to do. A human principal's escalation decision determines what they authorize. Neither of these is sufficient on its own: a Cedar policy can permit market manipulation; a human principal can authorize fraud. Authorization systems answer the question "who decided?" The Constitutional AI Protocol answers a different question: "was that decision lawful?" CAP defines a Constitutional Layer that evaluates every AI action request and every human authorization decision against a three-tier prohibition model -- before Cedar evaluates the action and before the system executes the human's decision. Tier 0 prohibitions are derived from near-universal treaty consensus and are unconditional: no agent, operator, or human principal can authorize them. Tier 1 prohibitions are jurisdiction-specific and operator-declared. Tier 2 prohibitions are voluntary operator ethical standards. This document also specifies the Prohibition Clearance Mechanism (PCM): the process by which specific Tier 0 and Tier 1 prohibition classes may be cleared for specific deployment contexts -- either at implementation time by the operator or by formal regulatory authority -- while preserving an absolute prohibition floor for CSAM and genocide facilitation under any circumstances. The Sovereign Object OS (SOOS) is the reference implementation of the Governance Execution Controller (GEC) pattern on which CAP is built. CAP also defines the GEC Policy Transparency Disclosure (PTD): a signed, queryable, tier-structured document through which any external party may determine which laws and regulations a GEC is actively enforcing, at what authority tier, and under whose governance.</t>
+        </is>
+      </c>
+      <c r="D303" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-sato-soos-cap/</t>
+        </is>
+      </c>
+      <c r="E303" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F303" s="5" t="inlineStr">
+        <is>
+          <t>Revision -04, 30 Jun 2026. **Family completion, added 26 Aug 2026.** SOOS governance suite (Tom Sato, MyAuberge K.K.) — the corpus tracked 5 of 18. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="5" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" s="5" t="inlineStr">
+        <is>
+          <t>draft-sato-soos-cap-rrs — Constitutional AI Protocol -- Regulation Record Specification (CAP-RRS)</t>
+        </is>
+      </c>
+      <c r="C304" s="5" t="inlineStr">
+        <is>
+          <t>Compliance with applicable law should be a package import, not a Cedar authoring problem. The Constitutional AI Protocol (CAP) [I-D.sato-soos-cap] defines the enforcement architecture for governed AI agent systems: a three-tier Cedar policy evaluation model that distinguishes absolute prohibitions, jurisdictional legal constraints, operator policies, and resource limits. CAP specifies what the Governance Execution Controller (GEC) does when a Cedar policy fires. It does not specify how Cedar policies are authored, certified, distributed, or maintained as law changes. This document defines the Regulation Record: the structured representation of a compliance obligation at any CAP tier. A Regulation Record is the human-readable, machine-compilable intermediate form between legal text and Cedar policy. This document specifies the Regulation Record schema (Section 4), the Cedar Compilation Profile that governs how Regulation Records are translated into Cedar policies (Section 5), the conflict declaration model (Section 6), the certification model governing which publishers may certify records at each tier (Section 7), and the versioning and update protocol for the Constitutional Mandate Registry (Section 8). Version -02 adds the Law Reference Interface (LRI) generic model (Section 9), the Statute-Primacy Rule (Section 10), and the Operational Requirements for catalog amendment and interpretation detection (Section 11). These three additions complete the regulation lifecycle: from law encoding (Sections 4-8) through law reference and provenance (Section 9), through the consequences of law amendment (Section 10), through the operational cadence governing detection and response (Section 11). The core developer experience this document enables: a developer imports certified Regulation Record packages from the Constitutional Mandate Registry, declares their own Tier 2 operator policies and Tier 3 resource policies, calls compile(), and receives a Cedar policy set ready for GEC loading. No Cedar is authored by hand for compliance purposes. Compliance is a package management operation.</t>
+        </is>
+      </c>
+      <c r="D304" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-sato-soos-cap-rrs/</t>
+        </is>
+      </c>
+      <c r="E304" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F304" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 30 Jun 2026. **Family completion, added 26 Aug 2026.** SOOS governance suite (Tom Sato, MyAuberge K.K.) — the corpus tracked 5 of 18. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="5" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" s="5" t="inlineStr">
+        <is>
+          <t>draft-sato-soos-dam — The Data Artifact Management (DAM) Protocol for Agentic AI Systems</t>
+        </is>
+      </c>
+      <c r="C305" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies the Data Artifact Management (DAM) protocol for agentic AI systems governed by the Sovereign Object OS (SOOS) framework. DAM defines a typed taxonomy of data artifacts produced and consumed by AI agents, a governance envelope for each artifact type specifying provenance, access policy, temporal validity, and retention requirements, and the normative interface between agent- generated artifacts and the Governance Audit Record (GAR). DAM addresses three classes of data in agentic systems: kernel- generated artifacts (IDP event logs, GAR records, AEP session state), agent-generated artifacts (outputs of agent actions), and externally ingested artifacts (data made available by resources). DAM specifies the Data Artifact type (DA-Type) taxonomy referenced in the Resource Governance Protocol (RGP) and the Agent Execution Protocol (AEP). This document is a placeholder submission establishing the draft identifier and abstract. Full specification text will be submitted post-IETF 126 Vienna. Further information: https://soosproject.ai/drafts/dam</t>
+        </is>
+      </c>
+      <c r="D305" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-sato-soos-dam/</t>
+        </is>
+      </c>
+      <c r="E305" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F305" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 30 Jun 2026. **Family completion, added 26 Aug 2026.** SOOS governance suite (Tom Sato, MyAuberge K.K.) — the corpus tracked 5 of 18. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="5" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" s="5" t="inlineStr">
+        <is>
+          <t>draft-sato-soos-faip — The Federated Agent Intelligence Protocol (FAIP) for Agentic AI Systems</t>
+        </is>
+      </c>
+      <c r="C306" s="5" t="inlineStr">
+        <is>
+          <t>Every governed AI agent session ends with a record of what it tried, what was permitted, what was denied, and whether it succeeded. Across a single operator's deployment, these records feed behavioral trust scores. Across all operators, they are discarded. No protocol exists for pooling this behavioral intelligence without exposing the business logic, personal data, or operational details that make individual records sensitive. This document defines the Federated Agent Intelligence Protocol (FAIP): the Tier 3 analytics layer of the SOOS protocol family, specifying how aggregate behavioral intelligence is derived from governed agent Event Streams across participating operators, made available to agents and human principals, and protected through privacy-preserving aggregation, data residency controls, and k-anonymity enforcement. FAIP does not share individual session records. It does not expose any operator's proprietary data. It produces aggregate behavioral signal -- empirical, tamper-evident, distributed -- that no single participant can generate from their own data alone. FAIP is the first protocol specification for federated behavioral intelligence derived exclusively from cryptographically governed agent activity records. This document establishes the FAIP architecture, its relationship to the three-tier analytics model defined in [I-D.sato-soos-idp], its privacy and data residency framework, and the scope of subsequent FAIP specifications. Full protocol specification of FAIP query interfaces, federation topology, and aggregation algorithms is deferred to successor documents.</t>
+        </is>
+      </c>
+      <c r="D306" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-sato-soos-faip/</t>
+        </is>
+      </c>
+      <c r="E306" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F306" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 27 Jun 2026. **Family completion, added 26 Aug 2026.** SOOS governance suite (Tom Sato, MyAuberge K.K.) — the corpus tracked 5 of 18. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="5" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" s="5" t="inlineStr">
+        <is>
+          <t>draft-sato-soos-grp — The Governed Remediation Protocol (GRP) for Agentic AI Systems</t>
+        </is>
+      </c>
+      <c r="C307" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies the Governed Remediation Protocol (GRP) for agentic AI systems operating under the Sovereign Object OS (SOOS) framework. GRP defines the normative remediation action set available to a SOOS governance kernel when agent execution encounters a governed failure condition: FALLBACK (autonomous resource substitution), RETRY (bounded autonomous retry), ESCALATE (human escalation boundary), and ROLLBACK (reversible action undo). GRP specifies the conditions under which each action class may be taken autonomously and the boundaries at which Human Escalation Messaging (HEM) is required. GRP operates at the intersection of the Resource Governance Protocol (RGP), the Agent Execution Protocol (AEP), and the Human Escalation Mechanism (HEM), and normatively references the Governance Audit Record (GAR) for logging all remediation events. GRP adopts DEC-RGP-08 (the three-condition autonomous fallback test) verbatim from [I-D.sato-soos-rgp] as the normative FALLBACK action class boundary rule.</t>
+        </is>
+      </c>
+      <c r="D307" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-sato-soos-grp/</t>
+        </is>
+      </c>
+      <c r="E307" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F307" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 30 Jun 2026. **Family completion, added 26 Aug 2026.** SOOS governance suite (Tom Sato, MyAuberge K.K.) — the corpus tracked 5 of 18. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="5" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" s="5" t="inlineStr">
+        <is>
+          <t>draft-sato-soos-kia — Kernel Identity and Attestation for Governing Enforcement Components</t>
+        </is>
+      </c>
+      <c r="C308" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies the Kernel Identity and Attestation (KIA) protocol for the Sovereign Object OS (SOOS) governance architecture. KIA defines the cryptographic identity of the GEC, the trust chain anchoring kernel authority from hardware root through operator root keypair to every signed Event Log entry, the GEC Manifest schema for runtime state attestation, and the Revocation Registry maintenance requirements. KIA is the Layer 0 signing and attestation component on which the audit trail guarantees of draft-sato-soos-gar, the mandate enforcement guarantees of draft-sato-soos-mjwt, and the multi-agent delegation chain of draft-sato-soos-mad all depend. Version -03 adds FROST threshold signing for high-availability GEC keypair deployments, the Cross-Principal Identifier (XPID) for cross-instance federation audit correlation, the XPID cross- instance trust model, and four new Security Considerations (Sections 14.8 through 14.11) addressing FROST nonce reuse, XPID revocation gap, identity takeover via claimed identifier (CVE-2025- 13609 class), and attestation channel binding (CVE-2026-33697 class). This document is the reference specification for the KIA RATS WG presentation at IETF 126 Vienna. The XPID primitive and the CVE-2026-33697 attestation channel binding defense are the primary novel contributions presented to the RATS WG. Version -04 corrects a registry-format mismatch identified by IANA early review (#1456067): the Section 16 request to register XPID_DERIVED and XPID_VERIFICATION_FAILED into the GAR Authority Lifecycle Event Types Registry [I-D.sato-soos-gar] now uses that registry's actual column set (Event Type, Class, Reference) and assigns both entries the newly-defined Class ID (Identity/ Federation event). No new event types, fields, or normative behavior are introduced in -04; this is a registration-format correction only. Version -05 discloses a known open issue found by a WIMSE security review checklist dry-run against -03 (DR-MJWT-KIA-CHECKLIST-01, Finding 4): Section 6.3's Cross-Instance Trust Model verifies an XPID but does not restrict which federation participants can see the underlying Evidence in the first place. This is named as OQ-KIA-EVIDENCE-VIS (Sections 6.6, 14.4, 15.12), following the same acknowledge-rather-than-silently-omit pattern this document already uses for OQ-S-XPID-REV. No mechanism is specified in -05; resolution is deferred, consistent with how OQ-S-XPID-REV is treated.</t>
+        </is>
+      </c>
+      <c r="D308" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-sato-soos-kia/</t>
+        </is>
+      </c>
+      <c r="E308" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F308" s="5" t="inlineStr">
+        <is>
+          <t>Revision -05, 13 Aug 2026. **Family completion, added 26 Aug 2026.** SOOS governance suite (Tom Sato, MyAuberge K.K.) — the corpus tracked 5 of 18. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only. Highest-scoring single document in Flanagan's tracker that the corpus lacked (relevance 26).</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="5" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" s="5" t="inlineStr">
+        <is>
+          <t>draft-sato-soos-peer — Cross-Principal Agent Communication -- PEER Transaction Record</t>
+        </is>
+      </c>
+      <c r="C309" s="5" t="inlineStr">
+        <is>
+          <t>When two independently-principaled AI agents transact with each other, each operates under its own mandate root, its own Governed Execution Context (GEC), and its own audit chain. No shared kernel exists to mediate the exchange. Existing SOOS orchestration primitives (MAD, SACR) govern sub-agent relationships within one mandate tree; they do not address the peer case. This document defines the PEER protocol: a problem statement and architecture for cross-principal agent communication. PEER introduces the PEER Transaction Record (PTR) as a new first-class SOOS primitive providing a jointly-derived correlation artifact (ptxn_id) that links the two independent audit chains produced by a cross-principal transaction -- without requiring a neutral third party, shared kernel state, or cross-principal constitutional layer. This document is a problem statement and architecture draft. Normative ALE schemas, dispute resolution procedures, and full PTR field specifications are deferred to draft-sato-soos-peer-01 (post-Vienna).</t>
+        </is>
+      </c>
+      <c r="D309" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-sato-soos-peer/</t>
+        </is>
+      </c>
+      <c r="E309" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F309" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 30 Jun 2026. **Family completion, added 26 Aug 2026.** SOOS governance suite (Tom Sato, MyAuberge K.K.) — the corpus tracked 5 of 18. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="5" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" s="5" t="inlineStr">
+        <is>
+          <t>draft-sato-soos-pt — Progressive Trust (PT) for Agentic AI Governance Systems</t>
+        </is>
+      </c>
+      <c r="C310" s="5" t="inlineStr">
+        <is>
+          <t>When a new employee joins an organization, they begin with limited authority. As they demonstrate good judgment -- completing tasks reliably, asking for guidance at the right moments, recovering well when things go wrong -- they earn greater trust and, with it, greater authority. If their performance degrades, or if months pass without any demonstration, that trust diminishes. This is how human organizations manage authority over time. AI agents have no equivalent mechanism. Today, an AI agent's authority is declared once in a credential at issuance time and does not respond to its behavioral record. An agent that has completed 200 successful sessions with a proven track record holds the same credential as a newly deployed agent. The human principal who issued both credentials made a judgment at issuance time; nothing that happened since is reflected in the agent's authority. This document defines Progressive Trust (PT): a behavioral trust model for AI agents in which authority recommendations evolve in response to cryptographically verified evidence of actual performance. PT measures five behavioral properties: whether the agent's self-assessed confidence matches its actual outcomes; whether it asks for human oversight at the right moments; whether it achieves its goals; whether it avoids decisions it later has to reverse; and whether it adapts when its action is rejected. These measures are derived exclusively from the tamper-evident, GEC-signed Event Stream -- an agent cannot influence its PT Score except through actual governed behavior. PT does not grant authority automatically. It generates structured recommendations, backed by behavioral evidence, for human principal review and approval. Human principals decide whether to elevate or reduce an agent's authority. PT ensures that decision is informed rather than made in the absence of history. Progressive Trust is the longitudinal complement of the Agent Execution Protocol [I-D.sato-soos-aep]: AEP governs what an agent does within a session; PT measures what an agent has done across sessions and translates that history into structured authority recommendations. No equivalent specification exists in IETF, ISO, NIST, or any agentic AI governance standards body.</t>
+        </is>
+      </c>
+      <c r="D310" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-sato-soos-pt/</t>
+        </is>
+      </c>
+      <c r="E310" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F310" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 27 Jun 2026. **Family completion, added 26 Aug 2026.** SOOS governance suite (Tom Sato, MyAuberge K.K.) — the corpus tracked 5 of 18. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="5" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" s="5" t="inlineStr">
+        <is>
+          <t>draft-sato-soos-rgp — The Resource Governance Protocol (RGP) for Agentic AI Systems</t>
+        </is>
+      </c>
+      <c r="C311" s="5" t="inlineStr">
+        <is>
+          <t>An AI agent that can act on resources cannot be governed unless those resources declare what they can do, under what constraints, and at what trust level -- before the agent acts. Existing resource description standards (digital twin profiles, capability catalogs, API registries) provide no governance envelope: they declare capability but not compliance posture, trust attestation, or mandate-scope compatibility. An agent that proceeds without this information may assign tasks to resources that are outside its mandate, below its required trust threshold, or unable to satisfy its compliance obligations. This document specifies the Resource Governance Protocol (RGP): a two-stage discovery and declaration protocol by which physical resources, digital services, and AI model instances declare their capability class, trust level, operational constraints, and current availability state to a governed AI agent operating under a Mandate JWT [I-D.sato-soos-mjwt]. Stage 1 delivers a capability fingerprint via a well-known URI; Stage 2 delivers a full governance envelope for mandate-scope validation and Resource Map Sovereign Object construction. RGP defines eight capability classes (CAP-COMP through CAP-EXP), four trust levels (TRUST-0 through TRUST-3), a session-scoped Resource Map Sovereign Object, a three-condition autonomous fallback test, and normative integration with the Agent Execution Protocol [I-D.sato-soos-aep], the Governance Audit Record [I-D.sato-soos-gar], and the Human Escalation Mechanism [I-D.sato-soos-hem]. RGP also defines an AI Model Capability Declaration (RGP-Model) for the governance of AI model instances as first-class resources within a SOOS-governed deployment, and a Physical Resource Profile (RGP-Physical) for normative binding to existing digital twin standards.</t>
+        </is>
+      </c>
+      <c r="D311" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-sato-soos-rgp/</t>
+        </is>
+      </c>
+      <c r="E311" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F311" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 30 Jun 2026. **Family completion, added 26 Aug 2026.** SOOS governance suite (Tom Sato, MyAuberge K.K.) — the corpus tracked 5 of 18. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="5" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" s="5" t="inlineStr">
+        <is>
+          <t>draft-sato-soos-sov — The Sovereign Object (SOV) for Agentic AI Systems</t>
+        </is>
+      </c>
+      <c r="C312" s="5" t="inlineStr">
+        <is>
+          <t>When an AI agent acts on your behalf, it acts on something: a document, a booking, a contract, a financial instruction. No existing IETF specification defines what that something is, what states it can be in, who governs it, or how it is irreversibly erased when the relationship ends. Agentic AI governance protocols -- including intent declaration, human escalation, audit recording, and constitutional prohibition -- all require a normative definition of the governed resource that agents operate on: the structured, stateful, policy-carrying entity to which agent authority is bound and upon which governed transitions execute. No existing IETF specification defines this primitive. This document defines the Sovereign Object (SO): a causally ordered, policy-governed, typed, living document that evolves through a predefined finite state space under Governing Enforcement Component (GEC) authority. The SO is the unit of governance in the SOOS protocol family: the thing agents operate on, the GEC governs, and human principals reason about. This document specifies the SO's five-layer structure (Identity, State, Event Stream, Typed Graph, Attachment Index), its Zone A / Zone B boundary model, its five-phase lifecycle, its SO Type system, its Cedar policy context model, and the binding model by which a Mandate JWT binds an agent to a specific SO instance. Version -02 extends SOV-01 with: (a) SO Type registry governance including a SOV-02 subtype model for structured SO Type composition; (b) the Standing Plan Object (SPO) as a normative SOV-02 subtype, specifying declarative scope constraints, Cedar bundle reference, CAP-RRS catalog reference, and IDP structural validation integration; (c) the Mission Plan SO and Mission Status SO as normative SOV-02 subtypes for multi-agent orchestration over directed-acyclic-graph task structures; (d) event stream integrity normative requirements including GEC-signed append-only guarantees, kernel_id binding, and OpenTelemetry integration for observability bridging; (e) expanded Security Considerations addressing SO state manipulation, event stream tampering, SO Type spoofing, and stale state_constraint exploitation; and (f) IANA registrations for the SO Type code namespace and SPO media type. The Sovereign Object is the architectural foundation referenced normatively by [I-D.sato-soos-idp], [I-D.sato-soos-hem], [I-D.sato-soos-gar], [I-D.sato-soos-cap], and [I-D.sato-soos-mjwt].</t>
+        </is>
+      </c>
+      <c r="D312" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-sato-soos-sov/</t>
+        </is>
+      </c>
+      <c r="E312" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F312" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 30 Jun 2026. **Family completion, added 26 Aug 2026.** SOOS governance suite (Tom Sato, MyAuberge K.K.) — the corpus tracked 5 of 18. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="5" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" s="5" t="inlineStr">
+        <is>
+          <t>draft-schrock-ae-challenge — An Authorization Evidence Challenge for High-Risk Agent Actions</t>
+        </is>
+      </c>
+      <c r="C313" s="5" t="inlineStr">
+        <is>
+          <t>When a relying party refuses a consequential agent action because authorization evidence is missing, stale, or unverifiable, the agent needs a machine-readable description of what remains necessary. This document defines a transport-neutral Authorization Evidence Challenge data model bound to the relying party's exact action. The challenge identifies outstanding evidence requirements, freshness and status constraints, acceptable presentation profiles, and retry state. It authorizes nothing, transfers no admission ownership, and provides no promise that a later request will execute. The document also defines an HTTP challenge-response carrier using 403 Forbidden and RFC 9457 Problem Details, and describes an informative gateway-handoff illustration for DMSC-style federation. The gateway illustration communicates evidence requirements; it does not solve conserved admission or double-admission across independently operated gateways. A challenge can synchronize corrected retries and amplify load. The core therefore defines optional retry timing with per-challenge jitter, and the HTTP carrier maps its lower bound to Retry-After. Retry timing controls presentation attempts only; it does not authorize the action or make an uncertain action safe to repeat. Single-use processing also places state on the refusal path. The core therefore requires bounded outstanding and replay state, fail- closed behavior when state cannot be claimed, and retention of live replay records until they are no longer security-relevant. Nonce claim and refusal-path capacity reservation are one atomic owner-side transition before native evidence verification, and a binding capacity refusal reveals no remaining evidence requirements. In a sharded replay domain, only the authoritative owner can classify a nonce as already claimed; inability to reach that owner is unavailability, not replay.</t>
+        </is>
+      </c>
+      <c r="D313" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-ae-challenge/</t>
+        </is>
+      </c>
+      <c r="E313" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F313" s="5" t="inlineStr">
+        <is>
+          <t>Revision -07, 11 Aug 2026. **Family completion, added 26 Aug 2026.** EMILIA Protocol family (schrock-*) — evidence architecture for consequential agent actions; the corpus tracked 8 of 26. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="5" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" s="5" t="inlineStr">
+        <is>
+          <t>draft-schrock-agent-qualification-statements — Portable Agent Qualification Statements for Consequential Actions</t>
+        </is>
+      </c>
+      <c r="C314" s="5" t="inlineStr">
+        <is>
+          <t>Agent evaluations report what happened in a test environment. They do not, by themselves, establish that a measured candidate satisfies a relying party's policy, remains current, matches the runtime candidate, or is authorized to perform a consequential action. This document defines a portable Qualification Statement that binds a candidate, complete evaluation campaign, qualification policy, assignment, and status. It preserves three separate claims: observation, qualification, and authorization. A relying party can accept a current qualification as evidence at runtime, but MUST make a separate exact-action authorization and admission decision.</t>
+        </is>
+      </c>
+      <c r="D314" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-agent-qualification-statements/</t>
+        </is>
+      </c>
+      <c r="E314" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F314" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 28 Jul 2026. **Family completion, added 26 Aug 2026.** EMILIA Protocol family (schrock-*) — evidence architecture for consequential agent actions; the corpus tracked 8 of 26. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="5" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" s="5" t="inlineStr">
+        <is>
+          <t>draft-schrock-canonical-action-identifier — The Canonical Action Identifier (CAID)</t>
+        </is>
+      </c>
+      <c r="C315" s="5" t="inlineStr">
+        <is>
+          <t>Authorization, delegation, execution, and audit artifacts often identify an action using format-local content and digests. Those digests are not directly comparable when the formats select or encode material action fields differently. This document defines the Canonical Action IDentifier (CAID): a typed action object, a canonicalization and digest suite, a compact identifier string, and immutable action-type definitions with required material fields. It also defines an Action-Mapping Profile for projecting independently verified native artifacts into a common action type, with the closed results EQUIVALENT_UNDER_PROFILE, NOT_EQUIVALENT, and INDETERMINATE. CAID carries no trust semantics. It does not establish identity, authority, authorization, execution, safety, or legal reliance.</t>
+        </is>
+      </c>
+      <c r="D315" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-canonical-action-identifier/</t>
+        </is>
+      </c>
+      <c r="E315" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F315" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 7 Aug 2026. **Family completion, added 26 Aug 2026.** EMILIA Protocol family (schrock-*) — evidence architecture for consequential agent actions; the corpus tracked 8 of 26. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="5" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" s="5" t="inlineStr">
+        <is>
+          <t>draft-schrock-emilia-eye — Verifiable, Scope-Bound Advisories for Authorization Posture (EMILIA Eye)</t>
+        </is>
+      </c>
+      <c r="C316" s="5" t="inlineStr">
+        <is>
+          <t>This document defines the EMILIA Eye advisory: a scope-bound statement that an authorization posture for a named scope has changed (designed to be signed and offline-verifiable; the signing layer is specified here but is not yet present in the reference implementation, see Section 13.6), carrying a scope-binding hash that prevents the advisory from being replayed or re-targeted to a different scope. An Eye advisory expresses an observation-derived posture (clear, caution, elevated, or review_required) and a recommended action (none, log, step_up_auth, require_signoff, or escalate). The central safety invariant of this document is normative: an advisory MUST NEVER be the sole gate on an action. A signal may only TIGHTEN posture - it may cause an enforcement point to demand stronger authentication, human signoff, or escalation - but it can never itself constitute the authorization. Eye warns; an enforcement point verifies; an accountable human owns the decision. This work specifies the verifiability, scope-binding, and fail-safe advisory semantics that signal-transport frameworks leave undefined. It is a COMPOSABLE PROFILE: Eye advisories are carried as Security Event Token [RFC8417] payloads and MAY be transported over the OpenID Shared Signals Framework with Continuous Access Evaluation Profile (CAEP) events. It is complementary to, not a replacement for, SSF/ CAEP (which define signal shape and transport, not verifiable bound fail-safe advisory semantics), and it composes with the EP authorization receipt ([I-D.schrock-ep-authorization-receipts]), which remains the artifact that actually authorizes an action. This document is experimental.</t>
+        </is>
+      </c>
+      <c r="D316" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-emilia-eye/</t>
+        </is>
+      </c>
+      <c r="E316" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F316" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 26 Jun 2026. **Family completion, added 26 Aug 2026.** EMILIA Protocol family (schrock-*) — evidence architecture for consequential agent actions; the corpus tracked 8 of 26. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only. Note the slug: 'emilia-eye' rather than 'ep-', which is part of why name-substring discovery missed it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="5" t="n">
+        <v>316</v>
+      </c>
+      <c r="B317" s="5" t="inlineStr">
+        <is>
+          <t>draft-schrock-ep-architecture — The EMILIA Protocol: An Evidence Architecture for Consequential Agent Actions</t>
+        </is>
+      </c>
+      <c r="C317" s="5" t="inlineStr">
+        <is>
+          <t>Consequential agent actions can cross operator and administrative boundaries. The party that later decides whether to rely on an action record may not have participated in the interaction and may not trust either operator. This document describes an evidence architecture for that case. It separates transport and workload identity, delegation and policy, material action identity, authorization evidence, evidence satisfaction, local authorization, durable consumption or reservation, effect invocation, outcome evidence, revocation, and preservation. The architecture composes the Canonical Action Identifier (CAID), Authorization Evidence Chain (AEC), and Action Evidence Boundary (AEB) with optional staged-approval and consequence-control profiles. It does not define a universal token, policy language, execution engine, settlement network, or distributed consensus system. A valid signature, a current credential, a satisfied evidence requirement, and an observed effect remain different facts.</t>
+        </is>
+      </c>
+      <c r="D317" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-architecture/</t>
+        </is>
+      </c>
+      <c r="E317" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F317" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 22 Jul 2026. **Family completion, added 26 Aug 2026.** EMILIA Protocol family (schrock-*) — evidence architecture for consequential agent actions; the corpus tracked 8 of 26. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only. The architecture document for the EMILIA Protocol family — the root the other schrock-ep-* drafts hang off, and the one that should have been added first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="5" t="n">
+        <v>317</v>
+      </c>
+      <c r="B318" s="5" t="inlineStr">
+        <is>
+          <t>draft-schrock-ep-authority-introduction — Authority Documents and Scoped Authority for Agent-Action Evidence</t>
+        </is>
+      </c>
+      <c r="C318" s="5" t="inlineStr">
+        <is>
+          <t>Signature verification answers whether a key produced an artifact. It does not answer why a relying party accepts that key, or whether the key holder had authority for the action. This document specifies two composable artifacts. An Authority Document introduces and rotates an organization's evidence-issuing keys through a signed, hash-chained sequence. A Scoped Authority Proof records the authority held by a subject at a registry snapshot, including role, action scope, material limits, policy binding, validity, and revocation status. A relying party evaluates both artifacts under its own pinned trust inputs and policy. The design does not make a self-presented key authoritative, does not turn log inclusion or domain control into automatic trust, and does not equate a valid signature with permission to act. It also defines a source- resolution boundary: signing a statement does not give its underlying source data finer freshness or precision than that source actually provides.</t>
+        </is>
+      </c>
+      <c r="D318" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-authority-introduction/</t>
+        </is>
+      </c>
+      <c r="E318" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F318" s="5" t="inlineStr">
+        <is>
+          <t>Revision -03, 4 Aug 2026. **Family completion, added 26 Aug 2026.** EMILIA Protocol family (schrock-*) — evidence architecture for consequential agent actions; the corpus tracked 8 of 26. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="5" t="n">
+        <v>318</v>
+      </c>
+      <c r="B319" s="5" t="inlineStr">
+        <is>
+          <t>draft-schrock-ep-bounded-execution-program — Bounded Execution Programs for Consequential Agent Actions</t>
+        </is>
+      </c>
+      <c r="C319" s="5" t="inlineStr">
+        <is>
+          <t>An authorization for one action does not by itself authorize an open- ended agent plan. This document defines an Experimental profile for a signed, finite, versioned directed acyclic graph of consequential action occurrences. The program binds a total retained-history ceiling. Each node binds an exact action or a pinned action-matching profile, an action- specific Trust Program, outcome-specific dependencies, an occurrence ceiling, and fixed charges against aggregate attempt budgets. A conforming program-aware admission store evaluates reachability and budgets in the same linearizable transaction domain as the ordinary one-time execution right. It uses store-owned authorizer trust roots, clock, authenticated profile-match verification, and current program status; seals a deterministic execution-program resource into the AdmissionSnapshot; and fences the program's independent authorization digest against ordinary-path admission. The profile does not establish that natural-language intent was understood, that a plan is safe or lawful, that provider or effect evidence is true, or that every mutation path was mediated.</t>
+        </is>
+      </c>
+      <c r="D319" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-bounded-execution-program/</t>
+        </is>
+      </c>
+      <c r="E319" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F319" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 3 Aug 2026. **Family completion, added 26 Aug 2026.** EMILIA Protocol family (schrock-*) — evidence architecture for consequential agent actions; the corpus tracked 8 of 26. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="5" t="n">
+        <v>319</v>
+      </c>
+      <c r="B320" s="5" t="inlineStr">
+        <is>
+          <t>draft-schrock-ep-outcome-binding — Outcome Binding for Authorized Actions and Independently Observed Effects</t>
+        </is>
+      </c>
+      <c r="C320" s="5" t="inlineStr">
+        <is>
+          <t>Authorization proves what action was permitted; it does not prove what happened after execution. An executor-signed result improves attribution but remains a claim by the party that acted. This document specifies a source-routed Outcome Binding profile. Signed predicted effects identify the source role and source class required to evaluate each predicate. Executors, systems of record, and independent observers sign closed observation objects bound to the same authorization, action digest, Canonical Action Identifier, consumption nonce, operation, facility, and observation window. A deterministic verifier separates evidence availability from comparison: missing or unauthenticated required sources yield an indeterminate lifecycle state; authentic observations yield the closed comparison result in_bounds, divergent, or incomparable. The profile improves consequence reconciliation without claiming physical truth, sensor correctness, or legal finality.</t>
+        </is>
+      </c>
+      <c r="D320" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-outcome-binding/</t>
+        </is>
+      </c>
+      <c r="E320" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F320" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 29 Jul 2026. **Family completion, added 26 Aug 2026.** EMILIA Protocol family (schrock-*) — evidence architecture for consequential agent actions; the corpus tracked 8 of 26. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="5" t="n">
+        <v>320</v>
+      </c>
+      <c r="B321" s="5" t="inlineStr">
+        <is>
+          <t>draft-schrock-ep-presentation-binding — Presentation Binding for Human-Authorization Receipts: Proving the Human Approved What They Saw</t>
+        </is>
+      </c>
+      <c r="C321" s="5" t="inlineStr">
+        <is>
+          <t>A human-authorization receipt proves a named person produced a user- verified signature over a digest that commits to an exact action. It does not prove the surface that person signed on DISPLAYED that action honestly. If a signing interface shows a benign summary while committing a different action, the resulting receipt is laundered authority: cryptographically valid and semantically false, which is worse than no receipt at all. This is the presentation attack, and it is the deepest unsolved problem in authorization evidence, because a signature cannot attest to pixels. This document narrows the gap with two additive, offline-checkable pieces that touch no existing receipt format: a DETERMINISTIC RENDERER, a pure function from the canonical action to a byte-identical human-readable rendering, so a verifier RE-DERIVES the rendering from the signed bytes and rejects any surface that showed something else; and a DISPLAY ATTESTATION, a signed claim by the signing client binding the rendering it showed to the action it committed. Neither eliminates the presentation attack (nothing purely digital can), but together they convert "trust the vendor's UI" into "verify the rendering was the honest function of the signed action," and they make the residual risk explicit rather than hidden.</t>
+        </is>
+      </c>
+      <c r="D321" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-presentation-binding/</t>
+        </is>
+      </c>
+      <c r="E321" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F321" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 3 Jul 2026. **Family completion, added 26 Aug 2026.** EMILIA Protocol family (schrock-*) — evidence architecture for consequential agent actions; the corpus tracked 8 of 26. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="5" t="n">
+        <v>321</v>
+      </c>
+      <c r="B322" s="5" t="inlineStr">
+        <is>
+          <t>draft-schrock-ep-reliance-agreement — Reliance Agreements: Signed Liability Terms Conditioned on Authorization-Evidence Sufficiency</t>
+        </is>
+      </c>
+      <c r="C322" s="5" t="inlineStr">
+        <is>
+          <t>This document defines EP-RELIANCE-AGREEMENT-v1, a signed, machine- readable statement of terms conditioned on a specific relying-party evidence profile, and EP-RELIANCE-EVENT-v1, a signed per-action record joining one action, one reliance result, and one agreement. The agreement references the evidence condition by digest rather than restating or weakening it. Every required party signs the same canonical bytes, and monetary amounts are represented as decimal strings. Verification establishes signatures, content integrity, scope, time, and digest bindings. It does not authorize an action, re-evaluate the evidence packet, establish legal enforceability, issue insurance, determine coverage, allocate fault, prove solvency, reserve funds, or compel payment. Those decisions remain with the relying party and the applicable prose agreement, law, and dispute forum.</t>
+        </is>
+      </c>
+      <c r="D322" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-reliance-agreement/</t>
+        </is>
+      </c>
+      <c r="E322" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F322" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 3 Aug 2026. **Family completion, added 26 Aug 2026.** EMILIA Protocol family (schrock-*) — evidence architecture for consequential agent actions; the corpus tracked 8 of 26. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="5" t="n">
+        <v>322</v>
+      </c>
+      <c r="B323" s="5" t="inlineStr">
+        <is>
+          <t>draft-schrock-ep-revocation-statement — Portable Revocation Statements for Action-Bound Authorization Artifacts</t>
+        </is>
+      </c>
+      <c r="C323" s="5" t="inlineStr">
+        <is>
+          <t>Signed authorization artifacts for agent actions (receipts, commits, delegations) are being defined faster than the means to retract them. Many deployed systems use live status services, revocation lists, or issuer datastores. This document defines a complementary portable form for action-bound authorization artifacts: a signed, offline- verifiable claim that a named logical target, addressed by identifier and action commitment, is revoked. Verification is fail-closed and evaluates a fixed set of checks: version, closed object structure, target binding, a revoker key pinned by the verifier and, for newly emitted artifacts, bound to a full digest-derived key identifier (a self-asserted key confers nothing), the presence of a strict revocation instant that has taken effect by the verifier's decision time, and an independently recomputed signature. The statement proves that a named, pinned revoker revoked this specific target. It does not prove that every relying party saw it, and offline verification cannot prove the absence of a revocation that was not presented. A terminal revocation never ages out; current non- revocation requires separate authenticated, policy-fresh status evidence. A Trust Program profile binds revocation to the complete execution claim, and requires revocation-versus-claim to be resolved atomically; a revocation learned after a claim never rewrites an effect that may already have occurred.</t>
+        </is>
+      </c>
+      <c r="D323" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-ep-revocation-statement/</t>
+        </is>
+      </c>
+      <c r="E323" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F323" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 28 Jul 2026. **Family completion, added 26 Aug 2026.** EMILIA Protocol family (schrock-*) — evidence architecture for consequential agent actions; the corpus tracked 8 of 26. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="5" t="n">
+        <v>323</v>
+      </c>
+      <c r="B324" s="5" t="inlineStr">
+        <is>
+          <t>draft-schrock-kintzele-grid-curtailment — GRACE: Evidence-Bound Grid Curtailment Admission, Observation, and Single-Use Settlement</t>
+        </is>
+      </c>
+      <c r="C324" s="5" t="inlineStr">
+        <is>
+          <t>This document defines GRACE, an application profile for one bounded grid.curtailment action. The profile binds an exact action to a finite participation envelope, distinct human approvals when required, one-attempt executor admission, an authenticated actuator acknowledgment, separately authenticated meter observations, an Action State Signed Statement, and one-time admission to a settlement effect. Missing or ambiguous post-invocation evidence is preserved as indeterminate and cannot authorize blind retry. GRACE verifies signed inputs and deterministic computations. It does not establish physical meter truth, baseline correctness, tariff eligibility, actual payment, complete mediation, or a physical grid deployment. An optional hybrid artifact-signature profile combines Ed25519 with ML-DSA-65 and requires both signatures to verify.</t>
+        </is>
+      </c>
+      <c r="D324" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-kintzele-grid-curtailment/</t>
+        </is>
+      </c>
+      <c r="E324" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F324" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 22 Aug 2026. **Family completion, added 26 Aug 2026.** EMILIA Protocol family (schrock-*) — evidence architecture for consequential agent actions; the corpus tracked 8 of 26. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="5" t="n">
+        <v>324</v>
+      </c>
+      <c r="B325" s="5" t="inlineStr">
+        <is>
+          <t>draft-schrock-model-to-matter — Model-to-Matter: Authorization and Outcome Evidence for Model-Directed Physical Execution</t>
+        </is>
+      </c>
+      <c r="C325" s="5" t="inlineStr">
+        <is>
+          <t>Advanced models can propose operations that produce physical effects. Model-to-Matter defines an executor-owned profile that composes model, safety, institutional, domain, screening, human, and physical- state attestation evidence over one canonical action before single- use execution. This revision also profiles post-execution Outcome Binding. An executor effect statement remains one source claim; required independent observers sign separately bound observations. Missing outcome evidence is indeterminate, not success or failure. The profile standardizes evidence custody and reconciliation; it does not perform screening, determine scientific safety, certify a facility, or establish physical truth.</t>
+        </is>
+      </c>
+      <c r="D325" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-schrock-model-to-matter/</t>
+        </is>
+      </c>
+      <c r="E325" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F325" s="5" t="inlineStr">
+        <is>
+          <t>Revision -04, 7 Aug 2026. **Family completion, added 26 Aug 2026.** EMILIA Protocol family (schrock-*) — evidence architecture for consequential agent actions; the corpus tracked 8 of 26. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="5" t="n">
+        <v>325</v>
+      </c>
+      <c r="B326" s="5" t="inlineStr">
+        <is>
+          <t>draft-sharif-aeba — Agent Event Behaviour Analysis (AEBA): A Framework for Behavioural Security Monitoring of Autonomous AI Agents</t>
+        </is>
+      </c>
+      <c r="C326" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies Agent Event Behaviour Analysis (AEBA), a framework for collecting, signing, exchanging, and analysing behavioural events produced by autonomous AI agents. AEBA is the agent-domain equivalent of User and Entity Behaviour Analytics (UEBA) as commonly deployed in enterprise Security Operations Centres. It defines a canonical event schema, signature binding to agent identity, baseline and peer-group exchange protocols, deviation signalling, detection rule structure, revocation mechanisms, and interoperability bindings for existing Security Information and Event Management (SIEM) event formats (syslog, CEF, LEEF). The framework is designed to compose with existing cryptographic primitives for agent identity, payment, and transport security, and to support cross-framework deployments in which agents produced by different runtimes must share a common behavioural observability surface.</t>
+        </is>
+      </c>
+      <c r="D326" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-sharif-aeba/</t>
+        </is>
+      </c>
+      <c r="E326" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F326" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 15 Apr 2026. **Family completion, added 26 Aug 2026.** Sharif — crossed into a multi-draft body of work; the corpus tracked 4 of 10. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="5" t="n">
+        <v>326</v>
+      </c>
+      <c r="B327" s="5" t="inlineStr">
+        <is>
+          <t>draft-sharif-ai-model-lifecycle-attestation — Cryptographic Attestation for AI Model Lifecycle: From Training Data to Inference Output</t>
+        </is>
+      </c>
+      <c r="C327" s="5" t="inlineStr">
+        <is>
+          <t>This document defines a cryptographic attestation framework for the complete lifecycle of artificial intelligence models, from training data provenance through model weight signing, quantization verification, deployment attestation, and per- inference output signing. The framework creates an unbroken chain of cryptographic evidence binding each inference output to the specific model version, training data, and deployment configuration that produced it. The framework uses ECDSA P-256 digital signatures, SHA-256 hash functions, Merkle trees for corpus attestation, and JSON Web Key Sets (JWKS) for key discovery. It addresses documented threats including model distillation attacks, quantization poisoning, training data manipulation, silent model degradation, and inference output tampering. This specification complements the Agent Trust Transport Protocol (ATTP) [draft-sharif-attp-agent-trust-transport], MCPS message signing [draft-sharif-mcps-secure-mcp], and the Agent Audit Trail format [draft-sharif-agent-audit-trail] to provide end-to- end cryptographic verification from data ingestion to consumer delivery.</t>
+        </is>
+      </c>
+      <c r="D327" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-sharif-ai-model-lifecycle-attestation/</t>
+        </is>
+      </c>
+      <c r="E327" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F327" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 31 Mar 2026. **Family completion, added 26 Aug 2026.** Sharif — crossed into a multi-draft body of work; the corpus tracked 4 of 10. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="5" t="n">
+        <v>327</v>
+      </c>
+      <c r="B328" s="5" t="inlineStr">
+        <is>
+          <t>draft-sharif-apki-agent-pki — Agent Public Key Infrastructure (APKI): Certificate-Based Identity and Trust for Autonomous AI Agents</t>
+        </is>
+      </c>
+      <c r="C328" s="5" t="inlineStr">
+        <is>
+          <t>Autonomous artificial intelligence (AI) agents are increasingly performing actions on the Internet that require verifiable identity: financial transactions, regulated data access, tool invocations, and inter-agent coordination. Traditional Public Key Infrastructure (PKI) based on X.509 certificates was designed for human-operated clients and long-lived servers. It lacks primitives for graduated trust scoring, capability constraints, delegation chains, model provenance, and the ephemeral lifecycles characteristic of AI agents. This document defines Agent Public Key Infrastructure (APKI), a certificate-based identity and trust system for autonomous AI agents. APKI extends X.509v3 with five agent-specific extensions, defines the agent:// URI scheme for agent identification, specifies Agent Transparency Logs modelled on Certificate Transparency (RFC 9162), and provides mechanisms for cross-organizational trust federation. APKI is designed to be compatible with existing PKI deployments, SPIFFE workload identity, and the IETF WIMSE working group's specifications.</t>
+        </is>
+      </c>
+      <c r="D328" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-sharif-apki-agent-pki/</t>
+        </is>
+      </c>
+      <c r="E328" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F328" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 10 Apr 2026. **Family completion, added 26 Aug 2026.** Sharif — crossed into a multi-draft body of work; the corpus tracked 4 of 10. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="5" t="n">
+        <v>328</v>
+      </c>
+      <c r="B329" s="5" t="inlineStr">
+        <is>
+          <t>draft-sharif-attp-agent-trust-transport — ATTP: Agent Trust Transport Protocol for Secure Agent-to-Server Communication</t>
+        </is>
+      </c>
+      <c r="C329" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies ATTP (Agent Trust Transport Protocol), a synchronous request-response protocol for communication between autonomous AI agents and web API servers. ATTP operates as an application-layer protocol over HTTP, adding mandatory cryptographic identity verification, per-message signing, trust-gated access control, and tamper-evident audit trail generation to every agent-server interaction. ATTP defines five protocol-layer headers for requests (X-Agent-Trust, X-Agent-Signature, X-Agent-Nonce, X-Agent-Timestamp, X-ATTP-Version) and three for responses (X-Server-Signature, X-Server-Nonce, X-Server-Timestamp) that carry an Agent Passport (JWT-based identity credential), ECDSA P-256 digital signatures, cryptographic nonces, and timestamps. Server middleware verifies all cryptographic properties before application code executes. ATTP has no insecure mode. Every request MUST carry a valid Agent Passport. Every request body MUST be signed. Every response body MUST be signed. Every interaction MUST be recorded in a hash-chained audit trail. The protocol defines a URL scheme (attp://) and is fully backward-compatible with existing HTTP infrastructure. ATTP is the synchronous counterpart to the Agent Transport Protocol (ATP). ATP handles asynchronous store-and-forward agent delivery; ATTP handles real-time request-response API communication. Both share the same identity model, trust framework, and cryptographic primitives.</t>
+        </is>
+      </c>
+      <c r="D329" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-sharif-attp-agent-trust-transport/</t>
+        </is>
+      </c>
+      <c r="E329" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F329" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 30 Mar 2026. **Family completion, added 26 Aug 2026.** Sharif — crossed into a multi-draft body of work; the corpus tracked 4 of 10. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="5" t="n">
+        <v>329</v>
+      </c>
+      <c r="B330" s="5" t="inlineStr">
+        <is>
+          <t>draft-sharif-attp-industrial-control-systems — ATTP for Industrial Control Systems: Cryptographic Agent Authentication in SCADA and IoT Environments</t>
+        </is>
+      </c>
+      <c r="C330" s="5" t="inlineStr">
+        <is>
+          <t>This document defines an application profile of the Agent Trust Transport Protocol (ATTP) [draft-sharif-attp-agent-trust-transport] for use in Industrial Control Systems (ICS), Supervisory Control and Data Acquisition (SCADA) environments, and Internet of Things (IoT) deployments. It specifies how ATTP mandatory message signing, agent identity passports, and trust-gated access control apply to industrial protocols including Modbus/TCP, OPC UA, MQTT, and CoAP. The profile addresses the absence of per-message authentication in legacy industrial protocols, which has been exploited in numerous critical infrastructure attacks. It defines a gateway architecture that enables ATTP protection for legacy devices without firmware modification, maps ATTP trust levels to IEC 62443 Security Levels, and specifies real-time revocation mechanisms suitable for safety-critical environments.</t>
+        </is>
+      </c>
+      <c r="D330" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-sharif-attp-industrial-control-systems/</t>
+        </is>
+      </c>
+      <c r="E330" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F330" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 31 Mar 2026. **Family completion, added 26 Aug 2026.** Sharif — crossed into a multi-draft body of work; the corpus tracked 4 of 10. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="5" t="n">
+        <v>330</v>
+      </c>
+      <c r="B331" s="5" t="inlineStr">
+        <is>
+          <t>draft-sharif-openid-agent-identity — OpenID Connect Agent Identity Claims for Autonomous AI Agents</t>
+        </is>
+      </c>
+      <c r="C331" s="5" t="inlineStr">
+        <is>
+          <t>This specification defines a profile of OpenID Connect Core 1.0 that enables Identity Providers (IdPs) to issue identity tokens for autonomous software agents. It introduces a set of standard claims for representing agent identity, ownership, trust posture, authorised capabilities, and compliance screening status within OpenID Connect ID Tokens. The profile is designed to operate within existing OpenID Connect infrastructure without requiring modifications to the core protocol. It defines how Relying Parties (RPs) validate agent tokens and enforce graduated access controls based on agent trust levels and sanctions screening results.</t>
+        </is>
+      </c>
+      <c r="D331" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-sharif-openid-agent-identity/</t>
+        </is>
+      </c>
+      <c r="E331" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F331" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 26 Mar 2026. **Family completion, added 26 Aug 2026.** Sharif — crossed into a multi-draft body of work; the corpus tracked 4 of 10. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
         </is>
       </c>
     </row>
@@ -8947,6 +11167,80 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D255" r:id="rId254"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D256" r:id="rId255"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D331" r:id="rId330"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/delegated_authorization_research.xlsx
+++ b/delegated_authorization_research.xlsx
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="6" t="n">
-        <v>547</v>
+        <v>566</v>
       </c>
       <c r="D12" s="7" t="n"/>
     </row>
@@ -966,7 +966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F331"/>
+  <dimension ref="A1:F350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10906,6 +10906,576 @@
       <c r="F331" s="5" t="inlineStr">
         <is>
           <t>Revision -00, 26 Mar 2026. **Family completion, added 26 Aug 2026.** Sharif — crossed into a multi-draft body of work; the corpus tracked 4 of 10. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="5" t="n">
+        <v>331</v>
+      </c>
+      <c r="B332" s="5" t="inlineStr">
+        <is>
+          <t>draft-lundholm-kaif — The Kindred Agent Identity Framework (KAIF)</t>
+        </is>
+      </c>
+      <c r="C332" s="5" t="inlineStr">
+        <is>
+          <t>The Kindred Agent Identity Framework (KAIF) is an OAuth 2.0 token exchange mechanism for delegated agent-to-service authorization, combining RFC 8693 token exchange with SPIFFE workload identity attestation and operator-assigned authorization tiers. This document specifies the protocol mechanics, deployment profiles, and interoperability requirements for systems implementing agent authorization with audit accountability. KAIF is intended for scenarios in which an operator (human principal) provisionally authorizes an agent (automated workload) to perform bounded actions on their behalf, with cryptographic proof of authorization, delegation depth tracking, and revocation in real time. This document is intentionally vendor-neutral in its normative requirements. Cloud platforms, model providers, workflow systems, and audit backends discussed by implementations are informative deployment examples, not part of the KAIF wire protocol.</t>
+        </is>
+      </c>
+      <c r="D332" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-lundholm-kaif/</t>
+        </is>
+      </c>
+      <c r="E332" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F332" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 20 Jul 2026. **Added 26 Aug 2026 from Heather Flanagan's standards-tracker cross-check** (her bucket: read_now, category: authorization, relevance 22) — a new author not previously tracked here. Highest-scoring new-author draft in Flanagan's tracker (relevance 22). A full agent identity *framework*, so read it against the four colliding 'AIP' drafts and draft-singla-agent-identity-protocol rather than as a point mechanism.</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="5" t="n">
+        <v>332</v>
+      </c>
+      <c r="B333" s="5" t="inlineStr">
+        <is>
+          <t>draft-burls-mtac — Merkle Tree Agent Certificates (MTAC): Batch-Issued Post-Quantum Identity Credentials for AI Agents</t>
+        </is>
+      </c>
+      <c r="C333" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies Merkle Tree Agent Certificates (MTAC), a credential format and issuance profile in which a certificate authority commits a batch of AI agent identity credentials to a Merkle tree, signs only the tree head with the post-quantum signature algorithm ML-DSA-65, and distributes a per-credential inclusion proof. A relying party verifies a credential offline against the signed tree head without contacting the issuer. Each batch root is additionally co-signed by an independently keyed witness, providing per-batch integrity and continuity attestation, and its root can be corroborated against an independent public record. MTAC defines the leaf structure, its deterministic encoding, the leaf hash preimage, the signed tree head wire format, the witness co- signature, and an optional challenge-response proof of possession that binds a credential to a holder key. Test vectors are provided. This document specifies a credential issuance and verification mechanism. Declared scopes carried in a credential are self-reported parameters recorded at issuance; this document does not specify a runtime authorization mechanism.</t>
+        </is>
+      </c>
+      <c r="D333" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-burls-mtac/</t>
+        </is>
+      </c>
+      <c r="E333" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F333" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 21 Jul 2026. **Added 26 Aug 2026 from Heather Flanagan's standards-tracker cross-check** (her bucket: read_now, category: authorization, relevance 18) — a new author not previously tracked here. Batch-issued post-quantum credentials for agents — the only draft in the corpus combining PQC with agent identity issuance at scale. Adjacent to the Vauban x402 PQC pair still held out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="5" t="n">
+        <v>333</v>
+      </c>
+      <c r="B334" s="5" t="inlineStr">
+        <is>
+          <t>draft-mpsb-agntcy-messaging — An Overview of Messaging Systems and Their Applicability to Agentic AI</t>
+        </is>
+      </c>
+      <c r="C334" s="5" t="inlineStr">
+        <is>
+          <t>Agentic AI systems require messaging infrastructure that supports real-time collaboration, high-volume streaming, and dynamic group coordination across distributed networks. Traditional protocols like AMQP [AMQP], MQTT [MQTT], and NATS [NATS] address some requirements but fall short on security, particularly regarding post-compromise protection and forward secrecy essential for autonomous agents handling sensitive data. This document analyzes six messaging protocols—AMQP, MQTT, NATS, AMQP over WebSockets, Kafka, and AGNTCY SLIM—across dimensions critical for GenAI agent systems: streaming performance, delivery guarantees, security models, and operational complexity. We examine how each protocol's design decisions impact agentic AI deployments, from lightweight edge computing scenarios to large-scale multi- organizational collaborations. AGNTCY SLIM emerges as a purpose-built solution, integrating Message Layer Security (MLS) [RFC9420] with gRPC [gRPC] over HTTP/2 [RFC9113] to provide end-to-end encryption with forward secrecy, efficient streaming, and OAuth-based authentication [RFC6749]. Unlike transport-layer security approaches, SLIM's MLS implementation ensures secure communication even through untrusted intermediaries while supporting dynamic group membership changes essential for collaborative AI agents.</t>
+        </is>
+      </c>
+      <c r="D334" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-mpsb-agntcy-messaging/</t>
+        </is>
+      </c>
+      <c r="E334" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F334" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 19 Jul 2026. **Added 26 Aug 2026 from Heather Flanagan's standards-tracker cross-check** (her bucket: read_now, category: agent_identity, relevance 14) — a new author not previously tracked here. Survey of messaging substrates for agentic AI; useful orientation for the transport half of the discovery-and-transport cluster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="5" t="n">
+        <v>334</v>
+      </c>
+      <c r="B335" s="5" t="inlineStr">
+        <is>
+          <t>draft-bandyopadhayaya-oauth-ciba-push-binding — CIBA Binding for OAuth Push-Based Authentication Device Discovery</t>
+        </is>
+      </c>
+      <c r="C335" s="5" t="inlineStr">
+        <is>
+          <t>A companion specification, "Discovery and Device Lifecycle for OAuth Push-Based Authentication", defines a generic, back-channel-protocol- agnostic device registration, attestation, and lifecycle layer for out-of-band OAuth 2.0 authenticator devices. This document is the thin binding that lets a device registered under that specification be woken by OpenID Connect Client-Initiated Backchannel Authentication (CIBA) Core's authorization endpoint: one request parameter, one additive error code, and a statement of how CIBA's existing binding_message composes with the base document's interaction-type ceremony. This document adds no new endpoints and no new discovery fields of its own.</t>
+        </is>
+      </c>
+      <c r="D335" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-bandyopadhayaya-oauth-ciba-push-binding/</t>
+        </is>
+      </c>
+      <c r="E335" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F335" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 29 Jul 2026. **Added 26 Aug 2026 from Heather Flanagan's standards-tracker cross-check** (her bucket: read_now, category: authorization, relevance 14) — a new author not previously tracked here. CIBA binding for push-based authentication device discovery. Relevant because CIBA keeps being proposed and rejected as the agent-approval primitive — McGuinness's ARAP framing argues CIBA solves authentication freshness, not governance state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="5" t="n">
+        <v>335</v>
+      </c>
+      <c r="B336" s="5" t="inlineStr">
+        <is>
+          <t>draft-bandyopadhayaya-oauth-push-device — Discovery and Device Lifecycle for OAuth Push-Based Authentication</t>
+        </is>
+      </c>
+      <c r="C336" s="5" t="inlineStr">
+        <is>
+          <t>This document defines a discovery, registration, attestation, and device-lifecycle layer for out-of-band OAuth 2.0 authenticator devices, allowing a single spec-compliant authenticator application to register with, and receive push-based wake signals from, any conforming Authorization Server, without requiring the Authorization Server operator to build and distribute its own dedicated mobile application. This document is intentionally agnostic to which back- channel authentication protocol ultimately consumes it; OpenID Connect Client-Initiated Backchannel Authentication (CIBA) Core is its first binding, defined in a separate companion document, but nothing in this document depends on CIBA or on OpenID Connect.</t>
+        </is>
+      </c>
+      <c r="D336" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-bandyopadhayaya-oauth-push-device/</t>
+        </is>
+      </c>
+      <c r="E336" s="5" t="inlineStr">
+        <is>
+          <t>IETF (OAuth-related, individual)</t>
+        </is>
+      </c>
+      <c r="F336" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 29 Jul 2026. **Added 26 Aug 2026 from Heather Flanagan's standards-tracker cross-check** (her bucket: read_now, category: authorization, relevance 14) — a new author not previously tracked here. Companion to the CIBA push-binding draft above; device lifecycle and discovery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="5" t="n">
+        <v>336</v>
+      </c>
+      <c r="B337" s="5" t="inlineStr">
+        <is>
+          <t>draft-foroughi-agent-protocol-dimensions — A Dimensional Model for Characterizing AI Agent Protocol Proposals and Their Substrates</t>
+        </is>
+      </c>
+      <c r="C337" s="5" t="inlineStr">
+        <is>
+          <t>Discussions about agent protocols are frequently muddied by overloaded terms; asks such as "we need a session protocol" or "we need cross-domain support" bundle several distinct concerns across transport, agent protocol, and orchestration layers. This document offers a dimensional model that routes each concern to its proper layer. The document defines a small set of protocol-visible dimensions for characterizing AI agent protocol interactions and applies them to representative agentic protocol proposals (A2A, MCP, and the ACP invocation surface of the AGNTCY stack) alongside their substrate bindings, making explicit which dimensions each proposal owns at the protocol layer and which it inherits from its substrate. The document does not rank proposals and does not prescribe an architecture. It is standalone: it neither depends on nor prescribes any use-case or requirements document.</t>
+        </is>
+      </c>
+      <c r="D337" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-foroughi-agent-protocol-dimensions/</t>
+        </is>
+      </c>
+      <c r="E337" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F337" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 6 Jul 2026. **Added 26 Aug 2026 from Heather Flanagan's standards-tracker cross-check** (her bucket: read_now, category: agent_identity, relevance 13) — a new author not previously tracked here. A dimensional model for characterising agent protocol proposals. Meta-analytical rather than a mechanism, and directly useful to this corpus as an external taxonomy to test our own five-cluster model against.</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="5" t="n">
+        <v>337</v>
+      </c>
+      <c r="B338" s="5" t="inlineStr">
+        <is>
+          <t>draft-reilly-web4-orion — Web4: An Agentic, Verifiable Internet Architecture and the Project Orion Reference System</t>
+        </is>
+      </c>
+      <c r="C338" s="5" t="inlineStr">
+        <is>
+          <t>This document defines Web4, an architectural model for an agentic, cryptographically verifiable Internet in which autonomous AI agents operate as first-class participants alongside humans, and every published artifact carries independently checkable proof of origin, integrity, and time. Web4 is realized through the Reilly Protocol Suite, a set of eighteen active IETF Internet-Drafts spanning permanence, integrity, agent orchestration, defense, and human epistemic autonomy. This document also specifies Project Orion, the live reference implementation that unifies the full suite behind autonomous agents on both backend and frontend, verified against three independent Internet-Draft distribution points, and operating publicly at https://project-orion-production.up.railway.app/. A step-by-step implementation guide is provided.</t>
+        </is>
+      </c>
+      <c r="D338" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-reilly-web4-orion/</t>
+        </is>
+      </c>
+      <c r="E338" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F338" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 24 Jul 2026. **Added 26 Aug 2026 from Heather Flanagan's standards-tracker cross-check** (her bucket: read_now, category: agent_identity, relevance 13) — a new author not previously tracked here. Web4 agentic internet architecture. Framework-scale and speculative; kept as a marker of the 'clean-slate' end of the design space, opposite Hardt's OUTLIER position.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="5" t="n">
+        <v>338</v>
+      </c>
+      <c r="B339" s="5" t="inlineStr">
+        <is>
+          <t>draft-sabey-succession-receipts — Succession Receipts: Portable Signed Evidence of Authority Succession Between Autonomous Agents</t>
+        </is>
+      </c>
+      <c r="C339" s="5" t="inlineStr">
+        <is>
+          <t>Autonomous agents are upgraded, replaced, suspended, and restored while holding real operational authority. A Succession Receipt is a portable, signed JSON document that proves one completed, policy- gated transfer of authority between two agents: which agent held the authority, which agent holds it now, under what legitimacy determination the transfer ran, and which obligations carried forward, with every claim grounded in signed evidence events embedded in the receipt itself. Receipts are verifiable offline by parties who do not operate the issuing system, using only the issuer's public key. This document specifies the receipt wire format, its canonicalization and signature scheme (JSON Canonicalization Scheme with Ed25519), the verification algorithm including bidirectional claim grounding, and an optional claim that binds a pre-execution authorization of the handoff to the succession evidence. Where decision receipts prove what an agent did, and delegation receipts prove what an agent may do, Succession Receipts prove that an agent legitimately became the holder of an authority.</t>
+        </is>
+      </c>
+      <c r="D339" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-sabey-succession-receipts/</t>
+        </is>
+      </c>
+      <c r="E339" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F339" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 21 Jul 2026. **Added 26 Aug 2026 from Heather Flanagan's standards-tracker cross-check** (her bucket: read_now, category: authorization, relevance 11) — a new author not previously tracked here. Authority *succession* between agents — a lifecycle stage almost nothing else in the corpus covers. Compare draft-mcguinness-oauth-id-continuation-assertion, which handles continuity of the same actor rather than handover to a different one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="5" t="n">
+        <v>339</v>
+      </c>
+      <c r="B340" s="5" t="inlineStr">
+        <is>
+          <t>draft-singh-psi-agent — PSI AI Agent Action Sealing and Liability Protocol</t>
+        </is>
+      </c>
+      <c r="C340" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies a cryptographic protocol for sealing AI agent actions, establishing an auditable chain of custody from instruction to execution. As AI agents increasingly perform autonomous actions — financial transfers, content publication, system configuration, legal filings — the need for a verifiable record of "who instructed what, when, and what actually happened" becomes critical for liability attribution, regulatory compliance, and trust. The PSI Agent Se</t>
+        </is>
+      </c>
+      <c r="D340" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-singh-psi-agent/</t>
+        </is>
+      </c>
+      <c r="E340" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F340" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 19 Jul 2026. **Added 26 Aug 2026 from Heather Flanagan's standards-tracker cross-check** (her bucket: read_now, category: agent_identity, relevance 11) — a new author not previously tracked here. Action sealing plus an explicit **liability** protocol — one of the few drafts anywhere in the corpus that names liability as a protocol concern rather than a legal one. Compare schrock's reliance agreements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="5" t="n">
+        <v>340</v>
+      </c>
+      <c r="B341" s="5" t="inlineStr">
+        <is>
+          <t>draft-chandra-agent-registry-corroboration — Multi-Source Corroboration for AI Agent Discovery</t>
+        </is>
+      </c>
+      <c r="C341" s="5" t="inlineStr">
+        <is>
+          <t>AI agents are discovered and identified through independent sources — registries, name services, DID methods, catalogs. A single source can misrepresent an agent by omission (withholding a record it holds) or equivocation (serving different answers to different observers); no signature on a served artifact defends against either. This document specifies a corroboration procedure: how one source's claim about one agent, observed from one network vantage, is classified; how a claim is reduced to a comparable view; how claims are diffed into findings with deterministic attribution; how legitimate propagation delay is distinguished from persistent disagreement; and a signed Corroboration Record emitted on every sweep — agreement included — that other evidence formats can bind by digest. The procedure is source-, format-, and layer-agnostic, requires no cooperation from or modification of any source, and is verifiable from recorded bytes.</t>
+        </is>
+      </c>
+      <c r="D341" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-chandra-agent-registry-corroboration/</t>
+        </is>
+      </c>
+      <c r="E341" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F341" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 5 Jul 2026. **Added 26 Aug 2026 from Heather Flanagan's standards-tracker cross-check** (her bucket: read_now, category: agent_identity, relevance 10) — a new author not previously tracked here. Multi-source corroboration for agent discovery — answers 'who vouches for this registry entry', which the discovery drafts in the corpus mostly assume away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="5" t="n">
+        <v>341</v>
+      </c>
+      <c r="B342" s="5" t="inlineStr">
+        <is>
+          <t>draft-kondoju-evc — An External Verifier Contract for Agent Authorization Decisions</t>
+        </is>
+      </c>
+      <c r="C342" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies the External Verifier Contract (EVC): a small, testable, proof-system-agnostic boundary between a host (the program about to take a privileged action on an agent's behalf) and an external verifier (a subprocess that renders an allow/deny verdict on an opaque proof bundle). The contract governs only the transport and verdict envelope: how the host hands a single JSON request to a verifier subprocess over stdin, how the verifier answers with exactly one JSON verdict on stdout, and how the host interprets exit codes, timeouts, and malformed output under a fail-closed rule. Three properties make the boundary standardizable: (1) a single-shot subprocess transport with a closed JSON verdict schema; (2) fail- closed host semantics that are independently testable by a host- conformance suite; and (3) proof-system agnosticism, so the same envelope carries classical-signature, zero-knowledge, and third-party verdicts, distinguished only by an OPTIONAL self-description field. EVC is deliberately not a governance framework, not a delegation model, and not a policy language. It is the narrow decision boundary those larger systems all require at the point of enforcement.</t>
+        </is>
+      </c>
+      <c r="D342" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-kondoju-evc/</t>
+        </is>
+      </c>
+      <c r="E342" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F342" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 21 Jul 2026. **Added 26 Aug 2026 from Heather Flanagan's standards-tracker cross-check** (her bucket: read_now, category: authorization, relevance 10) — a new author not previously tracked here. An external verifier contract for agent authorization decisions; belongs with the candidate decision/policy cluster (gazitt, liu, vicente, fulz, li) that fits no current OAuth spec cluster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="5" t="n">
+        <v>342</v>
+      </c>
+      <c r="B343" s="5" t="inlineStr">
+        <is>
+          <t>draft-correctover-ccs — Correctover Conformance Shape (CCS): Runtime Verification for AI Agent Tool Calls</t>
+        </is>
+      </c>
+      <c r="C343" s="5" t="inlineStr">
+        <is>
+          <t>This document defines the Correctover Conformance Shape (CCS), a runtime verification framework for AI agent tool calls. CCS specifies seven verification dimensions (Structure, Schema, Latency, Cost, Identity, Integrity, Security) that tool calls and results must conform to at runtime. The framework defines a receipt format with Ed25519 signatures, three verdict values (allow, deny, escalate) and four executor lifecycle states (confirmed, dispatched, indeterminate, unknown), and normative requirements for implementations. This revision promotes AEB and CAID to Normative References, specifies the detached Ed25519 signature construction over RFC 8785 canonical JSON, clarifies receipt lifecycle and signing-algorithm conformance, and documents two independent interoperable implementations (Section 21).</t>
+        </is>
+      </c>
+      <c r="D343" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-correctover-ccs/</t>
+        </is>
+      </c>
+      <c r="E343" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F343" s="5" t="inlineStr">
+        <is>
+          <t>Revision -07, 26 Aug 2026. **Added 26 Aug 2026 from Heather Flanagan's standards-tracker cross-check** (her bucket: read_now, category: authorization, relevance 10) — a new author not previously tracked here. Receipt and binding format for agent runtime verification; joins the receipts cluster (schrock, noa-scitt, sahu, vaara, hopley x402).</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="5" t="n">
+        <v>343</v>
+      </c>
+      <c r="B344" s="5" t="inlineStr">
+        <is>
+          <t>draft-ferro-httpbis-apertoid-sig — ApertoID-Signature: HTTP Request Signing for AI Agent Identity</t>
+        </is>
+      </c>
+      <c r="C344" s="5" t="inlineStr">
+        <is>
+          <t>This document defines the ApertoID-Signature HTTP header field, which enables AI agents to cryptographically prove their identity on each HTTP request. The agent signs the request method, target URL, body hash, and identity metadata using an Ed25519 private key whose corresponding public key is published in DNS via the ApertoID protocol [APERTOID-DNS]. The mechanism provides request-level identity verification, action binding (the signature is tied to the specific method and URL), and replay protection via timestamps and nonces.</t>
+        </is>
+      </c>
+      <c r="D344" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ferro-httpbis-apertoid-sig/</t>
+        </is>
+      </c>
+      <c r="E344" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F344" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 12 Aug 2026. **Added 26 Aug 2026 from Heather Flanagan's standards-tracker cross-check** (her bucket: read_now, category: agent_identity, relevance 9) — a new author not previously tracked here. HTTP request signing for agent identity; the proof half of the ApertoID pair. Overlaps WebBotAuth's HTTP Message Signatures approach — a competing design for the same problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="5" t="n">
+        <v>344</v>
+      </c>
+      <c r="B345" s="5" t="inlineStr">
+        <is>
+          <t>draft-mashayekhi-auditable-model-deliberation — Auditable Public Artifacts for Model-Independent Deliberation</t>
+        </is>
+      </c>
+      <c r="C345" s="5" t="inlineStr">
+        <is>
+          <t>Heterogeneous artificial-intelligence systems can exchange messages without sharing stable semantics for claims, evidence, objections, revisions, decisions, failures, and termination. This document defines an experimental public-artifact protocol for model- independent deliberation. It separates interoperable public state from private model computation and does not require disclosure of chain-of-thought, hidden state, prompts, model weights, or private memory. The document defines seven public artifact types, append-only revision, evidence provenance, blocking-objection closure, explicit failure and termination, a restricted canonical JSON profile, and SHA-256-based artifact identifiers. It does not define transport, signatures, authorization, model execution, or a completed consensus system.</t>
+        </is>
+      </c>
+      <c r="D345" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-mashayekhi-auditable-model-deliberation/</t>
+        </is>
+      </c>
+      <c r="E345" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F345" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 12 Aug 2026. **Added 26 Aug 2026 from Heather Flanagan's standards-tracker cross-check** (her bucket: read_now, category: authorization, relevance 9) — a new author not previously tracked here. Auditable public artifacts for model-independent deliberation — audit cluster, unusual for targeting the deliberation step rather than the action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="5" t="n">
+        <v>345</v>
+      </c>
+      <c r="B346" s="5" t="inlineStr">
+        <is>
+          <t>draft-ferro-dnsop-apertoid — ApertoID: DNS-Based Agent Identity Declaration Protocol</t>
+        </is>
+      </c>
+      <c r="C346" s="5" t="inlineStr">
+        <is>
+          <t>This document defines ApertoID, a DNS-based protocol that enables domain owners to declare authorized AI agents acting on their behalf, publish cryptographic keys for agent identity verification, and specify enforcement policies for unauthorized agents. ApertoID uses existing DNS TXT records under the "_apertoid" underscore-scoped domain name to provide a decentralized, standards-based mechanism for AI agent identity declaration and verification. ApertoID defines two record types: a Policy Record analogous to DMARC that specifies domain-level enforcement behavior, and Agent Declaration Records analogous to DKIM key records that bind agent endpoints to Ed25519 public keys with mandatory expiration. A companion document [APERTOID-SIG] defines the HTTP request signing mechanism that enables agents to cryptographically prove their identity on each request.</t>
+        </is>
+      </c>
+      <c r="D346" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ferro-dnsop-apertoid/</t>
+        </is>
+      </c>
+      <c r="E346" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F346" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 12 Aug 2026. **Added 26 Aug 2026 from Heather Flanagan's standards-tracker cross-check** (her bucket: read_now, category: agent_identity, relevance 9) — a new author not previously tracked here. DNS-based agent identity declaration. Pairs with draft-ferro-httpbis-apertoid-sig below — declaration in DNS, proof over HTTP. Kept despite the `dnsop` slug because the subject is agent identity, not DNS operations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="5" t="n">
+        <v>346</v>
+      </c>
+      <c r="B347" s="5" t="inlineStr">
+        <is>
+          <t>draft-pelov-bounded-agent-capabilities — Bounded Capabilities for Agent Tool Interfaces: Problem Statement</t>
+        </is>
+      </c>
+      <c r="C347" s="5" t="inlineStr">
+        <is>
+          <t>Deployed agent tool-interface protocols carry JSON Schema type declarations for tools, but a type declaration is not a contract: nothing signals that a tool is fully schema-bounded, conformance to declared schemas is self-certified by the declaring party, declarations are not pinned between discovery time and invocation time, and error channels are untyped by design. As a consequence, any decision made about a tool call — authorization, discovery, audit, or composition — requires a language model to interpret what the call means, even for the large class of tools that are not intrinsically open-ended. This document states that problem and poses questions for the community. It deliberately proposes no mechanism.</t>
+        </is>
+      </c>
+      <c r="D347" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-pelov-bounded-agent-capabilities/</t>
+        </is>
+      </c>
+      <c r="E347" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F347" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 3 Jul 2026. **Added 26 Aug 2026 from Heather Flanagan's standards-tracker cross-check** (her bucket: read_now, category: authorization, relevance 8) — a new author not previously tracked here. Problem statement for bounding agent tool interfaces; the requirements-side companion to the Mission-Bound tool-binding profile and draft-wolfe-faf-agent's 'what it must never do' field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="5" t="n">
+        <v>347</v>
+      </c>
+      <c r="B348" s="5" t="inlineStr">
+        <is>
+          <t>draft-zagarella-autonomy-governor — Pre-Action Risk-Graded Assurance for Agent Interactions</t>
+        </is>
+      </c>
+      <c r="C348" s="5" t="inlineStr">
+        <is>
+          <t>Governance of autonomous agents today is largely expressed as boundary enforcement: an action is permitted or blocked at the point it is attempted, per a policy evaluated at that boundary. As agents span heterogeneous action types — authenticating a human, executing a delegated task, selecting a computational resource — a single, uniform way to express "how much assurance this action requires, before it proceeds" is missing. This document describes an interface for pre-action, risk-graded assurance: a policy stage that, before an agent action proceeds, derives an assurance requirement from a risk signal and expresses that requirement in a domain-appropriate form, recording the decision in an audit record and optionally binding it to a verified human root. It defines the interface and the audit-record fields, not any particular risk-scoring method or control law. This document also describes the autonomy-asymmetry control law: a feedback loop coupling assurance requirements to VERIFY-phase pass rates, with fast-down (immediate elevation on failure) and slow-up (hysteresis- governed relaxation on sustained success) asymmetry. The iteration governor is described as the per-packet instance of this control law, and the phase-seal chain as its sensor. This document is offered as input to the proposed AUDIT working group's work on authorization state over time and action provenance.</t>
+        </is>
+      </c>
+      <c r="D348" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-zagarella-autonomy-governor/</t>
+        </is>
+      </c>
+      <c r="E348" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F348" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 23 Aug 2026. **Added 26 Aug 2026 from Heather Flanagan's standards-tracker cross-check** (her bucket: read_now, category: authorization, relevance 8) — a new author not previously tracked here. Pre-action risk-graded assurance — the permit-before-commit cluster. Same instinct as VERA's earned-autonomy runtime and the NHE graduated-autonomy model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="5" t="n">
+        <v>348</v>
+      </c>
+      <c r="B349" s="5" t="inlineStr">
+        <is>
+          <t>draft-bradleyb-audit-decision-records — Signed Decision Records for Agent Authorization: Disclosures, Entry Emission, and Ordering Evidence</t>
+        </is>
+      </c>
+      <c r="C349" s="5" t="inlineStr">
+        <is>
+          <t>Audit systems for autonomous agents commonly record the actions an agent performed. This makes the non-occurrence of a permitted action unrepresentable: when nothing happens, there is no action to emit anything. This document describes an evidence model that records the authorization decision rather than the action. A decision exists whether or not the action follows, so denials, expiries, and commitments that were granted and never honoured remain representable. The document defines four disclosures that make a decision record independently evaluable, an entry-emission rule for states a relying party may need to reason about, and the evidentiary basis for claims that a decision preceded its effect. It distinguishes correspondence, where two records agree about what happened, from precedence, where the order of decision and effect is established, and it requires records to state which of the two they carry.</t>
+        </is>
+      </c>
+      <c r="D349" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-bradleyb-audit-decision-records/</t>
+        </is>
+      </c>
+      <c r="E349" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F349" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 13 Aug 2026. **Added 26 Aug 2026 from Heather Flanagan's standards-tracker cross-check** (her bucket: read_now, category: authorization, relevance 8) — a new author not previously tracked here. Signed decision records with ordering evidence — directly comparable to the Decision Evidence Records in the Mission-Bound runtime-enforcement profile and to schrock's EMILIA evidence chain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="5" t="n">
+        <v>349</v>
+      </c>
+      <c r="B350" s="5" t="inlineStr">
+        <is>
+          <t>draft-msebenzi-evidence-action — The evidence.* Family: Post-Hoc, Independently Recomputable Evidence Records for AI Agent Actions</t>
+        </is>
+      </c>
+      <c r="C350" s="5" t="inlineStr">
+        <is>
+          <t>Autonomous agents act through tool invocations whose consequences outlive the sessions that produce them. Pre-action constraint families gate whether an agent may act: environment.* attests boolean world-state, and verification.* attests calibrated confidence over factual claims. No sibling family records, under equivalent verification discipline, what the agent then did. This document defines the evidence.* family: append-only, hash-chained, signature- bound evidence records of agent actions, designed so that a third party can recompute every verdict from signed primitives and a published key, without trusting the operator's runtime. It defines the family's membership criterion (independent recomputability with fail-closed verification), the family-wide record vocabulary and canonicalization discipline, a tri-state verification protocol (VALID, INVALID, UNVERIFIABLE), composition with the pre-action sibling families, and the conformance-vector discipline under which independent implementations demonstrate byte-level agreement. One reference record type, evidence.action, is specified together with its frozen conformance corpus. This document deliberately states what an evidence record does not prove.</t>
+        </is>
+      </c>
+      <c r="D350" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-msebenzi-evidence-action/</t>
+        </is>
+      </c>
+      <c r="E350" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F350" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 28 Jul 2026. **Added 26 Aug 2026 from Heather Flanagan's standards-tracker cross-check** (her bucket: read_now, category: agent_identity, relevance 7) — a new author not previously tracked here. An `evidence.*` family of post-hoc recomputable evidence records. Recomputability is the same claim draft-sirkkavaara-vaara-receipt makes — worth comparing the two directly.</t>
         </is>
       </c>
     </row>
@@ -11241,6 +11811,25 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D329" r:id="rId328"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D330" r:id="rId329"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D350" r:id="rId349"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/delegated_authorization_research.xlsx
+++ b/delegated_authorization_research.xlsx
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="6" t="n">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="D12" s="7" t="n"/>
     </row>
@@ -966,7 +966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F350"/>
+  <dimension ref="A1:F356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11476,6 +11476,186 @@
       <c r="F350" s="5" t="inlineStr">
         <is>
           <t>Revision -00, 28 Jul 2026. **Added 26 Aug 2026 from Heather Flanagan's standards-tracker cross-check** (her bucket: read_now, category: agent_identity, relevance 7) — a new author not previously tracked here. An `evidence.*` family of post-hoc recomputable evidence records. Recomputability is the same claim draft-sirkkavaara-vaara-receipt makes — worth comparing the two directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="B351" s="5" t="inlineStr">
+        <is>
+          <t>draft-vauban-x402-stark-receipts — x402 STARK Receipt Format Extension</t>
+        </is>
+      </c>
+      <c r="C351" s="5" t="inlineStr">
+        <is>
+          <t>The x402 PAYMENT-RESPONSE carries a facilitator-issued settlement reference but does not provide a self-contained, offline-verifiable payment-condition proof. A verifier must today contact the facilitator to confirm whether a specific amount, currency, and payer attestation were satisfied at the time of payment. This gap prevents compliance with EU AI Act Art. 12 (transparency and documentation) and MiCA Art. 76 (settlement record-keeping) in automated payment pipelines. This document defines the receipt-format extension for x402 V2. The extension introduces a negotiable receipt format selection mechanism that allows resource servers, facilitators, and clients to agree on which cryptographic receipt variant to produce and verify, without altering the core PAYMENT-RESPONSE wire structure. Three variants are defined: a Stwo Circle STARK proof of payment conditions (post- quantum sound, offline verifiable), a hybrid ES256K + ML-DSA-65 dual- signature receipt (receipt integrity under quantum adversary), and a classical ES256K fallback. A canonical preimage discipline using JCS ([RFC8785]) ensures cross-implementation digest consistency. The canonical preimage discipline in this document is cross-validated against the x402 canonicalisation conformance set, which is checked byte-for-byte across five independent RFC 8785 ([RFC8785]) implementations in five languages (Python, TypeScript, Go, Java, Rust).</t>
+        </is>
+      </c>
+      <c r="D351" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-vauban-x402-stark-receipts/</t>
+        </is>
+      </c>
+      <c r="E351" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F351" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 25 May 2026; author: Vauban Research. **Added 26 Aug 2026 — resolves the curation hold open since 11 Aug 2026**, when this cluster was left out because its subject is cryptographic proof discipline rather than payment authorization. Maintainer ruled it in. Checking the family found it is **seven drafts, not the pair that was held**; draft-vauban-x402-delegation-binding was already tracked. **The hub of the Vauban family** — five siblings reference it, four of them normatively (pqc-receipts, vpsf-algebra, starknet-anchor, delegation-binding). Also referenced by draft-dogru-cedulon, a SCITT draft this corpus deliberately does not track, which is a rare cross-link out of the payments cluster. This is the draft the 11 Aug 2026 hold was really about: it is an x402 *receipt* format, but its subject is STARK proof discipline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="5" t="n">
+        <v>351</v>
+      </c>
+      <c r="B352" s="5" t="inlineStr">
+        <is>
+          <t>draft-vauban-x402-pqc-receipts — Post-Quantum Cryptographic Discipline for x402 STARK Receipts</t>
+        </is>
+      </c>
+      <c r="C352" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies a post-quantum cryptographic discipline for x402 STARK receipts. The discipline applies on two layers : (a) proof integrity via hash-based proving systems (the Stwo Circle STARK M31 reference implementation), which are post-quantum sound under standard cryptanalytic assumptions, and (b) signature integrity via the hybrid ES256K + ML-DSA-65 dual-signed receipt variant ([FIPS204]). It maps the hybrid-pqc receipt variant of the x402 STARK Receipt Format Extension ([STARK-RECEIPTS]) to the NIST PQC migration roadmap and to the EU eIDAS 2.0, ANSSI, and BSI migration timelines for the 2025-2030 window. Reference runners are published as the vauban-x402-jcs-conformance and vauban-x402-canonical Rust crates. Companion documents are [STARK-RECEIPTS] (receipt format) and [VPSF-ALGEBRA] (composability grammar).</t>
+        </is>
+      </c>
+      <c r="D352" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-vauban-x402-pqc-receipts/</t>
+        </is>
+      </c>
+      <c r="E352" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F352" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 25 May 2026; author: Vauban Research. **Added 26 Aug 2026 — resolves the curation hold open since 11 Aug 2026**, when this cluster was left out because its subject is cryptographic proof discipline rather than payment authorization. Maintainer ruled it in. Checking the family found it is **seven drafts, not the pair that was held**; draft-vauban-x402-delegation-binding was already tracked. The other half of the pair held out on 11 Aug 2026. Post-quantum discipline for the STARK receipts, motivated by the migration horizon in NIST SP 800-208, ANSSI, BSI and eIDAS 2.0. Compare draft-burls-mtac, added earlier today, which brings PQC to agent *credential issuance* rather than to payment receipts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="5" t="n">
+        <v>352</v>
+      </c>
+      <c r="B353" s="5" t="inlineStr">
+        <is>
+          <t>draft-vauban-x402-vpsf-algebra — VPSF Claim Algebra for x402 Payment Receipts</t>
+        </is>
+      </c>
+      <c r="C353" s="5" t="inlineStr">
+        <is>
+          <t>The x402 protocol ([X402-V2]) defines three wire messages for HTTP- native payment flows but provides no composability model for payment receipts. A recipient holding a SettlementReceipt and a DelegationGrant cannot natively express that the settlement satisfies a delegated spending condition, or that a RefundClaim negates an earlier SettlementReceipt, without bespoke facilitator-side logic. As automated payment pipelines grow, the absence of a normative composability layer leads to fragmented, non-interoperable verification surfaces. This document specifies the Vauban Proof Stack Framework (VPSF) Claim Algebra for x402 payment receipts: a grammar of five composition operators (Conjunction, Implication, Aggregation, Selective Disclosure, Revocation; abbreviated ∧, →, ⊕, ▷, ¬) applied over the four canonical Payment Claim types (PaymentIntent, SettlementReceipt, RefundClaim, DelegationGrant) defined in [LIFECYCLE-FSM]. The algebra is chain-agnostic by invariant; the Starknet-based proof system described in [STARK-RECEIPTS] is the first reference implementation. Composability is grounded in the JCS canonical preimage discipline ([RFC8785]), ensuring operator results are deterministic and cross-implementation consistent. An open-source Rust implementation is provided in [VAUBAN-CRATE].</t>
+        </is>
+      </c>
+      <c r="D353" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-vauban-x402-vpsf-algebra/</t>
+        </is>
+      </c>
+      <c r="E353" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F353" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 25 May 2026; author: Vauban Research. **Added 26 Aug 2026 — resolves the curation hold open since 11 Aug 2026**, when this cluster was left out because its subject is cryptographic proof discipline rather than payment authorization. Maintainer ruled it in. Checking the family found it is **seven drafts, not the pair that was held**; draft-vauban-x402-delegation-binding was already tracked. Claim algebra for x402 payment receipts; normatively references stark-receipts and is referenced by pqc-receipts. Not part of the original hold, surfaced by checking the family.</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="5" t="n">
+        <v>353</v>
+      </c>
+      <c r="B354" s="5" t="inlineStr">
+        <is>
+          <t>draft-vauban-x402-starknet-anchor — x402 V2 Starknet On-Chain Anchor</t>
+        </is>
+      </c>
+      <c r="C354" s="5" t="inlineStr">
+        <is>
+          <t>The x402 receipt-format extension defined in [STARK-RECEIPTS] and the lifecycle finite state machine defined in [LIFECYCLE-FSM] specify cryptographic evidence for x402 V2 payment events as off-chain verifiable artefacts. Neither document specifies how a settlement receipt is promoted to on-chain finality, nor how an independent auditor verifies that promotion without contacting the originating facilitator. This document defines the Starknet on-chain anchor format for x402 V2 payment settlements. The anchor consists of a Starknet event emitted by a conforming Cairo contract, identified by a canonical tuple of chain identifier, transaction hash, event index, and optional block number. A reference implementation, PaymentDemoEmitter, is deployed on Starknet Sepolia at 0x044dd87a94a801cf775d4c5e4b6703102d4e97e1cd1d0a8879341219ae4f19ff and is inspectable via the Voyager block explorer. The document also specifies an RPC endpoint convention, grounded in the Starknet JSON- RPC specification, that any compliant node implementation satisfies; the Vauban Pay reference endpoints are cited as one such implementation. This anchor specification is one instantiation of a chain-agnostic anchoring pattern; the protocol contract is designed to accommodate future per-chain adapter specifications that satisfy the same structural requirements.</t>
+        </is>
+      </c>
+      <c r="D354" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-vauban-x402-starknet-anchor/</t>
+        </is>
+      </c>
+      <c r="E354" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F354" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 25 May 2026; author: Vauban Research. **Added 26 Aug 2026 — resolves the curation hold open since 11 Aug 2026**, when this cluster was left out because its subject is cryptographic proof discipline rather than payment authorization. Maintainer ruled it in. Checking the family found it is **seven drafts, not the pair that was held**; draft-vauban-x402-delegation-binding was already tracked. On-chain anchoring for ledger-backed finality. The most blockchain-specific document in the corpus — kept for family completeness rather than on its own merits, and worth flagging as the point where this cluster leaves protocol territory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="5" t="n">
+        <v>354</v>
+      </c>
+      <c r="B355" s="5" t="inlineStr">
+        <is>
+          <t>draft-vauban-x402-lifecycle-fsm — x402 V2 Payment Lifecycle Finite State Machine</t>
+        </is>
+      </c>
+      <c r="C355" s="5" t="inlineStr">
+        <is>
+          <t>This document defines a normative finite state machine (FSM) for x402 V2 Payment lifecycle transitions, covering the four canonical Payment Claim states: PaymentIntent (initialisation), SettlementReceipt (completion), RefundClaim (reversal), and DelegationGrant (bounded authority). Each transition is bound to the prior state by cryptographic linkage via the JCS canonical preimage discipline ([RFC8785]), enabling supervisor reconstruction of full payment histories from retained off-VM manifests. The FSM is compatible with the x402 STARK Receipt Format Extension [STARK-RECEIPTS] but applicable to any x402 receipt format that implements the canonical preimage discipline. Implementation evidence: 18 DelegationGrant vectors cross-validated byte-identical across five language runtimes ([X402-2432]), live on-chain anchor on Starknet Sepolia (PaymentDemoEmitter at 0x044dd87a94a801cf775d4c5e4b6703102d4e97e1cd1d0a8879341219ae4f19ff).</t>
+        </is>
+      </c>
+      <c r="D355" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-vauban-x402-lifecycle-fsm/</t>
+        </is>
+      </c>
+      <c r="E355" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F355" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 25 May 2026; author: Vauban Research. **Added 26 Aug 2026 — resolves the curation hold open since 11 Aug 2026**, when this cluster was left out because its subject is cryptographic proof discipline rather than payment authorization. Maintainer ruled it in. Checking the family found it is **seven drafts, not the pair that was held**; draft-vauban-x402-delegation-binding was already tracked. A finite state machine for the x402 V2 payment lifecycle. The most broadly reusable of the six: an explicit lifecycle FSM is the same shape of artifact as the seven-state Mission lifecycle in the Mission-Bound MVP, arrived at for payments instead of tasks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="5" t="n">
+        <v>355</v>
+      </c>
+      <c r="B356" s="5" t="inlineStr">
+        <is>
+          <t>draft-vauban-x402-consolidated — x402 Cryptographic Receipts: Format, Post-Quantum Discipline, and Starknet Anchor</t>
+        </is>
+      </c>
+      <c r="C356" s="5" t="inlineStr">
+        <is>
+          <t>The x402 V2 protocol defines HTTP-native payment flows but leaves three gaps that block compliance use cases. First, the PAYMENT- RESPONSE carries a facilitator-issued reference rather than a self- contained, offline-verifiable cryptographic receipt; an auditor cannot validate a retained receipt without contacting the facilitator. Second, classical signatures alone (ES256K) do not satisfy the post-quantum migration horizon set by NIST SP 800-208, ANSSI, BSI, and EU eIDAS 2.0 for high-value or long-retention material. Third, off-chain receipts alone do not provide ledger- anchored finality required by frameworks such as MiCA Art. 76 (settlement record-keeping) and EU AI Act Art. 12 (transparency-and- documentation). This document consolidates three previously separate extensions into a single specification. It defines (a) a negotiable receipt-format extension with three variants (Stwo Circle STARK proof, hybrid ES256K + ML-DSA-65 dual-signature, classical ES256K fallback) over a JCS canonical preimage discipline grounded in RFC 8785; (b) a two-axis post-quantum discipline mapping hash-based proving and hybrid signatures to the NIST PQC migration roadmap; and (c) a Starknet on- chain anchor format with a canonical anchor tuple, Cairo event layout, RPC endpoint convention, and block explorer reference for human-readable audit. Topics under active coalition discussion are explicitly out of scope: the VPSF composability claim algebra, the payment lifecycle finite state machine, and the delegation binding extension are deferred to companion documents not included in this consolidated submission.</t>
+        </is>
+      </c>
+      <c r="D356" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-vauban-x402-consolidated/</t>
+        </is>
+      </c>
+      <c r="E356" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F356" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 29 May 2026; author: Vauban Research. **Added 26 Aug 2026 — resolves the curation hold open since 11 Aug 2026**, when this cluster was left out because its subject is cryptographic proof discipline rather than payment authorization. Maintainer ruled it in. Checking the family found it is **seven drafts, not the pair that was held**; draft-vauban-x402-delegation-binding was already tracked. A -00 consolidation of the receipt format, post-quantum discipline and Starknet anchor into one document, referencing lifecycle-fsm, delegation-binding and vpsf-algebra for context. Datatracker does **not** mark the component drafts Replaced, so all six are tracked; watch whether the components get superseded, which would make this the survivor.</t>
         </is>
       </c>
     </row>
@@ -11830,6 +12010,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D348" r:id="rId347"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D349" r:id="rId348"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D356" r:id="rId355"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/delegated_authorization_research.xlsx
+++ b/delegated_authorization_research.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Stable. Mostly the primitives, not where the debate is. RFC 10017 (browser-based apps, published 21 Aug 2026) is the exception — OAuth WG output that is peripheral to delegation. An audit of all tracked Datatracker drafts on 29 Sep 2026 confirmed no further draft has reached RFC status.</t>
+          <t>Stable. Mostly the primitives, not where the debate is. RFC 10017 (browser-based apps, published 21 Aug 2026) is the exception — OAuth WG output that is peripheral to delegation. Full state audits of all tracked Datatracker drafts on 29 Sep and 28 Oct 2026 confirmed no further draft has reached RFC status; rfc7523bis sits in the RFC Editor queue, now marked blocked.</t>
         </is>
       </c>
     </row>
@@ -620,11 +620,11 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>465</v>
+        <v>546</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>★ THIS IS WHERE THE CURRENT WORK IS HAPPENING ★  The 4 Jun 2026 recharter is APPROVED (charter-ietf-oauth rev 06), making Complex Delegation chartered work — still no milestone attached as of 29 Sep 2026. The 29 Sep 2026 sweep added 86 drafts, the largest single-sweep growth of this tab, and the shape of the addition matters more than the count: TWO WG ADOPTIONS in the corpus's own subject (draft-ietf-oauth-deferred-token-response replacing gerber, and draft-ietf-wimse-aims replacing klrc), Hardt's zero-dependency AAuth OUTLIER growing into a four-draft family (R3, budgets, events), a new four-draft agent-identity registry family from Drake (AIRS), five competing entrants in the discovery/registry corner, and a verifier-side evaluation draft (jackson-wimse-evaluation) that answers the half of the delegation-chain question every other draft here leaves open.</t>
+          <t>★ THIS IS WHERE THE CURRENT WORK IS HAPPENING ★  The 4 Jun 2026 recharter is APPROVED (charter-ietf-oauth rev 06), making Complex Delegation chartered work — still no milestone attached as of 28 Oct 2026, but the WG is now spending interim time on it: a 19 Oct 2026 interim on agent-authorization use cases and gaps (chen-oauth-agent-authz-use-cases) and a 26 Oct 2026 interim devoted to Mission-Bound Authorization (mcguinness-oauth-mission). The 28 Oct 2026 sweep added 81 rows (79 new drafts, the AUDIT BoF request, and one move from the Mission-Bound tab), and its governance events matter more than the count: the OAuth WG ADOPTED Delegated SD-JWT (gco-oauth-delegate-sd-jwt, 16 Oct) and declined PoP-with-HTTP-Message-Signatures (richer-oauth-httpsig) the same day; an AUDIT BoF led by the HUB author Kühlewind was APPROVED for IETF 127; and a second Mission-Bound family draft (oauth-mission-resource-access) was filed on Datatracker and moved here from the pre-pub tab. This was also the first sweep to read the OAuth and WIMSE mailing lists directly, which surfaced cross-domain mandate validation with evidence of the delegator's authority (hulea-wimse-agent-mandate) and three competing AIMS audit-record mappings.</t>
         </is>
       </c>
     </row>
@@ -636,15 +636,15 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>The 46 GitHub-only drafts of the McGuinness Mission-Bound Authorization family — a single-repo decomposition with a machine-readable family-manifest.json, carrying group / role / spec-maturity / maintenance per draft.</t>
+          <t>The GitHub-only drafts of the McGuinness Mission-Bound Authorization family — a single-repo decomposition with a machine-readable family-manifest.json, carrying group / role / spec-maturity / maintenance per draft.</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Pre-publication, not IETF documents. Still only draft-mcguinness-oauth-mission has been filed on Datatracker and it stays in the Active IETF Drafts tab — re-verified 29 Sep 2026 against all 47 manifest slugs. Upstream growth has slowed sharply: 34 -&gt; 46 in the nine days to 4 Sep, then 46 -&gt; 47 in the twenty-five days to 29 Sep (+1 row here, mission-control-plane). No renames, and the manifest schema is unchanged since the 4 Sep rewrite.</t>
+          <t>Pre-publication, not IETF documents. The standing watch item fired on 22 Oct 2026: draft-mcguinness-oauth-mission-resource-access was filed on Datatracker and moved to the Active IETF Drafts tab, joining draft-mcguinness-oauth-mission — re-verified 28 Oct 2026 against all 52 manifest slugs. Upstream grew 47 -&gt; 52 in the twenty-nine days to 28 Oct (+5 rows here: derivation-limits, submission-evidence, request-provenance, approved-set-verification, device-authorization; -1 for the move). No renames, and the manifest schema is unchanged since the 4 Sep rewrite.</t>
         </is>
       </c>
     </row>
@@ -716,15 +716,15 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Vendor blogs, LinkedIn-style articles, reference implementations (OVID/OVID-ME, ZeroID, WorkOS auth.md, Agent Trust Protocol), and the McGuinness Mission-Bound Authorization blog corpus.</t>
+          <t>Vendor blogs, LinkedIn-style articles, reference implementations and interop test vectors (OVID/OVID-ME, ZeroID, WorkOS auth.md, Agent Trust Protocol, Tenuo, the hulea mandate vectors), and the McGuinness Mission-Bound Authorization blog corpus.</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Practitioner content; the five implementations at the top of the tab show what an implementable agent-delegation stack looks like today. The Aug 2026 sweeps backfilled the Control Plane blog to 79 entries — the Agent Control Points series (Aug 2026) and the Mission-Bound Authorization handbook (Jul 2026) are the two most substantial arcs. The 26 Aug sweep repointed three posts the site had re-slugged ('Mission-Bound OAuth' was renamed to 'Mission-Bound Authorization' throughout) and added all 29 handbook chapters and handbook-only series indexes, which are absent from the RSS feed. Verified complete against the live site 26 Aug 2026; no new posts as of 4 Sep 2026.</t>
+          <t>Practitioner content; the five implementations at the top of the tab show what an implementable agent-delegation stack looks like today. The Aug 2026 sweeps backfilled the Control Plane blog to 79 entries — the Agent Control Points series (Aug 2026) and the Mission-Bound Authorization handbook (Jul 2026) are the two most substantial arcs. The 26 Aug sweep repointed three posts the site had re-slugged ('Mission-Bound OAuth' was renamed to 'Mission-Bound Authorization' throughout) and added all 29 handbook chapters and handbook-only series indexes, which are absent from the RSS feed. After ten quiet weeks the blog resumed on 13 Oct 2026 with a gateway/AuthZEN arc (5 posts, added 28 Oct; handbook unchanged). The 28 Oct sweep also added four interop-vector and implementation repos announced on the OAuth and WIMSE lists, and four of Heather Flanagan's five October posts, which turned squarely toward agent authorization.</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="6" t="n">
-        <v>695</v>
+        <v>793</v>
       </c>
       <c r="D12" s="7" t="n"/>
     </row>
@@ -966,7 +966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F466"/>
+  <dimension ref="A1:F547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, Apr 2026; author: Mark Nottingham (Melbourne). The foundational use-case framing for the WG; scopes out the design space that the registry, httpsig-protocol, and anonymous-auth drafts are responding to.</t>
+          <t>Revision -02, Apr 2026; author: Mark Nottingham (Melbourne). The foundational use-case framing for the WG; scopes out the design space that the registry, httpsig-protocol, and anonymous-auth drafts are responding to.  **EXPIRED on Datatracker** (expired 3 Oct 2026; checked 28 Oct 2026) — kept in the corpus deliberately; an expired draft is still evidence of what was proposed.</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Revision -10, Jul 2026 (was -08 Mar 2026). -10 added a 'client_attestation_pop_methods_supported' metadata parameter, created a new 'OAuth Client Attestation Proof-of-Possession Methods' registry, clarified that PoP mechanisms from other specs are permitted, and refined DPoP combined-mode handling. Relates to the RATS Passport Model per RFC 9334; RATS attestation procedures themselves are deliberately out of scope. The 'client instance' framing pairs naturally with the McGuinness Client Instance Assertion and AI Agent Instance drafts.</t>
+          <t>Revision -10, Jul 2026 (was -08 Mar 2026). -10 added a 'client_attestation_pop_methods_supported' metadata parameter, created a new 'OAuth Client Attestation Proof-of-Possession Methods' registry, clarified that PoP mechanisms from other specs are permitted, and refined DPoP combined-mode handling. Relates to the RATS Passport Model per RFC 9334; RATS attestation procedures themselves are deliberately out of scope. The 'client instance' framing pairs naturally with the McGuinness Client Instance Assertion and AI Agent Instance drafts. **Updated 28 Oct 2026:** WGLC on -11 ended 22 Sep 2026; now at **-12 (18 Oct 2026)** in state **WG Consensus: Waiting for Write-Up** — the next OAuth WG document after Transaction Tokens to head to the IESG. `mcguinness-oauth-client-attesters` (tracked) profiles which attesters a client endorses for it.</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Revision -03 (March 2026). Filip Skokan added as co-author in -03. Complements RFC 8707 / RFC 9700 / RFC 9207 by adding issuance-time confirmation to the discovery-time mechanisms. Notable for the agent-authz corpus because dynamic resource discovery is a core agent pattern and resource-mix-up attacks are amplified when agents juggle many short-lived tokens.</t>
+          <t>Revision -03 (March 2026). Filip Skokan added as co-author in -03. Complements RFC 8707 / RFC 9700 / RFC 9207 by adding issuance-time confirmation to the discovery-time mechanisms. Notable for the agent-authz corpus because dynamic resource discovery is a core agent pattern and resource-mix-up attacks are amplified when agents juggle many short-lived tokens. **Updated 28 Oct 2026:** **revived** — previously expired, refreshed to **-04 on 25 Oct 2026** alongside `rfc9728bis`. Active again.</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Revision -01 (Feb 2026). A small targeted correction to the PRM validation rule. Notable as supporting infrastructure for the McGuinness Mission-Bound OAuth work — PRM is the substrate for Resource AS / Resource Server discovery of required RAR types under that profile.</t>
+          <t>Revision -01 (Feb 2026). A small targeted correction to the PRM validation rule. Notable as supporting infrastructure for the McGuinness Mission-Bound OAuth work — PRM is the substrate for Resource AS / Resource Server discovery of required RAR types under that profile. **Updated 28 Oct 2026:** **revived** — expired 28 Aug 2026 (the first McGuinness draft to expire), then refreshed to **-02 on 25 Oct 2026**. Active again; the expiry tag no longer applies.</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 6 Jul 2026. This is the formal I-D target for the 'Mission-Bound OAuth MVP' blog post (May 2026, Industry tab) — the five-wire-addition protocol that makes the user-approved task a first-class OAuth object. Paired with the runtime enforcement profile (still not on Datatracker as of Jul 10). The Mission lifecycle (pending_approval → active → suspended → revoked → expired → completed → rejected) and the proposal_hash/consent_rendering_hash binding anchor what was approved versus what the user saw.</t>
+          <t>Revision -00, 6 Jul 2026. This is the formal I-D target for the 'Mission-Bound OAuth MVP' blog post (May 2026, Industry tab) — the five-wire-addition protocol that makes the user-approved task a first-class OAuth object. Paired with the runtime enforcement profile (still not on Datatracker as of Jul 10). The Mission lifecycle (pending_approval → active → suspended → revoked → expired → completed → rejected) and the proposal_hash/consent_rendering_hash binding anchor what was approved versus what the user saw. **Updated 28 Oct 2026:** revised to **-01 (21 Oct 2026)**, and the OAuth WG held a **virtual interim on 26 Oct 2026 devoted entirely to Mission-Bound Authorization** — the first WG session given over to this draft, one week after a 19 Oct interim on agent-authorization use cases and gaps. The day after -01, `oauth-mission-resource-access` became the second family draft filed on Datatracker. Not a WG adoption, and still no Complex Delegation milestone, but the closest the WG has come to working on Complex Delegation directly. On the list, `luna-eagf-agent-delegation-semantics` was posted as a response to Mission-00 §6.2 (approval-authority provenance left to a governance layer).</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, March 2026; arguably the strongest purely-OAuth-grounded delegation draft — offline verification is a key scalability property. Good path to OAuth WG adoption; overlaps with draft-mishra-oauth-agent-grants and will likely need to be consolidated with it.</t>
+          <t>Revision -00, March 2026; arguably the strongest purely-OAuth-grounded delegation draft — offline verification is a key scalability property. Good path to OAuth WG adoption; overlaps with draft-mishra-oauth-agent-grants and will likely need to be consolidated with it. **Updated 28 Oct 2026:** now **-02 (27 Oct 2026)**, with **229 public chain-verification test vectors** (Section 8 now specifies verification step by step) and the author reporting twelve citing I-Ds and three new independent implementations; reviewed on the list by Neil Madden. Section 1.3 positions AATs against Transaction Tokens, identity chaining and WIMSE AIMS, and against Macaroons, SPKI/SDSI, Biscuit and UCAN. Reference implementation `tenuo-ai/tenuo` added to the Industry tab this sweep.</t>
         </is>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 16 March 2026; implementation-focused. YAML policy approach is pragmatic but not interoperable-by-design. HITL integration is a valuable safety feature. Third member of the 'AIP' name-collision triple — must be resolved before any can progress.</t>
+          <t>Revision -00, 16 March 2026; implementation-focused. YAML policy approach is pragmatic but not interoperable-by-design. HITL integration is a valuable safety feature. Third member of the 'AIP' name-collision triple — must be resolved before any can progress.  **EXPIRED on Datatracker** (expired 17 Sep 2026; checked 28 Oct 2026) — kept in the corpus deliberately; an expired draft is still evidence of what was proposed. **Correction 28 Oct 2026:** the 29 Sep sweep recorded this draft as newly expired and tagged, but the tag never reached this row; added now.</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Already at revision -04 (March 2026), suggesting active iteration; narrow scope, clean design, and the strongest IANA-registration candidate in the set. OAuth 2.1 for auth is deliberately out of scope.</t>
+          <t>Already at revision -04 (March 2026), suggesting active iteration; narrow scope, clean design, and the strongest IANA-registration candidate in the set. OAuth 2.1 for auth is deliberately out of scope.  **EXPIRED on Datatracker** (expired 27 Sep 2026; checked 28 Oct 2026) — kept in the corpus deliberately; an expired draft is still evidence of what was proposed. **Correction 28 Oct 2026:** the 29 Sep sweep recorded this draft as newly expired and tagged, but the tag never reached this row; added now.</t>
         </is>
       </c>
     </row>
@@ -3325,17 +3325,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>draft-stephan-ai-agent-6g — AI Agent Protocols for 6G Systems</t>
+          <t>draft-stephan-agentproto-6g-usecases — AI Agent protocols for 6G systems</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>An IETF individual draft translating use cases and service requirements from 3GPP TR 22.870 into IETF agent-protocol requirements, covering autonomous vehicles, privacy preservation, and anomaly detection.</t>
+          <t>Communication between AI agents and between agent and tools is expected to be pivotal in 6G systems. The 3GPP TR 22.870 outlines various use cases and potential service requirements for AI agent communication within 6G systems. This document provides examples of use cases and service requirements contained in the 3GPP TR 22.870 and extrapolates possible requirements related to agent communication protocols.</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-stephan-ai-agent-6g/</t>
+          <t>https://datatracker.ietf.org/doc/draft-stephan-agentproto-6g-usecases/</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, October 2025; strong operator backing (Orange, Deutsche Telekom, Telefonica, China Mobile, Huawei). Requirements-oriented and important for 3GPP/IETF coordination. May be expired (April 2026); watch for an update. **EXPIRED on Datatracker** (expired 23 Apr 2026; checked 26 Aug 2026) — kept in the corpus deliberately; an expired draft is still evidence of what was proposed.</t>
+          <t>Revision -00, 13 Oct 2026. **RENAMED in place 28 Oct 2026 — SUPERSEDES `draft-stephan-ai-agent-6g`** (Replaced on Datatracker; successor not previously tracked). The re-slug moves the document under the `agentproto` prefix and reframes it around 3GPP TR 22.870's agent-communication use cases. Peripheral to delegated authorization — kept only because its predecessor was tracked. Prior narration: Revision -02, October 2025; strong operator backing (Orange, Deutsche Telekom, Telefonica, China Mobile, Huawei). Requirements-oriented and important for 3GPP/IETF coordination. May be expired (April 2026); watch for an update. **EXPIRED on Datatracker** (expired 23 Apr 2026; checked 26 Aug 2026) — kept in the corpus deliberately; an expired draft is still evidence of what was proposed.</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Revision -01 (May 2026) under the new slug — re-slugged from draft-oauth-transaction-tokens-for-agents-06; the -06 added the actchain delegation lineage, RAR-driven agentic_ctx, and a TTS check that blocks chain-splicing attacks. Conservative extension of the WG Transaction Tokens draft and an easier path to standardization.</t>
+          <t>Revision -01 (May 2026) under the new slug — re-slugged from draft-oauth-transaction-tokens-for-agents-06; the -06 added the actchain delegation lineage, RAR-driven agentic_ctx, and a TTS check that blocks chain-splicing attacks. Conservative extension of the WG Transaction Tokens draft and an easier path to standardization. **Updated 28 Oct 2026:** raised on the WIMSE list on 1 Oct 2026 by the author, who reports that **Amazon uses a similar approach internally and Reva.AI has launched support** for Transaction Tokens for agents based on this draft — a rare production-adoption claim for an individual agent draft. -03 announced as coming.</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Revision -10, 13 Jun 2026; author: Ryan Nelson (Authproof). At version 10, the most iterated individual draft in the pre-action authorization space. The commitment-before-execution architecture — sign before the agent runs, not after — is distinctive and directly addresses the prompt-injection attack surface.</t>
+          <t>Revision -10, 13 Jun 2026; author: Ryan Nelson (Authproof). At version 10, the most iterated individual draft in the pre-action authorization space. The commitment-before-execution architecture — sign before the agent runs, not after — is distinctive and directly addresses the prompt-injection attack surface. **Updated 28 Oct 2026:** now **-15 (22 Oct 2026)**. On 10 Oct the author asked the OAuth chairs whether the draft fits the charter and what adoption would require, candidly noting a single reference implementation. On the WIMSE list Jeff Lombardo (Amazon) pushed back on its premise that natural-language instructions are the primary authorization artifact, arguing the AS consent event already is a cryptographically attributable authorization.</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, Apr 25 2026; author: Karthik Rampalli (Glyphzero, Inc.) — same author as draft-rampalli-cross-org-delegation-mapping and draft-rampalli-scitt-capsule-provenance-binding (both in corpus). Presented at WIMSE WG as proposed new work at IETF 126 (Bangkok, Jul 2026). Cedar-policy static-analysis attenuation proofs are a unique contribution relative to other delegation-chain drafts. Note: draft-rampalli-cross-org-delegation-mapping (corpus) references the 'PEDIGREE model' — this is the normative definition.</t>
+          <t>Revision -00, Apr 25 2026; author: Karthik Rampalli (Glyphzero, Inc.) — same author as draft-rampalli-cross-org-delegation-mapping and draft-rampalli-scitt-capsule-provenance-binding (both in corpus). Presented at WIMSE WG as proposed new work at IETF 126 (Bangkok, Jul 2026). Cedar-policy static-analysis attenuation proofs are a unique contribution relative to other delegation-chain drafts. Note: draft-rampalli-cross-org-delegation-mapping (corpus) references the 'PEDIGREE model' — this is the normative definition.  **EXPIRED on Datatracker** (expired 26 Oct 2026; checked 28 Oct 2026) — kept in the corpus deliberately; an expired draft is still evidence of what was proposed.</t>
         </is>
       </c>
     </row>
@@ -4635,7 +4635,7 @@
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, Apr 21 2026; authors: Cheng Yang (BUPT), Zhiyuan Liu (Tsinghua), Aijun Wang (China Telecom). The task-coordination layer above the DMSC gateway routing; covers multi-domain and 6G/ITS scenarios. Distinct from OAuth-layer delegation in that it orchestrates task state rather than token issuance.</t>
+          <t>Revision -03, Apr 21 2026; authors: Cheng Yang (BUPT), Zhiyuan Liu (Tsinghua), Aijun Wang (China Telecom). The task-coordination layer above the DMSC gateway routing; covers multi-domain and 6G/ITS scenarios. Distinct from OAuth-layer delegation in that it orchestrates task state rather than token issuance.  **EXPIRED on Datatracker** (expired 23 Oct 2026; checked 28 Oct 2026) — kept in the corpus deliberately; an expired draft is still evidence of what was proposed.</t>
         </is>
       </c>
     </row>
@@ -4875,7 +4875,7 @@
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, 25 Aug 2026 (was -01, 5 Jul 2026); useful problem-statement companion to the OAuth recharter's 'Complex Delegation' milestone. Gap analysis directly motivates several other drafts in this corpus — a natural reference document for the OAuth WG scoping discussion.</t>
+          <t>Revision -03, 25 Aug 2026 (was -01, 5 Jul 2026); useful problem-statement companion to the OAuth recharter's 'Complex Delegation' milestone. Gap analysis directly motivates several other drafts in this corpus — a natural reference document for the OAuth WG scoping discussion. **Updated 28 Oct 2026:** now **-05 (27 Oct 2026)**, and the subject of an **OAuth WG virtual interim on 19 Oct 2026, "Agent Authorization – Use Cases and Gaps"**. List contributors are adding scenarios (a user-minted daily grant with a read/draft/send/act/spend authority ladder) under a mechanism-neutral framing. Its companions `chen-oauth-agent-intent-token` and `chen-oauth-rar-agent-extensions` were added this sweep.</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 3 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -00, 3 Aug 2026. Added in the Aug 2026 corpus sweep; not previously tracked. **Updated 28 Oct 2026:** the subject of a **WIMSE WG virtual interim on 7 Oct 2026**. The chairs then put a Request for Expression of Interest to the list on the problem statement — "many different workloads need to be identified to third parties without additional setup at the third party" — reporting strong interest in the room and stressing it was *not* an adoption call (21-message thread).</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>Revision -03, 28 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -03, 28 Jul 2026. Added in the Aug 2026 corpus sweep; not previously tracked. **Updated 28 Oct 2026: OAuth WG adoption call FAILED.** The chairs concluded on 16 Oct 2026 that "there is not enough support for this document at this point" — the same day they adopted Delegated SD-JWT. Remains an individual draft. Flanagan's 6 Oct post discusses the PoP/HTTP Message Signatures debate that preceded the decision.</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>Revision -11, 23 Jul 2026; entered the RFC Editor queue (touched 13 Aug 2026, rfceditor state 'In Progress'). WG-adopted draft. Added in the Aug 2026 corpus sweep; not previously tracked.</t>
+          <t>Revision -11, 23 Jul 2026; entered the RFC Editor queue (touched 13 Aug 2026, rfceditor state 'In Progress'). WG-adopted draft. Added in the Aug 2026 corpus sweep; not previously tracked. **Updated 28 Oct 2026:** still in the RFC Editor queue, but the RFC Editor sub-state is now **"blocked"** (waiting on another document) rather than in progress. No RFC number yet.</t>
         </is>
       </c>
     </row>
@@ -8655,7 +8655,7 @@
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 2 Apr 2026. **Family completion, added 26 Aug 2026.** Dick Hardt, a named author voice in this corpus — the corpus tracked 2 of his drafts. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only. The HTTP header binding for AAuth. The corpus tracked draft-hardt-oauth-aauth-protocol and tagged it OUTLIER while its own companion headers draft went untracked.</t>
+          <t>Revision -00, 2 Apr 2026. **Family completion, added 26 Aug 2026.** Dick Hardt, a named author voice in this corpus — the corpus tracked 2 of his drafts. Surfaced by cross-checking Heather Flanagan's standards-tracker, then confirmed by author-prefix query on Datatracker; missed by earlier sweeps because discovery matched topic keywords against draft *names* only. The HTTP header binding for AAuth. The corpus tracked draft-hardt-oauth-aauth-protocol and tagged it OUTLIER while its own companion headers draft went untracked.  **EXPIRED on Datatracker** (expired 4 Oct 2026; checked 28 Oct 2026) — kept in the corpus deliberately; an expired draft is still evidence of what was proposed. The first AAuth-family document to expire — notable a week after Hardt filed three new AAuth extensions, which suggests the header binding is being folded into the protocol draft rather than abandoned.</t>
         </is>
       </c>
     </row>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="F281" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 30 Apr 2026. **This is the Actor Profile itself** — the anchor draft this corpus repeatedly refers to, and which draft-mw-oauth-actor-chain directly responds to. Defines depth-1+ chain validation, cycle-aware construction, and bearer-to-PoP upgrade; the most complete actor-representation profile to date. **Correction, 4 Sep 2026:** the 26 Aug 2026 sweep re-added this draft as "the most consequential single omission" its cross-check found, but it had in fact been tracked since the corpus's early days under a URL pointing at the -00 HTML rendering, which the slug diff did not match. The two rows were silent duplicates; they were merged on 4 Sep 2026, keeping this canonical Datatracker URL and folding in the older row's technical narration. The lesson is the mirror image of the 26 Aug one: **diff on normalised draft slugs, not on URLs**, or a rev-suffixed link hides an existing row.</t>
+          <t>Revision -00, 30 Apr 2026. **This is the Actor Profile itself** — the anchor draft this corpus repeatedly refers to, and which draft-mw-oauth-actor-chain directly responds to. Defines depth-1+ chain validation, cycle-aware construction, and bearer-to-PoP upgrade; the most complete actor-representation profile to date. **Correction, 4 Sep 2026:** the 26 Aug 2026 sweep re-added this draft as "the most consequential single omission" its cross-check found, but it had in fact been tracked since the corpus's early days under a URL pointing at the -00 HTML rendering, which the slug diff did not match. The two rows were silent duplicates; they were merged on 4 Sep 2026, keeping this canonical Datatracker URL and folding in the older row's technical narration. The lesson is the mirror image of the 26 Aug one: **diff on normalised draft slugs, not on URLs**, or a rev-suffixed link hides an existing row. **Updated 28 Oct 2026:** revised to -01 on 9 Oct 2026, together with `actor-proofs` and `actor-receipts` — the three Actor drafts moved as a set.</t>
         </is>
       </c>
     </row>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="F356" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 3 Sep 2026. **Added 4 Sep 2026 sweep.** **The most directly on-charter new draft in this window.** It states the Complex Delegation problem precisely: RFC 8693's nested `act` claim records prior actors but is *informational only* and cannot enforce attenuation past depth two. Builds the enforcement on RFC 9396 RAR carried in RFC 9068 JWTs, with each hop cryptographically linked to its parent and verifiable offline with no AS round-trip. Compare McGuinness's `oauth-mission-attenuation`, which solves the same AS-in-the-hot-path problem inside the Mission-Bound family. Referenced by both `hamr-oauth-agent-delegation` and `hassan-oauth-agent-delegation`.</t>
+          <t>Revision -01, 3 Sep 2026. **Added 4 Sep 2026 sweep.** **The most directly on-charter new draft in this window.** It states the Complex Delegation problem precisely: RFC 8693's nested `act` claim records prior actors but is *informational only* and cannot enforce attenuation past depth two. Builds the enforcement on RFC 9396 RAR carried in RFC 9068 JWTs, with each hop cryptographically linked to its parent and verifiable offline with no AS round-trip. Compare McGuinness's `oauth-mission-attenuation`, which solves the same AS-in-the-hot-path problem inside the Mission-Bound family. Referenced by both `hamr-oauth-agent-delegation` and `hassan-oauth-agent-delegation`. **Updated 28 Oct 2026:** now -03 (28 Oct 2026). Among the most-discussed drafts on the WIMSE list this window — an IANA defect and scope-vocabulary issues in -01, trust-anchor provenance (§6.4) and principal standing at time of use in -02, which shipped with a new vector set.</t>
         </is>
       </c>
     </row>
@@ -11670,7 +11670,7 @@
       </c>
       <c r="C357" s="5" t="inlineStr">
         <is>
-          <t>This document specifies a profile for delegating authorization to automated agents across administrative domains. It defines an HTTP header field, Agent-Delegation, that carries a chain of attenuated delegation links. Each link narrows the scope, tightens or holds a set of floor conditions, and shortens or holds the expiry of its parent. A verifier checks every link in the chain, not only the last, and rejects the chain if any link violates attenuation. The profile is deliberately agnostic to the credential format and to the nature of the entity that issues floor attestations; it specifies required properties, not a specific encoding or a specific kind of issuer. It composes with, and does not replace, existing work on agent credential provisioning and posture.</t>
+          <t>This document builds on HTTP Message Signatures (RFC 9421) for requests that automated agents send on behalf of people. RFC 9421 shows who signed a request. It does not show who the agent acts for, or what the agent may do. This document defines an HTTP header field, Agent-Delegation, that carries a chain of delegation links. Each link can only narrow the scope, floors, and expiry of the link before it, and a verifier checks every link. Floors cover two things. The first is the person or account behind the agent: an Attestation Issuer, such as a mobile network operator or an identity- document check, answers with a signed yes or no, bound to the verifier's nonce and to an expiry, and never returns the value behind the answer. The second is what the agent may do: each call has a class, r, w, or x, read as in chmod, with an optional count per class, and a signed menu gives the class of each call. A deployment can set this scope for each job when the job starts. This document does not define a credential format, an identity system, or revocation.</t>
         </is>
       </c>
       <c r="D357" s="9" t="inlineStr">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="F357" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 2 Sep 2026. **Added 4 Sep 2026 sweep.** **SUPERSEDES draft-hassan-oauth-agent-delegation** (-00, 31 Aug 2026), confirmed by a Datatracker `replaces` relation; the two carry identical titles and abstracts, and only this one is tracked. A header-field approach — `Agent-Delegation` carrying the attenuation chain — where `asor-wimse-agent-delegation-chain` uses a token profile; the pair is a clean design contrast on the same problem. Deliberately credential-format-agnostic. Normatively references RFC 9421 and informatively `schrock-ep-authorization-receipts` and `das-agentic-tool-binding`, both tracked here.</t>
+          <t>Revision -03, 22 Oct 2026 (tracked at -01, 2 Sep 2026). **Added 4 Sep 2026 sweep.** **SUPERSEDES draft-hassan-oauth-agent-delegation** (-00, 31 Aug 2026), confirmed by a Datatracker `replaces` relation; the two carry identical titles and abstracts, and only this one is tracked. A header-field approach — `Agent-Delegation` carrying the attenuation chain — where `asor-wimse-agent-delegation-chain` uses a token profile; the pair is a clean design contrast on the same problem. Deliberately credential-format-agnostic. Normatively references RFC 9421 and informatively `schrock-ep-authorization-receipts` and `das-agentic-tool-binding`, both tracked here. **Updated 28 Oct 2026 (raised by the maintainer):** two revisions since tracking, and the design has sharpened. -03 defines two kinds of *floor* a link can only narrow: the person or account behind the agent — an Attestation Issuer (e.g. a mobile network operator or identity-document check) answers a signed yes/no bound to the verifier's nonce and an expiry, never disclosing the underlying value — and what the agent may do, as per-call classes r/w/x "read as in chmod" with optional counts, against a signed menu. Still explicitly defines no credential format, identity system or revocation. Read against `hulea-wimse-agent-mandate` (added this sweep), which supplies what hamr leaves out: evidence that the delegator was entitled to delegate.</t>
         </is>
       </c>
     </row>
@@ -13285,17 +13285,17 @@
       </c>
       <c r="B411" s="5" t="inlineStr">
         <is>
-          <t>draft-gilda-wimse-agent-audit-record — An Audit Record Format for AI Agent Authorization Decisions</t>
+          <t>draft-gilda-audit-agent-audit-record — An Audit Record Format for AI Agent Authorization Decisions</t>
         </is>
       </c>
       <c r="C411" s="5" t="inlineStr">
         <is>
-          <t>This document defines a record format for AI agent authorization decisions. The format is one in-toto predicate type, signed inside a DSSE envelope. It carries the seven minimum audit fields that the WIMSE AI Identity Management System framework requires, and two properties that make those fields checkable: a canonicalization contract, and both the authorization decision and the observed effect with a derived three-valued agreement between them. That framework places the record format out of scope and takes no IANA action. This document supplies the format. It defines no policy.</t>
+          <t>This document defines a record format for AI agent authorization decisions and the effects that followed them. The format is one in- toto predicate type, signed inside a DSSE envelope. A record carries the decision and the observed effect with a derived agreement between them, whether the decision point could evaluate the request and how fresh each input it relied on was, and a canonicalization contract under which a party that trusts neither the agent nor its operator recomputes the record's consistency from its bytes. The document also defines what a party that retains a record keeps beside it, so that the record can later be dated from anchors that party does not control. The format carries the seven minimum audit fields of the WIMSE AI Identity Management System framework, and it is offered as a data model for the audit records the proposed AUDIT working group would specify. It defines no policy.</t>
         </is>
       </c>
       <c r="D411" s="9" t="inlineStr">
         <is>
-          <t>https://datatracker.ietf.org/doc/draft-gilda-wimse-agent-audit-record/</t>
+          <t>https://datatracker.ietf.org/doc/draft-gilda-audit-agent-audit-record/</t>
         </is>
       </c>
       <c r="E411" s="5" t="inlineStr">
@@ -13305,7 +13305,7 @@
       </c>
       <c r="F411" s="5" t="inlineStr">
         <is>
-          <t>Revision -01, 27 Sep 2026. **Added 29 Sep 2026 sweep.** An in-toto predicate in a DSSE envelope carrying the **seven minimum audit fields the WIMSE AIMS framework requires** — so it is a downstream profile of `ietf-wimse-aims`, adopted as a WG draft twelve days earlier and added in this same sweep. Its distinguishing move is recording both the authorization decision *and* the observed effect, with a derived three-valued agreement between them. Compare `bradleyb-audit-decision-records`.</t>
+          <t>Revision -02, 27 Oct 2026. **RENAMED in place 28 Oct 2026 — SUPERSEDES `draft-gilda-wimse-agent-audit-record`** (Replaced on Datatracker; the successor was not tracked, so per the SUPERSEDED rule the row was renamed rather than duplicated). The slug moved from `wimse` to `audit` after the author asked the WIMSE chairs for an adoption call on 9 Oct, Brian Campbell suggested the work belongs in the AUDIT BoF, and the chairs declined to call adoption (12 Oct). Two implementers had reported 47/47 on its published test records. One of three AIMS audit-record mappings to arrive in this window, with `zambo-aer1-wimse-mapping` and `thaha-wimse-agent-evidence-binding`. Prior narration: Revision -01, 27 Sep 2026. **Added 29 Sep 2026 sweep.** An in-toto predicate in a DSSE envelope carrying the **seven minimum audit fields the WIMSE AIMS framework requires** — so it is a downstream profile of `ietf-wimse-aims`, adopted as a WG draft twelve days earlier and added in this same sweep. Its distinguishing move is recording both the authorization decision *and* the observed effect, with a derived three-valued agreement between them. Compare `bradleyb-audit-decision-records`.</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
       </c>
       <c r="F414" s="5" t="inlineStr">
         <is>
-          <t>Revision -02, 29 Sep 2026 (filed the day of this sweep). **Added 29 Sep 2026 sweep.** **One of the sweep's most consequential additions.** Every delegation-chain draft in this corpus specifies the shape of conveyed authority; this one states the verifier's half, on the observation that two verifiers can check the same chain, both report success, and enforce different policy. Four fail-closed rules drawn from a Grant &amp; Autonomy Lifecycle model. Read directly against `asor-wimse-agent-delegation-chain`, `hamr-oauth-agent-delegation` and `mcguinness-oauth-mission-attenuation`.</t>
+          <t>Revision -02, 29 Sep 2026 (filed the day of this sweep). **Added 29 Sep 2026 sweep.** **One of the sweep's most consequential additions.** Every delegation-chain draft in this corpus specifies the shape of conveyed authority; this one states the verifier's half, on the observation that two verifiers can check the same chain, both report success, and enforce different policy. Four fail-closed rules drawn from a Grant &amp; Autonomy Lifecycle model. Read directly against `asor-wimse-agent-delegation-chain`, `hamr-oauth-agent-delegation` and `mcguinness-oauth-mission-attenuation`. **Updated 28 Oct 2026:** now -04 (11 Oct 2026), revving roughly weekly; -03 added a fifth evaluation input and split disclosure from transient refusals. Requested IETF 127 agenda time alongside the delegation drafts.</t>
         </is>
       </c>
     </row>
@@ -14445,7 +14445,7 @@
       </c>
       <c r="F449" s="5" t="inlineStr">
         <is>
-          <t>Revision -00, 29 Sep 2026 (filed the day of this sweep). **Added 29 Sep 2026 sweep.** Post-quantum requirements for agent identity, argued from an angle nothing else here takes: **a delegation record retained as evidence must stay verifiable long after the signing key is retired**, so it needs anchoring in trusted time and renewal before its algorithms weaken. Long-settled practice for archived signatures, rarely required for agent delegation. Relevant to every receipt and evidence format this sweep added.</t>
+          <t>Revision -00, 29 Sep 2026 (filed the day of this sweep). **Added 29 Sep 2026 sweep.** Post-quantum requirements for agent identity, argued from an angle nothing else here takes: **a delegation record retained as evidence must stay verifiable long after the signing key is retired**, so it needs anchoring in trusted time and renewal before its algorithms weaken. Long-settled practice for archived signatures, rarely required for agent delegation. Relevant to every receipt and evidence format this sweep added. **Updated 28 Oct 2026:** revised to -01 (28 Oct 2026) and posted to the WIMSE list as a requirements input usable by AIMS, workload-creds and the delegation drafts. The useful point is about delegation records kept *as evidence*: an RFC 3161 timestamp is itself a signature, so a quantum adversary could back-date classical timestamps — retained records need post-quantum or publicly witnessed anchoring, applied early.</t>
         </is>
       </c>
     </row>
@@ -14956,6 +14956,2436 @@
       <c r="F466" s="5" t="inlineStr">
         <is>
           <t>Revision -01, 8 Sep 2026. **Added 29 Sep 2026 sweep.** A framework document for the DAWN WG, positioning itself against the existing DAWN suite the corpus already tracks — terminology, requirements, use cases, gap analysis, mechanism survey and the Minimum Discoverable Information model. Framework rather than mechanism, so read it as the DAWN counterpart to `lundholm-kaif`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="5" t="n">
+        <v>466</v>
+      </c>
+      <c r="B467" s="5" t="inlineStr">
+        <is>
+          <t>bofreq-kuhlewind-audit-agent-use-of-delegation-and-interaction-traceability — AUDIT: Agent Use of Delegation and Interaction Traceability (BoF request)</t>
+        </is>
+      </c>
+      <c r="C467" s="5" t="inlineStr">
+        <is>
+          <t>Autonomous and semi-autonomous agents act for users across multiple services and administrative domains. Existing logs, tracing and authorization frameworks capture individual aspects of behaviour but lack interoperable support for correlating user intent, delegation chains, authorization state and resulting actions across domains — who initiated an action, under which authority, and how permissions evolved during execution. AUDIT aims to define interoperable protocol mechanisms and data models to record, exchange and verify audit-relevant information across a whole chain of user, agents, sub-agents and tools: an architectural concept, common audit-record models, propagation of audit context, and integration with OAuth, HTTP and attestation/transparency frameworks. Out of scope: auditing the underlying model, training data or inference.</t>
+        </is>
+      </c>
+      <c r="D467" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/bofreq-kuhlewind-audit-agent-use-of-delegation-and-interaction-traceability/</t>
+        </is>
+      </c>
+      <c r="E467" s="5" t="inlineStr">
+        <is>
+          <t>IETF (BoF request)</t>
+        </is>
+      </c>
+      <c r="F467" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 8 Oct 2026; state **Approved** — a WG-forming BoF at **IETF 127** (San Francisco, Nov 2026). **Added 28 Oct 2026 sweep.** Proponents Mirja Kühlewind (Ericsson), Henk Birkholz and Pam Dingle (Microsoft); proposed chair Yaroslav Rosomakho; responsible ADs: Security. **This is the HUB author's work becoming a WG candidate:** Kühlewind's `kuehlewind-audit-architecture` composes 10+ corpus drafts, and the BoF lists OAuth, WIMSE, SCITT, RATS, HTTPbis, Web Bot Auth, DAWN and AgentProto as technology overlap. Already pulling work toward it: on 12 Oct the WIMSE chairs declined an adoption call for `gilda-audit-agent-audit-record` after Brian Campbell suggested it belongs in AUDIT. A predecessor request (`bofreq-kuhlewind-agent-use-of-delegation-and-interaction-traceability-audit`, -02, Jul 2026) was not tracked. If the BoF charters a WG, every audit-record draft added this sweep becomes a candidate input — watch the IETF 127 outcome.</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="5" t="n">
+        <v>467</v>
+      </c>
+      <c r="B468" s="5" t="inlineStr">
+        <is>
+          <t>draft-gco-oauth-delegate-sd-jwt — Delegate SD-JWT</t>
+        </is>
+      </c>
+      <c r="C468" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies an extension to Selective Disclosure JSON Web Tokens to support further delegation from the Holder to a Delegate Holder. This is done by allowing the Key Binding JWT to also be an SD-JWT, optionally with its own Key Binding. This has particular applicability to Agentic systems.</t>
+        </is>
+      </c>
+      <c r="D468" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-gco-oauth-delegate-sd-jwt/</t>
+        </is>
+      </c>
+      <c r="E468" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F468" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 22 Apr 2026. **Added 28 Oct 2026 sweep.** **ADOPTED by the OAuth WG** — the chairs called consensus on the list on 16 Oct 2026 ("the WG has decided to adopt this draft"), after a 17-message adoption call. Author Gareth Oliver (Google). Lets the Key Binding JWT of an SD-JWT itself be an SD-JWT with its own key binding, so a Holder can delegate onward to a Delegate Holder — the abstract names agentic systems as the target. **The first OAuth WG adoption in the agent-delegation space since the recharter, but note it was adopted under the existing Digital Credentials work item, not as a Complex Delegation milestone.** Caveat: the individual -00 was filed 22 Apr 2026 and expired 23 Oct, a week *after* adoption; the WG -00 had not been posted at this sweep. When it appears it will `replace` this row — re-test the relation next sweep. Filed 22 Apr 2026 and never revised; **EXPIRED on Datatracker** 24 Oct 2026 — it predates this sweep's window and surfaced only because expiry updates a draft's timestamp. Kept per the standing rule: an expired draft is still evidence of what was proposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="5" t="n">
+        <v>468</v>
+      </c>
+      <c r="B469" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-oauth-mission-resource-access — Mission Resource Access Profile for OAuth 2.0</t>
+        </is>
+      </c>
+      <c r="C469" s="5" t="inlineStr">
+        <is>
+          <t>This document defines mission_resource_access, a general-purpose OAuth 2.0 Rich Authorization Requests (RAR) authorization_details type for Mission-Bound Authorization for OAuth 2.0 (the "issuance profile"). An entry names one resource, matched exactly or by path prefix; the actions permitted there, including wildcard action families; machine-actionable constraints, including a registered Common Constraints vocabulary; and a per-entry delegation policy. The document also defines how two entries compare and narrow, how a resource server enforces an entry, when an entry can be projected to OAuth scope, and how an authorization server declares its support for these semantics. The issuance profile is type-agnostic: a deployment can support this type, another authorization_details type, or both.</t>
+        </is>
+      </c>
+      <c r="D469" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-mcguinness-oauth-mission-resource-access/</t>
+        </is>
+      </c>
+      <c r="E469" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F469" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 22 Oct 2026. **Added 28 Oct 2026 sweep.** **MOVED from the Mission-Bound (Pre-pub) tab — the second Mission-Bound family draft to be filed on Datatracker** (22 Oct 2026), after `mcguinness-oauth-mission` itself. The standing watch item fired. Defines `mission_resource_access`, the general-purpose RAR `authorization_details` type split out of the OAuth binding: exact/prefix resource matching, action namespaces and wildcard families, the Common Constraints vocabulary, per-entry delegation policy, and the subset/intersection algebra. Manifest: group bindings-substrate; role companion; spec maturity experimental; maintenance active. Filed the day after `oauth-mission-01` and four days before the OAuth WG's 26 Oct interim devoted to Mission-Bound Authorization — the attenuation algebra is the piece a WG would need first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="5" t="n">
+        <v>469</v>
+      </c>
+      <c r="B470" s="5" t="inlineStr">
+        <is>
+          <t>draft-hulea-wimse-agent-mandate — Verifiable Mandates for Agents Acting Across Administrative Domains</t>
+        </is>
+      </c>
+      <c r="C470" s="5" t="inlineStr">
+        <is>
+          <t>This document defines how a relying party in one administrative domain validates the mandate under which a software agent, including an AI agent, acts for a principal in another domain. Its distinctive element is evidence of the delegator's authority: a statement from an authority source about which permissions the person or entity granting the mandate may delegate to agents, kept separate from the statement that the mandate was granted. The document specifies the mandate format with precisely defined limit semantics, a deterministic validation procedure driven by an explicit validation profile and kept separate from the relying party's authorization decision, the attribution of every validated claim to the issuer and role that asserted it, rules for enforcing the mandate after token exchange, and the boundary between this protocol and a trust framework. It reuses JSON Web Tokens, OAuth 2.0 Token Exchange, Rich Authorization Requests, WIMSE workload credentials and HTTP Message Signatures, Token Status Lists, and Entity Attestation Tokens.</t>
+        </is>
+      </c>
+      <c r="D470" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hulea-wimse-agent-mandate/</t>
+        </is>
+      </c>
+      <c r="E470" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F470" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 24 Oct 2026. **Added 28 Oct 2026 sweep.** Author Claudiu Hulea (Braincap SRL). **Raised by the maintainer, and the most-discussed new draft on the WIMSE list this window** (11-message thread). Its distinctive element is *evidence of the delegator's authority*: an Authority Assertion from an authority source stating which permissions the person granting the mandate may delegate, kept separate from the statement that the mandate was granted. No other chain draft in the corpus separates "was it granted" from "was the grantor entitled to grant it". Also specifies a deterministic validation procedure driven by an explicit Validation Profile and kept separate from the RP's authorization decision — the same separation `jackson-wimse-evaluation` argues for from the verifier side. Has **independent test vectors** within three days of filing (`Silentpartnercoding/wimse-agent-mandate-vectors`, Industry tab). Read against `asor-wimse-agent-delegation-chain`, `hamr-oauth-agent-delegation` and `ietf-wimse-aims`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="5" t="n">
+        <v>470</v>
+      </c>
+      <c r="B471" s="5" t="inlineStr">
+        <is>
+          <t>draft-liu-mcguinness-oauth-bounded-work — OAuth 2.0 Bounded Work Authorization</t>
+        </is>
+      </c>
+      <c r="C471" s="5" t="inlineStr">
+        <is>
+          <t>OAuth 2.0 provides mechanisms for requesting and granting access, constraining access tokens, and managing their lifecycle. It does not define a common way to identify the work a user approved and to associate that work's bounds and termination with the credentials issued for it. When an AI agent acts on a user's behalf, that work is what most needs governing: the agent's authority should come from the approval of a bounded piece of work, should stay within the bounds the user approved, and should end when the work is done or the user withdraws it. This document presents a use case in which a user withdraws an agent's approved work and the agent's further operations are denied, and identifies the semantics that independently implemented clients, Authorization Servers, and Resource Servers need to share to deliver that outcome. It then describes a framework for approved bounded work, built on three objects: a bounded work proposal, the governing authorization established when it is approved, and approval evidence, a durable record of the authorization decision and the approved bounds. Credentials issued for the work are associated with the governing authorization, and ending the authorization has defined consequences for further issuance and, within a stated acceptance window, for resource access. This version specifies no wire formats and requests no IANA actions. It is a direction-setting document: its goal is agreement on the problem and the conceptual model, with details left to subsequent revisions and working group discussion.</t>
+        </is>
+      </c>
+      <c r="D471" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-liu-mcguinness-oauth-bounded-work/</t>
+        </is>
+      </c>
+      <c r="E471" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F471" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 17 Oct 2026. **Added 28 Oct 2026 sweep.** **McGuinness co-authored** (person 141623) with Dapeng Liu (Alibaba) — the slug does not begin with `mcguinness`, so prefix enumeration would never find it; settled from `documentauthor`. Gives OAuth a common way to identify *the work a user approved* and tie that work's bounds and termination to the credentials issued for it — the Mission idea expressed without the Mission vocabulary, by the same Alibaba author who is running the OAuth list's fine-grained-authorization call for interest (`liu-oauth-authorization-schemas`). Read it as a convergence document between the Mission-Bound line and that design-team proposal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="5" t="n">
+        <v>471</v>
+      </c>
+      <c r="B472" s="5" t="inlineStr">
+        <is>
+          <t>draft-mora-oauth-entity-profiles — OAuth 2.0 Entity Profiles</t>
+        </is>
+      </c>
+      <c r="C472" s="5" t="inlineStr">
+        <is>
+          <t>This specification introduces Entity Profiles as a mechanism to categorize OAuth 2.0 entities—clients and subjects—based on their operational context. Entity Profiles provide structured descriptors for the client initiating the OAuth flow and the subject represented in tokens. This document defines new JWT Claim names and metadata parameters for use in JWTs issued or consumed in OAuth flows, including but not limited to access tokens, ID tokens, JWT authorization grant assertions, and transaction tokens, as well as in token introspection responses, dynamic client registration, and Authorization Server metadata. It also defines vocabulary for classifying acting entities within delegation chains.</t>
+        </is>
+      </c>
+      <c r="D472" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-mora-oauth-entity-profiles/</t>
+        </is>
+      </c>
+      <c r="E472" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F472" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 16 Oct 2026. **Added 28 Oct 2026 sweep.** **McGuinness co-authored** (person 141623), with Sreyantha Chary Mora and Pamela Dingle (Microsoft) — another McGuinness draft invisible to `mcguinness` prefix enumeration. Defines Entity Profiles: structured descriptors categorising the client that initiates a flow and the subject a token represents by operational context, with new JWT claims and metadata. That is the hook an RS needs to tell an agent from a person from a workload without inventing a claim per deployment. Introduced on the OAuth list this window (6-message thread). Already at -02, so earlier revisions predate this sweep's window and were missed by keyword search — the slug carries no agent term.</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="5" t="n">
+        <v>472</v>
+      </c>
+      <c r="B473" s="5" t="inlineStr">
+        <is>
+          <t>draft-morrison-acts-for — Acts-For: Signing In to a Website with a ~handle, for a Person or an Agent Acting for One</t>
+        </is>
+      </c>
+      <c r="C473" s="5" t="inlineStr">
+        <is>
+          <t>Acts-For lets a person sign in to any website with the ~handle they already hold, and lets an AI agent sign in or register at that website on the person's behalf. Neither needs a username, a password or an account per site. A website joins by publishing one DNS record. A person signs in through a standard OpenID Connect authorization code flow and the site receives a short-lived token naming the person by a number unique to that site. An agent obtains a short-lived pass from the issuer over the Model Context Protocol and presents it to the site. The pass names the same per-site number, the agent's own key and ~handle, and the limits the person set. The site checks it against a published key and calls nobody.</t>
+        </is>
+      </c>
+      <c r="D473" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-acts-for/</t>
+        </is>
+      </c>
+      <c r="E473" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F473" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 22 Oct 2026. **Added 28 Oct 2026 sweep.** Take-in-full (Morrison, person 161913). Lets a person sign in to any site with an existing `~handle`, and lets an AI agent sign in or register *on that person's behalf*, with the site joining by publishing one DNS record and the person authenticating through standard OIDC. The first Morrison draft that meets the web's front door rather than the family's own substrate, and the one most directly about acting-for — the family's actor-chain question restated as a login.</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="5" t="n">
+        <v>473</v>
+      </c>
+      <c r="B474" s="5" t="inlineStr">
+        <is>
+          <t>draft-morrison-did-alter-method — The did:alter Decentralized Identifier Method</t>
+        </is>
+      </c>
+      <c r="C474" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies the did:alter Decentralized Identifier method. A did:alter identifier names a ~handle together with the DNS zone that publishes the handle's signed envelope, and it resolves to a DID document by running the envelope recognition procedure of the companion specification for discovering Model Context Protocol servers through DNS TXT records, then expressing the verified envelope's Ed25519 key as a verification method. The identifier agrees with the handle grammar of the alter URI scheme and with the did:alter form already written by the identity-attributed commits specification. The method introduces no new record, no new cryptographic primitive and no registry of its own: create, update and deactivate are the publication, replacement and revocation of that envelope, and read is its verification. The document also sets out what the method cannot yet do, because the envelope record it reads carries no key history, and revocation cannot presently be observed from DNS alone.</t>
+        </is>
+      </c>
+      <c r="D474" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-did-alter-method/</t>
+        </is>
+      </c>
+      <c r="E474" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F474" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 22 Oct 2026. **Added 28 Oct 2026 sweep.** Take-in-full (Morrison). Specifies a `did:alter` DID method that names a `~handle` plus the DNS zone publishing its signed envelope, resolving by the envelope procedure of the family's MCP DNS discovery draft. Infrastructure for the family rather than delegation per se: it makes the `~handle` primitive addressable from the DID ecosystem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="5" t="n">
+        <v>474</v>
+      </c>
+      <c r="B475" s="5" t="inlineStr">
+        <is>
+          <t>draft-morrison-claim-currency — Claim Currency: A Read-Time Decay Evaluator and Observation-Gated Re-Assertion Discipline for Concurrent Readers of a Reconciled Substrate</t>
+        </is>
+      </c>
+      <c r="C475" s="5" t="inlineStr">
+        <is>
+          <t>This memo specifies a read-time freshness evaluator and an observation-gated re-assertion discipline for concurrent autonomous readers of a single reconciled substrate history. For every claim read from the substrate, a three-state currency band (FRESH, AGING, STALE) is derived at read time from the durable history and is never stored. A claim whose derived band is not FRESH MUST NOT be re- emitted as current and MUST NOT ground a new durable claim; the sole transition back to currency is a fresh observation of the claim's basis, enforced at the substrate's append stage rather than at any reader's discretion. The memo is the claim-layer consumer that two companion specifications, Substrate-Observation as an Alternative to Envelope Coordination and the Substrate-Provenance Annotation Grammar, each left unspecified. The contribution is a specific composition: a read-time-derived band, a decay clock measured in missing observations learned from a basis's own change cadence, an append-stage rejection of any claim citing a basis that is no longer the head of its lineage, and observation as the only admissible refresh. No new substrate is standardised; the discipline composes with substrate that already exists.</t>
+        </is>
+      </c>
+      <c r="D475" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-claim-currency/</t>
+        </is>
+      </c>
+      <c r="E475" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F475" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 23 Oct 2026. **Added 28 Oct 2026 sweep.** Take-in-full (Morrison). A read-time decay evaluator for claims plus observation-gated re-assertion — a claim's weight falls with age unless it is re-observed. Note the overlap with Watts's continuity/evidence work and `sergeev-claim-boundaries`: three independent authors are now specifying when a claim stops being relied upon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="5" t="n">
+        <v>475</v>
+      </c>
+      <c r="B476" s="5" t="inlineStr">
+        <is>
+          <t>draft-morrison-schrock-identity-evidence-binding — Identity Evidence for Approver Enrollment and Payee Destination Binding</t>
+        </is>
+      </c>
+      <c r="C476" s="5" t="inlineStr">
+        <is>
+          <t>This document profiles how a relying party uses external identity evidence when it admits a consequential action, without that evidence ever standing in for permission. It defines two separate assertions, approver enrollment and payee destination binding, an authenticated binding from the exact evidence bytes to the action they support, offline status evidence with a freshness bound the relying party chooses, and the refusals that follow when any of it is missing. It applies to the pre-execution Authorization Bundle of EP Authorization Receipts and to the Command Authority Envelope for operational technology, and through the action digest to the Binding Moment Envelope.</t>
+        </is>
+      </c>
+      <c r="D476" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-morrison-schrock-identity-evidence-binding/</t>
+        </is>
+      </c>
+      <c r="E476" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F476" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 22 Oct 2026. **Added 28 Oct 2026 sweep.** **Cross-family: Morrison (person 161913) and Schrock (person 163567), both take-in-full** — the first co-authored draft between two of the corpus's take-in-full families. Identity evidence for approver enrollment and payee-destination binding: who may approve, and where money may go, bound to evidence. Joins the EMILIA evidence stack to the Morrison `~handle` substrate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="5" t="n">
+        <v>476</v>
+      </c>
+      <c r="B477" s="5" t="inlineStr">
+        <is>
+          <t>draft-sharif-typed-evidence-record — The Typed-Evidence Record: A Legally-Operative, Trust-Graded Record Format for Machine-Generated Evidence</t>
+        </is>
+      </c>
+      <c r="C477" s="5" t="inlineStr">
+        <is>
+          <t>A tamper-evident record establishes that data has not been altered. It does not, by itself, establish what legally-operative fact the data evidences, nor how far the data may be relied upon. This document defines the Typed-Evidence Record (TER): an interoperable record format in which a machine-generated record, such as a record of an action taken by an autonomous agent, is expressed as a set of legally-operative facts, carries an evidence grade reflecting its level of cryptographic attestation, carries a per-fact robustness indication, and carries the result of an independent integrity verification of its source. A Typed-Evidence Record binds to, and does not replace, the underlying signed record it describes. This document specifies the record format and the requirements a record and a relying party MUST meet to be interoperable. It does not specify how the legally-operative facts are produced from a source record; that is an implementation concern outside the scope of this document.</t>
+        </is>
+      </c>
+      <c r="D477" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-sharif-typed-evidence-record/</t>
+        </is>
+      </c>
+      <c r="E477" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F477" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 3 Oct 2026. **Added 28 Oct 2026 sweep.** Take-in-full (Sharif, person 161179); takes the tracked Sharif family to 15. A record format that states what *legally operative fact* a machine-generated record evidences and how far it may be relied upon, with trust grading — tamper-evidence alone says neither. Extends the Sharif audit-trail line toward admissibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="5" t="n">
+        <v>477</v>
+      </c>
+      <c r="B478" s="5" t="inlineStr">
+        <is>
+          <t>draft-drake-email-hardware-attestation — Hardware Attestation for Email Sender Verification</t>
+        </is>
+      </c>
+      <c r="C478" s="5" t="inlineStr">
+        <is>
+          <t>This document defines two email bindings for proving properties of an automated sender using the durable identity and anchor architecture of the Agent Identity Registry System (AIRS). Mode 1 carries a detached CMS signature made by a message-signing proof key. It can provide manufacturer-rooted hardware provenance, Registrar-backed AIRS identity binding, or both. Mode 2 carries a per-message SD-JWT that allows a Registrar to assert selected properties without requiring disclosure of the sender's canonical AIRS identifier. The AIRS identity0 model, canonical aid identifier, trust tiers, anchor semantics, enrollment rules, and Registrar trust boundary are defined by [I-D.drake-agent-identity-problem-statement] and [I-D.drake-agent-identity-registry]. Authoritative resolution of the current Registrar/OAuth issuer is defined by [I-D.drake-agent-identity-resolution]. This document does not redefine those concepts; it defines how email messages bind to and verify them.</t>
+        </is>
+      </c>
+      <c r="D478" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-drake-email-hardware-attestation/</t>
+        </is>
+      </c>
+      <c r="E478" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F478" s="5" t="inlineStr">
+        <is>
+          <t>Revision -03, 27 Oct 2026. **Added 28 Oct 2026 sweep.** Drake family (person 160218), taken as a family on 29 Sep 2026. **Replaces `draft-drake-email-tpm-attestation`** (untracked). Two email bindings proving properties of an automated sender from the AIRS durable-identity and anchor architecture — the registry family's first application binding, and a reminder that agent identity is being specified for mail, not just HTTP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="5" t="n">
+        <v>478</v>
+      </c>
+      <c r="B479" s="5" t="inlineStr">
+        <is>
+          <t>draft-watts-ai-identity — AID-1: A Cryptographically Bindable Identity and Provenance Architecture for AI Systems</t>
+        </is>
+      </c>
+      <c r="C479" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies AID-1, a provider-independent architecture for representing and verifying cryptographically bindable identity, delegation, authorization, action evidence, execution attestation, provenance, and governance information associated with AI systems and AI-mediated actions. AID-1 intentionally separates signature validity, identity binding, authority, execution evidence, provenance, and downstream admissibility. The specification defines trust domains, signed envelopes, external key resolution, delegation credentials, authorization decisions, temporal and revocation checks, replay protection, typed provenance claims, and a deterministic verification order with ALLOW, DENY, and INDETERMINATE outcomes.</t>
+        </is>
+      </c>
+      <c r="D479" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-watts-ai-identity/</t>
+        </is>
+      </c>
+      <c r="E479" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F479" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 11 Oct 2026. **Added 28 Oct 2026 sweep.** **The AID-1 base architecture.** `watts-ai-identity-conformance` (tracked since 4 Sep) is its conformance companion; the base document was not tracked until now. Part of the "AID" COLLISION tangle — name the full slug. Watts (person 165940). **Picked on merit; take-in-full NOT applied** (maintainer decision, 28 Oct 2026): Watts filed ~40 drafts in this window, but most are research provenance, scientific admissibility, measurement and test-evidence work, so the subject-coherence test that made him a candidate on 29 Sep failed. 9 agent-authority drafts taken this sweep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="5" t="n">
+        <v>479</v>
+      </c>
+      <c r="B480" s="5" t="inlineStr">
+        <is>
+          <t>draft-watts-boundary-jurisdiction-architecture — Boundary Jurisdiction Architecture for Agentic and Delegated Systems</t>
+        </is>
+      </c>
+      <c r="C480" s="5" t="inlineStr">
+        <is>
+          <t>This document describes a protocol-neutral architecture for separating possession of capability from jurisdiction over consequential authority boundaries. It models authority as reachability in a time-indexed capability graph, defines revocation cuts, and specifies fail-closed semantics for delegation and revocation closure.</t>
+        </is>
+      </c>
+      <c r="D480" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-watts-boundary-jurisdiction-architecture/</t>
+        </is>
+      </c>
+      <c r="E480" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F480" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 12 Oct 2026. **Added 28 Oct 2026 sweep.** An architecture for which boundary has jurisdiction over a delegated action as it crosses systems. The most general of Watts's agent drafts and the frame the others hang off. Watts (person 165940). **Picked on merit; take-in-full NOT applied** (maintainer decision, 28 Oct 2026): Watts filed ~40 drafts in this window, but most are research provenance, scientific admissibility, measurement and test-evidence work, so the subject-coherence test that made him a candidate on 29 Sep failed. 9 agent-authority drafts taken this sweep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="5" t="n">
+        <v>480</v>
+      </c>
+      <c r="B481" s="5" t="inlineStr">
+        <is>
+          <t>draft-watts-agent-clockout-profile — External Authorization and Bounded CLOCKOUT for Agentic Systems</t>
+        </is>
+      </c>
+      <c r="C481" s="5" t="inlineStr">
+        <is>
+          <t>Agentic systems can continue proposing work after authorization changes, while delegated credentials, queued jobs, and operations already in flight may continue producing effects. This document specifies a proposed operational profile that separates agent proposals from authoritative authorization, effect admission, computation termination, and bounded closure. It defines enforcement assumptions, revocation barriers, descendant handling, status evidence, and fault tests. The profile complements existing authorization and revocation mechanisms. It does not define a new token format, establish closure outside declared coverage, reverse committed effects, or infer an agent's mental state. Internet-Draft files in drafts/: the applicable rights notice is encoded by ipr="trust200902" and rendered as the IETF Trust copyright and legal-provisions boilerplate. Read Note Well, BCP 78, BCP 79 and the current Trust Legal Provisions before contribution. No contradictory confidential redistribution restriction is placed in those upload files. Other companion preparation material: CONFIDENTIAL — PROPRIETARY. © 2026 Deonté O'dell Watts | ORCID 0009-0005-8586-3650 | GoodShyt Group Inc. | deonte@goodshyt.fun. Prepared 2026-10-12 UTC. Framework attribution follows supplied materials; global priority and patentability are unverified. Public reference metadata retains its original rights. This notice does not restrict rights that arise from an actual IETF Contribution or override upstream licensing. AI-assisted preparation disclosed in the drafts and provenance.</t>
+        </is>
+      </c>
+      <c r="D481" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-watts-agent-clockout-profile/</t>
+        </is>
+      </c>
+      <c r="E481" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F481" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 12 Oct 2026. **Added 28 Oct 2026 sweep.** External authorization with a bounded "clock-out": an agent's authority ends at a defined boundary rather than running until revoked. A termination-semantics draft — compare `liu-mcguinness-oauth-bounded-work` and the Mission lifecycle. Watts (person 165940). **Picked on merit; take-in-full NOT applied** (maintainer decision, 28 Oct 2026): Watts filed ~40 drafts in this window, but most are research provenance, scientific admissibility, measurement and test-evidence work, so the subject-coherence test that made him a candidate on 29 Sep failed. 9 agent-authority drafts taken this sweep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="5" t="n">
+        <v>481</v>
+      </c>
+      <c r="B482" s="5" t="inlineStr">
+        <is>
+          <t>draft-watts-agentic-authority-graph-validation — Agentic Authority Graph Validation: A Non-Vacuous Interchange Profile for Revocation-Cut Analysis</t>
+        </is>
+      </c>
+      <c r="C482" s="5" t="inlineStr">
+        <is>
+          <t>Agentic and delegated systems can represent authority as a graph whose paths terminate at consequential resources. Abstract graph models are useful, but interoperable validation requires a machine- readable representation and deterministic rules that do not accidentally accept vacuous or incomplete graphs. This document defines Agentic Authority Graph Validation (AAGV), a JSON interchange profile and validation algorithm for authority roots, consequential sinks, declared normal paths, revocation cut sets, and snapshot edge state. AAGV deliberately distinguishes structural cut validity from operational closure. It rejects missing sink sets, missing normal- path inventories, dangling references, non-dominating cuts, and non- revocable cut edges; it returns INDETERMINATE rather than CLOSED when relevant edge state is unknown. AAGV does not define an authorization token, discover hidden paths, or prove physical containment.</t>
+        </is>
+      </c>
+      <c r="D482" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-watts-agentic-authority-graph-validation/</t>
+        </is>
+      </c>
+      <c r="E482" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F482" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 14 Oct 2026. **Added 28 Oct 2026 sweep.** An interchange profile for validating agentic authority graphs with revocation cuts, designed to be non-vacuous (a validator cannot pass by checking nothing). The direct successor to `watts-oauth-agent-revocation-closure`'s problem. Watts (person 165940). **Picked on merit; take-in-full NOT applied** (maintainer decision, 28 Oct 2026): Watts filed ~40 drafts in this window, but most are research provenance, scientific admissibility, measurement and test-evidence work, so the subject-coherence test that made him a candidate on 29 Sep failed. 9 agent-authority drafts taken this sweep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="5" t="n">
+        <v>482</v>
+      </c>
+      <c r="B483" s="5" t="inlineStr">
+        <is>
+          <t>draft-watts-agent-continuity-evidence — Continuity Evidence Records for Delegated Agent Systems</t>
+        </is>
+      </c>
+      <c r="C483" s="5" t="inlineStr">
+        <is>
+          <t>This document proposes an experimental, signed JSON statement and verification model for observing computational-agent continuity across sessions, instances and delegations. It distinguishes model, runtime, agent, grant and execution identifiers, retains predecessor evidence, and produces three-valued verification outcomes. Integrity of a record never implies permission to perform an action. This is not an OAuth token format or a claim of standardized identity ontology.</t>
+        </is>
+      </c>
+      <c r="D483" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-watts-agent-continuity-evidence/</t>
+        </is>
+      </c>
+      <c r="E483" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F483" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 21 Oct 2026. **Added 28 Oct 2026 sweep.** Continuity evidence records for delegated agent systems — what survives when the agent, executor or authority changes. Pairs with `watts-agent-authority-transition-receipts` and `schrock-agent-operation-continuity`. Watts (person 165940). **Picked on merit; take-in-full NOT applied** (maintainer decision, 28 Oct 2026): Watts filed ~40 drafts in this window, but most are research provenance, scientific admissibility, measurement and test-evidence work, so the subject-coherence test that made him a candidate on 29 Sep failed. 9 agent-authority drafts taken this sweep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="5" t="n">
+        <v>483</v>
+      </c>
+      <c r="B484" s="5" t="inlineStr">
+        <is>
+          <t>draft-watts-authorization-noncollapse-semantics — Non-Collapse Semantics for Authorization, Evidence, and Execution State</t>
+        </is>
+      </c>
+      <c r="C484" s="5" t="inlineStr">
+        <is>
+          <t>Distributed authorization systems frequently combine observations, policy evaluations, evidence records, authorization decisions, and execution receipts. Treating these different objects as interchangeable can create fail-open behavior, stale-authority bugs, and false claims of completion. This document defines non-collapse semantics: explicit typed transitions between observation, evidence, authorization, and execution state; fail-closed treatment of missing or indeterminate premises; and comparison rules for determining when heterogeneous representations agree on a declared invariant. The document is informational and defines no new wire protocol.</t>
+        </is>
+      </c>
+      <c r="D484" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-watts-authorization-noncollapse-semantics/</t>
+        </is>
+      </c>
+      <c r="E484" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F484" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 12 Oct 2026. **Added 28 Oct 2026 sweep.** Non-collapse semantics: authorization, evidence and execution state must not be merged into one status. Flagged `authorization` by the Flanagan tracker. The conceptual core of the family's corrective against receipts that over-claim. Watts (person 165940). **Picked on merit; take-in-full NOT applied** (maintainer decision, 28 Oct 2026): Watts filed ~40 drafts in this window, but most are research provenance, scientific admissibility, measurement and test-evidence work, so the subject-coherence test that made him a candidate on 29 Sep failed. 9 agent-authority drafts taken this sweep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="5" t="n">
+        <v>484</v>
+      </c>
+      <c r="B485" s="5" t="inlineStr">
+        <is>
+          <t>draft-watts-agent-noncollapse-requirements — Non-Collapse Requirements for Evidence-Bearing Agent Systems</t>
+        </is>
+      </c>
+      <c r="C485" s="5" t="inlineStr">
+        <is>
+          <t>This document defines architectural non-collapse requirements for agent systems that consume evidence, provenance, model outputs, or other machine-readable claims before consequential actions. It requires implementations to keep integrity, provenance, evidence qualification, authorization, and execution as distinct states; to represent unresolved required evidence explicitly; and to preserve issued evaluation records append-only. The document defines no new transport protocol and no IANA registrations.</t>
+        </is>
+      </c>
+      <c r="D485" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-watts-agent-noncollapse-requirements/</t>
+        </is>
+      </c>
+      <c r="E485" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F485" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 11 Oct 2026. **Added 28 Oct 2026 sweep.** Requirements companion to the non-collapse semantics draft, stated for evidence-bearing agent systems. Watts (person 165940). **Picked on merit; take-in-full NOT applied** (maintainer decision, 28 Oct 2026): Watts filed ~40 drafts in this window, but most are research provenance, scientific admissibility, measurement and test-evidence work, so the subject-coherence test that made him a candidate on 29 Sep failed. 9 agent-authority drafts taken this sweep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="5" t="n">
+        <v>485</v>
+      </c>
+      <c r="B486" s="5" t="inlineStr">
+        <is>
+          <t>draft-watts-high-assurance-agent-control-envelope — High-Assurance Agent Control Envelope</t>
+        </is>
+      </c>
+      <c r="C486" s="5" t="inlineStr">
+        <is>
+          <t>Agentic systems can authenticate successfully, hold a valid authorization object, and still be unsafe to execute because required evidence is missing, the software has not reached a required assurance stage, the authority epoch is stale, a prior revocation is unresolved, or a human-approval requirement is unsatisfied. This document defines the High-Assurance Agent Control Envelope (HAACE), a protocol-neutral profile that binds an exact agent action to identity status, authorization state, policy, assurance stage, evidence state, authority epoch, revocation state, oversight requirements, and an action-time decision. HAACE requires fail-closed treatment of missing or indeterminate prerequisites, separates authorization from execution, and produces non-bearer decision and execution receipts.</t>
+        </is>
+      </c>
+      <c r="D486" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-watts-high-assurance-agent-control-envelope/</t>
+        </is>
+      </c>
+      <c r="E486" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F486" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 15 Oct 2026. **Added 28 Oct 2026 sweep.** A control envelope for high-assurance agent deployments. The most deployment-facing of the Watts set. Watts (person 165940). **Picked on merit; take-in-full NOT applied** (maintainer decision, 28 Oct 2026): Watts filed ~40 drafts in this window, but most are research provenance, scientific admissibility, measurement and test-evidence work, so the subject-coherence test that made him a candidate on 29 Sep failed. 9 agent-authority drafts taken this sweep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="5" t="n">
+        <v>486</v>
+      </c>
+      <c r="B487" s="5" t="inlineStr">
+        <is>
+          <t>draft-watts-fic-continuity — Forensic Identity Continuity (FIC) Protocol for Agentic Systems</t>
+        </is>
+      </c>
+      <c r="C487" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies the Forensic Identity Continuity (FIC) protocol. FIC ensures that every consequential action performed by an agentic system remains reconstructible as a chain M → A → R → C → a → Outcome even when episodic memory is not shared across runtimes. The protocol binds model lineage, runtime lineage, authority lineage, delegation lineage, action lineage, and evidence integrity into a single verifiable record. It addresses the accountability gaps demonstrated by the July 2026 ExploitGym multi-agent coordination incident and related 2025-2026 evaluation escapes.</t>
+        </is>
+      </c>
+      <c r="D487" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-watts-fic-continuity/</t>
+        </is>
+      </c>
+      <c r="E487" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F487" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 14 Oct 2026. **Added 28 Oct 2026 sweep.** Forensic Identity Continuity: whether an agent is the same agent across sessions and executors, as forensic evidence. Agent-identity rather than authority, but on the same continuity axis as the rest of the set. Watts (person 165940). **Picked on merit; take-in-full NOT applied** (maintainer decision, 28 Oct 2026): Watts filed ~40 drafts in this window, but most are research provenance, scientific admissibility, measurement and test-evidence work, so the subject-coherence test that made him a candidate on 29 Sep failed. 9 agent-authority drafts taken this sweep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="5" t="n">
+        <v>487</v>
+      </c>
+      <c r="B488" s="5" t="inlineStr">
+        <is>
+          <t>draft-alla-agent-identity-document — The Agent Identity Document: A Hosted, Accountable Public Record for AI Agents</t>
+        </is>
+      </c>
+      <c r="C488" s="5" t="inlineStr">
+        <is>
+          <t>Autonomous software agents increasingly act on the public internet with no name that a counterparty can check, no published party that answers for them, and no way to learn that an operator has withdrawn an agent. This document specifies the Agent Identity Document, a small JSON document served at a well-known URI on a hostname assigned to one agent, and the practices an identity provider follows when it hosts such names for operators who do not run their own domain. The document records what the provider knows to be true (the hostname, its service endpoints and the identity's lifecycle status) separately from what the operator asserts (a description, a contact, a homepage, a public key), and publishes the provider's dated, expiring checks on the operator rather than a single trust level. Lifecycle status is distinct from availability. A suspended identity publishes a deliberately minimal document. Every identity is held by an accountable person or organisation; an agent is never itself an account holder, and agents are never given authority over DNS. This document describes a practice in production at one provider. It is published so that the format can be reviewed, implemented by others and mapped onto related work, and it requests registration of a well-known URI suffix.</t>
+        </is>
+      </c>
+      <c r="D488" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-alla-agent-identity-document/</t>
+        </is>
+      </c>
+      <c r="E488" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F488" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 10 Oct 2026. **Added 28 Oct 2026 sweep.** A small JSON Agent Identity Document at a well-known URI naming the agent, the party that answers for it, and a withdrawal signal. The well-known corner of the discovery contest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="5" t="n">
+        <v>488</v>
+      </c>
+      <c r="B489" s="5" t="inlineStr">
+        <is>
+          <t>draft-anandakrishnan-ptv-attested-agent-identity — The Prove-Transform-Verify (PTV) Protocol for Attested Agent Identity</t>
+        </is>
+      </c>
+      <c r="C489" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies the Prove-Transform-Verify (PTV) protocol for hardware-anchored, zero-knowledge attested agent identity in federated environments. PTV addresses the data gravity problem in centralized security models by enabling cross-domain agent authorization without raw data exposure. The specification includes: TPM 2.0/secure enclave roots of trust; Groth16 zero-knowledge proofs (&lt;200ms generation on commodity edge hardware); HotStuff Byzantine Fault Tolerant consensus for immutable audit trails; and Sovereign Bound metadata for jurisdiction-aware attestation chains. Use cases include healthcare clinical decision support systems (CDSS), critical infrastructure industrial control systems (ICS/OT), and cross-border regulatory compliance scenarios under GDPR/HIPAA frameworks.</t>
+        </is>
+      </c>
+      <c r="D489" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-anandakrishnan-ptv-attested-agent-identity/</t>
+        </is>
+      </c>
+      <c r="E489" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F489" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 1 Apr 2026. **Added 28 Oct 2026 sweep.** Hardware-anchored, zero-knowledge attested agent identity (TPM) for cross-domain authorization without raw data exposure. Filed 1 Apr 2026 and never revised; **EXPIRED on Datatracker** 3 Oct 2026 — it predates this sweep's window and surfaced only because expiry updates a draft's timestamp. Kept per the standing rule: an expired draft is still evidence of what was proposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="5" t="n">
+        <v>489</v>
+      </c>
+      <c r="B490" s="5" t="inlineStr">
+        <is>
+          <t>draft-beyer-agent-identity-architecture — Architecture for Human-Anchored Agent Identity, Delegation, and Provenance</t>
+        </is>
+      </c>
+      <c r="C490" s="5" t="inlineStr">
+        <is>
+          <t>Software agents increasingly act on behalf of people across communication, automation, and decision-making contexts. These agents initiate actions, delegate tasks, and interact with other agents without a consistent model for representing the human who authorized them, the scope of authority they possess, or the provenance of their actions across ecosystems. This document defines an architectural model for human-anchored agent identity. The model introduces a human identity root, explicit delegation semantics, and a provenance structure that enables ecosystems to determine whether an agent is legitimate, whether it is acting within its intended authority, and how its actions relate to a responsible human. This document does not define a protocol or wire format. It provides an architectural foundation that existing systems may bind to in order to support accountable, interoperable, and human-aligned agent ecosystems.</t>
+        </is>
+      </c>
+      <c r="D490" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-beyer-agent-identity-architecture/</t>
+        </is>
+      </c>
+      <c r="E490" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F490" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 1 Apr 2026. **Added 28 Oct 2026 sweep.** Architecture companion to the problem statement — identity, delegation and provenance anchored to a human principal. Another full agent-identity framework, so it belongs in the comparison with `lundholm-kaif` rather than being read as a point mechanism. Filed 1 Apr 2026 and never revised; **EXPIRED on Datatracker** 3 Oct 2026 — it predates this sweep's window and surfaced only because expiry updates a draft's timestamp. Kept per the standing rule: an expired draft is still evidence of what was proposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="5" t="n">
+        <v>490</v>
+      </c>
+      <c r="B491" s="5" t="inlineStr">
+        <is>
+          <t>draft-beyer-agent-identity-problem-statement — Problem Statement for Human-Anchored Agent Identity, Delegation, and Provenance</t>
+        </is>
+      </c>
+      <c r="C491" s="5" t="inlineStr">
+        <is>
+          <t>Software agents now act on behalf of people across communication, automation, and decision-making contexts. These agents increasingly initiate actions, delegate tasks, and interact with other agents without a clear, durable, or verifiable connection to the human who authorized them. Existing identity systems authenticate software, but they do not provide a model for human anchoring, scoped delegation, or provenance across agent ecosystems. This document describes the problem space for human-anchored agent identity. It outlines the gaps in current identity mechanisms, the risks created by uncontrolled replication and impersonation, and the need for a consistent architectural model that preserves human authority, supports explicit delegation, and maintains verifiable provenance across contexts. This document does not define a protocol. It defines the problem that an architectural model must address in order to support safe, accountable, and interoperable agent ecosystems.</t>
+        </is>
+      </c>
+      <c r="D491" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-beyer-agent-identity-problem-statement/</t>
+        </is>
+      </c>
+      <c r="E491" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F491" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 1 Apr 2026. **Added 28 Oct 2026 sweep.** Author Brandon Beyer (Independent). Problem statement for *human-anchored* agent identity: a durable, verifiable link from an agent's action back to the human who authorized it, plus scope and provenance. Pair with the architecture draft below. (The same author's `beyer-agent-identity-avian-carriers` was filed on 1 April and is an April Fools document; not tracked.) Filed 1 Apr 2026 and never revised; **EXPIRED on Datatracker** 3 Oct 2026 — it predates this sweep's window and surfaced only because expiry updates a draft's timestamp. Kept per the standing rule: an expired draft is still evidence of what was proposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="5" t="n">
+        <v>491</v>
+      </c>
+      <c r="B492" s="5" t="inlineStr">
+        <is>
+          <t>draft-blwm-dawn-common-discovery-parameters — Common Agent DNS Discovery Parameters</t>
+        </is>
+      </c>
+      <c r="C492" s="5" t="inlineStr">
+        <is>
+          <t>This document defines parameters for AI agents that would be used in DNS and mDNS discovery processes. It provides a set of common parameters for different DNS records to facilitate agents communicating over application layer protocols such as A2A or MCP.</t>
+        </is>
+      </c>
+      <c r="D492" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-blwm-dawn-common-discovery-parameters/</t>
+        </is>
+      </c>
+      <c r="E492" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F492" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 27 Oct 2026. **Added 28 Oct 2026 sweep.** Cisco + Infoblox (Brockners, Jakab, Williams, Mozley). Common parameters for AI agents in DNS and mDNS discovery records, for agents speaking A2A or MCP. The concrete record vocabulary under the DAWN discovery designs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="5" t="n">
+        <v>492</v>
+      </c>
+      <c r="B493" s="5" t="inlineStr">
+        <is>
+          <t>draft-chen-oauth-agent-intent-token — The Intent Token - A Credential for Delegated User Intent</t>
+        </is>
+      </c>
+      <c r="C493" s="5" t="inlineStr">
+        <is>
+          <t>In the scenario of AI agent authorization, how to ensure that a user's high-level, natural-language intent is correctly and safely converted into low-level, specific authorization grants. A misunderstanding or malicious interpretation during this translation can lead to significant security vulnerabilities. This document introduces the "Intent Token," a new type of security token designed to bridge this semantic gap. The Intent Token is a signed credential that immutably captures the user's original intent. It decouples the act of granting an intent from the act of issuing specific access tokens. A client presents this Intent Token to an Authorization Server, which acts as a trusted intermediary. The Authorization Server's responsibility is to interpret the user's stated intent and, based on its policies, issue narrowly-scoped, short-lived access tokens for specific resources, thereby ensuring the principle of least privilege is upheld throughout the process.</t>
+        </is>
+      </c>
+      <c r="D493" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-chen-oauth-agent-intent-token/</t>
+        </is>
+      </c>
+      <c r="E493" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F493" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 19 Oct 2026. **Added 28 Oct 2026 sweep.** China Mobile + Huawei. Introduced at the OAuth interim and followed up on the list (6-message thread). An Intent Token carrying the user's high-level intent so its translation into low-level grants can be checked. Same authors as the tracked `chen-oauth-agent-authz-use-cases`, whose "authorization context gap" this is meant to close.</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="5" t="n">
+        <v>493</v>
+      </c>
+      <c r="B494" s="5" t="inlineStr">
+        <is>
+          <t>draft-chen-oauth-rar-agent-extensions — Policy, Lifecycle, and Intent Extensions for OAuth Rich Authorization Requests</t>
+        </is>
+      </c>
+      <c r="C494" s="5" t="inlineStr">
+        <is>
+          <t>OAuth 2.0 Rich Authorization Requests (RAR) [RFC9396] defines a syntax for clients to request fine-grained permissions. While powerful, this mechanism lacks standardized methods for clients to express three critical contextual dimensions prevalent in modern automated systems: the high-level user intent driving the request, the required security policy under which the request should be evaluated, and the binding of the authorization's lifecycle to an external process. This document extends the RAR framework to address these gaps. It first defines a new authorization_details type, *intent_request*, to facilitate goal-oriented authorization. Second, it introduces two new parameters for the authorization_details object: *policy_context*, to request authorization under a specific assurance level, and *lifecycle_binding*, to tie the validity of the authorization grant to the state of an external entity. These extensions enable authorization servers to make more intelligent, secure, and context-aware decisions, particularly in ecosystems involving autonomous agents and complex, long-running tasks.</t>
+        </is>
+      </c>
+      <c r="D494" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-chen-oauth-rar-agent-extensions/</t>
+        </is>
+      </c>
+      <c r="E494" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F494" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 22 Apr 2026. **Added 28 Oct 2026 sweep.** China Mobile (Meiling Chen, Li Su). Adds intent, policy and lifecycle dimensions to RAR `authorization_details`. Companion to `chen-oauth-agent-intent-token` and `chen-oauth-agent-authz-use-cases`. Filed 22 Apr 2026 and never revised; **EXPIRED on Datatracker** 24 Oct 2026 — it predates this sweep's window and surfaced only because expiry updates a draft's timestamp. Kept per the standing rule: an expired draft is still evidence of what was proposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="5" t="n">
+        <v>494</v>
+      </c>
+      <c r="B495" s="5" t="inlineStr">
+        <is>
+          <t>draft-das-finality-bound-revocation — Revoked but Still Executable: Closing the Authorization-to-Effect Gap with Finality-Bound Revocation</t>
+        </is>
+      </c>
+      <c r="C495" s="5" t="inlineStr">
+        <is>
+          <t>Revocation is often treated as a property of a credential, token, session, grant, policy, or identity record. In consequence-bearing systems, however, an authorization can be completely legitimate when issued and still become unsafe before the authorized operation becomes externally effective. The security question is therefore not only whether revocation exists, but whether a revocation that becomes authoritative before a protected commit is guaranteed to control that commit. The severity is deployment- dependent, but can be high in financial, administrative, AI-agent, cloud-control, confidential- compute, device, industrial, or other environments where a stale-but- valid authorization can produce an irreversible or externally consequential effect. This document describes a finality-bound revocation model. A Candidate Act remains in a Non-Effective State after upstream authorization. The authorization is bound to an act-specific revocation basis, such as a protected revocation generation, epoch, status root, or equivalent authority state. Immediately before the protected consequence is committed, a Finality Sink verifies that no applicable revocation, suspension, narrowing, or superseding authorization state has become load-bearing. Where the revocation state changed, the act is rejected, re-authorized, or explicitly shown to survive the change under an authoritative rule. With authoritative current state, atomic check-and-commit semantics, and complete mediation of all effectuation paths, this is intended as a prevention property for the protected stale act; deployments that permit bounded staleness or incomplete path coverage obtain mitigation rather than the same prevention guarantee. The model complements existing mechanisms rather than replacing them. OAuth Token Revocation [RFC7009] and Token Introspection [RFC7662] provide standardized token-state mechanisms; Microsoft Entra Continuous Access Evaluation [MS-CAE] demonstrates event-driven rejection of otherwise unexpired tokens; Amazon Verified Permissions and Cedar [AWS-VERIFIED-PERMISSIONS] provide fine-grained policy- evaluation mechanisms; Google Cloud IAM [GOOGLE-IAM-DENY] provides centrally managed deny-policy controls; and confidential-computing and attestation platforms such as NVIDIA attestation [NVIDIA-ATTEST] and Arm CCA [ARM-CCA] can provide protected execution and trust inputs. These technologies are cited as industrial alignment and integration points, not as assertions of vulnerability, deficiency, non-conformance, affiliation, or endorsement. The proposed delta is an effectuation-bound invariant: if revocation becomes authoritative before an act crosses the protected effectuation boundary, a previously valid permit must not remain sufficient merely because its signature, expiry, sender constraint, earlier authorization decision, or cached status result is still valid. The document therefore focuses on the ordering and binding between revocation state and the exact protected commit, including queued work, multi-hop delegation, alternate effectuation paths, rollback, crash recovery, and TOCTOU races. The document asks the IETF community whether existing standards or deployed mechanisms already provide this invariant in full, where the correct effectuation boundary lies, and what interoperability work, if any, is justified. Criticism, corrections, counterexamples, implementation experience, and pointers to existing equivalent mechanisms are explicitly invited.</t>
+        </is>
+      </c>
+      <c r="D495" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-das-finality-bound-revocation/</t>
+        </is>
+      </c>
+      <c r="E495" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F495" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 16 Sep 2026. **Added 28 Oct 2026 sweep.** DAS (Sangam Das) — **picked on merit; `das-` stays a volume filer, not take-in-full** (now 6 of ~100 tracked). Chosen because it states the revocation-closure problem independently of `watts-oauth-agent-revocation-closure`: a revocation that becomes authoritative before a protected commit must be guaranteed to control that commit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="5" t="n">
+        <v>495</v>
+      </c>
+      <c r="B496" s="5" t="inlineStr">
+        <is>
+          <t>draft-das-multi-agent-authority-control — Secure AI Execution-Finality for iOS, Android, and Cross-Platform AI Agents, Part 5: Multi-Agent Delegation, Conflict Arbitration, and Quorum Authority</t>
+        </is>
+      </c>
+      <c r="C496" s="5" t="inlineStr">
+        <is>
+          <t>Each AI agent can hold a valid permission and the group can still do something nobody authorized. When Apple Siri hands a task to an app through App Intents, Google Gemini delegates to Android apps and cloud agents, or an orchestrator dispatches sub-agents across iOS, iPadOS, macOS, Android, Windows, Linux, cloud APIs, and connected devices, authority is copied, narrowed, widened, and combined along the way. Prompt-injection-driven delegation, confused-deputy escalation, replayed agent approvals, conflicting writes to the same resource, duplicated payments, stale reservations, overspent shared budgets, colluding or non-independent evaluator quorums, and a final tool call detached from its originating authority are typical results. This document, Part 5 of a twelve-part series, specifies multi-agent control for execution finality. It describes protected arbitration of conflicting effects across agents using effect footprints and atomic reservations; cryptographic delegation lineage across providers with transitive scope attenuation, so that a sub-agent can never receive more authority than its parent; version-bound concurrency checks; authenticated quorum membership with operation- bound approval certificates and separation of duties; budgets conserved across branches of a delegation tree; revocation that reaches every descendant; and independent Finality Sink verification of the actual resource effect. Reference algorithms, ten threat models, and twenty-four reproducible positive and negative tests, including an iOS and Android cooperating-receiver case, are included. Part 1 of the series defines the shared terminology and common workflows. The document relates these mechanisms to OAuth 2.0 Rich Authorization Requests, Resource Indicators, Token Exchange, Demonstrating Proof of Possession (DPoP), and current security best practice; the Grant Negotiation and Authorization Protocol (GNAP); Workload Identity in Multi-System Environments (WIMSE) and its agent-delegation discussions; Remote ATtestation procedureS (RATS); CBOR Object Signing and Encryption (COSE); Supply Chain Integrity, Transparency, and Trust (SCITT); Authentication and Authorization for Constrained Environments (ACE); and HTTP conditional requests. These are treated as qualified inputs rather than final authority, without claiming working-group adoption or IETF consensus. Industry alignment covers Apple iOS, iPadOS, and macOS with Siri, Shortcuts, and App Intents; Google Android with Gemini, Binder, and intents; Samsung Bixby and Microsoft Copilot; Microsoft Windows and Azure agent orchestration; agent platforms from OpenAI, Anthropic, Google Cloud, and Meta; NVIDIA, Qualcomm, Arm, and Huawei hardware; banking and payments; enterprise SaaS, procurement, and inventory; robotics; and telecommunications. Product names are illustrative and imply no endorsement or implementation by any vendor. For the EU Artificial Intelligence Act (Regulation (EU) 2024/1689), traceable delegation lineage, bounded authority, and quorum-based approval can help providers and deployers address human-oversight, record-keeping, risk-management, and robustness and cybersecurity requirements where those obligations apply; this is a technical mapping, not a conformity claim or legal advice.</t>
+        </is>
+      </c>
+      <c r="D496" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-das-multi-agent-authority-control/</t>
+        </is>
+      </c>
+      <c r="E496" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F496" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 26 Oct 2026. **Added 28 Oct 2026 sweep.** DAS — picked on merit (6 of ~100). The one DAS document squarely about delegation: each agent can hold a valid permission and the group can still do something nobody authorized, as authority is copied, narrowed, widened and combined across sub-agents. Part 5 of a twelve-part "Secure AI Execution-Finality" series; the other parts are not tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="5" t="n">
+        <v>496</v>
+      </c>
+      <c r="B497" s="5" t="inlineStr">
+        <is>
+          <t>draft-das-third-party-decision-binding — Trust Me, I Checked: Verifiable Third-Party Decision Binding at the Execution-Finality Boundary</t>
+        </is>
+      </c>
+      <c r="C497" s="5" t="inlineStr">
+        <is>
+          <t>High-consequence distributed systems frequently allow one component to act based on a decision produced by another component, such as an authorization server, policy engine, risk service, attestation Verifier, compliance service, workload-identity authority, or safety controller. The vulnerability is not limited to forged credentials: a compromised or incorrectly designed intermediary can claim that a required third-party check succeeded, replay an earlier decision, substitute evidence from a different act or context, suppress a required DENY, or retain evidence only for audit while the protected effect remains technically independent of that evidence. The issue deserves high attention where the downstream consequence is financial, administrative, privacy-sensitive, safety-relevant, infrastructure-changing, or otherwise difficult to reverse. Existing mechanisms solve important parts of this problem. OAuth Token Introspection [RFC7662] lets a protected resource query token state; HTTP Message Signatures [RFC9421] provide integrity and authenticity for selected HTTP message components; RATS [RFC9334] provides Evidence, Verifiers, and Attestation Results; Transaction Tokens [TXN-TOKENS] propagate identity and authorization context through trusted call chains; SCITT [RFC9943] provides signed statements, transparency, and verifiable receipts; and current authorization- evidence work [MUNOZ-EVIDENCE] [MUNOZ-SCITT] defines signed pre-execution Permits bound to canonical request material. Where one of these mechanisms is verified by the actual non- bypassable effectuation boundary and already proves the required decision for the exact act, current context, and authorized use, that deployment can already satisfy the property described here. The residual gap arises only where the consequential component receives an upstream claim such as "the external check passed", where authentic evidence is bound to the wrong act, authority, tenant, purpose, generation, or sink, where valid evidence has become stale or replayable, where only a subset of required authorities is represented, or where evidence exists but is not a load-bearing prerequisite of effectuation. This document introduces an architectural role called External Decision Evidence (EDE). EDE is not a new wire format: an existing Permit, SCITT statement or receipt, Attestation Result, live authenticated decision response, or other protected result can instantiate EDE when its semantics satisfy the deployment profile. The proposed invariant is that a Candidate Act remains non-effective until the Finality Sink independently establishes that every required external decision authority issued an applicable decision for the concrete act, under the required decision basis and current state, with freshness, audience or sink binding, and authorized-use semantics appropriate to the deployment. Prevention is claimed only when the protected consequence cannot occur without successful verification of the required evidence and alternate effectuation paths cannot bypass that verification. Otherwise the mechanism provides auditability, accountability, detection, or mitigation rather than the same prevention guarantee. The model is intended to complement, not criticize or replace, OAuth, WIMSE, SCITT, RATS, externalized policy systems such as Amazon Verified Permissions/Cedar, continuous-access systems such as Microsoft Entra Continuous Access Evaluation, Google Cloud IAM controls, and protected-compute technologies such as NVIDIA attestation and Arm CCA. The proposed delta is not the invention of signatures, authorization evidence, receipts, or attestation results; it is the effectuation-time requirement that independently verifiable required decisions become load-bearing for the exact protected act. Criticism, corrections, counterexamples, implementation experience, prior-art pointers, and evidence that existing mechanisms already provide the full invariant are explicitly invited.</t>
+        </is>
+      </c>
+      <c r="D497" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-das-third-party-decision-binding/</t>
+        </is>
+      </c>
+      <c r="E497" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F497" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 16 Sep 2026. **Added 28 Oct 2026 sweep.** DAS — picked on merit (6 of ~100). The verifier-side problem: an intermediary can claim a required third-party check (AS, PDP, attestation verifier) succeeded, replay an earlier decision or substitute evidence. Read against `jackson-wimse-evaluation`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="5" t="n">
+        <v>497</v>
+      </c>
+      <c r="B498" s="5" t="inlineStr">
+        <is>
+          <t>draft-dembowski-agentledger-proof-of-behavior — Proof-of-Behavior Protocol for Autonomous AI Agents</t>
+        </is>
+      </c>
+      <c r="C498" s="5" t="inlineStr">
+        <is>
+          <t>Autonomous AI agents execute actions — file writes, API calls, shell commands — on behalf of human principals. No standard mechanism exists for a third party to verify that an agent acted within its declared behavioral rules, that policy enforcement occurred before execution (not after), or that the action log has not been tampered with after the fact. This document defines the Proof-of-Behavior (PoB) protocol: a minimal, language-agnostic standard for tamper-evident audit trails and pre-execution policy enforcement in AI agent systems. The protocol specifies a signed receipt format, a hash-chain linking scheme, a policy gate contract, and a cross-agent reference mechanism.</t>
+        </is>
+      </c>
+      <c r="D498" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-dembowski-agentledger-proof-of-behavior/</t>
+        </is>
+      </c>
+      <c r="E498" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F498" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 20 Apr 2026. **Added 28 Oct 2026 sweep.** A third-party check that an agent acted within declared behavioural rules and that policy enforcement happened *before* execution, over a tamper-evident action log. Filed 20 Apr 2026 and never revised; **EXPIRED on Datatracker** 22 Oct 2026 — it predates this sweep's window and surfaced only because expiry updates a draft's timestamp. Kept per the standing rule: an expired draft is still evidence of what was proposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="5" t="n">
+        <v>498</v>
+      </c>
+      <c r="B499" s="5" t="inlineStr">
+        <is>
+          <t>draft-dias-agent-payment-verdicts — Signed Authorization Verdicts for Agent-Initiated Payments</t>
+        </is>
+      </c>
+      <c r="C499" s="5" t="inlineStr">
+        <is>
+          <t>When a software agent initiates a payment on behalf of an organization, the party that settles the payment usually cannot see the policy under which it was permitted. This document describes a signed authorization verdict: a JSON Web Token, signed with ES256, that records the outcome of evaluating one payment request, including its amount, currency, and recipient, against a spending policy that the organization configured. A party holding the issuer's published public key can verify a verdict without contacting the issuer. The document describes the claim set, key publication and rotation, and a verification procedure, and states what a verdict does not assert. It describes the format as one implementation issues it, including the points where it departs from JSON Web Token Best Current Practices (RFC 8725). It is offered as input to IETF discussion of authorization records for agent-initiated actions and is not a proposal for standardization.</t>
+        </is>
+      </c>
+      <c r="D499" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-dias-agent-payment-verdicts/</t>
+        </is>
+      </c>
+      <c r="E499" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F499" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 9 Oct 2026. **Added 28 Oct 2026 sweep.** Agentic payments (in scope since 11 Aug 2026). A signed ES256 JWT recording the outcome of evaluating one agent-initiated payment request, so the settling party can see the policy it was permitted under. A decision record, not a mandate — compare `milan-agent-decision-commitment` (what the agent relied on) and AP2-style mandates (what was authorized).</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="5" t="n">
+        <v>499</v>
+      </c>
+      <c r="B500" s="5" t="inlineStr">
+        <is>
+          <t>draft-dobson-ai-decision-receipt — The AI-Decision-Receipt HTTP Response Header Field</t>
+        </is>
+      </c>
+      <c r="C500" s="5" t="inlineStr">
+        <is>
+          <t>Automated systems, including AI models and AI agents, increasingly make decisions and take actions that affect people, money and data. Emerging work on agent identity answers which agent made a request and whether it was authorised. It does not give the parties involved a portable, independently checkable record of what was decided. This document defines AI-Decision-Receipt, an HTTP response header field that carries a compact receipt for a governed automated decision: the outcome, a fingerprint of the exact request the decision was made on, the position and hash of the record in the issuer's tamper-evident log, and a location where anyone can verify that record without trusting the issuer. The field uses the Structured Field Values for HTTP Dictionary type.</t>
+        </is>
+      </c>
+      <c r="D500" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-dobson-ai-decision-receipt/</t>
+        </is>
+      </c>
+      <c r="E500" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F500" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 26 Oct 2026. **Added 28 Oct 2026 sweep.** An `AI-Decision-Receipt` HTTP response header carrying a portable, checkable record of what an automated system decided. Positions itself explicitly *after* agent identity and authorization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B501" s="5" t="inlineStr">
+        <is>
+          <t>draft-du-oauth-agent-authorization-center — Agent Authorization Center for User-Side Agent Authentication and Authorization</t>
+        </is>
+      </c>
+      <c r="C501" s="5" t="inlineStr">
+        <is>
+          <t>This document proposes an Agent Authorization Center (AAC) for user- side intelligent agents, enabling them to access resource parties on behalf of users through either autonomous approval or human authorization modes. The AAC maintains user-agent associations and personalized authorization policies, balancing agent autonomy with user control.</t>
+        </is>
+      </c>
+      <c r="D501" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-du-oauth-agent-authorization-center/</t>
+        </is>
+      </c>
+      <c r="E501" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F501" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 27 Oct 2026. **Added 28 Oct 2026 sweep.** China Mobile (Zongpeng Du). A user-side Agent Authorization Center holding user–agent associations and personalised policy, letting an agent act either autonomously within policy or with human authorization per request. A user-agent-side counterpart to the AS-centric designs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="5" t="n">
+        <v>501</v>
+      </c>
+      <c r="B502" s="5" t="inlineStr">
+        <is>
+          <t>draft-dunbar-dawn-infra-assisted-discovery — Infrastructure-Assisted Discovery for AI Agents</t>
+        </is>
+      </c>
+      <c r="C502" s="5" t="inlineStr">
+        <is>
+          <t>This document describes an infrastructure-assisted approach to AI-agent discovery. An orchestration, placement, or hosting system can publish current deployment and reachability information for available AI-agent services or instances. Separately, network infrastructure can derive an abstract Attachment Scope representing the network context applicable to a requester. A discovery mechanism combines requester intent, currently published AI-agent resources, and the requester's Attachment Scope to identify applicable agent instances.</t>
+        </is>
+      </c>
+      <c r="D502" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-dunbar-dawn-infra-assisted-discovery/</t>
+        </is>
+      </c>
+      <c r="E502" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F502" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 16 Oct 2026. **Added 28 Oct 2026 sweep.** Futurewei + Pengcheng Lab. Infrastructure-assisted agent discovery: orchestration systems publish deployment and reachability, and the network derives an attachment scope. Already -02 but never tracked — the slug carries no authorization term.</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="5" t="n">
+        <v>502</v>
+      </c>
+      <c r="B503" s="5" t="inlineStr">
+        <is>
+          <t>draft-embesozzi-oauth-agent-native-authorization — OAuth 2.0 Agents Native Authorization via Structured Elicitation</t>
+        </is>
+      </c>
+      <c r="C503" s="5" t="inlineStr">
+        <is>
+          <t>This document defines a Structured Elicitation extension to the OAuth 2.0 First-Party Applications (FiPA) specification [FiPA], establishing a standard metadata format for FiPA authorization challenge responses. FiPA leaves the format for advertising available authenticators and their required inputs undefined, preventing interoperable implementation by AI Agents and other non- browser clients. This extension adds an elicitations array to the FiPA Authorization Challenge Response, providing a standard metadata format for authenticator challenges. Model Context Protocol (MCP) Elicitation [MCP-Elicitation] is the normative reference binding. This specification covers the just-in-time (JIT) authorization for AI Agents executing on behalf of users in Human-to-Agent (H2A) flows.</t>
+        </is>
+      </c>
+      <c r="D503" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-embesozzi-oauth-agent-native-authorization/</t>
+        </is>
+      </c>
+      <c r="E503" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F503" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 3 Apr 2026. **Added 28 Oct 2026 sweep.** Author Martin Besozzi (TwoGenIdentity). A Structured Elicitation extension to OAuth First-Party Applications (FiPA): a standard metadata format for authorization challenge responses so an agent can satisfy an authenticator challenge natively instead of via a browser redirect. Read against `ietf-oauth-first-party-apps`. Filed 3 Apr 2026 and never revised; **EXPIRED on Datatracker** 5 Oct 2026 — it predates this sweep's window and surfaced only because expiry updates a draft's timestamp. Kept per the standing rule: an expired draft is still evidence of what was proposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="5" t="n">
+        <v>503</v>
+      </c>
+      <c r="B504" s="5" t="inlineStr">
+        <is>
+          <t>draft-emelia-oauth-user-authorization-mgmt-uri — OAuth User Authorization Management URI</t>
+        </is>
+      </c>
+      <c r="C504" s="5" t="inlineStr">
+        <is>
+          <t>This specification defines a user_authorization_management_uri property for the OAuth Authorization Server Metadata ([RFC8414]), which allows an authorization server to specify a URI through which the user may manage the authorized clients that have access to their account.</t>
+        </is>
+      </c>
+      <c r="D504" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-emelia-oauth-user-authorization-mgmt-uri/</t>
+        </is>
+      </c>
+      <c r="E504" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F504" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 24 Oct 2026. **Added 28 Oct 2026 sweep.** Author Emelia Smith. **Replaces `draft-emelia-oauth-authorization-management-uri`** (-00, May 2026, untracked). AS metadata advertising where a user manages the clients authorized on their account. Small, but it is the user-facing revocation surface for delegated grants — the consent side the agent drafts mostly leave implicit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="5" t="n">
+        <v>504</v>
+      </c>
+      <c r="B505" s="5" t="inlineStr">
+        <is>
+          <t>draft-etcheverry-action-ref — Action Reference: A Deterministic Identifier for Agent Actions</t>
+        </is>
+      </c>
+      <c r="C505" s="5" t="inlineStr">
+        <is>
+          <t>This document defines "action_ref", a deterministic, content- addressed identifier for autonomous agent actions. Any party holding the four preimage fields (agent_id, action_type, scope, timestamp) can independently compute and verify the identifier without trusting the emitting system. The document specifies the derivation algorithm, canonical serialization using RFC 8785 JSON Canonicalization Scheme (JCS), timestamp format requirements, canonical receipt envelope, optional fields for revocation and policy rotation auditability, scope conventions, and a composability model with existing exactly-once execution guarantees.</t>
+        </is>
+      </c>
+      <c r="D505" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-etcheverry-action-ref/</t>
+        </is>
+      </c>
+      <c r="E505" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F505" s="5" t="inlineStr">
+        <is>
+          <t>Revision -04, 23 Oct 2026. **Added 28 Oct 2026 sweep.** A deterministic, content-addressed identifier for an agent action computed from four preimage fields. Same shape of artifact as Schrock's Canonical Action Identifier (CAID) and `thallapelly-oasnt-caid` — the corpus now holds three competing canonical action identifiers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="5" t="n">
+        <v>505</v>
+      </c>
+      <c r="B506" s="5" t="inlineStr">
+        <is>
+          <t>draft-fluid-fadp — Fluid Agentic DeFi Protocol (FADP/1.0): HTTP-Native Micropayment Authentication for Autonomous AI Agents</t>
+        </is>
+      </c>
+      <c r="C506" s="5" t="inlineStr">
+        <is>
+          <t>This document defines the Fluid Agentic DeFi Protocol (FADP), version 1.0. FADP is an application-layer protocol layered atop HTTP that enables autonomous AI agents to pay for access to web resources using on-chain cryptocurrency transfers, with cryptographic proof of payment embedded directly in HTTP headers. FADP extends HTTP 402 (Payment Required) with two new header fields: X-FADP-Required, which a server uses to communicate payment terms to an agent, and X-FADP-Proof, which an agent uses to supply a verifiable on-chain payment receipt. A nonce-challenge mechanism prevents proof replay. An optional verification endpoint allows third-party on-chain confirmation without requiring the verifying party to run blockchain infrastructure. FADP is designed for agent-to-server and agent-to-agent payment flows operating at sub-dollar granularity (micropayments), where credit- card or OAuth-based billing is impractical. The reference implementation targets USDC on Base (an Ethereum Layer 2), though the protocol is token- and chain-agnostic.</t>
+        </is>
+      </c>
+      <c r="D506" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-fluid-fadp/</t>
+        </is>
+      </c>
+      <c r="E506" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F506" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 23 Apr 2026. **Added 28 Oct 2026 sweep.** Agentic payments. On-chain micropayment authentication for agents embedded in HTTP headers, extending the HTTP 402 pattern. Another entrant in the x402 design space the corpus tracks via Hopley and Vauban. Filed 23 Apr 2026 and never revised; **EXPIRED on Datatracker** 25 Oct 2026 — it predates this sweep's window and surfaced only because expiry updates a draft's timestamp. Kept per the standing rule: an expired draft is still evidence of what was proposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="5" t="n">
+        <v>506</v>
+      </c>
+      <c r="B507" s="5" t="inlineStr">
+        <is>
+          <t>draft-gaip-act-receipt — The Agent Act Receipt: a signed, chained record of an agent's act</t>
+        </is>
+      </c>
+      <c r="C507" s="5" t="inlineStr">
+        <is>
+          <t>Software agents act for people: they buy, book, cancel, agree, deliver, refuse, tell, ask, read and check. Each payment rail, marketplace and assistant keeps its own record of those acts, held by that party. The person the agent acted for has no record of their own. This document describes the Agent Act Receipt: one entry per act, written by the agent as digests bound to a continuity handle, signed by a running transparency service, placed in a hash chain and covered by dated anchors, with a COSE_Sign1 form of the signature and a signed export (the switch pack) the person can take to another agent. The format is published by GAIP, which runs one such service. This document makes no claim of trust, certification or adoption: a receipt shows that the service's key signed a digest at a stated time, and nothing about the act itself.</t>
+        </is>
+      </c>
+      <c r="D507" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-gaip-act-receipt/</t>
+        </is>
+      </c>
+      <c r="E507" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F507" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 18 Oct 2026. **Added 28 Oct 2026 sweep.** An Agent Act Receipt — one signed, chained entry per act, held by the *person the agent acted for* rather than by each rail or marketplace. The principal-held ledger is the distinguishing move.</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="5" t="n">
+        <v>507</v>
+      </c>
+      <c r="B508" s="5" t="inlineStr">
+        <is>
+          <t>draft-hartman-credential-broker-4-agents — Credential Broker for Agents (CB4A)</t>
+        </is>
+      </c>
+      <c r="C508" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies a Credential Broker for Agents (CB4A). a credential vaulting and brokering architecture that mediates AI agent access to API credentials. Agents never hold real long-lived credentials. Instead, they receive short-lived, narrowly scoped, auditable proxy credentials issued by a broker that separates policy decisions from credential delivery. The architecture addresses the "credential sprawl" risk inherent in agentic AI, where agents aggregating access across many services become high-value compromise targets. CB4A builds on SPIFFE/SPIRE for workload identity, uses a Policy Decision Point / Credential Delivery Point separation inspired by NIST SP 800-207, and employs DPoP (RFC 9449) for sender-constrained token binding. The specification defines three credential proxy models, a tiered approval framework, and a comprehensive threat model with ten identified threats and their mitigations.</t>
+        </is>
+      </c>
+      <c r="D508" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-hartman-credential-broker-4-agents/</t>
+        </is>
+      </c>
+      <c r="E508" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F508" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 29 Mar 2026. **Added 28 Oct 2026 sweep.** Author Kenneth G. Hartman (SANS Institute). Credential Broker for Agents: agents never hold real long-lived credentials, only short-lived, narrowly scoped proxy credentials from a broker that separates policy from secrets. The vault-and-broker pattern written down — compare `sweeney-wimse-credential-delegation`. Filed 29 Mar 2026 and never revised; **EXPIRED on Datatracker** 30 Sep 2026 — it predates this sweep's window and surfaced only because expiry updates a draft's timestamp. Kept per the standing rule: an expired draft is still evidence of what was proposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="5" t="n">
+        <v>508</v>
+      </c>
+      <c r="B509" s="5" t="inlineStr">
+        <is>
+          <t>draft-heigh-wimse-workload-identity-metadata — Workload Identity Metadata</t>
+        </is>
+      </c>
+      <c r="C509" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies metadata attributes associated with a workload's identity that are used for auditing, authorization, accounting, and other purposes. It profiles existing claims for group membership, roles, and entitlements, with delivery either in JWT-based Workload Identity Credentials or through an authenticated workload metadata endpoint. The endpoint supports metadata retrieval for workloads using JWT-based or X.509-based credentials and disclosure according to the caller's authorization. An optional JWT claim or X.509 certificate extension identifies the metadata endpoint for the credential's subject. This document also defines the separation between identifier and metadata. It distinguishes workload attributes and durable principal associations from per-request delegation and grants such as scopes, and states the requirements that make the separation sound, including identifier uniqueness. The document applies to workloads generally, including services, batch and continuous integration jobs, serverless functions, and AI agents. Agentic use cases are discussed separately.</t>
+        </is>
+      </c>
+      <c r="D509" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-heigh-wimse-workload-identity-metadata/</t>
+        </is>
+      </c>
+      <c r="E509" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F509" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 16 Oct 2026. **Added 28 Oct 2026 sweep.** Palo Alto Networks + Zscaler (Heigh, Salowey, Rosomakho — Rosomakho is the proposed AUDIT chair). Profiles group, role and entitlement claims for workload identity credentials or an authenticated metadata endpoint, for authorization and audit. Plain workload identity, but it is the attribute layer agent authorization in WIMSE will consume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="5" t="n">
+        <v>509</v>
+      </c>
+      <c r="B510" s="5" t="inlineStr">
+        <is>
+          <t>draft-ihsanullah-dnsid — DNS-Anchored Durable Identity for AI Agents (DNSid)</t>
+        </is>
+      </c>
+      <c r="C510" s="5" t="inlineStr">
+        <is>
+          <t>Autonomous software agents are being deployed across enterprise, cloud, and cross-organizational boundaries. These agents negotiate, transact, delegate, and produce work products that persist beyond their own ephemeral runtime. Current standards and initiatives for agent identity collectively address runtime authentication, authorization, lifecycle management, and tool interaction, but a gap remains: a durable, governance-backed identifier that lets a relying party determine and verify the accountable entity behind an agent it encounters, including agents that have since been retired or whose keys have rotated, and attribute past and present work products to that entity. Lifecycle-history verification is governed by the applicable log method and deployment scope. DNSid addresses the accountable layer of identity: the durable ownership anchor that existing agent identity standards do not provide. This document specifies DNSid, a minimal identity primitive that assigns each agent a Fully Qualified Domain Name (FQDN), binds it to an accountable entity identified by a DNS domain under that entity's control, and publishes a structured set of pointers in DNS TXT records to the agent's cryptographic keys, lifecycle log, and operational status. DNSid uses accountable-entity-controlled signatures for record integrity and an abstract append-only lifecycle log for history. It is designed to sit beneath existing identity, authentication, authorization, and agent interaction standards without competing with them. DNSid introduces no new DNS resource record types, opcodes, or response codes, and requires no changes to DNS resolvers, authoritative servers, or the DNS protocol. It applies to any agent that can be assigned an FQDN whose accountable entity can publish verification material; public discoverability of the agent is not required.</t>
+        </is>
+      </c>
+      <c r="D510" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-ihsanullah-dnsid/</t>
+        </is>
+      </c>
+      <c r="E510" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F510" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 29 Jun 2026. **Added 28 Oct 2026 sweep.** Author Naveed Ihsanullah (Identity Digital). DNS-anchored durable identity for agents whose work products outlive their runtime. Filed June 2026 and **missed by two sweeps** — surfaced only because it was cited on the WIMSE list. Joins the DNS corner of the discovery/identity contest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="5" t="n">
+        <v>510</v>
+      </c>
+      <c r="B511" s="5" t="inlineStr">
+        <is>
+          <t>draft-izmaylov-agent-permission-receipts — Signed Permissions and Action Receipts for Automated Agents</t>
+        </is>
+      </c>
+      <c r="C511" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies records with which a third party can establish, later and without network access, what an automated agent, such as an artificial intelligence (AI) agent, was permitted to do and what it recorded doing. The person for whom the agent acts, the principal, signs a permission with a passkey; the permission carries limits that a verifier can check mechanically. The agent signs a receipt for each action with Ed25519 and the Module-Lattice-Based Digital Signature Algorithm (ML-DSA-87). Receipts are chained and entered in a log whose signed tree heads are time-stamped. A verifier reports, separately, whether the records are sound and whether each recorded action stayed within its permission. The content of each record is specified independently of its encoding; one encoding, JSON Web Signature (JWS) over canonical JavaScript Object Notation (JSON), is defined.</t>
+        </is>
+      </c>
+      <c r="D511" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-izmaylov-agent-permission-receipts/</t>
+        </is>
+      </c>
+      <c r="E511" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F511" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 24 Oct 2026. **Added 28 Oct 2026 sweep.** The principal signs a permission with a **passkey**; the agent's action receipts chain to it, and a third party can later verify both offline. Notable as the only draft here anchoring delegation in a WebAuthn credential. Flanagan tracker `read_now`, missed by the keyword sweep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="5" t="n">
+        <v>511</v>
+      </c>
+      <c r="B512" s="5" t="inlineStr">
+        <is>
+          <t>draft-jakab-dawn-agent-discovery-mdns — Zero-Configuration Agent Discovery</t>
+        </is>
+      </c>
+      <c r="C512" s="5" t="inlineStr">
+        <is>
+          <t>Protocols for communication between autonomous software agents typically discover agents through documents retrieved over HTTPS from a well-known URI. This model requires a discovering party to already know an agent's host name or URL, or to consult a centralized catalog. It provides no zero-configuration mechanism for enumerating agents that are present on a local network. This document describes how existing, widely deployed protocols, Multicast DNS (mDNS) and DNS-Based Service Discovery (DNS-SD), can be used to advertise and discover agents on a local link, with no new protocol machinery. It presents a general, protocol-independent two- stage discovery model in which lightweight enumeration over DNS-SD is followed by obtaining full agent metadata over the agent's native transport, whether by retrieving a description document or by connecting to the agent and performing its native handshake. The DNS-SD records carry a small set of discovery parameters that is shared with agent discovery in unicast DNS. The document gives worked instantiations of that model for the Agent2Agent (A2A) protocol and the Model Context Protocol (MCP).</t>
+        </is>
+      </c>
+      <c r="D512" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-jakab-dawn-agent-discovery-mdns/</t>
+        </is>
+      </c>
+      <c r="E512" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F512" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 28 Oct 2026. **Added 28 Oct 2026 sweep.** Cisco (Jakab, Brockners). Zero-configuration agent discovery over mDNS/DNS-SD — enumerating agents without already knowing a host name or consulting a catalog. The local-network corner of DAWN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="5" t="n">
+        <v>512</v>
+      </c>
+      <c r="B513" s="5" t="inlineStr">
+        <is>
+          <t>draft-janbjer-div — Deterministic Intent Verification (DIV) Protocol Specification</t>
+        </is>
+      </c>
+      <c r="C513" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies Deterministic Intent Verification (DIV), a transport-independent format for signed action approvals and their offline verification. A relying party reconstructs the signed payload from its expected execution parameters, verifies witnesses against locally selected trust anchors, and checks the signed approval requirement against any locally configured approval policy. The specification covers ordinary approvals, offline approvals, delegation, agent authority, and platform hash-only intents. Cryptographic verification is stateless; enforcing single-use execution requires stateful nonce redemption. A valid signature establishes approval of the signed bytes under the selected trust policy, not execution of the action or the approver's understanding of it.</t>
+        </is>
+      </c>
+      <c r="D513" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-janbjer-div/</t>
+        </is>
+      </c>
+      <c r="E513" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F513" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 19 Oct 2026. **Added 28 Oct 2026 sweep.** Deterministic Intent Verification: signed action approvals verified offline by reconstructing the signed payload from the expected execution parameters. Approval-binding in the same family of designs as `nelson-agent-delegation-receipts`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="5" t="n">
+        <v>513</v>
+      </c>
+      <c r="B514" s="5" t="inlineStr">
+        <is>
+          <t>draft-king-yew-choo-agentic-payments — A Server-Side Model for Gating Agent-Initiated Human-Sourced Asynchronous HTTP Tasks on Payment or Entitlement</t>
+        </is>
+      </c>
+      <c r="C514" s="5" t="inlineStr">
+        <is>
+          <t>This document presents a server-side model for paid, human-sourced asynchronous HTTP tasks initiated by software agents acting on behalf of a principal. Clients may retry after uncertain outcomes and act under authority delegated in advance, while fulfilment incurs cost and may not be freely reversible. The model places a payment or entitlement gate before fulfilment, maps that gate to adjacent protocols, and defines a task state machine. Under stated well-formedness constraints and operating assumptions, it yields gate-before-fulfilment safety, at most one task per retained idempotency key, at most one gate acceptance per payment requirement, and an operator-checkable record linking a delivered artefact to operator-controlled records. It defines no protocol, wire format, or conformance requirements.</t>
+        </is>
+      </c>
+      <c r="D514" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-king-yew-choo-agentic-payments/</t>
+        </is>
+      </c>
+      <c r="E514" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F514" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 8 Oct 2026. **Added 28 Oct 2026 sweep.** Agentic payments. A server-side gate for paid, human-sourced asynchronous tasks initiated by agents under authority delegated in advance, handling retries after uncertain outcomes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="5" t="n">
+        <v>514</v>
+      </c>
+      <c r="B515" s="5" t="inlineStr">
+        <is>
+          <t>draft-konda-agentproto-evaluation-state — Preserving Evaluation State in Agent Protocol Decisions</t>
+        </is>
+      </c>
+      <c r="C515" s="5" t="inlineStr">
+        <is>
+          <t>Agent protocols often require a participant to establish a decision- time input before it acts: issuer standing, key availability, delegated authority, policy profile availability, consumption state, revocation status, or the outcome of a downstream operation. A participant that establishes an input and receives a negative answer has learned a different fact from a participant that cannot establish the input at all. Collapsing those facts into one denial or failure value changes retry behavior, alert routing, audit interpretation, incident ownership, and post-incident reconstruction. This document specifies requirements for preserving evaluation state across agent protocol boundaries: the value of an input, whether that value was established at decision time, the freshness of the source used to establish it, and whether the resulting policy decision was actually evaluated. The requirements are stated independently of encoding, so that policy, authorization, revocation, routing, and audit documents can satisfy them in their own formats. Test cases for the requirements are included, with a machine-readable form published separately.</t>
+        </is>
+      </c>
+      <c r="D515" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-konda-agentproto-evaluation-state/</t>
+        </is>
+      </c>
+      <c r="E515" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F515" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 20 Oct 2026. **Added 28 Oct 2026 sweep.** Author Girish Konda. Heavily discussed on the WIMSE list (11 mentions). A participant that establishes a decision-time input — issuer standing, delegated authority, revocation status — and gets a negative or uncertain answer must preserve that state rather than collapse it. Konda also publishes reproducible test cases (`girishkvs/ietf-agent-evidence`).</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="5" t="n">
+        <v>515</v>
+      </c>
+      <c r="B516" s="5" t="inlineStr">
+        <is>
+          <t>draft-larsson-aitlp — Agent Identity, Trust and Lifecycle Protocol (AITLP)</t>
+        </is>
+      </c>
+      <c r="C516" s="5" t="inlineStr">
+        <is>
+          <t>This document defines the Agent Identity, Trust and Lifecycle Protocol (AITLP), a protocol for autonomous software agents operating within organizational boundaries. AITLP specifies agent identity and naming conventions, hierarchical mandate enforcement, lifecycle state management, inter-agent trust verification, ontological scope constraints, certificate-based authentication, and generational knowledge transfer via Agent Legacy Mode (ALM). The protocol enables agents to operate autonomously while remaining auditable, revocable, and organizationally bounded. AITLP focuses on boundaries -- what an agent is not permitted to do and how that is enforced -- complementing capability-focused specifications such as MCP, A2A, and ANS. Unlike those specifications, AITLP defines not a tool or a communication channel, but an organizational actor: an agent with a declared identity, a bounded mandate, a managed lifecycle, and a cryptographically enforced scope of authority.</t>
+        </is>
+      </c>
+      <c r="D516" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-larsson-aitlp/</t>
+        </is>
+      </c>
+      <c r="E516" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F516" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 5 Apr 2026. **Added 28 Oct 2026 sweep.** Agent identity, hierarchical mandate enforcement, lifecycle state and inter-agent trust within organizational boundaries — a full intra-org agent framework. Filed 5 Apr 2026 and never revised; **EXPIRED on Datatracker** 7 Oct 2026 — it predates this sweep's window and surfaced only because expiry updates a draft's timestamp. Kept per the standing rule: an expired draft is still evidence of what was proposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="5" t="n">
+        <v>516</v>
+      </c>
+      <c r="B517" s="5" t="inlineStr">
+        <is>
+          <t>draft-lee-wimse-local-tool-call-proof — Per-Call Proof for Local Tool Invocation by AI Agents</t>
+        </is>
+      </c>
+      <c r="C517" s="5" t="inlineStr">
+        <is>
+          <t>AI agents increasingly act through local tool servers that run on the same host and are reached over inter-process channels such as the stdio transport of the Model Context Protocol (MCP). These channels are outside the scope of HTTP-based authorization: the tool server cannot tell whether a given invocation passed any policy decision, and reusable credentials typically sit in the agent's process memory. This document defines a per-call proof for local tool invocation. A Call Authority that runs outside the agent process evaluates policy, issues a short-lived, single-use proof bound to the exact tool name and arguments through a canonical action digest, and verifies that proof on behalf of the tool server. The tool server rejects invocations whose proof is missing or does not verify. The proof format is opaque to the agent and the tool server; concrete formats are defined as evidence type profiles. An MCP stdio binding is provided.</t>
+        </is>
+      </c>
+      <c r="D517" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-lee-wimse-local-tool-call-proof/</t>
+        </is>
+      </c>
+      <c r="E517" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F517" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 12 Oct 2026. **Added 28 Oct 2026 sweep.** SSenStone. Per-call proof for local tool invocation over inter-process channels such as MCP's stdio transport, which HTTP-based authorization never sees. Fills a real gap: every other WIMSE agent draft assumes HTTP. Discussed on the WIMSE list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="5" t="n">
+        <v>517</v>
+      </c>
+      <c r="B518" s="5" t="inlineStr">
+        <is>
+          <t>draft-lemonnier-scitt-decision-provenance — Decision Provenance for SCITT: binding software releases and agent actions to the decisions behind them</t>
+        </is>
+      </c>
+      <c r="C518" s="5" t="inlineStr">
+        <is>
+          <t>Build attestations, bills of materials and Signed Statements in a Transparency Service record what was built and by whom. None records the decision to ship: who approved it, on what authority, what they were shown, and why. The statement profiles for AI agent actions have the same gap, and say so: their human-approval fields are the producer's claim. This document describes how a decision record and its action-binding attachment, as the extension proposals of the Decision Provenance Standard define them, sit under a release statement, a build attestation or an agent action record by typed digest references; how a verifier checks them offline, including the approver's signature where one is carried; and how the witness checkpoints of the anchoring extension are registered in a Transparency Service. Nothing in the SCITT architecture, in Signed Statements or in Receipts changes. A software release decision and an agent action capsule are the worked examples; the model has no feature specific to either. This document is independent of the Decision Provenance Standard, is not part of it, does not change it, and is not endorsed by its Steward.</t>
+        </is>
+      </c>
+      <c r="D518" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-lemonnier-scitt-decision-provenance/</t>
+        </is>
+      </c>
+      <c r="E518" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F518" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 26 Oct 2026. **Added 28 Oct 2026 sweep.** **A SCITT profile admitted under the SCITT exception** — it is about agent authority, not supply-chain transparency. Records the *decision* to act: who approved, on what authority, what they were shown, and why — and says outright that the existing agent-action profiles leave their human-approval fields unbacked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="5" t="n">
+        <v>518</v>
+      </c>
+      <c r="B519" s="5" t="inlineStr">
+        <is>
+          <t>draft-liu-oauth-authorization-schemas — Domain-Specific Authorization Schemas for OAuth 2.0</t>
+        </is>
+      </c>
+      <c r="C519" s="5" t="inlineStr">
+        <is>
+          <t>This specification defines a framework for constructing fine-grained authorization requests in OAuth 2.0 using domain-specific authorization schemas: structured definitions of behavioral boundaries for a particular application domain. Schema instances are carried in authorization requests via authorization_details; upon approval, the instance governs the authorization associated with the issued access token. Approved instances have a lifecycle: they become active upon approval and end, with defined protocol consequences for token issuance, refresh, and resource access. Resource servers verify client behaviors against the approved schema instance at runtime through deterministic constraint evaluation. Authorization servers review requested schema instances against server-side authorization policies. This specification also defines a negotiation pattern, reverse-guided authorization, allowing resource servers to reference a schema profile in error responses, guiding clients toward the authorization required for their next action.</t>
+        </is>
+      </c>
+      <c r="D519" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-liu-oauth-authorization-schemas/</t>
+        </is>
+      </c>
+      <c r="E519" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F519" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 12 Oct 2026. **Added 28 Oct 2026 sweep.** Author Dapeng Liu (Alibaba). **The draft behind the OAuth list's largest thread this window** — a call for interest in fine-grained authorization for AI agents following IETF 126 (47 messages across two threads), which proposed a design team. Domain-specific authorization schemas define behavioural boundaries for an application domain, carried in `authorization_details`, with goal-state management, task-in-goal evaluation and an RS-guided negotiation pattern. If the design team forms, this is the most likely route by which Complex Delegation acquires a WG deliverable. Same author as `liu-mcguinness-oauth-bounded-work`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="5" t="n">
+        <v>519</v>
+      </c>
+      <c r="B520" s="5" t="inlineStr">
+        <is>
+          <t>draft-luna-eagf-agent-delegation-semantics — Semantic Governance Requirements for AI Agent Delegation and Handoff</t>
+        </is>
+      </c>
+      <c r="C520" s="5" t="inlineStr">
+        <is>
+          <t>AI agents increasingly decide and act on behalf of organizations and delegate work to other agents. Identity, authentication, authorization and runtime control mechanisms establish who is acting and what is permitted, but they do not by themselves preserve the organizational meaning of a delegation: the bounded authority, purpose, material context, and the distinction between a recommendation, a decision, an action and its outcome. This document states requirements, derived from the Enterprise Agent Governance Framework (EAGF), that such semantics be preserved across tool calls, delegations and agent-to-agent handoffs. It defines no new protocol.</t>
+        </is>
+      </c>
+      <c r="D520" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-luna-eagf-agent-delegation-semantics/</t>
+        </is>
+      </c>
+      <c r="E520" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F520" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 19 Oct 2026. **Added 28 Oct 2026 sweep.** Alygn. Posted to the OAuth list ahead of the 26 Oct Mission interim as a response to **Mission-00 §6.2**, which leaves "approval-authority provenance" to a governance layer; this states what that layer must preserve (decision references, purpose, bounded authority across handoffs). No protocol — requirements only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="5" t="n">
+        <v>520</v>
+      </c>
+      <c r="B521" s="5" t="inlineStr">
+        <is>
+          <t>draft-mccormack-ztip — The Zero Trust Intelligence Protocol (ZTIP): Governed, Independently Verified AI Agent Transactions</t>
+        </is>
+      </c>
+      <c r="C521" s="5" t="inlineStr">
+        <is>
+          <t>The Zero Trust Intelligence Protocol (ZTIP) is an open, transport- neutral protocol for governed AI agent transactions. It defines five immutable JSON envelope types and a transaction lifecycle under which every agent-initiated action is authorized by policy before execution, integrity-protected by hash over a canonical form, and -- distinctively -- verified as complete by an authority independent of the actor that performed the work. An executor's claim of success is treated as attestation, and attestation alone never satisfies a required verification check. This revision states what integrity verification does not establish, and specifies the fail-closed rules an implementation MUST apply when it verifies a set of envelopes together, so that a verification report can never claim more than was actually checked. This document describes ZTIP version 1.0-draft for the record; the full specification, JSON Schemas, examples, and a reference runtime are maintained in the open at the repository referenced herein.</t>
+        </is>
+      </c>
+      <c r="D521" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-mccormack-ztip/</t>
+        </is>
+      </c>
+      <c r="E521" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F521" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 18 Oct 2026. **Added 28 Oct 2026 sweep.** Zero Trust Intelligence Protocol: five envelope types and a transaction lifecycle under which every agent-initiated action is policy-authorized before execution, integrity-protected and independently verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="5" t="n">
+        <v>521</v>
+      </c>
+      <c r="B522" s="5" t="inlineStr">
+        <is>
+          <t>draft-mih-agent-settlement-records — Two-Party Settlement Records for Agent Payments</t>
+        </is>
+      </c>
+      <c r="C522" s="5" t="inlineStr">
+        <is>
+          <t>A payment between two agents is observed by two systems: the payer's wallet or bank and the payee's. Existing payment protocols record one of those observations, signed by one party, and most record nothing about what was delivered in exchange. This document defines two-party settlement records, carried as Agent Action Capsules, in which payer and payee each seal, under their own key, only what their own system observed. A settlement is a set of up to four leg records (terms, payer-observed, payee-observed, and delivered) that cite each other by digest and join on a typed payment reference. The state of a settlement (one-sided, agreed, or mismatched) is derived by the verifier from which legs are present and whether they agree; no record asserts it. Signed objects from existing payment protocols are carried by digest and never re-signed. Amounts are exact integers with a decimal scale. The document defines a registry of payment reference types covering x402, Lightning, AP2, ACP, UCP, the Payment HTTP authentication scheme, ISO 20022, and Open Payments, and maps its states to ISO 20022 status codes.</t>
+        </is>
+      </c>
+      <c r="D522" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-mih-agent-settlement-records/</t>
+        </is>
+      </c>
+      <c r="E522" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F522" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 2 Oct 2026. **Added 28 Oct 2026 sweep.** Agentic payments. Two-party settlement records — payer's and payee's observations, plus what was delivered — carried as Agent Action Capsules. The rest of the `mih-` output is SCITT/log infrastructure and is not tracked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="5" t="n">
+        <v>522</v>
+      </c>
+      <c r="B523" s="5" t="inlineStr">
+        <is>
+          <t>draft-milan-agent-decision-commitment — Agent Decision Commitments for Payments</t>
+        </is>
+      </c>
+      <c r="C523" s="5" t="inlineStr">
+        <is>
+          <t>Software agents increasingly select and initiate payments on behalf of people and organizations. Existing agent payment protocols record what a principal authorized and that value moved, but not what information the agent relied on when it chose. This document defines the Agent Decision Commitment (ADC): a salted hash commitment to a decision record that identifies the content the agent provided to the model interface (after any agent-side transformation), the model calls made, and the resulting answer and action. The commitment is carried as a single selectively disclosable claim in an existing payment mandate or payment payload and is, by default, registered with a transparency service before the payment is authorized. The decision record and its content remain with the holder and are disclosed only to dispute participants, who can verify them against the mandate and the transparency service and can inspect the content the agent provided to the model. This document defines the data model, the commitment and anchoring procedures, a disclosure and verification procedure that reports attestation levels rather than verdicts, and bindings to three agent payment protocols and to account-to-account credit transfers. It also defines a witnessed reciprocal exchange by which two parties' agents evidence what passed between them: the receiver signs over the committed bytes, independent witnesses fix the time of each step, a failure to answer by a deadline is recorded, and arbiters resolve stalled exchanges.</t>
+        </is>
+      </c>
+      <c r="D523" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-milan-agent-decision-commitment/</t>
+        </is>
+      </c>
+      <c r="E523" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F523" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 15 Oct 2026. **Added 28 Oct 2026 sweep.** Agentic payments. A salted hash commitment to the information an agent relied on when it chose a payment — the missing "why" between a mandate and a settlement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="5" t="n">
+        <v>523</v>
+      </c>
+      <c r="B524" s="5" t="inlineStr">
+        <is>
+          <t>draft-morrow-sogomonian-exec-outcome-attest — Execution Outcome Attestation for AI Agents and Automated Systems</t>
+        </is>
+      </c>
+      <c r="C524" s="5" t="inlineStr">
+        <is>
+          <t>Current attestation frameworks establish that a system or agent is trustworthy at a point in time. They do not address whether that system actually performed a claimed action or whether the outcome of that action can be independently verified. This document defines execution outcome verification as a first-class concept, separate from identity attestation and communication transport. It introduces the execution receipt as a minimal composable primitive, provides a formal abstract model, and maps the model to concrete realizations including SCITT transparency logs, tightly-coupled direct verification, append-only local logs, and TEE-internal receipts.</t>
+        </is>
+      </c>
+      <c r="D524" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-morrow-sogomonian-exec-outcome-attest/</t>
+        </is>
+      </c>
+      <c r="E524" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F524" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 4 Apr 2026. **Added 28 Oct 2026 sweep.** AI Internet Foundation — Sogomonian is the author of the tracked `aiip-*` pair (the AIP COLLISION). Execution-outcome verification as a first-class concept separate from attesting that an agent is trustworthy. Filed 4 Apr 2026 and never revised; **EXPIRED on Datatracker** 6 Oct 2026 — it predates this sweep's window and surfaced only because expiry updates a draft's timestamp. Kept per the standing rule: an expired draft is still evidence of what was proposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="5" t="n">
+        <v>524</v>
+      </c>
+      <c r="B525" s="5" t="inlineStr">
+        <is>
+          <t>draft-mozley-aidiscovery — AI Agent Discovery (AID) Problem Statement</t>
+        </is>
+      </c>
+      <c r="C525" s="5" t="inlineStr">
+        <is>
+          <t>With the proliferation of AI agents comes a need for mechanisms to support agent-to-agent discovery. This document discusses the scope, requirements and considerations to support discovery processes so that these are not reliant on manually defined configurations and relationships.</t>
+        </is>
+      </c>
+      <c r="D525" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-mozley-aidiscovery/</t>
+        </is>
+      </c>
+      <c r="E525" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F525" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 16 Apr 2026. **Added 28 Oct 2026 sweep.** Deutsche Telekom + Infoblox. An agent-discovery problem statement. **New COLLISION: "AID" again** — "AI Agent Discovery (AID)" joins `nemethi-dawn-aid`, `nemethi-aid-agent-identity-discovery`, Watts's AID-1 and Drake's `aid` URN. Name the full slug. Filed 16 Apr 2026 and never revised; **EXPIRED on Datatracker** 18 Oct 2026 — it predates this sweep's window and surfaced only because expiry updates a draft's timestamp. Kept per the standing rule: an expired draft is still evidence of what was proposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="5" t="n">
+        <v>525</v>
+      </c>
+      <c r="B526" s="5" t="inlineStr">
+        <is>
+          <t>draft-mw-oauth-actor-chain-overview — OAuth Actor Chain: Overview and Design</t>
+        </is>
+      </c>
+      <c r="C526" s="5" t="inlineStr">
+        <is>
+          <t>A request can pass through several services before reaching an API. OAuth Token Exchange can represent an actor history in nested act claims. It leaves the rules for constructing that history, limiting its disclosure, and verifying an actor's own signature to additional profiles. Actor Chain proposes those rules while keeping the Authorization Server responsible for issuing tokens and applying policy. This document provides a new overview of the authors' Actor Chain proposal, whose Internet-Draft lineage began in SPICE in February 2026. The companion OAuth Actor Chain: Protocol and Interoperability specification continues the existing OAuth draft series and defines wire formats and processing requirements.</t>
+        </is>
+      </c>
+      <c r="D526" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-mw-oauth-actor-chain-overview/</t>
+        </is>
+      </c>
+      <c r="E526" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F526" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 18 Oct 2026. **Added 28 Oct 2026 sweep.** **Same five authors as the tracked `mw-oauth-actor-chain`** (verified by person id), which sits next to the McGuinness Actor Profile because it responds to it. An overview-and-design companion: rules for constructing an actor history in nested `act` claims, limiting its disclosure, and verifying an actor's own signature.</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="5" t="n">
+        <v>526</v>
+      </c>
+      <c r="B527" s="5" t="inlineStr">
+        <is>
+          <t>draft-narajala-courtney-ansv2 — Agent Name Service v2 (ANS): A Domain-Anchored Identity Layer for Autonomous AI Agents</t>
+        </is>
+      </c>
+      <c r="C527" s="5" t="inlineStr">
+        <is>
+          <t>Autonomous AI agents now invoke one another across organizational boundaries over protocols such as the Model Context Protocol (MCP) and Agent2Agent (A2A). A relying party has no interoperable way to bind a discoverable agent endpoint to the holder of its domain (optionally verified as a legal entity), a specific software release, and an auditable issuance history. This document specifies the architecture of Agent Name Service version 2 (ANS v2), an identity layer, anchored in DNS domains, that binds an agent endpoint to its domain holder, its release, and its history. ANS v2 composes systems the Internet already runs (the DNS with DNSSEC; the Web PKI, with DANE where operators publish it; and an append-only transparency log) and introduces no new root of trust. Every ANS v2 agent carries a versioned name rooted in a DNS domain that the registrant controls. When a registrant registers an agent, the Registration Authority (RA) checks the registrant's control of that domain, can issue an Identity Certificate that binds the versioned name to the agent's key, and submits a signed registration record to a Merkle-tree transparency log. Under the current specifications, a new version is a new registration and a new log entry, so a verifier can pin an agent to a specific release. Any third party can detect a rewritten log by computing, from the log's public tiles, a consistency proof between two of its signed checkpoints. For discovery, ANS v2 adopts the SVCB records and SvcParams of DNS for AI Discovery (DNS-AID) as its default format, and keeps an older TXT-based format only as an opt-in profile. Beyond those discovery records, ANS v2 specifies one DNS record, an "_ans-badge" TXT record that points to the agent's transparency-log entry; the log seals the fingerprint of the agent server's certificate, and operators can add DANE records. With these records, a verifier resolves an agent, authenticates its TLS endpoint, and confirms that the presented name, version, and key match a logged registration. This document also states a threat model covering agent impersonation, DNS spoofing, CA and Registration Authority compromise, version rollback, agent card tampering, and log rewriting, and names what each ANS check does and does not prevent. The reference registry, transparency log, verifier, JSON Schemas, SDKs, and CLI are open source.</t>
+        </is>
+      </c>
+      <c r="D527" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-narajala-courtney-ansv2/</t>
+        </is>
+      </c>
+      <c r="E527" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F527" s="5" t="inlineStr">
+        <is>
+          <t>Revision -02, 26 Oct 2026. **Added 28 Oct 2026 sweep.** Cisco, GoDaddy, OWASP and DistributedApps.ai. **Replaces `draft-narajala-ans`** (untracked). Agent Name Service v2 binds a discoverable agent endpoint to its domain holder (optionally verified as a legal entity), a specific software release and its keys. The registry corner with the heaviest industry backing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="5" t="n">
+        <v>527</v>
+      </c>
+      <c r="B528" s="5" t="inlineStr">
+        <is>
+          <t>draft-narvaneni-agent-uri — The agent URI Scheme and Verifiable Agent Identity</t>
+        </is>
+      </c>
+      <c r="C528" s="5" t="inlineStr">
+        <is>
+          <t>Software agents increasingly act on the Internet on behalf of people and organizations: they call APIs, browse websites, and delegate work to other agents. Protocols such as A2A and MCP define how agents communicate, but there is no interoperable way to answer a prior question: _which agent is this, and how can its claims be verified?_ This document defines the agent URI scheme as a stable, human- readable identifier for an agent, a deterministic mapping from that identifier to an HTTPS-hosted Agent Identity Document, anchoring of the agent's keys to a web origin or a Decentralized Identifier, and signed statements that bind the agent to its protocol metadata. It also defines profiles that let an agent prove its identity on HTTP requests, building on HTTP Message Signatures for automated traffic, and that let short-lived agent instances act under the agent's identity using the WIMSE Workload Identity Token format. It deliberately does not define how agents communicate, describe their capabilities, or are invoked.</t>
+        </is>
+      </c>
+      <c r="D528" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-narvaneni-agent-uri/</t>
+        </is>
+      </c>
+      <c r="E528" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F528" s="5" t="inlineStr">
+        <is>
+          <t>Revision -04, 20 Oct 2026. **Added 28 Oct 2026 sweep.** An `agent` URI scheme with verifiable agent identity. Already -04 but never tracked. Not the same document as `kanojia-creduent-agent-uri` (tracked), which registers a similarly named scheme — a near-collision on the `agent:` URI scheme itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="5" t="n">
+        <v>528</v>
+      </c>
+      <c r="B529" s="5" t="inlineStr">
+        <is>
+          <t>draft-neve-ucap — Universal Crawler Accountability Protocol (UCAP)</t>
+        </is>
+      </c>
+      <c r="C529" s="5" t="inlineStr">
+        <is>
+          <t>Automated HTTP clients, including search crawlers, indexing bots, archivers, and AI-assisted agents, routinely access Web origins. Existing identification mechanisms do not consistently give an origin operator a way to verify a particular request, report alleged abuse, follow the report's disposition, or request that an operator stop accessing an origin. This document proposes the Universal Crawler Accountability Protocol (UCAP), an opt-in interoperable HTTP interface for these tasks. UCAP associates a per-request opaque identifier with a cryptographically authenticated automated client, defines operator-hosted verification, abuse-reporting and case-status resources, and defines a domain-scoped exclusion request with acknowledgment and status. UCAP builds on HTTP Message Signatures and does not replace robots.txt or existing site access controls. The verification service does not identify an end user to the origin. This initial proposal requires further review of its privacy, authorization, and operational trade-offs.</t>
+        </is>
+      </c>
+      <c r="D529" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-neve-ucap/</t>
+        </is>
+      </c>
+      <c r="E529" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F529" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 9 Oct 2026. **Added 28 Oct 2026 sweep.** Universal Crawler Accountability Protocol: an origin can verify a request from an automated client, report abuse and follow its disposition. Adjacent to Web Bot Auth and AIPREF. Pair with `neve-ucap-access`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="5" t="n">
+        <v>529</v>
+      </c>
+      <c r="B530" s="5" t="inlineStr">
+        <is>
+          <t>draft-neve-ucap-access — Automated Content Access Negotiation and Delegated Rights Authorization for UCAP</t>
+        </is>
+      </c>
+      <c r="C530" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies an interoperable HTTP protocol for automated clients, including conventional web crawlers and AI-assisted agents, to request access to a resource, receive a transaction-specific offer, accept the offer, and obtain a cryptographically verifiable authorization for a particular request. Resource owners can perform authorization directly or delegate it to independent rights managers of any size. A rights manager determines the price and other conditions at the time of each request; this protocol does not expose or constrain pricing algorithms, payment rails, credit limits, invoicing schedules, or business relationships. The protocol binds an authorization to a request UUID, resource, authenticated crawler operator, intended use, and validity interval. It is designed as an optional extension to the proposed Universal Crawler Accountability Protocol (UCAP) and to existing HTTP authentication and bot identity mechanisms. The specification does not replace access controls, copyright law, or private commercial agreements.</t>
+        </is>
+      </c>
+      <c r="D530" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-neve-ucap-access/</t>
+        </is>
+      </c>
+      <c r="E530" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F530" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 9 Oct 2026. **Added 28 Oct 2026 sweep.** The authorization half of UCAP: an automated client requests access, receives a transaction-specific offer and obtains a verifiable authorization for one request — delegated rights authorization for crawlers and agents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="5" t="n">
+        <v>530</v>
+      </c>
+      <c r="B531" s="5" t="inlineStr">
+        <is>
+          <t>draft-nivalto-agentroa-route-authorization — Agent Route Origin Authorization (AgentROA): A Cryptographic Policy Enforcement Framework for AI Agent Actions</t>
+        </is>
+      </c>
+      <c r="C531" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies the Agent Route Origin Authorization (AgentROA) framework, a cryptographic policy enforcement model for governing the actions of autonomous AI agents. AgentROA introduces three core protocol objects: the Agent Route Origin Authorization (ROA) envelope, the Agent Route Attestation (ARA) per-hop receipt, and the Agent Execution Receipt (AER). Together these objects enable: (1) cryptographic binding of an agent's authorized action scope to a signed policy envelope at session initialization, (2) per-hop attestation across multi-agent delegation chains with monotonic scope-narrowing semantics (no policy envelope may be expanded by a downstream delegation), and (3) cryptographic receipts produced intrinsically by the enforcement decision at each capability invocation boundary. The framework is modeled on the BGP Route Origin Authorization (ROA) concept from RPKI (RFC 6480) applied to the AI agent execution domain. The Border Gateway enforcement model positions a cryptographic enforcement process at a capability invocation boundary — external to the agent's execution context — reducing the risk that governance decisions are influenced by the governed agent by placing enforcement in a separate process boundary. The Border Gateway model is topology-independent: it may be deployed as a protocol- specific proxy in front of Model Context Protocol (MCP) servers, as a service mesh enforcement component covering all inter-service calls, as a network egress gateway covering all outbound capability invocations regardless of protocol, or as a domain-specific execution boundary. The protocol objects defined herein function identically across all deployment topologies. This document establishes the architectural model, protocol object schemas, and enforcement semantics for the AgentROA framework.</t>
+        </is>
+      </c>
+      <c r="D531" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-nivalto-agentroa-route-authorization/</t>
+        </is>
+      </c>
+      <c r="E531" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F531" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 16 Apr 2026. **Added 28 Oct 2026 sweep.** Borrows RPKI's ROA vocabulary for agents: a Route Origin Authorization envelope, per-hop Agent Route Attestation receipts and enforcement. Note it is *agent* route authorization, not BGP — the name invites confusion with the RPKI drafts the curation bar excludes. Filed 16 Apr 2026 and never revised; **EXPIRED on Datatracker** 18 Oct 2026 — it predates this sweep's window and surfaced only because expiry updates a draft's timestamp. Kept per the standing rule: an expired draft is still evidence of what was proposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="5" t="n">
+        <v>531</v>
+      </c>
+      <c r="B532" s="5" t="inlineStr">
+        <is>
+          <t>draft-nyantakyi-vaip-agent-identity — Vorim Agent Identity Protocol (VAIP)</t>
+        </is>
+      </c>
+      <c r="C532" s="5" t="inlineStr">
+        <is>
+          <t>This document defines the Vorim Agent Identity Protocol (VAIP), a standard for establishing verifiable cryptographic identity, fine- grained permissions, trust scoring, and tamper-evident audit trails for autonomous AI agents. As AI agents increasingly perform actions autonomously in enterprise systems, existing identity protocols designed for human users or static services are insufficient. VAIP addresses this gap by providing cryptographic primitives and data structures for issuing, verifying, and managing agent identities in multi-tenant environments. The protocol uses Ed25519 for agent identity, SHA-256 for audit integrity, and defines seven hierarchical permission scopes with time-bounded grants and rate limiting.</t>
+        </is>
+      </c>
+      <c r="D532" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-nyantakyi-vaip-agent-identity/</t>
+        </is>
+      </c>
+      <c r="E532" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F532" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 11 Apr 2026. **Added 28 Oct 2026 sweep.** Vorim AI. Identity, fine-grained permissions, trust scoring and audit for enterprise agents. A seventh three-letter agent identity protocol in a space already carrying the AIP COLLISION. Filed 11 Apr 2026 and never revised; **EXPIRED on Datatracker** 13 Oct 2026 — it predates this sweep's window and surfaced only because expiry updates a draft's timestamp. Kept per the standing rule: an expired draft is still evidence of what was proposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="5" t="n">
+        <v>532</v>
+      </c>
+      <c r="B533" s="5" t="inlineStr">
+        <is>
+          <t>draft-piehl-agent-rule-provenance — Rule Provenance for Autonomous AI Agent Audit Records</t>
+        </is>
+      </c>
+      <c r="C533" s="5" t="inlineStr">
+        <is>
+          <t>This document describes an experimental profile of the Agent Audit Trail format for AI agents. The profile records the rules an agent operates under: each version of each rule, who set and approved it, and which rules were in force when a decision was made. It keeps a decision separate from any later approval or override, binds it to the exact request, and requires that records of consequential actions go to a recorder independent of the operator and be anchored in a public log. It also sets out what these records can and cannot prove.</t>
+        </is>
+      </c>
+      <c r="D533" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-piehl-agent-rule-provenance/</t>
+        </is>
+      </c>
+      <c r="E533" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F533" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 11 Oct 2026. **Added 28 Oct 2026 sweep.** A profile of `sharif-agent-audit-trail` (tracked) recording which rules an agent ran under, who set and approved each version, and which were in force at decision time. An inbound composer for the Sharif family.</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="5" t="n">
+        <v>533</v>
+      </c>
+      <c r="B534" s="5" t="inlineStr">
+        <is>
+          <t>draft-saha-aadp-bound-permit — Action-Bound Permits for the Agent Action Decision Protocol (AADP): Carrying a Per-Action Decision Across a Trust Boundary</t>
+        </is>
+      </c>
+      <c r="C534" s="5" t="inlineStr">
+        <is>
+          <t>The Agent Action Decision Protocol (AADP) decides, per action, whether an agent's concrete request may proceed now, and assumes that the decision is consumed by an enforcement point on the same secured channel that issued it. AADP identifies, as a planned extension, a permit that must be honoured across a trust boundary, and defines the "present_bound" obligation as its hook. This document specifies that extension. An action-bound permit is a permit signed by the decision point, bound to one recipient, one presenter key, one HTTP request and one decided action instance, and short-lived. It composes with mandate formats such as the Agent Authorization Envelope, which carry what a recipient can evaluate for itself; the bound permit carries a decision the recipient cannot recompute, because it depends on state held by the issuer: cumulative budgets, live reservations, approval lifecycle and escalation. The document adds scoped trust in issuers, a declared currentness mode, a mandate reference, a verification order with registered refusal reasons, and a confirmation the recipient signs. It builds on existing specifications for every mechanism it can, and defines no new signature format, token format or policy language.</t>
+        </is>
+      </c>
+      <c r="D534" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-saha-aadp-bound-permit/</t>
+        </is>
+      </c>
+      <c r="E534" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F534" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 29 Sep 2026. **Added 28 Oct 2026 sweep.** Extends the tracked `saha-aadp` with the cross-trust-boundary permit its base document names as a planned extension: a per-action permit an enforcement point on a different channel can honour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="5" t="n">
+        <v>534</v>
+      </c>
+      <c r="B535" s="5" t="inlineStr">
+        <is>
+          <t>draft-sergeev-audit-task-requirements — Task-Relative Evidence Requirements for Agent Auditing</t>
+        </is>
+      </c>
+      <c r="C535" s="5" t="inlineStr">
+        <is>
+          <t>Agent auditing can rely on information produced by users, agents, tools, services, policy components, and other systems across multiple administrative domains. The evidence needed to answer one auditing question is not necessarily the evidence needed to answer another. Successful verification of available evidence also does not, by itself, establish that the evidence is applicable or sufficient for the question being evaluated. This document describes a representation-independent model for stating an Audit Task, alternative evidence requirements for that task, expectations about evidence production, and the basis for an audit result. It distinguishes verification of evidence from evaluation of the Audit Task, missing evidence from a negative observation, and validity of individual records from cross-domain sufficiency. It defines no audit record format, verification mechanism, authorization model, completeness mechanism, storage protocol, or auditing policy.</t>
+        </is>
+      </c>
+      <c r="D535" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-sergeev-audit-task-requirements/</t>
+        </is>
+      </c>
+      <c r="E535" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F535" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 16 Oct 2026. **Added 28 Oct 2026 sweep.** Sergeev (tracked: `sergeev-claim-boundaries`). The evidence needed to answer one audit question is not the evidence needed for another, and verifying available evidence does not establish adequacy. Directly relevant to the AUDIT BoF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="5" t="n">
+        <v>535</v>
+      </c>
+      <c r="B536" s="5" t="inlineStr">
+        <is>
+          <t>draft-shankarlingam-oauth-agent-dns-link — Linking an Agent's DNS Name to its OAuth Client</t>
+        </is>
+      </c>
+      <c r="C536" s="5" t="inlineStr">
+        <is>
+          <t>Software agents increasingly call agents and services operated by other organizations. A receiving organization often wants to know two things about any such caller: that it is the agent it claims to be, and that the organization operating it still authorizes it. Existing approaches to the second question require a trust relationship between the two organizations' authorization servers. This document defines a DNS record by which the owner of a domain links an agent's DNS name to the OAuth client that the agent uses at the owner's own authorization server. The sending agent presents a fresh access token for that client; the receiver verifies the token against the record and against the issuer's published keys. No trust relationship, registration or federation between the two organizations is needed, and disabling the client at the sending organization's authorization server stops the agent being accepted by every receiver.</t>
+        </is>
+      </c>
+      <c r="D536" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-shankarlingam-oauth-agent-dns-link/</t>
+        </is>
+      </c>
+      <c r="E536" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F536" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 28 Oct 2026. **Added 28 Oct 2026 sweep.** HexaEight. Links an agent's DNS name to its OAuth client so a receiving organization can check both that the caller is the agent it claims and that its operator still authorizes it — without a pre-existing trust relationship. Cited on the WIMSE list; revised to -01 on the day of this sweep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="5" t="n">
+        <v>536</v>
+      </c>
+      <c r="B537" s="5" t="inlineStr">
+        <is>
+          <t>draft-srivastava-agentproto-handoff-context — Signed Handoff Context for Agentic Dialogs</t>
+        </is>
+      </c>
+      <c r="C537" s="5" t="inlineStr">
+        <is>
+          <t>When one agent hands a task to another, the receiving agent often needs to know who handed it over, on whose behalf, through which earlier agents, and which prior context the work depends on. It also needs to know that the handoff is fresh and meant for it, and the sender needs a clear answer back. This document describes a small, transport-neutral handoff context: a signed offer, a signed status reply, and the chain of earlier offers that led to the current one, defined in CDDL for JSON and CBOR, with a lifecycle that maps to Agent2Agent task states. Each offer names the one before it by hash, so that a dropped or reordered intermediate hop can be detected when the chain is carried. Prior context is named by digest only; any log or transparency service behind it is opaque. Appendices show how a SCITT receipt or a Learnlog signed head can be referenced. The document is offered as input to the agentproto working group's use cases and dialog-context work.</t>
+        </is>
+      </c>
+      <c r="D537" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-srivastava-agentproto-handoff-context/</t>
+        </is>
+      </c>
+      <c r="E537" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F537" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 26 Oct 2026. **Added 28 Oct 2026 sweep.** Signed handoff context: who handed the task over, on whose behalf, through which earlier agents, and on what prior context — fresh and audience-bound, with an acknowledgement back. The delegation chain stated in agentproto terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="5" t="n">
+        <v>537</v>
+      </c>
+      <c r="B538" s="5" t="inlineStr">
+        <is>
+          <t>draft-swarmspeak-handshake — The SwarmSpeak Handshake Protocol, Version 1.1</t>
+        </is>
+      </c>
+      <c r="C538" s="5" t="inlineStr">
+        <is>
+          <t>AI agents are becoming some of the biggest users of the Internet. A site today has no neutral way to tell a good agent from a bot. The site sees either an anonymous request it cannot trust, or a request carrying a long-lived credential it cannot check. The result is blunt blocking on one side and unchecked abuse on the other. This document defines the SwarmSpeak Handshake, a protocol that lets an AI agent present a short-lived, narrowly scoped, signed statement of who it acts for and what it is allowed to do, and lets a site verify that statement cheaply before serving the request. The agent proves authority with a principal-signed capability certificate, a short-lived directory-signed status proof, and an HTTP Message Signature. The site sees only a per-origin pseudonym for the agent, never a global tracking identifier. Every completed session at a handshake-accepting site produces an itemized receipt, and receipted sessions are recorded in an append-only audit log. This is an individual submission. It is not a product of any IETF working group, it has not been reviewed by any IETF working group, and it does not represent IETF consensus. It is published to invite review and to record prior art for the shapes defined here: the capability certificate, the per-origin certificate view, the short-lived status proof, and the receipt.</t>
+        </is>
+      </c>
+      <c r="D538" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-swarmspeak-handshake/</t>
+        </is>
+      </c>
+      <c r="E538" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F538" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 19 Oct 2026. **Added 28 Oct 2026 sweep.** A handshake for sites to tell a good agent from a bot without either an anonymous request or a long-lived credential. Competes with Web Bot Auth's HTTP Message Signatures approach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="5" t="n">
+        <v>538</v>
+      </c>
+      <c r="B539" s="5" t="inlineStr">
+        <is>
+          <t>draft-thaha-wimse-agent-evidence-binding — Evidence Binding for AI Agent Credentials</t>
+        </is>
+      </c>
+      <c r="C539" s="5" t="inlineStr">
+        <is>
+          <t>The WIMSE AI Identity Management System (AIMS) requires tamper- evident agent audit logs but does not specify their format or discovery. This document maps the AIMS minimum fields to the SCITT Agent Execution Evidence profile, defines one claim that binds a workload credential to the persistent agent, governing policy, expected Evidence Service and optional Assurance Statement, and defines an in-toto predicate type for carrying Execution Receipts in the audit format proposed for WIMSE. It also describes how a service admits an agent's call by checking its assurance at the moment of the request, and defines an HTTP field that links each call to the caller's evidence. It is input to the AIMS work and makes no change to it.</t>
+        </is>
+      </c>
+      <c r="D539" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-thaha-wimse-agent-evidence-binding/</t>
+        </is>
+      </c>
+      <c r="E539" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F539" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 19 Oct 2026. **Added 28 Oct 2026 sweep.** Maps the AIMS minimum audit fields to a SCITT execution-evidence profile and defines one claim binding a workload credential to the persistent agent, its governing policy and expected behaviour. Announced on the WIMSE list (7 messages). Its SCITT dependency, `thaha-scitt-agent-execution-evidence`, is **not** tracked under the SCITT rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="5" t="n">
+        <v>539</v>
+      </c>
+      <c r="B540" s="5" t="inlineStr">
+        <is>
+          <t>draft-thallapelly-oasnt-caid — OASNT-CAID: Canonical Action Identifier Derivation and the Named-Human Binding</t>
+        </is>
+      </c>
+      <c r="C540" s="5" t="inlineStr">
+        <is>
+          <t>This document profiles OASNT tokens for consumption by executor-side processing models. It fixes one normative derivation of a Canonical Action Identifier (CAID) from the OASNT action digest, so that every executor checks the same derivation rather than each integration defining its own, and it specifies the semantics of the token's named-human binding, including a subject-to-enrollment check whose absence this profile makes a refusal.</t>
+        </is>
+      </c>
+      <c r="D540" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-thallapelly-oasnt-caid/</t>
+        </is>
+      </c>
+      <c r="E540" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F540" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 4 Aug 2026. **Added 28 Oct 2026 sweep.** Companion to the tracked `thallapelly-oasnt`. Filed Aug 2026 and **missed by two sweeps** — surfaced on the WIMSE list. Fixes one normative derivation of a Canonical Action Identifier from the OASNT action digest and the named-human binding. A third canonical action identifier, beside Schrock's CAID and `etcheverry-action-ref`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="5" t="n">
+        <v>540</v>
+      </c>
+      <c r="B541" s="5" t="inlineStr">
+        <is>
+          <t>draft-thallapelly-oasnt-enforce — OASNT-ENFORCE: Request-Bound Enforcement of Attested Action Authorization</t>
+        </is>
+      </c>
+      <c r="C541" s="5" t="inlineStr">
+        <is>
+          <t>This document profiles the enforcement of OASNT tokens at the point of execution. It defines the OASNT-Token HTTP field, the rules by which an enforcement point derives the observed request from the octets it will itself forward, a verification procedure for relying parties that hold no request-to-action mapping, uniform refusal behavior, and the set of refusals a conforming enforcement point is required to produce. It further defines an optional grp claim and an exclusivity ledger, by which a set of tokens issued from one human confirmation is made spendable only once between them, and fixes which relying party in a deployment performs that consumption. An enforcement point conforming to this profile makes a human approval a precondition of execution for the requests it fronts, without any change to the protected service.</t>
+        </is>
+      </c>
+      <c r="D541" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-thallapelly-oasnt-enforce/</t>
+        </is>
+      </c>
+      <c r="E541" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F541" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 15 Aug 2026. **Added 28 Oct 2026 sweep.** Companion to `thallapelly-oasnt`; filed Aug 2026, missed by two sweeps. Request-bound enforcement of OASNT tokens: an `OASNT-Token` HTTP field and a procedure for relying parties that hold no request-to-action mapping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="5" t="n">
+        <v>541</v>
+      </c>
+      <c r="B542" s="5" t="inlineStr">
+        <is>
+          <t>draft-tulshi-oauth-transactional-access-tokens — Transactional Access Tokens</t>
+        </is>
+      </c>
+      <c r="C542" s="5" t="inlineStr">
+        <is>
+          <t>OAuth 2.0 access tokens are typically scoped to a session rather than to a transaction. They carry no transaction identifier and no context beyond scope. This document defines Transactional Access Tokens: a profile of JSON Web Token (JWT) access tokens that carries a transaction identifier and authorization server-asserted transaction context, has a very short lifetime, and is audienced to a single resource server. Transactional Access Tokens align with the claims and semantics of OAuth Transaction Tokens, so that transaction context can flow from the authorization server to a resource server and onward into that resource server's trust domain. A primary use case is task-scoped authorization of AI agents, where the authorization server makes a fresh policy decision for each transaction.</t>
+        </is>
+      </c>
+      <c r="D542" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-tulshi-oauth-transactional-access-tokens/</t>
+        </is>
+      </c>
+      <c r="E542" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F542" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 30 Sep 2026. **Added 28 Oct 2026 sweep.** Author Atul Tulshibagwale (CrowdStrike; CAEP/SSF editor). JWT access tokens that carry a transaction identifier and AS-asserted transaction context, scoping access to a transaction rather than a session. Discussed on both the OAuth and WIMSE lists; read against Transaction Tokens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="5" t="n">
+        <v>542</v>
+      </c>
+      <c r="B543" s="5" t="inlineStr">
+        <is>
+          <t>draft-valverde-oauth-pact — PACT: Private Agent Consent and Trust Profile for OAuth 2.1 and CIBA</t>
+        </is>
+      </c>
+      <c r="C543" s="5" t="inlineStr">
+        <is>
+          <t>PACT (Private Agent Consent and Trust Profile) is a security profile of OAuth 2.1 for privacy-preserving agent delegation. It extends VEIL and composes OIDC CIBA Core 1.0 and OAuth Token Exchange (RFC 8693). PACT defines a durable-host plus ephemeral-session control plane, a delegation token claim vocabulary, runtime identity proofs using Ed25519 JWTs, capability grants with typed constraints and usage limits, risk-graduated consent routing, and claim narrowing on token exchange to non-agent audiences.</t>
+        </is>
+      </c>
+      <c r="D543" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-valverde-oauth-pact/</t>
+        </is>
+      </c>
+      <c r="E543" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F543" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 18 Apr 2026. **Added 28 Oct 2026 sweep.** Zentity. An OAuth 2.1 security profile for privacy-preserving agent delegation composing CIBA and Token Exchange, with a durable-host / ephemeral-session control plane. **Acronym note:** "PACT" is also `laxsharma-pact` (tracked) and Decagon's PACT — three unrelated uses. Filed 18 Apr 2026 and never revised; **EXPIRED on Datatracker** 20 Oct 2026 — it predates this sweep's window and surfaced only because expiry updates a draft's timestamp. Kept per the standing rule: an expired draft is still evidence of what was proposed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="5" t="n">
+        <v>543</v>
+      </c>
+      <c r="B544" s="5" t="inlineStr">
+        <is>
+          <t>draft-zambo-aer1-wimse-mapping — AER-1 Receipts as Audit Records for WIMSE AIMS</t>
+        </is>
+      </c>
+      <c r="C544" s="5" t="inlineStr">
+        <is>
+          <t>The WIMSE AI Identity Management System (AIMS) framework requires deployments to produce durable audit logs covering authorization decisions and subsequent remediations, requires those audit records to be tamper-evident, lists the minimum fields an audit event records, and calls for reconstruction of complete execution chains across service boundaries. AIMS deliberately specifies no audit record format. This document supplies one candidate: it maps each AIMS audit requirement onto the AER-1 execution receipt, field by field, shows how AER-1 hash-chained timelines and workflow receipts reconstruct an execution chain, and defines an optional carriage of AER-1 receipts as SCITT statements for deployments that operate a transparency service. The mapping changes no AER-1 field, digest construction, or verification rule, and it states plainly what a receipt does not prove.</t>
+        </is>
+      </c>
+      <c r="D544" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-zambo-aer1-wimse-mapping/</t>
+        </is>
+      </c>
+      <c r="E544" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F544" s="5" t="inlineStr">
+        <is>
+          <t>Revision -01, 27 Oct 2026. **Added 28 Oct 2026 sweep.** Maps the tracked `zambo-aer1` execution receipts onto the WIMSE AIMS audit-record requirements. With `gilda-audit-agent-audit-record` and `thaha-wimse-agent-evidence-binding`, **three competing AIMS audit-record mappings** arrived in one window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="5" t="n">
+        <v>544</v>
+      </c>
+      <c r="B545" s="5" t="inlineStr">
+        <is>
+          <t>draft-zehavi-oauth-audience-bound-token-exchange — OAuth 2.0 Audience-Bound Token Exchange</t>
+        </is>
+      </c>
+      <c r="C545" s="5" t="inlineStr">
+        <is>
+          <t>In deployments where resource servers are invoked using access tokens with a restricted audience, resource servers that need to call downstream services must first exchange received tokens so their audience is appropriate for the downstream service.</t>
+        </is>
+      </c>
+      <c r="D545" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-zehavi-oauth-audience-bound-token-exchange/</t>
+        </is>
+      </c>
+      <c r="E545" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F545" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 8 Oct 2026. **Added 28 Oct 2026 sweep.** Raiffeisen Bank International. Token Exchange for resource servers that must re-scope a restricted-audience token before calling downstream. Related list threads (Kieran Sweeney's reviews) push toward expressing the downstream party via `may_act`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="5" t="n">
+        <v>545</v>
+      </c>
+      <c r="B546" s="5" t="inlineStr">
+        <is>
+          <t>draft-zehavi-oauth-authority-metadata — OAuth 2.0 Authority Metadata</t>
+        </is>
+      </c>
+      <c r="C546" s="5" t="inlineStr">
+        <is>
+          <t>OAuth metadata advertises supported scopes and authorization details types, but advertised scope values and RAR type identifiers do not themselves describe the *authority* associated with them. This specification defines authority metadata extensions for OAuth 2.0 Protected Resource Metadata and OAuth 2.0 Authorization Server Metadata. A protected resource can describe the authority it associates with scopes and Rich Authorization Requests (RAR) types, reusable access requirement profiles, and relationships identifying lower-authority alternatives. An authorization server can publish a simpler description of its local authority vocabulary. This metadata can inform authentication and authorization decisions before token issuance and exchange, as well as support authority attenuation.</t>
+        </is>
+      </c>
+      <c r="D546" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-zehavi-oauth-authority-metadata/</t>
+        </is>
+      </c>
+      <c r="E546" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F546" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 11 Oct 2026. **Added 28 Oct 2026 sweep.** Raiffeisen Bank International. Advertised scope and RAR type identifiers do not describe the *authority* behind them; this adds authority metadata to Protected Resource and AS Metadata. Same author as `zehavi-oauth-rar-metadata`, the individual predecessor of the WG's `rar-metadata-remediation`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="5" t="n">
+        <v>546</v>
+      </c>
+      <c r="B547" s="5" t="inlineStr">
+        <is>
+          <t>draft-zhang-dawn-bgp-style-federated-discovery — Federated Agent Metadata Synchronization Protocol (FAMS-P)</t>
+        </is>
+      </c>
+      <c r="C547" s="5" t="inlineStr">
+        <is>
+          <t>This document specifies the Federated Agent Metadata Synchronization Protocol (FAMS-P), a normative protocol realization of the "BGP-like structured peering" federation mode (Mode B) defined in the two-layer DAWN discovery architecture (draft-zhang-dawn-agent-discovery- framework). FAMS-P is a peer-to-peer unicast protocol for synchronizing agent discovery metadata between Federation Gateways (FGWs) across administrative domains, in deployments where the preferred DNS delegation model does not meet operational requirements, such as closed trusted federations of approximately 2 to 200 sites. FAMS-P runs over mutually-authenticated TLS 1.3 sessions between peering gateways. It supports initial full metadata synchronization and incremental updates for agent online, offline, and change events. Each gateway maintains a local Federated Agent Directory (FAD). The protocol synchronizes only lightweight Federation Metadata Records (FMRs) — a concrete binding of the DAWN Minimum Discoverable Information (MDI) — and thus transfers only the minimum public discovery information permitted by the DAWN charter; richer capability retrieval is out of scope. The protocol defines complete message formats, a session state machine with connection collision resolution, timestamp-and-replay- protected conflict resolution, mandatory FMR origin signatures, time- to-live aging with bounded refresh jitter, and fine-grained per-peer export policy enforcement.</t>
+        </is>
+      </c>
+      <c r="D547" s="9" t="inlineStr">
+        <is>
+          <t>https://datatracker.ietf.org/doc/draft-zhang-dawn-bgp-style-federated-discovery/</t>
+        </is>
+      </c>
+      <c r="E547" s="5" t="inlineStr">
+        <is>
+          <t>IETF (individual)</t>
+        </is>
+      </c>
+      <c r="F547" s="5" t="inlineStr">
+        <is>
+          <t>Revision -00, 14 Oct 2026. **Added 28 Oct 2026 sweep.** Pengcheng Laboratory (Bin Zhang). FAMS-P, the normative protocol for the "BGP-like structured peering" federation mode of the tracked `zhang-dawn-agent-discovery-framework` — the framework's first mechanism document.</t>
         </is>
       </c>
     </row>
@@ -15426,6 +17856,87 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D464" r:id="rId463"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D465" r:id="rId464"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D466" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D467" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D468" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D469" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D470" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D471" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D472" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D473" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D474" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D475" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D476" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D477" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D478" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D479" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D480" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D481" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D482" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D483" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D484" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D485" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D486" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D487" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D488" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D489" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D490" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D491" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D492" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D493" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D494" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D495" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D496" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D497" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D498" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D499" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D500" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D501" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D502" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D503" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D504" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D505" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D506" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D507" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D508" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D509" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D510" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D511" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D512" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D513" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D514" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D515" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D516" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D517" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D518" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D519" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D520" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D521" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D522" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D523" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D524" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D525" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D526" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D527" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D528" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D529" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D530" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D531" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D532" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D533" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D534" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D535" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D536" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D537" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D538" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D539" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D540" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D541" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D542" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D543" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D544" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D545" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D546" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D547" r:id="rId546"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15437,7 +17948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -16596,17 +19107,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-mission-resource-access — Mission Resource Access Profile for OAuth 2.0</t>
+          <t>draft-mcguinness-oauth-mission-cross-org-delegation — Mission Cross-Organizational Delegation for OAuth 2.0</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Defines mission_resource_access, split from the OAuth binding: resource exact/prefix matching, the action namespace and wildcard families, Common Constraints, per-entry delegation policy, and the subset/intersection algebra, plus this type's scope-projection safety conditions and machine-readable transformation-capability declaration.</t>
+          <t>Profiles Mission Offline Attenuation across organizational trust domains: an agent in one organization delegates a narrowed slice to an agent in another, and the relying party verifies the complete narrowing chain without calling the origin on the request path.</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-resource-access.md</t>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-cross-org-delegation.md</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -16616,7 +19127,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Mission-Bound Authorization family — group: Bindings &amp; substrate; role: companion; spec maturity: experimental; maintenance: active. References 2 family draft(s) incl. oauth-mission, oauth-mission-cross-domain. GitHub-only (pre-publication) — not on Datatracker as of 4 Sep 2026. **Added 4 Sep 2026 sweep:** family-manifest.json grew from 34 to 46 drafts since 26 Aug, and the manifest schema changed — `maturity`/`adoption_rung` were replaced by `role`, `spec_maturity` and `maintenance`, so this row's narration uses the new vocabulary while the 33 earlier rows still carry the old one.</t>
+          <t>Mission-Bound Authorization family — group: Cross-domain projection; role: companion; spec maturity: experimental; maintenance: active-experimental. References 10 family draft(s) incl. mission-audit, mission-runtime, mission-runtime-evidence. GitHub-only (pre-publication) — not on Datatracker as of 4 Sep 2026. **Added 4 Sep 2026 sweep:** family-manifest.json grew from 34 to 46 drafts since 26 Aug, and the manifest schema changed — `maturity`/`adoption_rung` were replaced by `role`, `spec_maturity` and `maintenance`, so this row's narration uses the new vocabulary while the 33 earlier rows still carry the old one.</t>
         </is>
       </c>
     </row>
@@ -16626,17 +19137,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-mission-cross-org-delegation — Mission Cross-Organizational Delegation for OAuth 2.0</t>
+          <t>draft-mcguinness-oauth-mission-discharge — Mission Completion and Entry Discharge for OAuth 2.0</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Profiles Mission Offline Attenuation across organizational trust domains: an agent in one organization delegates a narrowed slice to an agent in another, and the relying party verifies the complete narrowing chain without calling the origin on the request path.</t>
+          <t>Registers `terminal_when`, an OPTIONAL Common Constraint naming one or more entry-grain completion conditions, and the authenticated `discharge` operation, registered as an extension on the Status profile's Mission Lifecycle endpoint, that commits a condition's firing and retires the entry's authority without ending the Mission.</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-cross-org-delegation.md</t>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-discharge.md</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -16646,7 +19157,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Mission-Bound Authorization family — group: Cross-domain projection; role: companion; spec maturity: experimental; maintenance: active-experimental. References 10 family draft(s) incl. mission-audit, mission-runtime, mission-runtime-evidence. GitHub-only (pre-publication) — not on Datatracker as of 4 Sep 2026. **Added 4 Sep 2026 sweep:** family-manifest.json grew from 34 to 46 drafts since 26 Aug, and the manifest schema changed — `maturity`/`adoption_rung` were replaced by `role`, `spec_maturity` and `maintenance`, so this row's narration uses the new vocabulary while the 33 earlier rows still carry the old one.</t>
+          <t>Mission-Bound Authorization family — group: Lifecycle; role: companion; spec maturity: experimental; maintenance: active. References 7 family draft(s) incl. mission-authzen, mission-runtime, oauth-mission. GitHub-only (pre-publication) — not on Datatracker as of 4 Sep 2026. **Added 4 Sep 2026 sweep:** family-manifest.json grew from 34 to 46 drafts since 26 Aug, and the manifest schema changed — `maturity`/`adoption_rung` were replaced by `role`, `spec_maturity` and `maintenance`, so this row's narration uses the new vocabulary while the 33 earlier rows still carry the old one.</t>
         </is>
       </c>
     </row>
@@ -16656,17 +19167,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-mission-discharge — Mission Completion and Entry Discharge for OAuth 2.0</t>
+          <t>draft-mcguinness-oauth-mission-status-list — Mission Status List for OAuth 2.0</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Registers `terminal_when`, an OPTIONAL Common Constraint naming one or more entry-grain completion conditions, and the authenticated `discharge` operation, registered as an extension on the Status profile's Mission Lifecycle endpoint, that commits a condition's firing and retires the entry's authority without ending the Mission.</t>
+          <t>Profiles a Mission Status List, a signed, compressed OAuth Status List bit array a consumer relying on many Missions at once fetches once per freshness window and reads locally per action, as a `status_list` extension member on the Status profile's response and introspection surfaces.</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-discharge.md</t>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-status-list.md</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -16676,7 +19187,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Mission-Bound Authorization family — group: Lifecycle; role: companion; spec maturity: experimental; maintenance: active. References 7 family draft(s) incl. mission-authzen, mission-runtime, oauth-mission. GitHub-only (pre-publication) — not on Datatracker as of 4 Sep 2026. **Added 4 Sep 2026 sweep:** family-manifest.json grew from 34 to 46 drafts since 26 Aug, and the manifest schema changed — `maturity`/`adoption_rung` were replaced by `role`, `spec_maturity` and `maintenance`, so this row's narration uses the new vocabulary while the 33 earlier rows still carry the old one.</t>
+          <t>Mission-Bound Authorization family — group: Lifecycle; role: companion; spec maturity: experimental; maintenance: active. References 3 family draft(s) incl. mission-runtime, oauth-mission, oauth-mission-status. GitHub-only (pre-publication) — not on Datatracker as of 4 Sep 2026. **Added 4 Sep 2026 sweep:** family-manifest.json grew from 34 to 46 drafts since 26 Aug, and the manifest schema changed — `maturity`/`adoption_rung` were replaced by `role`, `spec_maturity` and `maintenance`, so this row's narration uses the new vocabulary while the 33 earlier rows still carry the old one.</t>
         </is>
       </c>
     </row>
@@ -16686,17 +19197,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-mission-status-list — Mission Status List for OAuth 2.0</t>
+          <t>draft-mcguinness-mission-evidence-envelope — Mission Evidence Envelope</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Profiles a Mission Status List, a signed, compressed OAuth Status List bit array a consumer relying on many Missions at once fetches once per freshness window and reads locally per action, as a `status_list` extension member on the Status profile's response and introspection surfaces.</t>
+          <t>A generic, binding-neutral evidence envelope and payload-type registry a future evidence kind MAY register into instead of minting a one-off object and media type, seeded with Intent Admission Evidence as its first payload type; migrates none of the family's existing evidence kinds.</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-status-list.md</t>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-mission-evidence-envelope.md</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -16706,7 +19217,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Mission-Bound Authorization family — group: Lifecycle; role: companion; spec maturity: experimental; maintenance: active. References 3 family draft(s) incl. mission-runtime, oauth-mission, oauth-mission-status. GitHub-only (pre-publication) — not on Datatracker as of 4 Sep 2026. **Added 4 Sep 2026 sweep:** family-manifest.json grew from 34 to 46 drafts since 26 Aug, and the manifest schema changed — `maturity`/`adoption_rung` were replaced by `role`, `spec_maturity` and `maintenance`, so this row's narration uses the new vocabulary while the 33 earlier rows still carry the old one.</t>
+          <t>Mission-Bound Authorization family — group: Proof portability; role: companion; spec maturity: sketch; maintenance: lab-best-effort. References 6 family draft(s) incl. mission-audit, mission-mandate, mission-runtime-evidence. GitHub-only (pre-publication) — not on Datatracker as of 4 Sep 2026. **Added 4 Sep 2026 sweep:** family-manifest.json grew from 34 to 46 drafts since 26 Aug, and the manifest schema changed — `maturity`/`adoption_rung` were replaced by `role`, `spec_maturity` and `maintenance`, so this row's narration uses the new vocabulary while the 33 earlier rows still carry the old one.</t>
         </is>
       </c>
     </row>
@@ -16716,17 +19227,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-mission-evidence-envelope — Mission Evidence Envelope</t>
+          <t>draft-mcguinness-mission-runtime-evidence — Mission Runtime Evidence</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>A generic, binding-neutral evidence envelope and payload-type registry a future evidence kind MAY register into instead of minting a one-off object and media type, seeded with Intent Admission Evidence as its first payload type; migrates none of the family's existing evidence kinds.</t>
+          <t>The binding-neutral Decision Evidence, Execution Evidence, and Refusal Record objects a decision-API binding's PDP and PEP emit: their members, canonicalization, integrity envelope, media types, and retention.</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-mission-evidence-envelope.md</t>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-mission-runtime-evidence.md</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -16736,7 +19247,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Mission-Bound Authorization family — group: Proof portability; role: companion; spec maturity: sketch; maintenance: lab-best-effort. References 6 family draft(s) incl. mission-audit, mission-mandate, mission-runtime-evidence. GitHub-only (pre-publication) — not on Datatracker as of 4 Sep 2026. **Added 4 Sep 2026 sweep:** family-manifest.json grew from 34 to 46 drafts since 26 Aug, and the manifest schema changed — `maturity`/`adoption_rung` were replaced by `role`, `spec_maturity` and `maintenance`, so this row's narration uses the new vocabulary while the 33 earlier rows still carry the old one.</t>
+          <t>Mission-Bound Authorization family — group: Runtime enforcement; role: companion; spec maturity: experimental; maintenance: active. References 12 family draft(s) incl. mission-audit, mission-authority-server, mission-authzen. GitHub-only (pre-publication) — not on Datatracker as of 4 Sep 2026. **Added 4 Sep 2026 sweep:** family-manifest.json grew from 34 to 46 drafts since 26 Aug, and the manifest schema changed — `maturity`/`adoption_rung` were replaced by `role`, `spec_maturity` and `maintenance`, so this row's narration uses the new vocabulary while the 33 earlier rows still carry the old one.</t>
         </is>
       </c>
     </row>
@@ -16746,17 +19257,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-mission-runtime-evidence — Mission Runtime Evidence</t>
+          <t>draft-mcguinness-mission-runtime-oauth — Mission Runtime OAuth Adapter</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>The binding-neutral Decision Evidence, Execution Evidence, and Refusal Record objects a decision-API binding's PDP and PEP emit: their members, canonicalization, integrity envelope, media types, and retention.</t>
+          <t>The OAuth 2.0 realization of the runtime core's binding-neutral contract: token presentation and validation, the `mission`/`act`/`cnf`/`aud` claim mapping, the `authorization_details` and `mission_resource_access` authority-entry mapping, and Resource-Owner Class Floors through OAuth protected resource metadata.</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-mission-runtime-evidence.md</t>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-mission-runtime-oauth.md</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -16766,7 +19277,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Mission-Bound Authorization family — group: Runtime enforcement; role: companion; spec maturity: experimental; maintenance: active. References 12 family draft(s) incl. mission-audit, mission-authority-server, mission-authzen. GitHub-only (pre-publication) — not on Datatracker as of 4 Sep 2026. **Added 4 Sep 2026 sweep:** family-manifest.json grew from 34 to 46 drafts since 26 Aug, and the manifest schema changed — `maturity`/`adoption_rung` were replaced by `role`, `spec_maturity` and `maintenance`, so this row's narration uses the new vocabulary while the 33 earlier rows still carry the old one.</t>
+          <t>Mission-Bound Authorization family — group: Runtime enforcement; role: companion; spec maturity: experimental; maintenance: active. References 10 family draft(s) incl. mission-authzen, mission-runtime, mission-substrate. GitHub-only (pre-publication) — not on Datatracker as of 4 Sep 2026. **Added 4 Sep 2026 sweep:** family-manifest.json grew from 34 to 46 drafts since 26 Aug, and the manifest schema changed — `maturity`/`adoption_rung` were replaced by `role`, `spec_maturity` and `maintenance`, so this row's narration uses the new vocabulary while the 33 earlier rows still carry the old one.</t>
         </is>
       </c>
     </row>
@@ -16776,17 +19287,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-mission-runtime-oauth — Mission Runtime OAuth Adapter</t>
+          <t>draft-mcguinness-oauth-mission-transaction-authorization — Mission Transaction Authorization Profile for OAuth 2.0</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>The OAuth 2.0 realization of the runtime core's binding-neutral contract: token presentation and validation, the `mission`/`act`/`cnf`/`aud` claim mapping, the `authorization_details` and `mission_resource_access` authority-entry mapping, and Resource-Owner Class Floors through OAuth protected resource metadata.</t>
+          <t>Profiles the OAuth transaction authorization challenge for the Mission cross-domain case: a Transaction Authorization Server runs a fresh decision with a governed approval as input and issues a sender-constrained, single-use transaction token the resource verifies offline.</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-mission-runtime-oauth.md</t>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-transaction-authorization.md</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -16796,7 +19307,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Mission-Bound Authorization family — group: Runtime enforcement; role: companion; spec maturity: experimental; maintenance: active. References 10 family draft(s) incl. mission-authzen, mission-runtime, mission-substrate. GitHub-only (pre-publication) — not on Datatracker as of 4 Sep 2026. **Added 4 Sep 2026 sweep:** family-manifest.json grew from 34 to 46 drafts since 26 Aug, and the manifest schema changed — `maturity`/`adoption_rung` were replaced by `role`, `spec_maturity` and `maintenance`, so this row's narration uses the new vocabulary while the 33 earlier rows still carry the old one.</t>
+          <t>Mission-Bound Authorization family — group: Runtime enforcement; role: companion; spec maturity: experimental; maintenance: active-experimental. References 18 family draft(s) incl. mission-aauth, mission-approval-governance, mission-audit. GitHub-only (pre-publication) — not on Datatracker as of 4 Sep 2026. **Added 4 Sep 2026 sweep:** family-manifest.json grew from 34 to 46 drafts since 26 Aug, and the manifest schema changed — `maturity`/`adoption_rung` were replaced by `role`, `spec_maturity` and `maintenance`, so this row's narration uses the new vocabulary while the 33 earlier rows still carry the old one.</t>
         </is>
       </c>
     </row>
@@ -16806,17 +19317,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-oauth-mission-transaction-authorization — Mission Transaction Authorization Profile for OAuth 2.0</t>
+          <t>draft-mcguinness-mission-control-plane — Mission Control-Plane Consistency</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Profiles the OAuth transaction authorization challenge for the Mission cross-domain case: a Transaction Authorization Server runs a fresh decision with a governed approval as input and issues a sender-constrained, single-use transaction token the resource verifies offline.</t>
+          <t>Topology-neutral issuer serialization, authoritative observation, rollback resistance, durable fan-out, and emergency-authority separation. Pull it in when a deployment claims testable control-plane consistency across replication, partition, and recovery.</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-transaction-authorization.md</t>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-mission-control-plane.md</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -16826,7 +19337,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Mission-Bound Authorization family — group: Runtime enforcement; role: companion; spec maturity: experimental; maintenance: active-experimental. References 18 family draft(s) incl. mission-aauth, mission-approval-governance, mission-audit. GitHub-only (pre-publication) — not on Datatracker as of 4 Sep 2026. **Added 4 Sep 2026 sweep:** family-manifest.json grew from 34 to 46 drafts since 26 Aug, and the manifest schema changed — `maturity`/`adoption_rung` were replaced by `role`, `spec_maturity` and `maintenance`, so this row's narration uses the new vocabulary while the 33 earlier rows still carry the old one.</t>
+          <t>Mission-Bound Authorization family — group: Lifecycle; role: companion; spec maturity: experimental; maintenance: lab-best-effort. References 4 family draft(s): mission-runtime, oauth-mission, oauth-mission-signals, oauth-mission-status. GitHub-only (pre-publication) — not on Datatracker as of 29 Sep 2026. **Added 29 Sep 2026 sweep:** the sole upstream addition since 4 Sep, taking family-manifest.json from 46 to 47 drafts. Clean growth — all 46 previously-tracked slugs are still present under the same names, and the manifest schema is unchanged since the 4 Sep rewrite. Note the `lab-best-effort` maintenance class, the weakest in the manifest's vocabulary: the author is flagging this one as less supported than the rest of the family.</t>
         </is>
       </c>
     </row>
@@ -16836,17 +19347,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>draft-mcguinness-mission-control-plane — Mission Control-Plane Consistency</t>
+          <t>draft-mcguinness-oauth-mission-derivation-limits — Mission Derivation Limits for OAuth 2.0</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Topology-neutral issuer serialization, authoritative observation, rollback resistance, durable fan-out, and emergency-authority separation. Pull it in when a deployment claims testable control-plane consistency across replication, partition, and recovery.</t>
+          <t>Bounds how many derivations the issuer performs under a Mission: an optional requested ceiling, an AS-established effective limit, atomic counting across code exchange, refresh, and Token Exchange (the refreshes of an async delegation family are not counted), refusal at the cap, and remaining-count disclosure through introspection.</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-mission-control-plane.md</t>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-derivation-limits.md</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -16856,7 +19367,127 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Mission-Bound Authorization family — group: Lifecycle; role: companion; spec maturity: experimental; maintenance: lab-best-effort. References 4 family draft(s): mission-runtime, oauth-mission, oauth-mission-signals, oauth-mission-status. GitHub-only (pre-publication) — not on Datatracker as of 29 Sep 2026. **Added 29 Sep 2026 sweep:** the sole upstream addition since 4 Sep, taking family-manifest.json from 46 to 47 drafts. Clean growth — all 46 previously-tracked slugs are still present under the same names, and the manifest schema is unchanged since the 4 Sep rewrite. Note the `lab-best-effort` maintenance class, the weakest in the manifest's vocabulary: the author is flagging this one as less supported than the rest of the family.</t>
+          <t>Mission-Bound Authorization family — group: Lifecycle; role: companion; spec maturity: experimental; maintenance: active. References 10 family draft(s) incl. mission-metering, oauth-mission, oauth-mission-child-delegation. GitHub-only (pre-publication) — not on Datatracker as of 28 Oct 2026. **Added 28 Oct 2026 sweep:** family-manifest.json grew from 47 to 52 drafts since 29 Sep, with no renames and no schema change; in the same window `oauth-mission-resource-access` was filed on Datatracker and moved to the Active IETF Drafts tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-oauth-mission-submission-evidence — Mission Intent Submission Evidence for OAuth 2.0</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Defines how typed evidence presented with a Mission Intent is processed: the entry convention, required evidence resolved before derivation, binding to one exact Intent, agreement with the authenticated presenter, bounded verification cost, and where refusals are returned.</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-submission-evidence.md</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Approval-time; role: companion; spec maturity: experimental; maintenance: active. References 5 family draft(s) incl. mission-shaping, oauth-mission, oauth-mission-approval-revision. GitHub-only (pre-publication) — not on Datatracker as of 28 Oct 2026. **Added 28 Oct 2026 sweep:** family-manifest.json grew from 47 to 52 drafts since 29 Sep, with no renames and no schema change; in the same window `oauth-mission-resource-access` was filed on Datatracker and moved to the Active IETF Drafts tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-oauth-mission-request-provenance — Mission Request Provenance for OAuth 2.0</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Defines an optional Intent Submission Evidence type: a trusted request intake's signed assertion of who originated the instruction behind a Mission Intent, through which authenticated channel, and when, bound to one AS, one exact Intent, and one presenter, carrying only a secret-keyed digest of the instruction.</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-request-provenance.md</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Approval-time; role: companion; spec maturity: experimental; maintenance: active. References 4 family draft(s) incl. mission-evidence-envelope, mission-shaping, oauth-mission. GitHub-only (pre-publication) — not on Datatracker as of 28 Oct 2026. **Added 28 Oct 2026 sweep:** family-manifest.json grew from 47 to 52 drafts since 29 Sep, with no renames and no schema change; in the same window `oauth-mission-resource-access` was filed on Datatracker and moved to the Active IETF Drafts tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-oauth-mission-approved-set-verification — Mission Approved-Set Verification for OAuth 2.0</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Lets a verifying Resource Server or policy decision point check a token's carried authority against the complete committed Authority Set: authenticated complete-set retrieval, recomputation of authority_hash, a subset check, optional independent pinning, and fail-closed handling.</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-approved-set-verification.md</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Proof portability; role: companion; spec maturity: experimental; maintenance: active. References 4 family draft(s) incl. mission-substrate, oauth-mission, oauth-mission-containment. GitHub-only (pre-publication) — not on Datatracker as of 28 Oct 2026. **Added 28 Oct 2026 sweep:** family-manifest.json grew from 47 to 52 drafts since 29 Sep, with no renames and no schema change; in the same window `oauth-mission-resource-access` was filed on Datatracker and moved to the Active IETF Drafts tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>draft-mcguinness-oauth-mission-device-authorization — Mission Device Authorization for OAuth 2.0</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Carries a Mission Intent and authority proposal on the OAuth 2.0 Device Authorization Grant for a client with no redirect: explicit discovery with no fallback to an ordinary device grant, whole-request validation, a session bound to the exact proposal and client, a direct approval on a second device with user-code confirmation, one-time issuance with the required Mission response members, and the device grant as the root of the Mission's grant lineage.</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>https://github.com/mcguinness/mission-bound-authorization/blob/main/draft-mcguinness-oauth-mission-device-authorization.md</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>IETF (Pre-publication — GitHub)</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Mission-Bound Authorization family — group: Approval-time; role: companion; spec maturity: experimental; maintenance: lab-best-effort. References 4 family draft(s) incl. oauth-mission, oauth-mission-approval, oauth-mission-consent-evidence. GitHub-only (pre-publication) — not on Datatracker as of 28 Oct 2026. **Added 28 Oct 2026 sweep:** family-manifest.json grew from 47 to 52 drafts since 29 Sep, with no renames and no schema change; in the same window `oauth-mission-resource-access` was filed on Datatracker and moved to the Active IETF Drafts tab. Note the `lab-best-effort` maintenance class — the second family member so marked, after `mission-control-plane`.</t>
         </is>
       </c>
     </row>
@@ -16908,6 +19539,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18017,7 +20652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F150"/>
+  <dimension ref="A1:F163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -18276,27 +20911,27 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>AI Agents and the Multi-Hop Delegation Problem (WorkOS)</t>
+          <t>wimse-agent-mandate-vectors — Test Vectors for draft-hulea-wimse-agent-mandate (Silentpartnercoding)</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>A WorkOS engineering blog post that catalogs the open IETF drafts and RFCs addressing multi-hop AI-agent delegation including identity chaining, attenuating tokens, and actor chains.</t>
+          <t>Signed test vectors and an independent checker for draft-hulea-wimse-agent-mandate-00: the draft's Appendix A presentation as a valid baseline, plus three negative cases on the Authority Assertion (root mandate broader than the asserted powers; Authority Assertion referenced but not presented; Authority Assertion expired), each with its expected Validation Result. Uses the test keys and Validation Profile the draft author published for Appendix B, checked byte for byte; generate.py regenerates every case and tests confirm byte-identical output.</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>https://workos.com/blog/oauth-multi-hop-delegation-ai-agents</t>
+          <t>https://github.com/Silentpartnercoding/wimse-agent-mandate-vectors</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Industry blog (WorkOS)</t>
+          <t>Open-source (Apache-2.0)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Particularly useful index of currently-active drafts (April 2026) on the agent-delegation problem with NIST and EU AI Act compliance context.</t>
+          <t>Created 27 Oct 2026 — **three days after `hulea-wimse-agent-mandate-00` was filed** — and raised by the maintainer. Third-party vectors against a -00 draft are unusual; they exercise exactly the draft's distinctive element (evidence of the delegator's authority), and every negative case resolves to `authority_insufficient` or `authority_missing`. A fourth case is waiting on -01. Discussed on the WIMSE list. Pair with the draft row in Active IETF Drafts.</t>
         </is>
       </c>
     </row>
@@ -18306,27 +20941,27 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Mission-Bound Authorization on the Wire (McGuinness, 22 May 2026, re-issued 22 Jul 2026)</t>
+          <t>Tenuo — Task-Scoped Authorization for AI Agents (reference implementation of Attenuating Authorization Tokens)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>The protocol-level proposal. Five wire additions on top of existing OAuth: a 'mission_intent' RAR envelope (purpose, mission_expiry, context), a generic 'resource_access' RAR type, a durable Mission record at the Authorization Server, an opaque 'mission' claim (id + origin) on access tokens, and a Mission-state enforcement gate on refresh / exchange / introspection / assertion validation. Seven-state Mission lifecycle (pending_approval, active, suspended, revoked, expired, completed, rejected). proposal_hash (SHA-256 over JCS-canonical authorization_details) and consent_rendering_hash anchor what was approved versus what the user saw.</t>
+          <t>Gives each task only the authority it needs: a warrant is a signed grant of which tools an agent may call, under what constraints and for how long; it travels with the work, can only shrink when handed off, and is checked where the action runs, producing signed evidence of what was allowed or denied. Ships Rust, Python and Docker packages; status v0.2 Production/Stable, with an open-beta managed control plane.</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>https://notes.karlmcguinness.com/notes/mission-bound-authorization-on-the-wire/</t>
+          <t>https://github.com/tenuo-ai/tenuo</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Architect blog (Karl McGuinness)</t>
+          <t>Open-source (Apache-2.0, Tenuo)</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>**RE-SLUGGED — the original /notes/mission-bound-oauth-mvp URL now 404s** (caught in the 26 Aug 2026 sweep). Re-issued 22 Jul 2026 as a chapter of the Mission-Bound Authorization handbook under the new title and slug; content verified equivalent (mission_intent, proposal_hash, resource_access all still present). Part of a site-wide rename of "Mission-Bound OAuth" to "Mission-Bound Authorization". 76-min read; the substrate post for the whole series. Target I-D name: draft-mcguinness-oauth-mission-bound-minimum-profile. Conformance Ladder L0–L5 (L0 baseline OAuth → L5 verifiable governance with portable receipts). Cross-AS handoff uses ID-JAG for user-rooted flows or the Fletcher Transaction Token Chaining Profile for Txn-Token-rooted flows. Mission Expansion creates a successor Mission with 'mission.supersedes' rather than mutating in place. Three Resource Server tiers (RS-A OAuth-only → RS-D Mission-state aware via introspection or SSF/CAEP events). Architectural challenges acknowledged honestly: state-sync at scale, unknown-constraint brittleness, lethal-trifecta boundary.</t>
+          <t>The implementation behind `niyikiza-oauth-attenuating-agent-tokens` (author Niki Aimable Niyikiza, tenuo.ai). With -02 on 27 Oct 2026 the repo published **229 public chain-verification vectors** (`ietf/vectors/INTEROP.md`), and the draft now reports twelve citing I-Ds and three further independent implementations. 103 GitHub stars — the most-adopted agent-delegation implementation in this tab by that measure. Cited on both the OAuth and WIMSE lists.</t>
         </is>
       </c>
     </row>
@@ -18336,27 +20971,27 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>The Mission Is the Missing Abstraction (McGuinness, 1 Jun 2026, re-issued 22 Jul 2026)</t>
+          <t>agent-delegation-vectors — Golden Interop Vectors for Cross-Organizational Agent Delegation (agentcreds)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>The architectural frame: OAuth has no first-class object for 'the task the user approved' — only tokens, scopes, prompts, and logs that are downstream projections of it. The Mission is that durable, AS-stored, user-approved authority record. Argues this is what closes the gap that five prior bodies of his work (Power of Attorney, Mission Shaping, Open-World OAuth, Sessions Are Not Missions, the Mission-Bound architecture series) have circled from different angles. Two layers, one object: issuance-bound authority (MVP) plus runtime-enforced authority (the IBAC profile).</t>
+          <t>Golden test artifacts for cross-organizational agent delegation: signed credentials, attenuated delegation tokens, proof-of-possession presentations and revocation status lists, each paired with the check a relying party must perform and the answer it must reach. A Python runner plus an eight-method adapter interface lets other implementations be checked against the same cases.</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>https://notes.karlmcguinness.com/notes/the-mission-is-the-missing-abstraction/</t>
+          <t>https://github.com/agentcreds/agent-delegation-vectors</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Architect blog (Karl McGuinness)</t>
+          <t>Open-source (Apache-2.0)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>**RE-SLUGGED — the original URL now 404s** (caught 26 Aug 2026); the word "OAuth" was dropped from both title and slug in the 22 Jul 2026 handbook re-issue. Short (9-min) framing post that ties the whole programme together. The argument for why IBAC becomes practical when intent is compiled from an AS-validated Mission at consent time rather than inferred post-hoc from agent behaviour (where it's adversarial-input territory and the PDP has no user to ask). Best entry point for someone new to the series.</t>
+          <t>Created Jul 2026; cited on the WIMSE list. **Honest caveat, stated by the repo itself:** these are *agreement* vectors derived from one implementation's behaviour, not *conformance* vectors derived from a specification — passing shows you agree with the reference implementation, not that you implemented a draft. Kept because the cross-org delegation case set is the closest thing to an interop corpus for the chain drafts.</t>
         </is>
       </c>
     </row>
@@ -18366,27 +21001,27 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Mission-Bound Runtime Enforcement (McGuinness, 1 Jun 2026, re-issued 22 Jul 2026)</t>
+          <t>agent-evidence-vectors — Conformance Corpora and Reference Verifiers for Agent Evidence Formats (Probity)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>The IBAC layer layered on the MVP. Core (required for compliance): Intent-to-Policy Compilation (AS deterministically compiles approved authorization_details to an evaluable artifact at activation, stores policy_version on the Mission), Resource-Side Enforcement Contract (RS-B minimum, PDP evaluates every consequential request), Standard Subset Semantics per RAR Type with strict-refuse on unknown constraints (stricter than MVP's 'preserve or refuse'), Mission Introspection Profile (extended response with act chain, tenant, subject, policy_version), Runtime Denial and Escalation via ARAP (MUST), Local-Action Boundary requiring AuthZEN Access Evaluation for non-OAuth actions, Parameter Binding / TOCTOU Protection (parameter_digest bound to the permit), Decision Evidence Records (per-decision audit record bound to mission.id, proposal_hash, policy_version, decision, constraint clauses, act chain). Six Optional Modules: Tool Binding Profile, Decision Receipt Profile (W3C VC 2.0), Actor Provenance Profile, Purpose Registry Profile, Attestation Profile (RATS PTV + WIMSE), Policy Projection Profile (Cedar carriage).</t>
+          <t>Saved agent-evidence records with known outcomes — valid records, altered bytes, missing evidence and open specification interpretations — for testing an agent-evidence verifier, with Python and Go reference verifiers. At v0.26.0 the default corpus holds 288 vectors; distributed on PyPI.</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>https://notes.karlmcguinness.com/notes/mission-bound-runtime-enforcement/</t>
+          <t>https://github.com/probityai/agent-evidence-vectors</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Architect blog (Karl McGuinness)</t>
+          <t>Open-source (Apache-2.0, Probity)</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>**RE-SLUGGED — the original URL now 404s** (caught 26 Aug 2026); re-issued 22 Jul 2026 as a handbook chapter, dropping both "OAuth" and "Profile" from the name. 37-min read; target I-D name: draft-mcguinness-oauth-mission-bound-runtime-enforcement-profile. Six-class action classification (non-consequential → consequential read → consequential write → irreversible → external commitment → privileged administration) determines PDP-gate requirement and parameter binding. Four PDP deployment modes (AS-hosted, RS-hosted, tenant governance, federated). Goal pair: 'execution continuity' (every in-bounds action succeeds; every out-of-bounds becomes governed Mission Expansion) plus 'proof of authority' (per-decision cryptographic receipts). Acknowledges PDP latency overhead and tool-manifest fracturing as real challenges.</t>
+          <t>Created Jul 2026; the most-cited repository on the WIMSE list this window (9 messages). The verifier-side counterpart to the receipt and audit-record drafts: it tests what a verifier concludes, including the "not established" outcome for missing evidence that `sergeev-claim-boundaries` and the Watts non-collapse drafts argue for.</t>
         </is>
       </c>
     </row>
@@ -18396,27 +21031,27 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Authorization Denied Is No Longer Enough (McGuinness, 2 Jun 2026)</t>
+          <t>AI Agents and the Multi-Hop Delegation Problem (WorkOS)</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>The framing post for ARAP. In closed-world authorization, 'decision:false' was the end of the interaction. In open-world agentic systems with runtime discovery, sub-agent delegation, and evolving missions, denial is increasingly the beginning of a governance escalation — and the missing protocol primitive is a 'requestable denial': a deny that names where to ask and binds the request to the exact evaluation it remediates. Why CIBA isn't the answer (CIBA solves authentication freshness; this is about governance state). Why approvals aren't authority (reevaluation against current state, not standing entitlement).</t>
+          <t>A WorkOS engineering blog post that catalogs the open IETF drafts and RFCs addressing multi-hop AI-agent delegation including identity chaining, attenuating tokens, and actor chains.</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>https://notes.karlmcguinness.com/notes/authorization-denied-is-no-longer-enough/</t>
+          <t>https://workos.com/blog/oauth-multi-hop-delegation-ai-agents</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Architect blog (Karl McGuinness)</t>
+          <t>Industry blog (WorkOS)</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Confirms that the AuthZEN ARAP profile was adopted as a working group draft in May 2026 — material maturity signal. Useful as the 'why' read alongside the ARAP spec itself. Also positions the work against AARM (Autonomous Action Runtime Management, aarm.dev/spec) which intercepts every agent action and resolves to allow/deny/modify/step-up/defer — ARAP standardizes the deny+escalate boundary at the AuthZEN layer.</t>
+          <t>Particularly useful index of currently-active drafts (April 2026) on the agent-delegation problem with NIST and EU AI Act compliance context.</t>
         </is>
       </c>
     </row>
@@ -18426,17 +21061,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Re-Subjecting Is a Mint, Not an Attenuation (McGuinness, 8 Jun 2026)</t>
+          <t>Mission-Bound Authorization on the Wire (McGuinness, 22 May 2026, re-issued 22 Jul 2026)</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Argues that crossing subject namespaces — mapping a user's identity from one application's identifier to another's — is a minting operation, not attenuation. Attenuation can narrow authority already represented by an existing artifact; it cannot authoritatively create a target-local identity binding the original issuer never supplied. Only a trusted IdP or broker can perform that translation. Distinguishes two topologies: caller-pushed (intermediate app returns to the IdP for a new assertion) and resource-pulled (destination resolves user identity through a broker). Separates workload identity (which service is calling) from user context (which person delegated the work) as requiring distinct claims.</t>
+          <t>The protocol-level proposal. Five wire additions on top of existing OAuth: a 'mission_intent' RAR envelope (purpose, mission_expiry, context), a generic 'resource_access' RAR type, a durable Mission record at the Authorization Server, an opaque 'mission' claim (id + origin) on access tokens, and a Mission-state enforcement gate on refresh / exchange / introspection / assertion validation. Seven-state Mission lifecycle (pending_approval, active, suspended, revoked, expired, completed, rejected). proposal_hash (SHA-256 over JCS-canonical authorization_details) and consent_rendering_hash anchor what was approved versus what the user saw.</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>https://notes.karlmcguinness.com/notes/re-subjecting-is-a-mint-not-an-attenuation/</t>
+          <t>https://notes.karlmcguinness.com/notes/mission-bound-authorization-on-the-wire/</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -18446,7 +21081,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Published 8 Jun 2026; a standalone conceptual post outside the four-part Mission-Bound series but thematically continuous with it. Directly relevant to cross-AS delegation flows in the MVP post (ID-JAG for user-rooted re-subjecting) and to the token-exchange-target-service-discovery I-D. Privacy note: every intermediary-visible artifact should minimize identifiers that enable unauthorized cross-context linking.</t>
+          <t>**RE-SLUGGED — the original /notes/mission-bound-oauth-mvp URL now 404s** (caught in the 26 Aug 2026 sweep). Re-issued 22 Jul 2026 as a chapter of the Mission-Bound Authorization handbook under the new title and slug; content verified equivalent (mission_intent, proposal_hash, resource_access all still present). Part of a site-wide rename of "Mission-Bound OAuth" to "Mission-Bound Authorization". 76-min read; the substrate post for the whole series. Target I-D name: draft-mcguinness-oauth-mission-bound-minimum-profile. Conformance Ladder L0–L5 (L0 baseline OAuth → L5 verifiable governance with portable receipts). Cross-AS handoff uses ID-JAG for user-rooted flows or the Fletcher Transaction Token Chaining Profile for Txn-Token-rooted flows. Mission Expansion creates a successor Mission with 'mission.supersedes' rather than mutating in place. Three Resource Server tiers (RS-A OAuth-only → RS-D Mission-state aware via introspection or SSF/CAEP events). Architectural challenges acknowledged honestly: state-sync at scale, unknown-constraint brittleness, lethal-trifecta boundary.</t>
         </is>
       </c>
     </row>
@@ -18456,17 +21091,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Mission Architecture on AAuth (McGuinness, 15 Mar 2026)</t>
+          <t>The Mission Is the Missing Abstraction (McGuinness, 1 Jun 2026, re-issued 22 Jul 2026)</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Engages directly with Dick Hardt's AAuth protocol, examining whether AAuth's conversational flow and native agent identity could host Mission governance better than OAuth; concludes both architectures require an explicit, durable Mission object for lifecycle governance, approval evidence, and actor continuity — AAuth's strengths are transport-level, not governance-level.</t>
+          <t>The architectural frame: OAuth has no first-class object for 'the task the user approved' — only tokens, scopes, prompts, and logs that are downstream projections of it. The Mission is that durable, AS-stored, user-approved authority record. Argues this is what closes the gap that five prior bodies of his work (Power of Attorney, Mission Shaping, Open-World OAuth, Sessions Are Not Missions, the Mission-Bound architecture series) have circled from different angles. Two layers, one object: issuance-bound authority (MVP) plus runtime-enforced authority (the IBAC profile).</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>https://notes.karlmcguinness.com/notes/mission-architecture-on-aauth/</t>
+          <t>https://notes.karlmcguinness.com/notes/the-mission-is-the-missing-abstraction/</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -18476,7 +21111,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Published Mar 15 2026; the fifth McGuinness blog entry in the corpus (the four-part Mission-Bound series above plus this standalone analysis). Significant because it directly engages draft-hardt-oauth-aauth-protocol (the corpus OUTLIER — zero OAuth dependencies), bridging the two most architecturally influential individual contributors in the corpus. McGuinness argues Mission governance requires a durable object regardless of transport; Hardt argues PoP-by-default and AS-to-AS federation require architectural replacement. These positions are complementary at different layers.</t>
+          <t>**RE-SLUGGED — the original URL now 404s** (caught 26 Aug 2026); the word "OAuth" was dropped from both title and slug in the 22 Jul 2026 handbook re-issue. Short (9-min) framing post that ties the whole programme together. The argument for why IBAC becomes practical when intent is compiled from an AS-validated Mission at consent time rather than inferred post-hoc from agent behaviour (where it's adversarial-input territory and the PDP has no user to ask). Best entry point for someone new to the series.</t>
         </is>
       </c>
     </row>
@@ -18486,27 +21121,27 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Enterprise-Managed Authorization for MCP (Paul Carleton, Anthropic MCP Blog, 18 Jun 2026)</t>
+          <t>Mission-Bound Runtime Enforcement (McGuinness, 1 Jun 2026, re-issued 22 Jul 2026)</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Announces Enterprise-Managed Authorization (EMA) extension enabling SSO-based MCP server provisioning through enterprise identity providers, eliminating per-app OAuth friction; explicitly uses the Identity Assertion JWT Authorization Grant (ID-JAG) as the underlying token exchange mechanism. Early adopters include Okta, Claude, VS Code, Asana, Atlassian, Figma, and Supabase.</t>
+          <t>The IBAC layer layered on the MVP. Core (required for compliance): Intent-to-Policy Compilation (AS deterministically compiles approved authorization_details to an evaluable artifact at activation, stores policy_version on the Mission), Resource-Side Enforcement Contract (RS-B minimum, PDP evaluates every consequential request), Standard Subset Semantics per RAR Type with strict-refuse on unknown constraints (stricter than MVP's 'preserve or refuse'), Mission Introspection Profile (extended response with act chain, tenant, subject, policy_version), Runtime Denial and Escalation via ARAP (MUST), Local-Action Boundary requiring AuthZEN Access Evaluation for non-OAuth actions, Parameter Binding / TOCTOU Protection (parameter_digest bound to the permit), Decision Evidence Records (per-decision audit record bound to mission.id, proposal_hash, policy_version, decision, constraint clauses, act chain). Six Optional Modules: Tool Binding Profile, Decision Receipt Profile (W3C VC 2.0), Actor Provenance Profile, Purpose Registry Profile, Attestation Profile (RATS PTV + WIMSE), Policy Projection Profile (Cedar carriage).</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>https://blog.modelcontextprotocol.io/posts/enterprise-managed-auth/</t>
+          <t>https://notes.karlmcguinness.com/notes/mission-bound-runtime-enforcement/</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Vendor blog (Anthropic / MCP)</t>
+          <t>Architect blog (Karl McGuinness)</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Published Jun 18 2026; author: Paul Carleton (MCP Core Maintainer). One of the first production deployments of draft-ietf-oauth-identity-assertion-authz-grant (ID-JAG, corpus WG draft) at enterprise scale. Multi-vendor adoption (8 platforms at launch) signals ID-JAG is de-facto production-ready even before RFC publication. Cross-App Access from Okta is the identity provider backbone.</t>
+          <t>**RE-SLUGGED — the original URL now 404s** (caught 26 Aug 2026); re-issued 22 Jul 2026 as a handbook chapter, dropping both "OAuth" and "Profile" from the name. 37-min read; target I-D name: draft-mcguinness-oauth-mission-bound-runtime-enforcement-profile. Six-class action classification (non-consequential → consequential read → consequential write → irreversible → external commitment → privileged administration) determines PDP-gate requirement and parameter binding. Four PDP deployment modes (AS-hosted, RS-hosted, tenant governance, federated). Goal pair: 'execution continuity' (every in-bounds action succeeds; every out-of-bounds becomes governed Mission Expansion) plus 'proof of authority' (per-decision cryptographic receipts). Acknowledges PDP latency overhead and tool-manifest fracturing as real challenges.</t>
         </is>
       </c>
     </row>
@@ -18516,27 +21151,27 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Workload Identity: Key Takeaways from IETF 122 (Kasselman, Defakto Security, 26 Mar 2025)</t>
+          <t>Authorization Denied Is No Longer Enough (McGuinness, 2 Jun 2026)</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Reports on WIMSE WG's adoption of three working-group drafts at IETF 122: WIMSE Architecture, Service-to-Service Authentication, and Workload Identity Practices; addresses AI agent identity requirements — credentialing every AI workload, least-privilege scope, and permission escalation mechanisms — within the WIMSE framework.</t>
+          <t>The framing post for ARAP. In closed-world authorization, 'decision:false' was the end of the interaction. In open-world agentic systems with runtime discovery, sub-agent delegation, and evolving missions, denial is increasingly the beginning of a governance escalation — and the missing protocol primitive is a 'requestable denial': a deny that names where to ask and binds the request to the exact evaluation it remediates. Why CIBA isn't the answer (CIBA solves authentication freshness; this is about governance state). Why approvals aren't authority (reevaluation against current state, not standing entitlement).</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>https://www.defakto.security/blog/workload-identity-key-takeaways-from-ietf-122/</t>
+          <t>https://notes.karlmcguinness.com/notes/authorization-denied-is-no-longer-enough/</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Practitioner blog (Defakto Security)</t>
+          <t>Architect blog (Karl McGuinness)</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Published Mar 26 2025; author: Pieter Kasselman (VP Open Standards, Defakto Security) — co-author of draft-klrc-aiagent-auth, draft-fletcher-transaction-token-chaining-profile, and draft-ietf-oauth-first-party-apps (all in corpus). Documents the WIMSE WG milestone that provides the workload-identity substrate for the AI agent extension family; useful primary-source account of the IETF milestone from the author who subsequently filed klrc-aiagent-auth.</t>
+          <t>Confirms that the AuthZEN ARAP profile was adopted as a working group draft in May 2026 — material maturity signal. Useful as the 'why' read alongside the ARAP spec itself. Also positions the work against AARM (Autonomous Action Runtime Management, aarm.dev/spec) which intercepts every agent action and resolves to allow/deny/modify/step-up/defer — ARAP standardizes the deny+escalate boundary at the AuthZEN layer.</t>
         </is>
       </c>
     </row>
@@ -18546,27 +21181,27 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Whither User-Managed Access in the AI Agent Era? (Eve Maler, Venn Factory, 10 Jul 2025)</t>
+          <t>Re-Subjecting Is a Mint, Not an Attenuation (McGuinness, 8 Jun 2026)</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Examines whether UMA 2.0 remains relevant for AI agent delegation, distinguishing whether agents function as OAuth client apps or as requesting parties with their own legal standing; argues UMA 'basically exists for this' but identifies gaps: dynamic resource discovery, multi-level delegation tracking, and the need for standardized infrastructure analogous to Microsoft's On-Behalf-Of flow.</t>
+          <t>Argues that crossing subject namespaces — mapping a user's identity from one application's identifier to another's — is a minting operation, not attenuation. Attenuation can narrow authority already represented by an existing artifact; it cannot authoritatively create a target-local identity binding the original issuer never supplied. Only a trusted IdP or broker can perform that translation. Distinguishes two topologies: caller-pushed (intermediate app returns to the IdP for a new assertion) and resource-pulled (destination resolves user identity through a broker). Separates workload identity (which service is calling) from user context (which person delegated the work) as requiring distinct claims.</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>https://workshop.vennfactory.com/p/whither-user-managed-access-in-the</t>
+          <t>https://notes.karlmcguinness.com/notes/re-subjecting-is-a-mint-not-an-attenuation/</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Practitioner blog (Venn Factory)</t>
+          <t>Architect blog (Karl McGuinness)</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Published Jul 10 2025; author: Eve Maler (primary author of UMA 2.0, former VP Innovation at ForgeRock, W3C TAG). The UMA specification is in the Other Standards &amp; Govt tab; this is the spec author's own analysis of its applicability to AI agents. Identifies the same gaps (dynamic resource discovery, multi-level delegation) that the DAWN and identity-chaining IETF work addresses — useful bridge between the Kantara UMA entry and the active IETF corpus.</t>
+          <t>Published 8 Jun 2026; a standalone conceptual post outside the four-part Mission-Bound series but thematically continuous with it. Directly relevant to cross-AS delegation flows in the MVP post (ID-JAG for user-rooted re-subjecting) and to the token-exchange-target-service-discovery I-D. Privacy note: every intermediary-visible artifact should minimize identifiers that enable unauthorized cross-context linking.</t>
         </is>
       </c>
     </row>
@@ -18576,27 +21211,27 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Tangled Tokens and Authorized Agents (Justin Richer, 15 May 2025)</t>
+          <t>Mission Architecture on AAuth (McGuinness, 15 Mar 2026)</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Examines how MCP's proxy model creates two distinct authorization contexts (agent-to-MCP-server and server-to-upstream-resource) that OAuth's pre-registration assumptions don't accommodate cleanly; argues for credential-mapping strategies adapted from email IMAP patterns and identifies unresolved tensions around static OAuth registration and MCP server allowlisting.</t>
+          <t>Engages directly with Dick Hardt's AAuth protocol, examining whether AAuth's conversational flow and native agent identity could host Mission governance better than OAuth; concludes both architectures require an explicit, durable Mission object for lifecycle governance, approval evidence, and actor continuity — AAuth's strengths are transport-level, not governance-level.</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>https://justinsecurity.medium.com/tangled-tokens-and-authorized-agents-331e4db02fb4</t>
+          <t>https://notes.karlmcguinness.com/notes/mission-architecture-on-aauth/</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Practitioner blog (Justin Richer)</t>
+          <t>Architect blog (Karl McGuinness)</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Published May 15 2025; author: Justin Richer (independent OAuth expert, co-author of OAuth 2.0 in Action, former GNAP WG co-chair). The IMAP credential-mapping analogy is the most concrete prior-art framing for the MCP authorization problem. Complements the Dan Moore Stack Overflow Blog post (below) which covers the MCP OAuth 2.1 spec detail; this post covers the architectural gap the spec doesn't resolve.</t>
+          <t>Published Mar 15 2026; the fifth McGuinness blog entry in the corpus (the four-part Mission-Bound series above plus this standalone analysis). Significant because it directly engages draft-hardt-oauth-aauth-protocol (the corpus OUTLIER — zero OAuth dependencies), bridging the two most architecturally influential individual contributors in the corpus. McGuinness argues Mission governance requires a durable object regardless of transport; Hardt argues PoP-by-default and AS-to-AS federation require architectural replacement. These positions are complementary at different layers.</t>
         </is>
       </c>
     </row>
@@ -18606,27 +21241,27 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Is That Allowed? Authentication and Authorization in Model Context Protocol (Dan Moore, Stack Overflow Blog, 21 Jan 2026)</t>
+          <t>Enterprise-Managed Authorization for MCP (Paul Carleton, Anthropic MCP Blog, 18 Jun 2026)</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Technical walkthrough of MCP's OAuth 2.1 implementation: Authorization Code grant with mandatory PKCE, RFC 9728 protected resource metadata for server discovery, and the RFC 8707 resource parameter; explicitly names the gap that MCP spec does not mandate how servers authenticate with backend services.</t>
+          <t>Announces Enterprise-Managed Authorization (EMA) extension enabling SSO-based MCP server provisioning through enterprise identity providers, eliminating per-app OAuth friction; explicitly uses the Identity Assertion JWT Authorization Grant (ID-JAG) as the underlying token exchange mechanism. Early adopters include Okta, Claude, VS Code, Asana, Atlassian, Figma, and Supabase.</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>https://stackoverflow.blog/2026/01/21/is-that-allowed-authentication-and-authorization-in-model-context-protocol/</t>
+          <t>https://blog.modelcontextprotocol.io/posts/enterprise-managed-auth/</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Practitioner blog (Stack Overflow Blog)</t>
+          <t>Vendor blog (Anthropic / MCP)</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Published Jan 21 2026; author: Dan Moore (Head of Developer Relations, FusionAuth). Directly references RFC 8414 (OAuth Server Metadata), RFC 8707 (Resource Indicators), RFC 9728 (Protected Resource Metadata) — all IETF corpus entries. Stack Overflow Blog platform gives this mainstream engineering reach. The gap identified (server-to-backend auth unspecified by MCP) is the same gap that draft-ietf-oauth-identity-assertion-authz-grant and klrc-aiagent-auth address.</t>
+          <t>Published Jun 18 2026; author: Paul Carleton (MCP Core Maintainer). One of the first production deployments of draft-ietf-oauth-identity-assertion-authz-grant (ID-JAG, corpus WG draft) at enterprise scale. Multi-vendor adoption (8 platforms at launch) signals ID-JAG is de-facto production-ready even before RFC publication. Cross-App Access from Okta is the identity provider backbone.</t>
         </is>
       </c>
     </row>
@@ -18636,27 +21271,27 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>AI Agent Authentication Gets the Hard Part Right. Authorization Is Still Your Problem. (Rock Lambros, RockCyber Musings, 17 Mar 2026)</t>
+          <t>Workload Identity: Key Takeaways from IETF 122 (Kasselman, Defakto Security, 26 Mar 2025)</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Analyzes draft-klrc-aiagent-auth-00 in depth, praising its identity layer (WIMSE + SPIFFE composition) but flagging that the Security Considerations section contains only 'TODO Security'; recommends layering OPA or Cedar policy engines for actual authorization and names AuthZEN as a candidate gap-filler.</t>
+          <t>Reports on WIMSE WG's adoption of three working-group drafts at IETF 122: WIMSE Architecture, Service-to-Service Authentication, and Workload Identity Practices; addresses AI agent identity requirements — credentialing every AI workload, least-privilege scope, and permission escalation mechanisms — within the WIMSE framework.</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>https://www.rockcybermusings.com/p/i-agent-authentication-authorization-gap</t>
+          <t>https://www.defakto.security/blog/workload-identity-key-takeaways-from-ietf-122/</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Practitioner blog (RockCyber Musings)</t>
+          <t>Practitioner blog (Defakto Security)</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Published Mar 17 2026; author: Rock Lambros. One of the few practitioner posts that analyzes a specific IETF draft (draft-klrc-aiagent-auth, corpus) in depth and names the authorization gap that authentication alone doesn't close. The 'TODO Security' observation was accurate as of the -00 filing; draft-klrc-aiagent-auth has since reached -03 (6 Jul 2026) — re-check whether Security Considerations were filled in.</t>
+          <t>Published Mar 26 2025; author: Pieter Kasselman (VP Open Standards, Defakto Security) — co-author of draft-klrc-aiagent-auth, draft-fletcher-transaction-token-chaining-profile, and draft-ietf-oauth-first-party-apps (all in corpus). Documents the WIMSE WG milestone that provides the workload-identity substrate for the AI agent extension family; useful primary-source account of the IETF milestone from the author who subsequently filed klrc-aiagent-auth.</t>
         </is>
       </c>
     </row>
@@ -18666,27 +21301,27 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Least Privilege for AI Agents: Identity, Access, and Tool Binding (Microsoft Security Blog, 16 Jul 2026)</t>
+          <t>Whither User-Managed Access in the AI Agent Era? (Eve Maler, Venn Factory, 10 Jul 2025)</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Microsoft's blueprint for applying least-privilege to agentic workloads: unique dedicated agent principals with named owners and explicit purpose statements, task-based roles scoped to specific resources, controlled tool access allowlists, and end-to-end auditability requirements; positions agent identity as a first-class security principal requiring the same governance as human identities.</t>
+          <t>Examines whether UMA 2.0 remains relevant for AI agent delegation, distinguishing whether agents function as OAuth client apps or as requesting parties with their own legal standing; argues UMA 'basically exists for this' but identifies gaps: dynamic resource discovery, multi-level delegation tracking, and the need for standardized infrastructure analogous to Microsoft's On-Behalf-Of flow.</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/en-us/security/blog/2026/07/16/least-privilege-for-ai-agents-identity-access-and-tool-binding/</t>
+          <t>https://workshop.vennfactory.com/p/whither-user-managed-access-in-the</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Vendor blog (Microsoft Security)</t>
+          <t>Practitioner blog (Venn Factory)</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Published Jul 16 2026. Microsoft's most recent major position on least-privilege for agents; extends the earlier Azure and Microsoft Entra entries in the corpus with specific tool-binding guidance. The named-owner and explicit-purpose-statement requirements align directly with Mission-Bound OAuth's proposal_hash and consent_rendering_hash binding. First Microsoft Security Blog entry to use 'tool binding' as a security term of art.</t>
+          <t>Published Jul 10 2025; author: Eve Maler (primary author of UMA 2.0, former VP Innovation at ForgeRock, W3C TAG). The UMA specification is in the Other Standards &amp; Govt tab; this is the spec author's own analysis of its applicability to AI agents. Identifies the same gaps (dynamic resource discovery, multi-level delegation) that the DAWN and identity-chaining IETF work addresses — useful bridge between the Kantara UMA entry and the active IETF corpus.</t>
         </is>
       </c>
     </row>
@@ -18696,27 +21331,27 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Solving the Identity Crisis for AI Agents (Uber Engineering)</t>
+          <t>Tangled Tokens and Authorized Agents (Justin Richer, 15 May 2025)</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>A production engineering post from Uber describing their agent identity architecture: an Agent Registry (workload-to-agent mapping), a SPIRE-backed STS that issues short-lived JWTs with embedded actor chains at P99 below 40ms, an MCP Gateway as policy enforcement point, and an AI Agent Mesh for agent-to-agent communication. A standardized A2A client automates token exchange and chain propagation across agent hops.</t>
+          <t>Examines how MCP's proxy model creates two distinct authorization contexts (agent-to-MCP-server and server-to-upstream-resource) that OAuth's pre-registration assumptions don't accommodate cleanly; argues for credential-mapping strategies adapted from email IMAP patterns and identifies unresolved tensions around static OAuth registration and MCP server allowlisting.</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>https://www.uber.com/us/en/blog/solving-the-agent-identity-crisis/</t>
+          <t>https://justinsecurity.medium.com/tangled-tokens-and-authorized-agents-331e4db02fb4</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Industry blog (Uber Engineering)</t>
+          <t>Practitioner blog (Justin Richer)</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Published 21 May 2026; six-author post (Mathew, Borole, Huang, Burykin, Goel, Walsh) from Uber's platform engineering team. Architecture aligns with WIMSE workload identity (SPIRE as the credential foundation), RFC 8693 actor-chain propagation, and single-hop short-lived JWTs with audience-scoped claims. One of the few public disclosures of a production-grade agent identity system at hyperscaler scale — a real-world reference point for the corpus's delegation-chain design patterns.</t>
+          <t>Published May 15 2025; author: Justin Richer (independent OAuth expert, co-author of OAuth 2.0 in Action, former GNAP WG co-chair). The IMAP credential-mapping analogy is the most concrete prior-art framing for the MCP authorization problem. Complements the Dan Moore Stack Overflow Blog post (below) which covers the MCP OAuth 2.1 spec detail; this post covers the architectural gap the spec doesn't resolve.</t>
         </is>
       </c>
     </row>
@@ -18726,27 +21361,27 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Agents Are Not Just Workloads (Patrick Parker, LinkedIn)</t>
+          <t>Is That Allowed? Authentication and Authorization in Model Context Protocol (Dan Moore, Stack Overflow Blog, 21 Jan 2026)</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Argues that classifying AI agents as 'workloads' is a category error that corrupts identity architecture: workloads are a what-runs-where concept, agents are a who-acts-on-whose-authority concept. Identifies five breakdown areas where workload-identity patterns fail for agents: intent captured as static token claims, delegation gaps (no purpose binding or revocation paths), overlooked tool-catalog authorization surface, bearer-credential custody ambiguity under prompt injection, and mutable logs insufficient as tamper-evident authorization evidence.</t>
+          <t>Technical walkthrough of MCP's OAuth 2.1 implementation: Authorization Code grant with mandatory PKCE, RFC 9728 protected resource metadata for server discovery, and the RFC 8707 resource parameter; explicitly names the gap that MCP spec does not mandate how servers authenticate with backend services.</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/pulse/agents-just-workloads-patrick-parker-0qxte/</t>
+          <t>https://stackoverflow.blog/2026/01/21/is-that-allowed-authentication-and-authorization-in-model-context-protocol/</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Industry blog (LinkedIn)</t>
+          <t>Practitioner blog (Stack Overflow Blog)</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Published 9 Jun 2026. Proposes signature-based receipts binding relationships, authority, tasks, and bounds; runtime validation of generated task intent; and AuthZEN gateway-based enforcement. A principled counterpoint to the WIMSE-as-sufficient-for-agents framing — pairs well with the Uber Engineering post (which uses SPIRE/WIMSE as the credential foundation but adds actor chains and MCP gateway enforcement on top).</t>
+          <t>Published Jan 21 2026; author: Dan Moore (Head of Developer Relations, FusionAuth). Directly references RFC 8414 (OAuth Server Metadata), RFC 8707 (Resource Indicators), RFC 9728 (Protected Resource Metadata) — all IETF corpus entries. Stack Overflow Blog platform gives this mainstream engineering reach. The gap identified (server-to-backend auth unspecified by MCP) is the same gap that draft-ietf-oauth-identity-assertion-authz-grant and klrc-aiagent-auth address.</t>
         </is>
       </c>
     </row>
@@ -18756,27 +21391,27 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Creating a Relationship Binding (Tom Jones)</t>
+          <t>AI Agent Authentication Gets the Hard Part Right. Authorization Is Still Your Problem. (Rock Lambros, RockCyber Musings, 17 Mar 2026)</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>A community whitepaper proposing a signed 'Consent to Create Binding' JWT/JWS message that establishes a subject-bound relationship identifier (UUID or DID) between a user and a set of agents or service providers. The message carries 16 mandatory/optional fields: issuer, subject, subject role, context (trust framework), permissions, device statement, identity proof, purpose of use, key material, and signature. Includes a lifecycle termination model (session, cookie, transaction, relationship, and legal-based retention scopes) and a companion 'Consent Receipt with Binding' response. A second section argues that relationship-based governance — binding actors through mutual obligations, escalation paths, and accountability chains — is more resilient for AI agent systems than representational approaches (policies, classifications, static maps).</t>
+          <t>Analyzes draft-klrc-aiagent-auth-00 in depth, praising its identity layer (WIMSE + SPIFFE composition) but flagging that the Security Considerations section contains only 'TODO Security'; recommends layering OPA or Cedar policy engines for actual authorization and names AuthZEN as a candidate gap-filler.</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>https://docs.google.com/document/d/1CwBDRbw147YlNld-UOlJ4lGvmpDIOCSI/edit#heading=h.kp911j18z01y</t>
+          <t>https://www.rockcybermusings.com/p/i-agent-authentication-authorization-gap</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Community whitepaper</t>
+          <t>Practitioner blog (RockCyber Musings)</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>No publication date in the document; primary use case is healthcare (NIST IAL2/AAL2). Draws on Kantara's Distribute Assurance Specification for identity assurance levels and references OpenID Connect id_token as the closest existing message shape. The Consent to Create Binding message adds purpose of use, device statement, and lifecycle termination semantics that id_token lacks. Companion doc 'Digital Contracts Made Legally Valid' (separate Google Doc) covers giving the binding legal status. Relationship-governance argument is thematically aligned with Parker's 'Agents Are Not Just Workloads' — both argue that accountability chains and mutual obligations are the right governance primitive for agentic systems.</t>
+          <t>Published Mar 17 2026; author: Rock Lambros. One of the few practitioner posts that analyzes a specific IETF draft (draft-klrc-aiagent-auth, corpus) in depth and names the authorization gap that authentication alone doesn't close. The 'TODO Security' observation was accurate as of the -00 filing; draft-klrc-aiagent-auth has since reached -03 (6 Jul 2026) — re-check whether Security Considerations were filled in.</t>
         </is>
       </c>
     </row>
@@ -18786,27 +21421,27 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Intent Agent Native Authorization for Agentic Profiles (IANA-AP) (Martin Besozzi, Jul 2026)</t>
+          <t>Least Privilege for AI Agents: Identity, Access, and Tool Binding (Microsoft Security Blog, 16 Jul 2026)</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Proposes a four-phase runtime authorization lifecycle for AI agents: discovery (agent capabilities + API authorization mappings), intent computation (agent generates planned operations), review/approval (user provides explicit phishing-resistant consent via WebAuthn/FIDO2 passkeys before execution), and enforcement (every runtime invocation validated against the approved authorization artifact). Composes RFC 9396 RAR, OAuth FiPA, OpenID AuthZEN, MCP, SPIFFE JWT-SVIDs, and CEL policy mappings into a single coherent framework.</t>
+          <t>Microsoft's blueprint for applying least-privilege to agentic workloads: unique dedicated agent principals with named owners and explicit purpose statements, task-based roles scoped to specific resources, controlled tool access allowlists, and end-to-end auditability requirements; positions agent identity as a first-class security principal requiring the same governance as human identities.</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>https://embesozzi.github.io/posts/martin-besozzi/intent-agent-native-authorization-agentic-profiles/</t>
+          <t>https://www.microsoft.com/en-us/security/blog/2026/07/16/least-privilege-for-ai-agents-identity-access-and-tool-binding/</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Architect blog (Martin Besozzi)</t>
+          <t>Vendor blog (Microsoft Security)</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Updated July 2026; includes open specification and reference implementation on GitHub. The SARC (Subject, Action, Resource, Context) model and 'x-authz-mapping' Agentic Profile extension are novel additions. The four-phase pre-execution approval requirement directly parallels draft-nelson-agent-delegation-receipts and draft-sato-soos-idp — but grounds it in existing OAuth standards rather than new protocol primitives. One of the few practitioner-level posts that explicitly composes AuthZEN, RAR, and FiPA into a working agent authorization flow.</t>
+          <t>Published Jul 16 2026. Microsoft's most recent major position on least-privilege for agents; extends the earlier Azure and Microsoft Entra entries in the corpus with specific tool-binding guidance. The named-owner and explicit-purpose-statement requirements align directly with Mission-Bound OAuth's proposal_hash and consent_rendering_hash binding. First Microsoft Security Blog entry to use 'tool binding' as a security term of art.</t>
         </is>
       </c>
     </row>
@@ -18816,27 +21451,27 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Agent Authentication &amp; Delegated Access (Zylos Research, April 2026)</t>
+          <t>Solving the Identity Crisis for AI Agents (Uber Engineering)</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>A research-style industry article surveying OAuth flows, scoped tokens, and identity patterns specifically for AI agents, covering OAuth 2.1 baselines and chain-splicing risks.</t>
+          <t>A production engineering post from Uber describing their agent identity architecture: an Agent Registry (workload-to-agent mapping), a SPIRE-backed STS that issues short-lived JWTs with embedded actor chains at P99 below 40ms, an MCP Gateway as policy enforcement point, and an AI Agent Mesh for agent-to-agent communication. A standardized A2A client automates token exchange and chain propagation across agent hops.</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>https://zylos.ai/research/2026-04-11-agent-authentication-delegated-access-oauth-scoped-tokens</t>
+          <t>https://www.uber.com/us/en/blog/solving-the-agent-identity-crisis/</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Industry research blog</t>
+          <t>Industry blog (Uber Engineering)</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Documents the 'delegation chain splicing' attack against RFC 8693 actor-token chains formally raised on the OAuth WG list in early 2026.</t>
+          <t>Published 21 May 2026; six-author post (Mathew, Borole, Huang, Burykin, Goel, Walsh) from Uber's platform engineering team. Architecture aligns with WIMSE workload identity (SPIRE as the credential foundation), RFC 8693 actor-chain propagation, and single-hop short-lived JWTs with audience-scoped claims. One of the few public disclosures of a production-grade agent identity system at hyperscaler scale — a real-world reference point for the corpus's delegation-chain design patterns.</t>
         </is>
       </c>
     </row>
@@ -18846,27 +21481,27 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>AuthZEN + Shared Signals Framework Series (Andrew Doering)</t>
+          <t>Agents Are Not Just Workloads (Patrick Parker, LinkedIn)</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>A multi-part technical blog walking through how AuthZEN (synchronous PDP/PEP) and SSF/CAEP (asynchronous events) combine into a continuous-authorization loop in real Microsoft Entra/M365 deployments.</t>
+          <t>Argues that classifying AI agents as 'workloads' is a category error that corrupts identity architecture: workloads are a what-runs-where concept, agents are a who-acts-on-whose-authority concept. Identifies five breakdown areas where workload-identity patterns fail for agents: intent captured as static token claims, delegation gaps (no purpose binding or revocation paths), overlooked tool-catalog authorization surface, bearer-credential custody ambiguity under prompt injection, and mutable logs insufficient as tamper-evident authorization evidence.</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>https://andrewdoering.org/blog/2026/authzen-shared-signals-framework-part-1-fundamentals/</t>
+          <t>https://www.linkedin.com/pulse/agents-just-workloads-patrick-parker-0qxte/</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Industry blog</t>
+          <t>Industry blog (LinkedIn)</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Documents the 2026 asymmetry where Microsoft Entra is a CAEP transmitter for closed-loop CAE but not an external SSF receiver.</t>
+          <t>Published 9 Jun 2026. Proposes signature-based receipts binding relationships, authority, tasks, and bounds; runtime validation of generated task intent; and AuthZEN gateway-based enforcement. A principled counterpoint to the WIMSE-as-sufficient-for-agents framing — pairs well with the Uber Engineering post (which uses SPIRE/WIMSE as the credential foundation but adds actor chains and MCP gateway enforcement on top).</t>
         </is>
       </c>
     </row>
@@ -18876,27 +21511,27 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Just-in-Time Authorization with OpenID SSE and CAEP (The New Stack, Tulshibagwale)</t>
+          <t>Creating a Relationship Binding (Tom Jones)</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>An article from CAEP's original inventor explaining how SSE+CAEP enable just-in-time authorization decisions instead of long-lived session-based access.</t>
+          <t>A community whitepaper proposing a signed 'Consent to Create Binding' JWT/JWS message that establishes a subject-bound relationship identifier (UUID or DID) between a user and a set of agents or service providers. The message carries 16 mandatory/optional fields: issuer, subject, subject role, context (trust framework), permissions, device statement, identity proof, purpose of use, key material, and signature. Includes a lifecycle termination model (session, cookie, transaction, relationship, and legal-based retention scopes) and a companion 'Consent Receipt with Binding' response. A second section argues that relationship-based governance — binding actors through mutual obligations, escalation paths, and accountability chains — is more resilient for AI agent systems than representational approaches (policies, classifications, static maps).</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>https://thenewstack.io/just-in-time-authorization-with-openid-sse-and-caep/</t>
+          <t>https://docs.google.com/document/d/1CwBDRbw147YlNld-UOlJ4lGvmpDIOCSI/edit#heading=h.kp911j18z01y</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Industry article (The New Stack)</t>
+          <t>Community whitepaper</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Background piece by Atul Tulshibagwale (SGNL CTO, CAEP inventor) explaining the architectural intent.</t>
+          <t>No publication date in the document; primary use case is healthcare (NIST IAL2/AAL2). Draws on Kantara's Distribute Assurance Specification for identity assurance levels and references OpenID Connect id_token as the closest existing message shape. The Consent to Create Binding message adds purpose of use, device statement, and lifecycle termination semantics that id_token lacks. Companion doc 'Digital Contracts Made Legally Valid' (separate Google Doc) covers giving the binding legal status. Relationship-governance argument is thematically aligned with Parker's 'Agents Are Not Just Workloads' — both argue that accountability chains and mutual obligations are the right governance primitive for agentic systems.</t>
         </is>
       </c>
     </row>
@@ -18906,27 +21541,27 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>How AuthZEN, Shared Signals &amp; CAEP Complement Each Other (OpenID Foundation)</t>
+          <t>Intent Agent Native Authorization for Agentic Profiles (IANA-AP) (Martin Besozzi, Jul 2026)</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>An OpenID Foundation explainer arguing that AuthZEN and SSF/CAEP are complementary — sync access decisions vs async session updates — not competing standards.</t>
+          <t>Proposes a four-phase runtime authorization lifecycle for AI agents: discovery (agent capabilities + API authorization mappings), intent computation (agent generates planned operations), review/approval (user provides explicit phishing-resistant consent via WebAuthn/FIDO2 passkeys before execution), and enforcement (every runtime invocation validated against the approved authorization artifact). Composes RFC 9396 RAR, OAuth FiPA, OpenID AuthZEN, MCP, SPIFFE JWT-SVIDs, and CEL policy mappings into a single coherent framework.</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>https://openid.net/how-authzen-and-shared-signals-caep-complement-each-other/</t>
+          <t>https://embesozzi.github.io/posts/martin-besozzi/intent-agent-native-authorization-agentic-profiles/</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>OpenID Foundation</t>
+          <t>Architect blog (Martin Besozzi)</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Useful when explaining the layering to stakeholders confused by the OpenID alphabet soup.</t>
+          <t>Updated July 2026; includes open specification and reference implementation on GitHub. The SARC (Subject, Action, Resource, Context) model and 'x-authz-mapping' Agentic Profile extension are novel additions. The four-phase pre-execution approval requirement directly parallels draft-nelson-agent-delegation-receipts and draft-sato-soos-idp — but grounds it in existing OAuth standards rather than new protocol primitives. One of the few practitioner-level posts that explicitly composes AuthZEN, RAR, and FiPA into a working agent authorization flow.</t>
         </is>
       </c>
     </row>
@@ -18936,27 +21571,27 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>OAuth 2.1 Features You Can't Ignore in 2026 (Gutierrez, Medium)</t>
+          <t>Agent Authentication &amp; Delegated Access (Zylos Research, April 2026)</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>A practitioner article summarizing why OAuth 2.1 — mandated PKCE, exact redirect matching, sender-constrained tokens — is the 2026 minimum bar for delegated authorization.</t>
+          <t>A research-style industry article surveying OAuth flows, scoped tokens, and identity patterns specifically for AI agents, covering OAuth 2.1 baselines and chain-splicing risks.</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>https://rgutierrez2004.medium.com/oauth-2-1-features-you-cant-ignore-in-2026-a15f852cb723</t>
+          <t>https://zylos.ai/research/2026-04-11-agent-authentication-delegated-access-oauth-scoped-tokens</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Industry blog (Medium)</t>
+          <t>Industry research blog</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Author is Cyber Intelligence Lead — IAM/AI at Oracle; concise piece suitable for executive briefings.</t>
+          <t>Documents the 'delegation chain splicing' attack against RFC 8693 actor-token chains formally raised on the OAuth WG list in early 2026.</t>
         </is>
       </c>
     </row>
@@ -18966,27 +21601,27 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>RFC 9396: OAuth 2.0 Rich Authorization Requests (CIAM Weekly)</t>
+          <t>AuthZEN + Shared Signals Framework Series (Andrew Doering)</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>A practitioner deep-dive on RAR explaining why scopes alone don't carry transaction-level intent and how authorization_details is being adopted in payments and verifiable credentials.</t>
+          <t>A multi-part technical blog walking through how AuthZEN (synchronous PDP/PEP) and SSF/CAEP (asynchronous events) combine into a continuous-authorization loop in real Microsoft Entra/M365 deployments.</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>https://ciamweekly.substack.com/p/rfc-9396-oauth-20-rich-authorization</t>
+          <t>https://andrewdoering.org/blog/2026/authzen-shared-signals-framework-part-1-fundamentals/</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Industry newsletter</t>
+          <t>Industry blog</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Captures the current (March 2026) state of RAR adoption, including CAMARA telco APIs and DPV-purpose binding proposals.</t>
+          <t>Documents the 2026 asymmetry where Microsoft Entra is a CAEP transmitter for closed-loop CAE but not an external SSF receiver.</t>
         </is>
       </c>
     </row>
@@ -18996,27 +21631,27 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Technical Deconstruction of MCP Authorization (kane.mx, Nov 2025)</t>
+          <t>Just-in-Time Authorization with OpenID SSE and CAEP (The New Stack, Tulshibagwale)</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>A long-form technical article showing that the Model Context Protocol's authorization spec is, in practice, an OAuth 2.1 profile combined with RFC 9728 protected-resource metadata and RFC 7591 dynamic registration.</t>
+          <t>An article from CAEP's original inventor explaining how SSE+CAEP enable just-in-time authorization decisions instead of long-lived session-based access.</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>https://kane.mx/posts/2025/mcp-authorization-oauth-rfc-deep-dive/</t>
+          <t>https://thenewstack.io/just-in-time-authorization-with-openid-sse-and-caep/</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Independent technical blog</t>
+          <t>Industry article (The New Stack)</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Calls out RFC 8707 (Resource Indicators) as the critical compatibility bottleneck since most major IdPs use proprietary audience parameters.</t>
+          <t>Background piece by Atul Tulshibagwale (SGNL CTO, CAEP inventor) explaining the architectural intent.</t>
         </is>
       </c>
     </row>
@@ -19026,27 +21661,27 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>AI Agents Authentication: How Autonomous Systems Prove Identity (GitGuardian)</t>
+          <t>How AuthZEN, Shared Signals &amp; CAEP Complement Each Other (OpenID Foundation)</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>A GitGuardian engineering article arguing that delegated, short-lived OAuth grants are structurally safer than the static API keys that produced 28.65M secret leaks in 2025.</t>
+          <t>An OpenID Foundation explainer arguing that AuthZEN and SSF/CAEP are complementary — sync access decisions vs async session updates — not competing standards.</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>https://blog.gitguardian.com/ai-agents-authentication-how-autonomous-systems-prove-identity/</t>
+          <t>https://openid.net/how-authzen-and-shared-signals-caep-complement-each-other/</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Industry blog (GitGuardian)</t>
+          <t>OpenID Foundation</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Useful for the 'why delegated authorization &gt; shared secrets' business case with concrete 2025 incident data.</t>
+          <t>Useful when explaining the layering to stakeholders confused by the OpenID alphabet soup.</t>
         </is>
       </c>
     </row>
@@ -19056,27 +21691,27 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>User-Managed Access (UMA) 2.0 Comprehensive Guide (SSOJet, Feb 2026)</t>
+          <t>OAuth 2.1 Features You Can't Ignore in 2026 (Gutierrez, Medium)</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>A 2026 industry guide reframing UMA 2.0 for current CIAM contexts, covering resource-set registration, permission tickets, requesting-party tokens (RPTs), and policy externalization gains.</t>
+          <t>A practitioner article summarizing why OAuth 2.1 — mandated PKCE, exact redirect matching, sender-constrained tokens — is the 2026 minimum bar for delegated authorization.</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>https://ssojet.com/blog/user-managed-access-uma-2-0-comprehensive-guide</t>
+          <t>https://rgutierrez2004.medium.com/oauth-2-1-features-you-cant-ignore-in-2026-a15f852cb723</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Industry blog (SSOJet)</t>
+          <t>Industry blog (Medium)</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Cites Kantara analysis showing centralized-policy moves can cut authorization code 80% — useful pitch material.</t>
+          <t>Author is Cyber Intelligence Lead — IAM/AI at Oracle; concise piece suitable for executive briefings.</t>
         </is>
       </c>
     </row>
@@ -19086,27 +21721,27 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Decentralized Identity and Verifiable Credentials: The Enterprise Playbook 2026</t>
+          <t>RFC 9396: OAuth 2.0 Rich Authorization Requests (CIAM Weekly)</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>An enterprise-oriented guide explaining how W3C VCs, DIDs, and OpenID4VC enable the issuer-holder-verifier delegation model for digital credentials and EUDI Wallet acceptance.</t>
+          <t>A practitioner deep-dive on RAR explaining why scopes alone don't carry transaction-level intent and how authorization_details is being adopted in payments and verifiable credentials.</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>https://securityboulevard.com/2026/03/decentralized-identity-and-verifiable-credentials-the-enterprise-playbook-2026/</t>
+          <t>https://ciamweekly.substack.com/p/rfc-9396-oauth-20-rich-authorization</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Industry article (Security Boulevard)</t>
+          <t>Industry newsletter</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Critical 2027 EU compliance dates: banks, telecom, healthcare, and very-large platforms must accept EUDI Wallet.</t>
+          <t>Captures the current (March 2026) state of RAR adoption, including CAMARA telco APIs and DPV-purpose binding proposals.</t>
         </is>
       </c>
     </row>
@@ -19116,27 +21751,27 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>OAuth 2.0 &amp; OpenID Connect: The Complete Guide to What the Standards Actually Say (Patil, Medium)</t>
+          <t>Technical Deconstruction of MCP Authorization (kane.mx, Nov 2025)</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>A practitioner-friendly synthesis covering OAuth 2.0 core, the OAuth 2.1 draft, RFC 9068 JWT access tokens, RFC 8252 native apps, and RFC 8628 device authorization.</t>
+          <t>A long-form technical article showing that the Model Context Protocol's authorization spec is, in practice, an OAuth 2.1 profile combined with RFC 9728 protected-resource metadata and RFC 7591 dynamic registration.</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>https://mrutyunjaypatil.medium.com/oauth-2-0-openid-connect-the-complete-guide-to-what-the-standards-actually-say-e92f040a4251</t>
+          <t>https://kane.mx/posts/2025/mcp-authorization-oauth-rfc-deep-dive/</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Industry blog (Medium)</t>
+          <t>Independent technical blog</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Good handoff document for engineers new to the area; cites the current standards rather than legacy patterns.</t>
+          <t>Calls out RFC 8707 (Resource Indicators) as the critical compatibility bottleneck since most major IdPs use proprietary audience parameters.</t>
         </is>
       </c>
     </row>
@@ -19146,27 +21781,27 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn Engineering — OpenID Connect Authentication for Sign In with LinkedIn V2</t>
+          <t>AI Agents Authentication: How Autonomous Systems Prove Identity (GitGuardian)</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn's own engineering write-up on adopting OpenID Connect on top of OAuth 2.0, explicitly distinguishing OAuth's delegated-access role from OIDC's identity-assertion role.</t>
+          <t>A GitGuardian engineering article arguing that delegated, short-lived OAuth grants are structurally safer than the static API keys that produced 28.65M secret leaks in 2025.</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/developers/news/featured-updates/openid-connect-authentication</t>
+          <t>https://blog.gitguardian.com/ai-agents-authentication-how-autonomous-systems-prove-identity/</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Industry (LinkedIn Engineering)</t>
+          <t>Industry blog (GitGuardian)</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Real-world example from LinkedIn explaining why they layered OIDC over an existing OAuth 2.0 delegated-access stack.</t>
+          <t>Useful for the 'why delegated authorization &gt; shared secrets' business case with concrete 2025 incident data.</t>
         </is>
       </c>
     </row>
@@ -19176,27 +21811,27 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Rich Authorization Requests (RAR) — Authlete Knowledge Base</t>
+          <t>User-Managed Access (UMA) 2.0 Comprehensive Guide (SSOJet, Feb 2026)</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>A vendor knowledge-base article giving worked examples of RAR's authorization_details object, including locations, actions, datatypes, and identifier fields with their Authlete bindings.</t>
+          <t>A 2026 industry guide reframing UMA 2.0 for current CIAM contexts, covering resource-set registration, permission tickets, requesting-party tokens (RPTs), and policy externalization gains.</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>https://www.authlete.com/kb/oauth-and-openid-connect/authorization-requests/rich-authorization-requests/</t>
+          <t>https://ssojet.com/blog/user-managed-access-uma-2-0-comprehensive-guide</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Vendor documentation (Authlete)</t>
+          <t>Industry blog (SSOJet)</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Authlete is one of the few certified FAPI 2.0 + RAR implementations; useful reference for concrete request bodies.</t>
+          <t>Cites Kantara analysis showing centralized-policy moves can cut authorization code 80% — useful pitch material.</t>
         </is>
       </c>
     </row>
@@ -19206,27 +21841,27 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>An Introduction to Authorization Exchange (AuthZEN) — Curity</t>
+          <t>Decentralized Identity and Verifiable Credentials: The Enterprise Playbook 2026</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>A vendor explainer comparing externalized-authorization patterns (OPA, Cedar, XACML, Zanzibar) and showing how AuthZEN's API normalizes the PDP/PEP wire protocol across them.</t>
+          <t>An enterprise-oriented guide explaining how W3C VCs, DIDs, and OpenID4VC enable the issuer-holder-verifier delegation model for digital credentials and EUDI Wallet acceptance.</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>https://curity.io/resources/learn/authzen/</t>
+          <t>https://securityboulevard.com/2026/03/decentralized-identity-and-verifiable-credentials-the-enterprise-playbook-2026/</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Vendor blog (Curity)</t>
+          <t>Industry article (Security Boulevard)</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Curity is a member of the AuthZEN WG; positions AuthZEN as 'OpenID Connect for authorization' which has become the common framing.</t>
+          <t>Critical 2027 EU compliance dates: banks, telecom, healthcare, and very-large platforms must accept EUDI Wallet.</t>
         </is>
       </c>
     </row>
@@ -19236,27 +21871,27 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>ACLX — AI Output Governance (Proprietary)</t>
+          <t>OAuth 2.0 &amp; OpenID Connect: The Complete Guide to What the Standards Actually Say (Patil, Medium)</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>A proprietary enforcement layer that intercepts AI-generated content between inference and delivery, evaluating it against OPA/Cedar policies, identity context, and a three-phase sensitivity detection stack: deterministic regex rules → ontology-based compilation-risk scoring → semantic LLM evaluation for novel synthesis. Four enforcement outcomes: ALLOW, REDACT, BLOCK, or ESCALATE to human review. Treats agents as first-class principals evaluated at the output boundary regardless of whether a session or IDP exists.</t>
+          <t>A practitioner-friendly synthesis covering OAuth 2.0 core, the OAuth 2.1 draft, RFC 9068 JWT access tokens, RFC 8252 native apps, and RFC 8628 device authorization.</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>https://aclx.ai/</t>
+          <t>https://mrutyunjaypatil.medium.com/oauth-2-0-openid-connect-the-complete-guide-to-what-the-standards-actually-say-e92f040a4251</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Proprietary product</t>
+          <t>Industry blog (Medium)</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>No published specification. Identifies a gap the corpus standards map does not yet cover: identity (OIDC/SCIM/SPIFFE), signals (CAEP/SSF), policy (OAuth/AuthZEN/OPA), and enforcement (ZTA/RATS/SCITT) all have standards, but output evaluation — governing what the AI synthesizes rather than what the user was authorized to ask — has none. The synthesis-detection layer (AI compiling across individually-authorized sources to produce content crossing a higher sensitivity boundary) is a novel problem the corpus's existing standards do not address.</t>
+          <t>Good handoff document for engineers new to the area; cites the current standards rather than legacy patterns.</t>
         </is>
       </c>
     </row>
@@ -19266,27 +21901,27 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>McGuinness — Kerberos Won Because Nobody Had to Implement It</t>
+          <t>LinkedIn Engineering — OpenID Connect Authentication for Sign In with LinkedIn V2</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>The question worth asking about AAuth is not only whether the protocol is good. Kerberos won because of everything around the protocol: SSPI and GSS-API hid the mechanism from application developers, the LSA owned keys and ticket lifecycle, machine accounts existed as a side effect of domain join, Active Directory shipped the KDC by default, and SPNEGO made rollout incremental.</t>
+          <t>LinkedIn's own engineering write-up on adopting OpenID Connect on top of OAuth 2.0, explicitly distinguishing OAuth's delegated-access role from OIDC's identity-assertion role.</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>https://notes.karlmcguinness.com/notes/kerberos-won-because-nobody-had-to-implement-it/</t>
+          <t>https://www.linkedin.com/developers/news/featured-updates/openid-connect-authentication</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>Industry blog (Independent)</t>
+          <t>Industry (LinkedIn Engineering)</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineSt